--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -10,19 +10,19 @@
     <sheet name="作品数据" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：—。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-07-25T07:38:52+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -68,13 +68,44 @@
   </si>
   <si>
     <t>达标日期列表</t>
+  </si>
+  <si>
+    <t>穿越自带炼妖壶：桀桀，顷刻炼化</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>领主：我在苦痛世界，养成少女</t>
+  </si>
+  <si>
+    <t>早知道不这么玩了！</t>
+  </si>
+  <si>
+    <t>异世界：我的人生开了挂！</t>
+  </si>
+  <si>
+    <t>什么！我们家居然是邪神后裔？</t>
+  </si>
+  <si>
+    <t>西幻：我有一本冒险者指南</t>
+  </si>
+  <si>
+    <t>从零开始的黑暗童话世界</t>
+  </si>
+  <si>
+    <t>穿越异世界，我能看见经验条</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +136,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -126,7 +165,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -149,11 +188,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -163,6 +217,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -561,12 +627,286 @@
         <v>16</v>
       </c>
     </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5">
+        <v>81.3</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7">
+        <v>169000</v>
+      </c>
+      <c r="G5" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3</v>
+      </c>
+      <c r="I5" s="7">
+        <v>19000</v>
+      </c>
+      <c r="J5" s="5">
+        <v>58.5</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="7">
+        <v>433000</v>
+      </c>
+      <c r="G6" s="7">
+        <v>5000</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3</v>
+      </c>
+      <c r="I6" s="7">
+        <v>6000</v>
+      </c>
+      <c r="J6" s="5">
+        <v>54.2</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="7">
+        <v>191000</v>
+      </c>
+      <c r="G7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="7">
+        <v>3</v>
+      </c>
+      <c r="I7" s="7">
+        <v>500</v>
+      </c>
+      <c r="J7" s="5">
+        <v>50</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="7">
+        <v>179000</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>3</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>49.1</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5">
+        <v>72.2</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="7">
+        <v>152000</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2000</v>
+      </c>
+      <c r="H9" s="7">
+        <v>3</v>
+      </c>
+      <c r="I9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J9" s="5">
+        <v>49</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5">
+        <v>71.3</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="7">
+        <v>149000</v>
+      </c>
+      <c r="G10" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H10" s="7">
+        <v>3</v>
+      </c>
+      <c r="I10" s="7">
+        <v>2000</v>
+      </c>
+      <c r="J10" s="5">
+        <v>48.7</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="7">
+        <v>124000</v>
+      </c>
+      <c r="G11" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H11" s="7">
+        <v>3</v>
+      </c>
+      <c r="I11" s="7">
+        <v>3500</v>
+      </c>
+      <c r="J11" s="5">
+        <v>47.3</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="7">
+        <v>126000</v>
+      </c>
+      <c r="G12" s="7">
+        <v>2000</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3</v>
+      </c>
+      <c r="I12" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J12" s="5">
+        <v>46.2</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O5"/>
+  <autoFilter ref="A4:O12"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1"/>
+    <hyperlink ref="E6" r:id="rId2"/>
+    <hyperlink ref="E7" r:id="rId3"/>
+    <hyperlink ref="E8" r:id="rId4"/>
+    <hyperlink ref="E9" r:id="rId5"/>
+    <hyperlink ref="E10" r:id="rId6"/>
+    <hyperlink ref="E11" r:id="rId7"/>
+    <hyperlink ref="E12" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -10,19 +10,19 @@
     <sheet name="作品数据" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="68">
   <si>
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-07-25T07:38:52+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-07-26T09:05:09+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,31 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>全球死考：刚下刑场你让我去考试</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>重生后，姐姐非要嫁给我</t>
+  </si>
+  <si>
+    <t>什么叫高考满分，但人失踪了？</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>买卖词条，打造非凡俱乐部</t>
+  </si>
+  <si>
+    <t>桃花美人村</t>
+  </si>
+  <si>
+    <t>死对头证道成仙了，怎么办？！</t>
+  </si>
+  <si>
+    <t>改变人生：从千禧年开始</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>全民县令：我看广告无限刷资源</t>
+  </si>
+  <si>
+    <t>让你当众写检讨，你作洛神赋？</t>
+  </si>
+  <si>
+    <t>穿到女频，整顿满城霸总</t>
+  </si>
+  <si>
+    <t>封印神源百万年，悟性每天翻倍</t>
+  </si>
+  <si>
+    <t>刚上大学，睡出了个绝美教授老婆</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
+  </si>
+  <si>
+    <t>四合院，哈军工副院，部下李云龙</t>
+  </si>
+  <si>
+    <t>穿越保安，有个比我大三岁的老婆</t>
+  </si>
+  <si>
+    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>从变身少女开始斩妖除魔</t>
+  </si>
+  <si>
+    <t>四合院：开局保卫处，海中叫我叔</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>崩铁，穿越成怪兽，被爻光买回家</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>高武：废材逆袭？可我绝世天骄啊</t>
+  </si>
+  <si>
+    <t>领主：开局1金商店购买大车圣女</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>重生后，成了妹妹的专属爱物</t>
+  </si>
+  <si>
+    <t>徒弟有系统？我反手给他们关掉</t>
+  </si>
+  <si>
+    <t>希腊神话：从成为微风之神开始</t>
+  </si>
+  <si>
+    <t>左手E总右手E哥，假少爷又如何</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>拿下小秘书，极品老板娘沦陷了！</t>
+  </si>
+  <si>
+    <t>我才三岁，怎么会是灭世级灾厄</t>
+  </si>
+  <si>
+    <t>倚天：贫道张三丰</t>
+  </si>
+  <si>
+    <t>一人之下：我非魔修，再说杀你哦</t>
+  </si>
+  <si>
+    <t>诸界归一，还好我早已成仙</t>
+  </si>
+  <si>
+    <t>绝密使命</t>
+  </si>
+  <si>
+    <t>我在斩神当神秘，还是白发小萝莉</t>
+  </si>
+  <si>
     <t>穿越自带炼妖壶：桀桀，顷刻炼化</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>领主：我在苦痛世界，养成少女</t>
-  </si>
-  <si>
-    <t>早知道不这么玩了！</t>
-  </si>
-  <si>
-    <t>异世界：我的人生开了挂！</t>
-  </si>
-  <si>
-    <t>什么！我们家居然是邪神后裔？</t>
-  </si>
-  <si>
-    <t>西幻：我有一本冒险者指南</t>
-  </si>
-  <si>
-    <t>从零开始的黑暗童话世界</t>
-  </si>
-  <si>
-    <t>穿越异世界，我能看见经验条</t>
+    <t>僵尸世界：开局拜师雷电法王</t>
+  </si>
+  <si>
+    <t>仙界覆灭后，我收留了陨落仙子</t>
+  </si>
+  <si>
+    <t>领主：开局捡个落魄圣域老骑士</t>
+  </si>
+  <si>
+    <t>我的东莞梦：媚姐</t>
   </si>
 </sst>
 </file>
@@ -524,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -633,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>81.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>169000</v>
+        <v>1087000</v>
       </c>
       <c r="G5" s="7">
-        <v>19000</v>
+        <v>130000</v>
       </c>
       <c r="H5" s="7">
         <v>3</v>
       </c>
       <c r="I5" s="7">
-        <v>19000</v>
+        <v>151000</v>
       </c>
       <c r="J5" s="5">
-        <v>58.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -666,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>79.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>433000</v>
+        <v>468000</v>
       </c>
       <c r="G6" s="7">
-        <v>5000</v>
+        <v>78000</v>
       </c>
       <c r="H6" s="7">
         <v>3</v>
       </c>
       <c r="I6" s="7">
-        <v>6000</v>
+        <v>72000</v>
       </c>
       <c r="J6" s="5">
-        <v>54.2</v>
+        <v>82</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -699,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>74.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>191000</v>
+        <v>526000</v>
       </c>
       <c r="G7" s="7">
-        <v>1000</v>
+        <v>64000</v>
       </c>
       <c r="H7" s="7">
         <v>3</v>
       </c>
       <c r="I7" s="7">
-        <v>500</v>
+        <v>64500</v>
       </c>
       <c r="J7" s="5">
-        <v>50</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -732,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>72.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>179000</v>
+        <v>636000</v>
       </c>
       <c r="G8" s="7">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="H8" s="7">
         <v>3</v>
       </c>
       <c r="I8" s="7">
-        <v>0</v>
+        <v>53500</v>
       </c>
       <c r="J8" s="5">
-        <v>49.1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -765,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>72.2</v>
+        <v>99.2</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>152000</v>
+        <v>223000</v>
       </c>
       <c r="G9" s="7">
-        <v>2000</v>
+        <v>59000</v>
       </c>
       <c r="H9" s="7">
         <v>3</v>
       </c>
       <c r="I9" s="7">
-        <v>1000</v>
+        <v>53000</v>
       </c>
       <c r="J9" s="5">
-        <v>49</v>
+        <v>76.8</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -798,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>71.3</v>
+        <v>84.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>149000</v>
+        <v>2457000</v>
       </c>
       <c r="G10" s="7">
-        <v>3000</v>
+        <v>68000</v>
       </c>
       <c r="H10" s="7">
         <v>3</v>
       </c>
       <c r="I10" s="7">
-        <v>2000</v>
+        <v>76000</v>
       </c>
       <c r="J10" s="5">
-        <v>48.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -831,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>68.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>124000</v>
+        <v>373000</v>
       </c>
       <c r="G11" s="7">
-        <v>7000</v>
+        <v>42000</v>
       </c>
       <c r="H11" s="7">
         <v>3</v>
       </c>
       <c r="I11" s="7">
-        <v>3500</v>
+        <v>41000</v>
       </c>
       <c r="J11" s="5">
-        <v>47.3</v>
+        <v>71.3</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -864,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>67.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>126000</v>
+        <v>356000</v>
       </c>
       <c r="G12" s="7">
-        <v>2000</v>
+        <v>127000</v>
       </c>
       <c r="H12" s="7">
         <v>3</v>
       </c>
       <c r="I12" s="7">
-        <v>1000</v>
+        <v>59000</v>
       </c>
       <c r="J12" s="5">
-        <v>46.2</v>
+        <v>70.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -891,8 +1017,1396 @@
       <c r="N12" s="5"/>
       <c r="O12" s="4"/>
     </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="7">
+        <v>253000</v>
+      </c>
+      <c r="G13" s="7">
+        <v>21000</v>
+      </c>
+      <c r="H13" s="7">
+        <v>3</v>
+      </c>
+      <c r="I13" s="7">
+        <v>28500</v>
+      </c>
+      <c r="J13" s="5">
+        <v>69</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5">
+        <v>96.2</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="7">
+        <v>244000</v>
+      </c>
+      <c r="G14" s="7">
+        <v>24000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>3</v>
+      </c>
+      <c r="I14" s="7">
+        <v>27000</v>
+      </c>
+      <c r="J14" s="5">
+        <v>68.7</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="7">
+        <v>511000</v>
+      </c>
+      <c r="G15" s="7">
+        <v>35000</v>
+      </c>
+      <c r="H15" s="7">
+        <v>3</v>
+      </c>
+      <c r="I15" s="7">
+        <v>27500</v>
+      </c>
+      <c r="J15" s="5">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="7">
+        <v>210000</v>
+      </c>
+      <c r="G16" s="7">
+        <v>26000</v>
+      </c>
+      <c r="H16" s="7">
+        <v>3</v>
+      </c>
+      <c r="I16" s="7">
+        <v>19000</v>
+      </c>
+      <c r="J16" s="5">
+        <v>68.3</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5">
+        <v>92</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="7">
+        <v>370000</v>
+      </c>
+      <c r="G17" s="7">
+        <v>31000</v>
+      </c>
+      <c r="H17" s="7">
+        <v>3</v>
+      </c>
+      <c r="I17" s="7">
+        <v>33500</v>
+      </c>
+      <c r="J17" s="5">
+        <v>68</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="7">
+        <v>920000</v>
+      </c>
+      <c r="G18" s="7">
+        <v>54000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>3</v>
+      </c>
+      <c r="I18" s="7">
+        <v>50000</v>
+      </c>
+      <c r="J18" s="5">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5">
+        <v>98.2</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="7">
+        <v>146000</v>
+      </c>
+      <c r="G19" s="7">
+        <v>18000</v>
+      </c>
+      <c r="H19" s="7">
+        <v>3</v>
+      </c>
+      <c r="I19" s="7">
+        <v>18000</v>
+      </c>
+      <c r="J19" s="5">
+        <v>67.5</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="7">
+        <v>424000</v>
+      </c>
+      <c r="G20" s="7">
+        <v>29000</v>
+      </c>
+      <c r="H20" s="7">
+        <v>3</v>
+      </c>
+      <c r="I20" s="7">
+        <v>25500</v>
+      </c>
+      <c r="J20" s="5">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5">
+        <v>97.8</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="7">
+        <v>151000</v>
+      </c>
+      <c r="G21" s="7">
+        <v>18000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>3</v>
+      </c>
+      <c r="I21" s="7">
+        <v>17500</v>
+      </c>
+      <c r="J21" s="5">
+        <v>67.2</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="7">
+        <v>372000</v>
+      </c>
+      <c r="G22" s="7">
+        <v>26000</v>
+      </c>
+      <c r="H22" s="7">
+        <v>3</v>
+      </c>
+      <c r="I22" s="7">
+        <v>22000</v>
+      </c>
+      <c r="J22" s="5">
+        <v>67</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5">
+        <v>95.3</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="7">
+        <v>269000</v>
+      </c>
+      <c r="G23" s="7">
+        <v>24000</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>22500</v>
+      </c>
+      <c r="J23" s="5">
+        <v>67</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5">
+        <v>87.3</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="7">
+        <v>287000</v>
+      </c>
+      <c r="G24" s="7">
+        <v>62000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>3</v>
+      </c>
+      <c r="I24" s="7">
+        <v>39000</v>
+      </c>
+      <c r="J24" s="5">
+        <v>66.8</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5">
+        <v>95.3</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="7">
+        <v>114000</v>
+      </c>
+      <c r="G25" s="7">
+        <v>21000</v>
+      </c>
+      <c r="H25" s="7">
+        <v>3</v>
+      </c>
+      <c r="I25" s="7">
+        <v>21500</v>
+      </c>
+      <c r="J25" s="5">
+        <v>66.8</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="7">
+        <v>279000</v>
+      </c>
+      <c r="G26" s="7">
+        <v>54000</v>
+      </c>
+      <c r="H26" s="7">
+        <v>3</v>
+      </c>
+      <c r="I26" s="7">
+        <v>58000</v>
+      </c>
+      <c r="J26" s="5">
+        <v>66.5</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5">
+        <v>82.5</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="7">
+        <v>885000</v>
+      </c>
+      <c r="G27" s="7">
+        <v>44000</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3</v>
+      </c>
+      <c r="I27" s="7">
+        <v>47500</v>
+      </c>
+      <c r="J27" s="5">
+        <v>66.2</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5">
+        <v>86.3</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="7">
+        <v>440000</v>
+      </c>
+      <c r="G28" s="7">
+        <v>36000</v>
+      </c>
+      <c r="H28" s="7">
+        <v>3</v>
+      </c>
+      <c r="I28" s="7">
+        <v>38500</v>
+      </c>
+      <c r="J28" s="5">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5">
+        <v>96.5</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="7">
+        <v>170000</v>
+      </c>
+      <c r="G29" s="7">
+        <v>16000</v>
+      </c>
+      <c r="H29" s="7">
+        <v>3</v>
+      </c>
+      <c r="I29" s="7">
+        <v>15500</v>
+      </c>
+      <c r="J29" s="5">
+        <v>66</v>
+      </c>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="7">
+        <v>292000</v>
+      </c>
+      <c r="G30" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H30" s="7">
+        <v>3</v>
+      </c>
+      <c r="I30" s="7">
+        <v>21000</v>
+      </c>
+      <c r="J30" s="5">
+        <v>65.2</v>
+      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5">
+        <v>92.2</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="7">
+        <v>606000</v>
+      </c>
+      <c r="G31" s="7">
+        <v>24000</v>
+      </c>
+      <c r="H31" s="7">
+        <v>3</v>
+      </c>
+      <c r="I31" s="7">
+        <v>19500</v>
+      </c>
+      <c r="J31" s="5">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="7">
+        <v>260000</v>
+      </c>
+      <c r="G32" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H32" s="7">
+        <v>3</v>
+      </c>
+      <c r="I32" s="7">
+        <v>20500</v>
+      </c>
+      <c r="J32" s="5">
+        <v>64.5</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="7">
+        <v>296000</v>
+      </c>
+      <c r="G33" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H33" s="7">
+        <v>3</v>
+      </c>
+      <c r="I33" s="7">
+        <v>17000</v>
+      </c>
+      <c r="J33" s="5">
+        <v>64.2</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="7">
+        <v>149000</v>
+      </c>
+      <c r="G34" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H34" s="7">
+        <v>3</v>
+      </c>
+      <c r="I34" s="7">
+        <v>16500</v>
+      </c>
+      <c r="J34" s="5">
+        <v>64.2</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="7">
+        <v>245000</v>
+      </c>
+      <c r="G35" s="7">
+        <v>16000</v>
+      </c>
+      <c r="H35" s="7">
+        <v>3</v>
+      </c>
+      <c r="I35" s="7">
+        <v>14500</v>
+      </c>
+      <c r="J35" s="5">
+        <v>63.8</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5">
+        <v>93.7</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="7">
+        <v>133000</v>
+      </c>
+      <c r="G36" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H36" s="7">
+        <v>3</v>
+      </c>
+      <c r="I36" s="7">
+        <v>13000</v>
+      </c>
+      <c r="J36" s="5">
+        <v>63.8</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5">
+        <v>87.5</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="7">
+        <v>275000</v>
+      </c>
+      <c r="G37" s="7">
+        <v>20000</v>
+      </c>
+      <c r="H37" s="7">
+        <v>3</v>
+      </c>
+      <c r="I37" s="7">
+        <v>26000</v>
+      </c>
+      <c r="J37" s="5">
+        <v>63.6</v>
+      </c>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5">
+        <v>92.3</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="7">
+        <v>266000</v>
+      </c>
+      <c r="G38" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H38" s="7">
+        <v>3</v>
+      </c>
+      <c r="I38" s="7">
+        <v>15000</v>
+      </c>
+      <c r="J38" s="5">
+        <v>63.5</v>
+      </c>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="5">
+        <v>9</v>
+      </c>
+      <c r="C39" s="5">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="7">
+        <v>102000</v>
+      </c>
+      <c r="G39" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H39" s="7">
+        <v>3</v>
+      </c>
+      <c r="I39" s="7">
+        <v>12500</v>
+      </c>
+      <c r="J39" s="5">
+        <v>63.5</v>
+      </c>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="7">
+        <v>191000</v>
+      </c>
+      <c r="G40" s="7">
+        <v>16000</v>
+      </c>
+      <c r="H40" s="7">
+        <v>3</v>
+      </c>
+      <c r="I40" s="7">
+        <v>18500</v>
+      </c>
+      <c r="J40" s="5">
+        <v>63.4</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="7">
+        <v>159000</v>
+      </c>
+      <c r="G41" s="7">
+        <v>13000</v>
+      </c>
+      <c r="H41" s="7">
+        <v>3</v>
+      </c>
+      <c r="I41" s="7">
+        <v>9500</v>
+      </c>
+      <c r="J41" s="5">
+        <v>63.1</v>
+      </c>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5">
+        <v>90.2</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="7">
+        <v>208000</v>
+      </c>
+      <c r="G42" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H42" s="7">
+        <v>3</v>
+      </c>
+      <c r="I42" s="7">
+        <v>16000</v>
+      </c>
+      <c r="J42" s="5">
+        <v>62.6</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="7">
+        <v>155000</v>
+      </c>
+      <c r="G43" s="7">
+        <v>13000</v>
+      </c>
+      <c r="H43" s="7">
+        <v>3</v>
+      </c>
+      <c r="I43" s="7">
+        <v>19500</v>
+      </c>
+      <c r="J43" s="5">
+        <v>62.5</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5">
+        <v>87.5</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="7">
+        <v>145000</v>
+      </c>
+      <c r="G44" s="7">
+        <v>29000</v>
+      </c>
+      <c r="H44" s="7">
+        <v>3</v>
+      </c>
+      <c r="I44" s="7">
+        <v>20000</v>
+      </c>
+      <c r="J44" s="5">
+        <v>62.1</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5">
+        <v>90.3</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="7">
+        <v>182000</v>
+      </c>
+      <c r="G45" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H45" s="7">
+        <v>3</v>
+      </c>
+      <c r="I45" s="7">
+        <v>13500</v>
+      </c>
+      <c r="J45" s="5">
+        <v>62</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="4"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5">
+        <v>89.2</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="7">
+        <v>204000</v>
+      </c>
+      <c r="G46" s="7">
+        <v>16000</v>
+      </c>
+      <c r="H46" s="7">
+        <v>3</v>
+      </c>
+      <c r="I46" s="7">
+        <v>15000</v>
+      </c>
+      <c r="J46" s="5">
+        <v>61.8</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5">
+        <v>88.3</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="7">
+        <v>221000</v>
+      </c>
+      <c r="G47" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H47" s="7">
+        <v>3</v>
+      </c>
+      <c r="I47" s="7">
+        <v>16500</v>
+      </c>
+      <c r="J47" s="5">
+        <v>61.7</v>
+      </c>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="7">
+        <v>190000</v>
+      </c>
+      <c r="G48" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H48" s="7">
+        <v>3</v>
+      </c>
+      <c r="I48" s="7">
+        <v>12000</v>
+      </c>
+      <c r="J48" s="5">
+        <v>61.7</v>
+      </c>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5">
+        <v>90.8</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="7">
+        <v>166000</v>
+      </c>
+      <c r="G49" s="7">
+        <v>18000</v>
+      </c>
+      <c r="H49" s="7">
+        <v>3</v>
+      </c>
+      <c r="I49" s="7">
+        <v>11000</v>
+      </c>
+      <c r="J49" s="5">
+        <v>61.7</v>
+      </c>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="4"/>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5">
+        <v>81.2</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="7">
+        <v>187000</v>
+      </c>
+      <c r="G50" s="7">
+        <v>18000</v>
+      </c>
+      <c r="H50" s="7">
+        <v>4</v>
+      </c>
+      <c r="I50" s="7">
+        <v>18667</v>
+      </c>
+      <c r="J50" s="5">
+        <v>61.3</v>
+      </c>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="4"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5">
+        <v>79.5</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="7">
+        <v>253000</v>
+      </c>
+      <c r="G51" s="7">
+        <v>72000</v>
+      </c>
+      <c r="H51" s="7">
+        <v>3</v>
+      </c>
+      <c r="I51" s="7">
+        <v>33500</v>
+      </c>
+      <c r="J51" s="5">
+        <v>61.1</v>
+      </c>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="4"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5">
+        <v>89.3</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="7">
+        <v>309000</v>
+      </c>
+      <c r="G52" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H52" s="7">
+        <v>3</v>
+      </c>
+      <c r="I52" s="7">
+        <v>11500</v>
+      </c>
+      <c r="J52" s="5">
+        <v>61</v>
+      </c>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="4"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="7">
+        <v>160000</v>
+      </c>
+      <c r="G53" s="7">
+        <v>6000</v>
+      </c>
+      <c r="H53" s="7">
+        <v>3</v>
+      </c>
+      <c r="I53" s="7">
+        <v>12000</v>
+      </c>
+      <c r="J53" s="5">
+        <v>61</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="4"/>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="7">
+        <v>376000</v>
+      </c>
+      <c r="G54" s="7">
+        <v>40000</v>
+      </c>
+      <c r="H54" s="7">
+        <v>3</v>
+      </c>
+      <c r="I54" s="7">
+        <v>33500</v>
+      </c>
+      <c r="J54" s="5">
+        <v>60.8</v>
+      </c>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O12"/>
+  <autoFilter ref="A4:O54"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -906,6 +2420,48 @@
     <hyperlink ref="E10" r:id="rId6"/>
     <hyperlink ref="E11" r:id="rId7"/>
     <hyperlink ref="E12" r:id="rId8"/>
+    <hyperlink ref="E13" r:id="rId9"/>
+    <hyperlink ref="E14" r:id="rId10"/>
+    <hyperlink ref="E15" r:id="rId11"/>
+    <hyperlink ref="E16" r:id="rId12"/>
+    <hyperlink ref="E17" r:id="rId13"/>
+    <hyperlink ref="E18" r:id="rId14"/>
+    <hyperlink ref="E19" r:id="rId15"/>
+    <hyperlink ref="E20" r:id="rId16"/>
+    <hyperlink ref="E21" r:id="rId17"/>
+    <hyperlink ref="E22" r:id="rId18"/>
+    <hyperlink ref="E23" r:id="rId19"/>
+    <hyperlink ref="E24" r:id="rId20"/>
+    <hyperlink ref="E25" r:id="rId21"/>
+    <hyperlink ref="E26" r:id="rId22"/>
+    <hyperlink ref="E27" r:id="rId23"/>
+    <hyperlink ref="E28" r:id="rId24"/>
+    <hyperlink ref="E29" r:id="rId25"/>
+    <hyperlink ref="E30" r:id="rId26"/>
+    <hyperlink ref="E31" r:id="rId27"/>
+    <hyperlink ref="E32" r:id="rId28"/>
+    <hyperlink ref="E33" r:id="rId29"/>
+    <hyperlink ref="E34" r:id="rId30"/>
+    <hyperlink ref="E35" r:id="rId31"/>
+    <hyperlink ref="E36" r:id="rId32"/>
+    <hyperlink ref="E37" r:id="rId33"/>
+    <hyperlink ref="E38" r:id="rId34"/>
+    <hyperlink ref="E39" r:id="rId35"/>
+    <hyperlink ref="E40" r:id="rId36"/>
+    <hyperlink ref="E41" r:id="rId37"/>
+    <hyperlink ref="E42" r:id="rId38"/>
+    <hyperlink ref="E43" r:id="rId39"/>
+    <hyperlink ref="E44" r:id="rId40"/>
+    <hyperlink ref="E45" r:id="rId41"/>
+    <hyperlink ref="E46" r:id="rId42"/>
+    <hyperlink ref="E47" r:id="rId43"/>
+    <hyperlink ref="E48" r:id="rId44"/>
+    <hyperlink ref="E49" r:id="rId45"/>
+    <hyperlink ref="E50" r:id="rId46"/>
+    <hyperlink ref="E51" r:id="rId47"/>
+    <hyperlink ref="E52" r:id="rId48"/>
+    <hyperlink ref="E53" r:id="rId49"/>
+    <hyperlink ref="E54" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-07-26T09:05:09+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-07-27T12:44:29+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>诸神愚戏</t>
+  </si>
+  <si>
     <t>全球死考：刚下刑场你让我去考试</t>
   </si>
   <si>
-    <t>打开作品</t>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
     <t>重生后，姐姐非要嫁给我</t>
   </si>
   <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
     <t>什么叫高考满分，但人失踪了？</t>
   </si>
   <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>死对头证道成仙了，怎么办？！</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>领主：开局1金商店购买大车圣女</t>
+  </si>
+  <si>
+    <t>封印神源百万年，悟性每天翻倍</t>
+  </si>
+  <si>
+    <t>四合院，哈军工副院，部下李云龙</t>
+  </si>
+  <si>
+    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+  </si>
+  <si>
+    <t>桃花美人村</t>
+  </si>
+  <si>
+    <t>买卖词条，打造非凡俱乐部</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
+  </si>
+  <si>
+    <t>伪人降临！我是全场唯一预言家</t>
+  </si>
+  <si>
+    <t>僵尸世界：开局拜师雷电法王</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>中亿万大奖，我选择隐瞒试探人心</t>
+  </si>
+  <si>
+    <t>全民县令：我看广告无限刷资源</t>
+  </si>
+  <si>
+    <t>捡来的夫人是乱世魔头</t>
+  </si>
+  <si>
+    <t>崩铁，穿越成怪兽，被爻光买回家</t>
+  </si>
+  <si>
+    <t>末法时代出飞僵，可我是石坚啊</t>
+  </si>
+  <si>
+    <t>改变人生：从千禧年开始</t>
+  </si>
+  <si>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>我才三岁，怎么会是灭世级灾厄</t>
+  </si>
+  <si>
+    <t>四合院：开局保卫处，海中叫我叔</t>
+  </si>
+  <si>
+    <t>名义：调任汉东搞经济，制衡全局</t>
+  </si>
+  <si>
+    <t>绝密使命</t>
+  </si>
+  <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>希腊神话：从成为微风之神开始</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>穿到女频，整顿满城霸总</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>高武：废材逆袭？可我绝世天骄啊</t>
+  </si>
+  <si>
+    <t>我开启的宝箱品质永远加3</t>
+  </si>
+  <si>
+    <t>率土之滨：什么叫军费百倍到账？</t>
+  </si>
+  <si>
+    <t>穿越保安，有个比我大三岁的老婆</t>
   </si>
   <si>
     <t>这个游戏不对劲，我挖矿成神！</t>
   </si>
   <si>
-    <t>买卖词条，打造非凡俱乐部</t>
-  </si>
-  <si>
-    <t>桃花美人村</t>
-  </si>
-  <si>
-    <t>死对头证道成仙了，怎么办？！</t>
-  </si>
-  <si>
-    <t>改变人生：从千禧年开始</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>全民县令：我看广告无限刷资源</t>
+    <t>龙骑士先生，龙娘们在追杀你啊！</t>
+  </si>
+  <si>
+    <t>一人之下：我非魔修，再说杀你哦</t>
+  </si>
+  <si>
+    <t>仙界覆灭后，我收留了陨落仙子</t>
+  </si>
+  <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>冒姓琅琊</t>
   </si>
   <si>
     <t>让你当众写检讨，你作洛神赋？</t>
-  </si>
-  <si>
-    <t>穿到女频，整顿满城霸总</t>
-  </si>
-  <si>
-    <t>封印神源百万年，悟性每天翻倍</t>
-  </si>
-  <si>
-    <t>刚上大学，睡出了个绝美教授老婆</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>四合院，哈军工副院，部下李云龙</t>
-  </si>
-  <si>
-    <t>穿越保安，有个比我大三岁的老婆</t>
-  </si>
-  <si>
-    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>从变身少女开始斩妖除魔</t>
-  </si>
-  <si>
-    <t>四合院：开局保卫处，海中叫我叔</t>
-  </si>
-  <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
-  </si>
-  <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>崩铁，穿越成怪兽，被爻光买回家</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>高武：废材逆袭？可我绝世天骄啊</t>
-  </si>
-  <si>
-    <t>领主：开局1金商店购买大车圣女</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>重生后，成了妹妹的专属爱物</t>
-  </si>
-  <si>
-    <t>徒弟有系统？我反手给他们关掉</t>
-  </si>
-  <si>
-    <t>希腊神话：从成为微风之神开始</t>
-  </si>
-  <si>
-    <t>左手E总右手E哥，假少爷又如何</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>公安局长之扫黑风暴</t>
-  </si>
-  <si>
-    <t>拿下小秘书，极品老板娘沦陷了！</t>
-  </si>
-  <si>
-    <t>我才三岁，怎么会是灭世级灾厄</t>
-  </si>
-  <si>
-    <t>倚天：贫道张三丰</t>
-  </si>
-  <si>
-    <t>一人之下：我非魔修，再说杀你哦</t>
-  </si>
-  <si>
-    <t>诸界归一，还好我早已成仙</t>
-  </si>
-  <si>
-    <t>绝密使命</t>
-  </si>
-  <si>
-    <t>我在斩神当神秘，还是白发小萝莉</t>
-  </si>
-  <si>
-    <t>穿越自带炼妖壶：桀桀，顷刻炼化</t>
-  </si>
-  <si>
-    <t>僵尸世界：开局拜师雷电法王</t>
-  </si>
-  <si>
-    <t>仙界覆灭后，我收留了陨落仙子</t>
-  </si>
-  <si>
-    <t>领主：开局捡个落魄圣域老骑士</t>
-  </si>
-  <si>
-    <t>我的东莞梦：媚姐</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>92.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1087000</v>
+        <v>389000</v>
       </c>
       <c r="G5" s="7">
-        <v>130000</v>
+        <v>85000</v>
       </c>
       <c r="H5" s="7">
         <v>3</v>
       </c>
       <c r="I5" s="7">
-        <v>151000</v>
+        <v>91000</v>
       </c>
       <c r="J5" s="5">
-        <v>85.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>468000</v>
+        <v>1560000</v>
       </c>
       <c r="G6" s="7">
-        <v>78000</v>
+        <v>279000</v>
       </c>
       <c r="H6" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="7">
-        <v>72000</v>
+        <v>89667</v>
       </c>
       <c r="J6" s="5">
-        <v>82</v>
+        <v>85.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>87.8</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>526000</v>
+        <v>1177000</v>
       </c>
       <c r="G7" s="7">
-        <v>64000</v>
+        <v>90000</v>
       </c>
       <c r="H7" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" s="7">
-        <v>64500</v>
+        <v>130667</v>
       </c>
       <c r="J7" s="5">
-        <v>80.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>636000</v>
+        <v>738000</v>
       </c>
       <c r="G8" s="7">
-        <v>58000</v>
+        <v>102000</v>
       </c>
       <c r="H8" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
-        <v>53500</v>
+        <v>69667</v>
       </c>
       <c r="J8" s="5">
-        <v>76.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.2</v>
+        <v>95.8</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>223000</v>
+        <v>502000</v>
       </c>
       <c r="G9" s="7">
-        <v>59000</v>
+        <v>34000</v>
       </c>
       <c r="H9" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7">
-        <v>53000</v>
+        <v>59333</v>
       </c>
       <c r="J9" s="5">
-        <v>76.8</v>
+        <v>79.5</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>84.8</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>2457000</v>
+        <v>260000</v>
       </c>
       <c r="G10" s="7">
-        <v>68000</v>
+        <v>37000</v>
       </c>
       <c r="H10" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7">
-        <v>76000</v>
+        <v>47667</v>
       </c>
       <c r="J10" s="5">
-        <v>74.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>94.7</v>
+        <v>89.5</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>373000</v>
+        <v>371000</v>
       </c>
       <c r="G11" s="7">
-        <v>42000</v>
+        <v>92000</v>
       </c>
       <c r="H11" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="7">
-        <v>41000</v>
+        <v>69333</v>
       </c>
       <c r="J11" s="5">
-        <v>71.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>85.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>356000</v>
+        <v>567000</v>
       </c>
       <c r="G12" s="7">
-        <v>127000</v>
+        <v>41000</v>
       </c>
       <c r="H12" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="7">
-        <v>59000</v>
+        <v>56667</v>
       </c>
       <c r="J12" s="5">
-        <v>70.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>96.09999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>253000</v>
+        <v>676000</v>
       </c>
       <c r="G13" s="7">
-        <v>21000</v>
+        <v>70000</v>
       </c>
       <c r="H13" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="7">
-        <v>28500</v>
+        <v>36333</v>
       </c>
       <c r="J13" s="5">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>244000</v>
+        <v>286000</v>
       </c>
       <c r="G14" s="7">
-        <v>24000</v>
+        <v>33000</v>
       </c>
       <c r="H14" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="7">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="J14" s="5">
-        <v>68.7</v>
+        <v>74.5</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>511000</v>
+        <v>223000</v>
       </c>
       <c r="G15" s="7">
-        <v>35000</v>
+        <v>53000</v>
       </c>
       <c r="H15" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7">
-        <v>27500</v>
+        <v>28000</v>
       </c>
       <c r="J15" s="5">
-        <v>68.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>210000</v>
+        <v>295000</v>
       </c>
       <c r="G16" s="7">
-        <v>26000</v>
+        <v>50000</v>
       </c>
       <c r="H16" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7">
-        <v>19000</v>
+        <v>26333</v>
       </c>
       <c r="J16" s="5">
-        <v>68.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92</v>
+        <v>99.7</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>370000</v>
+        <v>190000</v>
       </c>
       <c r="G17" s="7">
-        <v>31000</v>
+        <v>44000</v>
       </c>
       <c r="H17" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="7">
-        <v>33500</v>
+        <v>26667</v>
       </c>
       <c r="J17" s="5">
-        <v>68</v>
+        <v>73.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>84.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>920000</v>
+        <v>411000</v>
       </c>
       <c r="G18" s="7">
-        <v>54000</v>
+        <v>39000</v>
       </c>
       <c r="H18" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="7">
-        <v>50000</v>
+        <v>27667</v>
       </c>
       <c r="J18" s="5">
-        <v>67.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>98.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>146000</v>
+        <v>358000</v>
       </c>
       <c r="G19" s="7">
-        <v>18000</v>
+        <v>71000</v>
       </c>
       <c r="H19" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
-        <v>18000</v>
+        <v>49667</v>
       </c>
       <c r="J19" s="5">
-        <v>67.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>94.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>424000</v>
+        <v>419000</v>
       </c>
       <c r="G20" s="7">
-        <v>29000</v>
+        <v>63000</v>
       </c>
       <c r="H20" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="7">
-        <v>25500</v>
+        <v>60333</v>
       </c>
       <c r="J20" s="5">
-        <v>67.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>97.8</v>
+        <v>92.7</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>151000</v>
+        <v>409000</v>
       </c>
       <c r="G21" s="7">
-        <v>18000</v>
+        <v>36000</v>
       </c>
       <c r="H21" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="7">
-        <v>17500</v>
+        <v>39333</v>
       </c>
       <c r="J21" s="5">
-        <v>67.2</v>
+        <v>72.8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>95.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>372000</v>
+        <v>187000</v>
       </c>
       <c r="G22" s="7">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="H22" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="7">
-        <v>22000</v>
+        <v>23667</v>
       </c>
       <c r="J22" s="5">
-        <v>67</v>
+        <v>72.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>95.3</v>
+        <v>98.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>269000</v>
+        <v>174000</v>
       </c>
       <c r="G23" s="7">
-        <v>24000</v>
+        <v>59000</v>
       </c>
       <c r="H23" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="7">
-        <v>22500</v>
+        <v>26000</v>
       </c>
       <c r="J23" s="5">
-        <v>67</v>
+        <v>72.8</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>87.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>287000</v>
+        <v>332000</v>
       </c>
       <c r="G24" s="7">
-        <v>62000</v>
+        <v>79000</v>
       </c>
       <c r="H24" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="7">
-        <v>39000</v>
+        <v>48667</v>
       </c>
       <c r="J24" s="5">
-        <v>66.8</v>
+        <v>72.3</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>95.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>114000</v>
+        <v>166000</v>
       </c>
       <c r="G25" s="7">
-        <v>21000</v>
+        <v>52000</v>
       </c>
       <c r="H25" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="7">
-        <v>21500</v>
+        <v>31667</v>
       </c>
       <c r="J25" s="5">
-        <v>66.8</v>
+        <v>71.8</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>78.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>279000</v>
+        <v>543000</v>
       </c>
       <c r="G26" s="7">
-        <v>54000</v>
+        <v>32000</v>
       </c>
       <c r="H26" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26" s="7">
-        <v>58000</v>
+        <v>29000</v>
       </c>
       <c r="J26" s="5">
-        <v>66.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>885000</v>
+        <v>158000</v>
       </c>
       <c r="G27" s="7">
-        <v>44000</v>
+        <v>25000</v>
       </c>
       <c r="H27" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="7">
-        <v>47500</v>
+        <v>17000</v>
       </c>
       <c r="J27" s="5">
-        <v>66.2</v>
+        <v>71.2</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>86.3</v>
+        <v>83.2</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>440000</v>
+        <v>434000</v>
       </c>
       <c r="G28" s="7">
-        <v>36000</v>
+        <v>58000</v>
       </c>
       <c r="H28" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="7">
-        <v>38500</v>
+        <v>51667</v>
       </c>
       <c r="J28" s="5">
-        <v>66.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>96.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>170000</v>
+        <v>234000</v>
       </c>
       <c r="G29" s="7">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="H29" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="7">
-        <v>15500</v>
+        <v>20667</v>
       </c>
       <c r="J29" s="5">
-        <v>66</v>
+        <v>70.7</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>92.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>292000</v>
+        <v>121000</v>
       </c>
       <c r="G30" s="7">
-        <v>19000</v>
+        <v>33000</v>
       </c>
       <c r="H30" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" s="7">
-        <v>21000</v>
+        <v>14667</v>
       </c>
       <c r="J30" s="5">
-        <v>65.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>92.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>606000</v>
+        <v>288000</v>
       </c>
       <c r="G31" s="7">
-        <v>24000</v>
+        <v>28000</v>
       </c>
       <c r="H31" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="7">
-        <v>19500</v>
+        <v>23000</v>
       </c>
       <c r="J31" s="5">
-        <v>64.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>91.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>260000</v>
+        <v>110000</v>
       </c>
       <c r="G32" s="7">
-        <v>17000</v>
+        <v>25000</v>
       </c>
       <c r="H32" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="7">
-        <v>20500</v>
+        <v>14667</v>
       </c>
       <c r="J32" s="5">
-        <v>64.5</v>
+        <v>70.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>296000</v>
+        <v>265000</v>
       </c>
       <c r="G33" s="7">
-        <v>17000</v>
+        <v>21000</v>
       </c>
       <c r="H33" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="7">
-        <v>17000</v>
+        <v>25000</v>
       </c>
       <c r="J33" s="5">
-        <v>64.2</v>
+        <v>70</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>149000</v>
+        <v>317000</v>
       </c>
       <c r="G34" s="7">
-        <v>17000</v>
+        <v>25000</v>
       </c>
       <c r="H34" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="7">
-        <v>16500</v>
+        <v>22333</v>
       </c>
       <c r="J34" s="5">
-        <v>64.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>93.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>245000</v>
+        <v>168000</v>
       </c>
       <c r="G35" s="7">
-        <v>16000</v>
+        <v>23000</v>
       </c>
       <c r="H35" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="7">
-        <v>14500</v>
+        <v>21000</v>
       </c>
       <c r="J35" s="5">
-        <v>63.8</v>
+        <v>69.7</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>93.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>133000</v>
+        <v>481000</v>
       </c>
       <c r="G36" s="7">
-        <v>10000</v>
+        <v>41000</v>
       </c>
       <c r="H36" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="7">
-        <v>13000</v>
+        <v>39333</v>
       </c>
       <c r="J36" s="5">
-        <v>63.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>87.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>275000</v>
+        <v>218000</v>
       </c>
       <c r="G37" s="7">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="H37" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="7">
-        <v>26000</v>
+        <v>13333</v>
       </c>
       <c r="J37" s="5">
-        <v>63.6</v>
+        <v>69.5</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>92.3</v>
+        <v>97</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>266000</v>
+        <v>216000</v>
       </c>
       <c r="G38" s="7">
-        <v>17000</v>
+        <v>26000</v>
       </c>
       <c r="H38" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38" s="7">
-        <v>15000</v>
+        <v>16667</v>
       </c>
       <c r="J38" s="5">
-        <v>63.5</v>
+        <v>69.5</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1879,30 +1879,28 @@
       <c r="A39" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="5">
-        <v>9</v>
-      </c>
+      <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>93.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>102000</v>
+        <v>236000</v>
       </c>
       <c r="G39" s="7">
-        <v>12000</v>
+        <v>28000</v>
       </c>
       <c r="H39" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" s="7">
-        <v>12500</v>
+        <v>20000</v>
       </c>
       <c r="J39" s="5">
-        <v>63.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,28 +1912,30 @@
       <c r="A40" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="5"/>
+      <c r="B40" s="5">
+        <v>9</v>
+      </c>
       <c r="C40" s="5">
-        <v>90.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>191000</v>
+        <v>124000</v>
       </c>
       <c r="G40" s="7">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="H40" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>18500</v>
+        <v>15667</v>
       </c>
       <c r="J40" s="5">
-        <v>63.4</v>
+        <v>69.3</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>94.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>159000</v>
+        <v>321000</v>
       </c>
       <c r="G41" s="7">
-        <v>13000</v>
+        <v>25000</v>
       </c>
       <c r="H41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="7">
-        <v>9500</v>
+        <v>19667</v>
       </c>
       <c r="J41" s="5">
-        <v>63.1</v>
+        <v>69.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>90.2</v>
+        <v>82.8</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>208000</v>
+        <v>954000</v>
       </c>
       <c r="G42" s="7">
-        <v>15000</v>
+        <v>34000</v>
       </c>
       <c r="H42" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="7">
-        <v>16000</v>
+        <v>44667</v>
       </c>
       <c r="J42" s="5">
-        <v>62.6</v>
+        <v>68.7</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>88.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>155000</v>
+        <v>177000</v>
       </c>
       <c r="G43" s="7">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="H43" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="7">
-        <v>19500</v>
+        <v>12333</v>
       </c>
       <c r="J43" s="5">
-        <v>62.5</v>
+        <v>68.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>87.5</v>
+        <v>93.7</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>145000</v>
+        <v>173000</v>
       </c>
       <c r="G44" s="7">
-        <v>29000</v>
+        <v>24000</v>
       </c>
       <c r="H44" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="J44" s="5">
-        <v>62.1</v>
+        <v>68.3</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>90.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>182000</v>
+        <v>220000</v>
       </c>
       <c r="G45" s="7">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="H45" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>13500</v>
+        <v>12333</v>
       </c>
       <c r="J45" s="5">
-        <v>62</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>89.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>204000</v>
+        <v>104000</v>
       </c>
       <c r="G46" s="7">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="H46" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="J46" s="5">
-        <v>61.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>88.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>221000</v>
+        <v>285000</v>
       </c>
       <c r="G47" s="7">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="H47" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="7">
-        <v>16500</v>
+        <v>20333</v>
       </c>
       <c r="J47" s="5">
-        <v>61.7</v>
+        <v>67.5</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>90.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>190000</v>
+        <v>2432000</v>
       </c>
       <c r="G48" s="7">
-        <v>17000</v>
+        <v>-25000</v>
       </c>
       <c r="H48" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48" s="7">
-        <v>12000</v>
+        <v>42333</v>
       </c>
       <c r="J48" s="5">
-        <v>61.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>90.8</v>
+        <v>96.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>166000</v>
+        <v>123000</v>
       </c>
       <c r="G49" s="7">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="H49" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I49" s="7">
-        <v>11000</v>
+        <v>8333</v>
       </c>
       <c r="J49" s="5">
-        <v>61.7</v>
+        <v>67</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>81.2</v>
+        <v>90.7</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>187000</v>
+        <v>219000</v>
       </c>
       <c r="G50" s="7">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="H50" s="7">
         <v>4</v>
       </c>
       <c r="I50" s="7">
-        <v>18667</v>
+        <v>15000</v>
       </c>
       <c r="J50" s="5">
-        <v>61.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>79.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>253000</v>
+        <v>324000</v>
       </c>
       <c r="G51" s="7">
-        <v>72000</v>
+        <v>15000</v>
       </c>
       <c r="H51" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I51" s="7">
-        <v>33500</v>
+        <v>12667</v>
       </c>
       <c r="J51" s="5">
-        <v>61.1</v>
+        <v>65.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>89.3</v>
+        <v>84.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>309000</v>
+        <v>114000</v>
       </c>
       <c r="G52" s="7">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="H52" s="7">
         <v>3</v>
       </c>
       <c r="I52" s="7">
-        <v>11500</v>
+        <v>38500</v>
       </c>
       <c r="J52" s="5">
-        <v>61</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>89.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>160000</v>
+        <v>1112000</v>
       </c>
       <c r="G53" s="7">
-        <v>6000</v>
+        <v>44000</v>
       </c>
       <c r="H53" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" s="7">
-        <v>12000</v>
+        <v>26000</v>
       </c>
       <c r="J53" s="5">
-        <v>61</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>376000</v>
+        <v>381000</v>
       </c>
       <c r="G54" s="7">
-        <v>40000</v>
+        <v>11000</v>
       </c>
       <c r="H54" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>33500</v>
+        <v>26000</v>
       </c>
       <c r="J54" s="5">
-        <v>60.8</v>
+        <v>64.8</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-07-27T12:44:29+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-07-28T10:14:49+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>全球死考：刚下刑场你让我去考试</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>桃花美人村</t>
+  </si>
+  <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>什么叫高考满分，但人失踪了？</t>
+  </si>
+  <si>
+    <t>全民县令：我看广告无限刷资源</t>
+  </si>
+  <si>
+    <t>诸神愚戏</t>
+  </si>
+  <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>重生后，姐姐非要嫁给我</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
     <t>三棍打散兄妹情，我家兄长不当人</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>诸神愚戏</t>
-  </si>
-  <si>
-    <t>全球死考：刚下刑场你让我去考试</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>重生后，姐姐非要嫁给我</t>
-  </si>
-  <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
+    <t>我的东莞梦：媚姐</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
   </si>
   <si>
     <t>穿越乱世：每天一份拼好饭</t>
   </si>
   <si>
-    <t>什么叫高考满分，但人失踪了？</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
+    <t>四合院，哈军工副院，部下李云龙</t>
+  </si>
+  <si>
+    <t>一人之下：我非魔修，再说杀你哦</t>
+  </si>
+  <si>
+    <t>买卖词条，打造非凡俱乐部</t>
+  </si>
+  <si>
+    <t>我开启的宝箱品质永远加3</t>
   </si>
   <si>
     <t>死对头证道成仙了，怎么办？！</t>
   </si>
   <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>领主：开局1金商店购买大车圣女</t>
+  </si>
+  <si>
     <t>领主巫师：从无限魔晶开始求学！</t>
   </si>
   <si>
-    <t>领主：开局1金商店购买大车圣女</t>
+    <t>糟了！我的网恋对象竟是苗疆圣女</t>
+  </si>
+  <si>
+    <t>崩铁，穿越成怪兽，被爻光买回家</t>
+  </si>
+  <si>
+    <t>老婆本地刀枪炮，高考后我认命了</t>
+  </si>
+  <si>
+    <t>穿越自带炼妖壶：桀桀，顷刻炼化</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>改变人生：从千禧年开始</t>
   </si>
   <si>
     <t>封印神源百万年，悟性每天翻倍</t>
   </si>
   <si>
-    <t>四合院，哈军工副院，部下李云龙</t>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>杀一怪叠一毒，我一人毒穿世界！</t>
+  </si>
+  <si>
+    <t>我操作的少女正在成为旧日之主</t>
   </si>
   <si>
     <t>狩猎北大荒：投亲路上遇到狼拦路</t>
   </si>
   <si>
-    <t>桃花美人村</t>
-  </si>
-  <si>
-    <t>买卖词条，打造非凡俱乐部</t>
-  </si>
-  <si>
     <t>都末世了，你们还想当版本T0？</t>
   </si>
   <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>从变身少女开始斩妖除魔</t>
+  </si>
+  <si>
+    <t>穿越保安，有个比我大三岁的老婆</t>
+  </si>
+  <si>
+    <t>霍格沃兹：开局复制满级火盾护身</t>
+  </si>
+  <si>
     <t>伪人降临！我是全场唯一预言家</t>
   </si>
   <si>
-    <t>僵尸世界：开局拜师雷电法王</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
+    <t>仙界覆灭后，我收留了陨落仙子</t>
+  </si>
+  <si>
+    <t>四合院：开局保卫处，海中叫我叔</t>
+  </si>
+  <si>
+    <t>让你当众写检讨，你作洛神赋？</t>
+  </si>
+  <si>
+    <t>名义：调任汉东搞经济，制衡全局</t>
   </si>
   <si>
     <t>编外法医：重案组抢疯了！</t>
   </si>
   <si>
-    <t>中亿万大奖，我选择隐瞒试探人心</t>
-  </si>
-  <si>
-    <t>全民县令：我看广告无限刷资源</t>
-  </si>
-  <si>
-    <t>捡来的夫人是乱世魔头</t>
-  </si>
-  <si>
-    <t>崩铁，穿越成怪兽，被爻光买回家</t>
-  </si>
-  <si>
-    <t>末法时代出飞僵，可我是石坚啊</t>
-  </si>
-  <si>
-    <t>改变人生：从千禧年开始</t>
-  </si>
-  <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
-  </si>
-  <si>
-    <t>我才三岁，怎么会是灭世级灾厄</t>
-  </si>
-  <si>
-    <t>四合院：开局保卫处，海中叫我叔</t>
-  </si>
-  <si>
-    <t>名义：调任汉东搞经济，制衡全局</t>
-  </si>
-  <si>
-    <t>绝密使命</t>
+    <t>穿到女频，整顿满城霸总</t>
+  </si>
+  <si>
+    <t>半山村乡野神医</t>
   </si>
   <si>
     <t>公安局长之扫黑风暴</t>
-  </si>
-  <si>
-    <t>希腊神话：从成为微风之神开始</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>穿到女频，整顿满城霸总</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>高武：废材逆袭？可我绝世天骄啊</t>
-  </si>
-  <si>
-    <t>我开启的宝箱品质永远加3</t>
-  </si>
-  <si>
-    <t>率土之滨：什么叫军费百倍到账？</t>
-  </si>
-  <si>
-    <t>穿越保安，有个比我大三岁的老婆</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>龙骑士先生，龙娘们在追杀你啊！</t>
-  </si>
-  <si>
-    <t>一人之下：我非魔修，再说杀你哦</t>
-  </si>
-  <si>
-    <t>仙界覆灭后，我收留了陨落仙子</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>冒姓琅琊</t>
-  </si>
-  <si>
-    <t>让你当众写检讨，你作洛神赋？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>98.8</v>
+        <v>94.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>389000</v>
+        <v>1346000</v>
       </c>
       <c r="G5" s="7">
-        <v>85000</v>
+        <v>169000</v>
       </c>
       <c r="H5" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" s="7">
-        <v>91000</v>
+        <v>140250</v>
       </c>
       <c r="J5" s="5">
-        <v>86.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1560000</v>
+        <v>754000</v>
       </c>
       <c r="G6" s="7">
-        <v>279000</v>
+        <v>78000</v>
       </c>
       <c r="H6" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="7">
-        <v>89667</v>
+        <v>46750</v>
       </c>
       <c r="J6" s="5">
-        <v>85.8</v>
+        <v>81.7</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>87.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1177000</v>
+        <v>485000</v>
       </c>
       <c r="G7" s="7">
-        <v>90000</v>
+        <v>66000</v>
       </c>
       <c r="H7" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="7">
-        <v>130667</v>
+        <v>61750</v>
       </c>
       <c r="J7" s="5">
-        <v>85.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>738000</v>
+        <v>290000</v>
       </c>
       <c r="G8" s="7">
-        <v>102000</v>
+        <v>30000</v>
       </c>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7">
-        <v>69667</v>
+        <v>43250</v>
       </c>
       <c r="J8" s="5">
-        <v>84.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>95.8</v>
+        <v>89.3</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>502000</v>
+        <v>738000</v>
       </c>
       <c r="G9" s="7">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="H9" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="7">
-        <v>59333</v>
+        <v>52250</v>
       </c>
       <c r="J9" s="5">
-        <v>79.5</v>
+        <v>77.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>260000</v>
+        <v>585000</v>
       </c>
       <c r="G10" s="7">
-        <v>37000</v>
+        <v>18000</v>
       </c>
       <c r="H10" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
-        <v>47667</v>
+        <v>47000</v>
       </c>
       <c r="J10" s="5">
-        <v>78.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>89.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>371000</v>
+        <v>264000</v>
       </c>
       <c r="G11" s="7">
-        <v>92000</v>
+        <v>30000</v>
       </c>
       <c r="H11" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
-        <v>69333</v>
+        <v>23000</v>
       </c>
       <c r="J11" s="5">
-        <v>78.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>94.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>567000</v>
+        <v>1560000</v>
       </c>
       <c r="G12" s="7">
-        <v>41000</v>
+        <v>0</v>
       </c>
       <c r="H12" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>56667</v>
+        <v>67250</v>
       </c>
       <c r="J12" s="5">
-        <v>78.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>676000</v>
+        <v>132000</v>
       </c>
       <c r="G13" s="7">
-        <v>70000</v>
+        <v>18000</v>
       </c>
       <c r="H13" s="7">
         <v>4</v>
       </c>
       <c r="I13" s="7">
-        <v>36333</v>
+        <v>31667</v>
       </c>
       <c r="J13" s="5">
-        <v>76</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>286000</v>
+        <v>502000</v>
       </c>
       <c r="G14" s="7">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="7">
-        <v>30000</v>
+        <v>44500</v>
       </c>
       <c r="J14" s="5">
-        <v>74.5</v>
+        <v>74.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>223000</v>
+        <v>567000</v>
       </c>
       <c r="G15" s="7">
-        <v>53000</v>
+        <v>24000</v>
       </c>
       <c r="H15" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" s="7">
-        <v>28000</v>
+        <v>27750</v>
       </c>
       <c r="J15" s="5">
-        <v>74</v>
+        <v>73.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>100</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>295000</v>
+        <v>389000</v>
       </c>
       <c r="G16" s="7">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="H16" s="7">
         <v>4</v>
       </c>
       <c r="I16" s="7">
-        <v>26333</v>
+        <v>60667</v>
       </c>
       <c r="J16" s="5">
-        <v>73.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>99.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>190000</v>
+        <v>479000</v>
       </c>
       <c r="G17" s="7">
-        <v>44000</v>
+        <v>67000</v>
       </c>
       <c r="H17" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>26667</v>
+        <v>42500</v>
       </c>
       <c r="J17" s="5">
-        <v>73.5</v>
+        <v>71.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>98.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>411000</v>
+        <v>191000</v>
       </c>
       <c r="G18" s="7">
-        <v>39000</v>
+        <v>14000</v>
       </c>
       <c r="H18" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="7">
-        <v>27667</v>
+        <v>12750</v>
       </c>
       <c r="J18" s="5">
-        <v>73.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>88.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>358000</v>
+        <v>251000</v>
       </c>
       <c r="G19" s="7">
-        <v>71000</v>
+        <v>36000</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>49667</v>
+        <v>21000</v>
       </c>
       <c r="J19" s="5">
-        <v>73.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>83.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>419000</v>
+        <v>371000</v>
       </c>
       <c r="G20" s="7">
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="H20" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>60333</v>
+        <v>52000</v>
       </c>
       <c r="J20" s="5">
-        <v>72.8</v>
+        <v>69</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>92.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>409000</v>
+        <v>411000</v>
       </c>
       <c r="G21" s="7">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="H21" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="7">
-        <v>39333</v>
+        <v>20750</v>
       </c>
       <c r="J21" s="5">
-        <v>72.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>99.7</v>
+        <v>90.7</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>187000</v>
+        <v>233000</v>
       </c>
       <c r="G22" s="7">
-        <v>36000</v>
+        <v>14000</v>
       </c>
       <c r="H22" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="7">
-        <v>23667</v>
+        <v>14750</v>
       </c>
       <c r="J22" s="5">
-        <v>72.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>98.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>174000</v>
+        <v>409000</v>
       </c>
       <c r="G23" s="7">
-        <v>59000</v>
+        <v>0</v>
       </c>
       <c r="H23" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="7">
-        <v>26000</v>
+        <v>29500</v>
       </c>
       <c r="J23" s="5">
-        <v>72.8</v>
+        <v>68.5</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>87.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>332000</v>
+        <v>233000</v>
       </c>
       <c r="G24" s="7">
-        <v>79000</v>
+        <v>13000</v>
       </c>
       <c r="H24" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="7">
-        <v>48667</v>
+        <v>12500</v>
       </c>
       <c r="J24" s="5">
-        <v>72.3</v>
+        <v>68.2</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>94.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>166000</v>
+        <v>284000</v>
       </c>
       <c r="G25" s="7">
-        <v>52000</v>
+        <v>-2000</v>
       </c>
       <c r="H25" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>31667</v>
+        <v>22000</v>
       </c>
       <c r="J25" s="5">
-        <v>71.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>94.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>543000</v>
+        <v>2432000</v>
       </c>
       <c r="G26" s="7">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="H26" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" s="7">
-        <v>29000</v>
+        <v>31750</v>
       </c>
       <c r="J26" s="5">
-        <v>71.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>100</v>
+        <v>86.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>158000</v>
+        <v>295000</v>
       </c>
       <c r="G27" s="7">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="7">
-        <v>17000</v>
+        <v>19750</v>
       </c>
       <c r="J27" s="5">
-        <v>71.2</v>
+        <v>67.5</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>83.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>434000</v>
+        <v>223000</v>
       </c>
       <c r="G28" s="7">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="H28" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" s="7">
-        <v>51667</v>
+        <v>21000</v>
       </c>
       <c r="J28" s="5">
-        <v>70.7</v>
+        <v>67.5</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>97.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>234000</v>
+        <v>145000</v>
       </c>
       <c r="G29" s="7">
-        <v>24000</v>
+        <v>30000</v>
       </c>
       <c r="H29" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" s="7">
-        <v>20667</v>
+        <v>17000</v>
       </c>
       <c r="J29" s="5">
-        <v>70.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>99.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>121000</v>
+        <v>288000</v>
       </c>
       <c r="G30" s="7">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="H30" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>14667</v>
+        <v>17250</v>
       </c>
       <c r="J30" s="5">
-        <v>70.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>95.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>288000</v>
+        <v>219000</v>
       </c>
       <c r="G31" s="7">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="H31" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="7">
-        <v>23000</v>
+        <v>11500</v>
       </c>
       <c r="J31" s="5">
-        <v>70.3</v>
+        <v>67.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>99.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>110000</v>
+        <v>219000</v>
       </c>
       <c r="G32" s="7">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="H32" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>14667</v>
+        <v>17600</v>
       </c>
       <c r="J32" s="5">
-        <v>70.3</v>
+        <v>67.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>94.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>265000</v>
+        <v>181000</v>
       </c>
       <c r="G33" s="7">
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="H33" s="7">
         <v>4</v>
       </c>
       <c r="I33" s="7">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="J33" s="5">
-        <v>70</v>
+        <v>67.3</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>95.2</v>
+        <v>86.3</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>317000</v>
+        <v>265000</v>
       </c>
       <c r="G34" s="7">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="H34" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="7">
-        <v>22333</v>
+        <v>18750</v>
       </c>
       <c r="J34" s="5">
-        <v>69.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>95.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>168000</v>
+        <v>190000</v>
       </c>
       <c r="G35" s="7">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="H35" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" s="7">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="J35" s="5">
-        <v>69.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>481000</v>
+        <v>317000</v>
       </c>
       <c r="G36" s="7">
-        <v>41000</v>
+        <v>0</v>
       </c>
       <c r="H36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>39333</v>
+        <v>16750</v>
       </c>
       <c r="J36" s="5">
-        <v>69.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>98.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>218000</v>
+        <v>166000</v>
       </c>
       <c r="G37" s="7">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" s="7">
-        <v>13333</v>
+        <v>23750</v>
       </c>
       <c r="J37" s="5">
-        <v>69.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>97</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>216000</v>
+        <v>151000</v>
       </c>
       <c r="G38" s="7">
-        <v>26000</v>
+        <v>18000</v>
       </c>
       <c r="H38" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I38" s="7">
-        <v>16667</v>
+        <v>10750</v>
       </c>
       <c r="J38" s="5">
-        <v>69.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>95.3</v>
+        <v>81.2</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>236000</v>
+        <v>1138000</v>
       </c>
       <c r="G39" s="7">
-        <v>28000</v>
+        <v>55000</v>
       </c>
       <c r="H39" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I39" s="7">
-        <v>20000</v>
+        <v>27750</v>
       </c>
       <c r="J39" s="5">
-        <v>69.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1912,30 +1912,28 @@
       <c r="A40" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="5">
-        <v>9</v>
-      </c>
+      <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>97.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>124000</v>
+        <v>358000</v>
       </c>
       <c r="G40" s="7">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="H40" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I40" s="7">
-        <v>15667</v>
+        <v>37250</v>
       </c>
       <c r="J40" s="5">
-        <v>69.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>95.09999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>321000</v>
+        <v>187000</v>
       </c>
       <c r="G41" s="7">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="H41" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>19667</v>
+        <v>17750</v>
       </c>
       <c r="J41" s="5">
-        <v>69.2</v>
+        <v>66.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>82.8</v>
+        <v>86.7</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>954000</v>
+        <v>321000</v>
       </c>
       <c r="G42" s="7">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I42" s="7">
-        <v>44667</v>
+        <v>14750</v>
       </c>
       <c r="J42" s="5">
-        <v>68.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>96.7</v>
+        <v>81.7</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>177000</v>
+        <v>892000</v>
       </c>
       <c r="G43" s="7">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="H43" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43" s="7">
-        <v>12333</v>
+        <v>25500</v>
       </c>
       <c r="J43" s="5">
-        <v>68.3</v>
+        <v>66.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>93.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>173000</v>
+        <v>285000</v>
       </c>
       <c r="G44" s="7">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="H44" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7">
-        <v>19000</v>
+        <v>15250</v>
       </c>
       <c r="J44" s="5">
-        <v>68.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>95.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>220000</v>
+        <v>212000</v>
       </c>
       <c r="G45" s="7">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="H45" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
-        <v>12333</v>
+        <v>9750</v>
       </c>
       <c r="J45" s="5">
-        <v>67.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>93.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>104000</v>
+        <v>174000</v>
       </c>
       <c r="G46" s="7">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="H46" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>17000</v>
+        <v>19500</v>
       </c>
       <c r="J46" s="5">
-        <v>67.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>91.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>285000</v>
+        <v>324000</v>
       </c>
       <c r="G47" s="7">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="H47" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="7">
-        <v>20333</v>
+        <v>9500</v>
       </c>
       <c r="J47" s="5">
-        <v>67.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>80.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>2432000</v>
+        <v>481000</v>
       </c>
       <c r="G48" s="7">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="H48" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
-        <v>42333</v>
+        <v>29500</v>
       </c>
       <c r="J48" s="5">
-        <v>67.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>96.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>123000</v>
+        <v>381000</v>
       </c>
       <c r="G49" s="7">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7">
-        <v>8333</v>
+        <v>19500</v>
       </c>
       <c r="J49" s="5">
-        <v>67</v>
+        <v>65.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>90.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>219000</v>
+        <v>222000</v>
       </c>
       <c r="G50" s="7">
-        <v>15000</v>
+        <v>4000</v>
       </c>
       <c r="H50" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="J50" s="5">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,23 +2277,23 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>91.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>324000</v>
+        <v>158000</v>
       </c>
       <c r="G51" s="7">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="H51" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I51" s="7">
-        <v>12667</v>
+        <v>12750</v>
       </c>
       <c r="J51" s="5">
         <v>65.5</v>
@@ -2312,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.5</v>
+        <v>77.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>114000</v>
+        <v>941000</v>
       </c>
       <c r="G52" s="7">
-        <v>24000</v>
+        <v>-13000</v>
       </c>
       <c r="H52" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I52" s="7">
-        <v>38500</v>
+        <v>30250</v>
       </c>
       <c r="J52" s="5">
-        <v>65.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>84.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>1112000</v>
+        <v>391000</v>
       </c>
       <c r="G53" s="7">
-        <v>44000</v>
+        <v>27000</v>
       </c>
       <c r="H53" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>26000</v>
+        <v>22500</v>
       </c>
       <c r="J53" s="5">
-        <v>64.90000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>84.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>381000</v>
+        <v>236000</v>
       </c>
       <c r="G54" s="7">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I54" s="7">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="J54" s="5">
-        <v>64.8</v>
+        <v>65.2</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-07-28T10:14:49+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-07-29T10:18:49+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>诸神愚戏</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>全球死考：刚下刑场你让我去考试</t>
   </si>
   <si>
-    <t>打开作品</t>
+    <t>重生后，姐姐非要嫁给我</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
     <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>全民县令：我看广告无限刷资源</t>
+  </si>
+  <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>伪人降临！我是全场唯一预言家</t>
+  </si>
+  <si>
+    <t>什么叫高考满分，但人失踪了？</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>捡来的夫人是乱世魔头</t>
+  </si>
+  <si>
+    <t>末法时代出飞僵，可我是石坚啊</t>
+  </si>
+  <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
+  </si>
+  <si>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>买卖词条，打造非凡俱乐部</t>
+  </si>
+  <si>
+    <t>四合院，哈军工副院，部下李云龙</t>
+  </si>
+  <si>
     <t>桃花美人村</t>
   </si>
   <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>什么叫高考满分，但人失踪了？</t>
-  </si>
-  <si>
-    <t>全民县令：我看广告无限刷资源</t>
-  </si>
-  <si>
-    <t>诸神愚戏</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>重生后，姐姐非要嫁给我</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
-  </si>
-  <si>
-    <t>我的东莞梦：媚姐</t>
+    <t>崩铁，穿越成怪兽，被爻光买回家</t>
+  </si>
+  <si>
+    <t>封印神源百万年，悟性每天翻倍</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>开局法相，未婚妻不退婚</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>仙界覆灭后，我收留了陨落仙子</t>
+  </si>
+  <si>
+    <t>爱你老哥，但邪神的你，必须善堕</t>
+  </si>
+  <si>
+    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>四合院：开局保卫处，海中叫我叔</t>
+  </si>
+  <si>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
+    <t>老婆本地刀枪炮，高考后我认命了</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>穿越保安，有个比我大三岁的老婆</t>
+  </si>
+  <si>
+    <t>我开启的宝箱品质永远加3</t>
+  </si>
+  <si>
+    <t>僵尸世界：开局拜师雷电法王</t>
+  </si>
+  <si>
+    <t>希腊神话：从成为微风之神开始</t>
+  </si>
+  <si>
+    <t>天幕直播：长乐公主被我吓哭了</t>
+  </si>
+  <si>
+    <t>率土之滨：什么叫军费百倍到账？</t>
+  </si>
+  <si>
+    <t>穿越自带炼妖壶：桀桀，顷刻炼化</t>
+  </si>
+  <si>
+    <t>我操作的少女正在成为旧日之主</t>
+  </si>
+  <si>
+    <t>让你当众写检讨，你作洛神赋？</t>
+  </si>
+  <si>
+    <t>全民神祇时代：我的词条每日刷新</t>
+  </si>
+  <si>
+    <t>村长，收手吧，外面全是套路！</t>
   </si>
   <si>
     <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>四合院，哈军工副院，部下李云龙</t>
-  </si>
-  <si>
-    <t>一人之下：我非魔修，再说杀你哦</t>
-  </si>
-  <si>
-    <t>买卖词条，打造非凡俱乐部</t>
-  </si>
-  <si>
-    <t>我开启的宝箱品质永远加3</t>
-  </si>
-  <si>
-    <t>死对头证道成仙了，怎么办？！</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>领主：开局1金商店购买大车圣女</t>
-  </si>
-  <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
-  </si>
-  <si>
-    <t>糟了！我的网恋对象竟是苗疆圣女</t>
-  </si>
-  <si>
-    <t>崩铁，穿越成怪兽，被爻光买回家</t>
-  </si>
-  <si>
-    <t>老婆本地刀枪炮，高考后我认命了</t>
-  </si>
-  <si>
-    <t>穿越自带炼妖壶：桀桀，顷刻炼化</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>改变人生：从千禧年开始</t>
-  </si>
-  <si>
-    <t>封印神源百万年，悟性每天翻倍</t>
-  </si>
-  <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>杀一怪叠一毒，我一人毒穿世界！</t>
-  </si>
-  <si>
-    <t>我操作的少女正在成为旧日之主</t>
-  </si>
-  <si>
-    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>从变身少女开始斩妖除魔</t>
-  </si>
-  <si>
-    <t>穿越保安，有个比我大三岁的老婆</t>
-  </si>
-  <si>
-    <t>霍格沃兹：开局复制满级火盾护身</t>
-  </si>
-  <si>
-    <t>伪人降临！我是全场唯一预言家</t>
-  </si>
-  <si>
-    <t>仙界覆灭后，我收留了陨落仙子</t>
-  </si>
-  <si>
-    <t>四合院：开局保卫处，海中叫我叔</t>
-  </si>
-  <si>
-    <t>让你当众写检讨，你作洛神赋？</t>
-  </si>
-  <si>
-    <t>名义：调任汉东搞经济，制衡全局</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>穿到女频，整顿满城霸总</t>
-  </si>
-  <si>
-    <t>半山村乡野神医</t>
-  </si>
-  <si>
-    <t>公安局长之扫黑风暴</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>94.2</v>
+        <v>92.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1346000</v>
+        <v>1779000</v>
       </c>
       <c r="G5" s="7">
-        <v>169000</v>
+        <v>219000</v>
       </c>
       <c r="H5" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>140250</v>
+        <v>97600</v>
       </c>
       <c r="J5" s="5">
-        <v>91.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>79.8</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>754000</v>
+        <v>1346000</v>
       </c>
       <c r="G6" s="7">
-        <v>78000</v>
+        <v>0</v>
       </c>
       <c r="H6" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="7">
-        <v>46750</v>
+        <v>112200</v>
       </c>
       <c r="J6" s="5">
-        <v>81.7</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>485000</v>
+        <v>564000</v>
       </c>
       <c r="G7" s="7">
-        <v>66000</v>
+        <v>62000</v>
       </c>
       <c r="H7" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="7">
-        <v>61750</v>
+        <v>48000</v>
       </c>
       <c r="J7" s="5">
-        <v>81.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>98.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>290000</v>
+        <v>779000</v>
       </c>
       <c r="G8" s="7">
-        <v>30000</v>
+        <v>41000</v>
       </c>
       <c r="H8" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>43250</v>
+        <v>50000</v>
       </c>
       <c r="J8" s="5">
-        <v>80.2</v>
+        <v>82.8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>89.3</v>
+        <v>95.2</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>738000</v>
+        <v>797000</v>
       </c>
       <c r="G9" s="7">
-        <v>0</v>
+        <v>43000</v>
       </c>
       <c r="H9" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>52250</v>
+        <v>46000</v>
       </c>
       <c r="J9" s="5">
-        <v>77.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>91.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>585000</v>
+        <v>751000</v>
       </c>
       <c r="G10" s="7">
-        <v>18000</v>
+        <v>247000</v>
       </c>
       <c r="H10" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>47000</v>
+        <v>52400</v>
       </c>
       <c r="J10" s="5">
-        <v>76.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>99.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>264000</v>
+        <v>310000</v>
       </c>
       <c r="G11" s="7">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="H11" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>23000</v>
+        <v>38600</v>
       </c>
       <c r="J11" s="5">
-        <v>75.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>78.5</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>1560000</v>
+        <v>258000</v>
       </c>
       <c r="G12" s="7">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="H12" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="7">
-        <v>67250</v>
+        <v>23800</v>
       </c>
       <c r="J12" s="5">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>132000</v>
+        <v>296000</v>
       </c>
       <c r="G13" s="7">
-        <v>18000</v>
+        <v>32000</v>
       </c>
       <c r="H13" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>31667</v>
+        <v>24800</v>
       </c>
       <c r="J13" s="5">
-        <v>74.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>88.5</v>
+        <v>99.7</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>502000</v>
+        <v>276000</v>
       </c>
       <c r="G14" s="7">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="H14" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>44500</v>
+        <v>20000</v>
       </c>
       <c r="J14" s="5">
-        <v>74.8</v>
+        <v>77.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93.2</v>
+        <v>98</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>567000</v>
+        <v>188000</v>
       </c>
       <c r="G15" s="7">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="H15" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>27750</v>
+        <v>23400</v>
       </c>
       <c r="J15" s="5">
-        <v>73.2</v>
+        <v>77.8</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>82.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>389000</v>
+        <v>198000</v>
       </c>
       <c r="G16" s="7">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="H16" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>60667</v>
+        <v>20400</v>
       </c>
       <c r="J16" s="5">
-        <v>72.3</v>
+        <v>77.3</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>83.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>479000</v>
+        <v>590000</v>
       </c>
       <c r="G17" s="7">
-        <v>67000</v>
+        <v>5000</v>
       </c>
       <c r="H17" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>42500</v>
+        <v>38600</v>
       </c>
       <c r="J17" s="5">
-        <v>71.5</v>
+        <v>76.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>94.3</v>
+        <v>84.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>191000</v>
+        <v>402000</v>
       </c>
       <c r="G18" s="7">
-        <v>14000</v>
+        <v>31000</v>
       </c>
       <c r="H18" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="7">
-        <v>12750</v>
+        <v>47800</v>
       </c>
       <c r="J18" s="5">
-        <v>70.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>90.3</v>
+        <v>100</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>251000</v>
+        <v>148000</v>
       </c>
       <c r="G19" s="7">
-        <v>36000</v>
+        <v>27000</v>
       </c>
       <c r="H19" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" s="7">
-        <v>21000</v>
+        <v>14200</v>
       </c>
       <c r="J19" s="5">
-        <v>69.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>74.5</v>
+        <v>99.7</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>371000</v>
+        <v>130000</v>
       </c>
       <c r="G20" s="7">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>52000</v>
+        <v>12800</v>
       </c>
       <c r="J20" s="5">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>88.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>411000</v>
+        <v>147000</v>
       </c>
       <c r="G21" s="7">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H21" s="7">
         <v>5</v>
       </c>
       <c r="I21" s="7">
-        <v>20750</v>
+        <v>27500</v>
       </c>
       <c r="J21" s="5">
-        <v>68.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>90.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>233000</v>
+        <v>406000</v>
       </c>
       <c r="G22" s="7">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="H22" s="7">
         <v>5</v>
       </c>
       <c r="I22" s="7">
-        <v>14750</v>
+        <v>49750</v>
       </c>
       <c r="J22" s="5">
-        <v>68.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>83.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>409000</v>
+        <v>204000</v>
       </c>
       <c r="G23" s="7">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="H23" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" s="7">
-        <v>29500</v>
+        <v>17600</v>
       </c>
       <c r="J23" s="5">
-        <v>68.5</v>
+        <v>75</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>233000</v>
+        <v>343000</v>
       </c>
       <c r="G24" s="7">
-        <v>13000</v>
+        <v>26000</v>
       </c>
       <c r="H24" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>12500</v>
+        <v>18600</v>
       </c>
       <c r="J24" s="5">
-        <v>68.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>86.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>284000</v>
+        <v>586000</v>
       </c>
       <c r="G25" s="7">
-        <v>-2000</v>
+        <v>93000</v>
       </c>
       <c r="H25" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" s="7">
-        <v>22000</v>
+        <v>24600</v>
       </c>
       <c r="J25" s="5">
-        <v>68.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>81.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>2432000</v>
+        <v>578000</v>
       </c>
       <c r="G26" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H26" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
-        <v>31750</v>
+        <v>24400</v>
       </c>
       <c r="J26" s="5">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>86.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>295000</v>
+        <v>425000</v>
       </c>
       <c r="G27" s="7">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="H27" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>19750</v>
+        <v>26800</v>
       </c>
       <c r="J27" s="5">
-        <v>67.5</v>
+        <v>74</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>85.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>223000</v>
+        <v>428000</v>
       </c>
       <c r="G28" s="7">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="H28" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" s="7">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="J28" s="5">
-        <v>67.5</v>
+        <v>73.8</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>87.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>145000</v>
+        <v>485000</v>
       </c>
       <c r="G29" s="7">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I29" s="7">
-        <v>17000</v>
+        <v>49400</v>
       </c>
       <c r="J29" s="5">
-        <v>67.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>87.3</v>
+        <v>92.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>288000</v>
+        <v>302000</v>
       </c>
       <c r="G30" s="7">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>17250</v>
+        <v>16600</v>
       </c>
       <c r="J30" s="5">
-        <v>67.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>89.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>219000</v>
+        <v>201000</v>
       </c>
       <c r="G31" s="7">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="H31" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" s="7">
-        <v>11500</v>
+        <v>18200</v>
       </c>
       <c r="J31" s="5">
-        <v>67.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>81.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>219000</v>
+        <v>169000</v>
       </c>
       <c r="G32" s="7">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="H32" s="7">
         <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>17600</v>
+        <v>12400</v>
       </c>
       <c r="J32" s="5">
-        <v>67.3</v>
+        <v>72.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.3</v>
+        <v>94.7</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>181000</v>
+        <v>215000</v>
       </c>
       <c r="G33" s="7">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="H33" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>18000</v>
+        <v>8200</v>
       </c>
       <c r="J33" s="5">
-        <v>67.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>86.3</v>
+        <v>94.3</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>265000</v>
+        <v>204000</v>
       </c>
       <c r="G34" s="7">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="H34" s="7">
         <v>5</v>
       </c>
       <c r="I34" s="7">
-        <v>18750</v>
+        <v>19250</v>
       </c>
       <c r="J34" s="5">
-        <v>67.2</v>
+        <v>71.7</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>85.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>190000</v>
+        <v>337000</v>
       </c>
       <c r="G35" s="7">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="H35" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>20000</v>
+        <v>10200</v>
       </c>
       <c r="J35" s="5">
-        <v>67.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.7</v>
+        <v>91</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>317000</v>
+        <v>162000</v>
       </c>
       <c r="G36" s="7">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>16750</v>
+        <v>9000</v>
       </c>
       <c r="J36" s="5">
-        <v>66.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>83.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>166000</v>
+        <v>370000</v>
       </c>
       <c r="G37" s="7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H37" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>23750</v>
+        <v>32200</v>
       </c>
       <c r="J37" s="5">
-        <v>66.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>89.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>151000</v>
+        <v>326000</v>
       </c>
       <c r="G38" s="7">
-        <v>18000</v>
+        <v>5000</v>
       </c>
       <c r="H38" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>10750</v>
+        <v>12800</v>
       </c>
       <c r="J38" s="5">
-        <v>66.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>81.2</v>
+        <v>81.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>1138000</v>
+        <v>497000</v>
       </c>
       <c r="G39" s="7">
-        <v>55000</v>
+        <v>16000</v>
       </c>
       <c r="H39" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" s="7">
-        <v>27750</v>
+        <v>26800</v>
       </c>
       <c r="J39" s="5">
-        <v>66.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>76.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>358000</v>
+        <v>267000</v>
       </c>
       <c r="G40" s="7">
-        <v>0</v>
+        <v>59000</v>
       </c>
       <c r="H40" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>37250</v>
+        <v>16400</v>
       </c>
       <c r="J40" s="5">
-        <v>66.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>85.5</v>
+        <v>88.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>187000</v>
+        <v>230000</v>
       </c>
       <c r="G41" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41" s="7">
-        <v>17750</v>
+        <v>11400</v>
       </c>
       <c r="J41" s="5">
-        <v>66.5</v>
+        <v>69.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>86.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>321000</v>
+        <v>2432000</v>
       </c>
       <c r="G42" s="7">
         <v>0</v>
       </c>
       <c r="H42" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I42" s="7">
-        <v>14750</v>
+        <v>25400</v>
       </c>
       <c r="J42" s="5">
-        <v>66.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>81.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>892000</v>
+        <v>290000</v>
       </c>
       <c r="G43" s="7">
-        <v>24000</v>
+        <v>5000</v>
       </c>
       <c r="H43" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I43" s="7">
-        <v>25500</v>
+        <v>13200</v>
       </c>
       <c r="J43" s="5">
-        <v>66.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>85.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>285000</v>
+        <v>238000</v>
       </c>
       <c r="G44" s="7">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H44" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>15250</v>
+        <v>11000</v>
       </c>
       <c r="J44" s="5">
-        <v>65.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>88.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>212000</v>
+        <v>354000</v>
       </c>
       <c r="G45" s="7">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="H45" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>9750</v>
+        <v>33600</v>
       </c>
       <c r="J45" s="5">
-        <v>65.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2110,28 +2110,30 @@
       <c r="A46" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="5"/>
+      <c r="B46" s="5">
+        <v>9</v>
+      </c>
       <c r="C46" s="5">
-        <v>83.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>174000</v>
+        <v>131000</v>
       </c>
       <c r="G46" s="7">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H46" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I46" s="7">
-        <v>19500</v>
+        <v>10800</v>
       </c>
       <c r="J46" s="5">
-        <v>65.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>87.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>324000</v>
+        <v>109000</v>
       </c>
       <c r="G47" s="7">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H47" s="7">
         <v>5</v>
       </c>
       <c r="I47" s="7">
-        <v>9500</v>
+        <v>10000</v>
       </c>
       <c r="J47" s="5">
-        <v>65.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>78.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>481000</v>
+        <v>107000</v>
       </c>
       <c r="G48" s="7">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H48" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7">
-        <v>29500</v>
+        <v>10800</v>
       </c>
       <c r="J48" s="5">
-        <v>65.5</v>
+        <v>68.7</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>82.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>381000</v>
+        <v>231000</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H49" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I49" s="7">
-        <v>19500</v>
+        <v>16667</v>
       </c>
       <c r="J49" s="5">
-        <v>65.5</v>
+        <v>68.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>86.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>222000</v>
+        <v>1168000</v>
       </c>
       <c r="G50" s="7">
-        <v>4000</v>
+        <v>30000</v>
       </c>
       <c r="H50" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50" s="7">
-        <v>11000</v>
+        <v>28200</v>
       </c>
       <c r="J50" s="5">
-        <v>65.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>158000</v>
+        <v>381000</v>
       </c>
       <c r="G51" s="7">
         <v>0</v>
       </c>
       <c r="H51" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I51" s="7">
-        <v>12750</v>
+        <v>15600</v>
       </c>
       <c r="J51" s="5">
-        <v>65.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>77.7</v>
+        <v>88.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>941000</v>
+        <v>221000</v>
       </c>
       <c r="G52" s="7">
-        <v>-13000</v>
+        <v>9000</v>
       </c>
       <c r="H52" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I52" s="7">
-        <v>30250</v>
+        <v>6800</v>
       </c>
       <c r="J52" s="5">
-        <v>65.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>81.2</v>
+        <v>87.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>391000</v>
+        <v>109000</v>
       </c>
       <c r="G53" s="7">
-        <v>27000</v>
+        <v>5000</v>
       </c>
       <c r="H53" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53" s="7">
-        <v>22500</v>
+        <v>6200</v>
       </c>
       <c r="J53" s="5">
-        <v>65.3</v>
+        <v>67.7</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>84.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>236000</v>
+        <v>191000</v>
       </c>
       <c r="G54" s="7">
         <v>0</v>
       </c>
       <c r="H54" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I54" s="7">
-        <v>15000</v>
+        <v>10200</v>
       </c>
       <c r="J54" s="5">
-        <v>65.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-07-29T10:18:49+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-07-30T09:41:06+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>全球死考：刚下刑场你让我去考试</t>
   </si>
   <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
     <t>重生后，姐姐非要嫁给我</t>
   </si>
   <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
     <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
+    <t>桃花美人村</t>
+  </si>
+  <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>封印神源百万年，悟性每天翻倍</t>
   </si>
   <si>
     <t>魔王叫我小同志，那就是世界错了</t>
   </si>
   <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
+    <t>末法时代出飞僵，可我是石坚啊</t>
+  </si>
+  <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>捡来的夫人是乱世魔头</t>
+  </si>
+  <si>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
   </si>
   <si>
     <t>全民县令：我看广告无限刷资源</t>
   </si>
   <si>
-    <t>公安局长之扫黑风暴</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>伪人降临！我是全场唯一预言家</t>
+    <t>买卖词条，打造非凡俱乐部</t>
+  </si>
+  <si>
+    <t>开局法相，未婚妻不退婚</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
+    <t>四合院，哈军工副院，部下李云龙</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
   </si>
   <si>
     <t>什么叫高考满分，但人失踪了？</t>
   </si>
   <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>捡来的夫人是乱世魔头</t>
-  </si>
-  <si>
-    <t>末法时代出飞僵，可我是石坚啊</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>买卖词条，打造非凡俱乐部</t>
-  </si>
-  <si>
-    <t>四合院，哈军工副院，部下李云龙</t>
-  </si>
-  <si>
-    <t>桃花美人村</t>
-  </si>
-  <si>
     <t>崩铁，穿越成怪兽，被爻光买回家</t>
   </si>
   <si>
-    <t>封印神源百万年，悟性每天翻倍</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>开局法相，未婚妻不退婚</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>仙界覆灭后，我收留了陨落仙子</t>
-  </si>
-  <si>
-    <t>爱你老哥，但邪神的你，必须善堕</t>
-  </si>
-  <si>
-    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+    <t>从金丹仙族开始的老祖之路！</t>
+  </si>
+  <si>
+    <t>瘟疫模拟：开局投放Necroa</t>
+  </si>
+  <si>
+    <t>暑假兼职赶尸，749局找上门！</t>
+  </si>
+  <si>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>三角洲：我一扶贫主播却被喊CS</t>
+  </si>
+  <si>
+    <t>你写的小说，给我惹了不少麻烦呢</t>
+  </si>
+  <si>
+    <t>希腊神话：从成为微风之神开始</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>我开启的宝箱品质永远加3</t>
+  </si>
+  <si>
+    <t>一人之下：我非魔修，再说杀你哦</t>
+  </si>
+  <si>
+    <t>老婆本地刀枪炮，高考后我认命了</t>
   </si>
   <si>
     <t>东北振兴，千万员工BUFF拉满</t>
   </si>
   <si>
+    <t>公路求生：最速传说</t>
+  </si>
+  <si>
+    <t>僵尸世界：开局拜师雷电法王</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>率土之滨：什么叫军费百倍到账？</t>
+  </si>
+  <si>
+    <t>开局知青下乡，我选择偷渡香港</t>
+  </si>
+  <si>
     <t>四合院：开局保卫处，海中叫我叔</t>
   </si>
   <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>老婆本地刀枪炮，高考后我认命了</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>穿越保安，有个比我大三岁的老婆</t>
-  </si>
-  <si>
-    <t>我开启的宝箱品质永远加3</t>
-  </si>
-  <si>
-    <t>僵尸世界：开局拜师雷电法王</t>
-  </si>
-  <si>
-    <t>希腊神话：从成为微风之神开始</t>
-  </si>
-  <si>
-    <t>天幕直播：长乐公主被我吓哭了</t>
-  </si>
-  <si>
-    <t>率土之滨：什么叫军费百倍到账？</t>
-  </si>
-  <si>
-    <t>穿越自带炼妖壶：桀桀，顷刻炼化</t>
-  </si>
-  <si>
-    <t>我操作的少女正在成为旧日之主</t>
-  </si>
-  <si>
-    <t>让你当众写检讨，你作洛神赋？</t>
-  </si>
-  <si>
-    <t>全民神祇时代：我的词条每日刷新</t>
-  </si>
-  <si>
-    <t>村长，收手吧，外面全是套路！</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
+    <t>实习教出金牌班，家长要换班主任</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>92.8</v>
+        <v>95.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1779000</v>
+        <v>2137000</v>
       </c>
       <c r="G5" s="7">
-        <v>219000</v>
+        <v>358000</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7">
-        <v>97600</v>
+        <v>141000</v>
       </c>
       <c r="J5" s="5">
-        <v>93.40000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>79.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1346000</v>
+        <v>1406000</v>
       </c>
       <c r="G6" s="7">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="H6" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>112200</v>
+        <v>103500</v>
       </c>
       <c r="J6" s="5">
-        <v>86.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>564000</v>
+        <v>922000</v>
       </c>
       <c r="G7" s="7">
-        <v>62000</v>
+        <v>171000</v>
       </c>
       <c r="H7" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>48000</v>
+        <v>72167</v>
       </c>
       <c r="J7" s="5">
-        <v>85</v>
+        <v>88.8</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>95</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>779000</v>
+        <v>826000</v>
       </c>
       <c r="G8" s="7">
-        <v>41000</v>
+        <v>47000</v>
       </c>
       <c r="H8" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>50000</v>
+        <v>49500</v>
       </c>
       <c r="J8" s="5">
-        <v>82.8</v>
+        <v>85</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>95.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>797000</v>
+        <v>595000</v>
       </c>
       <c r="G9" s="7">
-        <v>43000</v>
+        <v>31000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>46000</v>
+        <v>45167</v>
       </c>
       <c r="J9" s="5">
-        <v>81.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>91.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>751000</v>
+        <v>831000</v>
       </c>
       <c r="G10" s="7">
-        <v>247000</v>
+        <v>34000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>52400</v>
+        <v>44000</v>
       </c>
       <c r="J10" s="5">
-        <v>81.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>94.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>310000</v>
+        <v>536000</v>
       </c>
       <c r="G11" s="7">
-        <v>20000</v>
+        <v>51000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>38600</v>
+        <v>49667</v>
       </c>
       <c r="J11" s="5">
-        <v>79.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>258000</v>
+        <v>313000</v>
       </c>
       <c r="G12" s="7">
-        <v>35000</v>
+        <v>37000</v>
       </c>
       <c r="H12" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>23800</v>
+        <v>22833</v>
       </c>
       <c r="J12" s="5">
-        <v>79</v>
+        <v>80.3</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>98.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>296000</v>
+        <v>432000</v>
       </c>
       <c r="G13" s="7">
-        <v>32000</v>
+        <v>26000</v>
       </c>
       <c r="H13" s="7">
         <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>24800</v>
+        <v>45000</v>
       </c>
       <c r="J13" s="5">
-        <v>78.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>99.7</v>
+        <v>91.7</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>276000</v>
+        <v>680000</v>
       </c>
       <c r="G14" s="7">
-        <v>40000</v>
+        <v>94000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>20000</v>
+        <v>36167</v>
       </c>
       <c r="J14" s="5">
-        <v>77.8</v>
+        <v>79.5</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>98</v>
+        <v>96.5</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>188000</v>
+        <v>284000</v>
       </c>
       <c r="G15" s="7">
-        <v>22000</v>
+        <v>26000</v>
       </c>
       <c r="H15" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>23400</v>
+        <v>24167</v>
       </c>
       <c r="J15" s="5">
-        <v>77.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1129,19 +1129,19 @@
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>198000</v>
+        <v>228000</v>
       </c>
       <c r="G16" s="7">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="H16" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>20400</v>
+        <v>19667</v>
       </c>
       <c r="J16" s="5">
-        <v>77.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>88.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>590000</v>
+        <v>323000</v>
       </c>
       <c r="G17" s="7">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="7">
-        <v>38600</v>
+        <v>34333</v>
       </c>
       <c r="J17" s="5">
-        <v>76.5</v>
+        <v>79</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>84.7</v>
+        <v>100</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>402000</v>
+        <v>152000</v>
       </c>
       <c r="G18" s="7">
-        <v>31000</v>
+        <v>22000</v>
       </c>
       <c r="H18" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="7">
-        <v>47800</v>
+        <v>14333</v>
       </c>
       <c r="J18" s="5">
-        <v>76.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>148000</v>
+        <v>165000</v>
       </c>
       <c r="G19" s="7">
-        <v>27000</v>
+        <v>18000</v>
       </c>
       <c r="H19" s="7">
         <v>6</v>
       </c>
       <c r="I19" s="7">
-        <v>14200</v>
+        <v>25600</v>
       </c>
       <c r="J19" s="5">
-        <v>76.5</v>
+        <v>78.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>99.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>130000</v>
+        <v>207000</v>
       </c>
       <c r="G20" s="7">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="H20" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" s="7">
-        <v>12800</v>
+        <v>22667</v>
       </c>
       <c r="J20" s="5">
-        <v>76</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>97.2</v>
+        <v>99</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>147000</v>
+        <v>167000</v>
       </c>
       <c r="G21" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>7</v>
+      </c>
+      <c r="I21" s="7">
         <v>15000</v>
       </c>
-      <c r="H21" s="7">
-        <v>5</v>
-      </c>
-      <c r="I21" s="7">
-        <v>27500</v>
-      </c>
       <c r="J21" s="5">
-        <v>75.3</v>
+        <v>78.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>86.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>406000</v>
+        <v>373000</v>
       </c>
       <c r="G22" s="7">
-        <v>17000</v>
+        <v>30000</v>
       </c>
       <c r="H22" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>49750</v>
+        <v>20500</v>
       </c>
       <c r="J22" s="5">
-        <v>75.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>95.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>204000</v>
+        <v>431000</v>
       </c>
       <c r="G23" s="7">
-        <v>17000</v>
+        <v>29000</v>
       </c>
       <c r="H23" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>17600</v>
+        <v>44667</v>
       </c>
       <c r="J23" s="5">
-        <v>75</v>
+        <v>77.2</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>343000</v>
+        <v>313000</v>
       </c>
       <c r="G24" s="7">
-        <v>26000</v>
+        <v>17000</v>
       </c>
       <c r="H24" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="7">
-        <v>18600</v>
+        <v>23500</v>
       </c>
       <c r="J24" s="5">
-        <v>74.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>91.3</v>
+        <v>90.8</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>586000</v>
+        <v>443000</v>
       </c>
       <c r="G25" s="7">
-        <v>93000</v>
+        <v>18000</v>
       </c>
       <c r="H25" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>24600</v>
+        <v>25333</v>
       </c>
       <c r="J25" s="5">
-        <v>74.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>90.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>578000</v>
+        <v>237000</v>
       </c>
       <c r="G26" s="7">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="H26" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="7">
-        <v>24400</v>
+        <v>10500</v>
       </c>
       <c r="J26" s="5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>89.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>425000</v>
+        <v>219000</v>
       </c>
       <c r="G27" s="7">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>26800</v>
+        <v>17167</v>
       </c>
       <c r="J27" s="5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>92.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>428000</v>
+        <v>232000</v>
       </c>
       <c r="G28" s="7">
-        <v>17000</v>
+        <v>28000</v>
       </c>
       <c r="H28" s="7">
         <v>6</v>
       </c>
       <c r="I28" s="7">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="J28" s="5">
-        <v>73.8</v>
+        <v>75.8</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>77.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>485000</v>
+        <v>590000</v>
       </c>
       <c r="G29" s="7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H29" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>49400</v>
+        <v>22333</v>
       </c>
       <c r="J29" s="5">
-        <v>73</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>92.3</v>
+        <v>90.8</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>302000</v>
+        <v>314000</v>
       </c>
       <c r="G30" s="7">
-        <v>14000</v>
+        <v>47000</v>
       </c>
       <c r="H30" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" s="7">
-        <v>16600</v>
+        <v>21500</v>
       </c>
       <c r="J30" s="5">
-        <v>72.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>91.5</v>
+        <v>91.7</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>201000</v>
+        <v>443000</v>
       </c>
       <c r="G31" s="7">
-        <v>11000</v>
+        <v>15000</v>
       </c>
       <c r="H31" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>18200</v>
+        <v>19167</v>
       </c>
       <c r="J31" s="5">
-        <v>72.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>93.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>169000</v>
+        <v>183000</v>
       </c>
       <c r="G32" s="7">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="H32" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="7">
-        <v>12400</v>
+        <v>12667</v>
       </c>
       <c r="J32" s="5">
-        <v>72.3</v>
+        <v>75.2</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>94.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>215000</v>
+        <v>578000</v>
       </c>
       <c r="G33" s="7">
-        <v>16000</v>
+        <v>-12000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" s="7">
-        <v>8200</v>
+        <v>30167</v>
       </c>
       <c r="J33" s="5">
-        <v>72.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>94.3</v>
+        <v>91.5</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>204000</v>
+        <v>314000</v>
       </c>
       <c r="G34" s="7">
-        <v>23000</v>
+        <v>12000</v>
       </c>
       <c r="H34" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I34" s="7">
-        <v>19250</v>
+        <v>15833</v>
       </c>
       <c r="J34" s="5">
-        <v>71.7</v>
+        <v>74.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>91.7</v>
+        <v>94.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>337000</v>
+        <v>108000</v>
       </c>
       <c r="G35" s="7">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>10200</v>
+        <v>9167</v>
       </c>
       <c r="J35" s="5">
-        <v>71</v>
+        <v>74.2</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>162000</v>
+        <v>108000</v>
       </c>
       <c r="G36" s="7">
-        <v>19000</v>
+        <v>15000</v>
       </c>
       <c r="H36" s="7">
         <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>9000</v>
+        <v>12600</v>
       </c>
       <c r="J36" s="5">
-        <v>70.3</v>
+        <v>74</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>79.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>370000</v>
+        <v>102000</v>
       </c>
       <c r="G37" s="7">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="H37" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>32200</v>
+        <v>7833</v>
       </c>
       <c r="J37" s="5">
-        <v>69.8</v>
+        <v>74</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>88.3</v>
+        <v>94.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>326000</v>
+        <v>105000</v>
       </c>
       <c r="G38" s="7">
-        <v>5000</v>
+        <v>33000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="7">
-        <v>12800</v>
+        <v>7500</v>
       </c>
       <c r="J38" s="5">
-        <v>69.8</v>
+        <v>73.7</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>497000</v>
+        <v>100000</v>
       </c>
       <c r="G39" s="7">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="H39" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>26800</v>
+        <v>6000</v>
       </c>
       <c r="J39" s="5">
-        <v>69.7</v>
+        <v>73.3</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.3</v>
+        <v>91.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>267000</v>
+        <v>149000</v>
       </c>
       <c r="G40" s="7">
-        <v>59000</v>
+        <v>16000</v>
       </c>
       <c r="H40" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>16400</v>
+        <v>11167</v>
       </c>
       <c r="J40" s="5">
-        <v>69.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1945,28 +1945,30 @@
       <c r="A41" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="5"/>
+      <c r="B41" s="5">
+        <v>9</v>
+      </c>
       <c r="C41" s="5">
-        <v>88.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>230000</v>
+        <v>141000</v>
       </c>
       <c r="G41" s="7">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="H41" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>11400</v>
+        <v>10667</v>
       </c>
       <c r="J41" s="5">
-        <v>69.5</v>
+        <v>72.7</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>81.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>2432000</v>
+        <v>2467000</v>
       </c>
       <c r="G42" s="7">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="H42" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>25400</v>
+        <v>27000</v>
       </c>
       <c r="J42" s="5">
-        <v>69.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>87.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>290000</v>
+        <v>266000</v>
       </c>
       <c r="G43" s="7">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="H43" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="7">
-        <v>13200</v>
+        <v>16500</v>
       </c>
       <c r="J43" s="5">
-        <v>69.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>88.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>238000</v>
+        <v>245000</v>
       </c>
       <c r="G44" s="7">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="H44" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" s="7">
-        <v>11000</v>
+        <v>10333</v>
       </c>
       <c r="J44" s="5">
-        <v>69.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>77.7</v>
+        <v>88.7</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>354000</v>
+        <v>241000</v>
       </c>
       <c r="G45" s="7">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I45" s="7">
-        <v>33600</v>
+        <v>11167</v>
       </c>
       <c r="J45" s="5">
-        <v>69.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2110,30 +2112,28 @@
       <c r="A46" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="5">
-        <v>9</v>
-      </c>
+      <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>87.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>131000</v>
+        <v>240000</v>
       </c>
       <c r="G46" s="7">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="H46" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I46" s="7">
-        <v>10800</v>
+        <v>11167</v>
       </c>
       <c r="J46" s="5">
-        <v>69</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>93.5</v>
+        <v>88.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>109000</v>
+        <v>331000</v>
       </c>
       <c r="G47" s="7">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H47" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I47" s="7">
-        <v>10000</v>
+        <v>11500</v>
       </c>
       <c r="J47" s="5">
-        <v>68.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.2</v>
+        <v>96.8</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>107000</v>
+        <v>108000</v>
       </c>
       <c r="G48" s="7">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="H48" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
-        <v>10800</v>
+        <v>12000</v>
       </c>
       <c r="J48" s="5">
-        <v>68.7</v>
+        <v>71.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>80.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>231000</v>
+        <v>378000</v>
       </c>
       <c r="G49" s="7">
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="H49" s="7">
         <v>7</v>
       </c>
       <c r="I49" s="7">
-        <v>16667</v>
+        <v>32000</v>
       </c>
       <c r="J49" s="5">
-        <v>68.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>78.8</v>
+        <v>87.7</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>1168000</v>
+        <v>195000</v>
       </c>
       <c r="G50" s="7">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="H50" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I50" s="7">
-        <v>28200</v>
+        <v>9167</v>
       </c>
       <c r="J50" s="5">
-        <v>68.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>84.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>381000</v>
+        <v>111000</v>
       </c>
       <c r="G51" s="7">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H51" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I51" s="7">
-        <v>15600</v>
+        <v>9667</v>
       </c>
       <c r="J51" s="5">
-        <v>68.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,14 +2312,14 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>88.5</v>
+        <v>91.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>221000</v>
+        <v>104000</v>
       </c>
       <c r="G52" s="7">
         <v>9000</v>
@@ -2328,10 +2328,10 @@
         <v>6</v>
       </c>
       <c r="I52" s="7">
-        <v>6800</v>
+        <v>8800</v>
       </c>
       <c r="J52" s="5">
-        <v>68.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>87.5</v>
+        <v>80.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>109000</v>
+        <v>507000</v>
       </c>
       <c r="G53" s="7">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H53" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I53" s="7">
-        <v>6200</v>
+        <v>24000</v>
       </c>
       <c r="J53" s="5">
-        <v>67.7</v>
+        <v>70.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>85.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>191000</v>
+        <v>422000</v>
       </c>
       <c r="G54" s="7">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="H54" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I54" s="7">
-        <v>10200</v>
+        <v>3667</v>
       </c>
       <c r="J54" s="5">
-        <v>67.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-07-30T09:41:06+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-07-31T10:08:42+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
     <t>全球死考：刚下刑场你让我去考试</t>
   </si>
   <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
+    <t>刚证道混沌天帝，让我身化禁区？</t>
   </si>
   <si>
     <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
     <t>重生后，姐姐非要嫁给我</t>
   </si>
   <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>桃花美人村</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
     <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
-    <t>桃花美人村</t>
-  </si>
-  <si>
-    <t>公安局长之扫黑风暴</t>
-  </si>
-  <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>科举：陛下！新科状元又惹事了！</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
   </si>
   <si>
     <t>我，最强毒士，女帝直呼活阎王</t>
   </si>
   <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
     <t>领主巫师：从无限魔晶开始求学！</t>
   </si>
   <si>
+    <t>四合院，哈军工副院，部下李云龙</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>天幕直播：长乐公主被我吓哭了</t>
+  </si>
+  <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>妖魔乱世：从造畜法开始左道成仙</t>
+  </si>
+  <si>
+    <t>买卖词条，打造非凡俱乐部</t>
+  </si>
+  <si>
+    <t>崩铁，穿越成怪兽，被爻光买回家</t>
+  </si>
+  <si>
+    <t>瘟疫模拟：开局投放Necroa</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
+  </si>
+  <si>
+    <t>开局法相，未婚妻不退婚</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>国运班级求生：机电2班闹翻荒野</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>穿越刘备，死后和我说这是型月？</t>
+  </si>
+  <si>
+    <t>希腊神话：从成为微风之神开始</t>
+  </si>
+  <si>
+    <t>率土之滨：什么叫军费百倍到账？</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>末法时代出飞僵，可我是石坚啊</t>
+  </si>
+  <si>
+    <t>什么叫高考满分，但人失踪了？</t>
+  </si>
+  <si>
+    <t>公路求生：最速传说</t>
+  </si>
+  <si>
+    <t>暑假兼职赶尸，749局找上门！</t>
+  </si>
+  <si>
     <t>封印神源百万年，悟性每天翻倍</t>
   </si>
   <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
-  </si>
-  <si>
-    <t>末法时代出飞僵，可我是石坚啊</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>捡来的夫人是乱世魔头</t>
-  </si>
-  <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
     <t>全民县令：我看广告无限刷资源</t>
   </si>
   <si>
-    <t>买卖词条，打造非凡俱乐部</t>
-  </si>
-  <si>
-    <t>开局法相，未婚妻不退婚</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>四合院，哈军工副院，部下李云龙</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>什么叫高考满分，但人失踪了？</t>
-  </si>
-  <si>
-    <t>崩铁，穿越成怪兽，被爻光买回家</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>瘟疫模拟：开局投放Necroa</t>
-  </si>
-  <si>
-    <t>暑假兼职赶尸，749局找上门！</t>
-  </si>
-  <si>
-    <t>我提前三天被丢进了末世</t>
-  </si>
-  <si>
-    <t>三角洲：我一扶贫主播却被喊CS</t>
-  </si>
-  <si>
-    <t>你写的小说，给我惹了不少麻烦呢</t>
-  </si>
-  <si>
-    <t>希腊神话：从成为微风之神开始</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>暑假失踪，开学归来成元婴老祖！</t>
+  </si>
+  <si>
+    <t>僵尸世界：开局拜师雷电法王</t>
   </si>
   <si>
     <t>我开启的宝箱品质永远加3</t>
-  </si>
-  <si>
-    <t>一人之下：我非魔修，再说杀你哦</t>
-  </si>
-  <si>
-    <t>老婆本地刀枪炮，高考后我认命了</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>公路求生：最速传说</t>
-  </si>
-  <si>
-    <t>僵尸世界：开局拜师雷电法王</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>率土之滨：什么叫军费百倍到账？</t>
-  </si>
-  <si>
-    <t>开局知青下乡，我选择偷渡香港</t>
-  </si>
-  <si>
-    <t>四合院：开局保卫处，海中叫我叔</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>95.8</v>
+        <v>94.5</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>2137000</v>
+        <v>2441000</v>
       </c>
       <c r="G5" s="7">
-        <v>358000</v>
+        <v>304000</v>
       </c>
       <c r="H5" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>141000</v>
+        <v>164286</v>
       </c>
       <c r="J5" s="5">
-        <v>97.7</v>
+        <v>97</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>84.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1406000</v>
+        <v>1083000</v>
       </c>
       <c r="G6" s="7">
-        <v>60000</v>
+        <v>161000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>103500</v>
+        <v>84857</v>
       </c>
       <c r="J6" s="5">
-        <v>91.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>92.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>922000</v>
+        <v>1470000</v>
       </c>
       <c r="G7" s="7">
-        <v>171000</v>
+        <v>64000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>72167</v>
+        <v>97857</v>
       </c>
       <c r="J7" s="5">
-        <v>88.8</v>
+        <v>91</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>95.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>826000</v>
+        <v>423000</v>
       </c>
       <c r="G8" s="7">
-        <v>47000</v>
+        <v>110000</v>
       </c>
       <c r="H8" s="7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I8" s="7">
-        <v>49500</v>
+        <v>88000</v>
       </c>
       <c r="J8" s="5">
-        <v>85</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>94.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>595000</v>
+        <v>862000</v>
       </c>
       <c r="G9" s="7">
-        <v>31000</v>
+        <v>36000</v>
       </c>
       <c r="H9" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="7">
-        <v>45167</v>
+        <v>47571</v>
       </c>
       <c r="J9" s="5">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>93.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>831000</v>
+        <v>355000</v>
       </c>
       <c r="G10" s="7">
-        <v>34000</v>
+        <v>42000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="7">
-        <v>44000</v>
+        <v>25571</v>
       </c>
       <c r="J10" s="5">
-        <v>82.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>88.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>536000</v>
+        <v>610000</v>
       </c>
       <c r="G11" s="7">
-        <v>51000</v>
+        <v>15000</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
-        <v>49667</v>
+        <v>40857</v>
       </c>
       <c r="J11" s="5">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>99.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>313000</v>
+        <v>447000</v>
       </c>
       <c r="G12" s="7">
-        <v>37000</v>
+        <v>15000</v>
       </c>
       <c r="H12" s="7">
         <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>22833</v>
+        <v>40000</v>
       </c>
       <c r="J12" s="5">
-        <v>80.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>92.09999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>432000</v>
+        <v>572000</v>
       </c>
       <c r="G13" s="7">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>45000</v>
+        <v>47714</v>
       </c>
       <c r="J13" s="5">
-        <v>79.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>680000</v>
+        <v>216000</v>
       </c>
       <c r="G14" s="7">
-        <v>94000</v>
+        <v>33000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
-        <v>36167</v>
+        <v>15571</v>
       </c>
       <c r="J14" s="5">
-        <v>79.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>96.5</v>
+        <v>89.7</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>284000</v>
+        <v>832000</v>
       </c>
       <c r="G15" s="7">
-        <v>26000</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>24167</v>
+        <v>37857</v>
       </c>
       <c r="J15" s="5">
-        <v>79.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>98.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>228000</v>
+        <v>179000</v>
       </c>
       <c r="G16" s="7">
-        <v>27000</v>
+        <v>14000</v>
       </c>
       <c r="H16" s="7">
         <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>19667</v>
+        <v>23667</v>
       </c>
       <c r="J16" s="5">
-        <v>79.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>91.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>323000</v>
+        <v>111000</v>
       </c>
       <c r="G17" s="7">
-        <v>13000</v>
+        <v>19000</v>
       </c>
       <c r="H17" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>34333</v>
+        <v>11286</v>
       </c>
       <c r="J17" s="5">
-        <v>79</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>100</v>
+        <v>83.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>152000</v>
+        <v>458000</v>
       </c>
       <c r="G18" s="7">
-        <v>22000</v>
+        <v>27000</v>
       </c>
       <c r="H18" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I18" s="7">
-        <v>14333</v>
+        <v>42143</v>
       </c>
       <c r="J18" s="5">
-        <v>78.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>98.3</v>
+        <v>97.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>165000</v>
+        <v>127000</v>
       </c>
       <c r="G19" s="7">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="H19" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>25600</v>
+        <v>10571</v>
       </c>
       <c r="J19" s="5">
-        <v>78.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>95.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>207000</v>
+        <v>731000</v>
       </c>
       <c r="G20" s="7">
-        <v>19000</v>
+        <v>51000</v>
       </c>
       <c r="H20" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" s="7">
-        <v>22667</v>
+        <v>38286</v>
       </c>
       <c r="J20" s="5">
-        <v>78.40000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>99</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>167000</v>
+        <v>299000</v>
       </c>
       <c r="G21" s="7">
-        <v>19000</v>
+        <v>33000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>15000</v>
+        <v>18857</v>
       </c>
       <c r="J21" s="5">
-        <v>78.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>95.8</v>
+        <v>91.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>373000</v>
+        <v>221000</v>
       </c>
       <c r="G22" s="7">
-        <v>30000</v>
+        <v>14000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>20500</v>
+        <v>21429</v>
       </c>
       <c r="J22" s="5">
-        <v>77.8</v>
+        <v>75.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>83.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>431000</v>
+        <v>122000</v>
       </c>
       <c r="G23" s="7">
-        <v>29000</v>
+        <v>17000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I23" s="7">
-        <v>44667</v>
+        <v>8857</v>
       </c>
       <c r="J23" s="5">
-        <v>77.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>93.2</v>
+        <v>89.5</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>313000</v>
+        <v>356000</v>
       </c>
       <c r="G24" s="7">
-        <v>17000</v>
+        <v>42000</v>
       </c>
       <c r="H24" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I24" s="7">
-        <v>23500</v>
+        <v>24429</v>
       </c>
       <c r="J24" s="5">
-        <v>77.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>443000</v>
+        <v>295000</v>
       </c>
       <c r="G25" s="7">
-        <v>18000</v>
+        <v>11000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>25333</v>
+        <v>22286</v>
       </c>
       <c r="J25" s="5">
-        <v>76.3</v>
+        <v>75.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>97.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>237000</v>
+        <v>458000</v>
       </c>
       <c r="G26" s="7">
-        <v>22000</v>
+        <v>15000</v>
       </c>
       <c r="H26" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>10500</v>
+        <v>18571</v>
       </c>
       <c r="J26" s="5">
-        <v>76</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>94.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>219000</v>
+        <v>246000</v>
       </c>
       <c r="G27" s="7">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="H27" s="7">
         <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>17167</v>
+        <v>19833</v>
       </c>
       <c r="J27" s="5">
-        <v>76</v>
+        <v>74.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>95.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>232000</v>
+        <v>144000</v>
       </c>
       <c r="G28" s="7">
-        <v>28000</v>
+        <v>31000</v>
       </c>
       <c r="H28" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>21000</v>
+        <v>857</v>
       </c>
       <c r="J28" s="5">
-        <v>75.8</v>
+        <v>74.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>590000</v>
+        <v>124000</v>
       </c>
       <c r="G29" s="7">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="H29" s="7">
         <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>22333</v>
+        <v>9167</v>
       </c>
       <c r="J29" s="5">
-        <v>75.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>90.8</v>
+        <v>85</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>314000</v>
+        <v>315000</v>
       </c>
       <c r="G30" s="7">
-        <v>47000</v>
+        <v>-8000</v>
       </c>
       <c r="H30" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I30" s="7">
-        <v>21500</v>
+        <v>28286</v>
       </c>
       <c r="J30" s="5">
-        <v>75.3</v>
+        <v>73.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>91.7</v>
+        <v>89.2</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>443000</v>
+        <v>381000</v>
       </c>
       <c r="G31" s="7">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>19167</v>
+        <v>18714</v>
       </c>
       <c r="J31" s="5">
-        <v>75.2</v>
+        <v>73.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>94.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>183000</v>
+        <v>102000</v>
       </c>
       <c r="G32" s="7">
-        <v>14000</v>
+        <v>11000</v>
       </c>
       <c r="H32" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>12667</v>
+        <v>4143</v>
       </c>
       <c r="J32" s="5">
-        <v>75.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>85.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>578000</v>
+        <v>448000</v>
       </c>
       <c r="G33" s="7">
-        <v>-12000</v>
+        <v>5000</v>
       </c>
       <c r="H33" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" s="7">
-        <v>30167</v>
+        <v>22429</v>
       </c>
       <c r="J33" s="5">
-        <v>74.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>91.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>314000</v>
+        <v>322000</v>
       </c>
       <c r="G34" s="7">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="H34" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" s="7">
-        <v>15833</v>
+        <v>14714</v>
       </c>
       <c r="J34" s="5">
-        <v>74.3</v>
+        <v>73.2</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>94.3</v>
+        <v>91.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>108000</v>
+        <v>117000</v>
       </c>
       <c r="G35" s="7">
-        <v>17000</v>
+        <v>9000</v>
       </c>
       <c r="H35" s="7">
         <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>9167</v>
+        <v>12000</v>
       </c>
       <c r="J35" s="5">
-        <v>74.2</v>
+        <v>73.2</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>96</v>
+        <v>89.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>108000</v>
+        <v>225000</v>
       </c>
       <c r="G36" s="7">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="H36" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>12600</v>
+        <v>15571</v>
       </c>
       <c r="J36" s="5">
-        <v>74</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>94.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>102000</v>
+        <v>248000</v>
       </c>
       <c r="G37" s="7">
         <v>11000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I37" s="7">
-        <v>7833</v>
+        <v>10571</v>
       </c>
       <c r="J37" s="5">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>94.3</v>
+        <v>83.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>105000</v>
+        <v>2500000</v>
       </c>
       <c r="G38" s="7">
         <v>33000</v>
       </c>
       <c r="H38" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7">
-        <v>7500</v>
+        <v>27857</v>
       </c>
       <c r="J38" s="5">
-        <v>73.7</v>
+        <v>72.8</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>94.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>100000</v>
+        <v>199000</v>
       </c>
       <c r="G39" s="7">
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="H39" s="7">
         <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>6000</v>
+        <v>10167</v>
       </c>
       <c r="J39" s="5">
-        <v>73.3</v>
+        <v>72.8</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>91.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>149000</v>
+        <v>452000</v>
       </c>
       <c r="G40" s="7">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="H40" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I40" s="7">
-        <v>11167</v>
+        <v>7429</v>
       </c>
       <c r="J40" s="5">
-        <v>73</v>
+        <v>72.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1945,30 +1945,28 @@
       <c r="A41" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="5">
-        <v>9</v>
-      </c>
+      <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>90.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>141000</v>
+        <v>324000</v>
       </c>
       <c r="G41" s="7">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="H41" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>10667</v>
+        <v>21250</v>
       </c>
       <c r="J41" s="5">
-        <v>72.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,28 +1978,30 @@
       <c r="A42" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="5"/>
+      <c r="B42" s="5">
+        <v>9</v>
+      </c>
       <c r="C42" s="5">
-        <v>83.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>2467000</v>
+        <v>151000</v>
       </c>
       <c r="G42" s="7">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I42" s="7">
-        <v>27000</v>
+        <v>10571</v>
       </c>
       <c r="J42" s="5">
-        <v>72.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>86.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>266000</v>
+        <v>118000</v>
       </c>
       <c r="G43" s="7">
-        <v>15000</v>
+        <v>7000</v>
       </c>
       <c r="H43" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>16500</v>
+        <v>9286</v>
       </c>
       <c r="J43" s="5">
-        <v>71.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>89.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>245000</v>
+        <v>578000</v>
       </c>
       <c r="G44" s="7">
-        <v>7000</v>
+        <v>-12000</v>
       </c>
       <c r="H44" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="7">
-        <v>10333</v>
+        <v>17429</v>
       </c>
       <c r="J44" s="5">
-        <v>71.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>88.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>241000</v>
+        <v>157000</v>
       </c>
       <c r="G45" s="7">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H45" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I45" s="7">
-        <v>11167</v>
+        <v>13000</v>
       </c>
       <c r="J45" s="5">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>88.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>240000</v>
+        <v>555000</v>
       </c>
       <c r="G46" s="7">
-        <v>10000</v>
+        <v>-23000</v>
       </c>
       <c r="H46" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" s="7">
-        <v>11167</v>
+        <v>22571</v>
       </c>
       <c r="J46" s="5">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>88.3</v>
+        <v>92.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>331000</v>
+        <v>120000</v>
       </c>
       <c r="G47" s="7">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="H47" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I47" s="7">
-        <v>11500</v>
+        <v>12000</v>
       </c>
       <c r="J47" s="5">
-        <v>71.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>96.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>108000</v>
+        <v>109000</v>
       </c>
       <c r="G48" s="7">
-        <v>15000</v>
+        <v>7000</v>
       </c>
       <c r="H48" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I48" s="7">
-        <v>12000</v>
+        <v>7714</v>
       </c>
       <c r="J48" s="5">
-        <v>71.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>378000</v>
+        <v>228000</v>
       </c>
       <c r="G49" s="7">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I49" s="7">
-        <v>32000</v>
+        <v>16857</v>
       </c>
       <c r="J49" s="5">
-        <v>70.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>87.7</v>
+        <v>82.3</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>195000</v>
+        <v>343000</v>
       </c>
       <c r="G50" s="7">
-        <v>4000</v>
+        <v>30000</v>
       </c>
       <c r="H50" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I50" s="7">
-        <v>9167</v>
+        <v>24429</v>
       </c>
       <c r="J50" s="5">
-        <v>70.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>87.3</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>111000</v>
+        <v>337000</v>
       </c>
       <c r="G51" s="7">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H51" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" s="7">
-        <v>9667</v>
+        <v>10714</v>
       </c>
       <c r="J51" s="5">
-        <v>70.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>91.2</v>
+        <v>89.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>104000</v>
+        <v>109000</v>
       </c>
       <c r="G52" s="7">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="H52" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I52" s="7">
-        <v>8800</v>
+        <v>8714</v>
       </c>
       <c r="J52" s="5">
-        <v>70.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>80.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>507000</v>
+        <v>397000</v>
       </c>
       <c r="G53" s="7">
-        <v>10000</v>
+        <v>19000</v>
       </c>
       <c r="H53" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I53" s="7">
-        <v>24000</v>
+        <v>30143</v>
       </c>
       <c r="J53" s="5">
-        <v>70.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>89.7</v>
+        <v>88.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>422000</v>
+        <v>250000</v>
       </c>
       <c r="G54" s="7">
-        <v>23000</v>
+        <v>5000</v>
       </c>
       <c r="H54" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I54" s="7">
-        <v>3667</v>
+        <v>9571</v>
       </c>
       <c r="J54" s="5">
-        <v>70.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-07-31T10:08:42+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-01T07:59:37+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -85,142 +85,142 @@
     <t>刚证道混沌天帝，让我身化禁区？</t>
   </si>
   <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
     <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
-    <t>公安局长之扫黑风暴</t>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>穿越刘备，死后和我说这是型月？</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
     <t>重生后，姐姐非要嫁给我</t>
   </si>
   <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>国运班级求生：机电2班闹翻荒野</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
   </si>
   <si>
     <t>桃花美人村</t>
   </si>
   <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
+    <t>开局日军围城，系统让我当德皇</t>
+  </si>
+  <si>
+    <t>瘟疫模拟：开局投放Necroa</t>
   </si>
   <si>
     <t>科举：陛下！新科状元又惹事了！</t>
   </si>
   <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
+    <t>暑假失踪，开学归来成元婴老祖！</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
   </si>
   <si>
     <t>我提前三天被丢进了末世</t>
   </si>
   <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
-  </si>
-  <si>
-    <t>四合院，哈军工副院，部下李云龙</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
+    <t>规则怪谈：我即怪谈</t>
+  </si>
+  <si>
+    <t>率土之滨：什么叫军费百倍到账？</t>
+  </si>
+  <si>
+    <t>崩铁，穿越成怪兽，被爻光买回家</t>
+  </si>
+  <si>
+    <t>开局法相，未婚妻不退婚</t>
   </si>
   <si>
     <t>天幕直播：长乐公主被我吓哭了</t>
   </si>
   <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
-  </si>
-  <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
+    <t>moba：联盟是个运气游戏！</t>
+  </si>
+  <si>
+    <t>重生后，成了妹妹的专属爱物</t>
   </si>
   <si>
     <t>妖魔乱世：从造畜法开始左道成仙</t>
   </si>
   <si>
-    <t>买卖词条，打造非凡俱乐部</t>
-  </si>
-  <si>
-    <t>崩铁，穿越成怪兽，被爻光买回家</t>
-  </si>
-  <si>
-    <t>瘟疫模拟：开局投放Necroa</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>开局法相，未婚妻不退婚</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>国运班级求生：机电2班闹翻荒野</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>穿越刘备，死后和我说这是型月？</t>
+    <t>全民县令：我看广告无限刷资源</t>
+  </si>
+  <si>
+    <t>死对头证道成仙了，怎么办？！</t>
   </si>
   <si>
     <t>希腊神话：从成为微风之神开始</t>
   </si>
   <si>
-    <t>率土之滨：什么叫军费百倍到账？</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
+    <t>僵尸世界：开局拜师雷电法王</t>
+  </si>
+  <si>
+    <t>我真不想修仙啊！</t>
+  </si>
+  <si>
+    <t>暑假兼职赶尸，749局找上门！</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
   </si>
   <si>
     <t>末法时代出飞僵，可我是石坚啊</t>
-  </si>
-  <si>
-    <t>什么叫高考满分，但人失踪了？</t>
-  </si>
-  <si>
-    <t>公路求生：最速传说</t>
-  </si>
-  <si>
-    <t>暑假兼职赶尸，749局找上门！</t>
-  </si>
-  <si>
-    <t>封印神源百万年，悟性每天翻倍</t>
-  </si>
-  <si>
-    <t>全民县令：我看广告无限刷资源</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>暑假失踪，开学归来成元婴老祖！</t>
-  </si>
-  <si>
-    <t>僵尸世界：开局拜师雷电法王</t>
-  </si>
-  <si>
-    <t>我开启的宝箱品质永远加3</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>2441000</v>
+        <v>2760000</v>
       </c>
       <c r="G5" s="7">
-        <v>304000</v>
+        <v>319000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="7">
-        <v>164286</v>
+        <v>183625</v>
       </c>
       <c r="J5" s="5">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>92.7</v>
+        <v>89.8</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1083000</v>
+        <v>1212000</v>
       </c>
       <c r="G6" s="7">
-        <v>161000</v>
+        <v>129000</v>
       </c>
       <c r="H6" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="7">
-        <v>84857</v>
+        <v>90375</v>
       </c>
       <c r="J6" s="5">
-        <v>92.2</v>
+        <v>92</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>84.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1470000</v>
+        <v>1528000</v>
       </c>
       <c r="G7" s="7">
-        <v>64000</v>
+        <v>58000</v>
       </c>
       <c r="H7" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="7">
-        <v>97857</v>
+        <v>92875</v>
       </c>
       <c r="J7" s="5">
-        <v>91</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>423000</v>
+        <v>513000</v>
       </c>
       <c r="G8" s="7">
-        <v>110000</v>
+        <v>90000</v>
       </c>
       <c r="H8" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
-        <v>88000</v>
+        <v>88667</v>
       </c>
       <c r="J8" s="5">
-        <v>85.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>862000</v>
+        <v>454000</v>
       </c>
       <c r="G9" s="7">
-        <v>36000</v>
+        <v>99000</v>
       </c>
       <c r="H9" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>47571</v>
+        <v>34750</v>
       </c>
       <c r="J9" s="5">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99.5</v>
+        <v>92.2</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>355000</v>
+        <v>883000</v>
       </c>
       <c r="G10" s="7">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="H10" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="7">
-        <v>25571</v>
+        <v>44250</v>
       </c>
       <c r="J10" s="5">
-        <v>81.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>91.40000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>610000</v>
+        <v>372000</v>
       </c>
       <c r="G11" s="7">
-        <v>15000</v>
+        <v>73000</v>
       </c>
       <c r="H11" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7">
-        <v>40857</v>
+        <v>25625</v>
       </c>
       <c r="J11" s="5">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>447000</v>
+        <v>250000</v>
       </c>
       <c r="G12" s="7">
-        <v>15000</v>
+        <v>34000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I12" s="7">
-        <v>40000</v>
+        <v>17875</v>
       </c>
       <c r="J12" s="5">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>85.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>572000</v>
+        <v>457000</v>
       </c>
       <c r="G13" s="7">
-        <v>36000</v>
+        <v>10000</v>
       </c>
       <c r="H13" s="7">
         <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>47714</v>
+        <v>35714</v>
       </c>
       <c r="J13" s="5">
-        <v>79</v>
+        <v>77.8</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>216000</v>
+        <v>357000</v>
       </c>
       <c r="G14" s="7">
         <v>33000</v>
       </c>
       <c r="H14" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>15571</v>
+        <v>23600</v>
       </c>
       <c r="J14" s="5">
-        <v>78.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>89.7</v>
+        <v>94.8</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>832000</v>
+        <v>271000</v>
       </c>
       <c r="G15" s="7">
-        <v>1000</v>
+        <v>25000</v>
       </c>
       <c r="H15" s="7">
         <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>37857</v>
+        <v>20571</v>
       </c>
       <c r="J15" s="5">
-        <v>78.8</v>
+        <v>77.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>94.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>179000</v>
+        <v>824000</v>
       </c>
       <c r="G16" s="7">
-        <v>14000</v>
+        <v>-8000</v>
       </c>
       <c r="H16" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>23667</v>
+        <v>32125</v>
       </c>
       <c r="J16" s="5">
-        <v>78</v>
+        <v>76.8</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>98.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>111000</v>
+        <v>601000</v>
       </c>
       <c r="G17" s="7">
-        <v>19000</v>
+        <v>-9000</v>
       </c>
       <c r="H17" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7">
-        <v>11286</v>
+        <v>34625</v>
       </c>
       <c r="J17" s="5">
-        <v>77.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,23 +1188,23 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>83.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>458000</v>
+        <v>496000</v>
       </c>
       <c r="G18" s="7">
-        <v>27000</v>
+        <v>44000</v>
       </c>
       <c r="H18" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7">
-        <v>42143</v>
+        <v>12000</v>
       </c>
       <c r="J18" s="5">
         <v>76.59999999999999</v>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>97.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>127000</v>
+        <v>403000</v>
       </c>
       <c r="G19" s="7">
-        <v>19000</v>
+        <v>47000</v>
       </c>
       <c r="H19" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I19" s="7">
-        <v>10571</v>
+        <v>27250</v>
       </c>
       <c r="J19" s="5">
-        <v>76.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>84.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>731000</v>
+        <v>483000</v>
       </c>
       <c r="G20" s="7">
-        <v>51000</v>
+        <v>25000</v>
       </c>
       <c r="H20" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>38286</v>
+        <v>40000</v>
       </c>
       <c r="J20" s="5">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>93.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>299000</v>
+        <v>311000</v>
       </c>
       <c r="G21" s="7">
-        <v>33000</v>
+        <v>16000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" s="7">
-        <v>18857</v>
+        <v>21500</v>
       </c>
       <c r="J21" s="5">
-        <v>75.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>91.8</v>
+        <v>92</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>221000</v>
+        <v>189000</v>
       </c>
       <c r="G22" s="7">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="H22" s="7">
         <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>21429</v>
+        <v>21714</v>
       </c>
       <c r="J22" s="5">
-        <v>75.8</v>
+        <v>76</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>97.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>122000</v>
+        <v>177000</v>
       </c>
       <c r="G23" s="7">
-        <v>17000</v>
+        <v>33000</v>
       </c>
       <c r="H23" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I23" s="7">
-        <v>8857</v>
+        <v>4875</v>
       </c>
       <c r="J23" s="5">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>89.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>356000</v>
+        <v>770000</v>
       </c>
       <c r="G24" s="7">
-        <v>42000</v>
+        <v>39000</v>
       </c>
       <c r="H24" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="7">
-        <v>24429</v>
+        <v>38375</v>
       </c>
       <c r="J24" s="5">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>295000</v>
+        <v>154000</v>
       </c>
       <c r="G25" s="7">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>22286</v>
+        <v>25750</v>
       </c>
       <c r="J25" s="5">
-        <v>75.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>91.7</v>
+        <v>91.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>458000</v>
+        <v>235000</v>
       </c>
       <c r="G26" s="7">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="H26" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I26" s="7">
-        <v>18571</v>
+        <v>20500</v>
       </c>
       <c r="J26" s="5">
-        <v>75.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>90.5</v>
+        <v>87.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>246000</v>
+        <v>315000</v>
       </c>
       <c r="G27" s="7">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I27" s="7">
-        <v>19833</v>
+        <v>24750</v>
       </c>
       <c r="J27" s="5">
-        <v>74.7</v>
+        <v>74.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>99.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>144000</v>
+        <v>222000</v>
       </c>
       <c r="G28" s="7">
-        <v>31000</v>
+        <v>23000</v>
       </c>
       <c r="H28" s="7">
         <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>857</v>
+        <v>12000</v>
       </c>
       <c r="J28" s="5">
-        <v>74.7</v>
+        <v>74.3</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>94.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>124000</v>
+        <v>142000</v>
       </c>
       <c r="G29" s="7">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" s="7">
-        <v>9167</v>
+        <v>11125</v>
       </c>
       <c r="J29" s="5">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>85</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>315000</v>
+        <v>574000</v>
       </c>
       <c r="G30" s="7">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="H30" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I30" s="7">
-        <v>28286</v>
+        <v>42000</v>
       </c>
       <c r="J30" s="5">
-        <v>73.8</v>
+        <v>74</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>89.2</v>
+        <v>93.3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>381000</v>
+        <v>103000</v>
       </c>
       <c r="G31" s="7">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H31" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>18714</v>
+        <v>10000</v>
       </c>
       <c r="J31" s="5">
-        <v>73.7</v>
+        <v>73.8</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>95.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>102000</v>
+        <v>127000</v>
       </c>
       <c r="G32" s="7">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="7">
         <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>4143</v>
+        <v>11714</v>
       </c>
       <c r="J32" s="5">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>86.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>448000</v>
+        <v>119000</v>
       </c>
       <c r="G33" s="7">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="H33" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I33" s="7">
-        <v>22429</v>
+        <v>10875</v>
       </c>
       <c r="J33" s="5">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>90.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>322000</v>
+        <v>119000</v>
       </c>
       <c r="G34" s="7">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H34" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="7">
-        <v>14714</v>
+        <v>8875</v>
       </c>
       <c r="J34" s="5">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,23 +1749,23 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>91.2</v>
+        <v>83.5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>117000</v>
+        <v>2537000</v>
       </c>
       <c r="G35" s="7">
-        <v>9000</v>
+        <v>37000</v>
       </c>
       <c r="H35" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>12000</v>
+        <v>29000</v>
       </c>
       <c r="J35" s="5">
         <v>73.2</v>
@@ -1782,23 +1782,23 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>89.5</v>
+        <v>88.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>225000</v>
+        <v>387000</v>
       </c>
       <c r="G36" s="7">
         <v>6000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I36" s="7">
-        <v>15571</v>
+        <v>17125</v>
       </c>
       <c r="J36" s="5">
         <v>73.09999999999999</v>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>91.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>248000</v>
+        <v>232000</v>
       </c>
       <c r="G37" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I37" s="7">
-        <v>10571</v>
+        <v>14500</v>
       </c>
       <c r="J37" s="5">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>83.3</v>
+        <v>91.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>2500000</v>
+        <v>133000</v>
       </c>
       <c r="G38" s="7">
-        <v>33000</v>
+        <v>11000</v>
       </c>
       <c r="H38" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>27857</v>
+        <v>9125</v>
       </c>
       <c r="J38" s="5">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>91.3</v>
+        <v>84.7</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>199000</v>
+        <v>405000</v>
       </c>
       <c r="G39" s="7">
-        <v>15000</v>
+        <v>123000</v>
       </c>
       <c r="H39" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I39" s="7">
-        <v>10167</v>
+        <v>22625</v>
       </c>
       <c r="J39" s="5">
-        <v>72.8</v>
+        <v>72.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>92.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>452000</v>
+        <v>125000</v>
       </c>
       <c r="G40" s="7">
-        <v>30000</v>
+        <v>7000</v>
       </c>
       <c r="H40" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I40" s="7">
-        <v>7429</v>
+        <v>9000</v>
       </c>
       <c r="J40" s="5">
-        <v>72.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>94.7</v>
+        <v>88.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>324000</v>
+        <v>325000</v>
       </c>
       <c r="G41" s="7">
-        <v>24000</v>
+        <v>3000</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I41" s="7">
-        <v>21250</v>
+        <v>13250</v>
       </c>
       <c r="J41" s="5">
-        <v>72.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1978,30 +1978,28 @@
       <c r="A42" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="5">
-        <v>9</v>
-      </c>
+      <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>90.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>151000</v>
+        <v>255000</v>
       </c>
       <c r="G42" s="7">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="H42" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I42" s="7">
-        <v>10571</v>
+        <v>10125</v>
       </c>
       <c r="J42" s="5">
-        <v>72.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>90.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>118000</v>
+        <v>133000</v>
       </c>
       <c r="G43" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H43" s="7">
         <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>9286</v>
+        <v>9143</v>
       </c>
       <c r="J43" s="5">
-        <v>72.3</v>
+        <v>72</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>578000</v>
+        <v>106000</v>
       </c>
       <c r="G44" s="7">
-        <v>-12000</v>
+        <v>9000</v>
       </c>
       <c r="H44" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I44" s="7">
-        <v>17429</v>
+        <v>7625</v>
       </c>
       <c r="J44" s="5">
-        <v>72.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>88.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>157000</v>
+        <v>304000</v>
       </c>
       <c r="G45" s="7">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="H45" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I45" s="7">
-        <v>13000</v>
+        <v>10125</v>
       </c>
       <c r="J45" s="5">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>83.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>555000</v>
+        <v>111000</v>
       </c>
       <c r="G46" s="7">
-        <v>-23000</v>
+        <v>9000</v>
       </c>
       <c r="H46" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I46" s="7">
-        <v>22571</v>
+        <v>4750</v>
       </c>
       <c r="J46" s="5">
-        <v>71.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>92.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>120000</v>
+        <v>369000</v>
       </c>
       <c r="G47" s="7">
-        <v>12000</v>
+        <v>26000</v>
       </c>
       <c r="H47" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>12000</v>
+        <v>24625</v>
       </c>
       <c r="J47" s="5">
-        <v>71.8</v>
+        <v>71.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>90.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>109000</v>
+        <v>261000</v>
       </c>
       <c r="G48" s="7">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>7714</v>
+        <v>8125</v>
       </c>
       <c r="J48" s="5">
-        <v>71.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,28 +2209,30 @@
       <c r="A49" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B49" s="5"/>
+      <c r="B49" s="5">
+        <v>9</v>
+      </c>
       <c r="C49" s="5">
-        <v>86</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>228000</v>
+        <v>158000</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H49" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I49" s="7">
-        <v>16857</v>
+        <v>10125</v>
       </c>
       <c r="J49" s="5">
-        <v>71.5</v>
+        <v>71</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>82.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>343000</v>
+        <v>409000</v>
       </c>
       <c r="G50" s="7">
-        <v>30000</v>
+        <v>12000</v>
       </c>
       <c r="H50" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I50" s="7">
-        <v>24429</v>
+        <v>27875</v>
       </c>
       <c r="J50" s="5">
-        <v>71.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>88.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>337000</v>
+        <v>388000</v>
       </c>
       <c r="G51" s="7">
-        <v>6000</v>
+        <v>73000</v>
       </c>
       <c r="H51" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I51" s="7">
-        <v>10714</v>
+        <v>16250</v>
       </c>
       <c r="J51" s="5">
-        <v>71.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>89.5</v>
+        <v>88.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>109000</v>
+        <v>114000</v>
       </c>
       <c r="G52" s="7">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="H52" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I52" s="7">
-        <v>8714</v>
+        <v>7375</v>
       </c>
       <c r="J52" s="5">
-        <v>71.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>78.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>397000</v>
+        <v>337000</v>
       </c>
       <c r="G53" s="7">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="H53" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>30143</v>
+        <v>9375</v>
       </c>
       <c r="J53" s="5">
-        <v>70.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>88.2</v>
+        <v>85.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>250000</v>
+        <v>158000</v>
       </c>
       <c r="G54" s="7">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H54" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7">
-        <v>9571</v>
+        <v>11500</v>
       </c>
       <c r="J54" s="5">
-        <v>70.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-01T07:59:37+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-02T07:59:11+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -91,136 +91,136 @@
     <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>穿越刘备，死后和我说这是型月？</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
+  </si>
+  <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>重生后，姐姐非要嫁给我</t>
+  </si>
+  <si>
     <t>系统想害我，我选择上交国家</t>
   </si>
   <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
     <t>编外法医：重案组抢疯了！</t>
   </si>
   <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
-  </si>
-  <si>
-    <t>穿越刘备，死后和我说这是型月？</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>穿书百合文，我只想安稳苟到结局</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>国运班级求生：机电2班闹翻荒野</t>
+  </si>
+  <si>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>封印神源百万年，悟性每天翻倍</t>
+  </si>
+  <si>
+    <t>暑假失踪，开学归来成元婴老祖！</t>
   </si>
   <si>
     <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
-    <t>重生后，姐姐非要嫁给我</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
+    <t>妖魔乱世：从造畜法开始左道成仙</t>
+  </si>
+  <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>桃花美人村</t>
+  </si>
+  <si>
+    <t>你写的小说，给我惹了不少麻烦呢</t>
+  </si>
+  <si>
+    <t>瘟疫模拟：开局投放Necroa</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
+  </si>
+  <si>
+    <t>科举：陛下！新科状元又惹事了！</t>
+  </si>
+  <si>
+    <t>我真不想修仙啊！</t>
+  </si>
+  <si>
+    <t>开局法相，未婚妻不退婚</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>重生后，成了妹妹的专属爱物</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>我的修仙马甲，被小兕子曝光了</t>
+  </si>
+  <si>
+    <t>死对头证道成仙了，怎么办？！</t>
+  </si>
+  <si>
+    <t>moba：联盟是个运气游戏！</t>
   </si>
   <si>
     <t>我创立的组织，被重生者曝光了！</t>
   </si>
   <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
-  </si>
-  <si>
-    <t>国运班级求生：机电2班闹翻荒野</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>桃花美人村</t>
-  </si>
-  <si>
-    <t>开局日军围城，系统让我当德皇</t>
-  </si>
-  <si>
-    <t>瘟疫模拟：开局投放Necroa</t>
-  </si>
-  <si>
-    <t>科举：陛下！新科状元又惹事了！</t>
-  </si>
-  <si>
-    <t>暑假失踪，开学归来成元婴老祖！</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
+    <t>公路求生：最速传说</t>
+  </si>
+  <si>
+    <t>穿到女频，整顿满城霸总</t>
+  </si>
+  <si>
+    <t>崩铁，穿越成怪兽，被爻光买回家</t>
+  </si>
+  <si>
+    <t>天幕洛神赋，曹家父子社死</t>
   </si>
   <si>
     <t>有钱有势回县城，开局睡了白月光</t>
   </si>
   <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>我提前三天被丢进了末世</t>
-  </si>
-  <si>
-    <t>规则怪谈：我即怪谈</t>
-  </si>
-  <si>
-    <t>率土之滨：什么叫军费百倍到账？</t>
-  </si>
-  <si>
-    <t>崩铁，穿越成怪兽，被爻光买回家</t>
-  </si>
-  <si>
-    <t>开局法相，未婚妻不退婚</t>
-  </si>
-  <si>
     <t>天幕直播：长乐公主被我吓哭了</t>
   </si>
   <si>
-    <t>moba：联盟是个运气游戏！</t>
-  </si>
-  <si>
-    <t>重生后，成了妹妹的专属爱物</t>
-  </si>
-  <si>
-    <t>妖魔乱世：从造畜法开始左道成仙</t>
-  </si>
-  <si>
-    <t>全民县令：我看广告无限刷资源</t>
-  </si>
-  <si>
-    <t>死对头证道成仙了，怎么办？！</t>
-  </si>
-  <si>
-    <t>希腊神话：从成为微风之神开始</t>
-  </si>
-  <si>
-    <t>僵尸世界：开局拜师雷电法王</t>
-  </si>
-  <si>
-    <t>我真不想修仙啊！</t>
-  </si>
-  <si>
-    <t>暑假兼职赶尸，749局找上门！</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>末法时代出飞僵，可我是石坚啊</t>
+    <t>什么天幕？明明是古人破防日记</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>94.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>2760000</v>
+        <v>2940000</v>
       </c>
       <c r="G5" s="7">
-        <v>319000</v>
+        <v>180000</v>
       </c>
       <c r="H5" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="7">
-        <v>183625</v>
+        <v>183222</v>
       </c>
       <c r="J5" s="5">
-        <v>96.90000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>89.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1212000</v>
+        <v>1309000</v>
       </c>
       <c r="G6" s="7">
-        <v>129000</v>
+        <v>97000</v>
       </c>
       <c r="H6" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>90375</v>
+        <v>91111</v>
       </c>
       <c r="J6" s="5">
-        <v>92</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>84</v>
+        <v>85.8</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1528000</v>
+        <v>1613000</v>
       </c>
       <c r="G7" s="7">
-        <v>58000</v>
+        <v>85000</v>
       </c>
       <c r="H7" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7">
-        <v>92875</v>
+        <v>92000</v>
       </c>
       <c r="J7" s="5">
-        <v>89.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>513000</v>
+        <v>568000</v>
       </c>
       <c r="G8" s="7">
-        <v>90000</v>
+        <v>55000</v>
       </c>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7">
-        <v>88667</v>
+        <v>80250</v>
       </c>
       <c r="J8" s="5">
-        <v>89.2</v>
+        <v>89.8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -898,19 +898,19 @@
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>454000</v>
+        <v>534000</v>
       </c>
       <c r="G9" s="7">
-        <v>99000</v>
+        <v>80000</v>
       </c>
       <c r="H9" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" s="7">
-        <v>34750</v>
+        <v>39778</v>
       </c>
       <c r="J9" s="5">
-        <v>83.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>92.2</v>
+        <v>91</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>883000</v>
+        <v>894000</v>
       </c>
       <c r="G10" s="7">
-        <v>21000</v>
+        <v>11000</v>
       </c>
       <c r="H10" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>44250</v>
+        <v>40556</v>
       </c>
       <c r="J10" s="5">
-        <v>81.8</v>
+        <v>80.2</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>97.90000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>372000</v>
+        <v>299000</v>
       </c>
       <c r="G11" s="7">
-        <v>73000</v>
+        <v>28000</v>
       </c>
       <c r="H11" s="7">
         <v>9</v>
       </c>
       <c r="I11" s="7">
-        <v>25625</v>
+        <v>21500</v>
       </c>
       <c r="J11" s="5">
-        <v>80.3</v>
+        <v>78.7</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>250000</v>
+        <v>384000</v>
       </c>
       <c r="G12" s="7">
-        <v>34000</v>
+        <v>27000</v>
       </c>
       <c r="H12" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>17875</v>
+        <v>24167</v>
       </c>
       <c r="J12" s="5">
-        <v>79.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,23 +1023,23 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>88.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>457000</v>
+        <v>545000</v>
       </c>
       <c r="G13" s="7">
-        <v>10000</v>
+        <v>49000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I13" s="7">
-        <v>35714</v>
+        <v>16111</v>
       </c>
       <c r="J13" s="5">
         <v>77.8</v>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>97.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>357000</v>
+        <v>175000</v>
       </c>
       <c r="G14" s="7">
-        <v>33000</v>
+        <v>21000</v>
       </c>
       <c r="H14" s="7">
         <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>23600</v>
+        <v>24800</v>
       </c>
       <c r="J14" s="5">
-        <v>77.3</v>
+        <v>77.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>271000</v>
+        <v>112000</v>
       </c>
       <c r="G15" s="7">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I15" s="7">
-        <v>20571</v>
+        <v>10889</v>
       </c>
       <c r="J15" s="5">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>88.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>824000</v>
+        <v>465000</v>
       </c>
       <c r="G16" s="7">
-        <v>-8000</v>
+        <v>8000</v>
       </c>
       <c r="H16" s="7">
         <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>32125</v>
+        <v>32250</v>
       </c>
       <c r="J16" s="5">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>87.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>601000</v>
+        <v>599000</v>
       </c>
       <c r="G17" s="7">
-        <v>-9000</v>
+        <v>-2000</v>
       </c>
       <c r="H17" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="7">
-        <v>34625</v>
+        <v>30556</v>
       </c>
       <c r="J17" s="5">
-        <v>76.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>97.40000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>496000</v>
+        <v>398000</v>
       </c>
       <c r="G18" s="7">
-        <v>44000</v>
+        <v>26000</v>
       </c>
       <c r="H18" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="7">
-        <v>12000</v>
+        <v>25667</v>
       </c>
       <c r="J18" s="5">
-        <v>76.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>90.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>403000</v>
+        <v>200000</v>
       </c>
       <c r="G19" s="7">
-        <v>47000</v>
+        <v>11000</v>
       </c>
       <c r="H19" s="7">
         <v>9</v>
       </c>
       <c r="I19" s="7">
-        <v>27250</v>
+        <v>20375</v>
       </c>
       <c r="J19" s="5">
-        <v>76.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>83.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>483000</v>
+        <v>265000</v>
       </c>
       <c r="G20" s="7">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I20" s="7">
-        <v>40000</v>
+        <v>17556</v>
       </c>
       <c r="J20" s="5">
-        <v>76.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>92.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>311000</v>
+        <v>506000</v>
       </c>
       <c r="G21" s="7">
-        <v>16000</v>
+        <v>23000</v>
       </c>
       <c r="H21" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21" s="7">
-        <v>21500</v>
+        <v>38111</v>
       </c>
       <c r="J21" s="5">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>92</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>189000</v>
+        <v>102000</v>
       </c>
       <c r="G22" s="7">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="7">
-        <v>21714</v>
+        <v>9500</v>
       </c>
       <c r="J22" s="5">
-        <v>76</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>99.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>177000</v>
+        <v>801000</v>
       </c>
       <c r="G23" s="7">
-        <v>33000</v>
+        <v>31000</v>
       </c>
       <c r="H23" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I23" s="7">
-        <v>4875</v>
+        <v>37556</v>
       </c>
       <c r="J23" s="5">
-        <v>76</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>83.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>770000</v>
+        <v>322000</v>
       </c>
       <c r="G24" s="7">
-        <v>39000</v>
+        <v>11000</v>
       </c>
       <c r="H24" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I24" s="7">
-        <v>38375</v>
+        <v>20333</v>
       </c>
       <c r="J24" s="5">
-        <v>75.7</v>
+        <v>74.7</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>98.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>154000</v>
+        <v>243000</v>
       </c>
       <c r="G25" s="7">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="H25" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I25" s="7">
-        <v>25750</v>
+        <v>13125</v>
       </c>
       <c r="J25" s="5">
-        <v>75.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>91.5</v>
+        <v>86</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>235000</v>
+        <v>441000</v>
       </c>
       <c r="G26" s="7">
-        <v>14000</v>
+        <v>38000</v>
       </c>
       <c r="H26" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I26" s="7">
-        <v>20500</v>
+        <v>28444</v>
       </c>
       <c r="J26" s="5">
-        <v>75.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>315000</v>
+        <v>246000</v>
       </c>
       <c r="G27" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H27" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>24750</v>
+        <v>19444</v>
       </c>
       <c r="J27" s="5">
-        <v>74.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,23 +1518,23 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>93.3</v>
+        <v>92.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>222000</v>
+        <v>236000</v>
       </c>
       <c r="G28" s="7">
-        <v>23000</v>
+        <v>14000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I28" s="7">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="J28" s="5">
         <v>74.3</v>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>93.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>142000</v>
+        <v>129000</v>
       </c>
       <c r="G29" s="7">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="H29" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I29" s="7">
-        <v>11125</v>
+        <v>9000</v>
       </c>
       <c r="J29" s="5">
-        <v>74.2</v>
+        <v>74</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>79.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>574000</v>
+        <v>798000</v>
       </c>
       <c r="G30" s="7">
-        <v>2000</v>
+        <v>-26000</v>
       </c>
       <c r="H30" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30" s="7">
-        <v>42000</v>
+        <v>25667</v>
       </c>
       <c r="J30" s="5">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>93.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>103000</v>
+        <v>123000</v>
       </c>
       <c r="G31" s="7">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I31" s="7">
-        <v>10000</v>
+        <v>5556</v>
       </c>
       <c r="J31" s="5">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>92.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>127000</v>
+        <v>315000</v>
       </c>
       <c r="G32" s="7">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I32" s="7">
-        <v>11714</v>
+        <v>22000</v>
       </c>
       <c r="J32" s="5">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>119000</v>
+        <v>574000</v>
       </c>
       <c r="G33" s="7">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I33" s="7">
-        <v>10875</v>
+        <v>37333</v>
       </c>
       <c r="J33" s="5">
-        <v>73.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>92.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>119000</v>
+        <v>177000</v>
       </c>
       <c r="G34" s="7">
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="H34" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I34" s="7">
-        <v>8875</v>
+        <v>10556</v>
       </c>
       <c r="J34" s="5">
-        <v>73.3</v>
+        <v>72.7</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>83.5</v>
+        <v>90.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>2537000</v>
+        <v>135000</v>
       </c>
       <c r="G35" s="7">
-        <v>37000</v>
+        <v>8000</v>
       </c>
       <c r="H35" s="7">
         <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>29000</v>
+        <v>11250</v>
       </c>
       <c r="J35" s="5">
-        <v>73.2</v>
+        <v>72.5</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>88.7</v>
+        <v>90.3</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>387000</v>
+        <v>153000</v>
       </c>
       <c r="G36" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H36" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I36" s="7">
-        <v>17125</v>
+        <v>11111</v>
       </c>
       <c r="J36" s="5">
-        <v>73.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>89.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>232000</v>
+        <v>125000</v>
       </c>
       <c r="G37" s="7">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="H37" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I37" s="7">
-        <v>14500</v>
+        <v>10333</v>
       </c>
       <c r="J37" s="5">
-        <v>73.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>91.3</v>
+        <v>86</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>133000</v>
+        <v>428000</v>
       </c>
       <c r="G38" s="7">
-        <v>11000</v>
+        <v>40000</v>
       </c>
       <c r="H38" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I38" s="7">
-        <v>9125</v>
+        <v>18889</v>
       </c>
       <c r="J38" s="5">
-        <v>72.5</v>
+        <v>72</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>84.7</v>
+        <v>89.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>405000</v>
+        <v>262000</v>
       </c>
       <c r="G39" s="7">
-        <v>123000</v>
+        <v>7000</v>
       </c>
       <c r="H39" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>22625</v>
+        <v>9778</v>
       </c>
       <c r="J39" s="5">
-        <v>72.2</v>
+        <v>71.8</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>90.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>125000</v>
+        <v>235000</v>
       </c>
       <c r="G40" s="7">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="H40" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I40" s="7">
-        <v>9000</v>
+        <v>13222</v>
       </c>
       <c r="J40" s="5">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>325000</v>
+        <v>2540000</v>
       </c>
       <c r="G41" s="7">
         <v>3000</v>
       </c>
       <c r="H41" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" s="7">
-        <v>13250</v>
+        <v>26111</v>
       </c>
       <c r="J41" s="5">
-        <v>72</v>
+        <v>71.7</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>255000</v>
+        <v>325000</v>
       </c>
       <c r="G42" s="7">
-        <v>7000</v>
+        <v>21000</v>
       </c>
       <c r="H42" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I42" s="7">
-        <v>10125</v>
+        <v>11333</v>
       </c>
       <c r="J42" s="5">
-        <v>72</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>90.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>133000</v>
+        <v>553000</v>
       </c>
       <c r="G43" s="7">
-        <v>9000</v>
+        <v>-1000</v>
       </c>
       <c r="H43" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I43" s="7">
-        <v>9143</v>
+        <v>10778</v>
       </c>
       <c r="J43" s="5">
-        <v>72</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>91.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>106000</v>
+        <v>307000</v>
       </c>
       <c r="G44" s="7">
-        <v>9000</v>
+        <v>39000</v>
       </c>
       <c r="H44" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I44" s="7">
-        <v>7625</v>
+        <v>15333</v>
       </c>
       <c r="J44" s="5">
-        <v>72</v>
+        <v>71.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>304000</v>
+        <v>267000</v>
       </c>
       <c r="G45" s="7">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="H45" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I45" s="7">
-        <v>10125</v>
+        <v>7889</v>
       </c>
       <c r="J45" s="5">
-        <v>71.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>91.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>111000</v>
+        <v>113000</v>
       </c>
       <c r="G46" s="7">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="H46" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I46" s="7">
-        <v>4750</v>
+        <v>7556</v>
       </c>
       <c r="J46" s="5">
-        <v>71.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>82.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>369000</v>
+        <v>187000</v>
       </c>
       <c r="G47" s="7">
-        <v>26000</v>
+        <v>10000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I47" s="7">
-        <v>24625</v>
+        <v>5444</v>
       </c>
       <c r="J47" s="5">
-        <v>71.3</v>
+        <v>71</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>89.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>261000</v>
+        <v>132000</v>
       </c>
       <c r="G48" s="7">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I48" s="7">
-        <v>8125</v>
+        <v>10286</v>
       </c>
       <c r="J48" s="5">
-        <v>71.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2209,30 +2209,28 @@
       <c r="A49" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B49" s="5">
-        <v>9</v>
-      </c>
+      <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>88.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>158000</v>
+        <v>966000</v>
       </c>
       <c r="G49" s="7">
-        <v>7000</v>
+        <v>46000</v>
       </c>
       <c r="H49" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I49" s="7">
-        <v>10125</v>
+        <v>16222</v>
       </c>
       <c r="J49" s="5">
-        <v>71</v>
+        <v>70.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>79.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>409000</v>
+        <v>326000</v>
       </c>
       <c r="G50" s="7">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="H50" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I50" s="7">
-        <v>27875</v>
+        <v>11889</v>
       </c>
       <c r="J50" s="5">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>84.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>388000</v>
+        <v>114000</v>
       </c>
       <c r="G51" s="7">
-        <v>73000</v>
+        <v>6000</v>
       </c>
       <c r="H51" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I51" s="7">
-        <v>16250</v>
+        <v>10333</v>
       </c>
       <c r="J51" s="5">
-        <v>70.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>88.2</v>
+        <v>85.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>114000</v>
+        <v>380000</v>
       </c>
       <c r="G52" s="7">
-        <v>5000</v>
+        <v>-7000</v>
       </c>
       <c r="H52" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I52" s="7">
-        <v>7375</v>
+        <v>14444</v>
       </c>
       <c r="J52" s="5">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>86.8</v>
+        <v>87.7</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>337000</v>
+        <v>139000</v>
       </c>
       <c r="G53" s="7">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H53" s="7">
         <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>9375</v>
+        <v>8750</v>
       </c>
       <c r="J53" s="5">
-        <v>70.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>85.8</v>
+        <v>88.3</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>158000</v>
+        <v>106000</v>
       </c>
       <c r="G54" s="7">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I54" s="7">
-        <v>11500</v>
+        <v>7333</v>
       </c>
       <c r="J54" s="5">
-        <v>70.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-02T07:59:11+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-03T12:44:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,154 +70,154 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>刚证道混沌天帝，让我身化禁区？</t>
+  </si>
+  <si>
+    <t>全球死考：刚下刑场你让我去考试</t>
+  </si>
+  <si>
     <t>诸神愚戏</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>全球死考：刚下刑场你让我去考试</t>
-  </si>
-  <si>
-    <t>刚证道混沌天帝，让我身化禁区？</t>
-  </si>
-  <si>
     <t>公安局长之扫黑风暴</t>
   </si>
   <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
     <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
-    <t>名义：开局我举报我自己</t>
+    <t>国运班级求生：机电2班闹翻荒野</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>死对头证道成仙了，怎么办？！</t>
+  </si>
+  <si>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
+  </si>
+  <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>妖魔乱世：从造畜法开始左道成仙</t>
+  </si>
+  <si>
+    <t>穿书百合文，我只想安稳苟到结局</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
   </si>
   <si>
     <t>穿越刘备，死后和我说这是型月？</t>
   </si>
   <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>开局四选一，我选成为沪圈少爷！</t>
-  </si>
-  <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
+    <t>捡来的妹妹修仙后，回来抢亲了</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>全民县令：我看广告无限刷资源</t>
+  </si>
+  <si>
+    <t>你写的小说，给我惹了不少麻烦呢</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>天幕直播：长乐公主被我吓哭了</t>
   </si>
   <si>
     <t>重生后，姐姐非要嫁给我</t>
   </si>
   <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>穿书百合文，我只想安稳苟到结局</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
-  </si>
-  <si>
-    <t>国运班级求生：机电2班闹翻荒野</t>
-  </si>
-  <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
+    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
+  </si>
+  <si>
+    <t>开局被魅魔收养，异世界尽情攻略</t>
+  </si>
+  <si>
+    <t>开局日军围城，系统让我当德皇</t>
   </si>
   <si>
     <t>封印神源百万年，悟性每天翻倍</t>
   </si>
   <si>
-    <t>暑假失踪，开学归来成元婴老祖！</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>妖魔乱世：从造畜法开始左道成仙</t>
+    <t>开局大限将至，我携帝兵问道禁区</t>
   </si>
   <si>
     <t>魔王叫我小同志，那就是世界错了</t>
   </si>
   <si>
-    <t>桃花美人村</t>
-  </si>
-  <si>
-    <t>你写的小说，给我惹了不少麻烦呢</t>
-  </si>
-  <si>
-    <t>瘟疫模拟：开局投放Necroa</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>科举：陛下！新科状元又惹事了！</t>
-  </si>
-  <si>
-    <t>我真不想修仙啊！</t>
-  </si>
-  <si>
-    <t>开局法相，未婚妻不退婚</t>
-  </si>
-  <si>
     <t>都末世了，你们还想当版本T0？</t>
   </si>
   <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>重生后，成了妹妹的专属爱物</t>
+    <t>天幕洛神赋，曹家父子社死</t>
   </si>
   <si>
     <t>我都宇宙之主了，你们还在地球？</t>
   </si>
   <si>
-    <t>我的修仙马甲，被小兕子曝光了</t>
-  </si>
-  <si>
-    <t>死对头证道成仙了，怎么办？！</t>
-  </si>
-  <si>
-    <t>moba：联盟是个运气游戏！</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
-  </si>
-  <si>
-    <t>公路求生：最速传说</t>
-  </si>
-  <si>
-    <t>穿到女频，整顿满城霸总</t>
-  </si>
-  <si>
-    <t>崩铁，穿越成怪兽，被爻光买回家</t>
-  </si>
-  <si>
-    <t>天幕洛神赋，曹家父子社死</t>
-  </si>
-  <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
-  </si>
-  <si>
-    <t>天幕直播：长乐公主被我吓哭了</t>
+    <t>每天属性翻一倍，我黑化爆杀一切</t>
+  </si>
+  <si>
+    <t>领证三天，我被未婚妻杀死</t>
+  </si>
+  <si>
+    <t>四合院：从李云龙战友开始</t>
+  </si>
+  <si>
+    <t>抗战：从湘江开始一路横推</t>
+  </si>
+  <si>
+    <t>这个猫娘？怎么是尼古喵喵啊！！</t>
+  </si>
+  <si>
+    <t>神豪太青涩，校花闺蜜团只好倒追</t>
   </si>
   <si>
     <t>什么天幕？明明是古人破防日记</t>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>88</v>
+        <v>91.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>2940000</v>
+        <v>1474000</v>
       </c>
       <c r="G5" s="7">
-        <v>180000</v>
+        <v>165000</v>
       </c>
       <c r="H5" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="7">
-        <v>183222</v>
+        <v>98500</v>
       </c>
       <c r="J5" s="5">
-        <v>93.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>86.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1309000</v>
+        <v>681000</v>
       </c>
       <c r="G6" s="7">
-        <v>97000</v>
+        <v>113000</v>
       </c>
       <c r="H6" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I6" s="7">
-        <v>91111</v>
+        <v>86800</v>
       </c>
       <c r="J6" s="5">
-        <v>90.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>85.8</v>
+        <v>87.7</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1613000</v>
+        <v>1731000</v>
       </c>
       <c r="G7" s="7">
-        <v>85000</v>
+        <v>118000</v>
       </c>
       <c r="H7" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="7">
-        <v>92000</v>
+        <v>94600</v>
       </c>
       <c r="J7" s="5">
-        <v>90.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,23 +858,23 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99.5</v>
+        <v>81.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>568000</v>
+        <v>2915000</v>
       </c>
       <c r="G8" s="7">
-        <v>55000</v>
+        <v>-25000</v>
       </c>
       <c r="H8" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I8" s="7">
-        <v>80250</v>
+        <v>162400</v>
       </c>
       <c r="J8" s="5">
         <v>89.8</v>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>534000</v>
+        <v>595000</v>
       </c>
       <c r="G9" s="7">
-        <v>80000</v>
+        <v>61000</v>
       </c>
       <c r="H9" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="7">
-        <v>39778</v>
+        <v>41900</v>
       </c>
       <c r="J9" s="5">
-        <v>84.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>894000</v>
+        <v>340000</v>
       </c>
       <c r="G10" s="7">
-        <v>11000</v>
+        <v>41000</v>
       </c>
       <c r="H10" s="7">
         <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>40556</v>
+        <v>23667</v>
       </c>
       <c r="J10" s="5">
-        <v>80.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>96.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>299000</v>
+        <v>204000</v>
       </c>
       <c r="G11" s="7">
-        <v>28000</v>
+        <v>29000</v>
       </c>
       <c r="H11" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>21500</v>
+        <v>25500</v>
       </c>
       <c r="J11" s="5">
-        <v>78.7</v>
+        <v>80.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>384000</v>
+        <v>628000</v>
       </c>
       <c r="G12" s="7">
-        <v>27000</v>
+        <v>83000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I12" s="7">
-        <v>24167</v>
+        <v>22800</v>
       </c>
       <c r="J12" s="5">
-        <v>78.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>97.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>545000</v>
+        <v>521000</v>
       </c>
       <c r="G13" s="7">
-        <v>49000</v>
+        <v>80000</v>
       </c>
       <c r="H13" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="7">
-        <v>16111</v>
+        <v>33600</v>
       </c>
       <c r="J13" s="5">
-        <v>77.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>97.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>175000</v>
+        <v>907000</v>
       </c>
       <c r="G14" s="7">
-        <v>21000</v>
+        <v>13000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
-        <v>24800</v>
+        <v>37800</v>
       </c>
       <c r="J14" s="5">
-        <v>77.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>99.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>112000</v>
+        <v>287000</v>
       </c>
       <c r="G15" s="7">
-        <v>30000</v>
+        <v>44000</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
       </c>
       <c r="I15" s="7">
-        <v>10889</v>
+        <v>16556</v>
       </c>
       <c r="J15" s="5">
-        <v>77.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>88.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>465000</v>
+        <v>157000</v>
       </c>
       <c r="G16" s="7">
-        <v>8000</v>
+        <v>45000</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I16" s="7">
-        <v>32250</v>
+        <v>14300</v>
       </c>
       <c r="J16" s="5">
-        <v>76.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>88.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>599000</v>
+        <v>432000</v>
       </c>
       <c r="G17" s="7">
-        <v>-2000</v>
+        <v>34000</v>
       </c>
       <c r="H17" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="7">
-        <v>30556</v>
+        <v>26500</v>
       </c>
       <c r="J17" s="5">
-        <v>76.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>90.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>398000</v>
+        <v>863000</v>
       </c>
       <c r="G18" s="7">
-        <v>26000</v>
+        <v>62000</v>
       </c>
       <c r="H18" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="7">
-        <v>25667</v>
+        <v>40000</v>
       </c>
       <c r="J18" s="5">
-        <v>76.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>200000</v>
+        <v>304000</v>
       </c>
       <c r="G19" s="7">
-        <v>11000</v>
+        <v>37000</v>
       </c>
       <c r="H19" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I19" s="7">
-        <v>20375</v>
+        <v>10800</v>
       </c>
       <c r="J19" s="5">
-        <v>75.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>265000</v>
+        <v>158000</v>
       </c>
       <c r="G20" s="7">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="H20" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="7">
-        <v>17556</v>
+        <v>9800</v>
       </c>
       <c r="J20" s="5">
-        <v>75.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>506000</v>
+        <v>234000</v>
       </c>
       <c r="G21" s="7">
-        <v>23000</v>
+        <v>47000</v>
       </c>
       <c r="H21" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="7">
-        <v>38111</v>
+        <v>9600</v>
       </c>
       <c r="J21" s="5">
-        <v>75.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>95.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>102000</v>
+        <v>476000</v>
       </c>
       <c r="G22" s="7">
-        <v>24000</v>
+        <v>11000</v>
       </c>
       <c r="H22" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I22" s="7">
-        <v>9500</v>
+        <v>29889</v>
       </c>
       <c r="J22" s="5">
-        <v>75.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>82.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>801000</v>
+        <v>176000</v>
       </c>
       <c r="G23" s="7">
-        <v>31000</v>
+        <v>23000</v>
       </c>
       <c r="H23" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="7">
-        <v>37556</v>
+        <v>12300</v>
       </c>
       <c r="J23" s="5">
-        <v>74.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>90.2</v>
+        <v>94.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>322000</v>
+        <v>215000</v>
       </c>
       <c r="G24" s="7">
-        <v>11000</v>
+        <v>15000</v>
       </c>
       <c r="H24" s="7">
         <v>10</v>
       </c>
       <c r="I24" s="7">
-        <v>20333</v>
+        <v>19778</v>
       </c>
       <c r="J24" s="5">
-        <v>74.7</v>
+        <v>76.8</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>93.09999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>243000</v>
+        <v>142000</v>
       </c>
       <c r="G25" s="7">
-        <v>21000</v>
+        <v>19000</v>
       </c>
       <c r="H25" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I25" s="7">
-        <v>13125</v>
+        <v>6900</v>
       </c>
       <c r="J25" s="5">
-        <v>74.5</v>
+        <v>76.7</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>86</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>441000</v>
+        <v>151000</v>
       </c>
       <c r="G26" s="7">
-        <v>38000</v>
+        <v>49000</v>
       </c>
       <c r="H26" s="7">
         <v>10</v>
       </c>
       <c r="I26" s="7">
-        <v>28444</v>
+        <v>13889</v>
       </c>
       <c r="J26" s="5">
-        <v>74.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>90</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>246000</v>
+        <v>535000</v>
       </c>
       <c r="G27" s="7">
-        <v>11000</v>
+        <v>29000</v>
       </c>
       <c r="H27" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="7">
-        <v>19444</v>
+        <v>37200</v>
       </c>
       <c r="J27" s="5">
-        <v>74.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>92.3</v>
+        <v>90.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>236000</v>
+        <v>398000</v>
       </c>
       <c r="G28" s="7">
         <v>14000</v>
       </c>
       <c r="H28" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>14000</v>
+        <v>22714</v>
       </c>
       <c r="J28" s="5">
-        <v>74.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>94</v>
+        <v>96.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>129000</v>
+        <v>121000</v>
       </c>
       <c r="G29" s="7">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="H29" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>9000</v>
+        <v>10429</v>
       </c>
       <c r="J29" s="5">
-        <v>74</v>
+        <v>75.5</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>86.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>798000</v>
+        <v>199000</v>
       </c>
       <c r="G30" s="7">
-        <v>-26000</v>
+        <v>22000</v>
       </c>
       <c r="H30" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="7">
-        <v>25667</v>
+        <v>5700</v>
       </c>
       <c r="J30" s="5">
-        <v>73.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>95.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>123000</v>
+        <v>435000</v>
       </c>
       <c r="G31" s="7">
-        <v>12000</v>
+        <v>43000</v>
       </c>
       <c r="H31" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="7">
-        <v>5556</v>
+        <v>26300</v>
       </c>
       <c r="J31" s="5">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>87.5</v>
+        <v>94.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>315000</v>
+        <v>198000</v>
       </c>
       <c r="G32" s="7">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="H32" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="7">
-        <v>22000</v>
+        <v>11600</v>
       </c>
       <c r="J32" s="5">
-        <v>73.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>78.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>574000</v>
+        <v>276000</v>
       </c>
       <c r="G33" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H33" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I33" s="7">
-        <v>37333</v>
+        <v>16900</v>
       </c>
       <c r="J33" s="5">
-        <v>72.7</v>
+        <v>74.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>91</v>
+        <v>85.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>177000</v>
+        <v>668000</v>
       </c>
       <c r="G34" s="7">
-        <v>17000</v>
+        <v>159000</v>
       </c>
       <c r="H34" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I34" s="7">
-        <v>10556</v>
+        <v>28700</v>
       </c>
       <c r="J34" s="5">
-        <v>72.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>90.3</v>
+        <v>88.5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>135000</v>
+        <v>790000</v>
       </c>
       <c r="G35" s="7">
-        <v>8000</v>
+        <v>-8000</v>
       </c>
       <c r="H35" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I35" s="7">
-        <v>11250</v>
+        <v>22300</v>
       </c>
       <c r="J35" s="5">
-        <v>72.5</v>
+        <v>74.3</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>90.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>153000</v>
+        <v>254000</v>
       </c>
       <c r="G36" s="7">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="H36" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I36" s="7">
-        <v>11111</v>
+        <v>18300</v>
       </c>
       <c r="J36" s="5">
-        <v>72.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>90.5</v>
+        <v>92.8</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>125000</v>
+        <v>152000</v>
       </c>
       <c r="G37" s="7">
-        <v>6000</v>
+        <v>13000</v>
       </c>
       <c r="H37" s="7">
         <v>10</v>
       </c>
       <c r="I37" s="7">
-        <v>10333</v>
+        <v>9222</v>
       </c>
       <c r="J37" s="5">
-        <v>72.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>86</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>428000</v>
+        <v>577000</v>
       </c>
       <c r="G38" s="7">
-        <v>40000</v>
+        <v>-22000</v>
       </c>
       <c r="H38" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I38" s="7">
-        <v>18889</v>
+        <v>25300</v>
       </c>
       <c r="J38" s="5">
-        <v>72</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>89.8</v>
+        <v>98</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>262000</v>
+        <v>183000</v>
       </c>
       <c r="G39" s="7">
-        <v>7000</v>
+        <v>43000</v>
       </c>
       <c r="H39" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I39" s="7">
-        <v>9778</v>
+        <v>28667</v>
       </c>
       <c r="J39" s="5">
-        <v>71.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>88.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>235000</v>
+        <v>116000</v>
       </c>
       <c r="G40" s="7">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="H40" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I40" s="7">
-        <v>13222</v>
+        <v>5500</v>
       </c>
       <c r="J40" s="5">
-        <v>71.8</v>
+        <v>72.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>82.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>2540000</v>
+        <v>114000</v>
       </c>
       <c r="G41" s="7">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="H41" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I41" s="7">
-        <v>26111</v>
+        <v>8875</v>
       </c>
       <c r="J41" s="5">
-        <v>71.7</v>
+        <v>72.8</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>325000</v>
+        <v>245000</v>
       </c>
       <c r="G42" s="7">
-        <v>21000</v>
+        <v>9000</v>
       </c>
       <c r="H42" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I42" s="7">
-        <v>11333</v>
+        <v>13500</v>
       </c>
       <c r="J42" s="5">
-        <v>71.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>88.5</v>
+        <v>96.8</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>553000</v>
+        <v>105000</v>
       </c>
       <c r="G43" s="7">
-        <v>-1000</v>
+        <v>24000</v>
       </c>
       <c r="H43" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I43" s="7">
-        <v>10778</v>
+        <v>16500</v>
       </c>
       <c r="J43" s="5">
-        <v>71.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2053,19 +2053,19 @@
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>307000</v>
+        <v>311000</v>
       </c>
       <c r="G44" s="7">
-        <v>39000</v>
+        <v>-4000</v>
       </c>
       <c r="H44" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I44" s="7">
-        <v>15333</v>
+        <v>19400</v>
       </c>
       <c r="J44" s="5">
-        <v>71.2</v>
+        <v>72.3</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>89.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>267000</v>
+        <v>241000</v>
       </c>
       <c r="G45" s="7">
         <v>6000</v>
       </c>
       <c r="H45" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I45" s="7">
-        <v>7889</v>
+        <v>12500</v>
       </c>
       <c r="J45" s="5">
-        <v>71.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>89.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>113000</v>
+        <v>124000</v>
       </c>
       <c r="G46" s="7">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="H46" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I46" s="7">
-        <v>7556</v>
+        <v>10286</v>
       </c>
       <c r="J46" s="5">
-        <v>71.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>187000</v>
+        <v>559000</v>
       </c>
       <c r="G47" s="7">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H47" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I47" s="7">
-        <v>5444</v>
+        <v>10300</v>
       </c>
       <c r="J47" s="5">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>132000</v>
+        <v>202000</v>
       </c>
       <c r="G48" s="7">
-        <v>7000</v>
+        <v>30000</v>
       </c>
       <c r="H48" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
-        <v>10286</v>
+        <v>19000</v>
       </c>
       <c r="J48" s="5">
-        <v>70.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>84.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>966000</v>
+        <v>270000</v>
       </c>
       <c r="G49" s="7">
-        <v>46000</v>
+        <v>64000</v>
       </c>
       <c r="H49" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I49" s="7">
-        <v>16222</v>
+        <v>3800</v>
       </c>
       <c r="J49" s="5">
-        <v>70.8</v>
+        <v>71.7</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>87</v>
+        <v>91.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>326000</v>
+        <v>200000</v>
       </c>
       <c r="G50" s="7">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="H50" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I50" s="7">
-        <v>11889</v>
+        <v>6300</v>
       </c>
       <c r="J50" s="5">
-        <v>70.8</v>
+        <v>71.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>87.5</v>
+        <v>97.3</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>114000</v>
+        <v>110000</v>
       </c>
       <c r="G51" s="7">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="H51" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I51" s="7">
-        <v>10333</v>
+        <v>12250</v>
       </c>
       <c r="J51" s="5">
-        <v>70.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>85.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>380000</v>
+        <v>224000</v>
       </c>
       <c r="G52" s="7">
-        <v>-7000</v>
+        <v>21000</v>
       </c>
       <c r="H52" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I52" s="7">
-        <v>14444</v>
+        <v>18000</v>
       </c>
       <c r="J52" s="5">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>87.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>139000</v>
+        <v>360000</v>
       </c>
       <c r="G53" s="7">
-        <v>6000</v>
+        <v>21000</v>
       </c>
       <c r="H53" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>8750</v>
+        <v>26000</v>
       </c>
       <c r="J53" s="5">
-        <v>70.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>88.3</v>
+        <v>89.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>106000</v>
+        <v>116000</v>
       </c>
       <c r="G54" s="7">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H54" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I54" s="7">
-        <v>7333</v>
+        <v>7714</v>
       </c>
       <c r="J54" s="5">
-        <v>70.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-03T12:44:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-04T10:19:43+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>诸神愚戏</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>全球死考：刚下刑场你让我去考试</t>
+  </si>
+  <si>
+    <t>刚证道混沌天帝，让我身化禁区？</t>
+  </si>
+  <si>
     <t>规则怪谈：无所谓，系统会出手</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>刚证道混沌天帝，让我身化禁区？</t>
-  </si>
-  <si>
-    <t>全球死考：刚下刑场你让我去考试</t>
-  </si>
-  <si>
-    <t>诸神愚戏</t>
+    <t>系统想害我，我选择上交国家</t>
   </si>
   <si>
     <t>公安局长之扫黑风暴</t>
   </si>
   <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>重生后，姐姐非要嫁给我</t>
+  </si>
+  <si>
+    <t>穿越刘备，死后和我说这是型月？</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
+  </si>
+  <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
+  </si>
+  <si>
     <t>名义：开局我举报我自己</t>
   </si>
   <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>我根骨平庸，但分身都是绝世天才</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
   </si>
   <si>
     <t>年代1960：穿越南锣鼓巷，</t>
   </si>
   <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
+    <t>神豪太青涩，校花闺蜜团只好倒追</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
   </si>
   <si>
     <t>国运班级求生：机电2班闹翻荒野</t>
   </si>
   <si>
-    <t>开局四选一，我选成为沪圈少爷！</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>死对头证道成仙了，怎么办？！</t>
+    <t>封印神源百万年，悟性每天翻倍</t>
+  </si>
+  <si>
+    <t>开局大限将至，我携帝兵问道禁区</t>
+  </si>
+  <si>
+    <t>开局法相，未婚妻不退婚</t>
+  </si>
+  <si>
+    <t>开局日军围城，系统让我当德皇</t>
+  </si>
+  <si>
+    <t>我操作的少女正在成为旧日之主</t>
+  </si>
+  <si>
+    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>崩铁，穿越成怪兽，被爻光买回家</t>
   </si>
   <si>
     <t>我提前三天被丢进了末世</t>
   </si>
   <si>
-    <t>我创立的组织，被重生者曝光了！</t>
-  </si>
-  <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>妖魔乱世：从造畜法开始左道成仙</t>
-  </si>
-  <si>
-    <t>穿书百合文，我只想安稳苟到结局</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>穿越刘备，死后和我说这是型月？</t>
-  </si>
-  <si>
-    <t>捡来的妹妹修仙后，回来抢亲了</t>
-  </si>
-  <si>
     <t>秦始皇：朕有华夏全明星阵容</t>
   </si>
   <si>
-    <t>全民县令：我看广告无限刷资源</t>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>四合院，哈军工副院，部下李云龙</t>
   </si>
   <si>
     <t>你写的小说，给我惹了不少麻烦呢</t>
   </si>
   <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
+    <t>瘟疫模拟：开局投放Necroa</t>
+  </si>
+  <si>
+    <t>十日终焉</t>
+  </si>
+  <si>
+    <t>重生后，成了妹妹的专属爱物</t>
+  </si>
+  <si>
+    <t>爱你老哥，但邪神的你，必须善堕</t>
   </si>
   <si>
     <t>天幕直播：长乐公主被我吓哭了</t>
   </si>
   <si>
-    <t>重生后，姐姐非要嫁给我</t>
-  </si>
-  <si>
-    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
-  </si>
-  <si>
-    <t>开局被魅魔收养，异世界尽情攻略</t>
-  </si>
-  <si>
-    <t>开局日军围城，系统让我当德皇</t>
-  </si>
-  <si>
-    <t>封印神源百万年，悟性每天翻倍</t>
-  </si>
-  <si>
-    <t>开局大限将至，我携帝兵问道禁区</t>
-  </si>
-  <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>天幕洛神赋，曹家父子社死</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>每天属性翻一倍，我黑化爆杀一切</t>
-  </si>
-  <si>
-    <t>领证三天，我被未婚妻杀死</t>
-  </si>
-  <si>
-    <t>四合院：从李云龙战友开始</t>
-  </si>
-  <si>
-    <t>抗战：从湘江开始一路横推</t>
-  </si>
-  <si>
-    <t>这个猫娘？怎么是尼古喵喵啊！！</t>
-  </si>
-  <si>
-    <t>神豪太青涩，校花闺蜜团只好倒追</t>
-  </si>
-  <si>
-    <t>什么天幕？明明是古人破防日记</t>
+    <t>末法时代出飞僵，可我是石坚啊</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>91.8</v>
+        <v>82.3</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1474000</v>
+        <v>2915000</v>
       </c>
       <c r="G5" s="7">
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="H5" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="7">
-        <v>98500</v>
+        <v>147636</v>
       </c>
       <c r="J5" s="5">
-        <v>95.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>83.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>681000</v>
+        <v>1788000</v>
       </c>
       <c r="G6" s="7">
-        <v>113000</v>
+        <v>57000</v>
       </c>
       <c r="H6" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I6" s="7">
-        <v>86800</v>
+        <v>91182</v>
       </c>
       <c r="J6" s="5">
-        <v>94.7</v>
+        <v>88.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>87.7</v>
+        <v>89.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1731000</v>
+        <v>681000</v>
       </c>
       <c r="G7" s="7">
-        <v>118000</v>
+        <v>0</v>
       </c>
       <c r="H7" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>94600</v>
+        <v>72333</v>
       </c>
       <c r="J7" s="5">
-        <v>91.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>81.5</v>
+        <v>79.2</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>2915000</v>
+        <v>1474000</v>
       </c>
       <c r="G8" s="7">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="H8" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" s="7">
-        <v>162400</v>
+        <v>89545</v>
       </c>
       <c r="J8" s="5">
-        <v>89.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>595000</v>
+        <v>538000</v>
       </c>
       <c r="G9" s="7">
-        <v>61000</v>
+        <v>106000</v>
       </c>
       <c r="H9" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" s="7">
-        <v>41900</v>
+        <v>33727</v>
       </c>
       <c r="J9" s="5">
-        <v>85.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>340000</v>
+        <v>630000</v>
       </c>
       <c r="G10" s="7">
-        <v>41000</v>
+        <v>35000</v>
       </c>
       <c r="H10" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I10" s="7">
-        <v>23667</v>
+        <v>41273</v>
       </c>
       <c r="J10" s="5">
-        <v>80.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>99</v>
+        <v>89.8</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>204000</v>
+        <v>907000</v>
       </c>
       <c r="G11" s="7">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I11" s="7">
-        <v>25500</v>
+        <v>34364</v>
       </c>
       <c r="J11" s="5">
-        <v>80.8</v>
+        <v>78</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>628000</v>
+        <v>750000</v>
       </c>
       <c r="G12" s="7">
-        <v>83000</v>
+        <v>82000</v>
       </c>
       <c r="H12" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I12" s="7">
-        <v>22800</v>
+        <v>33545</v>
       </c>
       <c r="J12" s="5">
-        <v>80.7</v>
+        <v>77</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>93.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>521000</v>
+        <v>656000</v>
       </c>
       <c r="G13" s="7">
-        <v>80000</v>
+        <v>28000</v>
       </c>
       <c r="H13" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I13" s="7">
-        <v>33600</v>
+        <v>23273</v>
       </c>
       <c r="J13" s="5">
-        <v>79.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>91.2</v>
+        <v>96</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>907000</v>
+        <v>255000</v>
       </c>
       <c r="G14" s="7">
-        <v>13000</v>
+        <v>21000</v>
       </c>
       <c r="H14" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I14" s="7">
-        <v>37800</v>
+        <v>10636</v>
       </c>
       <c r="J14" s="5">
-        <v>79.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>99</v>
+        <v>88.8</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>287000</v>
+        <v>577000</v>
       </c>
       <c r="G15" s="7">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="H15" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I15" s="7">
-        <v>16556</v>
+        <v>23000</v>
       </c>
       <c r="J15" s="5">
-        <v>78.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>157000</v>
+        <v>405000</v>
       </c>
       <c r="G16" s="7">
-        <v>45000</v>
+        <v>7000</v>
       </c>
       <c r="H16" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>14300</v>
+        <v>20750</v>
       </c>
       <c r="J16" s="5">
-        <v>78.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>94.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>432000</v>
+        <v>212000</v>
       </c>
       <c r="G17" s="7">
-        <v>34000</v>
+        <v>8000</v>
       </c>
       <c r="H17" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>26500</v>
+        <v>23000</v>
       </c>
       <c r="J17" s="5">
-        <v>78.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>87.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>863000</v>
+        <v>476000</v>
       </c>
       <c r="G18" s="7">
-        <v>62000</v>
+        <v>0</v>
       </c>
       <c r="H18" s="7">
         <v>11</v>
       </c>
       <c r="I18" s="7">
-        <v>40000</v>
+        <v>26900</v>
       </c>
       <c r="J18" s="5">
-        <v>78.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>304000</v>
+        <v>790000</v>
       </c>
       <c r="G19" s="7">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="H19" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" s="7">
-        <v>10800</v>
+        <v>20273</v>
       </c>
       <c r="J19" s="5">
-        <v>77.7</v>
+        <v>74.3</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>158000</v>
+        <v>221000</v>
       </c>
       <c r="G20" s="7">
-        <v>25000</v>
+        <v>6000</v>
       </c>
       <c r="H20" s="7">
         <v>11</v>
       </c>
       <c r="I20" s="7">
-        <v>9800</v>
+        <v>18400</v>
       </c>
       <c r="J20" s="5">
-        <v>77.5</v>
+        <v>73.8</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>234000</v>
+        <v>165000</v>
       </c>
       <c r="G21" s="7">
-        <v>47000</v>
+        <v>8000</v>
       </c>
       <c r="H21" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I21" s="7">
-        <v>9600</v>
+        <v>13727</v>
       </c>
       <c r="J21" s="5">
-        <v>77.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>89.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>476000</v>
+        <v>340000</v>
       </c>
       <c r="G22" s="7">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H22" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="7">
-        <v>29889</v>
+        <v>21300</v>
       </c>
       <c r="J22" s="5">
-        <v>76.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>97.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>176000</v>
+        <v>258000</v>
       </c>
       <c r="G23" s="7">
-        <v>23000</v>
+        <v>4000</v>
       </c>
       <c r="H23" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I23" s="7">
-        <v>12300</v>
+        <v>17000</v>
       </c>
       <c r="J23" s="5">
-        <v>76.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>94.2</v>
+        <v>79.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>215000</v>
+        <v>863000</v>
       </c>
       <c r="G24" s="7">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="H24" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I24" s="7">
-        <v>19778</v>
+        <v>36364</v>
       </c>
       <c r="J24" s="5">
-        <v>76.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>99.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>142000</v>
+        <v>311000</v>
       </c>
       <c r="G25" s="7">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="H25" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I25" s="7">
-        <v>6900</v>
+        <v>17636</v>
       </c>
       <c r="J25" s="5">
-        <v>76.7</v>
+        <v>72.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>95.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>151000</v>
+        <v>539000</v>
       </c>
       <c r="G26" s="7">
-        <v>49000</v>
+        <v>4000</v>
       </c>
       <c r="H26" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I26" s="7">
-        <v>13889</v>
+        <v>34182</v>
       </c>
       <c r="J26" s="5">
-        <v>76.2</v>
+        <v>72.2</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>84.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>535000</v>
+        <v>173000</v>
       </c>
       <c r="G27" s="7">
-        <v>29000</v>
+        <v>16000</v>
       </c>
       <c r="H27" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>37200</v>
+        <v>14800</v>
       </c>
       <c r="J27" s="5">
-        <v>75.7</v>
+        <v>72</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>90.8</v>
+        <v>87.2</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>398000</v>
+        <v>276000</v>
       </c>
       <c r="G28" s="7">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I28" s="7">
-        <v>22714</v>
+        <v>15364</v>
       </c>
       <c r="J28" s="5">
-        <v>75.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>96.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>121000</v>
+        <v>308000</v>
       </c>
       <c r="G29" s="7">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I29" s="7">
-        <v>10429</v>
+        <v>15364</v>
       </c>
       <c r="J29" s="5">
-        <v>75.5</v>
+        <v>71.5</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>97.3</v>
+        <v>87.8</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>199000</v>
+        <v>183000</v>
       </c>
       <c r="G30" s="7">
-        <v>22000</v>
+        <v>7000</v>
       </c>
       <c r="H30" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I30" s="7">
-        <v>5700</v>
+        <v>11818</v>
       </c>
       <c r="J30" s="5">
-        <v>74.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>435000</v>
+        <v>521000</v>
       </c>
       <c r="G31" s="7">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="H31" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I31" s="7">
-        <v>26300</v>
+        <v>30545</v>
       </c>
       <c r="J31" s="5">
-        <v>74.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>94.2</v>
+        <v>86.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>198000</v>
+        <v>366000</v>
       </c>
       <c r="G32" s="7">
-        <v>21000</v>
+        <v>6000</v>
       </c>
       <c r="H32" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>11600</v>
+        <v>22000</v>
       </c>
       <c r="J32" s="5">
-        <v>74.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>91.40000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>276000</v>
+        <v>241000</v>
       </c>
       <c r="G33" s="7">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I33" s="7">
-        <v>16900</v>
+        <v>11364</v>
       </c>
       <c r="J33" s="5">
-        <v>74.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>85.8</v>
+        <v>87.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>668000</v>
+        <v>554000</v>
       </c>
       <c r="G34" s="7">
-        <v>159000</v>
+        <v>-5000</v>
       </c>
       <c r="H34" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I34" s="7">
-        <v>28700</v>
+        <v>8909</v>
       </c>
       <c r="J34" s="5">
-        <v>74.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>88.5</v>
+        <v>84.8</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>790000</v>
+        <v>287000</v>
       </c>
       <c r="G35" s="7">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="H35" s="7">
         <v>11</v>
       </c>
       <c r="I35" s="7">
-        <v>22300</v>
+        <v>14900</v>
       </c>
       <c r="J35" s="5">
-        <v>74.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>89.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>254000</v>
+        <v>245000</v>
       </c>
       <c r="G36" s="7">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="H36" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I36" s="7">
-        <v>18300</v>
+        <v>12273</v>
       </c>
       <c r="J36" s="5">
-        <v>73.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>92.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>152000</v>
+        <v>112000</v>
       </c>
       <c r="G37" s="7">
-        <v>13000</v>
+        <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>9222</v>
+        <v>14600</v>
       </c>
       <c r="J37" s="5">
-        <v>73.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>85.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>577000</v>
+        <v>264000</v>
       </c>
       <c r="G38" s="7">
-        <v>-22000</v>
+        <v>0</v>
       </c>
       <c r="H38" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I38" s="7">
-        <v>25300</v>
+        <v>8182</v>
       </c>
       <c r="J38" s="5">
-        <v>73.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>98</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>183000</v>
+        <v>117000</v>
       </c>
       <c r="G39" s="7">
-        <v>43000</v>
+        <v>3000</v>
       </c>
       <c r="H39" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>28667</v>
+        <v>8222</v>
       </c>
       <c r="J39" s="5">
-        <v>73.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>93.5</v>
+        <v>79.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>116000</v>
+        <v>1289000</v>
       </c>
       <c r="G40" s="7">
-        <v>12000</v>
+        <v>33000</v>
       </c>
       <c r="H40" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I40" s="7">
-        <v>5500</v>
+        <v>23818</v>
       </c>
       <c r="J40" s="5">
-        <v>72.8</v>
+        <v>69.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>92</v>
+        <v>88.3</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>114000</v>
+        <v>197000</v>
       </c>
       <c r="G41" s="7">
-        <v>8000</v>
+        <v>14000</v>
       </c>
       <c r="H41" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>8875</v>
+        <v>25000</v>
       </c>
       <c r="J41" s="5">
-        <v>72.8</v>
+        <v>69.8</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89.09999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>245000</v>
+        <v>335000</v>
       </c>
       <c r="G42" s="7">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I42" s="7">
-        <v>13500</v>
+        <v>6636</v>
       </c>
       <c r="J42" s="5">
-        <v>72.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>96.8</v>
+        <v>86.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>105000</v>
+        <v>291000</v>
       </c>
       <c r="G43" s="7">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I43" s="7">
-        <v>16500</v>
+        <v>6545</v>
       </c>
       <c r="J43" s="5">
-        <v>72.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.2</v>
+        <v>85.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>311000</v>
+        <v>158000</v>
       </c>
       <c r="G44" s="7">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="H44" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I44" s="7">
-        <v>19400</v>
+        <v>8909</v>
       </c>
       <c r="J44" s="5">
-        <v>72.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>89.5</v>
+        <v>86.5</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>241000</v>
+        <v>199000</v>
       </c>
       <c r="G45" s="7">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="H45" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I45" s="7">
-        <v>12500</v>
+        <v>5182</v>
       </c>
       <c r="J45" s="5">
-        <v>72.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>90.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>124000</v>
+        <v>2486000</v>
       </c>
       <c r="G46" s="7">
-        <v>10000</v>
+        <v>-16000</v>
       </c>
       <c r="H46" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I46" s="7">
-        <v>10286</v>
+        <v>16455</v>
       </c>
       <c r="J46" s="5">
-        <v>72.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>89.8</v>
+        <v>87.7</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>559000</v>
+        <v>354000</v>
       </c>
       <c r="G47" s="7">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="H47" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I47" s="7">
-        <v>10300</v>
+        <v>2364</v>
       </c>
       <c r="J47" s="5">
-        <v>72</v>
+        <v>68.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>94.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>202000</v>
+        <v>198000</v>
       </c>
       <c r="G48" s="7">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H48" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I48" s="7">
-        <v>19000</v>
+        <v>10545</v>
       </c>
       <c r="J48" s="5">
-        <v>71.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>92.2</v>
+        <v>84</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>270000</v>
+        <v>138000</v>
       </c>
       <c r="G49" s="7">
-        <v>64000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7">
         <v>11</v>
       </c>
       <c r="I49" s="7">
-        <v>3800</v>
+        <v>9300</v>
       </c>
       <c r="J49" s="5">
-        <v>71.7</v>
+        <v>68.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>91.2</v>
+        <v>83.7</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>200000</v>
+        <v>2673000</v>
       </c>
       <c r="G50" s="7">
-        <v>19000</v>
+        <v>40000</v>
       </c>
       <c r="H50" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I50" s="7">
-        <v>6300</v>
+        <v>9273</v>
       </c>
       <c r="J50" s="5">
-        <v>71.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>97.3</v>
+        <v>83.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>110000</v>
+        <v>334000</v>
       </c>
       <c r="G51" s="7">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="H51" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I51" s="7">
-        <v>12250</v>
+        <v>10091</v>
       </c>
       <c r="J51" s="5">
-        <v>71.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>94.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>224000</v>
+        <v>191000</v>
       </c>
       <c r="G52" s="7">
-        <v>21000</v>
+        <v>5000</v>
       </c>
       <c r="H52" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I52" s="7">
-        <v>18000</v>
+        <v>6727</v>
       </c>
       <c r="J52" s="5">
-        <v>71.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>90.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>360000</v>
+        <v>153000</v>
       </c>
       <c r="G53" s="7">
-        <v>21000</v>
+        <v>1000</v>
       </c>
       <c r="H53" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I53" s="7">
-        <v>26000</v>
+        <v>8400</v>
       </c>
       <c r="J53" s="5">
-        <v>71.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>89.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>116000</v>
+        <v>141000</v>
       </c>
       <c r="G54" s="7">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="H54" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I54" s="7">
-        <v>7714</v>
+        <v>6818</v>
       </c>
       <c r="J54" s="5">
-        <v>71.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-04T10:19:43+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-05T10:15:44+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>刚证道混沌天帝，让我身化禁区？</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
     <t>诸神愚戏</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
     <t>全球死考：刚下刑场你让我去考试</t>
   </si>
   <si>
-    <t>刚证道混沌天帝，让我身化禁区？</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>抗战：从湘江开始一路横推</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
   </si>
   <si>
     <t>系统想害我，我选择上交国家</t>
   </si>
   <si>
-    <t>公安局长之扫黑风暴</t>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>天仙怀了我的娃，千年世家被曝光</t>
+  </si>
+  <si>
+    <t>全民县令：我看广告无限刷资源</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>谍战：我当恶霸能爆奖励！</t>
+  </si>
+  <si>
+    <t>国运班级求生：机电2班闹翻荒野</t>
+  </si>
+  <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>我在精神病院学斩神</t>
+  </si>
+  <si>
+    <t>穿越刘备，死后和我说这是型月？</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>每天属性翻一倍，我黑化爆杀一切</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>重生后，姐姐非要嫁给我</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>兵王之我是一个交警</t>
+  </si>
+  <si>
+    <t>开局大限将至，我携帝兵问道禁区</t>
+  </si>
+  <si>
+    <t>封印神源百万年，悟性每天翻倍</t>
+  </si>
+  <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>神豪太青涩，校花闺蜜团只好倒追</t>
+  </si>
+  <si>
+    <t>重生神医：参加网综炸翻医学界</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>这个猫娘？怎么是尼古喵喵啊！！</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
+  </si>
+  <si>
+    <t>别人夺嫡偷偷来，我家皇帝下圣旨</t>
+  </si>
+  <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>妖魔乱世：从造畜法开始左道成仙</t>
   </si>
   <si>
     <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
+    <t>领证三天，我被未婚妻杀死</t>
+  </si>
+  <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>四合院：我家住隔壁，看众禽互咬</t>
+  </si>
+  <si>
     <t>文字武侠：开局破庙夜会帮主夫人</t>
   </si>
   <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
-  </si>
-  <si>
-    <t>重生后，姐姐非要嫁给我</t>
-  </si>
-  <si>
-    <t>穿越刘备，死后和我说这是型月？</t>
-  </si>
-  <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>开局四选一，我选成为沪圈少爷！</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>什么天幕？明明是古人破防日记</t>
+  </si>
+  <si>
+    <t>四合院，哈军工副院，部下李云龙</t>
   </si>
   <si>
     <t>我根骨平庸，但分身都是绝世天才</t>
   </si>
   <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>神豪太青涩，校花闺蜜团只好倒追</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>国运班级求生：机电2班闹翻荒野</t>
-  </si>
-  <si>
-    <t>封印神源百万年，悟性每天翻倍</t>
-  </si>
-  <si>
-    <t>开局大限将至，我携帝兵问道禁区</t>
-  </si>
-  <si>
-    <t>开局法相，未婚妻不退婚</t>
-  </si>
-  <si>
-    <t>开局日军围城，系统让我当德皇</t>
-  </si>
-  <si>
     <t>我操作的少女正在成为旧日之主</t>
-  </si>
-  <si>
-    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>崩铁，穿越成怪兽，被爻光买回家</t>
-  </si>
-  <si>
-    <t>我提前三天被丢进了末世</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>四合院，哈军工副院，部下李云龙</t>
-  </si>
-  <si>
-    <t>你写的小说，给我惹了不少麻烦呢</t>
-  </si>
-  <si>
-    <t>瘟疫模拟：开局投放Necroa</t>
-  </si>
-  <si>
-    <t>十日终焉</t>
-  </si>
-  <si>
-    <t>重生后，成了妹妹的专属爱物</t>
-  </si>
-  <si>
-    <t>爱你老哥，但邪神的你，必须善堕</t>
-  </si>
-  <si>
-    <t>天幕直播：长乐公主被我吓哭了</t>
-  </si>
-  <si>
-    <t>末法时代出飞僵，可我是石坚啊</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>82.3</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>2915000</v>
+        <v>792000</v>
       </c>
       <c r="G5" s="7">
-        <v>0</v>
+        <v>111000</v>
       </c>
       <c r="H5" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>147636</v>
+        <v>77857</v>
       </c>
       <c r="J5" s="5">
-        <v>90.3</v>
+        <v>94.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>83.7</v>
+        <v>84.2</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1788000</v>
+        <v>1547000</v>
       </c>
       <c r="G6" s="7">
-        <v>57000</v>
+        <v>73000</v>
       </c>
       <c r="H6" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6" s="7">
-        <v>91182</v>
+        <v>88167</v>
       </c>
       <c r="J6" s="5">
-        <v>88.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>89.2</v>
+        <v>78.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>681000</v>
+        <v>2797000</v>
       </c>
       <c r="G7" s="7">
-        <v>0</v>
+        <v>-118000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I7" s="7">
-        <v>72333</v>
+        <v>125500</v>
       </c>
       <c r="J7" s="5">
-        <v>87.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>79.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>1474000</v>
+        <v>1788000</v>
       </c>
       <c r="G8" s="7">
         <v>0</v>
       </c>
       <c r="H8" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" s="7">
-        <v>89545</v>
+        <v>83583</v>
       </c>
       <c r="J8" s="5">
-        <v>85.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>538000</v>
+        <v>624000</v>
       </c>
       <c r="G9" s="7">
-        <v>106000</v>
+        <v>103000</v>
       </c>
       <c r="H9" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I9" s="7">
-        <v>33727</v>
+        <v>36583</v>
       </c>
       <c r="J9" s="5">
-        <v>83.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>94</v>
+        <v>91.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>630000</v>
+        <v>647000</v>
       </c>
       <c r="G10" s="7">
-        <v>35000</v>
+        <v>17000</v>
       </c>
       <c r="H10" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="7">
-        <v>41273</v>
+        <v>39250</v>
       </c>
       <c r="J10" s="5">
-        <v>82</v>
+        <v>80.3</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>89.8</v>
+        <v>100</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>907000</v>
+        <v>186000</v>
       </c>
       <c r="G11" s="7">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="H11" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I11" s="7">
-        <v>34364</v>
+        <v>10500</v>
       </c>
       <c r="J11" s="5">
-        <v>78</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>88.3</v>
+        <v>98.3</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>750000</v>
+        <v>125000</v>
       </c>
       <c r="G12" s="7">
-        <v>82000</v>
+        <v>15000</v>
       </c>
       <c r="H12" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>33545</v>
+        <v>10667</v>
       </c>
       <c r="J12" s="5">
-        <v>77</v>
+        <v>76.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>92.7</v>
+        <v>92</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>656000</v>
+        <v>680000</v>
       </c>
       <c r="G13" s="7">
-        <v>28000</v>
+        <v>24000</v>
       </c>
       <c r="H13" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" s="7">
-        <v>23273</v>
+        <v>23333</v>
       </c>
       <c r="J13" s="5">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>255000</v>
+        <v>538000</v>
       </c>
       <c r="G14" s="7">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" s="7">
-        <v>10636</v>
+        <v>30917</v>
       </c>
       <c r="J14" s="5">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>88.8</v>
+        <v>96.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>577000</v>
+        <v>122000</v>
       </c>
       <c r="G15" s="7">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="H15" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>23000</v>
+        <v>9286</v>
       </c>
       <c r="J15" s="5">
-        <v>74.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>89.8</v>
+        <v>94</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>405000</v>
+        <v>201000</v>
       </c>
       <c r="G16" s="7">
-        <v>7000</v>
+        <v>54000</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>20750</v>
+        <v>21200</v>
       </c>
       <c r="J16" s="5">
-        <v>74.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>88.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>212000</v>
+        <v>481000</v>
       </c>
       <c r="G17" s="7">
-        <v>8000</v>
+        <v>46000</v>
       </c>
       <c r="H17" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I17" s="7">
-        <v>23000</v>
+        <v>25750</v>
       </c>
       <c r="J17" s="5">
-        <v>74.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>86.7</v>
+        <v>82.3</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>476000</v>
+        <v>885000</v>
       </c>
       <c r="G18" s="7">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="H18" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I18" s="7">
-        <v>26900</v>
+        <v>35167</v>
       </c>
       <c r="J18" s="5">
-        <v>74.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>89.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>790000</v>
+        <v>333000</v>
       </c>
       <c r="G19" s="7">
-        <v>0</v>
+        <v>32000</v>
       </c>
       <c r="H19" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>20273</v>
+        <v>25667</v>
       </c>
       <c r="J19" s="5">
-        <v>74.3</v>
+        <v>74</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,23 +1254,23 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>89.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>221000</v>
+        <v>300000</v>
       </c>
       <c r="G20" s="7">
-        <v>6000</v>
+        <v>13000</v>
       </c>
       <c r="H20" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I20" s="7">
-        <v>18400</v>
+        <v>14727</v>
       </c>
       <c r="J20" s="5">
         <v>73.8</v>
@@ -1287,23 +1287,23 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>91.2</v>
+        <v>86.3</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>165000</v>
+        <v>478000</v>
       </c>
       <c r="G21" s="7">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="H21" s="7">
         <v>12</v>
       </c>
       <c r="I21" s="7">
-        <v>13727</v>
+        <v>24636</v>
       </c>
       <c r="J21" s="5">
         <v>73.59999999999999</v>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>86.8</v>
+        <v>89.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>340000</v>
+        <v>2101000</v>
       </c>
       <c r="G22" s="7">
-        <v>0</v>
+        <v>189000</v>
       </c>
       <c r="H22" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I22" s="7">
-        <v>21300</v>
+        <v>16583</v>
       </c>
       <c r="J22" s="5">
-        <v>73.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,23 +1353,23 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>258000</v>
+        <v>405000</v>
       </c>
       <c r="G23" s="7">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H23" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I23" s="7">
-        <v>17000</v>
+        <v>18444</v>
       </c>
       <c r="J23" s="5">
         <v>73</v>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>79.7</v>
+        <v>93.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>863000</v>
+        <v>213000</v>
       </c>
       <c r="G24" s="7">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="H24" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I24" s="7">
-        <v>36364</v>
+        <v>5917</v>
       </c>
       <c r="J24" s="5">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>87.5</v>
+        <v>89.3</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>311000</v>
+        <v>214000</v>
       </c>
       <c r="G25" s="7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H25" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>17636</v>
+        <v>14667</v>
       </c>
       <c r="J25" s="5">
-        <v>72.5</v>
+        <v>72.8</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>79.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>539000</v>
+        <v>778000</v>
       </c>
       <c r="G26" s="7">
-        <v>4000</v>
+        <v>-12000</v>
       </c>
       <c r="H26" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26" s="7">
-        <v>34182</v>
+        <v>17583</v>
       </c>
       <c r="J26" s="5">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>91.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>173000</v>
+        <v>262000</v>
       </c>
       <c r="G27" s="7">
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I27" s="7">
-        <v>14800</v>
+        <v>15917</v>
       </c>
       <c r="J27" s="5">
-        <v>72</v>
+        <v>72.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>87.2</v>
+        <v>86.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>276000</v>
+        <v>564000</v>
       </c>
       <c r="G28" s="7">
-        <v>0</v>
+        <v>-13000</v>
       </c>
       <c r="H28" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I28" s="7">
-        <v>15364</v>
+        <v>20000</v>
       </c>
       <c r="J28" s="5">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>86.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>308000</v>
+        <v>281000</v>
       </c>
       <c r="G29" s="7">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H29" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I29" s="7">
-        <v>15364</v>
+        <v>14500</v>
       </c>
       <c r="J29" s="5">
-        <v>71.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>87.8</v>
+        <v>90.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>183000</v>
+        <v>234000</v>
       </c>
       <c r="G30" s="7">
-        <v>7000</v>
+        <v>52000</v>
       </c>
       <c r="H30" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I30" s="7">
-        <v>11818</v>
+        <v>11833</v>
       </c>
       <c r="J30" s="5">
-        <v>71.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>78.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>521000</v>
+        <v>118000</v>
       </c>
       <c r="G31" s="7">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H31" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>30545</v>
+        <v>13167</v>
       </c>
       <c r="J31" s="5">
-        <v>70.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>86.2</v>
+        <v>89</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>366000</v>
+        <v>252000</v>
       </c>
       <c r="G32" s="7">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H32" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I32" s="7">
-        <v>22000</v>
+        <v>11833</v>
       </c>
       <c r="J32" s="5">
-        <v>70.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,14 +1683,14 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>86.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>241000</v>
+        <v>221000</v>
       </c>
       <c r="G33" s="7">
         <v>0</v>
@@ -1699,10 +1699,10 @@
         <v>12</v>
       </c>
       <c r="I33" s="7">
-        <v>11364</v>
+        <v>16727</v>
       </c>
       <c r="J33" s="5">
-        <v>70.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>87.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>554000</v>
+        <v>311000</v>
       </c>
       <c r="G34" s="7">
-        <v>-5000</v>
+        <v>3000</v>
       </c>
       <c r="H34" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I34" s="7">
-        <v>8909</v>
+        <v>14333</v>
       </c>
       <c r="J34" s="5">
-        <v>70.5</v>
+        <v>71.8</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>287000</v>
+        <v>212000</v>
       </c>
       <c r="G35" s="7">
         <v>0</v>
       </c>
       <c r="H35" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>14900</v>
+        <v>20125</v>
       </c>
       <c r="J35" s="5">
-        <v>70.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>245000</v>
+        <v>539000</v>
       </c>
       <c r="G36" s="7">
         <v>0</v>
       </c>
       <c r="H36" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I36" s="7">
-        <v>12273</v>
+        <v>31333</v>
       </c>
       <c r="J36" s="5">
-        <v>70.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>112000</v>
+        <v>366000</v>
       </c>
       <c r="G37" s="7">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>14600</v>
+        <v>18333</v>
       </c>
       <c r="J37" s="5">
-        <v>70.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>264000</v>
+        <v>189000</v>
       </c>
       <c r="G38" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H38" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" s="7">
-        <v>8182</v>
+        <v>5667</v>
       </c>
       <c r="J38" s="5">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>87.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>117000</v>
+        <v>331000</v>
       </c>
       <c r="G39" s="7">
-        <v>3000</v>
+        <v>-9000</v>
       </c>
       <c r="H39" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I39" s="7">
-        <v>8222</v>
+        <v>18545</v>
       </c>
       <c r="J39" s="5">
-        <v>70</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>79.8</v>
+        <v>86.5</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>1289000</v>
+        <v>229000</v>
       </c>
       <c r="G40" s="7">
-        <v>33000</v>
+        <v>5000</v>
       </c>
       <c r="H40" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>23818</v>
+        <v>12833</v>
       </c>
       <c r="J40" s="5">
-        <v>69.8</v>
+        <v>70.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>197000</v>
+        <v>165000</v>
       </c>
       <c r="G41" s="7">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I41" s="7">
-        <v>25000</v>
+        <v>12583</v>
       </c>
       <c r="J41" s="5">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>86.8</v>
+        <v>83.3</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>335000</v>
+        <v>341000</v>
       </c>
       <c r="G42" s="7">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="H42" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I42" s="7">
-        <v>6636</v>
+        <v>18143</v>
       </c>
       <c r="J42" s="5">
-        <v>69.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>86.5</v>
+        <v>87</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>291000</v>
+        <v>255000</v>
       </c>
       <c r="G43" s="7">
         <v>0</v>
       </c>
       <c r="H43" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I43" s="7">
-        <v>6545</v>
+        <v>9750</v>
       </c>
       <c r="J43" s="5">
-        <v>69.2</v>
+        <v>70.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>85.2</v>
+        <v>88.5</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>158000</v>
+        <v>147000</v>
       </c>
       <c r="G44" s="7">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H44" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I44" s="7">
-        <v>8909</v>
+        <v>6167</v>
       </c>
       <c r="J44" s="5">
-        <v>69.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>86.5</v>
+        <v>77.3</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>199000</v>
+        <v>892000</v>
       </c>
       <c r="G45" s="7">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="H45" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I45" s="7">
-        <v>5182</v>
+        <v>30250</v>
       </c>
       <c r="J45" s="5">
-        <v>68.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>81.3</v>
+        <v>88.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>2486000</v>
+        <v>300000</v>
       </c>
       <c r="G46" s="7">
-        <v>-16000</v>
+        <v>30000</v>
       </c>
       <c r="H46" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I46" s="7">
-        <v>16455</v>
+        <v>5667</v>
       </c>
       <c r="J46" s="5">
-        <v>68.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>87.7</v>
+        <v>83.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>354000</v>
+        <v>299000</v>
       </c>
       <c r="G47" s="7">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="H47" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I47" s="7">
-        <v>2364</v>
+        <v>15167</v>
       </c>
       <c r="J47" s="5">
-        <v>68.8</v>
+        <v>69.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>84</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>198000</v>
+        <v>219000</v>
       </c>
       <c r="G48" s="7">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H48" s="7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7">
-        <v>10545</v>
+        <v>14000</v>
       </c>
       <c r="J48" s="5">
-        <v>68.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>138000</v>
+        <v>750000</v>
       </c>
       <c r="G49" s="7">
         <v>0</v>
       </c>
       <c r="H49" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I49" s="7">
-        <v>9300</v>
+        <v>30750</v>
       </c>
       <c r="J49" s="5">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>83.7</v>
+        <v>86.7</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>2673000</v>
+        <v>543000</v>
       </c>
       <c r="G50" s="7">
-        <v>40000</v>
+        <v>-11000</v>
       </c>
       <c r="H50" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I50" s="7">
-        <v>9273</v>
+        <v>7250</v>
       </c>
       <c r="J50" s="5">
-        <v>68.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>334000</v>
+        <v>121000</v>
       </c>
       <c r="G51" s="7">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H51" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I51" s="7">
-        <v>10091</v>
+        <v>6556</v>
       </c>
       <c r="J51" s="5">
-        <v>68.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>191000</v>
+        <v>356000</v>
       </c>
       <c r="G52" s="7">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H52" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I52" s="7">
-        <v>6727</v>
+        <v>2333</v>
       </c>
       <c r="J52" s="5">
-        <v>68.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>84.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>153000</v>
+        <v>173000</v>
       </c>
       <c r="G53" s="7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H53" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I53" s="7">
-        <v>8400</v>
+        <v>12333</v>
       </c>
       <c r="J53" s="5">
-        <v>68.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>84.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>141000</v>
+        <v>1305000</v>
       </c>
       <c r="G54" s="7">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="H54" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I54" s="7">
-        <v>6818</v>
+        <v>23167</v>
       </c>
       <c r="J54" s="5">
-        <v>68.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-05T10:15:44+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-06T10:18:47+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>全球死考：刚下刑场你让我去考试</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>诸神愚戏</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
     <t>刚证道混沌天帝，让我身化禁区？</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>诸神愚戏</t>
-  </si>
-  <si>
-    <t>全球死考：刚下刑场你让我去考试</t>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>重生后，姐姐非要嫁给我</t>
+  </si>
+  <si>
+    <t>开局日军围城，系统让我当德皇</t>
+  </si>
+  <si>
+    <t>神豪太青涩，校花闺蜜团只好倒追</t>
+  </si>
+  <si>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
+  </si>
+  <si>
+    <t>奥特：最强债主！借债十倍返还！</t>
+  </si>
+  <si>
+    <t>穿越刘备，死后和我说这是型月？</t>
+  </si>
+  <si>
+    <t>封印神源百万年，悟性每天翻倍</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>谍战：我当恶霸能爆奖励！</t>
   </si>
   <si>
     <t>年代1960：穿越南锣鼓巷，</t>
   </si>
   <si>
-    <t>公安局长之扫黑风暴</t>
+    <t>这个猫娘？怎么是尼古喵喵啊！！</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>洪武苟神：我只想活到永乐拿十亿</t>
+  </si>
+  <si>
+    <t>四合院：我家住隔壁，看众禽互咬</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>国运班级求生：机电2班闹翻荒野</t>
+  </si>
+  <si>
+    <t>我根骨平庸，但分身都是绝世天才</t>
+  </si>
+  <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>我在诡异副本女装直播后爆火了</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
   </si>
   <si>
     <t>我提前三天被丢进了末世</t>
   </si>
   <si>
+    <t>三棍打散兄妹情，我家兄长不当人</t>
+  </si>
+  <si>
+    <t>每天属性翻一倍，我黑化爆杀一切</t>
+  </si>
+  <si>
+    <t>西幻：从鹰人部落到天使帝国</t>
+  </si>
+  <si>
+    <t>开局大限将至，我携帝兵问道禁区</t>
+  </si>
+  <si>
+    <t>天仙怀了我的娃，千年世家被曝光</t>
+  </si>
+  <si>
+    <t>重生神医：参加网综炸翻医学界</t>
+  </si>
+  <si>
+    <t>魔王叫我小同志，那就是世界错了</t>
+  </si>
+  <si>
+    <t>重生后，成了妹妹的专属爱物</t>
+  </si>
+  <si>
+    <t>瘟疫模拟：开局投放Necroa</t>
+  </si>
+  <si>
     <t>抗战：从湘江开始一路横推</t>
   </si>
   <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>天仙怀了我的娃，千年世家被曝光</t>
-  </si>
-  <si>
-    <t>全民县令：我看广告无限刷资源</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>谍战：我当恶霸能爆奖励！</t>
-  </si>
-  <si>
-    <t>国运班级求生：机电2班闹翻荒野</t>
-  </si>
-  <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
-  </si>
-  <si>
-    <t>我在精神病院学斩神</t>
-  </si>
-  <si>
-    <t>穿越刘备，死后和我说这是型月？</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>每天属性翻一倍，我黑化爆杀一切</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>重生后，姐姐非要嫁给我</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>兵王之我是一个交警</t>
-  </si>
-  <si>
-    <t>开局大限将至，我携帝兵问道禁区</t>
-  </si>
-  <si>
-    <t>封印神源百万年，悟性每天翻倍</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
-  </si>
-  <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>神豪太青涩，校花闺蜜团只好倒追</t>
-  </si>
-  <si>
-    <t>重生神医：参加网综炸翻医学界</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>这个猫娘？怎么是尼古喵喵啊！！</t>
-  </si>
-  <si>
-    <t>开局四选一，我选成为沪圈少爷！</t>
-  </si>
-  <si>
-    <t>别人夺嫡偷偷来，我家皇帝下圣旨</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
-  </si>
-  <si>
-    <t>妖魔乱世：从造畜法开始左道成仙</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>领证三天，我被未婚妻杀死</t>
-  </si>
-  <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
-  </si>
-  <si>
-    <t>四合院：我家住隔壁，看众禽互咬</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>什么天幕？明明是古人破防日记</t>
-  </si>
-  <si>
-    <t>四合院，哈军工副院，部下李云龙</t>
-  </si>
-  <si>
-    <t>我根骨平庸，但分身都是绝世天才</t>
-  </si>
-  <si>
-    <t>我操作的少女正在成为旧日之主</t>
+    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+  </si>
+  <si>
+    <t>桃花美人村</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>792000</v>
+        <v>2044000</v>
       </c>
       <c r="G5" s="7">
-        <v>111000</v>
+        <v>256000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I5" s="7">
-        <v>77857</v>
+        <v>96846</v>
       </c>
       <c r="J5" s="5">
-        <v>94.5</v>
+        <v>96.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>84.2</v>
+        <v>82.2</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1547000</v>
+        <v>2797000</v>
       </c>
       <c r="G6" s="7">
-        <v>73000</v>
+        <v>0</v>
       </c>
       <c r="H6" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="7">
-        <v>88167</v>
+        <v>115846</v>
       </c>
       <c r="J6" s="5">
-        <v>88.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>78.2</v>
+        <v>85</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>2797000</v>
+        <v>1634000</v>
       </c>
       <c r="G7" s="7">
-        <v>-118000</v>
+        <v>87000</v>
       </c>
       <c r="H7" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="7">
-        <v>125500</v>
+        <v>88077</v>
       </c>
       <c r="J7" s="5">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>80.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>1788000</v>
+        <v>792000</v>
       </c>
       <c r="G8" s="7">
         <v>0</v>
       </c>
       <c r="H8" s="7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I8" s="7">
-        <v>83583</v>
+        <v>68125</v>
       </c>
       <c r="J8" s="5">
-        <v>85.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>94</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>624000</v>
+        <v>647000</v>
       </c>
       <c r="G9" s="7">
-        <v>103000</v>
+        <v>0</v>
       </c>
       <c r="H9" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="7">
-        <v>36583</v>
+        <v>36231</v>
       </c>
       <c r="J9" s="5">
-        <v>80.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>91.8</v>
+        <v>94.3</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>647000</v>
+        <v>217000</v>
       </c>
       <c r="G10" s="7">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="H10" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>39250</v>
+        <v>20000</v>
       </c>
       <c r="J10" s="5">
-        <v>80.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>100</v>
+        <v>86.8</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>186000</v>
+        <v>829000</v>
       </c>
       <c r="G11" s="7">
-        <v>28000</v>
+        <v>79000</v>
       </c>
       <c r="H11" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="7">
-        <v>10500</v>
+        <v>34462</v>
       </c>
       <c r="J11" s="5">
-        <v>77.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>98.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>125000</v>
+        <v>302000</v>
       </c>
       <c r="G12" s="7">
+        <v>21000</v>
+      </c>
+      <c r="H12" s="7">
+        <v>14</v>
+      </c>
+      <c r="I12" s="7">
         <v>15000</v>
       </c>
-      <c r="H12" s="7">
-        <v>7</v>
-      </c>
-      <c r="I12" s="7">
-        <v>10667</v>
-      </c>
       <c r="J12" s="5">
-        <v>76.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>92</v>
+        <v>91.2</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>680000</v>
+        <v>225000</v>
       </c>
       <c r="G13" s="7">
-        <v>24000</v>
+        <v>13000</v>
       </c>
       <c r="H13" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I13" s="7">
-        <v>23333</v>
+        <v>19333</v>
       </c>
       <c r="J13" s="5">
-        <v>76.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>87</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>538000</v>
+        <v>908000</v>
       </c>
       <c r="G14" s="7">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="H14" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="7">
-        <v>30917</v>
+        <v>34231</v>
       </c>
       <c r="J14" s="5">
-        <v>75.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>96.3</v>
+        <v>88.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>122000</v>
+        <v>680000</v>
       </c>
       <c r="G15" s="7">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I15" s="7">
-        <v>9286</v>
+        <v>21538</v>
       </c>
       <c r="J15" s="5">
-        <v>75.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>94</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>201000</v>
+        <v>341000</v>
       </c>
       <c r="G16" s="7">
-        <v>54000</v>
+        <v>10000</v>
       </c>
       <c r="H16" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I16" s="7">
-        <v>21200</v>
+        <v>17833</v>
       </c>
       <c r="J16" s="5">
-        <v>75</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>87.3</v>
+        <v>88.8</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>481000</v>
+        <v>564000</v>
       </c>
       <c r="G17" s="7">
-        <v>46000</v>
+        <v>0</v>
       </c>
       <c r="H17" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="7">
-        <v>25750</v>
+        <v>18462</v>
       </c>
       <c r="J17" s="5">
-        <v>74.5</v>
+        <v>73.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>82.3</v>
+        <v>93.2</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>885000</v>
+        <v>126000</v>
       </c>
       <c r="G18" s="7">
-        <v>22000</v>
+        <v>9000</v>
       </c>
       <c r="H18" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I18" s="7">
-        <v>35167</v>
+        <v>7545</v>
       </c>
       <c r="J18" s="5">
-        <v>74.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>86.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>333000</v>
+        <v>376000</v>
       </c>
       <c r="G19" s="7">
-        <v>32000</v>
+        <v>10000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>25667</v>
+        <v>17143</v>
       </c>
       <c r="J19" s="5">
-        <v>74</v>
+        <v>72.7</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>91.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>300000</v>
+        <v>225000</v>
       </c>
       <c r="G20" s="7">
-        <v>13000</v>
+        <v>4000</v>
       </c>
       <c r="H20" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="7">
-        <v>14727</v>
+        <v>15667</v>
       </c>
       <c r="J20" s="5">
-        <v>73.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>86.3</v>
+        <v>80.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>478000</v>
+        <v>603000</v>
       </c>
       <c r="G21" s="7">
-        <v>2000</v>
+        <v>65000</v>
       </c>
       <c r="H21" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I21" s="7">
-        <v>24636</v>
+        <v>33538</v>
       </c>
       <c r="J21" s="5">
-        <v>73.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1327,19 +1327,19 @@
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>2101000</v>
+        <v>171000</v>
       </c>
       <c r="G22" s="7">
-        <v>189000</v>
+        <v>6000</v>
       </c>
       <c r="H22" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="7">
-        <v>16583</v>
+        <v>12077</v>
       </c>
       <c r="J22" s="5">
-        <v>73.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>405000</v>
+        <v>197000</v>
       </c>
       <c r="G23" s="7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>18444</v>
+        <v>13667</v>
       </c>
       <c r="J23" s="5">
-        <v>73</v>
+        <v>72.3</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>93.7</v>
+        <v>87.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>213000</v>
+        <v>402000</v>
       </c>
       <c r="G24" s="7">
-        <v>14000</v>
+        <v>-3000</v>
       </c>
       <c r="H24" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I24" s="7">
-        <v>5917</v>
+        <v>16300</v>
       </c>
       <c r="J24" s="5">
-        <v>73</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>214000</v>
+        <v>260000</v>
       </c>
       <c r="G25" s="7">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I25" s="7">
-        <v>14667</v>
+        <v>11538</v>
       </c>
       <c r="J25" s="5">
-        <v>72.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>87.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>778000</v>
+        <v>551000</v>
       </c>
       <c r="G26" s="7">
-        <v>-12000</v>
+        <v>12000</v>
       </c>
       <c r="H26" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" s="7">
-        <v>17583</v>
+        <v>29846</v>
       </c>
       <c r="J26" s="5">
-        <v>72.7</v>
+        <v>72</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>88.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>262000</v>
+        <v>356000</v>
       </c>
       <c r="G27" s="7">
-        <v>4000</v>
+        <v>23000</v>
       </c>
       <c r="H27" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>15917</v>
+        <v>25286</v>
       </c>
       <c r="J27" s="5">
-        <v>72.7</v>
+        <v>72</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>86.5</v>
+        <v>79</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>564000</v>
+        <v>624000</v>
       </c>
       <c r="G28" s="7">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="H28" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="7">
-        <v>20000</v>
+        <v>33769</v>
       </c>
       <c r="J28" s="5">
-        <v>72.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>89.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>281000</v>
+        <v>237000</v>
       </c>
       <c r="G29" s="7">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="H29" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>14500</v>
+        <v>12143</v>
       </c>
       <c r="J29" s="5">
-        <v>72.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>90.2</v>
+        <v>87.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>234000</v>
+        <v>761000</v>
       </c>
       <c r="G30" s="7">
-        <v>52000</v>
+        <v>-17000</v>
       </c>
       <c r="H30" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" s="7">
-        <v>11833</v>
+        <v>14923</v>
       </c>
       <c r="J30" s="5">
-        <v>72.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>89</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>118000</v>
+        <v>262000</v>
       </c>
       <c r="G31" s="7">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I31" s="7">
-        <v>13167</v>
+        <v>14692</v>
       </c>
       <c r="J31" s="5">
-        <v>72.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>89</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>252000</v>
+        <v>478000</v>
       </c>
       <c r="G32" s="7">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="H32" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I32" s="7">
-        <v>11833</v>
+        <v>24833</v>
       </c>
       <c r="J32" s="5">
-        <v>71.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>86.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>221000</v>
+        <v>224000</v>
       </c>
       <c r="G33" s="7">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H33" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I33" s="7">
-        <v>16727</v>
+        <v>12500</v>
       </c>
       <c r="J33" s="5">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>87.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
@@ -1726,16 +1726,16 @@
         <v>311000</v>
       </c>
       <c r="G34" s="7">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H34" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I34" s="7">
-        <v>14333</v>
+        <v>13231</v>
       </c>
       <c r="J34" s="5">
-        <v>71.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>85</v>
+        <v>86.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>212000</v>
+        <v>299000</v>
       </c>
       <c r="G35" s="7">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="H35" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I35" s="7">
-        <v>20125</v>
+        <v>13417</v>
       </c>
       <c r="J35" s="5">
-        <v>71.8</v>
+        <v>70.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>78.7</v>
+        <v>87</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>539000</v>
+        <v>180000</v>
       </c>
       <c r="G36" s="7">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H36" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>31333</v>
+        <v>11571</v>
       </c>
       <c r="J36" s="5">
-        <v>71.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>84.5</v>
+        <v>87.8</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>366000</v>
+        <v>257000</v>
       </c>
       <c r="G37" s="7">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I37" s="7">
-        <v>18333</v>
+        <v>9154</v>
       </c>
       <c r="J37" s="5">
-        <v>71.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>90.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>189000</v>
+        <v>543000</v>
       </c>
       <c r="G38" s="7">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H38" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I38" s="7">
-        <v>5667</v>
+        <v>6692</v>
       </c>
       <c r="J38" s="5">
-        <v>71</v>
+        <v>70.5</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>84.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>331000</v>
+        <v>892000</v>
       </c>
       <c r="G39" s="7">
-        <v>-9000</v>
+        <v>0</v>
       </c>
       <c r="H39" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I39" s="7">
-        <v>18545</v>
+        <v>27923</v>
       </c>
       <c r="J39" s="5">
-        <v>70.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.5</v>
+        <v>95</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>229000</v>
+        <v>102000</v>
       </c>
       <c r="G40" s="7">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="H40" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I40" s="7">
-        <v>12833</v>
+        <v>12750</v>
       </c>
       <c r="J40" s="5">
-        <v>70.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>86.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>165000</v>
+        <v>221000</v>
       </c>
       <c r="G41" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H41" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I41" s="7">
-        <v>12583</v>
+        <v>8077</v>
       </c>
       <c r="J41" s="5">
-        <v>70.5</v>
+        <v>70</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>83.3</v>
+        <v>85.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>341000</v>
+        <v>186000</v>
       </c>
       <c r="G42" s="7">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I42" s="7">
-        <v>18143</v>
+        <v>9692</v>
       </c>
       <c r="J42" s="5">
-        <v>70.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>87</v>
+        <v>81.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>255000</v>
+        <v>424000</v>
       </c>
       <c r="G43" s="7">
-        <v>0</v>
+        <v>-54000</v>
       </c>
       <c r="H43" s="7">
         <v>13</v>
       </c>
       <c r="I43" s="7">
-        <v>9750</v>
+        <v>18083</v>
       </c>
       <c r="J43" s="5">
-        <v>70.3</v>
+        <v>69.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>88.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>147000</v>
+        <v>218000</v>
       </c>
       <c r="G44" s="7">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H44" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I44" s="7">
-        <v>6167</v>
+        <v>13143</v>
       </c>
       <c r="J44" s="5">
-        <v>70.2</v>
+        <v>69.3</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>77.3</v>
+        <v>82.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>892000</v>
+        <v>193000</v>
       </c>
       <c r="G45" s="7">
-        <v>-15000</v>
+        <v>20000</v>
       </c>
       <c r="H45" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I45" s="7">
-        <v>30250</v>
+        <v>16167</v>
       </c>
       <c r="J45" s="5">
-        <v>70.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>88.5</v>
+        <v>84.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>300000</v>
+        <v>118000</v>
       </c>
       <c r="G46" s="7">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H46" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I46" s="7">
-        <v>5667</v>
+        <v>11286</v>
       </c>
       <c r="J46" s="5">
-        <v>70.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>83.5</v>
+        <v>81.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>299000</v>
+        <v>201000</v>
       </c>
       <c r="G47" s="7">
-        <v>-12000</v>
+        <v>0</v>
       </c>
       <c r="H47" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I47" s="7">
-        <v>15167</v>
+        <v>17667</v>
       </c>
       <c r="J47" s="5">
-        <v>69.7</v>
+        <v>69.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.40000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>219000</v>
+        <v>193000</v>
       </c>
       <c r="G48" s="7">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H48" s="7">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I48" s="7">
-        <v>14000</v>
+        <v>5538</v>
       </c>
       <c r="J48" s="5">
-        <v>69.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>76</v>
+        <v>83.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>750000</v>
+        <v>287000</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="H49" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I49" s="7">
-        <v>30750</v>
+        <v>13077</v>
       </c>
       <c r="J49" s="5">
-        <v>69.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>86.7</v>
+        <v>85.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>543000</v>
+        <v>333000</v>
       </c>
       <c r="G50" s="7">
-        <v>-11000</v>
+        <v>3000</v>
       </c>
       <c r="H50" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I50" s="7">
-        <v>7250</v>
+        <v>8462</v>
       </c>
       <c r="J50" s="5">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>121000</v>
+        <v>140000</v>
       </c>
       <c r="G51" s="7">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H51" s="7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I51" s="7">
-        <v>6556</v>
+        <v>7917</v>
       </c>
       <c r="J51" s="5">
-        <v>69.2</v>
+        <v>69</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>88.3</v>
+        <v>84.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>356000</v>
+        <v>125000</v>
       </c>
       <c r="G52" s="7">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H52" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I52" s="7">
-        <v>2333</v>
+        <v>9143</v>
       </c>
       <c r="J52" s="5">
-        <v>69.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2350,19 +2350,19 @@
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>173000</v>
+        <v>352000</v>
       </c>
       <c r="G53" s="7">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="H53" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I53" s="7">
-        <v>12333</v>
+        <v>11000</v>
       </c>
       <c r="J53" s="5">
-        <v>69.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>1305000</v>
+        <v>525000</v>
       </c>
       <c r="G54" s="7">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="H54" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I54" s="7">
-        <v>23167</v>
+        <v>22077</v>
       </c>
       <c r="J54" s="5">
-        <v>69</v>
+        <v>68.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-06T10:18:47+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-07T05:57:09+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>刚证道混沌天帝，让我身化禁区？</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>诸神愚戏</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
     <t>全球死考：刚下刑场你让我去考试</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>诸神愚戏</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>刚证道混沌天帝，让我身化禁区？</t>
-  </si>
-  <si>
     <t>公安局长之扫黑风暴</t>
   </si>
   <si>
+    <t>天仙怀了我的娃，千年世家被曝光</t>
+  </si>
+  <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
     <t>玄幻：我堕魔后把绝美师尊抓回来</t>
   </si>
   <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
     <t>文字武侠：开局破庙夜会帮主夫人</t>
   </si>
   <si>
+    <t>每天属性翻一倍，我黑化爆杀一切</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>我成假少爷后，八个妹妹不再隐忍</t>
+  </si>
+  <si>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>三角洲：资源无限供应，提现成壕</t>
+  </si>
+  <si>
+    <t>我在诡异副本女装直播后爆火了</t>
+  </si>
+  <si>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>开局大限将至，我携帝兵问道禁区</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
+  </si>
+  <si>
+    <t>奥特：最强债主！借债十倍返还！</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>我根骨平庸，但分身都是绝世天才</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
+  </si>
+  <si>
+    <t>捡来的妹妹修仙后，回来抢亲了</t>
+  </si>
+  <si>
+    <t>四合院：我家住隔壁，看众禽互咬</t>
+  </si>
+  <si>
+    <t>女多男少，开局被瓦学妹喊爸爸</t>
+  </si>
+  <si>
+    <t>抗战：从湘江开始一路横推</t>
+  </si>
+  <si>
+    <t>谍战：我当恶霸能爆奖励！</t>
+  </si>
+  <si>
     <t>编外法医：重案组抢疯了！</t>
   </si>
   <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>重生后，姐姐非要嫁给我</t>
+    <t>洲：质检打手，你五分钟诛仙清图</t>
   </si>
   <si>
     <t>开局日军围城，系统让我当德皇</t>
   </si>
   <si>
-    <t>神豪太青涩，校花闺蜜团只好倒追</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>开局四选一，我选成为沪圈少爷！</t>
-  </si>
-  <si>
-    <t>奥特：最强债主！借债十倍返还！</t>
-  </si>
-  <si>
-    <t>穿越刘备，死后和我说这是型月？</t>
-  </si>
-  <si>
-    <t>封印神源百万年，悟性每天翻倍</t>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
+  </si>
+  <si>
+    <t>国运班级求生：机电2班闹翻荒野</t>
+  </si>
+  <si>
+    <t>乡村神医，赵大牛的妖孽人生</t>
+  </si>
+  <si>
+    <t>家父造反成功，我被迫成为皇太子</t>
+  </si>
+  <si>
+    <t>全民县令：我看广告无限刷资源</t>
+  </si>
+  <si>
+    <t>封神守关，万界大阵成叹息之墙</t>
+  </si>
+  <si>
+    <t>领主巫师：从无限魔晶开始求学！</t>
+  </si>
+  <si>
+    <t>当紫袍天师降临诡异规则怪谈</t>
+  </si>
+  <si>
+    <t>桃花美人村</t>
+  </si>
+  <si>
+    <t>离婚后，我成了刀枪炮！</t>
   </si>
   <si>
     <t>穿越乱世：每天一份拼好饭</t>
   </si>
   <si>
-    <t>谍战：我当恶霸能爆奖励！</t>
-  </si>
-  <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>这个猫娘？怎么是尼古喵喵啊！！</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
     <t>我只想砍死各位，或者被各位砍死</t>
   </si>
   <si>
-    <t>洪武苟神：我只想活到永乐拿十亿</t>
-  </si>
-  <si>
-    <t>四合院：我家住隔壁，看众禽互咬</t>
-  </si>
-  <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
-  </si>
-  <si>
-    <t>国运班级求生：机电2班闹翻荒野</t>
-  </si>
-  <si>
-    <t>我根骨平庸，但分身都是绝世天才</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
+    <t>在病娇的摧残下，我选择跑路了</t>
   </si>
   <si>
     <t>我都宇宙之主了，你们还在地球？</t>
   </si>
   <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>我在诡异副本女装直播后爆火了</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>我提前三天被丢进了末世</t>
-  </si>
-  <si>
-    <t>三棍打散兄妹情，我家兄长不当人</t>
-  </si>
-  <si>
-    <t>每天属性翻一倍，我黑化爆杀一切</t>
-  </si>
-  <si>
-    <t>西幻：从鹰人部落到天使帝国</t>
-  </si>
-  <si>
-    <t>开局大限将至，我携帝兵问道禁区</t>
-  </si>
-  <si>
-    <t>天仙怀了我的娃，千年世家被曝光</t>
-  </si>
-  <si>
-    <t>重生神医：参加网综炸翻医学界</t>
-  </si>
-  <si>
-    <t>魔王叫我小同志，那就是世界错了</t>
-  </si>
-  <si>
-    <t>重生后，成了妹妹的专属爱物</t>
-  </si>
-  <si>
-    <t>瘟疫模拟：开局投放Necroa</t>
-  </si>
-  <si>
-    <t>抗战：从湘江开始一路横推</t>
-  </si>
-  <si>
-    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
-  </si>
-  <si>
-    <t>桃花美人村</t>
+    <t>战龙令</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>2044000</v>
+        <v>854000</v>
       </c>
       <c r="G5" s="7">
-        <v>256000</v>
+        <v>62000</v>
       </c>
       <c r="H5" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I5" s="7">
-        <v>96846</v>
+        <v>67444</v>
       </c>
       <c r="J5" s="5">
-        <v>96.5</v>
+        <v>90.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>82.2</v>
+        <v>81.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>2797000</v>
+        <v>2783000</v>
       </c>
       <c r="G6" s="7">
-        <v>0</v>
+        <v>-14000</v>
       </c>
       <c r="H6" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" s="7">
-        <v>115846</v>
+        <v>106571</v>
       </c>
       <c r="J6" s="5">
-        <v>90.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>85</v>
+        <v>84.7</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1634000</v>
+        <v>1719000</v>
       </c>
       <c r="G7" s="7">
-        <v>87000</v>
+        <v>85000</v>
       </c>
       <c r="H7" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="7">
-        <v>88077</v>
+        <v>87857</v>
       </c>
       <c r="J7" s="5">
-        <v>88.8</v>
+        <v>88.5</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>89.5</v>
+        <v>81.2</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>792000</v>
+        <v>2053000</v>
       </c>
       <c r="G8" s="7">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="H8" s="7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I8" s="7">
-        <v>68125</v>
+        <v>90571</v>
       </c>
       <c r="J8" s="5">
-        <v>86.3</v>
+        <v>87.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>89.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>647000</v>
+        <v>657000</v>
       </c>
       <c r="G9" s="7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H9" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" s="7">
-        <v>36231</v>
+        <v>34357</v>
       </c>
       <c r="J9" s="5">
-        <v>78.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>94.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>217000</v>
+        <v>238000</v>
       </c>
       <c r="G10" s="7">
-        <v>20000</v>
+        <v>37000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="7">
-        <v>20000</v>
+        <v>20429</v>
       </c>
       <c r="J10" s="5">
-        <v>76.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>86.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>829000</v>
+        <v>382000</v>
       </c>
       <c r="G11" s="7">
-        <v>79000</v>
+        <v>73000</v>
       </c>
       <c r="H11" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
-        <v>34462</v>
+        <v>38250</v>
       </c>
       <c r="J11" s="5">
-        <v>76.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>94.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>302000</v>
+        <v>240000</v>
       </c>
       <c r="G12" s="7">
-        <v>21000</v>
+        <v>23000</v>
       </c>
       <c r="H12" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>15000</v>
+        <v>20429</v>
       </c>
       <c r="J12" s="5">
-        <v>75.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>91.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>225000</v>
+        <v>288000</v>
       </c>
       <c r="G13" s="7">
-        <v>13000</v>
+        <v>31000</v>
       </c>
       <c r="H13" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I13" s="7">
-        <v>19333</v>
+        <v>10714</v>
       </c>
       <c r="J13" s="5">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>82.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>908000</v>
+        <v>715000</v>
       </c>
       <c r="G14" s="7">
-        <v>23000</v>
+        <v>112000</v>
       </c>
       <c r="H14" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" s="7">
-        <v>34231</v>
+        <v>39143</v>
       </c>
       <c r="J14" s="5">
-        <v>73.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>88.3</v>
+        <v>91.5</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>680000</v>
+        <v>701000</v>
       </c>
       <c r="G15" s="7">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="H15" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" s="7">
-        <v>21538</v>
+        <v>21500</v>
       </c>
       <c r="J15" s="5">
-        <v>73.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>89.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>341000</v>
+        <v>884000</v>
       </c>
       <c r="G16" s="7">
-        <v>10000</v>
+        <v>55000</v>
       </c>
       <c r="H16" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I16" s="7">
-        <v>17833</v>
+        <v>35929</v>
       </c>
       <c r="J16" s="5">
-        <v>73.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>88.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>564000</v>
+        <v>239000</v>
       </c>
       <c r="G17" s="7">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="H17" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7">
-        <v>18462</v>
+        <v>14125</v>
       </c>
       <c r="J17" s="5">
-        <v>73.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>93.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>126000</v>
+        <v>353000</v>
       </c>
       <c r="G18" s="7">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="H18" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I18" s="7">
-        <v>7545</v>
+        <v>17385</v>
       </c>
       <c r="J18" s="5">
-        <v>73.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>88.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>376000</v>
+        <v>189000</v>
       </c>
       <c r="G19" s="7">
-        <v>10000</v>
+        <v>19000</v>
       </c>
       <c r="H19" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I19" s="7">
-        <v>17143</v>
+        <v>14400</v>
       </c>
       <c r="J19" s="5">
-        <v>72.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>88.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>225000</v>
+        <v>652000</v>
       </c>
       <c r="G20" s="7">
-        <v>4000</v>
+        <v>28000</v>
       </c>
       <c r="H20" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I20" s="7">
-        <v>15667</v>
+        <v>33357</v>
       </c>
       <c r="J20" s="5">
-        <v>72.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>80.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>603000</v>
+        <v>260000</v>
       </c>
       <c r="G21" s="7">
-        <v>65000</v>
+        <v>34000</v>
       </c>
       <c r="H21" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I21" s="7">
-        <v>33538</v>
+        <v>21500</v>
       </c>
       <c r="J21" s="5">
-        <v>72.5</v>
+        <v>73.8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>89.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>171000</v>
+        <v>104000</v>
       </c>
       <c r="G22" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H22" s="7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>12077</v>
+        <v>7333</v>
       </c>
       <c r="J22" s="5">
-        <v>72.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>197000</v>
+        <v>123000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>21000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I23" s="7">
-        <v>13667</v>
+        <v>14400</v>
       </c>
       <c r="J23" s="5">
-        <v>72.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>87.3</v>
+        <v>92.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>402000</v>
+        <v>199000</v>
       </c>
       <c r="G24" s="7">
-        <v>-3000</v>
+        <v>13000</v>
       </c>
       <c r="H24" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I24" s="7">
-        <v>16300</v>
+        <v>9929</v>
       </c>
       <c r="J24" s="5">
-        <v>72.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>260000</v>
+        <v>126000</v>
       </c>
       <c r="G25" s="7">
         <v>8000</v>
       </c>
       <c r="H25" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I25" s="7">
-        <v>11538</v>
+        <v>10875</v>
       </c>
       <c r="J25" s="5">
-        <v>72.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>80.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>551000</v>
+        <v>232000</v>
       </c>
       <c r="G26" s="7">
-        <v>12000</v>
+        <v>7000</v>
       </c>
       <c r="H26" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I26" s="7">
-        <v>29846</v>
+        <v>18100</v>
       </c>
       <c r="J26" s="5">
-        <v>72</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>83</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>356000</v>
+        <v>211000</v>
       </c>
       <c r="G27" s="7">
-        <v>23000</v>
+        <v>14000</v>
       </c>
       <c r="H27" s="7">
         <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>25286</v>
+        <v>13714</v>
       </c>
       <c r="J27" s="5">
-        <v>72</v>
+        <v>72.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>79</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>624000</v>
+        <v>915000</v>
       </c>
       <c r="G28" s="7">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H28" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="7">
-        <v>33769</v>
+        <v>32286</v>
       </c>
       <c r="J28" s="5">
-        <v>71.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>88.7</v>
+        <v>89.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>237000</v>
+        <v>192000</v>
       </c>
       <c r="G29" s="7">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" s="7">
-        <v>12143</v>
+        <v>11625</v>
       </c>
       <c r="J29" s="5">
-        <v>71.8</v>
+        <v>72.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>87.2</v>
+        <v>89.7</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>761000</v>
+        <v>177000</v>
       </c>
       <c r="G30" s="7">
-        <v>-17000</v>
+        <v>6000</v>
       </c>
       <c r="H30" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" s="7">
-        <v>14923</v>
+        <v>11643</v>
       </c>
       <c r="J30" s="5">
-        <v>71.7</v>
+        <v>72.2</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>262000</v>
+        <v>123000</v>
       </c>
       <c r="G31" s="7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H31" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I31" s="7">
-        <v>14692</v>
+        <v>6818</v>
       </c>
       <c r="J31" s="5">
-        <v>71.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>81.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>478000</v>
+        <v>233000</v>
       </c>
       <c r="G32" s="7">
-        <v>20000</v>
+        <v>9000</v>
       </c>
       <c r="H32" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>24833</v>
+        <v>12000</v>
       </c>
       <c r="J32" s="5">
-        <v>71.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>87.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>224000</v>
+        <v>180000</v>
       </c>
       <c r="G33" s="7">
-        <v>5000</v>
+        <v>47000</v>
       </c>
       <c r="H33" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>12500</v>
+        <v>21250</v>
       </c>
       <c r="J33" s="5">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>86.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>311000</v>
+        <v>132000</v>
       </c>
       <c r="G34" s="7">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H34" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I34" s="7">
-        <v>13231</v>
+        <v>8875</v>
       </c>
       <c r="J34" s="5">
-        <v>70.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>86.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>299000</v>
+        <v>373000</v>
       </c>
       <c r="G35" s="7">
-        <v>-1000</v>
+        <v>17000</v>
       </c>
       <c r="H35" s="7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>13417</v>
+        <v>24250</v>
       </c>
       <c r="J35" s="5">
-        <v>70.8</v>
+        <v>71.5</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>87</v>
+        <v>86.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>180000</v>
+        <v>300000</v>
       </c>
       <c r="G36" s="7">
-        <v>7000</v>
+        <v>-2000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I36" s="7">
-        <v>11571</v>
+        <v>13786</v>
       </c>
       <c r="J36" s="5">
-        <v>70.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>87.8</v>
+        <v>86.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>257000</v>
+        <v>224000</v>
       </c>
       <c r="G37" s="7">
-        <v>2000</v>
+        <v>-1000</v>
       </c>
       <c r="H37" s="7">
         <v>14</v>
       </c>
       <c r="I37" s="7">
-        <v>9154</v>
+        <v>14385</v>
       </c>
       <c r="J37" s="5">
-        <v>70.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>88.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>543000</v>
+        <v>131000</v>
       </c>
       <c r="G38" s="7">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H38" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I38" s="7">
-        <v>6692</v>
+        <v>7333</v>
       </c>
       <c r="J38" s="5">
-        <v>70.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>78.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>892000</v>
+        <v>743000</v>
       </c>
       <c r="G39" s="7">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="H39" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I39" s="7">
-        <v>27923</v>
+        <v>12571</v>
       </c>
       <c r="J39" s="5">
-        <v>70.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>102000</v>
+        <v>226000</v>
       </c>
       <c r="G40" s="7">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="H40" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I40" s="7">
-        <v>12750</v>
+        <v>7857</v>
       </c>
       <c r="J40" s="5">
-        <v>70.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>87.2</v>
+        <v>86.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>221000</v>
+        <v>302000</v>
       </c>
       <c r="G41" s="7">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="H41" s="7">
         <v>14</v>
       </c>
       <c r="I41" s="7">
-        <v>8077</v>
+        <v>12615</v>
       </c>
       <c r="J41" s="5">
-        <v>70</v>
+        <v>70.8</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>85.5</v>
+        <v>87.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>186000</v>
+        <v>110000</v>
       </c>
       <c r="G42" s="7">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H42" s="7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>9692</v>
+        <v>9667</v>
       </c>
       <c r="J42" s="5">
-        <v>69.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>81.5</v>
+        <v>93.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>424000</v>
+        <v>156000</v>
       </c>
       <c r="G43" s="7">
-        <v>-54000</v>
+        <v>31000</v>
       </c>
       <c r="H43" s="7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I43" s="7">
-        <v>18083</v>
+        <v>39500</v>
       </c>
       <c r="J43" s="5">
-        <v>69.3</v>
+        <v>70.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>83.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>218000</v>
+        <v>496000</v>
       </c>
       <c r="G44" s="7">
-        <v>4000</v>
+        <v>15000</v>
       </c>
       <c r="H44" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I44" s="7">
-        <v>13143</v>
+        <v>23143</v>
       </c>
       <c r="J44" s="5">
-        <v>69.3</v>
+        <v>70.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>82.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>193000</v>
+        <v>167000</v>
       </c>
       <c r="G45" s="7">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="H45" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>16167</v>
+        <v>11000</v>
       </c>
       <c r="J45" s="5">
-        <v>69.3</v>
+        <v>70.2</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>84.5</v>
+        <v>85.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>118000</v>
+        <v>305000</v>
       </c>
       <c r="G46" s="7">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="H46" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I46" s="7">
-        <v>11286</v>
+        <v>11857</v>
       </c>
       <c r="J46" s="5">
-        <v>69.3</v>
+        <v>70</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>81.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>201000</v>
+        <v>133000</v>
       </c>
       <c r="G47" s="7">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H47" s="7">
         <v>7</v>
       </c>
       <c r="I47" s="7">
-        <v>17667</v>
+        <v>6000</v>
       </c>
       <c r="J47" s="5">
-        <v>69.2</v>
+        <v>69.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>86.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>193000</v>
+        <v>533000</v>
       </c>
       <c r="G48" s="7">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="H48" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I48" s="7">
-        <v>5538</v>
+        <v>21071</v>
       </c>
       <c r="J48" s="5">
-        <v>69.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>83.3</v>
+        <v>92</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>287000</v>
+        <v>298000</v>
       </c>
       <c r="G49" s="7">
-        <v>-12000</v>
+        <v>24000</v>
       </c>
       <c r="H49" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7">
-        <v>13077</v>
+        <v>15000</v>
       </c>
       <c r="J49" s="5">
-        <v>69.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>85.2</v>
+        <v>77.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>333000</v>
+        <v>543000</v>
       </c>
       <c r="G50" s="7">
-        <v>3000</v>
+        <v>-8000</v>
       </c>
       <c r="H50" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I50" s="7">
-        <v>8462</v>
+        <v>27143</v>
       </c>
       <c r="J50" s="5">
-        <v>69</v>
+        <v>69.2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>140000</v>
+        <v>253000</v>
       </c>
       <c r="G51" s="7">
-        <v>2000</v>
+        <v>-9000</v>
       </c>
       <c r="H51" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I51" s="7">
-        <v>7917</v>
+        <v>13000</v>
       </c>
       <c r="J51" s="5">
-        <v>69</v>
+        <v>69.2</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.7</v>
+        <v>87.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>125000</v>
+        <v>165000</v>
       </c>
       <c r="G52" s="7">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H52" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I52" s="7">
-        <v>9143</v>
+        <v>5143</v>
       </c>
       <c r="J52" s="5">
-        <v>68.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>83.7</v>
+        <v>86.8</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>352000</v>
+        <v>533000</v>
       </c>
       <c r="G53" s="7">
-        <v>25000</v>
+        <v>-10000</v>
       </c>
       <c r="H53" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I53" s="7">
-        <v>11000</v>
+        <v>5500</v>
       </c>
       <c r="J53" s="5">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>78.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>525000</v>
+        <v>210000</v>
       </c>
       <c r="G54" s="7">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="H54" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I54" s="7">
-        <v>22077</v>
+        <v>12545</v>
       </c>
       <c r="J54" s="5">
-        <v>68.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-07T05:57:09+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-08T04:21:56+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>诸神愚戏</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
     <t>刚证道混沌天帝，让我身化禁区？</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>诸神愚戏</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
     <t>全球死考：刚下刑场你让我去考试</t>
   </si>
   <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
+    <t>天仙怀了我的娃，千年世家被曝光</t>
+  </si>
+  <si>
+    <t>每天属性翻一倍，我黑化爆杀一切</t>
+  </si>
+  <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>我成假少爷后，八个妹妹不再隐忍</t>
+  </si>
+  <si>
+    <t>我在诡异副本女装直播后爆火了</t>
+  </si>
+  <si>
+    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
+  </si>
+  <si>
     <t>公安局长之扫黑风暴</t>
   </si>
   <si>
-    <t>天仙怀了我的娃，千年世家被曝光</t>
-  </si>
-  <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>努力就变强的我，被重生者曝光了</t>
+  </si>
+  <si>
+    <t>国运班级求生：机电2班闹翻荒野</t>
+  </si>
+  <si>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>南部档案：我真不想当张家主事人</t>
   </si>
   <si>
     <t>实习教出金牌班，家长要换班主任</t>
   </si>
   <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>每天属性翻一倍，我黑化爆杀一切</t>
-  </si>
-  <si>
     <t>名义：开局我举报我自己</t>
   </si>
   <si>
-    <t>我成假少爷后，八个妹妹不再隐忍</t>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>师尊嫌我肮脏？反手退师帖送上</t>
+  </si>
+  <si>
+    <t>乡村神医，赵大牛的妖孽人生</t>
+  </si>
+  <si>
+    <t>开局大限将至，我携帝兵问道禁区</t>
+  </si>
+  <si>
+    <t>北平37：从抽到警局到拥兵百万</t>
+  </si>
+  <si>
+    <t>时停起手，邪神也得给我跪下！</t>
   </si>
   <si>
     <t>年代1960：穿越南锣鼓巷，</t>
   </si>
   <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>捡来的妹妹修仙后，回来抢亲了</t>
   </si>
   <si>
     <t>三角洲：资源无限供应，提现成壕</t>
   </si>
   <si>
-    <t>我在诡异副本女装直播后爆火了</t>
-  </si>
-  <si>
-    <t>我提前三天被丢进了末世</t>
-  </si>
-  <si>
-    <t>开局大限将至，我携帝兵问道禁区</t>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>离婚后，我成了刀枪炮！</t>
+  </si>
+  <si>
+    <t>奥特：最强债主！借债十倍返还！</t>
+  </si>
+  <si>
+    <t>家父造反成功，我被迫成为皇太子</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
+  </si>
+  <si>
+    <t>开局三千重甲步兵，我大明怎么输</t>
+  </si>
+  <si>
+    <t>女多男少，开局被瓦学妹喊爸爸</t>
+  </si>
+  <si>
+    <t>四合院：我家住隔壁，看众禽互咬</t>
   </si>
   <si>
     <t>西游，你都成了猴子还要什么挂</t>
   </si>
   <si>
-    <t>奥特：最强债主！借债十倍返还！</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>我根骨平庸，但分身都是绝世天才</t>
-  </si>
-  <si>
-    <t>开局四选一，我选成为沪圈少爷！</t>
-  </si>
-  <si>
-    <t>捡来的妹妹修仙后，回来抢亲了</t>
-  </si>
-  <si>
-    <t>四合院：我家住隔壁，看众禽互咬</t>
-  </si>
-  <si>
-    <t>女多男少，开局被瓦学妹喊爸爸</t>
-  </si>
-  <si>
-    <t>抗战：从湘江开始一路横推</t>
-  </si>
-  <si>
-    <t>谍战：我当恶霸能爆奖励！</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
+    <t>在病娇的摧残下，我选择跑路了</t>
   </si>
   <si>
     <t>洲：质检打手，你五分钟诛仙清图</t>
   </si>
   <si>
-    <t>开局日军围城，系统让我当德皇</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>国运班级求生：机电2班闹翻荒野</t>
-  </si>
-  <si>
-    <t>乡村神医，赵大牛的妖孽人生</t>
-  </si>
-  <si>
-    <t>家父造反成功，我被迫成为皇太子</t>
-  </si>
-  <si>
-    <t>全民县令：我看广告无限刷资源</t>
+    <t>规则怪谈：我即怪谈</t>
+  </si>
+  <si>
+    <t>农村女婿</t>
   </si>
   <si>
     <t>封神守关，万界大阵成叹息之墙</t>
   </si>
   <si>
-    <t>领主巫师：从无限魔晶开始求学！</t>
-  </si>
-  <si>
-    <t>当紫袍天师降临诡异规则怪谈</t>
-  </si>
-  <si>
-    <t>桃花美人村</t>
-  </si>
-  <si>
-    <t>离婚后，我成了刀枪炮！</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>在病娇的摧残下，我选择跑路了</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
     <t>战龙令</t>
+  </si>
+  <si>
+    <t>修仙界搞回收，破产仙子请自重</t>
+  </si>
+  <si>
+    <t>魂穿民国成为教导总队中校参谋</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>97.5</v>
+        <v>82</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>854000</v>
+        <v>2776000</v>
       </c>
       <c r="G5" s="7">
-        <v>62000</v>
+        <v>-7000</v>
       </c>
       <c r="H5" s="7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I5" s="7">
-        <v>67444</v>
+        <v>99000</v>
       </c>
       <c r="J5" s="5">
-        <v>90.5</v>
+        <v>89.8</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>81.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>2783000</v>
+        <v>1809000</v>
       </c>
       <c r="G6" s="7">
-        <v>-14000</v>
+        <v>90000</v>
       </c>
       <c r="H6" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" s="7">
-        <v>106571</v>
+        <v>88000</v>
       </c>
       <c r="J6" s="5">
-        <v>89.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,23 +825,23 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>84.7</v>
+        <v>95</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1719000</v>
+        <v>899000</v>
       </c>
       <c r="G7" s="7">
-        <v>85000</v>
+        <v>45000</v>
       </c>
       <c r="H7" s="7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I7" s="7">
-        <v>87857</v>
+        <v>65200</v>
       </c>
       <c r="J7" s="5">
         <v>88.5</v>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>81.2</v>
+        <v>78.2</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>2053000</v>
+        <v>2003000</v>
       </c>
       <c r="G8" s="7">
-        <v>9000</v>
+        <v>-50000</v>
       </c>
       <c r="H8" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" s="7">
-        <v>90571</v>
+        <v>81200</v>
       </c>
       <c r="J8" s="5">
-        <v>87.3</v>
+        <v>83.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>90.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>657000</v>
+        <v>447000</v>
       </c>
       <c r="G9" s="7">
-        <v>10000</v>
+        <v>65000</v>
       </c>
       <c r="H9" s="7">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>34357</v>
+        <v>43600</v>
       </c>
       <c r="J9" s="5">
-        <v>78.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>96.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>238000</v>
+        <v>279000</v>
       </c>
       <c r="G10" s="7">
-        <v>37000</v>
+        <v>41000</v>
       </c>
       <c r="H10" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="7">
-        <v>20429</v>
+        <v>23000</v>
       </c>
       <c r="J10" s="5">
-        <v>78.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>97.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>382000</v>
+        <v>273000</v>
       </c>
       <c r="G11" s="7">
-        <v>73000</v>
+        <v>34000</v>
       </c>
       <c r="H11" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I11" s="7">
-        <v>38250</v>
+        <v>16333</v>
       </c>
       <c r="J11" s="5">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>240000</v>
+        <v>343000</v>
       </c>
       <c r="G12" s="7">
-        <v>23000</v>
+        <v>55000</v>
       </c>
       <c r="H12" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I12" s="7">
-        <v>20429</v>
+        <v>13667</v>
       </c>
       <c r="J12" s="5">
-        <v>77.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>99.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>288000</v>
+        <v>857000</v>
       </c>
       <c r="G13" s="7">
-        <v>31000</v>
+        <v>142000</v>
       </c>
       <c r="H13" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" s="7">
-        <v>10714</v>
+        <v>46000</v>
       </c>
       <c r="J13" s="5">
-        <v>77.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>84.3</v>
+        <v>96.8</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>715000</v>
+        <v>213000</v>
       </c>
       <c r="G14" s="7">
-        <v>112000</v>
+        <v>24000</v>
       </c>
       <c r="H14" s="7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>39143</v>
+        <v>16000</v>
       </c>
       <c r="J14" s="5">
-        <v>76.2</v>
+        <v>77.2</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>91.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>701000</v>
+        <v>140000</v>
       </c>
       <c r="G15" s="7">
-        <v>21000</v>
+        <v>17000</v>
       </c>
       <c r="H15" s="7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>21500</v>
+        <v>14833</v>
       </c>
       <c r="J15" s="5">
-        <v>75.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>83</v>
+        <v>94.2</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>884000</v>
+        <v>263000</v>
       </c>
       <c r="G16" s="7">
-        <v>55000</v>
+        <v>23000</v>
       </c>
       <c r="H16" s="7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>35929</v>
+        <v>20750</v>
       </c>
       <c r="J16" s="5">
-        <v>74.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>239000</v>
+        <v>656000</v>
       </c>
       <c r="G17" s="7">
-        <v>21000</v>
+        <v>-1000</v>
       </c>
       <c r="H17" s="7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I17" s="7">
-        <v>14125</v>
+        <v>32000</v>
       </c>
       <c r="J17" s="5">
-        <v>74.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>90.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>353000</v>
+        <v>277000</v>
       </c>
       <c r="G18" s="7">
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="H18" s="7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I18" s="7">
-        <v>17385</v>
+        <v>13733</v>
       </c>
       <c r="J18" s="5">
-        <v>74.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>95.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>189000</v>
+        <v>943000</v>
       </c>
       <c r="G19" s="7">
-        <v>19000</v>
+        <v>59000</v>
       </c>
       <c r="H19" s="7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I19" s="7">
-        <v>14400</v>
+        <v>37467</v>
       </c>
       <c r="J19" s="5">
-        <v>73.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>82.7</v>
+        <v>96.8</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>652000</v>
+        <v>335000</v>
       </c>
       <c r="G20" s="7">
-        <v>28000</v>
+        <v>46000</v>
       </c>
       <c r="H20" s="7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I20" s="7">
-        <v>33357</v>
+        <v>57000</v>
       </c>
       <c r="J20" s="5">
-        <v>73.8</v>
+        <v>76.5</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>260000</v>
+        <v>331000</v>
       </c>
       <c r="G21" s="7">
-        <v>34000</v>
+        <v>29000</v>
       </c>
       <c r="H21" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I21" s="7">
-        <v>21500</v>
+        <v>13786</v>
       </c>
       <c r="J21" s="5">
-        <v>73.8</v>
+        <v>76.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>104000</v>
+        <v>288000</v>
       </c>
       <c r="G22" s="7">
-        <v>11000</v>
+        <v>28000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I22" s="7">
-        <v>7333</v>
+        <v>22800</v>
       </c>
       <c r="J22" s="5">
-        <v>73.8</v>
+        <v>75.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>94.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>123000</v>
+        <v>316000</v>
       </c>
       <c r="G23" s="7">
-        <v>21000</v>
+        <v>16000</v>
       </c>
       <c r="H23" s="7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I23" s="7">
-        <v>14400</v>
+        <v>13933</v>
       </c>
       <c r="J23" s="5">
-        <v>73.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>92.7</v>
+        <v>96.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>199000</v>
+        <v>112000</v>
       </c>
       <c r="G24" s="7">
         <v>13000</v>
       </c>
       <c r="H24" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" s="7">
-        <v>9929</v>
+        <v>4133</v>
       </c>
       <c r="J24" s="5">
-        <v>73.5</v>
+        <v>74.2</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>92.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>126000</v>
+        <v>706000</v>
       </c>
       <c r="G25" s="7">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H25" s="7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I25" s="7">
-        <v>10875</v>
+        <v>20400</v>
       </c>
       <c r="J25" s="5">
-        <v>73.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>88.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>232000</v>
+        <v>365000</v>
       </c>
       <c r="G26" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H26" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I26" s="7">
-        <v>18100</v>
+        <v>17000</v>
       </c>
       <c r="J26" s="5">
-        <v>73.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>89.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>211000</v>
+        <v>101000</v>
       </c>
       <c r="G27" s="7">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="H27" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I27" s="7">
-        <v>13714</v>
+        <v>6500</v>
       </c>
       <c r="J27" s="5">
-        <v>72.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>80.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>915000</v>
+        <v>230000</v>
       </c>
       <c r="G28" s="7">
-        <v>7000</v>
+        <v>26000</v>
       </c>
       <c r="H28" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I28" s="7">
-        <v>32286</v>
+        <v>18250</v>
       </c>
       <c r="J28" s="5">
-        <v>72.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>89.7</v>
+        <v>92.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>192000</v>
+        <v>119000</v>
       </c>
       <c r="G29" s="7">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="H29" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>11625</v>
+        <v>9571</v>
       </c>
       <c r="J29" s="5">
-        <v>72.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89.7</v>
+        <v>92</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>177000</v>
+        <v>135000</v>
       </c>
       <c r="G30" s="7">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="H30" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I30" s="7">
-        <v>11643</v>
+        <v>10667</v>
       </c>
       <c r="J30" s="5">
-        <v>72.2</v>
+        <v>73.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>91.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>123000</v>
+        <v>107000</v>
       </c>
       <c r="G31" s="7">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="H31" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I31" s="7">
-        <v>6818</v>
+        <v>4000</v>
       </c>
       <c r="J31" s="5">
-        <v>72.2</v>
+        <v>73.2</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>89.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>233000</v>
+        <v>1693000</v>
       </c>
       <c r="G32" s="7">
-        <v>9000</v>
+        <v>288000</v>
       </c>
       <c r="H32" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I32" s="7">
-        <v>12000</v>
+        <v>6067</v>
       </c>
       <c r="J32" s="5">
-        <v>72.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>93.8</v>
+        <v>81.7</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>180000</v>
+        <v>669000</v>
       </c>
       <c r="G33" s="7">
-        <v>47000</v>
+        <v>17000</v>
       </c>
       <c r="H33" s="7">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I33" s="7">
-        <v>21250</v>
+        <v>32267</v>
       </c>
       <c r="J33" s="5">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>90.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>132000</v>
+        <v>211000</v>
       </c>
       <c r="G34" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H34" s="7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I34" s="7">
-        <v>8875</v>
+        <v>10067</v>
       </c>
       <c r="J34" s="5">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>82.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>373000</v>
+        <v>134000</v>
       </c>
       <c r="G35" s="7">
-        <v>17000</v>
+        <v>11000</v>
       </c>
       <c r="H35" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I35" s="7">
-        <v>24250</v>
+        <v>7167</v>
       </c>
       <c r="J35" s="5">
-        <v>71.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>300000</v>
+        <v>113000</v>
       </c>
       <c r="G36" s="7">
-        <v>-2000</v>
+        <v>9000</v>
       </c>
       <c r="H36" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>13786</v>
+        <v>7571</v>
       </c>
       <c r="J36" s="5">
-        <v>71.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>86.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>224000</v>
+        <v>922000</v>
       </c>
       <c r="G37" s="7">
-        <v>-1000</v>
+        <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I37" s="7">
-        <v>14385</v>
+        <v>30600</v>
       </c>
       <c r="J37" s="5">
-        <v>71.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>89.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>131000</v>
+        <v>320000</v>
       </c>
       <c r="G38" s="7">
-        <v>5000</v>
+        <v>22000</v>
       </c>
       <c r="H38" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>7333</v>
+        <v>16400</v>
       </c>
       <c r="J38" s="5">
-        <v>71.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>87</v>
+        <v>88.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>743000</v>
+        <v>223000</v>
       </c>
       <c r="G39" s="7">
-        <v>-18000</v>
+        <v>12000</v>
       </c>
       <c r="H39" s="7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I39" s="7">
-        <v>12571</v>
+        <v>13500</v>
       </c>
       <c r="J39" s="5">
-        <v>71</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>89</v>
+        <v>92.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>226000</v>
+        <v>186000</v>
       </c>
       <c r="G40" s="7">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="H40" s="7">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>7857</v>
+        <v>36333</v>
       </c>
       <c r="J40" s="5">
-        <v>70.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>86.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>302000</v>
+        <v>182000</v>
       </c>
       <c r="G41" s="7">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H41" s="7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I41" s="7">
-        <v>12615</v>
+        <v>11200</v>
       </c>
       <c r="J41" s="5">
-        <v>70.8</v>
+        <v>71.8</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>87.2</v>
+        <v>91.8</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>110000</v>
+        <v>104000</v>
       </c>
       <c r="G42" s="7">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I42" s="7">
-        <v>9667</v>
+        <v>5333</v>
       </c>
       <c r="J42" s="5">
-        <v>70.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>93.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>156000</v>
+        <v>225000</v>
       </c>
       <c r="G43" s="7">
-        <v>31000</v>
+        <v>45000</v>
       </c>
       <c r="H43" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I43" s="7">
-        <v>39500</v>
+        <v>26000</v>
       </c>
       <c r="J43" s="5">
-        <v>70.3</v>
+        <v>71.7</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>80.8</v>
+        <v>88.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>496000</v>
+        <v>240000</v>
       </c>
       <c r="G44" s="7">
-        <v>15000</v>
+        <v>7000</v>
       </c>
       <c r="H44" s="7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I44" s="7">
-        <v>23143</v>
+        <v>11375</v>
       </c>
       <c r="J44" s="5">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>89.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>167000</v>
+        <v>233000</v>
       </c>
       <c r="G45" s="7">
-        <v>18000</v>
+        <v>1000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I45" s="7">
-        <v>11000</v>
+        <v>16545</v>
       </c>
       <c r="J45" s="5">
-        <v>70.2</v>
+        <v>71.2</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>305000</v>
+        <v>175000</v>
       </c>
       <c r="G46" s="7">
-        <v>-6000</v>
+        <v>10000</v>
       </c>
       <c r="H46" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I46" s="7">
-        <v>11857</v>
+        <v>5467</v>
       </c>
       <c r="J46" s="5">
-        <v>70</v>
+        <v>71.2</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>87.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>133000</v>
+        <v>224000</v>
       </c>
       <c r="G47" s="7">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H47" s="7">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I47" s="7">
-        <v>6000</v>
+        <v>13357</v>
       </c>
       <c r="J47" s="5">
-        <v>69.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>80.2</v>
+        <v>85</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>533000</v>
+        <v>469000</v>
       </c>
       <c r="G48" s="7">
-        <v>8000</v>
+        <v>52000</v>
       </c>
       <c r="H48" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I48" s="7">
-        <v>21071</v>
+        <v>16333</v>
       </c>
       <c r="J48" s="5">
-        <v>69.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>92</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>298000</v>
+        <v>228000</v>
       </c>
       <c r="G49" s="7">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="H49" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I49" s="7">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="J49" s="5">
-        <v>69.3</v>
+        <v>70.7</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>77.2</v>
+        <v>87.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>543000</v>
+        <v>177000</v>
       </c>
       <c r="G50" s="7">
-        <v>-8000</v>
+        <v>10000</v>
       </c>
       <c r="H50" s="7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I50" s="7">
-        <v>27143</v>
+        <v>10833</v>
       </c>
       <c r="J50" s="5">
-        <v>69.2</v>
+        <v>70.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>253000</v>
+        <v>234000</v>
       </c>
       <c r="G51" s="7">
-        <v>-9000</v>
+        <v>24000</v>
       </c>
       <c r="H51" s="7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I51" s="7">
-        <v>13000</v>
+        <v>13500</v>
       </c>
       <c r="J51" s="5">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>87.2</v>
+        <v>91.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>165000</v>
+        <v>125000</v>
       </c>
       <c r="G52" s="7">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="H52" s="7">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I52" s="7">
-        <v>5143</v>
+        <v>9600</v>
       </c>
       <c r="J52" s="5">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>86.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>533000</v>
+        <v>102000</v>
       </c>
       <c r="G53" s="7">
-        <v>-10000</v>
+        <v>7000</v>
       </c>
       <c r="H53" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I53" s="7">
-        <v>5500</v>
+        <v>6333</v>
       </c>
       <c r="J53" s="5">
-        <v>69.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>83.5</v>
+        <v>91.5</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>210000</v>
+        <v>103000</v>
       </c>
       <c r="G54" s="7">
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="H54" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I54" s="7">
-        <v>12545</v>
+        <v>600</v>
       </c>
       <c r="J54" s="5">
-        <v>69.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-08T04:21:56+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-09T04:50:29+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>刚证道混沌天帝，让我身化禁区？</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>诸神愚戏</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
     <t>规则怪谈：无所谓，系统会出手</t>
   </si>
   <si>
-    <t>刚证道混沌天帝，让我身化禁区？</t>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>女多男少，开局被瓦学妹喊爸爸</t>
   </si>
   <si>
     <t>全球死考：刚下刑场你让我去考试</t>
   </si>
   <si>
+    <t>每天属性翻一倍，我黑化爆杀一切</t>
+  </si>
+  <si>
     <t>说好造桥游戏，打穿天山什么鬼？</t>
   </si>
   <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>奥特：最强债主！借债十倍返还！</t>
+  </si>
+  <si>
+    <t>努力就变强的我，被重生者曝光了</t>
+  </si>
+  <si>
+    <t>时停起手，邪神也得给我跪下！</t>
+  </si>
+  <si>
     <t>天仙怀了我的娃，千年世家被曝光</t>
   </si>
   <si>
-    <t>每天属性翻一倍，我黑化爆杀一切</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>家父造反成功，我被迫成为皇太子</t>
   </si>
   <si>
     <t>我成假少爷后，八个妹妹不再隐忍</t>
   </si>
   <si>
+    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
+  </si>
+  <si>
+    <t>捡来的妹妹修仙后，回来抢亲了</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>开局大限将至，我携帝兵问道禁区</t>
+  </si>
+  <si>
+    <t>师尊嫌我肮脏？反手退师帖送上</t>
+  </si>
+  <si>
+    <t>四合院：从李云龙战友开始</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>瘟疫模拟：开局投放Necroa</t>
+  </si>
+  <si>
     <t>我在诡异副本女装直播后爆火了</t>
   </si>
   <si>
-    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
-  </si>
-  <si>
-    <t>公安局长之扫黑风暴</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>努力就变强的我，被重生者曝光了</t>
+    <t>我根骨平庸，但分身都是绝世天才</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>重生之我成了太子麾下头号党魁</t>
+  </si>
+  <si>
+    <t>我都帝皇铠甲了，妹妹国运召唤？</t>
+  </si>
+  <si>
+    <t>四合院：我家住隔壁，看众禽互咬</t>
+  </si>
+  <si>
+    <t>名义：从接替老刘开始</t>
+  </si>
+  <si>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>杀人犯？哼！在学校内我才是校霸</t>
+  </si>
+  <si>
+    <t>都末世了，你们还想当版本T0？</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
   </si>
   <si>
     <t>国运班级求生：机电2班闹翻荒野</t>
   </si>
   <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>南部档案：我真不想当张家主事人</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>师尊嫌我肮脏？反手退师帖送上</t>
-  </si>
-  <si>
-    <t>乡村神医，赵大牛的妖孽人生</t>
-  </si>
-  <si>
-    <t>开局大限将至，我携帝兵问道禁区</t>
-  </si>
-  <si>
-    <t>北平37：从抽到警局到拥兵百万</t>
-  </si>
-  <si>
-    <t>时停起手，邪神也得给我跪下！</t>
-  </si>
-  <si>
     <t>年代1960：穿越南锣鼓巷，</t>
   </si>
   <si>
-    <t>我提前三天被丢进了末世</t>
-  </si>
-  <si>
-    <t>捡来的妹妹修仙后，回来抢亲了</t>
+    <t>抗战：从湘江开始一路横推</t>
   </si>
   <si>
     <t>三角洲：资源无限供应，提现成壕</t>
   </si>
   <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>离婚后，我成了刀枪炮！</t>
-  </si>
-  <si>
-    <t>奥特：最强债主！借债十倍返还！</t>
-  </si>
-  <si>
-    <t>家父造反成功，我被迫成为皇太子</t>
+    <t>封神守关，万界大阵成叹息之墙</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
   </si>
   <si>
     <t>开局四选一，我选成为沪圈少爷！</t>
   </si>
   <si>
-    <t>开局三千重甲步兵，我大明怎么输</t>
-  </si>
-  <si>
-    <t>女多男少，开局被瓦学妹喊爸爸</t>
-  </si>
-  <si>
-    <t>四合院：我家住隔壁，看众禽互咬</t>
-  </si>
-  <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>在病娇的摧残下，我选择跑路了</t>
-  </si>
-  <si>
-    <t>洲：质检打手，你五分钟诛仙清图</t>
-  </si>
-  <si>
-    <t>规则怪谈：我即怪谈</t>
+    <t>西幻：从鹰人部落到天使帝国</t>
   </si>
   <si>
     <t>农村女婿</t>
   </si>
   <si>
-    <t>封神守关，万界大阵成叹息之墙</t>
-  </si>
-  <si>
-    <t>战龙令</t>
-  </si>
-  <si>
-    <t>修仙界搞回收，破产仙子请自重</t>
-  </si>
-  <si>
-    <t>魂穿民国成为教导总队中校参谋</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
+    <t>这个猫娘？怎么是尼古喵喵啊！！</t>
+  </si>
+  <si>
+    <t>灾厄，四臂两面？这不宿傩嘛！</t>
+  </si>
+  <si>
+    <t>名义，汉东第一拳王，汉东王来了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>82</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>2776000</v>
+        <v>953000</v>
       </c>
       <c r="G5" s="7">
-        <v>-7000</v>
+        <v>54000</v>
       </c>
       <c r="H5" s="7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I5" s="7">
-        <v>99000</v>
+        <v>64182</v>
       </c>
       <c r="J5" s="5">
-        <v>89.8</v>
+        <v>88.8</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>84.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1809000</v>
+        <v>2768000</v>
       </c>
       <c r="G6" s="7">
-        <v>90000</v>
+        <v>-8000</v>
       </c>
       <c r="H6" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="7">
-        <v>88000</v>
+        <v>92312</v>
       </c>
       <c r="J6" s="5">
-        <v>88.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>95</v>
+        <v>83.8</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>899000</v>
+        <v>1883000</v>
       </c>
       <c r="G7" s="7">
-        <v>45000</v>
+        <v>74000</v>
       </c>
       <c r="H7" s="7">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I7" s="7">
-        <v>65200</v>
+        <v>87125</v>
       </c>
       <c r="J7" s="5">
-        <v>88.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>78.2</v>
+        <v>95</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>2003000</v>
+        <v>1000000</v>
       </c>
       <c r="G8" s="7">
-        <v>-50000</v>
+        <v>143000</v>
       </c>
       <c r="H8" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="7">
-        <v>81200</v>
+        <v>52062</v>
       </c>
       <c r="J8" s="5">
-        <v>83.3</v>
+        <v>85.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>96.59999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>447000</v>
+        <v>263000</v>
       </c>
       <c r="G9" s="7">
-        <v>65000</v>
+        <v>38000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>43600</v>
+        <v>28000</v>
       </c>
       <c r="J9" s="5">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>97.2</v>
+        <v>78</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>279000</v>
+        <v>1951000</v>
       </c>
       <c r="G10" s="7">
-        <v>41000</v>
+        <v>-52000</v>
       </c>
       <c r="H10" s="7">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I10" s="7">
-        <v>23000</v>
+        <v>72875</v>
       </c>
       <c r="J10" s="5">
-        <v>79.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>98.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>273000</v>
+        <v>353000</v>
       </c>
       <c r="G11" s="7">
-        <v>34000</v>
+        <v>80000</v>
       </c>
       <c r="H11" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="7">
-        <v>16333</v>
+        <v>22700</v>
       </c>
       <c r="J11" s="5">
-        <v>78.5</v>
+        <v>80.3</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>100</v>
+        <v>90.8</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>343000</v>
+        <v>469000</v>
       </c>
       <c r="G12" s="7">
-        <v>55000</v>
+        <v>22000</v>
       </c>
       <c r="H12" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>13667</v>
+        <v>40000</v>
       </c>
       <c r="J12" s="5">
-        <v>78.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>84.7</v>
+        <v>100</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>857000</v>
+        <v>387000</v>
       </c>
       <c r="G13" s="7">
-        <v>142000</v>
+        <v>44000</v>
       </c>
       <c r="H13" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" s="7">
-        <v>46000</v>
+        <v>15562</v>
       </c>
       <c r="J13" s="5">
-        <v>78.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>96.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>213000</v>
+        <v>277000</v>
       </c>
       <c r="G14" s="7">
-        <v>24000</v>
+        <v>54000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I14" s="7">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="J14" s="5">
-        <v>77.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>97.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>140000</v>
+        <v>387000</v>
       </c>
       <c r="G15" s="7">
-        <v>17000</v>
+        <v>52000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7">
-        <v>14833</v>
+        <v>55333</v>
       </c>
       <c r="J15" s="5">
-        <v>77.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>94.2</v>
+        <v>94</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>263000</v>
+        <v>2013000</v>
       </c>
       <c r="G16" s="7">
-        <v>23000</v>
+        <v>320000</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I16" s="7">
-        <v>20750</v>
+        <v>25688</v>
       </c>
       <c r="J16" s="5">
-        <v>77</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>88.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>656000</v>
+        <v>305000</v>
       </c>
       <c r="G17" s="7">
-        <v>-1000</v>
+        <v>26000</v>
       </c>
       <c r="H17" s="7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I17" s="7">
-        <v>32000</v>
+        <v>23333</v>
       </c>
       <c r="J17" s="5">
-        <v>76.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>96.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>277000</v>
+        <v>312000</v>
       </c>
       <c r="G18" s="7">
         <v>24000</v>
       </c>
       <c r="H18" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I18" s="7">
-        <v>13733</v>
+        <v>23000</v>
       </c>
       <c r="J18" s="5">
-        <v>76.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>85.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>943000</v>
+        <v>207000</v>
       </c>
       <c r="G19" s="7">
-        <v>59000</v>
+        <v>21000</v>
       </c>
       <c r="H19" s="7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>37467</v>
+        <v>32500</v>
       </c>
       <c r="J19" s="5">
-        <v>76.5</v>
+        <v>77</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>96.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>335000</v>
+        <v>239000</v>
       </c>
       <c r="G20" s="7">
-        <v>46000</v>
+        <v>26000</v>
       </c>
       <c r="H20" s="7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I20" s="7">
-        <v>57000</v>
+        <v>17429</v>
       </c>
       <c r="J20" s="5">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>96.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>331000</v>
+        <v>285000</v>
       </c>
       <c r="G21" s="7">
-        <v>29000</v>
+        <v>22000</v>
       </c>
       <c r="H21" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I21" s="7">
-        <v>13786</v>
+        <v>20889</v>
       </c>
       <c r="J21" s="5">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>94.7</v>
+        <v>98.5</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>288000</v>
+        <v>156000</v>
       </c>
       <c r="G22" s="7">
-        <v>28000</v>
+        <v>22000</v>
       </c>
       <c r="H22" s="7">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I22" s="7">
-        <v>22800</v>
+        <v>8308</v>
       </c>
       <c r="J22" s="5">
-        <v>75.8</v>
+        <v>76.3</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>92.8</v>
+        <v>84.5</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>316000</v>
+        <v>1001000</v>
       </c>
       <c r="G23" s="7">
-        <v>16000</v>
+        <v>58000</v>
       </c>
       <c r="H23" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="7">
-        <v>13933</v>
+        <v>38750</v>
       </c>
       <c r="J23" s="5">
-        <v>74.5</v>
+        <v>76.2</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>96.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>112000</v>
+        <v>653000</v>
       </c>
       <c r="G24" s="7">
-        <v>13000</v>
+        <v>-3000</v>
       </c>
       <c r="H24" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" s="7">
-        <v>4133</v>
+        <v>29812</v>
       </c>
       <c r="J24" s="5">
-        <v>74.2</v>
+        <v>76.2</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>706000</v>
+        <v>296000</v>
       </c>
       <c r="G25" s="7">
-        <v>5000</v>
+        <v>19000</v>
       </c>
       <c r="H25" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" s="7">
-        <v>20400</v>
+        <v>14062</v>
       </c>
       <c r="J25" s="5">
-        <v>74.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>90.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>365000</v>
+        <v>148000</v>
       </c>
       <c r="G26" s="7">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="H26" s="7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I26" s="7">
-        <v>17000</v>
+        <v>10900</v>
       </c>
       <c r="J26" s="5">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>95</v>
+        <v>94.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>101000</v>
+        <v>251000</v>
       </c>
       <c r="G27" s="7">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="H27" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>6500</v>
+        <v>18800</v>
       </c>
       <c r="J27" s="5">
-        <v>73.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>230000</v>
+        <v>197000</v>
       </c>
       <c r="G28" s="7">
-        <v>26000</v>
+        <v>24000</v>
       </c>
       <c r="H28" s="7">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I28" s="7">
-        <v>18250</v>
+        <v>3750</v>
       </c>
       <c r="J28" s="5">
-        <v>73.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>92.7</v>
+        <v>91.5</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>119000</v>
+        <v>381000</v>
       </c>
       <c r="G29" s="7">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I29" s="7">
-        <v>9571</v>
+        <v>16933</v>
       </c>
       <c r="J29" s="5">
-        <v>73.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>92</v>
+        <v>95.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>135000</v>
+        <v>163000</v>
       </c>
       <c r="G30" s="7">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="H30" s="7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I30" s="7">
-        <v>10667</v>
+        <v>7867</v>
       </c>
       <c r="J30" s="5">
-        <v>73.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>107000</v>
+        <v>151000</v>
       </c>
       <c r="G31" s="7">
         <v>11000</v>
       </c>
       <c r="H31" s="7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>4000</v>
+        <v>14286</v>
       </c>
       <c r="J31" s="5">
-        <v>73.2</v>
+        <v>74.2</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>93.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>1693000</v>
+        <v>215000</v>
       </c>
       <c r="G32" s="7">
-        <v>288000</v>
+        <v>18000</v>
       </c>
       <c r="H32" s="7">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I32" s="7">
-        <v>6067</v>
+        <v>11600</v>
       </c>
       <c r="J32" s="5">
-        <v>73</v>
+        <v>73.8</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>81.7</v>
+        <v>88.3</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>669000</v>
+        <v>705000</v>
       </c>
       <c r="G33" s="7">
-        <v>17000</v>
+        <v>-1000</v>
       </c>
       <c r="H33" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" s="7">
-        <v>32267</v>
+        <v>19062</v>
       </c>
       <c r="J33" s="5">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>91.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>211000</v>
+        <v>108000</v>
       </c>
       <c r="G34" s="7">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="H34" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I34" s="7">
-        <v>10067</v>
+        <v>8167</v>
       </c>
       <c r="J34" s="5">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1756,19 +1756,19 @@
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>134000</v>
+        <v>308000</v>
       </c>
       <c r="G35" s="7">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="H35" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>7167</v>
+        <v>16000</v>
       </c>
       <c r="J35" s="5">
-        <v>72.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>91.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>113000</v>
+        <v>252000</v>
       </c>
       <c r="G36" s="7">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I36" s="7">
-        <v>7571</v>
+        <v>11444</v>
       </c>
       <c r="J36" s="5">
-        <v>72.2</v>
+        <v>72.5</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>80.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>922000</v>
+        <v>171000</v>
       </c>
       <c r="G37" s="7">
-        <v>7000</v>
+        <v>19000</v>
       </c>
       <c r="H37" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I37" s="7">
-        <v>30600</v>
+        <v>0</v>
       </c>
       <c r="J37" s="5">
-        <v>72</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>90.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>320000</v>
+        <v>221000</v>
       </c>
       <c r="G38" s="7">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I38" s="7">
-        <v>16400</v>
+        <v>10062</v>
       </c>
       <c r="J38" s="5">
-        <v>72</v>
+        <v>72.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>88.3</v>
+        <v>88.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>223000</v>
+        <v>320000</v>
       </c>
       <c r="G39" s="7">
-        <v>12000</v>
+        <v>4000</v>
       </c>
       <c r="H39" s="7">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I39" s="7">
-        <v>13500</v>
+        <v>13312</v>
       </c>
       <c r="J39" s="5">
-        <v>71.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>92.2</v>
+        <v>89.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>186000</v>
+        <v>194000</v>
       </c>
       <c r="G40" s="7">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="H40" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>36333</v>
+        <v>20400</v>
       </c>
       <c r="J40" s="5">
-        <v>71.8</v>
+        <v>72.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>89.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>182000</v>
+        <v>237000</v>
       </c>
       <c r="G41" s="7">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H41" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" s="7">
-        <v>11200</v>
+        <v>7562</v>
       </c>
       <c r="J41" s="5">
-        <v>71.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>91.8</v>
+        <v>80.7</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>104000</v>
+        <v>930000</v>
       </c>
       <c r="G42" s="7">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="H42" s="7">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I42" s="7">
-        <v>5333</v>
+        <v>29188</v>
       </c>
       <c r="J42" s="5">
-        <v>71.8</v>
+        <v>71.7</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>225000</v>
+        <v>335000</v>
       </c>
       <c r="G43" s="7">
-        <v>45000</v>
+        <v>4000</v>
       </c>
       <c r="H43" s="7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I43" s="7">
-        <v>26000</v>
+        <v>13133</v>
       </c>
       <c r="J43" s="5">
         <v>71.7</v>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>88.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>240000</v>
+        <v>674000</v>
       </c>
       <c r="G44" s="7">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="H44" s="7">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I44" s="7">
-        <v>11375</v>
+        <v>30562</v>
       </c>
       <c r="J44" s="5">
-        <v>71.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>85.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>233000</v>
+        <v>139000</v>
       </c>
       <c r="G45" s="7">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="H45" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I45" s="7">
-        <v>16545</v>
+        <v>7800</v>
       </c>
       <c r="J45" s="5">
-        <v>71.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>90.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>175000</v>
+        <v>121000</v>
       </c>
       <c r="G46" s="7">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="H46" s="7">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I46" s="7">
-        <v>5467</v>
+        <v>7625</v>
       </c>
       <c r="J46" s="5">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>86.8</v>
+        <v>88.2</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>224000</v>
+        <v>189000</v>
       </c>
       <c r="G47" s="7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H47" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I47" s="7">
-        <v>13357</v>
+        <v>11000</v>
       </c>
       <c r="J47" s="5">
-        <v>71.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>469000</v>
+        <v>235000</v>
       </c>
       <c r="G48" s="7">
-        <v>52000</v>
+        <v>2000</v>
       </c>
       <c r="H48" s="7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I48" s="7">
-        <v>16333</v>
+        <v>15333</v>
       </c>
       <c r="J48" s="5">
-        <v>70.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>88.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>228000</v>
+        <v>185000</v>
       </c>
       <c r="G49" s="7">
-        <v>27000</v>
+        <v>3000</v>
       </c>
       <c r="H49" s="7">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I49" s="7">
-        <v>8000</v>
+        <v>10688</v>
       </c>
       <c r="J49" s="5">
-        <v>70.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>87.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>177000</v>
+        <v>254000</v>
       </c>
       <c r="G50" s="7">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="H50" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I50" s="7">
-        <v>10833</v>
+        <v>17556</v>
       </c>
       <c r="J50" s="5">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.8</v>
+        <v>86.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>234000</v>
+        <v>254000</v>
       </c>
       <c r="G51" s="7">
-        <v>24000</v>
+        <v>26000</v>
       </c>
       <c r="H51" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I51" s="7">
-        <v>13500</v>
+        <v>9800</v>
       </c>
       <c r="J51" s="5">
-        <v>70.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>91.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>125000</v>
+        <v>238000</v>
       </c>
       <c r="G52" s="7">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H52" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I52" s="7">
-        <v>9600</v>
+        <v>8600</v>
       </c>
       <c r="J52" s="5">
-        <v>70.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>89.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>102000</v>
+        <v>189000</v>
       </c>
       <c r="G53" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H53" s="7">
         <v>10</v>
       </c>
       <c r="I53" s="7">
-        <v>6333</v>
+        <v>8667</v>
       </c>
       <c r="J53" s="5">
-        <v>70.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>91.5</v>
+        <v>86.5</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>103000</v>
+        <v>202000</v>
       </c>
       <c r="G54" s="7">
-        <v>7000</v>
+        <v>14000</v>
       </c>
       <c r="H54" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I54" s="7">
-        <v>600</v>
+        <v>9833</v>
       </c>
       <c r="J54" s="5">
-        <v>70.5</v>
+        <v>70</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-09T04:50:29+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-10T05:14:27+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,52 +70,73 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>诸神愚戏</t>
+  </si>
+  <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
     <t>刚证道混沌天帝，让我身化禁区？</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>诸神愚戏</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
+    <t>全球死考：刚下刑场你让我去考试</t>
+  </si>
+  <si>
+    <t>奥特：最强债主！借债十倍返还！</t>
+  </si>
+  <si>
+    <t>时停起手，邪神也得给我跪下！</t>
+  </si>
+  <si>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>天仙怀了我的娃，千年世家被曝光</t>
   </si>
   <si>
     <t>女多男少，开局被瓦学妹喊爸爸</t>
   </si>
   <si>
-    <t>全球死考：刚下刑场你让我去考试</t>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>家父造反成功，我被迫成为皇太子</t>
+  </si>
+  <si>
+    <t>公安局长之扫黑风暴</t>
   </si>
   <si>
     <t>每天属性翻一倍，我黑化爆杀一切</t>
   </si>
   <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
-  </si>
-  <si>
-    <t>奥特：最强债主！借债十倍返还！</t>
-  </si>
-  <si>
     <t>努力就变强的我，被重生者曝光了</t>
   </si>
   <si>
-    <t>时停起手，邪神也得给我跪下！</t>
-  </si>
-  <si>
-    <t>天仙怀了我的娃，千年世家被曝光</t>
-  </si>
-  <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
-  </si>
-  <si>
-    <t>家父造反成功，我被迫成为皇太子</t>
+    <t>捡来的妹妹修仙后，回来抢亲了</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>师尊嫌我肮脏？反手退师帖送上</t>
+  </si>
+  <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>修仙界搞回收，破产仙子请自重</t>
   </si>
   <si>
     <t>我成假少爷后，八个妹妹不再隐忍</t>
@@ -124,28 +145,37 @@
     <t>玄幻：我堕魔后把绝美师尊抓回来</t>
   </si>
   <si>
-    <t>捡来的妹妹修仙后，回来抢亲了</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>公安局长之扫黑风暴</t>
+    <t>开局大限将至，我携帝兵问道禁区</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
   </si>
   <si>
     <t>我只想砍死各位，或者被各位砍死</t>
   </si>
   <si>
-    <t>开局大限将至，我携帝兵问道禁区</t>
-  </si>
-  <si>
-    <t>师尊嫌我肮脏？反手退师帖送上</t>
+    <t>大唐：开局魔丸闺女炮轰长安城</t>
+  </si>
+  <si>
+    <t>名义：从接替老刘开始</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
   </si>
   <si>
     <t>四合院：从李云龙战友开始</t>
   </si>
   <si>
-    <t>名义：开局我举报我自己</t>
+    <t>开局流落皇子，可我已经人间无敌</t>
+  </si>
+  <si>
+    <t>杀人犯？哼！在学校内我才是校霸</t>
+  </si>
+  <si>
+    <t>抗战：从湘江开始一路横推</t>
+  </si>
+  <si>
+    <t>离婚后，我成了刀枪炮！</t>
   </si>
   <si>
     <t>瘟疫模拟：开局投放Necroa</t>
@@ -154,73 +184,43 @@
     <t>我在诡异副本女装直播后爆火了</t>
   </si>
   <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>魂穿民国成为教导总队中校参谋</t>
+  </si>
+  <si>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>从变身少女开始斩妖除魔</t>
+  </si>
+  <si>
+    <t>我都帝皇铠甲了，妹妹国运召唤？</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
+  </si>
+  <si>
+    <t>入学第一天，千金学姐成了我老婆</t>
+  </si>
+  <si>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
+  </si>
+  <si>
     <t>我根骨平庸，但分身都是绝世天才</t>
   </si>
   <si>
-    <t>实习教出金牌班，家长要换班主任</t>
+    <t>穿梭八零，工业克苏鲁吓傻老外</t>
   </si>
   <si>
     <t>重生之我成了太子麾下头号党魁</t>
   </si>
   <si>
-    <t>我都帝皇铠甲了，妹妹国运召唤？</t>
-  </si>
-  <si>
-    <t>四合院：我家住隔壁，看众禽互咬</t>
-  </si>
-  <si>
-    <t>名义：从接替老刘开始</t>
-  </si>
-  <si>
-    <t>我提前三天被丢进了末世</t>
-  </si>
-  <si>
     <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>杀人犯？哼！在学校内我才是校霸</t>
-  </si>
-  <si>
-    <t>都末世了，你们还想当版本T0？</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>国运班级求生：机电2班闹翻荒野</t>
-  </si>
-  <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>抗战：从湘江开始一路横推</t>
-  </si>
-  <si>
-    <t>三角洲：资源无限供应，提现成壕</t>
-  </si>
-  <si>
-    <t>封神守关，万界大阵成叹息之墙</t>
-  </si>
-  <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>开局四选一，我选成为沪圈少爷！</t>
-  </si>
-  <si>
-    <t>西幻：从鹰人部落到天使帝国</t>
-  </si>
-  <si>
-    <t>农村女婿</t>
-  </si>
-  <si>
-    <t>这个猫娘？怎么是尼古喵喵啊！！</t>
-  </si>
-  <si>
-    <t>灾厄，四臂两面？这不宿傩嘛！</t>
-  </si>
-  <si>
-    <t>名义，汉东第一拳王，汉东王来了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>95.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>953000</v>
+        <v>1952000</v>
       </c>
       <c r="G5" s="7">
-        <v>54000</v>
+        <v>69000</v>
       </c>
       <c r="H5" s="7">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I5" s="7">
-        <v>64182</v>
+        <v>86059</v>
       </c>
       <c r="J5" s="5">
-        <v>88.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>81.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>2768000</v>
+        <v>1138000</v>
       </c>
       <c r="G6" s="7">
-        <v>-8000</v>
+        <v>138000</v>
       </c>
       <c r="H6" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="7">
-        <v>92312</v>
+        <v>57118</v>
       </c>
       <c r="J6" s="5">
-        <v>88.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>83.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1883000</v>
+        <v>2737000</v>
       </c>
       <c r="G7" s="7">
-        <v>74000</v>
+        <v>-31000</v>
       </c>
       <c r="H7" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="7">
-        <v>87125</v>
+        <v>85059</v>
       </c>
       <c r="J7" s="5">
-        <v>87.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>95</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>1000000</v>
+        <v>517000</v>
       </c>
       <c r="G8" s="7">
-        <v>143000</v>
+        <v>48000</v>
       </c>
       <c r="H8" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
-        <v>52062</v>
+        <v>41143</v>
       </c>
       <c r="J8" s="5">
-        <v>85.3</v>
+        <v>83.7</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>263000</v>
+        <v>931000</v>
       </c>
       <c r="G9" s="7">
-        <v>38000</v>
+        <v>-22000</v>
       </c>
       <c r="H9" s="7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I9" s="7">
-        <v>28000</v>
+        <v>57000</v>
       </c>
       <c r="J9" s="5">
-        <v>81.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>78</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>1951000</v>
+        <v>1919000</v>
       </c>
       <c r="G10" s="7">
-        <v>-52000</v>
+        <v>-32000</v>
       </c>
       <c r="H10" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="7">
-        <v>72875</v>
+        <v>66706</v>
       </c>
       <c r="J10" s="5">
-        <v>81.09999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>353000</v>
+        <v>317000</v>
       </c>
       <c r="G11" s="7">
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="H11" s="7">
         <v>11</v>
       </c>
       <c r="I11" s="7">
-        <v>22700</v>
+        <v>20200</v>
       </c>
       <c r="J11" s="5">
-        <v>80.3</v>
+        <v>80</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>90.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>469000</v>
+        <v>2240000</v>
       </c>
       <c r="G12" s="7">
-        <v>22000</v>
+        <v>227000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I12" s="7">
-        <v>40000</v>
+        <v>37529</v>
       </c>
       <c r="J12" s="5">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>387000</v>
+        <v>343000</v>
       </c>
       <c r="G13" s="7">
-        <v>44000</v>
+        <v>31000</v>
       </c>
       <c r="H13" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>15562</v>
+        <v>24143</v>
       </c>
       <c r="J13" s="5">
-        <v>78.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>98.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>277000</v>
+        <v>334000</v>
       </c>
       <c r="G14" s="7">
-        <v>54000</v>
+        <v>29000</v>
       </c>
       <c r="H14" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
-        <v>18000</v>
+        <v>23900</v>
       </c>
       <c r="J14" s="5">
         <v>78.90000000000001</v>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>96.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>387000</v>
+        <v>286000</v>
       </c>
       <c r="G15" s="7">
-        <v>52000</v>
+        <v>23000</v>
       </c>
       <c r="H15" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>55333</v>
+        <v>27286</v>
       </c>
       <c r="J15" s="5">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>94</v>
+        <v>98.2</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>2013000</v>
+        <v>426000</v>
       </c>
       <c r="G16" s="7">
-        <v>320000</v>
+        <v>39000</v>
       </c>
       <c r="H16" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I16" s="7">
-        <v>25688</v>
+        <v>16941</v>
       </c>
       <c r="J16" s="5">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>95.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>305000</v>
+        <v>226000</v>
       </c>
       <c r="G17" s="7">
-        <v>26000</v>
+        <v>19000</v>
       </c>
       <c r="H17" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>23333</v>
+        <v>29800</v>
       </c>
       <c r="J17" s="5">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>94.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>312000</v>
+        <v>674000</v>
       </c>
       <c r="G18" s="7">
-        <v>24000</v>
+        <v>21000</v>
       </c>
       <c r="H18" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I18" s="7">
-        <v>23000</v>
+        <v>29294</v>
       </c>
       <c r="J18" s="5">
-        <v>77.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>97.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>207000</v>
+        <v>382000</v>
       </c>
       <c r="G19" s="7">
-        <v>21000</v>
+        <v>29000</v>
       </c>
       <c r="H19" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I19" s="7">
-        <v>32500</v>
+        <v>23273</v>
       </c>
       <c r="J19" s="5">
-        <v>77</v>
+        <v>77.3</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>94.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>239000</v>
+        <v>417000</v>
       </c>
       <c r="G20" s="7">
-        <v>26000</v>
+        <v>30000</v>
       </c>
       <c r="H20" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>17429</v>
+        <v>49000</v>
       </c>
       <c r="J20" s="5">
-        <v>76.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>93.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>285000</v>
+        <v>195000</v>
       </c>
       <c r="G21" s="7">
-        <v>22000</v>
+        <v>39000</v>
       </c>
       <c r="H21" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I21" s="7">
-        <v>20889</v>
+        <v>10500</v>
       </c>
       <c r="J21" s="5">
-        <v>76.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>98.5</v>
+        <v>85.2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>156000</v>
+        <v>1068000</v>
       </c>
       <c r="G22" s="7">
-        <v>22000</v>
+        <v>67000</v>
       </c>
       <c r="H22" s="7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I22" s="7">
-        <v>8308</v>
+        <v>40412</v>
       </c>
       <c r="J22" s="5">
-        <v>76.3</v>
+        <v>77</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>84.5</v>
+        <v>94.3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>1001000</v>
+        <v>271000</v>
       </c>
       <c r="G23" s="7">
-        <v>58000</v>
+        <v>20000</v>
       </c>
       <c r="H23" s="7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>38750</v>
+        <v>19000</v>
       </c>
       <c r="J23" s="5">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>88.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>653000</v>
+        <v>1324000</v>
       </c>
       <c r="G24" s="7">
-        <v>-3000</v>
+        <v>485000</v>
       </c>
       <c r="H24" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I24" s="7">
-        <v>29812</v>
+        <v>17059</v>
       </c>
       <c r="J24" s="5">
-        <v>76.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>296000</v>
+        <v>404000</v>
       </c>
       <c r="G25" s="7">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="H25" s="7">
         <v>17</v>
       </c>
       <c r="I25" s="7">
-        <v>14062</v>
+        <v>17312</v>
       </c>
       <c r="J25" s="5">
-        <v>75.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>94.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>148000</v>
+        <v>167000</v>
       </c>
       <c r="G26" s="7">
-        <v>13000</v>
+        <v>37000</v>
       </c>
       <c r="H26" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>10900</v>
+        <v>12857</v>
       </c>
       <c r="J26" s="5">
-        <v>74.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>94.5</v>
+        <v>93</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>251000</v>
+        <v>261000</v>
       </c>
       <c r="G27" s="7">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I27" s="7">
-        <v>18800</v>
+        <v>18000</v>
       </c>
       <c r="J27" s="5">
-        <v>74.7</v>
+        <v>75.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>97.8</v>
+        <v>90.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>197000</v>
+        <v>301000</v>
       </c>
       <c r="G28" s="7">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="H28" s="7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I28" s="7">
-        <v>3750</v>
+        <v>20400</v>
       </c>
       <c r="J28" s="5">
-        <v>74.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>91.5</v>
+        <v>94.8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>381000</v>
+        <v>161000</v>
       </c>
       <c r="G29" s="7">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="H29" s="7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I29" s="7">
-        <v>16933</v>
+        <v>11091</v>
       </c>
       <c r="J29" s="5">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>95.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>163000</v>
+        <v>120000</v>
       </c>
       <c r="G30" s="7">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="H30" s="7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I30" s="7">
-        <v>7867</v>
+        <v>7000</v>
       </c>
       <c r="J30" s="5">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>92.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>151000</v>
+        <v>311000</v>
       </c>
       <c r="G31" s="7">
-        <v>11000</v>
+        <v>15000</v>
       </c>
       <c r="H31" s="7">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I31" s="7">
-        <v>14286</v>
+        <v>14118</v>
       </c>
       <c r="J31" s="5">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>92.5</v>
+        <v>94.3</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>215000</v>
+        <v>170000</v>
       </c>
       <c r="G32" s="7">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="H32" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I32" s="7">
-        <v>11600</v>
+        <v>9167</v>
       </c>
       <c r="J32" s="5">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>88.3</v>
+        <v>97.7</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>705000</v>
+        <v>196000</v>
       </c>
       <c r="G33" s="7">
-        <v>-1000</v>
+        <v>25000</v>
       </c>
       <c r="H33" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" s="7">
-        <v>19062</v>
+        <v>1471</v>
       </c>
       <c r="J33" s="5">
-        <v>73.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>92.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>108000</v>
+        <v>706000</v>
       </c>
       <c r="G34" s="7">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H34" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I34" s="7">
-        <v>8167</v>
+        <v>18000</v>
       </c>
       <c r="J34" s="5">
-        <v>73.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>92.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>308000</v>
+        <v>219000</v>
       </c>
       <c r="G35" s="7">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I35" s="7">
-        <v>16000</v>
+        <v>4824</v>
       </c>
       <c r="J35" s="5">
-        <v>72.7</v>
+        <v>73.7</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>90.3</v>
+        <v>90.8</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>252000</v>
+        <v>211000</v>
       </c>
       <c r="G36" s="7">
-        <v>12000</v>
+        <v>35000</v>
       </c>
       <c r="H36" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>11444</v>
+        <v>19000</v>
       </c>
       <c r="J36" s="5">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>95.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>171000</v>
+        <v>208000</v>
       </c>
       <c r="G37" s="7">
-        <v>19000</v>
+        <v>14000</v>
       </c>
       <c r="H37" s="7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>0</v>
+        <v>19333</v>
       </c>
       <c r="J37" s="5">
-        <v>72.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>90.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>221000</v>
+        <v>148000</v>
       </c>
       <c r="G38" s="7">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="H38" s="7">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I38" s="7">
-        <v>10062</v>
+        <v>7909</v>
       </c>
       <c r="J38" s="5">
-        <v>72.3</v>
+        <v>72.7</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1888,19 +1888,19 @@
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>320000</v>
+        <v>339000</v>
       </c>
       <c r="G39" s="7">
-        <v>4000</v>
+        <v>17000</v>
       </c>
       <c r="H39" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I39" s="7">
-        <v>13312</v>
+        <v>14429</v>
       </c>
       <c r="J39" s="5">
-        <v>72.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>89.2</v>
+        <v>91.3</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>194000</v>
+        <v>174000</v>
       </c>
       <c r="G40" s="7">
-        <v>22000</v>
+        <v>11000</v>
       </c>
       <c r="H40" s="7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I40" s="7">
-        <v>20400</v>
+        <v>8062</v>
       </c>
       <c r="J40" s="5">
         <v>72.2</v>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>91.3</v>
+        <v>88.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>237000</v>
+        <v>159000</v>
       </c>
       <c r="G41" s="7">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="H41" s="7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I41" s="7">
-        <v>7562</v>
+        <v>13500</v>
       </c>
       <c r="J41" s="5">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>80.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>930000</v>
+        <v>941000</v>
       </c>
       <c r="G42" s="7">
-        <v>8000</v>
+        <v>11000</v>
       </c>
       <c r="H42" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I42" s="7">
-        <v>29188</v>
+        <v>28118</v>
       </c>
       <c r="J42" s="5">
-        <v>71.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>335000</v>
+        <v>114000</v>
       </c>
       <c r="G43" s="7">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="H43" s="7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I43" s="7">
-        <v>13133</v>
+        <v>6273</v>
       </c>
       <c r="J43" s="5">
-        <v>71.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>79.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>674000</v>
+        <v>228000</v>
       </c>
       <c r="G44" s="7">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="H44" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I44" s="7">
-        <v>30562</v>
+        <v>9882</v>
       </c>
       <c r="J44" s="5">
-        <v>71.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>90.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>139000</v>
+        <v>843000</v>
       </c>
       <c r="G45" s="7">
-        <v>6000</v>
+        <v>127000</v>
       </c>
       <c r="H45" s="7">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I45" s="7">
-        <v>7800</v>
+        <v>3118</v>
       </c>
       <c r="J45" s="5">
-        <v>71.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,23 +2112,23 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>90</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>121000</v>
+        <v>312000</v>
       </c>
       <c r="G46" s="7">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="H46" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I46" s="7">
-        <v>7625</v>
+        <v>14000</v>
       </c>
       <c r="J46" s="5">
         <v>71.40000000000001</v>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>88.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>189000</v>
+        <v>237000</v>
       </c>
       <c r="G47" s="7">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="H47" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I47" s="7">
-        <v>11000</v>
+        <v>14308</v>
       </c>
       <c r="J47" s="5">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>86</v>
+        <v>91.7</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>235000</v>
+        <v>167000</v>
       </c>
       <c r="G48" s="7">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="H48" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7">
-        <v>15333</v>
+        <v>11400</v>
       </c>
       <c r="J48" s="5">
-        <v>71.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>88</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>185000</v>
+        <v>679000</v>
       </c>
       <c r="G49" s="7">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H49" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I49" s="7">
-        <v>10688</v>
+        <v>29059</v>
       </c>
       <c r="J49" s="5">
-        <v>71.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>84.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>254000</v>
+        <v>189000</v>
       </c>
       <c r="G50" s="7">
-        <v>24000</v>
+        <v>4000</v>
       </c>
       <c r="H50" s="7">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I50" s="7">
-        <v>17556</v>
+        <v>10294</v>
       </c>
       <c r="J50" s="5">
-        <v>70.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86.8</v>
+        <v>87.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>254000</v>
+        <v>221000</v>
       </c>
       <c r="G51" s="7">
-        <v>26000</v>
+        <v>6000</v>
       </c>
       <c r="H51" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I51" s="7">
-        <v>9800</v>
+        <v>11091</v>
       </c>
       <c r="J51" s="5">
-        <v>70.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>87.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>238000</v>
+        <v>100000</v>
       </c>
       <c r="G52" s="7">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="H52" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I52" s="7">
-        <v>8600</v>
+        <v>3667</v>
       </c>
       <c r="J52" s="5">
-        <v>70.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>87.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>189000</v>
+        <v>113000</v>
       </c>
       <c r="G53" s="7">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="H53" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I53" s="7">
-        <v>8667</v>
+        <v>7714</v>
       </c>
       <c r="J53" s="5">
-        <v>70.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>202000</v>
+        <v>317000</v>
       </c>
       <c r="G54" s="7">
-        <v>14000</v>
+        <v>-3000</v>
       </c>
       <c r="H54" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I54" s="7">
-        <v>9833</v>
+        <v>12353</v>
       </c>
       <c r="J54" s="5">
-        <v>70</v>
+        <v>70.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-10T05:14:27+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-11T04:54:29+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>系统想害我，我选择上交国家</t>
   </si>
   <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
+    <t>刚证道混沌天帝，让我身化禁区？</t>
+  </si>
+  <si>
+    <t>努力就变强的我，被重生者曝光了</t>
+  </si>
+  <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
     <t>诸神愚戏</t>
   </si>
   <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>刚证道混沌天帝，让我身化禁区？</t>
+    <t>十岁混圈，小爷娱乐圈圈霸</t>
   </si>
   <si>
     <t>全球死考：刚下刑场你让我去考试</t>
   </si>
   <si>
+    <t>天仙怀了我的娃，千年世家被曝光</t>
+  </si>
+  <si>
+    <t>家父造反成功，我被迫成为皇太子</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>我成假少爷后，八个妹妹不再隐忍</t>
+  </si>
+  <si>
+    <t>修仙界搞回收，破产仙子请自重</t>
+  </si>
+  <si>
     <t>奥特：最强债主！借债十倍返还！</t>
   </si>
   <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>我创立的组织，被重生者曝光了！</t>
+  </si>
+  <si>
+    <t>开局流落皇子，可我已经人间无敌</t>
+  </si>
+  <si>
+    <t>女多男少，开局被瓦学妹喊爸爸</t>
+  </si>
+  <si>
+    <t>师尊嫌我肮脏？反手退师帖送上</t>
+  </si>
+  <si>
+    <t>杀人犯？哼！在学校内我才是校霸</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>大唐：开局魔丸闺女炮轰长安城</t>
+  </si>
+  <si>
+    <t>洪荒之青莲大道</t>
+  </si>
+  <si>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>天幕盘点开国，红色华夏震撼千古</t>
+  </si>
+  <si>
+    <t>村长，收手吧，外面全是套路！</t>
+  </si>
+  <si>
+    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>四合院：从李云龙战友开始</t>
+  </si>
+  <si>
+    <t>捡来的妹妹修仙后，回来抢亲了</t>
+  </si>
+  <si>
     <t>时停起手，邪神也得给我跪下！</t>
   </si>
   <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
-  </si>
-  <si>
-    <t>天仙怀了我的娃，千年世家被曝光</t>
-  </si>
-  <si>
-    <t>女多男少，开局被瓦学妹喊爸爸</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
-  </si>
-  <si>
-    <t>家父造反成功，我被迫成为皇太子</t>
-  </si>
-  <si>
-    <t>公安局长之扫黑风暴</t>
+    <t>我都帝皇铠甲了，妹妹国运召唤？</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>重生后，成了妹妹的专属爱物</t>
+  </si>
+  <si>
+    <t>西幻：从鹰人部落到天使帝国</t>
+  </si>
+  <si>
+    <t>领主：从猎人卡开始</t>
   </si>
   <si>
     <t>每天属性翻一倍，我黑化爆杀一切</t>
   </si>
   <si>
-    <t>努力就变强的我，被重生者曝光了</t>
-  </si>
-  <si>
-    <t>捡来的妹妹修仙后，回来抢亲了</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>师尊嫌我肮脏？反手退师帖送上</t>
-  </si>
-  <si>
-    <t>冒姓琅琊</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>修仙界搞回收，破产仙子请自重</t>
-  </si>
-  <si>
-    <t>我成假少爷后，八个妹妹不再隐忍</t>
-  </si>
-  <si>
-    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
+    <t>崩铁：这是我家的令使</t>
+  </si>
+  <si>
+    <t>我，最强毒士，女帝直呼活阎王</t>
+  </si>
+  <si>
+    <t>我在诡异副本女装直播后爆火了</t>
+  </si>
+  <si>
+    <t>西游，你都成了猴子还要什么挂</t>
+  </si>
+  <si>
+    <t>年代1960：穿越南锣鼓巷，</t>
+  </si>
+  <si>
+    <t>天幕直播语文课，古人破防了</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
   </si>
   <si>
     <t>开局大限将至，我携帝兵问道禁区</t>
   </si>
   <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>大唐：开局魔丸闺女炮轰长安城</t>
-  </si>
-  <si>
-    <t>名义：从接替老刘开始</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>四合院：从李云龙战友开始</t>
-  </si>
-  <si>
-    <t>开局流落皇子，可我已经人间无敌</t>
-  </si>
-  <si>
-    <t>杀人犯？哼！在学校内我才是校霸</t>
-  </si>
-  <si>
-    <t>抗战：从湘江开始一路横推</t>
-  </si>
-  <si>
-    <t>离婚后，我成了刀枪炮！</t>
-  </si>
-  <si>
-    <t>瘟疫模拟：开局投放Necroa</t>
-  </si>
-  <si>
-    <t>我在诡异副本女装直播后爆火了</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>魂穿民国成为教导总队中校参谋</t>
-  </si>
-  <si>
-    <t>我提前三天被丢进了末世</t>
-  </si>
-  <si>
-    <t>从变身少女开始斩妖除魔</t>
-  </si>
-  <si>
-    <t>我都帝皇铠甲了，妹妹国运召唤？</t>
-  </si>
-  <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>入学第一天，千金学姐成了我老婆</t>
-  </si>
-  <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>开局四选一，我选成为沪圈少爷！</t>
-  </si>
-  <si>
-    <t>我根骨平庸，但分身都是绝世天才</t>
-  </si>
-  <si>
-    <t>穿梭八零，工业克苏鲁吓傻老外</t>
-  </si>
-  <si>
-    <t>重生之我成了太子麾下头号党魁</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
+    <t>悬疑凶案：公安局长重案手记</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>83.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1952000</v>
+        <v>2024000</v>
       </c>
       <c r="G5" s="7">
-        <v>69000</v>
+        <v>72000</v>
       </c>
       <c r="H5" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" s="7">
-        <v>86059</v>
+        <v>85278</v>
       </c>
       <c r="J5" s="5">
-        <v>87.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>94.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1138000</v>
+        <v>1236000</v>
       </c>
       <c r="G6" s="7">
-        <v>138000</v>
+        <v>98000</v>
       </c>
       <c r="H6" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="7">
-        <v>57118</v>
+        <v>59389</v>
       </c>
       <c r="J6" s="5">
-        <v>86</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>81.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>2737000</v>
+        <v>566000</v>
       </c>
       <c r="G7" s="7">
-        <v>-31000</v>
+        <v>49000</v>
       </c>
       <c r="H7" s="7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I7" s="7">
-        <v>85059</v>
+        <v>42125</v>
       </c>
       <c r="J7" s="5">
-        <v>85.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>97.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>517000</v>
+        <v>923000</v>
       </c>
       <c r="G8" s="7">
-        <v>48000</v>
+        <v>-8000</v>
       </c>
       <c r="H8" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I8" s="7">
-        <v>41143</v>
+        <v>52000</v>
       </c>
       <c r="J8" s="5">
-        <v>83.7</v>
+        <v>82</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>87.5</v>
+        <v>94.2</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>931000</v>
+        <v>442000</v>
       </c>
       <c r="G9" s="7">
-        <v>-22000</v>
+        <v>25000</v>
       </c>
       <c r="H9" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>57000</v>
+        <v>44200</v>
       </c>
       <c r="J9" s="5">
-        <v>82.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>78.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>1919000</v>
+        <v>1594000</v>
       </c>
       <c r="G10" s="7">
-        <v>-32000</v>
+        <v>270000</v>
       </c>
       <c r="H10" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" s="7">
-        <v>66706</v>
+        <v>31111</v>
       </c>
       <c r="J10" s="5">
-        <v>80.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>317000</v>
+        <v>2537000</v>
       </c>
       <c r="G11" s="7">
-        <v>40000</v>
+        <v>-200000</v>
       </c>
       <c r="H11" s="7">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I11" s="7">
-        <v>20200</v>
+        <v>69222</v>
       </c>
       <c r="J11" s="5">
-        <v>80</v>
+        <v>79.7</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>2240000</v>
+        <v>385000</v>
       </c>
       <c r="G12" s="7">
-        <v>227000</v>
+        <v>61000</v>
       </c>
       <c r="H12" s="7">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>37529</v>
+        <v>38000</v>
       </c>
       <c r="J12" s="5">
-        <v>79.7</v>
+        <v>79.5</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>97.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>343000</v>
+        <v>1875000</v>
       </c>
       <c r="G13" s="7">
-        <v>31000</v>
+        <v>-44000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I13" s="7">
-        <v>24143</v>
+        <v>60556</v>
       </c>
       <c r="J13" s="5">
-        <v>79.7</v>
+        <v>77.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>96.3</v>
+        <v>93.5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>334000</v>
+        <v>356000</v>
       </c>
       <c r="G14" s="7">
-        <v>29000</v>
+        <v>22000</v>
       </c>
       <c r="H14" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I14" s="7">
-        <v>23900</v>
+        <v>23727</v>
       </c>
       <c r="J14" s="5">
-        <v>78.90000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>286000</v>
+        <v>238000</v>
       </c>
       <c r="G15" s="7">
-        <v>23000</v>
+        <v>12000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>27286</v>
+        <v>26833</v>
       </c>
       <c r="J15" s="5">
-        <v>78.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>98.2</v>
+        <v>85.2</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>426000</v>
+        <v>1130000</v>
       </c>
       <c r="G16" s="7">
-        <v>39000</v>
+        <v>62000</v>
       </c>
       <c r="H16" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I16" s="7">
-        <v>16941</v>
+        <v>41611</v>
       </c>
       <c r="J16" s="5">
-        <v>78.2</v>
+        <v>77.3</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>226000</v>
+        <v>145000</v>
       </c>
       <c r="G17" s="7">
-        <v>19000</v>
+        <v>25000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I17" s="7">
-        <v>29800</v>
+        <v>8385</v>
       </c>
       <c r="J17" s="5">
-        <v>78.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>92.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>674000</v>
+        <v>287000</v>
       </c>
       <c r="G18" s="7">
-        <v>21000</v>
+        <v>26000</v>
       </c>
       <c r="H18" s="7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I18" s="7">
-        <v>29294</v>
+        <v>18889</v>
       </c>
       <c r="J18" s="5">
-        <v>78.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>93.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>382000</v>
+        <v>197000</v>
       </c>
       <c r="G19" s="7">
-        <v>29000</v>
+        <v>30000</v>
       </c>
       <c r="H19" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I19" s="7">
-        <v>23273</v>
+        <v>15000</v>
       </c>
       <c r="J19" s="5">
-        <v>77.3</v>
+        <v>76.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>417000</v>
+        <v>337000</v>
       </c>
       <c r="G20" s="7">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I20" s="7">
-        <v>49000</v>
+        <v>20182</v>
       </c>
       <c r="J20" s="5">
-        <v>77.2</v>
+        <v>76.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>99</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>195000</v>
+        <v>679000</v>
       </c>
       <c r="G21" s="7">
-        <v>39000</v>
+        <v>5000</v>
       </c>
       <c r="H21" s="7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I21" s="7">
-        <v>10500</v>
+        <v>27944</v>
       </c>
       <c r="J21" s="5">
-        <v>77.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>85.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>1068000</v>
+        <v>453000</v>
       </c>
       <c r="G22" s="7">
-        <v>67000</v>
+        <v>27000</v>
       </c>
       <c r="H22" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I22" s="7">
-        <v>40412</v>
+        <v>17500</v>
       </c>
       <c r="J22" s="5">
-        <v>77</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,14 +1353,14 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>94.3</v>
+        <v>93.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>271000</v>
+        <v>231000</v>
       </c>
       <c r="G23" s="7">
         <v>20000</v>
@@ -1369,10 +1369,10 @@
         <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>19000</v>
+        <v>19167</v>
       </c>
       <c r="J23" s="5">
-        <v>76.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>94.8</v>
+        <v>90.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>1324000</v>
+        <v>299000</v>
       </c>
       <c r="G24" s="7">
-        <v>485000</v>
+        <v>13000</v>
       </c>
       <c r="H24" s="7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I24" s="7">
-        <v>17059</v>
+        <v>25500</v>
       </c>
       <c r="J24" s="5">
-        <v>76.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>94.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>404000</v>
+        <v>291000</v>
       </c>
       <c r="G25" s="7">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="H25" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>17312</v>
+        <v>19143</v>
       </c>
       <c r="J25" s="5">
-        <v>76.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>96.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>167000</v>
+        <v>227000</v>
       </c>
       <c r="G26" s="7">
-        <v>37000</v>
+        <v>19000</v>
       </c>
       <c r="H26" s="7">
         <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>12857</v>
+        <v>19286</v>
       </c>
       <c r="J26" s="5">
-        <v>76.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>93</v>
+        <v>92.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>261000</v>
+        <v>423000</v>
       </c>
       <c r="G27" s="7">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H27" s="7">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I27" s="7">
-        <v>18000</v>
+        <v>17412</v>
       </c>
       <c r="J27" s="5">
-        <v>75.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>90.5</v>
+        <v>95.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>301000</v>
+        <v>190000</v>
       </c>
       <c r="G28" s="7">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="H28" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>20400</v>
+        <v>10714</v>
       </c>
       <c r="J28" s="5">
-        <v>74.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>94.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>161000</v>
+        <v>109000</v>
       </c>
       <c r="G29" s="7">
-        <v>13000</v>
+        <v>24000</v>
       </c>
       <c r="H29" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I29" s="7">
-        <v>11091</v>
+        <v>7200</v>
       </c>
       <c r="J29" s="5">
-        <v>74.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,23 +1584,23 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>95.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>120000</v>
+        <v>353000</v>
       </c>
       <c r="G30" s="7">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="H30" s="7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I30" s="7">
-        <v>7000</v>
+        <v>22375</v>
       </c>
       <c r="J30" s="5">
         <v>74.5</v>
@@ -1617,23 +1617,23 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>311000</v>
+        <v>207000</v>
       </c>
       <c r="G31" s="7">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="H31" s="7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I31" s="7">
-        <v>14118</v>
+        <v>29667</v>
       </c>
       <c r="J31" s="5">
         <v>74.40000000000001</v>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>94.3</v>
+        <v>97.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>170000</v>
+        <v>121000</v>
       </c>
       <c r="G32" s="7">
         <v>14000</v>
       </c>
       <c r="H32" s="7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I32" s="7">
-        <v>9167</v>
+        <v>2389</v>
       </c>
       <c r="J32" s="5">
-        <v>74.2</v>
+        <v>74.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,23 +1683,23 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>97.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>196000</v>
+        <v>310000</v>
       </c>
       <c r="G33" s="7">
-        <v>25000</v>
+        <v>9000</v>
       </c>
       <c r="H33" s="7">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I33" s="7">
-        <v>1471</v>
+        <v>19364</v>
       </c>
       <c r="J33" s="5">
         <v>74.09999999999999</v>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>89.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>706000</v>
+        <v>712000</v>
       </c>
       <c r="G34" s="7">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="H34" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I34" s="7">
-        <v>18000</v>
+        <v>17333</v>
       </c>
       <c r="J34" s="5">
-        <v>73.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>95.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>219000</v>
+        <v>241000</v>
       </c>
       <c r="G35" s="7">
         <v>22000</v>
       </c>
       <c r="H35" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I35" s="7">
-        <v>4824</v>
+        <v>5778</v>
       </c>
       <c r="J35" s="5">
-        <v>73.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>90.8</v>
+        <v>91.8</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>211000</v>
+        <v>210000</v>
       </c>
       <c r="G36" s="7">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="H36" s="7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I36" s="7">
-        <v>19000</v>
+        <v>10800</v>
       </c>
       <c r="J36" s="5">
-        <v>72.7</v>
+        <v>73.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>87.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>208000</v>
+        <v>2231000</v>
       </c>
       <c r="G37" s="7">
-        <v>14000</v>
+        <v>-9000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I37" s="7">
-        <v>19333</v>
+        <v>34944</v>
       </c>
       <c r="J37" s="5">
-        <v>72.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>92.3</v>
+        <v>89.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>148000</v>
+        <v>320000</v>
       </c>
       <c r="G38" s="7">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="H38" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7">
-        <v>7909</v>
+        <v>13143</v>
       </c>
       <c r="J38" s="5">
-        <v>72.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>88.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>339000</v>
+        <v>323000</v>
       </c>
       <c r="G39" s="7">
-        <v>17000</v>
+        <v>6000</v>
       </c>
       <c r="H39" s="7">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I39" s="7">
-        <v>14429</v>
+        <v>12000</v>
       </c>
       <c r="J39" s="5">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>91.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>174000</v>
+        <v>236000</v>
       </c>
       <c r="G40" s="7">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="H40" s="7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I40" s="7">
-        <v>8062</v>
+        <v>9778</v>
       </c>
       <c r="J40" s="5">
         <v>72.2</v>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>159000</v>
+        <v>314000</v>
       </c>
       <c r="G41" s="7">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="H41" s="7">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I41" s="7">
         <v>13500</v>
       </c>
       <c r="J41" s="5">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>81.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>941000</v>
+        <v>350000</v>
       </c>
       <c r="G42" s="7">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="H42" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I42" s="7">
-        <v>28118</v>
+        <v>7056</v>
       </c>
       <c r="J42" s="5">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>91</v>
+        <v>85.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>114000</v>
+        <v>304000</v>
       </c>
       <c r="G43" s="7">
-        <v>7000</v>
+        <v>27000</v>
       </c>
       <c r="H43" s="7">
         <v>12</v>
       </c>
       <c r="I43" s="7">
-        <v>6273</v>
+        <v>18909</v>
       </c>
       <c r="J43" s="5">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>89.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>228000</v>
+        <v>106000</v>
       </c>
       <c r="G44" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H44" s="7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I44" s="7">
-        <v>9882</v>
+        <v>6125</v>
       </c>
       <c r="J44" s="5">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,23 +2079,23 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>92.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>843000</v>
+        <v>371000</v>
       </c>
       <c r="G45" s="7">
-        <v>127000</v>
+        <v>-11000</v>
       </c>
       <c r="H45" s="7">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I45" s="7">
-        <v>3118</v>
+        <v>20417</v>
       </c>
       <c r="J45" s="5">
         <v>71.40000000000001</v>
@@ -2112,23 +2112,23 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>87.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>312000</v>
+        <v>260000</v>
       </c>
       <c r="G46" s="7">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="H46" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" s="7">
-        <v>14000</v>
+        <v>12571</v>
       </c>
       <c r="J46" s="5">
         <v>71.40000000000001</v>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>86.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>237000</v>
+        <v>957000</v>
       </c>
       <c r="G47" s="7">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="H47" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I47" s="7">
-        <v>14308</v>
+        <v>27444</v>
       </c>
       <c r="J47" s="5">
-        <v>71.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,23 +2178,23 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>91.7</v>
+        <v>87.7</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>167000</v>
+        <v>163000</v>
       </c>
       <c r="G48" s="7">
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="H48" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I48" s="7">
-        <v>11400</v>
+        <v>12444</v>
       </c>
       <c r="J48" s="5">
         <v>71.3</v>
@@ -2211,23 +2211,23 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>79.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>679000</v>
+        <v>239000</v>
       </c>
       <c r="G49" s="7">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H49" s="7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I49" s="7">
-        <v>29059</v>
+        <v>13429</v>
       </c>
       <c r="J49" s="5">
         <v>71.2</v>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>88.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>189000</v>
+        <v>685000</v>
       </c>
       <c r="G50" s="7">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H50" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I50" s="7">
-        <v>10294</v>
+        <v>27778</v>
       </c>
       <c r="J50" s="5">
-        <v>71.2</v>
+        <v>71</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>87.8</v>
+        <v>91.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>221000</v>
+        <v>200000</v>
       </c>
       <c r="G51" s="7">
-        <v>6000</v>
+        <v>13000</v>
       </c>
       <c r="H51" s="7">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I51" s="7">
-        <v>11091</v>
+        <v>778</v>
       </c>
       <c r="J51" s="5">
-        <v>71.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>91.2</v>
+        <v>87.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>100000</v>
+        <v>191000</v>
       </c>
       <c r="G52" s="7">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="H52" s="7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I52" s="7">
-        <v>3667</v>
+        <v>9833</v>
       </c>
       <c r="J52" s="5">
-        <v>71.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>89.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>113000</v>
+        <v>163000</v>
       </c>
       <c r="G53" s="7">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H53" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I53" s="7">
-        <v>7714</v>
+        <v>10333</v>
       </c>
       <c r="J53" s="5">
-        <v>70.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>86.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>317000</v>
+        <v>112000</v>
       </c>
       <c r="G54" s="7">
-        <v>-3000</v>
+        <v>6000</v>
       </c>
       <c r="H54" s="7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7">
-        <v>12353</v>
+        <v>6000</v>
       </c>
       <c r="J54" s="5">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-11T04:54:29+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-12T05:50:26+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>努力就变强的我，被重生者曝光了</t>
+  </si>
+  <si>
+    <t>时停起手，邪神也得给我跪下！</t>
+  </si>
+  <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
     <t>规则怪谈：无所谓，系统会出手</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
     <t>刚证道混沌天帝，让我身化禁区？</t>
   </si>
   <si>
-    <t>努力就变强的我，被重生者曝光了</t>
-  </si>
-  <si>
-    <t>冒姓琅琊</t>
+    <t>天幕盘点开国，红色华夏震撼千古</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>编外法医：重案组抢疯了！</t>
+  </si>
+  <si>
+    <t>十岁混圈，小爷娱乐圈圈霸</t>
+  </si>
+  <si>
+    <t>全球死考：刚下刑场你让我去考试</t>
+  </si>
+  <si>
+    <t>家父造反成功，我被迫成为皇太子</t>
+  </si>
+  <si>
+    <t>南部档案：我真不想当张家主事人</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>奥特：最强债主！借债十倍返还！</t>
+  </si>
+  <si>
+    <t>大唐：开局魔丸闺女炮轰长安城</t>
+  </si>
+  <si>
+    <t>洪荒之青莲大道</t>
   </si>
   <si>
     <t>诸神愚戏</t>
   </si>
   <si>
-    <t>十岁混圈，小爷娱乐圈圈霸</t>
-  </si>
-  <si>
-    <t>全球死考：刚下刑场你让我去考试</t>
+    <t>我成假少爷后，八个妹妹不再隐忍</t>
+  </si>
+  <si>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>杀人犯？哼！在学校内我才是校霸</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>四合院：从李云龙战友开始</t>
+  </si>
+  <si>
+    <t>离婚后，我成了刀枪炮！</t>
   </si>
   <si>
     <t>天仙怀了我的娃，千年世家被曝光</t>
   </si>
   <si>
-    <t>家父造反成功，我被迫成为皇太子</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>我成假少爷后，八个妹妹不再隐忍</t>
-  </si>
-  <si>
-    <t>修仙界搞回收，破产仙子请自重</t>
-  </si>
-  <si>
-    <t>奥特：最强债主！借债十倍返还！</t>
-  </si>
-  <si>
-    <t>公安局长之扫黑风暴</t>
-  </si>
-  <si>
-    <t>我创立的组织，被重生者曝光了！</t>
+    <t>网约车百倍补贴，我转身提迈巴赫</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>女多男少，开局被瓦学妹喊爸爸</t>
+  </si>
+  <si>
+    <t>我根骨平庸，但分身都是绝世天才</t>
+  </si>
+  <si>
+    <t>我都帝皇铠甲了，妹妹国运召唤？</t>
+  </si>
+  <si>
+    <t>师尊嫌我肮脏？反手退师帖送上</t>
+  </si>
+  <si>
+    <t>西幻：从鹰人部落到天使帝国</t>
+  </si>
+  <si>
+    <t>崩铁：这是我家的令使</t>
+  </si>
+  <si>
+    <t>我在诡异副本女装直播后爆火了</t>
+  </si>
+  <si>
+    <t>综导：开局接手跑男后整蛊全明星</t>
+  </si>
+  <si>
+    <t>悬疑凶案：公安局长重案手记</t>
+  </si>
+  <si>
+    <t>我提前三天被丢进了末世</t>
+  </si>
+  <si>
+    <t>开局四选一，我选成为沪圈少爷！</t>
+  </si>
+  <si>
+    <t>我从吃神开始反向晋升</t>
+  </si>
+  <si>
+    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
+  </si>
+  <si>
+    <t>名义，汉东第一拳王，汉东王来了</t>
+  </si>
+  <si>
+    <t>领主：从猎人卡开始</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
   </si>
   <si>
     <t>开局流落皇子，可我已经人间无敌</t>
   </si>
   <si>
-    <t>女多男少，开局被瓦学妹喊爸爸</t>
-  </si>
-  <si>
-    <t>师尊嫌我肮脏？反手退师帖送上</t>
-  </si>
-  <si>
-    <t>杀人犯？哼！在学校内我才是校霸</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>大唐：开局魔丸闺女炮轰长安城</t>
-  </si>
-  <si>
-    <t>洪荒之青莲大道</t>
-  </si>
-  <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
-  </si>
-  <si>
-    <t>天幕盘点开国，红色华夏震撼千古</t>
-  </si>
-  <si>
-    <t>村长，收手吧，外面全是套路！</t>
-  </si>
-  <si>
-    <t>玄幻：我堕魔后把绝美师尊抓回来</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>四合院：从李云龙战友开始</t>
+    <t>名义：从接替老刘开始</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>大秦：我，嬴政！开局面壁穿越者</t>
   </si>
   <si>
     <t>捡来的妹妹修仙后，回来抢亲了</t>
-  </si>
-  <si>
-    <t>时停起手，邪神也得给我跪下！</t>
-  </si>
-  <si>
-    <t>我都帝皇铠甲了，妹妹国运召唤？</t>
-  </si>
-  <si>
-    <t>编外法医：重案组抢疯了！</t>
-  </si>
-  <si>
-    <t>我提前三天被丢进了末世</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>重生后，成了妹妹的专属爱物</t>
-  </si>
-  <si>
-    <t>西幻：从鹰人部落到天使帝国</t>
-  </si>
-  <si>
-    <t>领主：从猎人卡开始</t>
-  </si>
-  <si>
-    <t>每天属性翻一倍，我黑化爆杀一切</t>
-  </si>
-  <si>
-    <t>崩铁：这是我家的令使</t>
-  </si>
-  <si>
-    <t>我，最强毒士，女帝直呼活阎王</t>
-  </si>
-  <si>
-    <t>我在诡异副本女装直播后爆火了</t>
-  </si>
-  <si>
-    <t>西游，你都成了猴子还要什么挂</t>
-  </si>
-  <si>
-    <t>年代1960：穿越南锣鼓巷，</t>
-  </si>
-  <si>
-    <t>天幕直播语文课，古人破防了</t>
-  </si>
-  <si>
-    <t>开局四选一，我选成为沪圈少爷！</t>
-  </si>
-  <si>
-    <t>开局大限将至，我携帝兵问道禁区</t>
-  </si>
-  <si>
-    <t>悬疑凶案：公安局长重案手记</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>84.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>2024000</v>
+        <v>1836000</v>
       </c>
       <c r="G5" s="7">
-        <v>72000</v>
+        <v>242000</v>
       </c>
       <c r="H5" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I5" s="7">
-        <v>85278</v>
+        <v>42211</v>
       </c>
       <c r="J5" s="5">
-        <v>87.7</v>
+        <v>83.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>89.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1236000</v>
+        <v>474000</v>
       </c>
       <c r="G6" s="7">
-        <v>98000</v>
+        <v>32000</v>
       </c>
       <c r="H6" s="7">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>59389</v>
+        <v>42167</v>
       </c>
       <c r="J6" s="5">
-        <v>83.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>96.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>566000</v>
+        <v>2468000</v>
       </c>
       <c r="G7" s="7">
-        <v>49000</v>
+        <v>237000</v>
       </c>
       <c r="H7" s="7">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I7" s="7">
-        <v>42125</v>
+        <v>45579</v>
       </c>
       <c r="J7" s="5">
-        <v>83.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>89</v>
+        <v>93.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>923000</v>
+        <v>597000</v>
       </c>
       <c r="G8" s="7">
-        <v>-8000</v>
+        <v>31000</v>
       </c>
       <c r="H8" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I8" s="7">
-        <v>52000</v>
+        <v>40889</v>
       </c>
       <c r="J8" s="5">
-        <v>82</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>94.2</v>
+        <v>84.5</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>442000</v>
+        <v>1285000</v>
       </c>
       <c r="G9" s="7">
-        <v>25000</v>
+        <v>49000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I9" s="7">
-        <v>44200</v>
+        <v>58842</v>
       </c>
       <c r="J9" s="5">
-        <v>80.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>96</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>1594000</v>
+        <v>1916000</v>
       </c>
       <c r="G10" s="7">
-        <v>270000</v>
+        <v>-108000</v>
       </c>
       <c r="H10" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I10" s="7">
-        <v>31111</v>
+        <v>75105</v>
       </c>
       <c r="J10" s="5">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>77</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>2537000</v>
+        <v>907000</v>
       </c>
       <c r="G11" s="7">
-        <v>-200000</v>
+        <v>-16000</v>
       </c>
       <c r="H11" s="7">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I11" s="7">
-        <v>69222</v>
+        <v>47143</v>
       </c>
       <c r="J11" s="5">
-        <v>79.7</v>
+        <v>80.2</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -997,19 +997,19 @@
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>385000</v>
+        <v>236000</v>
       </c>
       <c r="G12" s="7">
-        <v>61000</v>
+        <v>29000</v>
       </c>
       <c r="H12" s="7">
         <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>38000</v>
+        <v>29500</v>
       </c>
       <c r="J12" s="5">
-        <v>79.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>77.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>1875000</v>
+        <v>169000</v>
       </c>
       <c r="G13" s="7">
-        <v>-44000</v>
+        <v>24000</v>
       </c>
       <c r="H13" s="7">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I13" s="7">
-        <v>60556</v>
+        <v>9500</v>
       </c>
       <c r="J13" s="5">
-        <v>77.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>93.5</v>
+        <v>98</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
@@ -1066,16 +1066,16 @@
         <v>356000</v>
       </c>
       <c r="G14" s="7">
-        <v>22000</v>
+        <v>33000</v>
       </c>
       <c r="H14" s="7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I14" s="7">
-        <v>23727</v>
+        <v>13105</v>
       </c>
       <c r="J14" s="5">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>92.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>238000</v>
+        <v>405000</v>
       </c>
       <c r="G15" s="7">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>26833</v>
+        <v>34400</v>
       </c>
       <c r="J15" s="5">
-        <v>77.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>85.2</v>
+        <v>77.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>1130000</v>
+        <v>1835000</v>
       </c>
       <c r="G16" s="7">
-        <v>62000</v>
+        <v>-40000</v>
       </c>
       <c r="H16" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I16" s="7">
-        <v>41611</v>
+        <v>55263</v>
       </c>
       <c r="J16" s="5">
-        <v>77.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>145000</v>
+        <v>248000</v>
       </c>
       <c r="G17" s="7">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="H17" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>8385</v>
+        <v>24429</v>
       </c>
       <c r="J17" s="5">
-        <v>77.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>287000</v>
+        <v>145000</v>
       </c>
       <c r="G18" s="7">
-        <v>26000</v>
+        <v>24000</v>
       </c>
       <c r="H18" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I18" s="7">
-        <v>18889</v>
+        <v>5000</v>
       </c>
       <c r="J18" s="5">
-        <v>76.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>96.5</v>
+        <v>82.7</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>197000</v>
+        <v>1166000</v>
       </c>
       <c r="G19" s="7">
-        <v>30000</v>
+        <v>36000</v>
       </c>
       <c r="H19" s="7">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I19" s="7">
-        <v>15000</v>
+        <v>41316</v>
       </c>
       <c r="J19" s="5">
-        <v>76.8</v>
+        <v>75.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>93.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>337000</v>
+        <v>353000</v>
       </c>
       <c r="G20" s="7">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="H20" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="7">
-        <v>20182</v>
+        <v>19833</v>
       </c>
       <c r="J20" s="5">
-        <v>76.7</v>
+        <v>75.8</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>679000</v>
+        <v>211000</v>
       </c>
       <c r="G21" s="7">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="H21" s="7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I21" s="7">
-        <v>27944</v>
+        <v>12000</v>
       </c>
       <c r="J21" s="5">
-        <v>76.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>94.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>453000</v>
+        <v>126000</v>
       </c>
       <c r="G22" s="7">
-        <v>27000</v>
+        <v>17000</v>
       </c>
       <c r="H22" s="7">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I22" s="7">
-        <v>17500</v>
+        <v>8091</v>
       </c>
       <c r="J22" s="5">
-        <v>76.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>93.8</v>
+        <v>75.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>231000</v>
+        <v>2323000</v>
       </c>
       <c r="G23" s="7">
-        <v>20000</v>
+        <v>-214000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I23" s="7">
-        <v>19167</v>
+        <v>54316</v>
       </c>
       <c r="J23" s="5">
-        <v>76.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>90.3</v>
+        <v>91</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>299000</v>
+        <v>302000</v>
       </c>
       <c r="G24" s="7">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="H24" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I24" s="7">
-        <v>25500</v>
+        <v>18500</v>
       </c>
       <c r="J24" s="5">
-        <v>76</v>
+        <v>74.7</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>93</v>
+        <v>89.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>291000</v>
+        <v>361000</v>
       </c>
       <c r="G25" s="7">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I25" s="7">
-        <v>19143</v>
+        <v>20778</v>
       </c>
       <c r="J25" s="5">
-        <v>75.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>92.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>227000</v>
+        <v>661000</v>
       </c>
       <c r="G26" s="7">
-        <v>19000</v>
+        <v>-18000</v>
       </c>
       <c r="H26" s="7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I26" s="7">
-        <v>19286</v>
+        <v>25526</v>
       </c>
       <c r="J26" s="5">
-        <v>75.8</v>
+        <v>74</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>92.8</v>
+        <v>89.3</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>423000</v>
+        <v>240000</v>
       </c>
       <c r="G27" s="7">
-        <v>19000</v>
+        <v>13000</v>
       </c>
       <c r="H27" s="7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I27" s="7">
-        <v>17412</v>
+        <v>18500</v>
       </c>
       <c r="J27" s="5">
-        <v>75.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>95.7</v>
+        <v>89.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>190000</v>
+        <v>714000</v>
       </c>
       <c r="G28" s="7">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I28" s="7">
-        <v>10714</v>
+        <v>16526</v>
       </c>
       <c r="J28" s="5">
-        <v>75.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>96.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>109000</v>
+        <v>262000</v>
       </c>
       <c r="G29" s="7">
-        <v>24000</v>
+        <v>21000</v>
       </c>
       <c r="H29" s="7">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I29" s="7">
-        <v>7200</v>
+        <v>6579</v>
       </c>
       <c r="J29" s="5">
-        <v>75.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>353000</v>
+        <v>366000</v>
       </c>
       <c r="G30" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="H30" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30" s="7">
-        <v>22375</v>
+        <v>14222</v>
       </c>
       <c r="J30" s="5">
-        <v>74.5</v>
+        <v>72.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>100</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>207000</v>
+        <v>353000</v>
       </c>
       <c r="G31" s="7">
-        <v>27000</v>
+        <v>-3000</v>
       </c>
       <c r="H31" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I31" s="7">
-        <v>29667</v>
+        <v>21500</v>
       </c>
       <c r="J31" s="5">
-        <v>74.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>97.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>121000</v>
+        <v>335000</v>
       </c>
       <c r="G32" s="7">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="H32" s="7">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>2389</v>
+        <v>21800</v>
       </c>
       <c r="J32" s="5">
-        <v>74.3</v>
+        <v>72.7</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>89.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>310000</v>
+        <v>423000</v>
       </c>
       <c r="G33" s="7">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I33" s="7">
-        <v>19364</v>
+        <v>16444</v>
       </c>
       <c r="J33" s="5">
-        <v>74.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>90.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>712000</v>
+        <v>299000</v>
       </c>
       <c r="G34" s="7">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="H34" s="7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I34" s="7">
-        <v>17333</v>
+        <v>22667</v>
       </c>
       <c r="J34" s="5">
-        <v>73.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>95.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>241000</v>
+        <v>234000</v>
       </c>
       <c r="G35" s="7">
-        <v>22000</v>
+        <v>14000</v>
       </c>
       <c r="H35" s="7">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I35" s="7">
-        <v>5778</v>
+        <v>10385</v>
       </c>
       <c r="J35" s="5">
-        <v>73.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>91.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>210000</v>
+        <v>326000</v>
       </c>
       <c r="G36" s="7">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="H36" s="7">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I36" s="7">
-        <v>10800</v>
+        <v>12250</v>
       </c>
       <c r="J36" s="5">
-        <v>73.2</v>
+        <v>71.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>79.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>2231000</v>
+        <v>293000</v>
       </c>
       <c r="G37" s="7">
-        <v>-9000</v>
+        <v>2000</v>
       </c>
       <c r="H37" s="7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I37" s="7">
-        <v>34944</v>
+        <v>17000</v>
       </c>
       <c r="J37" s="5">
-        <v>72.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>89.3</v>
+        <v>84.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>320000</v>
+        <v>330000</v>
       </c>
       <c r="G38" s="7">
-        <v>8000</v>
+        <v>26000</v>
       </c>
       <c r="H38" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I38" s="7">
-        <v>13143</v>
+        <v>19500</v>
       </c>
       <c r="J38" s="5">
-        <v>72.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>89.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>323000</v>
+        <v>268000</v>
       </c>
       <c r="G39" s="7">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="H39" s="7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I39" s="7">
         <v>12000</v>
       </c>
       <c r="J39" s="5">
-        <v>72.2</v>
+        <v>71.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>90.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>236000</v>
+        <v>166000</v>
       </c>
       <c r="G40" s="7">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="H40" s="7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I40" s="7">
-        <v>9778</v>
+        <v>11500</v>
       </c>
       <c r="J40" s="5">
-        <v>72.2</v>
+        <v>71.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>314000</v>
+        <v>170000</v>
       </c>
       <c r="G41" s="7">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="H41" s="7">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>13500</v>
+        <v>10500</v>
       </c>
       <c r="J41" s="5">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>91.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>350000</v>
+        <v>119000</v>
       </c>
       <c r="G42" s="7">
-        <v>22000</v>
+        <v>7000</v>
       </c>
       <c r="H42" s="7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I42" s="7">
-        <v>7056</v>
+        <v>6111</v>
       </c>
       <c r="J42" s="5">
-        <v>71.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85.5</v>
+        <v>88.2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>304000</v>
+        <v>239000</v>
       </c>
       <c r="G43" s="7">
-        <v>27000</v>
+        <v>3000</v>
       </c>
       <c r="H43" s="7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I43" s="7">
-        <v>18909</v>
+        <v>9421</v>
       </c>
       <c r="J43" s="5">
-        <v>71.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>91.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>106000</v>
+        <v>194000</v>
       </c>
       <c r="G44" s="7">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="H44" s="7">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I44" s="7">
-        <v>6125</v>
+        <v>9474</v>
       </c>
       <c r="J44" s="5">
-        <v>71.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>84.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>371000</v>
+        <v>704000</v>
       </c>
       <c r="G45" s="7">
-        <v>-11000</v>
+        <v>51000</v>
       </c>
       <c r="H45" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>20417</v>
+        <v>54000</v>
       </c>
       <c r="J45" s="5">
-        <v>71.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>87.7</v>
+        <v>84</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>260000</v>
+        <v>302000</v>
       </c>
       <c r="G46" s="7">
-        <v>8000</v>
+        <v>-8000</v>
       </c>
       <c r="H46" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I46" s="7">
-        <v>12571</v>
+        <v>17083</v>
       </c>
       <c r="J46" s="5">
-        <v>71.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>80.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>957000</v>
+        <v>227000</v>
       </c>
       <c r="G47" s="7">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="H47" s="7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I47" s="7">
-        <v>27444</v>
+        <v>9333</v>
       </c>
       <c r="J47" s="5">
-        <v>71.3</v>
+        <v>70.5</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>163000</v>
+        <v>112000</v>
       </c>
       <c r="G48" s="7">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
         <v>10</v>
       </c>
       <c r="I48" s="7">
-        <v>12444</v>
+        <v>6111</v>
       </c>
       <c r="J48" s="5">
-        <v>71.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>239000</v>
+        <v>246000</v>
       </c>
       <c r="G49" s="7">
-        <v>2000</v>
+        <v>28000</v>
       </c>
       <c r="H49" s="7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I49" s="7">
-        <v>13429</v>
+        <v>29000</v>
       </c>
       <c r="J49" s="5">
-        <v>71.2</v>
+        <v>69.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>80.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>685000</v>
+        <v>232000</v>
       </c>
       <c r="G50" s="7">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="H50" s="7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I50" s="7">
-        <v>27778</v>
+        <v>16571</v>
       </c>
       <c r="J50" s="5">
-        <v>71</v>
+        <v>69.8</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>91.8</v>
+        <v>89.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>200000</v>
+        <v>226000</v>
       </c>
       <c r="G51" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H51" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I51" s="7">
-        <v>778</v>
+        <v>2895</v>
       </c>
       <c r="J51" s="5">
-        <v>70.7</v>
+        <v>69.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>87.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>191000</v>
+        <v>168000</v>
       </c>
       <c r="G52" s="7">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="H52" s="7">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I52" s="7">
-        <v>9833</v>
+        <v>13000</v>
       </c>
       <c r="J52" s="5">
-        <v>70.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>87.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>163000</v>
+        <v>660000</v>
       </c>
       <c r="G53" s="7">
-        <v>2000</v>
+        <v>42000</v>
       </c>
       <c r="H53" s="7">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I53" s="7">
-        <v>10333</v>
+        <v>8842</v>
       </c>
       <c r="J53" s="5">
-        <v>70.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>89.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>112000</v>
+        <v>211000</v>
       </c>
       <c r="G54" s="7">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I54" s="7">
-        <v>6000</v>
+        <v>10188</v>
       </c>
       <c r="J54" s="5">
-        <v>70.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-13T05:52:12+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-14T05:50:34+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-14T05:50:34+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-15T03:08:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -10,19 +10,19 @@
     <sheet name="作品数据" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="68">
   <si>
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-15T03:08:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-16T03:30:26+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -68,13 +68,170 @@
   </si>
   <si>
     <t>达标日期列表</t>
+  </si>
+  <si>
+    <t>时停起手，邪神也得给我跪下！</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>三十多没娶亲，捡个孕妻还嫌亏</t>
+  </si>
+  <si>
+    <t>入学第一天，千金学姐成了我老婆</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>亮剑：军校毕业，我给老李当参谋</t>
+  </si>
+  <si>
+    <t>站中间抽两边，什么叫霸之意志呀</t>
+  </si>
+  <si>
+    <t>穿成大周宰相，皇后腰疼关我啥事</t>
+  </si>
+  <si>
+    <t>沉劫</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>人在潮汕，开局连抛十八圣杯</t>
+  </si>
+  <si>
+    <t>我从吃神开始反向晋升</t>
+  </si>
+  <si>
+    <t>我在精神病院学斩神</t>
+  </si>
+  <si>
+    <t>东北往事：野种的母亲</t>
+  </si>
+  <si>
+    <t>全员悍匪：你管这叫正经公司？</t>
+  </si>
+  <si>
+    <t>抑郁少女总想自杀？那就恶堕吧！</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>大唐：玄武门前夜，我绑父投秦王</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>五哈：千年家族曝光，误闯天家！</t>
+  </si>
+  <si>
+    <t>一战：我成了白毛德皇的治国轮椅</t>
+  </si>
+  <si>
+    <t>大秦：我，嬴政！开局面壁穿越者</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>四合院：我表哥是神棍</t>
+  </si>
+  <si>
+    <t>相亲失败！我把精神小妹捧成天后</t>
+  </si>
+  <si>
+    <t>末世的UN小队</t>
+  </si>
+  <si>
+    <t>动物城：开局被大先生捡到</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>猪猪侠：什么叫主攻手空手接大？</t>
+  </si>
+  <si>
+    <t>长枪绑手电，还说你不是邪修？</t>
+  </si>
+  <si>
+    <t>双胞胎校花是病娇？我养的！</t>
+  </si>
+  <si>
+    <t>天幕盘点开国，红色华夏震撼千古</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>凡人修仙，捡个仙子做老婆</t>
+  </si>
+  <si>
+    <t>江裴拔剑，狼子野心</t>
+  </si>
+  <si>
+    <t>怪物图鉴：从哥布林血脉开始</t>
+  </si>
+  <si>
+    <t>西幻：从鹰人部落到天使帝国</t>
+  </si>
+  <si>
+    <t>修仙界搞回收，破产仙子请自重</t>
+  </si>
+  <si>
+    <t>全民英雄协会：开局招募一拳光头</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>开局长生万古，苟到天荒地老</t>
+  </si>
+  <si>
+    <t>镇国驸马爷</t>
+  </si>
+  <si>
+    <t>远离男主保命！校花后宫倒追我？</t>
+  </si>
+  <si>
+    <t>小区求生：每人每天给我一块面包</t>
+  </si>
+  <si>
+    <t>农村女婿</t>
+  </si>
+  <si>
+    <t>四合院，开局我选入赘</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>转生火影，卡普模版</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +262,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -126,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -149,11 +314,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -163,6 +343,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -561,12 +753,1716 @@
         <v>16</v>
       </c>
     </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5">
+        <v>89.5</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3233000</v>
+      </c>
+      <c r="G5" s="7">
+        <v>211000</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3</v>
+      </c>
+      <c r="I5" s="7">
+        <v>190000</v>
+      </c>
+      <c r="J5" s="5">
+        <v>83.2</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5">
+        <v>84.2</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="7">
+        <v>474000</v>
+      </c>
+      <c r="G6" s="7">
+        <v>70000</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3</v>
+      </c>
+      <c r="I6" s="7">
+        <v>74500</v>
+      </c>
+      <c r="J6" s="5">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5">
+        <v>97.7</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="7">
+        <v>276000</v>
+      </c>
+      <c r="G7" s="7">
+        <v>30000</v>
+      </c>
+      <c r="H7" s="7">
+        <v>3</v>
+      </c>
+      <c r="I7" s="7">
+        <v>39500</v>
+      </c>
+      <c r="J7" s="5">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="7">
+        <v>386000</v>
+      </c>
+      <c r="G8" s="7">
+        <v>30000</v>
+      </c>
+      <c r="H8" s="7">
+        <v>3</v>
+      </c>
+      <c r="I8" s="7">
+        <v>37500</v>
+      </c>
+      <c r="J8" s="5">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5">
+        <v>100</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="7">
+        <v>153000</v>
+      </c>
+      <c r="G9" s="7">
+        <v>22000</v>
+      </c>
+      <c r="H9" s="7">
+        <v>3</v>
+      </c>
+      <c r="I9" s="7">
+        <v>26000</v>
+      </c>
+      <c r="J9" s="5">
+        <v>70.5</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5">
+        <v>96</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="7">
+        <v>109000</v>
+      </c>
+      <c r="G10" s="7">
+        <v>26000</v>
+      </c>
+      <c r="H10" s="7">
+        <v>3</v>
+      </c>
+      <c r="I10" s="7">
+        <v>30000</v>
+      </c>
+      <c r="J10" s="5">
+        <v>69.3</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5">
+        <v>91.2</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="7">
+        <v>252000</v>
+      </c>
+      <c r="G11" s="7">
+        <v>33000</v>
+      </c>
+      <c r="H11" s="7">
+        <v>3</v>
+      </c>
+      <c r="I11" s="7">
+        <v>39500</v>
+      </c>
+      <c r="J11" s="5">
+        <v>69</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5">
+        <v>95.8</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="7">
+        <v>210000</v>
+      </c>
+      <c r="G12" s="7">
+        <v>28000</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3</v>
+      </c>
+      <c r="I12" s="7">
+        <v>29000</v>
+      </c>
+      <c r="J12" s="5">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5">
+        <v>99.8</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="7">
+        <v>134000</v>
+      </c>
+      <c r="G13" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H13" s="7">
+        <v>3</v>
+      </c>
+      <c r="I13" s="7">
+        <v>20000</v>
+      </c>
+      <c r="J13" s="5">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5">
+        <v>96.7</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="7">
+        <v>103000</v>
+      </c>
+      <c r="G14" s="7">
+        <v>22000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>3</v>
+      </c>
+      <c r="I14" s="7">
+        <v>21500</v>
+      </c>
+      <c r="J14" s="5">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5">
+        <v>98.7</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="7">
+        <v>117000</v>
+      </c>
+      <c r="G15" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H15" s="7">
+        <v>3</v>
+      </c>
+      <c r="I15" s="7">
+        <v>16500</v>
+      </c>
+      <c r="J15" s="5">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="7">
+        <v>372000</v>
+      </c>
+      <c r="G16" s="7">
+        <v>23000</v>
+      </c>
+      <c r="H16" s="7">
+        <v>3</v>
+      </c>
+      <c r="I16" s="7">
+        <v>27000</v>
+      </c>
+      <c r="J16" s="5">
+        <v>67.2</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="7">
+        <v>897000</v>
+      </c>
+      <c r="G17" s="7">
+        <v>43000</v>
+      </c>
+      <c r="H17" s="7">
+        <v>3</v>
+      </c>
+      <c r="I17" s="7">
+        <v>50000</v>
+      </c>
+      <c r="J17" s="5">
+        <v>65.8</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="7">
+        <v>2124000</v>
+      </c>
+      <c r="G18" s="7">
+        <v>51000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>3</v>
+      </c>
+      <c r="I18" s="7">
+        <v>38500</v>
+      </c>
+      <c r="J18" s="5">
+        <v>63.9</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="7">
+        <v>135000</v>
+      </c>
+      <c r="G19" s="7">
+        <v>13000</v>
+      </c>
+      <c r="H19" s="7">
+        <v>3</v>
+      </c>
+      <c r="I19" s="7">
+        <v>11000</v>
+      </c>
+      <c r="J19" s="5">
+        <v>63.8</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="7">
+        <v>123000</v>
+      </c>
+      <c r="G20" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H20" s="7">
+        <v>3</v>
+      </c>
+      <c r="I20" s="7">
+        <v>9500</v>
+      </c>
+      <c r="J20" s="5">
+        <v>63.3</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5">
+        <v>88.8</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="7">
+        <v>349000</v>
+      </c>
+      <c r="G21" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>3</v>
+      </c>
+      <c r="I21" s="7">
+        <v>20500</v>
+      </c>
+      <c r="J21" s="5">
+        <v>63</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="7">
+        <v>115000</v>
+      </c>
+      <c r="G22" s="7">
+        <v>20000</v>
+      </c>
+      <c r="H22" s="7">
+        <v>3</v>
+      </c>
+      <c r="I22" s="7">
+        <v>20500</v>
+      </c>
+      <c r="J22" s="5">
+        <v>62.9</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5">
+        <v>93.3</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="7">
+        <v>113000</v>
+      </c>
+      <c r="G23" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>9000</v>
+      </c>
+      <c r="J23" s="5">
+        <v>62.6</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5">
+        <v>91.3</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="7">
+        <v>222000</v>
+      </c>
+      <c r="G24" s="7">
+        <v>13000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>3</v>
+      </c>
+      <c r="I24" s="7">
+        <v>13000</v>
+      </c>
+      <c r="J24" s="5">
+        <v>62.5</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5">
+        <v>89.3</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="7">
+        <v>170000</v>
+      </c>
+      <c r="G25" s="7">
+        <v>14000</v>
+      </c>
+      <c r="H25" s="7">
+        <v>3</v>
+      </c>
+      <c r="I25" s="7">
+        <v>17000</v>
+      </c>
+      <c r="J25" s="5">
+        <v>62.4</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5">
+        <v>9.6</v>
+      </c>
+      <c r="C26" s="5">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="7">
+        <v>110000</v>
+      </c>
+      <c r="G26" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H26" s="7">
+        <v>3</v>
+      </c>
+      <c r="I26" s="7">
+        <v>11500</v>
+      </c>
+      <c r="J26" s="5">
+        <v>62.4</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="7">
+        <v>797000</v>
+      </c>
+      <c r="G27" s="7">
+        <v>24000</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3</v>
+      </c>
+      <c r="I27" s="7">
+        <v>30500</v>
+      </c>
+      <c r="J27" s="5">
+        <v>62.1</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="7">
+        <v>633000</v>
+      </c>
+      <c r="G28" s="7">
+        <v>23000</v>
+      </c>
+      <c r="H28" s="7">
+        <v>3</v>
+      </c>
+      <c r="I28" s="7">
+        <v>31500</v>
+      </c>
+      <c r="J28" s="5">
+        <v>61.9</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="7">
+        <v>452000</v>
+      </c>
+      <c r="G29" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H29" s="7">
+        <v>3</v>
+      </c>
+      <c r="I29" s="7">
+        <v>12500</v>
+      </c>
+      <c r="J29" s="5">
+        <v>61.9</v>
+      </c>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5">
+        <v>90.2</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="7">
+        <v>261000</v>
+      </c>
+      <c r="G30" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H30" s="7">
+        <v>3</v>
+      </c>
+      <c r="I30" s="7">
+        <v>13000</v>
+      </c>
+      <c r="J30" s="5">
+        <v>61.9</v>
+      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5">
+        <v>86.7</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="7">
+        <v>223000</v>
+      </c>
+      <c r="G31" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H31" s="7">
+        <v>3</v>
+      </c>
+      <c r="I31" s="7">
+        <v>20000</v>
+      </c>
+      <c r="J31" s="5">
+        <v>61.7</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5">
+        <v>92</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="7">
+        <v>105000</v>
+      </c>
+      <c r="G32" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H32" s="7">
+        <v>3</v>
+      </c>
+      <c r="I32" s="7">
+        <v>8500</v>
+      </c>
+      <c r="J32" s="5">
+        <v>61.7</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5">
+        <v>90.5</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="7">
+        <v>301000</v>
+      </c>
+      <c r="G33" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H33" s="7">
+        <v>3</v>
+      </c>
+      <c r="I33" s="7">
+        <v>10500</v>
+      </c>
+      <c r="J33" s="5">
+        <v>61.4</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="7">
+        <v>251000</v>
+      </c>
+      <c r="G34" s="7">
+        <v>23000</v>
+      </c>
+      <c r="H34" s="7">
+        <v>3</v>
+      </c>
+      <c r="I34" s="7">
+        <v>23500</v>
+      </c>
+      <c r="J34" s="5">
+        <v>61.4</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="7">
+        <v>183000</v>
+      </c>
+      <c r="G35" s="7">
+        <v>14000</v>
+      </c>
+      <c r="H35" s="7">
+        <v>3</v>
+      </c>
+      <c r="I35" s="7">
+        <v>12500</v>
+      </c>
+      <c r="J35" s="5">
+        <v>61.4</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="7">
+        <v>154000</v>
+      </c>
+      <c r="G36" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H36" s="7">
+        <v>3</v>
+      </c>
+      <c r="I36" s="7">
+        <v>13000</v>
+      </c>
+      <c r="J36" s="5">
+        <v>61.4</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5">
+        <v>79.3</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="7">
+        <v>589000</v>
+      </c>
+      <c r="G37" s="7">
+        <v>26000</v>
+      </c>
+      <c r="H37" s="7">
+        <v>3</v>
+      </c>
+      <c r="I37" s="7">
+        <v>34000</v>
+      </c>
+      <c r="J37" s="5">
+        <v>61.1</v>
+      </c>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5">
+        <v>89.8</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="7">
+        <v>304000</v>
+      </c>
+      <c r="G38" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H38" s="7">
+        <v>3</v>
+      </c>
+      <c r="I38" s="7">
+        <v>10500</v>
+      </c>
+      <c r="J38" s="5">
+        <v>61</v>
+      </c>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5">
+        <v>89.3</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="7">
+        <v>283000</v>
+      </c>
+      <c r="G39" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H39" s="7">
+        <v>3</v>
+      </c>
+      <c r="I39" s="7">
+        <v>11000</v>
+      </c>
+      <c r="J39" s="5">
+        <v>60.9</v>
+      </c>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="7">
+        <v>324000</v>
+      </c>
+      <c r="G40" s="7">
+        <v>30000</v>
+      </c>
+      <c r="H40" s="7">
+        <v>3</v>
+      </c>
+      <c r="I40" s="7">
+        <v>23000</v>
+      </c>
+      <c r="J40" s="5">
+        <v>60.7</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5">
+        <v>89.5</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="7">
+        <v>110000</v>
+      </c>
+      <c r="G41" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H41" s="7">
+        <v>3</v>
+      </c>
+      <c r="I41" s="7">
+        <v>8500</v>
+      </c>
+      <c r="J41" s="5">
+        <v>60.4</v>
+      </c>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="7">
+        <v>136000</v>
+      </c>
+      <c r="G42" s="7">
+        <v>6000</v>
+      </c>
+      <c r="H42" s="7">
+        <v>3</v>
+      </c>
+      <c r="I42" s="7">
+        <v>8500</v>
+      </c>
+      <c r="J42" s="5">
+        <v>60.3</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5">
+        <v>82.7</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="7">
+        <v>442000</v>
+      </c>
+      <c r="G43" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H43" s="7">
+        <v>3</v>
+      </c>
+      <c r="I43" s="7">
+        <v>22500</v>
+      </c>
+      <c r="J43" s="5">
+        <v>60.1</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5">
+        <v>87.2</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="7">
+        <v>228000</v>
+      </c>
+      <c r="G44" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H44" s="7">
+        <v>3</v>
+      </c>
+      <c r="I44" s="7">
+        <v>12000</v>
+      </c>
+      <c r="J44" s="5">
+        <v>60</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5">
+        <v>86.8</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="7">
+        <v>104000</v>
+      </c>
+      <c r="G45" s="7">
+        <v>14000</v>
+      </c>
+      <c r="H45" s="7">
+        <v>3</v>
+      </c>
+      <c r="I45" s="7">
+        <v>11500</v>
+      </c>
+      <c r="J45" s="5">
+        <v>59.6</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="4"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="7">
+        <v>1295000</v>
+      </c>
+      <c r="G46" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H46" s="7">
+        <v>3</v>
+      </c>
+      <c r="I46" s="7">
+        <v>24500</v>
+      </c>
+      <c r="J46" s="5">
+        <v>59.5</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="7">
+        <v>1197000</v>
+      </c>
+      <c r="G47" s="7">
+        <v>22000</v>
+      </c>
+      <c r="H47" s="7">
+        <v>3</v>
+      </c>
+      <c r="I47" s="7">
+        <v>24500</v>
+      </c>
+      <c r="J47" s="5">
+        <v>59.5</v>
+      </c>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="7">
+        <v>251000</v>
+      </c>
+      <c r="G48" s="7">
+        <v>24000</v>
+      </c>
+      <c r="H48" s="7">
+        <v>3</v>
+      </c>
+      <c r="I48" s="7">
+        <v>25000</v>
+      </c>
+      <c r="J48" s="5">
+        <v>59.3</v>
+      </c>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5">
+        <v>87.2</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="7">
+        <v>213000</v>
+      </c>
+      <c r="G49" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H49" s="7">
+        <v>3</v>
+      </c>
+      <c r="I49" s="7">
+        <v>9500</v>
+      </c>
+      <c r="J49" s="5">
+        <v>59.3</v>
+      </c>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="4"/>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="7">
+        <v>336000</v>
+      </c>
+      <c r="G50" s="7">
+        <v>21000</v>
+      </c>
+      <c r="H50" s="7">
+        <v>3</v>
+      </c>
+      <c r="I50" s="7">
+        <v>19000</v>
+      </c>
+      <c r="J50" s="5">
+        <v>59.2</v>
+      </c>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="4"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="7">
+        <v>282000</v>
+      </c>
+      <c r="G51" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H51" s="7">
+        <v>3</v>
+      </c>
+      <c r="I51" s="7">
+        <v>16000</v>
+      </c>
+      <c r="J51" s="5">
+        <v>59</v>
+      </c>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="4"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5">
+        <v>86.3</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="7">
+        <v>151000</v>
+      </c>
+      <c r="G52" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H52" s="7">
+        <v>3</v>
+      </c>
+      <c r="I52" s="7">
+        <v>9500</v>
+      </c>
+      <c r="J52" s="5">
+        <v>58.8</v>
+      </c>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="4"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="7">
+        <v>1411000</v>
+      </c>
+      <c r="G53" s="7">
+        <v>26000</v>
+      </c>
+      <c r="H53" s="7">
+        <v>3</v>
+      </c>
+      <c r="I53" s="7">
+        <v>17000</v>
+      </c>
+      <c r="J53" s="5">
+        <v>58.7</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="4"/>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5">
+        <v>81.2</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="7">
+        <v>279000</v>
+      </c>
+      <c r="G54" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H54" s="7">
+        <v>3</v>
+      </c>
+      <c r="I54" s="7">
+        <v>19500</v>
+      </c>
+      <c r="J54" s="5">
+        <v>58.5</v>
+      </c>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O5"/>
+  <autoFilter ref="A4:O54"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1"/>
+    <hyperlink ref="E6" r:id="rId2"/>
+    <hyperlink ref="E7" r:id="rId3"/>
+    <hyperlink ref="E8" r:id="rId4"/>
+    <hyperlink ref="E9" r:id="rId5"/>
+    <hyperlink ref="E10" r:id="rId6"/>
+    <hyperlink ref="E11" r:id="rId7"/>
+    <hyperlink ref="E12" r:id="rId8"/>
+    <hyperlink ref="E13" r:id="rId9"/>
+    <hyperlink ref="E14" r:id="rId10"/>
+    <hyperlink ref="E15" r:id="rId11"/>
+    <hyperlink ref="E16" r:id="rId12"/>
+    <hyperlink ref="E17" r:id="rId13"/>
+    <hyperlink ref="E18" r:id="rId14"/>
+    <hyperlink ref="E19" r:id="rId15"/>
+    <hyperlink ref="E20" r:id="rId16"/>
+    <hyperlink ref="E21" r:id="rId17"/>
+    <hyperlink ref="E22" r:id="rId18"/>
+    <hyperlink ref="E23" r:id="rId19"/>
+    <hyperlink ref="E24" r:id="rId20"/>
+    <hyperlink ref="E25" r:id="rId21"/>
+    <hyperlink ref="E26" r:id="rId22"/>
+    <hyperlink ref="E27" r:id="rId23"/>
+    <hyperlink ref="E28" r:id="rId24"/>
+    <hyperlink ref="E29" r:id="rId25"/>
+    <hyperlink ref="E30" r:id="rId26"/>
+    <hyperlink ref="E31" r:id="rId27"/>
+    <hyperlink ref="E32" r:id="rId28"/>
+    <hyperlink ref="E33" r:id="rId29"/>
+    <hyperlink ref="E34" r:id="rId30"/>
+    <hyperlink ref="E35" r:id="rId31"/>
+    <hyperlink ref="E36" r:id="rId32"/>
+    <hyperlink ref="E37" r:id="rId33"/>
+    <hyperlink ref="E38" r:id="rId34"/>
+    <hyperlink ref="E39" r:id="rId35"/>
+    <hyperlink ref="E40" r:id="rId36"/>
+    <hyperlink ref="E41" r:id="rId37"/>
+    <hyperlink ref="E42" r:id="rId38"/>
+    <hyperlink ref="E43" r:id="rId39"/>
+    <hyperlink ref="E44" r:id="rId40"/>
+    <hyperlink ref="E45" r:id="rId41"/>
+    <hyperlink ref="E46" r:id="rId42"/>
+    <hyperlink ref="E47" r:id="rId43"/>
+    <hyperlink ref="E48" r:id="rId44"/>
+    <hyperlink ref="E49" r:id="rId45"/>
+    <hyperlink ref="E50" r:id="rId46"/>
+    <hyperlink ref="E51" r:id="rId47"/>
+    <hyperlink ref="E52" r:id="rId48"/>
+    <hyperlink ref="E53" r:id="rId49"/>
+    <hyperlink ref="E54" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-16T03:30:26+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-17T03:31:15+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>入学第一天，千金学姐成了我老婆</t>
+  </si>
+  <si>
+    <t>穿成大周宰相，皇后腰疼关我啥事</t>
+  </si>
+  <si>
+    <t>站中间抽两边，什么叫霸之意志呀</t>
+  </si>
+  <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>我的绝世表嫂</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>警告！邪神眷属正在杀入诡异副本</t>
+  </si>
+  <si>
+    <t>每天属性翻一倍，我黑化爆杀一切</t>
+  </si>
+  <si>
+    <t>沉劫</t>
+  </si>
+  <si>
     <t>三十多没娶亲，捡个孕妻还嫌亏</t>
   </si>
   <si>
-    <t>入学第一天，千金学姐成了我老婆</t>
+    <t>领主：从猎人卡开始</t>
+  </si>
+  <si>
+    <t>亮剑：军校毕业，我给老李当参谋</t>
   </si>
   <si>
     <t>我只想砍死各位，或者被各位砍死</t>
   </si>
   <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>别人穿四合院，我为啥上战场</t>
-  </si>
-  <si>
-    <t>亮剑：军校毕业，我给老李当参谋</t>
-  </si>
-  <si>
-    <t>站中间抽两边，什么叫霸之意志呀</t>
-  </si>
-  <si>
-    <t>穿成大周宰相，皇后腰疼关我啥事</t>
-  </si>
-  <si>
-    <t>沉劫</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
+    <t>全员悍匪：你管这叫正经公司？</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
+    <t>大唐：玄武门前夜，我绑父投秦王</t>
+  </si>
+  <si>
+    <t>我在精神病院学斩神</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>我从吃神开始反向晋升</t>
   </si>
   <si>
     <t>人在潮汕，开局连抛十八圣杯</t>
   </si>
   <si>
-    <t>我从吃神开始反向晋升</t>
-  </si>
-  <si>
-    <t>我在精神病院学斩神</t>
+    <t>相亲失败！我把精神小妹捧成天后</t>
   </si>
   <si>
     <t>东北往事：野种的母亲</t>
   </si>
   <si>
-    <t>全员悍匪：你管这叫正经公司？</t>
-  </si>
-  <si>
-    <t>抑郁少女总想自杀？那就恶堕吧！</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>大唐：玄武门前夜，我绑父投秦王</t>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>天幕盘点开国，红色华夏震撼千古</t>
+  </si>
+  <si>
+    <t>五哈：千年家族曝光，误闯天家！</t>
+  </si>
+  <si>
+    <t>长枪绑手电，还说你不是邪修？</t>
+  </si>
+  <si>
+    <t>末世的UN小队</t>
+  </si>
+  <si>
+    <t>凡人修仙，捡个仙子做老婆</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>猪猪侠：什么叫主攻手空手接大？</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>杀人犯？哼！在学校内我才是校霸</t>
+  </si>
+  <si>
+    <t>怪物图鉴：从哥布林血脉开始</t>
+  </si>
+  <si>
+    <t>一战：我成了白毛德皇的治国轮椅</t>
+  </si>
+  <si>
+    <t>全民英雄协会：开局招募一拳光头</t>
+  </si>
+  <si>
+    <t>大秦：我，嬴政！开局面壁穿越者</t>
+  </si>
+  <si>
+    <t>动物城：开局被大先生捡到</t>
+  </si>
+  <si>
+    <t>小区求生：每人每天给我一块面包</t>
+  </si>
+  <si>
+    <t>双胞胎校花是病娇？我养的！</t>
+  </si>
+  <si>
+    <t>转生火影，卡普模版</t>
+  </si>
+  <si>
+    <t>镇国驸马爷</t>
+  </si>
+  <si>
+    <t>开局长生万古，苟到天荒地老</t>
   </si>
   <si>
     <t>奥特：天蝎座第一道光</t>
   </si>
   <si>
-    <t>五哈：千年家族曝光，误闯天家！</t>
-  </si>
-  <si>
-    <t>一战：我成了白毛德皇的治国轮椅</t>
-  </si>
-  <si>
-    <t>大秦：我，嬴政！开局面壁穿越者</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>四合院：我表哥是神棍</t>
-  </si>
-  <si>
-    <t>相亲失败！我把精神小妹捧成天后</t>
-  </si>
-  <si>
-    <t>末世的UN小队</t>
-  </si>
-  <si>
-    <t>动物城：开局被大先生捡到</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>猪猪侠：什么叫主攻手空手接大？</t>
-  </si>
-  <si>
-    <t>长枪绑手电，还说你不是邪修？</t>
-  </si>
-  <si>
-    <t>双胞胎校花是病娇？我养的！</t>
-  </si>
-  <si>
-    <t>天幕盘点开国，红色华夏震撼千古</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>凡人修仙，捡个仙子做老婆</t>
-  </si>
-  <si>
-    <t>江裴拔剑，狼子野心</t>
-  </si>
-  <si>
-    <t>怪物图鉴：从哥布林血脉开始</t>
-  </si>
-  <si>
-    <t>西幻：从鹰人部落到天使帝国</t>
+    <t>远离男主保命！校花后宫倒追我？</t>
+  </si>
+  <si>
+    <t>四合院，开局我选入赘</t>
   </si>
   <si>
     <t>修仙界搞回收，破产仙子请自重</t>
-  </si>
-  <si>
-    <t>全民英雄协会：开局招募一拳光头</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>开局长生万古，苟到天荒地老</t>
-  </si>
-  <si>
-    <t>镇国驸马爷</t>
-  </si>
-  <si>
-    <t>远离男主保命！校花后宫倒追我？</t>
-  </si>
-  <si>
-    <t>小区求生：每人每天给我一块面包</t>
-  </si>
-  <si>
-    <t>农村女婿</t>
-  </si>
-  <si>
-    <t>四合院，开局我选入赘</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>转生火影，卡普模版</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>89.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>3233000</v>
+        <v>3456000</v>
       </c>
       <c r="G5" s="7">
-        <v>211000</v>
+        <v>223000</v>
       </c>
       <c r="H5" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="7">
-        <v>190000</v>
+        <v>201000</v>
       </c>
       <c r="J5" s="5">
-        <v>83.2</v>
+        <v>86.3</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>84.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>474000</v>
+        <v>133000</v>
       </c>
       <c r="G6" s="7">
-        <v>70000</v>
+        <v>24000</v>
       </c>
       <c r="H6" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="7">
-        <v>74500</v>
+        <v>28000</v>
       </c>
       <c r="J6" s="5">
-        <v>73.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>276000</v>
+        <v>298000</v>
       </c>
       <c r="G7" s="7">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="H7" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" s="7">
-        <v>39500</v>
+        <v>33667</v>
       </c>
       <c r="J7" s="5">
-        <v>72.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>386000</v>
+        <v>155000</v>
       </c>
       <c r="G8" s="7">
-        <v>30000</v>
+        <v>21000</v>
       </c>
       <c r="H8" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
-        <v>37500</v>
+        <v>20333</v>
       </c>
       <c r="J8" s="5">
-        <v>71.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>153000</v>
+        <v>238000</v>
       </c>
       <c r="G9" s="7">
-        <v>22000</v>
+        <v>28000</v>
       </c>
       <c r="H9" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7">
-        <v>26000</v>
+        <v>28667</v>
       </c>
       <c r="J9" s="5">
-        <v>70.5</v>
+        <v>72</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>96</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>109000</v>
+        <v>171000</v>
       </c>
       <c r="G10" s="7">
-        <v>26000</v>
+        <v>18000</v>
       </c>
       <c r="H10" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7">
-        <v>30000</v>
+        <v>23333</v>
       </c>
       <c r="J10" s="5">
-        <v>69.3</v>
+        <v>71.7</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>91.2</v>
+        <v>94.2</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>252000</v>
+        <v>150000</v>
       </c>
       <c r="G11" s="7">
-        <v>33000</v>
+        <v>54000</v>
       </c>
       <c r="H11" s="7">
         <v>3</v>
       </c>
       <c r="I11" s="7">
-        <v>39500</v>
+        <v>41000</v>
       </c>
       <c r="J11" s="5">
-        <v>69</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>95.8</v>
+        <v>99.8</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>210000</v>
+        <v>135000</v>
       </c>
       <c r="G12" s="7">
-        <v>28000</v>
+        <v>18000</v>
       </c>
       <c r="H12" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="7">
-        <v>29000</v>
+        <v>17000</v>
       </c>
       <c r="J12" s="5">
-        <v>68.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>99.8</v>
+        <v>82.5</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>134000</v>
+        <v>319000</v>
       </c>
       <c r="G13" s="7">
-        <v>19000</v>
+        <v>58000</v>
       </c>
       <c r="H13" s="7">
         <v>3</v>
       </c>
       <c r="I13" s="7">
-        <v>20000</v>
+        <v>63000</v>
       </c>
       <c r="J13" s="5">
-        <v>68.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>103000</v>
+        <v>342000</v>
       </c>
       <c r="G14" s="7">
-        <v>22000</v>
+        <v>45000</v>
       </c>
       <c r="H14" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="7">
-        <v>21500</v>
+        <v>9000</v>
       </c>
       <c r="J14" s="5">
-        <v>67.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>98.7</v>
+        <v>94.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>117000</v>
+        <v>114000</v>
       </c>
       <c r="G15" s="7">
-        <v>17000</v>
+        <v>11000</v>
       </c>
       <c r="H15" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7">
-        <v>16500</v>
+        <v>18000</v>
       </c>
       <c r="J15" s="5">
-        <v>67.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>93.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>372000</v>
+        <v>500000</v>
       </c>
       <c r="G16" s="7">
-        <v>23000</v>
+        <v>26000</v>
       </c>
       <c r="H16" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7">
-        <v>27000</v>
+        <v>58333</v>
       </c>
       <c r="J16" s="5">
-        <v>67.2</v>
+        <v>68.2</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>80.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>897000</v>
+        <v>135000</v>
       </c>
       <c r="G17" s="7">
-        <v>43000</v>
+        <v>20000</v>
       </c>
       <c r="H17" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="7">
-        <v>50000</v>
+        <v>6000</v>
       </c>
       <c r="J17" s="5">
-        <v>65.8</v>
+        <v>68</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>82.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>2124000</v>
+        <v>276000</v>
       </c>
       <c r="G18" s="7">
-        <v>51000</v>
+        <v>24000</v>
       </c>
       <c r="H18" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="7">
-        <v>38500</v>
+        <v>34333</v>
       </c>
       <c r="J18" s="5">
-        <v>63.9</v>
+        <v>67.8</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>94.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>135000</v>
+        <v>414000</v>
       </c>
       <c r="G19" s="7">
-        <v>13000</v>
+        <v>28000</v>
       </c>
       <c r="H19" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
-        <v>11000</v>
+        <v>34333</v>
       </c>
       <c r="J19" s="5">
-        <v>63.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>94.40000000000001</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>123000</v>
+        <v>135000</v>
       </c>
       <c r="G20" s="7">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="H20" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="7">
-        <v>9500</v>
+        <v>10333</v>
       </c>
       <c r="J20" s="5">
-        <v>63.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>88.8</v>
+        <v>96.8</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>349000</v>
+        <v>105000</v>
       </c>
       <c r="G21" s="7">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="H21" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="7">
-        <v>20500</v>
+        <v>7333</v>
       </c>
       <c r="J21" s="5">
-        <v>63</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>88.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>115000</v>
+        <v>126000</v>
       </c>
       <c r="G22" s="7">
-        <v>20000</v>
+        <v>13000</v>
       </c>
       <c r="H22" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="7">
-        <v>20500</v>
+        <v>10333</v>
       </c>
       <c r="J22" s="5">
-        <v>62.9</v>
+        <v>67</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>93.3</v>
+        <v>81.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>113000</v>
+        <v>2162000</v>
       </c>
       <c r="G23" s="7">
-        <v>10000</v>
+        <v>38000</v>
       </c>
       <c r="H23" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="7">
-        <v>9000</v>
+        <v>38333</v>
       </c>
       <c r="J23" s="5">
-        <v>62.6</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.3</v>
+        <v>90.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>222000</v>
+        <v>130000</v>
       </c>
       <c r="G24" s="7">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="H24" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="7">
-        <v>13000</v>
+        <v>18667</v>
       </c>
       <c r="J24" s="5">
-        <v>62.5</v>
+        <v>66.3</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>170000</v>
+        <v>926000</v>
       </c>
       <c r="G25" s="7">
-        <v>14000</v>
+        <v>29000</v>
       </c>
       <c r="H25" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="7">
-        <v>17000</v>
+        <v>43000</v>
       </c>
       <c r="J25" s="5">
-        <v>62.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1450,30 +1450,28 @@
       <c r="A26" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5">
-        <v>9.6</v>
-      </c>
+      <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>91.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>110000</v>
+        <v>379000</v>
       </c>
       <c r="G26" s="7">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="H26" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26" s="7">
-        <v>11500</v>
+        <v>20333</v>
       </c>
       <c r="J26" s="5">
-        <v>62.4</v>
+        <v>66</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1487,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>82.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>797000</v>
+        <v>241000</v>
       </c>
       <c r="G27" s="7">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="H27" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="7">
-        <v>30500</v>
+        <v>19333</v>
       </c>
       <c r="J27" s="5">
-        <v>62.1</v>
+        <v>65.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1520,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>81.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>633000</v>
+        <v>145000</v>
       </c>
       <c r="G28" s="7">
-        <v>23000</v>
+        <v>10000</v>
       </c>
       <c r="H28" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="7">
-        <v>31500</v>
+        <v>10667</v>
       </c>
       <c r="J28" s="5">
-        <v>61.9</v>
+        <v>65.5</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1553,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90.5</v>
+        <v>83</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>452000</v>
+        <v>663000</v>
       </c>
       <c r="G29" s="7">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="H29" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="7">
-        <v>12500</v>
+        <v>31000</v>
       </c>
       <c r="J29" s="5">
-        <v>61.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1586,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>90.2</v>
+        <v>91.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>261000</v>
+        <v>465000</v>
       </c>
       <c r="G30" s="7">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="H30" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" s="7">
-        <v>13000</v>
+        <v>12667</v>
       </c>
       <c r="J30" s="5">
-        <v>61.9</v>
+        <v>65.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1619,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>86.7</v>
+        <v>91.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>223000</v>
+        <v>317000</v>
       </c>
       <c r="G31" s="7">
-        <v>17000</v>
+        <v>13000</v>
       </c>
       <c r="H31" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="7">
-        <v>20000</v>
+        <v>11333</v>
       </c>
       <c r="J31" s="5">
-        <v>61.7</v>
+        <v>65.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1652,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>92</v>
+        <v>89.3</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>105000</v>
+        <v>185000</v>
       </c>
       <c r="G32" s="7">
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="H32" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="7">
-        <v>8500</v>
+        <v>16333</v>
       </c>
       <c r="J32" s="5">
-        <v>61.7</v>
+        <v>65.2</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1685,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>90.5</v>
+        <v>89.7</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>301000</v>
+        <v>166000</v>
       </c>
       <c r="G33" s="7">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="H33" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="7">
-        <v>10500</v>
+        <v>12667</v>
       </c>
       <c r="J33" s="5">
-        <v>61.4</v>
+        <v>64.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>84.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>251000</v>
+        <v>114000</v>
       </c>
       <c r="G34" s="7">
-        <v>23000</v>
+        <v>9000</v>
       </c>
       <c r="H34" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="7">
-        <v>23500</v>
+        <v>8667</v>
       </c>
       <c r="J34" s="5">
-        <v>61.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>89.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>183000</v>
+        <v>355000</v>
       </c>
       <c r="G35" s="7">
-        <v>14000</v>
+        <v>31000</v>
       </c>
       <c r="H35" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="7">
-        <v>12500</v>
+        <v>25667</v>
       </c>
       <c r="J35" s="5">
-        <v>61.4</v>
+        <v>64.2</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>89.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>154000</v>
+        <v>293000</v>
       </c>
       <c r="G36" s="7">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="H36" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="7">
-        <v>13000</v>
+        <v>10667</v>
       </c>
       <c r="J36" s="5">
-        <v>61.4</v>
+        <v>64.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>79.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>589000</v>
+        <v>194000</v>
       </c>
       <c r="G37" s="7">
-        <v>26000</v>
+        <v>11000</v>
       </c>
       <c r="H37" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="7">
-        <v>34000</v>
+        <v>12000</v>
       </c>
       <c r="J37" s="5">
-        <v>61.1</v>
+        <v>64</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>89.8</v>
+        <v>83.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>304000</v>
+        <v>1446000</v>
       </c>
       <c r="G38" s="7">
-        <v>7000</v>
+        <v>35000</v>
       </c>
       <c r="H38" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38" s="7">
-        <v>10500</v>
+        <v>23000</v>
       </c>
       <c r="J38" s="5">
-        <v>61</v>
+        <v>63.6</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>89.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>283000</v>
+        <v>273000</v>
       </c>
       <c r="G39" s="7">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="H39" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" s="7">
-        <v>11000</v>
+        <v>23000</v>
       </c>
       <c r="J39" s="5">
-        <v>60.9</v>
+        <v>63.6</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>83.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>324000</v>
+        <v>229000</v>
       </c>
       <c r="G40" s="7">
-        <v>30000</v>
+        <v>19000</v>
       </c>
       <c r="H40" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>23000</v>
+        <v>3000</v>
       </c>
       <c r="J40" s="5">
-        <v>60.7</v>
+        <v>63.6</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>89.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>110000</v>
+        <v>143000</v>
       </c>
       <c r="G41" s="7">
         <v>7000</v>
       </c>
       <c r="H41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="7">
-        <v>8500</v>
+        <v>8000</v>
       </c>
       <c r="J41" s="5">
-        <v>60.4</v>
+        <v>63.6</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,28 +1978,30 @@
       <c r="A42" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="5"/>
+      <c r="B42" s="5">
+        <v>9.6</v>
+      </c>
       <c r="C42" s="5">
-        <v>89.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>136000</v>
+        <v>118000</v>
       </c>
       <c r="G42" s="7">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="H42" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="7">
-        <v>8500</v>
+        <v>10333</v>
       </c>
       <c r="J42" s="5">
-        <v>60.3</v>
+        <v>63.3</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>82.7</v>
+        <v>87.8</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>442000</v>
+        <v>117000</v>
       </c>
       <c r="G43" s="7">
-        <v>19000</v>
+        <v>13000</v>
       </c>
       <c r="H43" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="7">
-        <v>22500</v>
+        <v>12000</v>
       </c>
       <c r="J43" s="5">
-        <v>60.1</v>
+        <v>63.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>87.2</v>
+        <v>81.3</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>228000</v>
+        <v>811000</v>
       </c>
       <c r="G44" s="7">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="H44" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="J44" s="5">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>86.8</v>
+        <v>88.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>104000</v>
+        <v>305000</v>
       </c>
       <c r="G45" s="7">
-        <v>14000</v>
+        <v>4000</v>
       </c>
       <c r="H45" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>11500</v>
+        <v>8333</v>
       </c>
       <c r="J45" s="5">
-        <v>59.6</v>
+        <v>62.9</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>80.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>1295000</v>
+        <v>358000</v>
       </c>
       <c r="G46" s="7">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="H46" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
-        <v>24500</v>
+        <v>20000</v>
       </c>
       <c r="J46" s="5">
-        <v>59.5</v>
+        <v>62.5</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>80.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>1197000</v>
+        <v>609000</v>
       </c>
       <c r="G47" s="7">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="H47" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="7">
-        <v>24500</v>
+        <v>29333</v>
       </c>
       <c r="J47" s="5">
-        <v>59.5</v>
+        <v>62.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>80.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>251000</v>
+        <v>298000</v>
       </c>
       <c r="G48" s="7">
-        <v>24000</v>
+        <v>19000</v>
       </c>
       <c r="H48" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48" s="7">
-        <v>25000</v>
+        <v>19333</v>
       </c>
       <c r="J48" s="5">
-        <v>59.3</v>
+        <v>62.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>87.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>213000</v>
+        <v>273000</v>
       </c>
       <c r="G49" s="7">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="H49" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I49" s="7">
-        <v>9500</v>
+        <v>24000</v>
       </c>
       <c r="J49" s="5">
-        <v>59.3</v>
+        <v>62.1</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>82.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>336000</v>
+        <v>1217000</v>
       </c>
       <c r="G50" s="7">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="H50" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" s="7">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="J50" s="5">
-        <v>59.2</v>
+        <v>62</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>282000</v>
+        <v>223000</v>
       </c>
       <c r="G51" s="7">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="H51" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I51" s="7">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="J51" s="5">
-        <v>59</v>
+        <v>61.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>86.3</v>
+        <v>85.8</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>151000</v>
+        <v>220000</v>
       </c>
       <c r="G52" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H52" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52" s="7">
-        <v>9500</v>
+        <v>8667</v>
       </c>
       <c r="J52" s="5">
-        <v>58.8</v>
+        <v>61.4</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>82.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>1411000</v>
+        <v>161000</v>
       </c>
       <c r="G53" s="7">
-        <v>26000</v>
+        <v>10000</v>
       </c>
       <c r="H53" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" s="7">
-        <v>17000</v>
+        <v>9667</v>
       </c>
       <c r="J53" s="5">
-        <v>58.7</v>
+        <v>61.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>81.2</v>
+        <v>84.5</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>279000</v>
+        <v>234000</v>
       </c>
       <c r="G54" s="7">
-        <v>17000</v>
+        <v>6000</v>
       </c>
       <c r="H54" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>19500</v>
+        <v>10000</v>
       </c>
       <c r="J54" s="5">
-        <v>58.5</v>
+        <v>61</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-17T03:31:15+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-18T03:15:04+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>别人穿四合院，我为啥上战场</t>
   </si>
   <si>
+    <t>我的绝世表嫂</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
     <t>入学第一天，千金学姐成了我老婆</t>
   </si>
   <si>
+    <t>站中间抽两边，什么叫霸之意志呀</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>警告！邪神眷属正在杀入诡异副本</t>
+  </si>
+  <si>
     <t>穿成大周宰相，皇后腰疼关我啥事</t>
   </si>
   <si>
-    <t>站中间抽两边，什么叫霸之意志呀</t>
-  </si>
-  <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>我的绝世表嫂</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>警告！邪神眷属正在杀入诡异副本</t>
+    <t>只想躺平开民宿，咋就活成顶流了</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>大唐：玄武门前夜，我绑父投秦王</t>
   </si>
   <si>
     <t>每天属性翻一倍，我黑化爆杀一切</t>
   </si>
   <si>
-    <t>沉劫</t>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
+    <t>列车求生，我能升华一切！</t>
+  </si>
+  <si>
+    <t>美恐：我，人间真神</t>
+  </si>
+  <si>
+    <t>全员悍匪：你管这叫正经公司？</t>
+  </si>
+  <si>
+    <t>凡人修仙，捡个仙子做老婆</t>
+  </si>
+  <si>
+    <t>天幕盘点开国，红色华夏震撼千古</t>
+  </si>
+  <si>
+    <t>青梅是性转祖国人？可我是大超</t>
+  </si>
+  <si>
+    <t>我在精神病院学斩神</t>
+  </si>
+  <si>
+    <t>王者：你的天赋很好现在我也有了</t>
+  </si>
+  <si>
+    <t>镇国驸马爷</t>
+  </si>
+  <si>
+    <t>相亲失败！我把精神小妹捧成天后</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>我，亿万天赋，天才不过见我门槛</t>
+  </si>
+  <si>
+    <t>转生火影，卡普模版</t>
+  </si>
+  <si>
+    <t>修仙界搞回收，破产仙子请自重</t>
+  </si>
+  <si>
+    <t>东北往事：野种的母亲</t>
+  </si>
+  <si>
+    <t>四合院：穿成傻柱发小，一脚踹翻</t>
   </si>
   <si>
     <t>三十多没娶亲，捡个孕妻还嫌亏</t>
   </si>
   <si>
+    <t>怪物图鉴：从哥布林血脉开始</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>远离男主保命！校花后宫倒追我？</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>亮剑：军校毕业，我给老李当参谋</t>
+  </si>
+  <si>
+    <t>两界倒爷：从1988到2025</t>
+  </si>
+  <si>
+    <t>四合院，开局我选入赘</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>一战：我成了白毛德皇的治国轮椅</t>
+  </si>
+  <si>
+    <t>大秦：我，嬴政！开局面壁穿越者</t>
+  </si>
+  <si>
+    <t>我根骨平庸，但分身都是绝世天才</t>
+  </si>
+  <si>
+    <t>四合院：我表哥是神棍</t>
+  </si>
+  <si>
+    <t>双胞胎校花是病娇？我养的！</t>
+  </si>
+  <si>
+    <t>小区求生：每人每天给我一块面包</t>
+  </si>
+  <si>
+    <t>赦夜人</t>
+  </si>
+  <si>
     <t>领主：从猎人卡开始</t>
-  </si>
-  <si>
-    <t>亮剑：军校毕业，我给老李当参谋</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>全员悍匪：你管这叫正经公司？</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>大唐：玄武门前夜，我绑父投秦王</t>
-  </si>
-  <si>
-    <t>我在精神病院学斩神</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>我从吃神开始反向晋升</t>
-  </si>
-  <si>
-    <t>人在潮汕，开局连抛十八圣杯</t>
-  </si>
-  <si>
-    <t>相亲失败！我把精神小妹捧成天后</t>
-  </si>
-  <si>
-    <t>东北往事：野种的母亲</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>天幕盘点开国，红色华夏震撼千古</t>
-  </si>
-  <si>
-    <t>五哈：千年家族曝光，误闯天家！</t>
-  </si>
-  <si>
-    <t>长枪绑手电，还说你不是邪修？</t>
-  </si>
-  <si>
-    <t>末世的UN小队</t>
-  </si>
-  <si>
-    <t>凡人修仙，捡个仙子做老婆</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>猪猪侠：什么叫主攻手空手接大？</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>杀人犯？哼！在学校内我才是校霸</t>
-  </si>
-  <si>
-    <t>怪物图鉴：从哥布林血脉开始</t>
-  </si>
-  <si>
-    <t>一战：我成了白毛德皇的治国轮椅</t>
-  </si>
-  <si>
-    <t>全民英雄协会：开局招募一拳光头</t>
-  </si>
-  <si>
-    <t>大秦：我，嬴政！开局面壁穿越者</t>
-  </si>
-  <si>
-    <t>动物城：开局被大先生捡到</t>
-  </si>
-  <si>
-    <t>小区求生：每人每天给我一块面包</t>
-  </si>
-  <si>
-    <t>双胞胎校花是病娇？我养的！</t>
-  </si>
-  <si>
-    <t>转生火影，卡普模版</t>
-  </si>
-  <si>
-    <t>镇国驸马爷</t>
-  </si>
-  <si>
-    <t>开局长生万古，苟到天荒地老</t>
-  </si>
-  <si>
-    <t>奥特：天蝎座第一道光</t>
-  </si>
-  <si>
-    <t>远离男主保命！校花后宫倒追我？</t>
-  </si>
-  <si>
-    <t>四合院，开局我选入赘</t>
-  </si>
-  <si>
-    <t>修仙界搞回收，破产仙子请自重</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>89.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>3456000</v>
+        <v>3515000</v>
       </c>
       <c r="G5" s="7">
-        <v>223000</v>
+        <v>59000</v>
       </c>
       <c r="H5" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="7">
-        <v>201000</v>
+        <v>165500</v>
       </c>
       <c r="J5" s="5">
-        <v>86.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>133000</v>
+        <v>172000</v>
       </c>
       <c r="G6" s="7">
-        <v>24000</v>
+        <v>39000</v>
       </c>
       <c r="H6" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="7">
-        <v>28000</v>
+        <v>30750</v>
       </c>
       <c r="J6" s="5">
-        <v>73</v>
+        <v>77.7</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>95.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>298000</v>
+        <v>212000</v>
       </c>
       <c r="G7" s="7">
-        <v>22000</v>
+        <v>62000</v>
       </c>
       <c r="H7" s="7">
         <v>4</v>
       </c>
       <c r="I7" s="7">
-        <v>33667</v>
+        <v>48000</v>
       </c>
       <c r="J7" s="5">
-        <v>72.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>155000</v>
+        <v>137000</v>
       </c>
       <c r="G8" s="7">
-        <v>21000</v>
+        <v>44000</v>
       </c>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7">
-        <v>20333</v>
+        <v>21250</v>
       </c>
       <c r="J8" s="5">
-        <v>72.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>238000</v>
+        <v>158000</v>
       </c>
       <c r="G9" s="7">
-        <v>28000</v>
+        <v>23000</v>
       </c>
       <c r="H9" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="7">
-        <v>28667</v>
+        <v>18500</v>
       </c>
       <c r="J9" s="5">
-        <v>72</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>97.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>171000</v>
+        <v>173000</v>
       </c>
       <c r="G10" s="7">
-        <v>18000</v>
+        <v>43000</v>
       </c>
       <c r="H10" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
-        <v>23333</v>
+        <v>24750</v>
       </c>
       <c r="J10" s="5">
-        <v>71.7</v>
+        <v>74.5</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -964,19 +964,19 @@
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>150000</v>
+        <v>318000</v>
       </c>
       <c r="G11" s="7">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="H11" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
-        <v>41000</v>
+        <v>30250</v>
       </c>
       <c r="J11" s="5">
-        <v>71.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>99.8</v>
+        <v>93.8</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>135000</v>
+        <v>262000</v>
       </c>
       <c r="G12" s="7">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="H12" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>17000</v>
+        <v>27500</v>
       </c>
       <c r="J12" s="5">
-        <v>71.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>82.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>319000</v>
+        <v>460000</v>
       </c>
       <c r="G13" s="7">
-        <v>58000</v>
+        <v>46000</v>
       </c>
       <c r="H13" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I13" s="7">
-        <v>63000</v>
+        <v>37250</v>
       </c>
       <c r="J13" s="5">
-        <v>70.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>342000</v>
+        <v>185000</v>
       </c>
       <c r="G14" s="7">
-        <v>45000</v>
+        <v>14000</v>
       </c>
       <c r="H14" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="7">
-        <v>9000</v>
+        <v>21000</v>
       </c>
       <c r="J14" s="5">
-        <v>69.2</v>
+        <v>72.2</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.3</v>
+        <v>84</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>114000</v>
+        <v>360000</v>
       </c>
       <c r="G15" s="7">
-        <v>11000</v>
+        <v>41000</v>
       </c>
       <c r="H15" s="7">
         <v>4</v>
       </c>
       <c r="I15" s="7">
-        <v>18000</v>
+        <v>55667</v>
       </c>
       <c r="J15" s="5">
-        <v>68.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>75.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>500000</v>
+        <v>169000</v>
       </c>
       <c r="G16" s="7">
-        <v>26000</v>
+        <v>14000</v>
       </c>
       <c r="H16" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="7">
-        <v>58333</v>
+        <v>18750</v>
       </c>
       <c r="J16" s="5">
-        <v>68.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>135000</v>
+        <v>326000</v>
       </c>
       <c r="G17" s="7">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="H17" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="J17" s="5">
-        <v>68</v>
+        <v>71.3</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>276000</v>
+        <v>711000</v>
       </c>
       <c r="G18" s="7">
-        <v>24000</v>
+        <v>48000</v>
       </c>
       <c r="H18" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="7">
-        <v>34333</v>
+        <v>35250</v>
       </c>
       <c r="J18" s="5">
-        <v>67.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>84.5</v>
+        <v>96</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>414000</v>
+        <v>141000</v>
       </c>
       <c r="G19" s="7">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>34333</v>
+        <v>11500</v>
       </c>
       <c r="J19" s="5">
-        <v>67.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>95.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>135000</v>
+        <v>369000</v>
       </c>
       <c r="G20" s="7">
-        <v>12000</v>
+        <v>27000</v>
       </c>
       <c r="H20" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>10333</v>
+        <v>13500</v>
       </c>
       <c r="J20" s="5">
-        <v>67.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>96.8</v>
+        <v>96.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>105000</v>
+        <v>119000</v>
       </c>
       <c r="G21" s="7">
-        <v>20000</v>
+        <v>14000</v>
       </c>
       <c r="H21" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="7">
-        <v>7333</v>
+        <v>9000</v>
       </c>
       <c r="J21" s="5">
-        <v>67.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>95.3</v>
+        <v>90.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>126000</v>
+        <v>305000</v>
       </c>
       <c r="G22" s="7">
-        <v>13000</v>
+        <v>74000</v>
       </c>
       <c r="H22" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="7">
-        <v>10333</v>
+        <v>20500</v>
       </c>
       <c r="J22" s="5">
-        <v>67</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>81.8</v>
+        <v>94.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>2162000</v>
+        <v>110000</v>
       </c>
       <c r="G23" s="7">
-        <v>38000</v>
+        <v>11000</v>
       </c>
       <c r="H23" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="7">
-        <v>38333</v>
+        <v>11750</v>
       </c>
       <c r="J23" s="5">
-        <v>66.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>90.3</v>
+        <v>94.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>130000</v>
+        <v>147000</v>
       </c>
       <c r="G24" s="7">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="H24" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="7">
-        <v>18667</v>
+        <v>10750</v>
       </c>
       <c r="J24" s="5">
-        <v>66.3</v>
+        <v>69.8</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>78.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>926000</v>
+        <v>393000</v>
       </c>
       <c r="G25" s="7">
-        <v>29000</v>
+        <v>38000</v>
       </c>
       <c r="H25" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>43000</v>
+        <v>28750</v>
       </c>
       <c r="J25" s="5">
-        <v>66.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>88.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>379000</v>
+        <v>334000</v>
       </c>
       <c r="G26" s="7">
-        <v>7000</v>
+        <v>17000</v>
       </c>
       <c r="H26" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" s="7">
-        <v>20333</v>
+        <v>12750</v>
       </c>
       <c r="J26" s="5">
-        <v>66</v>
+        <v>69.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>89.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>241000</v>
+        <v>163000</v>
       </c>
       <c r="G27" s="7">
-        <v>18000</v>
+        <v>36000</v>
       </c>
       <c r="H27" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" s="7">
-        <v>19333</v>
+        <v>30500</v>
       </c>
       <c r="J27" s="5">
-        <v>65.8</v>
+        <v>69</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>92.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>145000</v>
+        <v>2192000</v>
       </c>
       <c r="G28" s="7">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="H28" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" s="7">
-        <v>10667</v>
+        <v>36250</v>
       </c>
       <c r="J28" s="5">
-        <v>65.5</v>
+        <v>68.8</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>83</v>
+        <v>93.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>663000</v>
+        <v>107000</v>
       </c>
       <c r="G29" s="7">
-        <v>30000</v>
+        <v>8000</v>
       </c>
       <c r="H29" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" s="7">
-        <v>31000</v>
+        <v>7500</v>
       </c>
       <c r="J29" s="5">
-        <v>65.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>91.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>465000</v>
+        <v>304000</v>
       </c>
       <c r="G30" s="7">
-        <v>13000</v>
+        <v>31000</v>
       </c>
       <c r="H30" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>12667</v>
+        <v>25750</v>
       </c>
       <c r="J30" s="5">
-        <v>65.3</v>
+        <v>68</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>91.8</v>
+        <v>87.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>317000</v>
+        <v>255000</v>
       </c>
       <c r="G31" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H31" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="7">
-        <v>11333</v>
+        <v>18000</v>
       </c>
       <c r="J31" s="5">
-        <v>65.3</v>
+        <v>67.8</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>89.3</v>
+        <v>90.3</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>185000</v>
+        <v>474000</v>
       </c>
       <c r="G32" s="7">
-        <v>15000</v>
+        <v>9000</v>
       </c>
       <c r="H32" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>16333</v>
+        <v>11750</v>
       </c>
       <c r="J32" s="5">
-        <v>65.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>89.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>166000</v>
+        <v>480000</v>
       </c>
       <c r="G33" s="7">
-        <v>12000</v>
+        <v>77000</v>
       </c>
       <c r="H33" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>12667</v>
+        <v>32000</v>
       </c>
       <c r="J33" s="5">
-        <v>64.5</v>
+        <v>67.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>91.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>114000</v>
+        <v>327000</v>
       </c>
       <c r="G34" s="7">
-        <v>9000</v>
+        <v>29000</v>
       </c>
       <c r="H34" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="7">
-        <v>8667</v>
+        <v>21750</v>
       </c>
       <c r="J34" s="5">
-        <v>64.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>83.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>355000</v>
+        <v>251000</v>
       </c>
       <c r="G35" s="7">
-        <v>31000</v>
+        <v>17000</v>
       </c>
       <c r="H35" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" s="7">
-        <v>25667</v>
+        <v>11750</v>
       </c>
       <c r="J35" s="5">
-        <v>64.2</v>
+        <v>67.5</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>293000</v>
+        <v>154000</v>
       </c>
       <c r="G36" s="7">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="H36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>10667</v>
+        <v>10250</v>
       </c>
       <c r="J36" s="5">
-        <v>64.2</v>
+        <v>67.3</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>194000</v>
+        <v>145000</v>
       </c>
       <c r="G37" s="7">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="H37" s="7">
         <v>4</v>
       </c>
       <c r="I37" s="7">
-        <v>12000</v>
+        <v>15333</v>
       </c>
       <c r="J37" s="5">
-        <v>64</v>
+        <v>66.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>83.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>1446000</v>
+        <v>511000</v>
       </c>
       <c r="G38" s="7">
-        <v>35000</v>
+        <v>11000</v>
       </c>
       <c r="H38" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I38" s="7">
-        <v>23000</v>
+        <v>46500</v>
       </c>
       <c r="J38" s="5">
-        <v>63.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>83.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>273000</v>
+        <v>150000</v>
       </c>
       <c r="G39" s="7">
-        <v>22000</v>
+        <v>7000</v>
       </c>
       <c r="H39" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I39" s="7">
-        <v>23000</v>
+        <v>7750</v>
       </c>
       <c r="J39" s="5">
-        <v>63.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>92.5</v>
+        <v>82.5</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>229000</v>
+        <v>1470000</v>
       </c>
       <c r="G40" s="7">
-        <v>19000</v>
+        <v>24000</v>
       </c>
       <c r="H40" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I40" s="7">
-        <v>3000</v>
+        <v>23250</v>
       </c>
       <c r="J40" s="5">
-        <v>63.6</v>
+        <v>66.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>90.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>143000</v>
+        <v>233000</v>
       </c>
       <c r="G41" s="7">
-        <v>7000</v>
+        <v>13000</v>
       </c>
       <c r="H41" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>8000</v>
+        <v>9750</v>
       </c>
       <c r="J41" s="5">
-        <v>63.6</v>
+        <v>66.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1978,30 +1978,28 @@
       <c r="A42" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="5">
-        <v>9.6</v>
-      </c>
+      <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>118000</v>
+        <v>299000</v>
       </c>
       <c r="G42" s="7">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="H42" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I42" s="7">
-        <v>10333</v>
+        <v>9500</v>
       </c>
       <c r="J42" s="5">
-        <v>63.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>87.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>117000</v>
+        <v>286000</v>
       </c>
       <c r="G43" s="7">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="H43" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43" s="7">
-        <v>12000</v>
+        <v>28250</v>
       </c>
       <c r="J43" s="5">
-        <v>63.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>81.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>811000</v>
+        <v>285000</v>
       </c>
       <c r="G44" s="7">
-        <v>14000</v>
+        <v>32000</v>
       </c>
       <c r="H44" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7">
-        <v>25000</v>
+        <v>17000</v>
       </c>
       <c r="J44" s="5">
-        <v>63</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>88.8</v>
+        <v>88</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>305000</v>
+        <v>172000</v>
       </c>
       <c r="G45" s="7">
-        <v>4000</v>
+        <v>11000</v>
       </c>
       <c r="H45" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
-        <v>8333</v>
+        <v>10000</v>
       </c>
       <c r="J45" s="5">
-        <v>62.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>82.7</v>
+        <v>88.7</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>358000</v>
+        <v>229000</v>
       </c>
       <c r="G46" s="7">
-        <v>22000</v>
+        <v>6000</v>
       </c>
       <c r="H46" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>20000</v>
+        <v>8250</v>
       </c>
       <c r="J46" s="5">
-        <v>62.5</v>
+        <v>65.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,28 +2143,30 @@
       <c r="A47" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="5"/>
+      <c r="B47" s="5">
+        <v>9.6</v>
+      </c>
       <c r="C47" s="5">
-        <v>78.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>609000</v>
+        <v>125000</v>
       </c>
       <c r="G47" s="7">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="H47" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="7">
-        <v>29333</v>
+        <v>9500</v>
       </c>
       <c r="J47" s="5">
-        <v>62.3</v>
+        <v>65.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>82.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>298000</v>
+        <v>827000</v>
       </c>
       <c r="G48" s="7">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H48" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
-        <v>19333</v>
+        <v>22750</v>
       </c>
       <c r="J48" s="5">
-        <v>62.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>80.09999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>273000</v>
+        <v>281000</v>
       </c>
       <c r="G49" s="7">
-        <v>22000</v>
+        <v>11000</v>
       </c>
       <c r="H49" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7">
-        <v>24000</v>
+        <v>5000</v>
       </c>
       <c r="J49" s="5">
-        <v>62.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>80.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>1217000</v>
+        <v>259000</v>
       </c>
       <c r="G50" s="7">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="H50" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7">
-        <v>23000</v>
+        <v>6000</v>
       </c>
       <c r="J50" s="5">
-        <v>62</v>
+        <v>65.2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>223000</v>
+        <v>628000</v>
       </c>
       <c r="G51" s="7">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="H51" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I51" s="7">
-        <v>9000</v>
+        <v>26750</v>
       </c>
       <c r="J51" s="5">
-        <v>61.8</v>
+        <v>65</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>85.8</v>
+        <v>81.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>220000</v>
+        <v>377000</v>
       </c>
       <c r="G52" s="7">
-        <v>7000</v>
+        <v>19000</v>
       </c>
       <c r="H52" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I52" s="7">
-        <v>8667</v>
+        <v>19750</v>
       </c>
       <c r="J52" s="5">
-        <v>61.4</v>
+        <v>64.8</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>85.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>161000</v>
+        <v>516000</v>
       </c>
       <c r="G53" s="7">
-        <v>10000</v>
+        <v>36000</v>
       </c>
       <c r="H53" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>9667</v>
+        <v>29750</v>
       </c>
       <c r="J53" s="5">
-        <v>61.3</v>
+        <v>64.7</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>84.5</v>
+        <v>87.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>234000</v>
+        <v>140000</v>
       </c>
       <c r="G54" s="7">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I54" s="7">
-        <v>10000</v>
+        <v>5750</v>
       </c>
       <c r="J54" s="5">
-        <v>61</v>
+        <v>64.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-18T03:15:04+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-19T03:18:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>我的绝世表嫂</t>
+  </si>
+  <si>
     <t>别人穿四合院，我为啥上战场</t>
   </si>
   <si>
-    <t>我的绝世表嫂</t>
+    <t>猎魔人小姐，我真不是血族</t>
   </si>
   <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>站中间抽两边，什么叫霸之意志呀</t>
+  </si>
+  <si>
+    <t>入学第一天，千金学姐成了我老婆</t>
+  </si>
+  <si>
     <t>我有一个女鬼催眠APP</t>
   </si>
   <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>入学第一天，千金学姐成了我老婆</t>
-  </si>
-  <si>
-    <t>站中间抽两边，什么叫霸之意志呀</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
+    <t>列车求生，我能升华一切！</t>
+  </si>
+  <si>
+    <t>我，亿万天赋，天才不过见我门槛</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>警告！邪神眷属正在杀入诡异副本</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>青梅是性转祖国人？可我是大超</t>
+  </si>
+  <si>
+    <t>美恐：我，人间真神</t>
+  </si>
+  <si>
+    <t>两界倒爷：从1988到2025</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>每天属性翻一倍，我黑化爆杀一切</t>
+  </si>
+  <si>
+    <t>修仙界搞回收，破产仙子请自重</t>
+  </si>
+  <si>
+    <t>大唐：玄武门前夜，我绑父投秦王</t>
+  </si>
+  <si>
+    <t>天幕盘点开国，红色华夏震撼千古</t>
+  </si>
+  <si>
+    <t>镇国驸马爷</t>
+  </si>
+  <si>
+    <t>文臣尽头是武斗？我在朝堂横着走</t>
+  </si>
+  <si>
+    <t>只想躺平开民宿，咋就活成顶流了</t>
+  </si>
+  <si>
+    <t>四合院：穿成傻柱发小，一脚踹翻</t>
   </si>
   <si>
     <t>你管这叫警察？重炮都架租界口了</t>
   </si>
   <si>
-    <t>警告！邪神眷属正在杀入诡异副本</t>
-  </si>
-  <si>
     <t>穿成大周宰相，皇后腰疼关我啥事</t>
   </si>
   <si>
-    <t>只想躺平开民宿，咋就活成顶流了</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>大唐：玄武门前夜，我绑父投秦王</t>
-  </si>
-  <si>
-    <t>每天属性翻一倍，我黑化爆杀一切</t>
+    <t>开局签到常务副皇帝，权倾朝野！</t>
+  </si>
+  <si>
+    <t>一战：我成了白毛德皇的治国轮椅</t>
   </si>
   <si>
     <t>末日灾变序列</t>
   </si>
   <si>
-    <t>列车求生，我能升华一切！</t>
-  </si>
-  <si>
-    <t>美恐：我，人间真神</t>
-  </si>
-  <si>
     <t>全员悍匪：你管这叫正经公司？</t>
   </si>
   <si>
     <t>凡人修仙，捡个仙子做老婆</t>
   </si>
   <si>
-    <t>天幕盘点开国，红色华夏震撼千古</t>
-  </si>
-  <si>
-    <t>青梅是性转祖国人？可我是大超</t>
-  </si>
-  <si>
-    <t>我在精神病院学斩神</t>
+    <t>相亲失败！我把精神小妹捧成天后</t>
+  </si>
+  <si>
+    <t>转生火影，卡普模版</t>
+  </si>
+  <si>
+    <t>东北往事：野种的母亲</t>
+  </si>
+  <si>
+    <t>怪物图鉴：从哥布林血脉开始</t>
+  </si>
+  <si>
+    <t>沉劫</t>
+  </si>
+  <si>
+    <t>四合院，开局我选入赘</t>
   </si>
   <si>
     <t>王者：你的天赋很好现在我也有了</t>
   </si>
   <si>
-    <t>镇国驸马爷</t>
-  </si>
-  <si>
-    <t>相亲失败！我把精神小妹捧成天后</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>我，亿万天赋，天才不过见我门槛</t>
-  </si>
-  <si>
-    <t>转生火影，卡普模版</t>
-  </si>
-  <si>
-    <t>修仙界搞回收，破产仙子请自重</t>
-  </si>
-  <si>
-    <t>东北往事：野种的母亲</t>
-  </si>
-  <si>
-    <t>四合院：穿成傻柱发小，一脚踹翻</t>
+    <t>人在诡异，靠第四天灾登顶至高</t>
   </si>
   <si>
     <t>三十多没娶亲，捡个孕妻还嫌亏</t>
   </si>
   <si>
-    <t>怪物图鉴：从哥布林血脉开始</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
+    <t>同学们都选阐教，我选截教杀疯了</t>
   </si>
   <si>
     <t>远离男主保命！校花后宫倒追我？</t>
   </si>
   <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>亮剑：军校毕业，我给老李当参谋</t>
-  </si>
-  <si>
-    <t>两界倒爷：从1988到2025</t>
-  </si>
-  <si>
-    <t>四合院，开局我选入赘</t>
-  </si>
-  <si>
-    <t>奥特：天蝎座第一道光</t>
-  </si>
-  <si>
-    <t>一战：我成了白毛德皇的治国轮椅</t>
+    <t>对头死后，疯批校花挖我坟求婚！</t>
   </si>
   <si>
     <t>大秦：我，嬴政！开局面壁穿越者</t>
   </si>
   <si>
-    <t>我根骨平庸，但分身都是绝世天才</t>
-  </si>
-  <si>
-    <t>四合院：我表哥是神棍</t>
-  </si>
-  <si>
-    <t>双胞胎校花是病娇？我养的！</t>
+    <t>领主：从猎人卡开始</t>
+  </si>
+  <si>
+    <t>赦夜人</t>
   </si>
   <si>
     <t>小区求生：每人每天给我一块面包</t>
   </si>
   <si>
-    <t>赦夜人</t>
-  </si>
-  <si>
-    <t>领主：从猎人卡开始</t>
+    <t>系统延迟一坤年，我成了全球股东</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>84.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>3515000</v>
+        <v>3548000</v>
       </c>
       <c r="G5" s="7">
-        <v>59000</v>
+        <v>33000</v>
       </c>
       <c r="H5" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>165500</v>
+        <v>139000</v>
       </c>
       <c r="J5" s="5">
-        <v>86.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>172000</v>
+        <v>252000</v>
       </c>
       <c r="G6" s="7">
-        <v>39000</v>
+        <v>40000</v>
       </c>
       <c r="H6" s="7">
         <v>5</v>
       </c>
       <c r="I6" s="7">
-        <v>30750</v>
+        <v>46000</v>
       </c>
       <c r="J6" s="5">
-        <v>77.7</v>
+        <v>81.5</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>212000</v>
+        <v>213000</v>
       </c>
       <c r="G7" s="7">
-        <v>62000</v>
+        <v>41000</v>
       </c>
       <c r="H7" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I7" s="7">
-        <v>48000</v>
+        <v>32800</v>
       </c>
       <c r="J7" s="5">
-        <v>77.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>137000</v>
+        <v>223000</v>
       </c>
       <c r="G8" s="7">
-        <v>44000</v>
+        <v>50000</v>
       </c>
       <c r="H8" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>21250</v>
+        <v>29800</v>
       </c>
       <c r="J8" s="5">
-        <v>74.8</v>
+        <v>80</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -898,19 +898,19 @@
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>158000</v>
+        <v>175000</v>
       </c>
       <c r="G9" s="7">
-        <v>23000</v>
+        <v>38000</v>
       </c>
       <c r="H9" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>18500</v>
+        <v>24600</v>
       </c>
       <c r="J9" s="5">
-        <v>74.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>97</v>
+        <v>91.5</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>173000</v>
+        <v>523000</v>
       </c>
       <c r="G10" s="7">
-        <v>43000</v>
+        <v>63000</v>
       </c>
       <c r="H10" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>24750</v>
+        <v>42400</v>
       </c>
       <c r="J10" s="5">
-        <v>74.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>94.2</v>
+        <v>96.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>318000</v>
+        <v>291000</v>
       </c>
       <c r="G11" s="7">
-        <v>20000</v>
+        <v>29000</v>
       </c>
       <c r="H11" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>30250</v>
+        <v>27800</v>
       </c>
       <c r="J11" s="5">
-        <v>74.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>93.8</v>
+        <v>95.5</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>262000</v>
+        <v>343000</v>
       </c>
       <c r="G12" s="7">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="H12" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="7">
-        <v>27500</v>
+        <v>29200</v>
       </c>
       <c r="J12" s="5">
-        <v>73.5</v>
+        <v>77.8</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>460000</v>
+        <v>180000</v>
       </c>
       <c r="G13" s="7">
-        <v>46000</v>
+        <v>22000</v>
       </c>
       <c r="H13" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>37250</v>
+        <v>19200</v>
       </c>
       <c r="J13" s="5">
-        <v>73</v>
+        <v>77.8</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>94.5</v>
+        <v>91.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>185000</v>
+        <v>374000</v>
       </c>
       <c r="G14" s="7">
-        <v>14000</v>
+        <v>69000</v>
       </c>
       <c r="H14" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>21000</v>
+        <v>30200</v>
       </c>
       <c r="J14" s="5">
-        <v>72.2</v>
+        <v>75.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>84</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>360000</v>
+        <v>558000</v>
       </c>
       <c r="G15" s="7">
-        <v>41000</v>
+        <v>78000</v>
       </c>
       <c r="H15" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>55667</v>
+        <v>41200</v>
       </c>
       <c r="J15" s="5">
-        <v>72.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>94.3</v>
+        <v>85.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>169000</v>
+        <v>760000</v>
       </c>
       <c r="G16" s="7">
-        <v>14000</v>
+        <v>49000</v>
       </c>
       <c r="H16" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>18750</v>
+        <v>38000</v>
       </c>
       <c r="J16" s="5">
-        <v>71.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>96</v>
+        <v>83.3</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>326000</v>
+        <v>400000</v>
       </c>
       <c r="G17" s="7">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="H17" s="7">
         <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>14000</v>
+        <v>51750</v>
       </c>
       <c r="J17" s="5">
-        <v>71.3</v>
+        <v>73.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>85.7</v>
+        <v>94.2</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>711000</v>
+        <v>501000</v>
       </c>
       <c r="G18" s="7">
-        <v>48000</v>
+        <v>27000</v>
       </c>
       <c r="H18" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="7">
-        <v>35250</v>
+        <v>14800</v>
       </c>
       <c r="J18" s="5">
-        <v>70.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>96</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>141000</v>
+        <v>193000</v>
       </c>
       <c r="G19" s="7">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="H19" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
-        <v>11500</v>
+        <v>30333</v>
       </c>
       <c r="J19" s="5">
-        <v>70.7</v>
+        <v>73.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>369000</v>
+        <v>122000</v>
       </c>
       <c r="G20" s="7">
-        <v>27000</v>
+        <v>12000</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>13500</v>
+        <v>11800</v>
       </c>
       <c r="J20" s="5">
-        <v>70.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>96.2</v>
+        <v>89.3</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>119000</v>
+        <v>340000</v>
       </c>
       <c r="G21" s="7">
-        <v>14000</v>
+        <v>55000</v>
       </c>
       <c r="H21" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" s="7">
-        <v>9000</v>
+        <v>24600</v>
       </c>
       <c r="J21" s="5">
-        <v>70.2</v>
+        <v>73.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>90.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>305000</v>
+        <v>248000</v>
       </c>
       <c r="G22" s="7">
-        <v>74000</v>
+        <v>19000</v>
       </c>
       <c r="H22" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I22" s="7">
-        <v>20500</v>
+        <v>10400</v>
       </c>
       <c r="J22" s="5">
-        <v>70.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>94.7</v>
+        <v>92.3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>110000</v>
+        <v>388000</v>
       </c>
       <c r="G23" s="7">
-        <v>11000</v>
+        <v>19000</v>
       </c>
       <c r="H23" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" s="7">
-        <v>11750</v>
+        <v>14600</v>
       </c>
       <c r="J23" s="5">
-        <v>70</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>94.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>147000</v>
+        <v>273000</v>
       </c>
       <c r="G24" s="7">
-        <v>12000</v>
+        <v>22000</v>
       </c>
       <c r="H24" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>10750</v>
+        <v>13800</v>
       </c>
       <c r="J24" s="5">
-        <v>69.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>86.2</v>
+        <v>93.5</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>393000</v>
+        <v>154000</v>
       </c>
       <c r="G25" s="7">
-        <v>38000</v>
+        <v>13000</v>
       </c>
       <c r="H25" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" s="7">
-        <v>28750</v>
+        <v>11800</v>
       </c>
       <c r="J25" s="5">
-        <v>69.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>93</v>
+        <v>92.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>334000</v>
+        <v>350000</v>
       </c>
       <c r="G26" s="7">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="H26" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
-        <v>12750</v>
+        <v>13400</v>
       </c>
       <c r="J26" s="5">
-        <v>69.3</v>
+        <v>72.2</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>95.2</v>
+        <v>86</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>163000</v>
+        <v>337000</v>
       </c>
       <c r="G27" s="7">
-        <v>36000</v>
+        <v>33000</v>
       </c>
       <c r="H27" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>30500</v>
+        <v>27200</v>
       </c>
       <c r="J27" s="5">
-        <v>69</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>81.40000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>2192000</v>
+        <v>112000</v>
       </c>
       <c r="G28" s="7">
-        <v>30000</v>
+        <v>16000</v>
       </c>
       <c r="H28" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" s="7">
-        <v>36250</v>
+        <v>1600</v>
       </c>
       <c r="J28" s="5">
-        <v>68.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>93.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>107000</v>
+        <v>343000</v>
       </c>
       <c r="G29" s="7">
-        <v>8000</v>
+        <v>17000</v>
       </c>
       <c r="H29" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I29" s="7">
-        <v>7500</v>
+        <v>14600</v>
       </c>
       <c r="J29" s="5">
-        <v>68.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>84.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>304000</v>
+        <v>167000</v>
       </c>
       <c r="G30" s="7">
-        <v>31000</v>
+        <v>22000</v>
       </c>
       <c r="H30" s="7">
         <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>25750</v>
+        <v>17000</v>
       </c>
       <c r="J30" s="5">
-        <v>68</v>
+        <v>71.2</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87.8</v>
+        <v>88.3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>255000</v>
+        <v>190000</v>
       </c>
       <c r="G31" s="7">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="H31" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" s="7">
-        <v>18000</v>
+        <v>17800</v>
       </c>
       <c r="J31" s="5">
-        <v>67.8</v>
+        <v>71</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>90.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>474000</v>
+        <v>175000</v>
       </c>
       <c r="G32" s="7">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H32" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>11750</v>
+        <v>16200</v>
       </c>
       <c r="J32" s="5">
-        <v>67.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>80.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>480000</v>
+        <v>103000</v>
       </c>
       <c r="G33" s="7">
-        <v>77000</v>
+        <v>9000</v>
       </c>
       <c r="H33" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>32000</v>
+        <v>8600</v>
       </c>
       <c r="J33" s="5">
-        <v>67.5</v>
+        <v>70.8</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1714,28 +1714,30 @@
       <c r="A34" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="5"/>
+      <c r="B34" s="5">
+        <v>9.6</v>
+      </c>
       <c r="C34" s="5">
-        <v>85.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>327000</v>
+        <v>136000</v>
       </c>
       <c r="G34" s="7">
-        <v>29000</v>
+        <v>11000</v>
       </c>
       <c r="H34" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>21750</v>
+        <v>9800</v>
       </c>
       <c r="J34" s="5">
-        <v>67.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>90.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>251000</v>
+        <v>129000</v>
       </c>
       <c r="G35" s="7">
-        <v>17000</v>
+        <v>10000</v>
       </c>
       <c r="H35" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>11750</v>
+        <v>9200</v>
       </c>
       <c r="J35" s="5">
-        <v>67.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,7 +1784,7 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>90.5</v>
+        <v>90.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
@@ -1792,16 +1794,16 @@
         <v>154000</v>
       </c>
       <c r="G36" s="7">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>10250</v>
+        <v>10000</v>
       </c>
       <c r="J36" s="5">
-        <v>67.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>92.5</v>
+        <v>82.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>145000</v>
+        <v>417000</v>
       </c>
       <c r="G37" s="7">
         <v>24000</v>
       </c>
       <c r="H37" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>15333</v>
+        <v>27800</v>
       </c>
       <c r="J37" s="5">
-        <v>66.7</v>
+        <v>70.3</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>72.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>511000</v>
+        <v>266000</v>
       </c>
       <c r="G38" s="7">
         <v>11000</v>
       </c>
       <c r="H38" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>46500</v>
+        <v>16600</v>
       </c>
       <c r="J38" s="5">
-        <v>66.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>89.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>150000</v>
+        <v>352000</v>
       </c>
       <c r="G39" s="7">
-        <v>7000</v>
+        <v>25000</v>
       </c>
       <c r="H39" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" s="7">
-        <v>7750</v>
+        <v>22400</v>
       </c>
       <c r="J39" s="5">
-        <v>66.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>82.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>1470000</v>
+        <v>162000</v>
       </c>
       <c r="G40" s="7">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="H40" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>23250</v>
+        <v>9800</v>
       </c>
       <c r="J40" s="5">
-        <v>66.2</v>
+        <v>69.7</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>233000</v>
+        <v>157000</v>
       </c>
       <c r="G41" s="7">
-        <v>13000</v>
+        <v>7000</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41" s="7">
-        <v>9750</v>
+        <v>7600</v>
       </c>
       <c r="J41" s="5">
-        <v>66.2</v>
+        <v>69.7</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>88.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>299000</v>
+        <v>122000</v>
       </c>
       <c r="G42" s="7">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H42" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I42" s="7">
-        <v>9500</v>
+        <v>12400</v>
       </c>
       <c r="J42" s="5">
-        <v>66.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>80.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>286000</v>
+        <v>183000</v>
       </c>
       <c r="G43" s="7">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="H43" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I43" s="7">
-        <v>28250</v>
+        <v>10200</v>
       </c>
       <c r="J43" s="5">
-        <v>66.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>84.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>285000</v>
+        <v>112000</v>
       </c>
       <c r="G44" s="7">
-        <v>32000</v>
+        <v>5000</v>
       </c>
       <c r="H44" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>17000</v>
+        <v>7000</v>
       </c>
       <c r="J44" s="5">
-        <v>65.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>172000</v>
+        <v>310000</v>
       </c>
       <c r="G45" s="7">
-        <v>11000</v>
+        <v>23000</v>
       </c>
       <c r="H45" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>10000</v>
+        <v>21200</v>
       </c>
       <c r="J45" s="5">
-        <v>65.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>88.7</v>
+        <v>73.8</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>229000</v>
+        <v>529000</v>
       </c>
       <c r="G46" s="7">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="H46" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I46" s="7">
-        <v>8250</v>
+        <v>40800</v>
       </c>
       <c r="J46" s="5">
-        <v>65.8</v>
+        <v>68.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2143,30 +2145,28 @@
       <c r="A47" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="5">
-        <v>9.6</v>
-      </c>
+      <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>88.09999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>125000</v>
+        <v>304000</v>
       </c>
       <c r="G47" s="7">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="H47" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I47" s="7">
-        <v>9500</v>
+        <v>8600</v>
       </c>
       <c r="J47" s="5">
-        <v>65.8</v>
+        <v>68.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>81.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>827000</v>
+        <v>244000</v>
       </c>
       <c r="G48" s="7">
-        <v>16000</v>
+        <v>11000</v>
       </c>
       <c r="H48" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7">
-        <v>22750</v>
+        <v>10000</v>
       </c>
       <c r="J48" s="5">
-        <v>65.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>89.7</v>
+        <v>98</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>281000</v>
+        <v>185000</v>
       </c>
       <c r="G49" s="7">
-        <v>11000</v>
+        <v>28000</v>
       </c>
       <c r="H49" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I49" s="7">
-        <v>5000</v>
+        <v>22500</v>
       </c>
       <c r="J49" s="5">
-        <v>65.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>88.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>259000</v>
+        <v>845000</v>
       </c>
       <c r="G50" s="7">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="H50" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50" s="7">
-        <v>6000</v>
+        <v>21800</v>
       </c>
       <c r="J50" s="5">
-        <v>65.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>78.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>628000</v>
+        <v>146000</v>
       </c>
       <c r="G51" s="7">
-        <v>19000</v>
+        <v>6000</v>
       </c>
       <c r="H51" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I51" s="7">
-        <v>26750</v>
+        <v>5800</v>
       </c>
       <c r="J51" s="5">
-        <v>65</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>81.5</v>
+        <v>76.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>377000</v>
+        <v>552000</v>
       </c>
       <c r="G52" s="7">
-        <v>19000</v>
+        <v>36000</v>
       </c>
       <c r="H52" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I52" s="7">
-        <v>19750</v>
+        <v>31000</v>
       </c>
       <c r="J52" s="5">
-        <v>64.8</v>
+        <v>67.8</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>76.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>516000</v>
+        <v>397000</v>
       </c>
       <c r="G53" s="7">
-        <v>36000</v>
+        <v>20000</v>
       </c>
       <c r="H53" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53" s="7">
-        <v>29750</v>
+        <v>19800</v>
       </c>
       <c r="J53" s="5">
-        <v>64.7</v>
+        <v>67.8</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>87.8</v>
+        <v>82</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>140000</v>
+        <v>542000</v>
       </c>
       <c r="G54" s="7">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="H54" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I54" s="7">
-        <v>5750</v>
+        <v>18200</v>
       </c>
       <c r="J54" s="5">
-        <v>64.7</v>
+        <v>67.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-19T03:18:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-20T03:16:27+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -88,139 +88,139 @@
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
+    <t>站中间抽两边，什么叫霸之意志呀</t>
+  </si>
+  <si>
     <t>我只想砍死各位，或者被各位砍死</t>
   </si>
   <si>
-    <t>站中间抽两边，什么叫霸之意志呀</t>
+    <t>列车求生，我能升华一切！</t>
+  </si>
+  <si>
+    <t>两界倒爷：从1988到2025</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
   </si>
   <si>
     <t>入学第一天，千金学姐成了我老婆</t>
   </si>
   <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>列车求生，我能升华一切！</t>
-  </si>
-  <si>
     <t>我，亿万天赋，天才不过见我门槛</t>
   </si>
   <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>警告！邪神眷属正在杀入诡异副本</t>
+  </si>
+  <si>
+    <t>我老婆有白月光？她怎么不知道</t>
+  </si>
+  <si>
+    <t>青梅是性转祖国人？可我是大超</t>
+  </si>
+  <si>
+    <t>美恐：我，人间真神</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
     <t>穿越乱世：每天一份拼好饭</t>
   </si>
   <si>
-    <t>警告！邪神眷属正在杀入诡异副本</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>青梅是性转祖国人？可我是大超</t>
-  </si>
-  <si>
-    <t>美恐：我，人间真神</t>
-  </si>
-  <si>
-    <t>两界倒爷：从1988到2025</t>
-  </si>
-  <si>
-    <t>奥特：天蝎座第一道光</t>
+    <t>只想躺平开民宿，咋就活成顶流了</t>
   </si>
   <si>
     <t>每天属性翻一倍，我黑化爆杀一切</t>
   </si>
   <si>
-    <t>修仙界搞回收，破产仙子请自重</t>
+    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+  </si>
+  <si>
+    <t>镇国驸马爷</t>
+  </si>
+  <si>
+    <t>一战：我成了白毛德皇的治国轮椅</t>
+  </si>
+  <si>
+    <t>文臣尽头是武斗？我在朝堂横着走</t>
+  </si>
+  <si>
+    <t>人在潮汕，开局连抛十八圣杯</t>
+  </si>
+  <si>
+    <t>天幕盘点开国，红色华夏震撼千古</t>
+  </si>
+  <si>
+    <t>转生火影，卡普模版</t>
+  </si>
+  <si>
+    <t>全员悍匪：你管这叫正经公司？</t>
+  </si>
+  <si>
+    <t>五哈：千年家族曝光，误闯天家！</t>
+  </si>
+  <si>
+    <t>相亲失败！我把精神小妹捧成天后</t>
   </si>
   <si>
     <t>大唐：玄武门前夜，我绑父投秦王</t>
   </si>
   <si>
-    <t>天幕盘点开国，红色华夏震撼千古</t>
-  </si>
-  <si>
-    <t>镇国驸马爷</t>
-  </si>
-  <si>
-    <t>文臣尽头是武斗？我在朝堂横着走</t>
-  </si>
-  <si>
-    <t>只想躺平开民宿，咋就活成顶流了</t>
-  </si>
-  <si>
-    <t>四合院：穿成傻柱发小，一脚踹翻</t>
+    <t>开局签到常务副皇帝，权倾朝野！</t>
+  </si>
+  <si>
+    <t>猪猪侠：什么叫主攻手空手接大？</t>
+  </si>
+  <si>
+    <t>王者：你的天赋很好现在我也有了</t>
+  </si>
+  <si>
+    <t>远离男主保命！校花后宫倒追我？</t>
+  </si>
+  <si>
+    <t>东北往事：野种的母亲</t>
+  </si>
+  <si>
+    <t>亮剑：军校毕业，我给老李当参谋</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>穿成大周宰相，皇后腰疼关我啥事</t>
+  </si>
+  <si>
+    <t>沉劫</t>
+  </si>
+  <si>
+    <t>四合院，开局我选入赘</t>
+  </si>
+  <si>
+    <t>怪物图鉴：从哥布林血脉开始</t>
+  </si>
+  <si>
+    <t>全班同学拜大宗师，我拜菩提祖师</t>
   </si>
   <si>
     <t>你管这叫警察？重炮都架租界口了</t>
   </si>
   <si>
-    <t>穿成大周宰相，皇后腰疼关我啥事</t>
-  </si>
-  <si>
-    <t>开局签到常务副皇帝，权倾朝野！</t>
-  </si>
-  <si>
-    <t>一战：我成了白毛德皇的治国轮椅</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>全员悍匪：你管这叫正经公司？</t>
-  </si>
-  <si>
-    <t>凡人修仙，捡个仙子做老婆</t>
-  </si>
-  <si>
-    <t>相亲失败！我把精神小妹捧成天后</t>
-  </si>
-  <si>
-    <t>转生火影，卡普模版</t>
-  </si>
-  <si>
-    <t>东北往事：野种的母亲</t>
-  </si>
-  <si>
-    <t>怪物图鉴：从哥布林血脉开始</t>
-  </si>
-  <si>
-    <t>沉劫</t>
-  </si>
-  <si>
-    <t>四合院，开局我选入赘</t>
-  </si>
-  <si>
-    <t>王者：你的天赋很好现在我也有了</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>三十多没娶亲，捡个孕妻还嫌亏</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>远离男主保命！校花后宫倒追我？</t>
-  </si>
-  <si>
-    <t>对头死后，疯批校花挖我坟求婚！</t>
-  </si>
-  <si>
     <t>大秦：我，嬴政！开局面壁穿越者</t>
   </si>
   <si>
-    <t>领主：从猎人卡开始</t>
-  </si>
-  <si>
-    <t>赦夜人</t>
-  </si>
-  <si>
-    <t>小区求生：每人每天给我一块面包</t>
-  </si>
-  <si>
-    <t>系统延迟一坤年，我成了全球股东</t>
+    <t>奥特：最强债主！借债十倍返还！</t>
+  </si>
+  <si>
+    <t>四合院：我表哥是神棍</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>83.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>3548000</v>
+        <v>3559000</v>
       </c>
       <c r="G5" s="7">
-        <v>33000</v>
+        <v>11000</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7">
-        <v>139000</v>
+        <v>117667</v>
       </c>
       <c r="J5" s="5">
-        <v>89</v>
+        <v>90.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>252000</v>
+        <v>294000</v>
       </c>
       <c r="G6" s="7">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="H6" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="7">
-        <v>46000</v>
+        <v>45200</v>
       </c>
       <c r="J6" s="5">
-        <v>81.5</v>
+        <v>84.3</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,19 +832,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>213000</v>
+        <v>252000</v>
       </c>
       <c r="G7" s="7">
-        <v>41000</v>
+        <v>39000</v>
       </c>
       <c r="H7" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>32800</v>
+        <v>33833</v>
       </c>
       <c r="J7" s="5">
-        <v>81.2</v>
+        <v>83.5</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>223000</v>
+        <v>257000</v>
       </c>
       <c r="G8" s="7">
-        <v>50000</v>
+        <v>34000</v>
       </c>
       <c r="H8" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>29800</v>
+        <v>30500</v>
       </c>
       <c r="J8" s="5">
-        <v>80</v>
+        <v>82.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -898,19 +898,19 @@
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>175000</v>
+        <v>216000</v>
       </c>
       <c r="G9" s="7">
-        <v>38000</v>
+        <v>41000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>24600</v>
+        <v>27333</v>
       </c>
       <c r="J9" s="5">
-        <v>79.2</v>
+        <v>81.8</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>91.5</v>
+        <v>97</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>523000</v>
+        <v>321000</v>
       </c>
       <c r="G10" s="7">
-        <v>63000</v>
+        <v>30000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>42400</v>
+        <v>28167</v>
       </c>
       <c r="J10" s="5">
-        <v>78.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>96.7</v>
+        <v>88.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>291000</v>
+        <v>579000</v>
       </c>
       <c r="G11" s="7">
-        <v>29000</v>
+        <v>56000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>27800</v>
+        <v>44667</v>
       </c>
       <c r="J11" s="5">
-        <v>78.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>95.5</v>
+        <v>91.5</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>343000</v>
+        <v>433000</v>
       </c>
       <c r="G12" s="7">
-        <v>25000</v>
+        <v>59000</v>
       </c>
       <c r="H12" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>29200</v>
+        <v>35000</v>
       </c>
       <c r="J12" s="5">
-        <v>77.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>180000</v>
+        <v>417000</v>
       </c>
       <c r="G13" s="7">
-        <v>22000</v>
+        <v>77000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>19200</v>
+        <v>33333</v>
       </c>
       <c r="J13" s="5">
-        <v>77.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>91.2</v>
+        <v>98.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>374000</v>
+        <v>201000</v>
       </c>
       <c r="G14" s="7">
-        <v>69000</v>
+        <v>21000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>30200</v>
+        <v>19500</v>
       </c>
       <c r="J14" s="5">
-        <v>75.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>85.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>558000</v>
+        <v>359000</v>
       </c>
       <c r="G15" s="7">
-        <v>78000</v>
+        <v>16000</v>
       </c>
       <c r="H15" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>41200</v>
+        <v>27000</v>
       </c>
       <c r="J15" s="5">
-        <v>75.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>85.5</v>
+        <v>83.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>760000</v>
+        <v>625000</v>
       </c>
       <c r="G16" s="7">
-        <v>49000</v>
+        <v>67000</v>
       </c>
       <c r="H16" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>38000</v>
+        <v>45500</v>
       </c>
       <c r="J16" s="5">
-        <v>74.5</v>
+        <v>77.3</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>83.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>400000</v>
+        <v>10079000</v>
       </c>
       <c r="G17" s="7">
-        <v>40000</v>
+        <v>56000</v>
       </c>
       <c r="H17" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I17" s="7">
-        <v>51750</v>
+        <v>61500</v>
       </c>
       <c r="J17" s="5">
-        <v>73.8</v>
+        <v>77</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>94.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>501000</v>
+        <v>442000</v>
       </c>
       <c r="G18" s="7">
-        <v>27000</v>
+        <v>42000</v>
       </c>
       <c r="H18" s="7">
         <v>6</v>
       </c>
       <c r="I18" s="7">
-        <v>14800</v>
+        <v>49800</v>
       </c>
       <c r="J18" s="5">
-        <v>73.5</v>
+        <v>77</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>98.09999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>193000</v>
+        <v>302000</v>
       </c>
       <c r="G19" s="7">
-        <v>30000</v>
+        <v>68000</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19" s="7">
-        <v>30333</v>
+        <v>53000</v>
       </c>
       <c r="J19" s="5">
-        <v>73.5</v>
+        <v>76.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>95.5</v>
+        <v>98.7</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>122000</v>
+        <v>221000</v>
       </c>
       <c r="G20" s="7">
-        <v>12000</v>
+        <v>28000</v>
       </c>
       <c r="H20" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>11800</v>
+        <v>29750</v>
       </c>
       <c r="J20" s="5">
-        <v>73.5</v>
+        <v>76.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>340000</v>
+        <v>138000</v>
       </c>
       <c r="G21" s="7">
-        <v>55000</v>
+        <v>16000</v>
       </c>
       <c r="H21" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>24600</v>
+        <v>12500</v>
       </c>
       <c r="J21" s="5">
-        <v>73.3</v>
+        <v>76.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>94.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>248000</v>
+        <v>271000</v>
       </c>
       <c r="G22" s="7">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="H22" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>10400</v>
+        <v>12500</v>
       </c>
       <c r="J22" s="5">
-        <v>72.5</v>
+        <v>75.7</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>92.3</v>
+        <v>93.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>388000</v>
+        <v>524000</v>
       </c>
       <c r="G23" s="7">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="H23" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>14600</v>
+        <v>16167</v>
       </c>
       <c r="J23" s="5">
-        <v>72.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>92.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>273000</v>
+        <v>795000</v>
       </c>
       <c r="G24" s="7">
-        <v>22000</v>
+        <v>35000</v>
       </c>
       <c r="H24" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="7">
-        <v>13800</v>
+        <v>37500</v>
       </c>
       <c r="J24" s="5">
-        <v>72.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>93.5</v>
+        <v>92</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>154000</v>
+        <v>366000</v>
       </c>
       <c r="G25" s="7">
-        <v>13000</v>
+        <v>23000</v>
       </c>
       <c r="H25" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>11800</v>
+        <v>16000</v>
       </c>
       <c r="J25" s="5">
-        <v>72.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>92.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>350000</v>
+        <v>405000</v>
       </c>
       <c r="G26" s="7">
-        <v>16000</v>
+        <v>17000</v>
       </c>
       <c r="H26" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="7">
-        <v>13400</v>
+        <v>15000</v>
       </c>
       <c r="J26" s="5">
-        <v>72.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>86</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>337000</v>
+        <v>392000</v>
       </c>
       <c r="G27" s="7">
-        <v>33000</v>
+        <v>48000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>27200</v>
+        <v>19667</v>
       </c>
       <c r="J27" s="5">
-        <v>72.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>97.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>112000</v>
+        <v>370000</v>
       </c>
       <c r="G28" s="7">
-        <v>16000</v>
+        <v>33000</v>
       </c>
       <c r="H28" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>1600</v>
+        <v>28167</v>
       </c>
       <c r="J28" s="5">
-        <v>72.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1549,28 +1549,30 @@
       <c r="A29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="5"/>
+      <c r="B29" s="5">
+        <v>9.6</v>
+      </c>
       <c r="C29" s="5">
-        <v>90.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>343000</v>
+        <v>149000</v>
       </c>
       <c r="G29" s="7">
-        <v>17000</v>
+        <v>13000</v>
       </c>
       <c r="H29" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>14600</v>
+        <v>10333</v>
       </c>
       <c r="J29" s="5">
-        <v>71.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1586,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>94.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>167000</v>
+        <v>126000</v>
       </c>
       <c r="G30" s="7">
-        <v>22000</v>
+        <v>14000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I30" s="7">
-        <v>17000</v>
+        <v>3667</v>
       </c>
       <c r="J30" s="5">
-        <v>71.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1619,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>88.3</v>
+        <v>91.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>190000</v>
+        <v>384000</v>
       </c>
       <c r="G31" s="7">
-        <v>5000</v>
+        <v>19000</v>
       </c>
       <c r="H31" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>17800</v>
+        <v>11000</v>
       </c>
       <c r="J31" s="5">
-        <v>71</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1652,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>88.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>175000</v>
+        <v>360000</v>
       </c>
       <c r="G32" s="7">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="7">
-        <v>16200</v>
+        <v>12833</v>
       </c>
       <c r="J32" s="5">
-        <v>70.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>103000</v>
+        <v>381000</v>
       </c>
       <c r="G33" s="7">
-        <v>9000</v>
+        <v>29000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" s="7">
-        <v>8600</v>
+        <v>23500</v>
       </c>
       <c r="J33" s="5">
-        <v>70.8</v>
+        <v>72.8</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1714,30 +1716,28 @@
       <c r="A34" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="5">
-        <v>9.6</v>
-      </c>
+      <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>91.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>136000</v>
+        <v>162000</v>
       </c>
       <c r="G34" s="7">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="H34" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" s="7">
-        <v>9800</v>
+        <v>9667</v>
       </c>
       <c r="J34" s="5">
-        <v>70.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>91.5</v>
+        <v>90.7</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>129000</v>
+        <v>198000</v>
       </c>
       <c r="G35" s="7">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>9200</v>
+        <v>10333</v>
       </c>
       <c r="J35" s="5">
-        <v>70.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>90.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>154000</v>
+        <v>278000</v>
       </c>
       <c r="G36" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H36" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="7">
-        <v>10000</v>
+        <v>15833</v>
       </c>
       <c r="J36" s="5">
-        <v>70.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>82.5</v>
+        <v>89.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>417000</v>
+        <v>161000</v>
       </c>
       <c r="G37" s="7">
-        <v>24000</v>
+        <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>27800</v>
+        <v>11000</v>
       </c>
       <c r="J37" s="5">
-        <v>70.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.3</v>
+        <v>90.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>266000</v>
+        <v>111000</v>
       </c>
       <c r="G38" s="7">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="7">
-        <v>16600</v>
+        <v>8500</v>
       </c>
       <c r="J38" s="5">
-        <v>70.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>84.5</v>
+        <v>90</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>352000</v>
+        <v>208000</v>
       </c>
       <c r="G39" s="7">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="H39" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>22400</v>
+        <v>8333</v>
       </c>
       <c r="J39" s="5">
-        <v>70.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>89.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>162000</v>
+        <v>118000</v>
       </c>
       <c r="G40" s="7">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="H40" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>9800</v>
+        <v>6833</v>
       </c>
       <c r="J40" s="5">
-        <v>69.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>90.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>157000</v>
+        <v>255000</v>
       </c>
       <c r="G41" s="7">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="H41" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>7600</v>
+        <v>10167</v>
       </c>
       <c r="J41" s="5">
-        <v>69.7</v>
+        <v>71.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>88.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>122000</v>
+        <v>170000</v>
       </c>
       <c r="G42" s="7">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="H42" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>12400</v>
+        <v>9500</v>
       </c>
       <c r="J42" s="5">
-        <v>69.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>88.5</v>
+        <v>82.8</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>183000</v>
+        <v>312000</v>
       </c>
       <c r="G43" s="7">
-        <v>11000</v>
+        <v>18000</v>
       </c>
       <c r="H43" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="7">
-        <v>10200</v>
+        <v>23167</v>
       </c>
       <c r="J43" s="5">
-        <v>69.2</v>
+        <v>71.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>89.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>112000</v>
+        <v>333000</v>
       </c>
       <c r="G44" s="7">
-        <v>5000</v>
+        <v>23000</v>
       </c>
       <c r="H44" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" s="7">
-        <v>7000</v>
+        <v>21500</v>
       </c>
       <c r="J44" s="5">
-        <v>69.2</v>
+        <v>70.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>83</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>310000</v>
+        <v>311000</v>
       </c>
       <c r="G45" s="7">
-        <v>23000</v>
+        <v>7000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I45" s="7">
-        <v>21200</v>
+        <v>8333</v>
       </c>
       <c r="J45" s="5">
-        <v>69</v>
+        <v>70.5</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>73.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>529000</v>
+        <v>174000</v>
       </c>
       <c r="G46" s="7">
-        <v>18000</v>
+        <v>-1000</v>
       </c>
       <c r="H46" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I46" s="7">
-        <v>40800</v>
+        <v>13333</v>
       </c>
       <c r="J46" s="5">
-        <v>68.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>88.3</v>
+        <v>86.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>304000</v>
+        <v>127000</v>
       </c>
       <c r="G47" s="7">
         <v>5000</v>
       </c>
       <c r="H47" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" s="7">
-        <v>8600</v>
+        <v>11167</v>
       </c>
       <c r="J47" s="5">
-        <v>68.7</v>
+        <v>70.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>244000</v>
+        <v>190000</v>
       </c>
       <c r="G48" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H48" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I48" s="7">
-        <v>10000</v>
+        <v>9667</v>
       </c>
       <c r="J48" s="5">
-        <v>68.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>98</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>185000</v>
+        <v>160000</v>
       </c>
       <c r="G49" s="7">
-        <v>28000</v>
+        <v>3000</v>
       </c>
       <c r="H49" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I49" s="7">
-        <v>22500</v>
+        <v>6833</v>
       </c>
       <c r="J49" s="5">
-        <v>68.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>81.8</v>
+        <v>90.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>845000</v>
+        <v>123000</v>
       </c>
       <c r="G50" s="7">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="H50" s="7">
         <v>6</v>
       </c>
       <c r="I50" s="7">
-        <v>21800</v>
+        <v>9200</v>
       </c>
       <c r="J50" s="5">
-        <v>68.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>88.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>146000</v>
+        <v>187000</v>
       </c>
       <c r="G51" s="7">
-        <v>6000</v>
+        <v>-3000</v>
       </c>
       <c r="H51" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I51" s="7">
-        <v>5800</v>
+        <v>14333</v>
       </c>
       <c r="J51" s="5">
-        <v>68.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>76.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>552000</v>
+        <v>857000</v>
       </c>
       <c r="G52" s="7">
-        <v>36000</v>
+        <v>12000</v>
       </c>
       <c r="H52" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" s="7">
-        <v>31000</v>
+        <v>20167</v>
       </c>
       <c r="J52" s="5">
-        <v>67.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>81.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>397000</v>
+        <v>409000</v>
       </c>
       <c r="G53" s="7">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="H53" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I53" s="7">
-        <v>19800</v>
+        <v>11000</v>
       </c>
       <c r="J53" s="5">
-        <v>67.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>82</v>
+        <v>87.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>542000</v>
+        <v>266000</v>
       </c>
       <c r="G54" s="7">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="H54" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I54" s="7">
-        <v>18200</v>
+        <v>5167</v>
       </c>
       <c r="J54" s="5">
-        <v>67.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-20T03:16:27+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-21T01:49:23+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -82,145 +82,145 @@
     <t>别人穿四合院，我为啥上战场</t>
   </si>
   <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
+    <t>我老婆有白月光？她怎么不知道</t>
+  </si>
+  <si>
+    <t>青梅是性转祖国人？可我是大超</t>
+  </si>
+  <si>
     <t>站中间抽两边，什么叫霸之意志呀</t>
   </si>
   <si>
+    <t>神通者</t>
+  </si>
+  <si>
     <t>我只想砍死各位，或者被各位砍死</t>
   </si>
   <si>
     <t>列车求生，我能升华一切！</t>
   </si>
   <si>
+    <t>大唐长生者，但开局在玄武门？</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>警告！邪神眷属正在杀入诡异副本</t>
+  </si>
+  <si>
+    <t>灵气复苏：开局获得呼吸法</t>
+  </si>
+  <si>
+    <t>五哈：千年家族曝光，误闯天家！</t>
+  </si>
+  <si>
+    <t>名义：我避开祁同伟几十年</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
     <t>两界倒爷：从1988到2025</t>
   </si>
   <si>
-    <t>我有一个女鬼催眠APP</t>
+    <t>名义：开局我举报我自己</t>
   </si>
   <si>
     <t>入学第一天，千金学姐成了我老婆</t>
   </si>
   <si>
-    <t>我，亿万天赋，天才不过见我门槛</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
-    <t>警告！邪神眷属正在杀入诡异副本</t>
-  </si>
-  <si>
-    <t>我老婆有白月光？她怎么不知道</t>
-  </si>
-  <si>
-    <t>青梅是性转祖国人？可我是大超</t>
-  </si>
-  <si>
-    <t>美恐：我，人间真神</t>
+    <t>只想躺平开民宿，咋就活成顶流了</t>
+  </si>
+  <si>
+    <t>东北往事：野种的母亲</t>
+  </si>
+  <si>
+    <t>旧日家族求生，我家族谱全是禁忌</t>
+  </si>
+  <si>
+    <t>镇国驸马爷</t>
+  </si>
+  <si>
+    <t>开局签到常务副皇帝，权倾朝野！</t>
+  </si>
+  <si>
+    <t>退休勇者买下魔王当女仆</t>
+  </si>
+  <si>
+    <t>转生火影，卡普模版</t>
+  </si>
+  <si>
+    <t>一战：我成了白毛德皇的治国轮椅</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
+    <t>天幕盘点开国，红色华夏震撼千古</t>
+  </si>
+  <si>
+    <t>亮剑：军校毕业，我给老李当参谋</t>
+  </si>
+  <si>
+    <t>王者：你的天赋很好现在我也有了</t>
+  </si>
+  <si>
+    <t>综漫：捡碎片的我开局拼出虚式茈</t>
+  </si>
+  <si>
+    <t>盗墓手法太熟练，惊呆校花学姐！</t>
+  </si>
+  <si>
+    <t>猪猪侠：什么叫主攻手空手接大？</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
   </si>
   <si>
     <t>奥特：天蝎座第一道光</t>
   </si>
   <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>只想躺平开民宿，咋就活成顶流了</t>
-  </si>
-  <si>
-    <t>每天属性翻一倍，我黑化爆杀一切</t>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>小区求生：每人每天给我一块面包</t>
+  </si>
+  <si>
+    <t>抗战：这个系统不正经</t>
+  </si>
+  <si>
+    <t>大秦：我，嬴政！开局面壁穿越者</t>
+  </si>
+  <si>
+    <t>相亲失败！我把精神小妹捧成天后</t>
+  </si>
+  <si>
+    <t>抑郁少女总想自杀？那就恶堕吧！</t>
   </si>
   <si>
     <t>狩猎北大荒：投亲路上遇到狼拦路</t>
   </si>
   <si>
-    <t>镇国驸马爷</t>
-  </si>
-  <si>
-    <t>一战：我成了白毛德皇的治国轮椅</t>
-  </si>
-  <si>
-    <t>文臣尽头是武斗？我在朝堂横着走</t>
-  </si>
-  <si>
-    <t>人在潮汕，开局连抛十八圣杯</t>
-  </si>
-  <si>
-    <t>天幕盘点开国，红色华夏震撼千古</t>
-  </si>
-  <si>
-    <t>转生火影，卡普模版</t>
-  </si>
-  <si>
-    <t>全员悍匪：你管这叫正经公司？</t>
-  </si>
-  <si>
-    <t>五哈：千年家族曝光，误闯天家！</t>
-  </si>
-  <si>
-    <t>相亲失败！我把精神小妹捧成天后</t>
-  </si>
-  <si>
-    <t>大唐：玄武门前夜，我绑父投秦王</t>
-  </si>
-  <si>
-    <t>开局签到常务副皇帝，权倾朝野！</t>
-  </si>
-  <si>
-    <t>猪猪侠：什么叫主攻手空手接大？</t>
-  </si>
-  <si>
-    <t>王者：你的天赋很好现在我也有了</t>
-  </si>
-  <si>
-    <t>远离男主保命！校花后宫倒追我？</t>
-  </si>
-  <si>
-    <t>东北往事：野种的母亲</t>
-  </si>
-  <si>
-    <t>亮剑：军校毕业，我给老李当参谋</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>穿成大周宰相，皇后腰疼关我啥事</t>
-  </si>
-  <si>
-    <t>沉劫</t>
-  </si>
-  <si>
-    <t>四合院，开局我选入赘</t>
-  </si>
-  <si>
-    <t>怪物图鉴：从哥布林血脉开始</t>
-  </si>
-  <si>
-    <t>全班同学拜大宗师，我拜菩提祖师</t>
-  </si>
-  <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>大秦：我，嬴政！开局面壁穿越者</t>
-  </si>
-  <si>
-    <t>奥特：最强债主！借债十倍返还！</t>
-  </si>
-  <si>
-    <t>四合院：我表哥是神棍</t>
+    <t>盗墓：背棺送葬，奖励龙象般若功</t>
+  </si>
+  <si>
+    <t>我都成烛龙了，人类怎么才诞生？</t>
+  </si>
+  <si>
+    <t>诡异国运：开局扮演鬼眼杨间</t>
+  </si>
+  <si>
+    <t>村长，收手吧，外面全是套路！</t>
+  </si>
+  <si>
+    <t>赦夜人</t>
+  </si>
+  <si>
+    <t>民国：张家逆子，我才是东北王</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>83.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>3559000</v>
+        <v>3544000</v>
       </c>
       <c r="G5" s="7">
-        <v>11000</v>
+        <v>-15000</v>
       </c>
       <c r="H5" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>117667</v>
+        <v>98714</v>
       </c>
       <c r="J5" s="5">
-        <v>90.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>294000</v>
+        <v>366000</v>
       </c>
       <c r="G6" s="7">
-        <v>42000</v>
+        <v>72000</v>
       </c>
       <c r="H6" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>45200</v>
+        <v>49667</v>
       </c>
       <c r="J6" s="5">
-        <v>84.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,16 +832,16 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>252000</v>
+        <v>287000</v>
       </c>
       <c r="G7" s="7">
-        <v>39000</v>
+        <v>35000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>33833</v>
+        <v>34000</v>
       </c>
       <c r="J7" s="5">
         <v>83.5</v>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>257000</v>
+        <v>254000</v>
       </c>
       <c r="G8" s="7">
-        <v>34000</v>
+        <v>38000</v>
       </c>
       <c r="H8" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
-        <v>30500</v>
+        <v>28857</v>
       </c>
       <c r="J8" s="5">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -898,19 +898,19 @@
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>216000</v>
+        <v>363000</v>
       </c>
       <c r="G9" s="7">
-        <v>41000</v>
+        <v>61000</v>
       </c>
       <c r="H9" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7">
-        <v>27333</v>
+        <v>55667</v>
       </c>
       <c r="J9" s="5">
-        <v>81.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>97</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>321000</v>
+        <v>250000</v>
       </c>
       <c r="G10" s="7">
-        <v>30000</v>
+        <v>29000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>28167</v>
+        <v>29600</v>
       </c>
       <c r="J10" s="5">
-        <v>80.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>88.7</v>
+        <v>94.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>579000</v>
+        <v>346000</v>
       </c>
       <c r="G11" s="7">
-        <v>56000</v>
+        <v>25000</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
-        <v>44667</v>
+        <v>27714</v>
       </c>
       <c r="J11" s="5">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>91.5</v>
+        <v>95.5</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>433000</v>
+        <v>10126000</v>
       </c>
       <c r="G12" s="7">
-        <v>59000</v>
+        <v>47000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I12" s="7">
-        <v>35000</v>
+        <v>56667</v>
       </c>
       <c r="J12" s="5">
-        <v>79.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>92.3</v>
+        <v>84.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>417000</v>
+        <v>617000</v>
       </c>
       <c r="G13" s="7">
-        <v>77000</v>
+        <v>38000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>33333</v>
+        <v>43714</v>
       </c>
       <c r="J13" s="5">
-        <v>79.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>98.2</v>
+        <v>86.7</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>201000</v>
+        <v>476000</v>
       </c>
       <c r="G14" s="7">
-        <v>21000</v>
+        <v>43000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
-        <v>19500</v>
+        <v>36143</v>
       </c>
       <c r="J14" s="5">
-        <v>78.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>92.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>359000</v>
+        <v>490000</v>
       </c>
       <c r="G15" s="7">
-        <v>16000</v>
+        <v>98000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="J15" s="5">
-        <v>77.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>83.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>625000</v>
+        <v>216000</v>
       </c>
       <c r="G16" s="7">
-        <v>67000</v>
+        <v>15000</v>
       </c>
       <c r="H16" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I16" s="7">
-        <v>45500</v>
+        <v>18857</v>
       </c>
       <c r="J16" s="5">
-        <v>77.3</v>
+        <v>76.5</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>95.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>10079000</v>
+        <v>473000</v>
       </c>
       <c r="G17" s="7">
-        <v>56000</v>
+        <v>31000</v>
       </c>
       <c r="H17" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I17" s="7">
-        <v>61500</v>
+        <v>46667</v>
       </c>
       <c r="J17" s="5">
-        <v>77</v>
+        <v>76.3</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>84.59999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>442000</v>
+        <v>109000</v>
       </c>
       <c r="G18" s="7">
-        <v>42000</v>
+        <v>12000</v>
       </c>
       <c r="H18" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I18" s="7">
-        <v>49800</v>
+        <v>9143</v>
       </c>
       <c r="J18" s="5">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>99.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>302000</v>
+        <v>222000</v>
       </c>
       <c r="G19" s="7">
-        <v>68000</v>
+        <v>24000</v>
       </c>
       <c r="H19" s="7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>53000</v>
+        <v>12286</v>
       </c>
       <c r="J19" s="5">
-        <v>76.8</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>98.7</v>
+        <v>98.3</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>221000</v>
+        <v>213000</v>
       </c>
       <c r="G20" s="7">
-        <v>28000</v>
+        <v>38000</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I20" s="7">
-        <v>29750</v>
+        <v>48000</v>
       </c>
       <c r="J20" s="5">
-        <v>76.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>97.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>138000</v>
+        <v>828000</v>
       </c>
       <c r="G21" s="7">
-        <v>16000</v>
+        <v>33000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>12500</v>
+        <v>36857</v>
       </c>
       <c r="J21" s="5">
-        <v>76.5</v>
+        <v>74.8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>95.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>271000</v>
+        <v>440000</v>
       </c>
       <c r="G22" s="7">
         <v>23000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>12500</v>
+        <v>31857</v>
       </c>
       <c r="J22" s="5">
-        <v>75.7</v>
+        <v>74</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>93.2</v>
+        <v>90.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>524000</v>
+        <v>535000</v>
       </c>
       <c r="G23" s="7">
-        <v>23000</v>
+        <v>11000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I23" s="7">
-        <v>16167</v>
+        <v>15429</v>
       </c>
       <c r="J23" s="5">
-        <v>75.3</v>
+        <v>73.7</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>795000</v>
+        <v>358000</v>
       </c>
       <c r="G24" s="7">
-        <v>35000</v>
+        <v>-1000</v>
       </c>
       <c r="H24" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I24" s="7">
-        <v>37500</v>
+        <v>23000</v>
       </c>
       <c r="J24" s="5">
-        <v>75.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>92</v>
+        <v>89.8</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>366000</v>
+        <v>379000</v>
       </c>
       <c r="G25" s="7">
-        <v>23000</v>
+        <v>13000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>16000</v>
+        <v>15571</v>
       </c>
       <c r="J25" s="5">
-        <v>74.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>91.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>405000</v>
+        <v>182000</v>
       </c>
       <c r="G26" s="7">
-        <v>17000</v>
+        <v>12000</v>
       </c>
       <c r="H26" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>15000</v>
+        <v>9857</v>
       </c>
       <c r="J26" s="5">
-        <v>74.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>89.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>392000</v>
+        <v>104000</v>
       </c>
       <c r="G27" s="7">
-        <v>48000</v>
+        <v>12000</v>
       </c>
       <c r="H27" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>19667</v>
+        <v>7714</v>
       </c>
       <c r="J27" s="5">
-        <v>74.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>85.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>370000</v>
+        <v>399000</v>
       </c>
       <c r="G28" s="7">
-        <v>33000</v>
+        <v>29000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>28167</v>
+        <v>28286</v>
       </c>
       <c r="J28" s="5">
-        <v>73.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1549,30 +1549,28 @@
       <c r="A29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="5">
-        <v>9.6</v>
-      </c>
+      <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>92.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>149000</v>
+        <v>121000</v>
       </c>
       <c r="G29" s="7">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>10333</v>
+        <v>8714</v>
       </c>
       <c r="J29" s="5">
-        <v>73.7</v>
+        <v>72.7</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1586,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>126000</v>
+        <v>113000</v>
       </c>
       <c r="G30" s="7">
-        <v>14000</v>
+        <v>23000</v>
       </c>
       <c r="H30" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>3667</v>
+        <v>17500</v>
       </c>
       <c r="J30" s="5">
-        <v>73.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1619,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>91.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>384000</v>
+        <v>409000</v>
       </c>
       <c r="G31" s="7">
-        <v>19000</v>
+        <v>28000</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>11000</v>
+        <v>24143</v>
       </c>
       <c r="J31" s="5">
-        <v>73.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,28 +1648,30 @@
       <c r="A32" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="5"/>
+      <c r="B32" s="5">
+        <v>9.6</v>
+      </c>
       <c r="C32" s="5">
-        <v>90.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>360000</v>
+        <v>160000</v>
       </c>
       <c r="G32" s="7">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="H32" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>12833</v>
+        <v>10429</v>
       </c>
       <c r="J32" s="5">
-        <v>73</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1685,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>85.3</v>
+        <v>91.7</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>381000</v>
+        <v>142000</v>
       </c>
       <c r="G33" s="7">
-        <v>29000</v>
+        <v>10000</v>
       </c>
       <c r="H33" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" s="7">
-        <v>23500</v>
+        <v>8429</v>
       </c>
       <c r="J33" s="5">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>91.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>162000</v>
+        <v>364000</v>
       </c>
       <c r="G34" s="7">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="H34" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" s="7">
-        <v>9667</v>
+        <v>11571</v>
       </c>
       <c r="J34" s="5">
-        <v>72.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>90.7</v>
+        <v>82.5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>198000</v>
+        <v>330000</v>
       </c>
       <c r="G35" s="7">
         <v>18000</v>
       </c>
       <c r="H35" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I35" s="7">
-        <v>10333</v>
+        <v>22429</v>
       </c>
       <c r="J35" s="5">
-        <v>72.5</v>
+        <v>71</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>87.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>278000</v>
+        <v>123000</v>
       </c>
       <c r="G36" s="7">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="H36" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>15833</v>
+        <v>6571</v>
       </c>
       <c r="J36" s="5">
-        <v>72.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>89.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>161000</v>
+        <v>153000</v>
       </c>
       <c r="G37" s="7">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>11000</v>
+        <v>11400</v>
       </c>
       <c r="J37" s="5">
-        <v>72.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>90.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>111000</v>
+        <v>101000</v>
       </c>
       <c r="G38" s="7">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="H38" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7">
-        <v>8500</v>
+        <v>6429</v>
       </c>
       <c r="J38" s="5">
-        <v>71.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>90</v>
+        <v>88.2</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>208000</v>
+        <v>213000</v>
       </c>
       <c r="G39" s="7">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H39" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I39" s="7">
-        <v>8333</v>
+        <v>7857</v>
       </c>
       <c r="J39" s="5">
-        <v>71.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>90.7</v>
+        <v>81.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>118000</v>
+        <v>352000</v>
       </c>
       <c r="G40" s="7">
-        <v>6000</v>
+        <v>19000</v>
       </c>
       <c r="H40" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I40" s="7">
-        <v>6833</v>
+        <v>21143</v>
       </c>
       <c r="J40" s="5">
-        <v>71.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>89</v>
+        <v>84.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>255000</v>
+        <v>298000</v>
       </c>
       <c r="G41" s="7">
-        <v>11000</v>
+        <v>27000</v>
       </c>
       <c r="H41" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I41" s="7">
-        <v>10167</v>
+        <v>14571</v>
       </c>
       <c r="J41" s="5">
-        <v>71.5</v>
+        <v>70.3</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>170000</v>
+        <v>115000</v>
       </c>
       <c r="G42" s="7">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I42" s="7">
-        <v>9500</v>
+        <v>3714</v>
       </c>
       <c r="J42" s="5">
-        <v>71.5</v>
+        <v>70.2</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>82.8</v>
+        <v>81.8</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>312000</v>
+        <v>437000</v>
       </c>
       <c r="G43" s="7">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H43" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>23167</v>
+        <v>19857</v>
       </c>
       <c r="J43" s="5">
-        <v>71.3</v>
+        <v>70</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>82.5</v>
+        <v>86.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>333000</v>
+        <v>103000</v>
       </c>
       <c r="G44" s="7">
-        <v>23000</v>
+        <v>6000</v>
       </c>
       <c r="H44" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="7">
-        <v>21500</v>
+        <v>9857</v>
       </c>
       <c r="J44" s="5">
-        <v>70.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>88.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>311000</v>
+        <v>870000</v>
       </c>
       <c r="G45" s="7">
-        <v>7000</v>
+        <v>13000</v>
       </c>
       <c r="H45" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I45" s="7">
-        <v>8333</v>
+        <v>19143</v>
       </c>
       <c r="J45" s="5">
-        <v>70.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>174000</v>
+        <v>279000</v>
       </c>
       <c r="G46" s="7">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="H46" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" s="7">
-        <v>13333</v>
+        <v>13714</v>
       </c>
       <c r="J46" s="5">
-        <v>70.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>86.3</v>
+        <v>100</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>127000</v>
+        <v>496000</v>
       </c>
       <c r="G47" s="7">
-        <v>5000</v>
+        <v>55000</v>
       </c>
       <c r="H47" s="7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I47" s="7">
-        <v>11167</v>
+        <v>21000</v>
       </c>
       <c r="J47" s="5">
-        <v>70.3</v>
+        <v>69.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>86.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>190000</v>
+        <v>409000</v>
       </c>
       <c r="G48" s="7">
-        <v>7000</v>
+        <v>17000</v>
       </c>
       <c r="H48" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I48" s="7">
-        <v>9667</v>
+        <v>19286</v>
       </c>
       <c r="J48" s="5">
-        <v>70.2</v>
+        <v>69.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>87.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>160000</v>
+        <v>102000</v>
       </c>
       <c r="G49" s="7">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="H49" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I49" s="7">
-        <v>6833</v>
+        <v>6286</v>
       </c>
       <c r="J49" s="5">
-        <v>70.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>90.2</v>
+        <v>94.8</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>123000</v>
+        <v>135000</v>
       </c>
       <c r="G50" s="7">
-        <v>15000</v>
+        <v>19000</v>
       </c>
       <c r="H50" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I50" s="7">
-        <v>9200</v>
+        <v>19667</v>
       </c>
       <c r="J50" s="5">
-        <v>69.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>187000</v>
+        <v>111000</v>
       </c>
       <c r="G51" s="7">
-        <v>-3000</v>
+        <v>4000</v>
       </c>
       <c r="H51" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" s="7">
-        <v>14333</v>
+        <v>2429</v>
       </c>
       <c r="J51" s="5">
-        <v>69.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>81.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>857000</v>
+        <v>133000</v>
       </c>
       <c r="G52" s="7">
-        <v>12000</v>
+        <v>4000</v>
       </c>
       <c r="H52" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I52" s="7">
-        <v>20167</v>
+        <v>286</v>
       </c>
       <c r="J52" s="5">
-        <v>69.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>85.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>409000</v>
+        <v>603000</v>
       </c>
       <c r="G53" s="7">
-        <v>27000</v>
+        <v>21000</v>
       </c>
       <c r="H53" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I53" s="7">
-        <v>11000</v>
+        <v>29429</v>
       </c>
       <c r="J53" s="5">
-        <v>69.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>87.8</v>
+        <v>94.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>266000</v>
+        <v>101000</v>
       </c>
       <c r="G54" s="7">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="H54" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>5167</v>
+        <v>19333</v>
       </c>
       <c r="J54" s="5">
-        <v>69.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-21T01:49:23+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-22T01:41:54+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>我老婆有白月光？她怎么不知道</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>大唐长生者，但开局在玄武门？</t>
+  </si>
+  <si>
+    <t>青梅是性转祖国人？可我是大超</t>
+  </si>
+  <si>
     <t>时停起手，邪神也得给我跪下！</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>我的绝世表嫂</t>
-  </si>
-  <si>
-    <t>别人穿四合院，我为啥上战场</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>我老婆有白月光？她怎么不知道</t>
-  </si>
-  <si>
-    <t>青梅是性转祖国人？可我是大超</t>
+    <t>抑郁少女总想自杀？那就恶堕吧！</t>
+  </si>
+  <si>
+    <t>退休勇者买下魔王当女仆</t>
   </si>
   <si>
     <t>站中间抽两边，什么叫霸之意志呀</t>
   </si>
   <si>
-    <t>神通者</t>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>开局盗大墓，系统让我去自首</t>
+  </si>
+  <si>
+    <t>警告！邪神眷属正在杀入诡异副本</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>名义：我避开祁同伟几十年</t>
+  </si>
+  <si>
+    <t>入学第一天，千金学姐成了我老婆</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>东北往事•关东娘们儿与土匪</t>
   </si>
   <si>
     <t>我只想砍死各位，或者被各位砍死</t>
   </si>
   <si>
-    <t>列车求生，我能升华一切！</t>
-  </si>
-  <si>
-    <t>大唐长生者，但开局在玄武门？</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>警告！邪神眷属正在杀入诡异副本</t>
-  </si>
-  <si>
     <t>灵气复苏：开局获得呼吸法</t>
   </si>
   <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>我都成烛龙了，人类怎么才诞生？</t>
+  </si>
+  <si>
+    <t>转生火影，卡普模版</t>
+  </si>
+  <si>
+    <t>综漫：捡碎片的我开局拼出虚式茈</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
+    <t>1985，出租车司机的悠闲生活</t>
+  </si>
+  <si>
+    <t>别人夺嫡偷偷来，我家皇帝下圣旨</t>
+  </si>
+  <si>
+    <t>穿成丧尸小萝莉，凤傲天求放过</t>
+  </si>
+  <si>
+    <t>一战：我成了白毛德皇的治国轮椅</t>
+  </si>
+  <si>
     <t>五哈：千年家族曝光，误闯天家！</t>
   </si>
   <si>
-    <t>名义：我避开祁同伟几十年</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>两界倒爷：从1988到2025</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>入学第一天，千金学姐成了我老婆</t>
-  </si>
-  <si>
-    <t>只想躺平开民宿，咋就活成顶流了</t>
-  </si>
-  <si>
-    <t>东北往事：野种的母亲</t>
-  </si>
-  <si>
-    <t>旧日家族求生，我家族谱全是禁忌</t>
-  </si>
-  <si>
-    <t>镇国驸马爷</t>
-  </si>
-  <si>
-    <t>开局签到常务副皇帝，权倾朝野！</t>
-  </si>
-  <si>
-    <t>退休勇者买下魔王当女仆</t>
-  </si>
-  <si>
-    <t>转生火影，卡普模版</t>
-  </si>
-  <si>
-    <t>一战：我成了白毛德皇的治国轮椅</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>天幕盘点开国，红色华夏震撼千古</t>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>姐姐，轻点撩</t>
+  </si>
+  <si>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>魔龙与地下城：恶龙请求出狱</t>
   </si>
   <si>
     <t>亮剑：军校毕业，我给老李当参谋</t>
   </si>
   <si>
-    <t>王者：你的天赋很好现在我也有了</t>
-  </si>
-  <si>
-    <t>综漫：捡碎片的我开局拼出虚式茈</t>
+    <t>抗战：这个系统不正经</t>
+  </si>
+  <si>
+    <t>小区求生：每人每天给我一块面包</t>
+  </si>
+  <si>
+    <t>重生后无敌，我开始养成女帝</t>
+  </si>
+  <si>
+    <t>四合院，开局我选入赘</t>
+  </si>
+  <si>
+    <t>港综：骆天虹亲哥，开局金刚不坏</t>
+  </si>
+  <si>
+    <t>肝肝肝肝肝！往死里肝！</t>
+  </si>
+  <si>
+    <t>大秦我带秦始皇长生不老</t>
+  </si>
+  <si>
+    <t>奥特：最强债主！借债十倍返还！</t>
+  </si>
+  <si>
+    <t>我根骨平庸，但分身都是绝世天才</t>
+  </si>
+  <si>
+    <t>相亲失败！我把精神小妹捧成天后</t>
+  </si>
+  <si>
+    <t>名义：梁璐逼婚？家父赵蒙生</t>
   </si>
   <si>
     <t>盗墓手法太熟练，惊呆校花学姐！</t>
   </si>
   <si>
-    <t>猪猪侠：什么叫主攻手空手接大？</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
     <t>奥特：天蝎座第一道光</t>
   </si>
   <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
-  </si>
-  <si>
-    <t>小区求生：每人每天给我一块面包</t>
-  </si>
-  <si>
-    <t>抗战：这个系统不正经</t>
-  </si>
-  <si>
-    <t>大秦：我，嬴政！开局面壁穿越者</t>
-  </si>
-  <si>
-    <t>相亲失败！我把精神小妹捧成天后</t>
-  </si>
-  <si>
-    <t>抑郁少女总想自杀？那就恶堕吧！</t>
-  </si>
-  <si>
-    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
-  </si>
-  <si>
-    <t>盗墓：背棺送葬，奖励龙象般若功</t>
-  </si>
-  <si>
-    <t>我都成烛龙了，人类怎么才诞生？</t>
-  </si>
-  <si>
-    <t>诡异国运：开局扮演鬼眼杨间</t>
-  </si>
-  <si>
-    <t>村长，收手吧，外面全是套路！</t>
-  </si>
-  <si>
-    <t>赦夜人</t>
-  </si>
-  <si>
-    <t>民国：张家逆子，我才是东北王</t>
+    <t>开局模拟被打爆，金丹爆星什么鬼</t>
+  </si>
+  <si>
+    <t>反派老婆破产后，她们都盯上我？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>82.3</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>3544000</v>
+        <v>323000</v>
       </c>
       <c r="G5" s="7">
-        <v>-15000</v>
+        <v>36000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="7">
-        <v>98714</v>
+        <v>34250</v>
       </c>
       <c r="J5" s="5">
-        <v>89.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>366000</v>
+        <v>408000</v>
       </c>
       <c r="G6" s="7">
-        <v>72000</v>
+        <v>45000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I6" s="7">
-        <v>49667</v>
+        <v>53000</v>
       </c>
       <c r="J6" s="5">
-        <v>87.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,19 +832,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>287000</v>
+        <v>291000</v>
       </c>
       <c r="G7" s="7">
-        <v>35000</v>
+        <v>37000</v>
       </c>
       <c r="H7" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="7">
-        <v>34000</v>
+        <v>29875</v>
       </c>
       <c r="J7" s="5">
-        <v>83.5</v>
+        <v>82.5</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>254000</v>
+        <v>10177000</v>
       </c>
       <c r="G8" s="7">
-        <v>38000</v>
+        <v>51000</v>
       </c>
       <c r="H8" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7">
-        <v>28857</v>
+        <v>55250</v>
       </c>
       <c r="J8" s="5">
-        <v>82.2</v>
+        <v>81.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>363000</v>
+        <v>583000</v>
       </c>
       <c r="G9" s="7">
-        <v>61000</v>
+        <v>93000</v>
       </c>
       <c r="H9" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>55667</v>
+        <v>37875</v>
       </c>
       <c r="J9" s="5">
-        <v>80.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>98.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>250000</v>
+        <v>271000</v>
       </c>
       <c r="G10" s="7">
-        <v>29000</v>
+        <v>21000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>29600</v>
+        <v>28167</v>
       </c>
       <c r="J10" s="5">
-        <v>79.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>94.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>346000</v>
+        <v>3319000</v>
       </c>
       <c r="G11" s="7">
-        <v>25000</v>
+        <v>-225000</v>
       </c>
       <c r="H11" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7">
-        <v>27714</v>
+        <v>58250</v>
       </c>
       <c r="J11" s="5">
-        <v>79</v>
+        <v>77.2</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>10126000</v>
+        <v>577000</v>
       </c>
       <c r="G12" s="7">
-        <v>47000</v>
+        <v>81000</v>
       </c>
       <c r="H12" s="7">
         <v>4</v>
       </c>
       <c r="I12" s="7">
-        <v>56667</v>
+        <v>41000</v>
       </c>
       <c r="J12" s="5">
-        <v>78.7</v>
+        <v>77.2</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>84.7</v>
+        <v>99</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>617000</v>
+        <v>136000</v>
       </c>
       <c r="G13" s="7">
-        <v>38000</v>
+        <v>23000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>43714</v>
+        <v>18600</v>
       </c>
       <c r="J13" s="5">
-        <v>77.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>86.7</v>
+        <v>90.7</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>476000</v>
+        <v>359000</v>
       </c>
       <c r="G14" s="7">
-        <v>43000</v>
+        <v>13000</v>
       </c>
       <c r="H14" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7">
-        <v>36143</v>
+        <v>25875</v>
       </c>
       <c r="J14" s="5">
-        <v>76.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>89.3</v>
+        <v>93.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>490000</v>
+        <v>230000</v>
       </c>
       <c r="G15" s="7">
-        <v>98000</v>
+        <v>14000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7">
-        <v>30000</v>
+        <v>18250</v>
       </c>
       <c r="J15" s="5">
-        <v>76.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>94.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>216000</v>
+        <v>104000</v>
       </c>
       <c r="G16" s="7">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="H16" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>18857</v>
+        <v>7000</v>
       </c>
       <c r="J16" s="5">
-        <v>76.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>81.2</v>
+        <v>80</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>473000</v>
+        <v>496000</v>
       </c>
       <c r="G17" s="7">
-        <v>31000</v>
+        <v>23000</v>
       </c>
       <c r="H17" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>46667</v>
+        <v>43286</v>
       </c>
       <c r="J17" s="5">
-        <v>76.3</v>
+        <v>74.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>97.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>109000</v>
+        <v>104000</v>
       </c>
       <c r="G18" s="7">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="H18" s="7">
         <v>8</v>
       </c>
       <c r="I18" s="7">
-        <v>9143</v>
+        <v>10429</v>
       </c>
       <c r="J18" s="5">
-        <v>76</v>
+        <v>74.8</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>222000</v>
+        <v>237000</v>
       </c>
       <c r="G19" s="7">
         <v>24000</v>
       </c>
       <c r="H19" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
-        <v>12286</v>
+        <v>40000</v>
       </c>
       <c r="J19" s="5">
-        <v>75.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>98.3</v>
+        <v>89.2</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>213000</v>
+        <v>363000</v>
       </c>
       <c r="G20" s="7">
-        <v>38000</v>
+        <v>5000</v>
       </c>
       <c r="H20" s="7">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>48000</v>
+        <v>20750</v>
       </c>
       <c r="J20" s="5">
-        <v>75.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>82.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>828000</v>
+        <v>851000</v>
       </c>
       <c r="G21" s="7">
-        <v>33000</v>
+        <v>23000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" s="7">
-        <v>36857</v>
+        <v>35125</v>
       </c>
       <c r="J21" s="5">
-        <v>74.8</v>
+        <v>73.7</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>83.7</v>
+        <v>92.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>440000</v>
+        <v>195000</v>
       </c>
       <c r="G22" s="7">
-        <v>23000</v>
+        <v>13000</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="7">
-        <v>31857</v>
+        <v>10250</v>
       </c>
       <c r="J22" s="5">
-        <v>74</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>90.7</v>
+        <v>78.3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>535000</v>
+        <v>618000</v>
       </c>
       <c r="G23" s="7">
-        <v>11000</v>
+        <v>1000</v>
       </c>
       <c r="H23" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I23" s="7">
-        <v>15429</v>
+        <v>38375</v>
       </c>
       <c r="J23" s="5">
-        <v>73.7</v>
+        <v>72.7</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>358000</v>
+        <v>116000</v>
       </c>
       <c r="G24" s="7">
-        <v>-1000</v>
+        <v>7000</v>
       </c>
       <c r="H24" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="7">
-        <v>23000</v>
+        <v>8875</v>
       </c>
       <c r="J24" s="5">
-        <v>73.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>379000</v>
+        <v>535000</v>
       </c>
       <c r="G25" s="7">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" s="7">
-        <v>15571</v>
+        <v>13500</v>
       </c>
       <c r="J25" s="5">
-        <v>73.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>92.5</v>
+        <v>94.2</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>182000</v>
+        <v>154000</v>
       </c>
       <c r="G26" s="7">
-        <v>12000</v>
+        <v>19000</v>
       </c>
       <c r="H26" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I26" s="7">
-        <v>9857</v>
+        <v>19500</v>
       </c>
       <c r="J26" s="5">
-        <v>73.3</v>
+        <v>71.7</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>93.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>104000</v>
+        <v>431000</v>
       </c>
       <c r="G27" s="7">
-        <v>12000</v>
+        <v>22000</v>
       </c>
       <c r="H27" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I27" s="7">
-        <v>7714</v>
+        <v>23875</v>
       </c>
       <c r="J27" s="5">
-        <v>73.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>83.3</v>
+        <v>88.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>399000</v>
+        <v>161000</v>
       </c>
       <c r="G28" s="7">
-        <v>29000</v>
+        <v>8000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>28286</v>
+        <v>10833</v>
       </c>
       <c r="J28" s="5">
-        <v>72.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>91.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>121000</v>
+        <v>150000</v>
       </c>
       <c r="G29" s="7">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" s="7">
-        <v>8714</v>
+        <v>8375</v>
       </c>
       <c r="J29" s="5">
-        <v>72.7</v>
+        <v>71.5</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>96.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>113000</v>
+        <v>103000</v>
       </c>
       <c r="G30" s="7">
-        <v>23000</v>
+        <v>6000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I30" s="7">
-        <v>17500</v>
+        <v>7500</v>
       </c>
       <c r="J30" s="5">
-        <v>72.7</v>
+        <v>71.2</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>84.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>409000</v>
+        <v>417000</v>
       </c>
       <c r="G31" s="7">
-        <v>28000</v>
+        <v>41000</v>
       </c>
       <c r="H31" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="7">
-        <v>24143</v>
+        <v>12375</v>
       </c>
       <c r="J31" s="5">
-        <v>72.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1648,30 +1648,28 @@
       <c r="A32" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="5">
-        <v>9.6</v>
-      </c>
+      <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>90.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>160000</v>
+        <v>103000</v>
       </c>
       <c r="G32" s="7">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="H32" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>10429</v>
+        <v>17250</v>
       </c>
       <c r="J32" s="5">
-        <v>72.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,28 +1681,30 @@
       <c r="A33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="5"/>
+      <c r="B33" s="5">
+        <v>9.6</v>
+      </c>
       <c r="C33" s="5">
-        <v>91.7</v>
+        <v>88</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>142000</v>
+        <v>167000</v>
       </c>
       <c r="G33" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H33" s="7">
+        <v>9</v>
+      </c>
+      <c r="I33" s="7">
         <v>10000</v>
       </c>
-      <c r="H33" s="7">
-        <v>8</v>
-      </c>
-      <c r="I33" s="7">
-        <v>8429</v>
-      </c>
       <c r="J33" s="5">
-        <v>72.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>88.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>364000</v>
+        <v>228000</v>
       </c>
       <c r="G34" s="7">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H34" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="7">
-        <v>11571</v>
+        <v>11500</v>
       </c>
       <c r="J34" s="5">
-        <v>71.8</v>
+        <v>70.7</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>82.5</v>
+        <v>93.5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>330000</v>
+        <v>172000</v>
       </c>
       <c r="G35" s="7">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="H35" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I35" s="7">
-        <v>22429</v>
+        <v>16500</v>
       </c>
       <c r="J35" s="5">
-        <v>71</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>89.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>123000</v>
+        <v>101000</v>
       </c>
       <c r="G36" s="7">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I36" s="7">
-        <v>6571</v>
+        <v>1625</v>
       </c>
       <c r="J36" s="5">
-        <v>71</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>90.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>153000</v>
+        <v>128000</v>
       </c>
       <c r="G37" s="7">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="H37" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I37" s="7">
-        <v>11400</v>
+        <v>4875</v>
       </c>
       <c r="J37" s="5">
-        <v>70.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>89.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>101000</v>
+        <v>103000</v>
       </c>
       <c r="G38" s="7">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="H38" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>6429</v>
+        <v>3625</v>
       </c>
       <c r="J38" s="5">
-        <v>70.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>88.2</v>
+        <v>80.5</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>213000</v>
+        <v>342000</v>
       </c>
       <c r="G39" s="7">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="H39" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" s="7">
-        <v>7857</v>
+        <v>21125</v>
       </c>
       <c r="J39" s="5">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>81.8</v>
+        <v>86</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>352000</v>
+        <v>109000</v>
       </c>
       <c r="G40" s="7">
-        <v>19000</v>
+        <v>6000</v>
       </c>
       <c r="H40" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I40" s="7">
-        <v>21143</v>
+        <v>9375</v>
       </c>
       <c r="J40" s="5">
-        <v>70.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>84.8</v>
+        <v>80.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>298000</v>
+        <v>454000</v>
       </c>
       <c r="G41" s="7">
-        <v>27000</v>
+        <v>17000</v>
       </c>
       <c r="H41" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" s="7">
-        <v>14571</v>
+        <v>19500</v>
       </c>
       <c r="J41" s="5">
-        <v>70.3</v>
+        <v>69.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89.5</v>
+        <v>81.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>115000</v>
+        <v>278000</v>
       </c>
       <c r="G42" s="7">
-        <v>12000</v>
+        <v>34000</v>
       </c>
       <c r="H42" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>3714</v>
+        <v>18167</v>
       </c>
       <c r="J42" s="5">
-        <v>70.2</v>
+        <v>69.2</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>81.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>437000</v>
+        <v>199000</v>
       </c>
       <c r="G43" s="7">
-        <v>22000</v>
+        <v>6000</v>
       </c>
       <c r="H43" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I43" s="7">
-        <v>19857</v>
+        <v>8375</v>
       </c>
       <c r="J43" s="5">
-        <v>70</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>103000</v>
+        <v>164000</v>
       </c>
       <c r="G44" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H44" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I44" s="7">
-        <v>9857</v>
+        <v>10833</v>
       </c>
       <c r="J44" s="5">
-        <v>69.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>81.2</v>
+        <v>95.3</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>870000</v>
+        <v>110000</v>
       </c>
       <c r="G45" s="7">
         <v>13000</v>
       </c>
       <c r="H45" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>19143</v>
+        <v>18333</v>
       </c>
       <c r="J45" s="5">
-        <v>69.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>83.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>279000</v>
+        <v>250000</v>
       </c>
       <c r="G46" s="7">
-        <v>1000</v>
+        <v>59000</v>
       </c>
       <c r="H46" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I46" s="7">
-        <v>13714</v>
+        <v>9750</v>
       </c>
       <c r="J46" s="5">
-        <v>69.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>100</v>
+        <v>82.7</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>496000</v>
+        <v>446000</v>
       </c>
       <c r="G47" s="7">
-        <v>55000</v>
+        <v>19000</v>
       </c>
       <c r="H47" s="7">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>21000</v>
+        <v>12875</v>
       </c>
       <c r="J47" s="5">
-        <v>69.2</v>
+        <v>68.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>80.7</v>
+        <v>87</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>409000</v>
+        <v>288000</v>
       </c>
       <c r="G48" s="7">
-        <v>17000</v>
+        <v>4000</v>
       </c>
       <c r="H48" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>19286</v>
+        <v>3375</v>
       </c>
       <c r="J48" s="5">
-        <v>69.2</v>
+        <v>68.7</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>102000</v>
+        <v>277000</v>
       </c>
       <c r="G49" s="7">
-        <v>4000</v>
+        <v>-2000</v>
       </c>
       <c r="H49" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I49" s="7">
-        <v>6286</v>
+        <v>11750</v>
       </c>
       <c r="J49" s="5">
-        <v>69.2</v>
+        <v>68.7</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>94.8</v>
+        <v>90.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>135000</v>
+        <v>160000</v>
       </c>
       <c r="G50" s="7">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H50" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7">
-        <v>19667</v>
+        <v>15500</v>
       </c>
       <c r="J50" s="5">
-        <v>69.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>88.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>111000</v>
+        <v>105000</v>
       </c>
       <c r="G51" s="7">
         <v>4000</v>
       </c>
       <c r="H51" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I51" s="7">
-        <v>2429</v>
+        <v>6125</v>
       </c>
       <c r="J51" s="5">
-        <v>69.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>88.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>133000</v>
+        <v>317000</v>
       </c>
       <c r="G52" s="7">
-        <v>4000</v>
+        <v>19000</v>
       </c>
       <c r="H52" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I52" s="7">
-        <v>286</v>
+        <v>15125</v>
       </c>
       <c r="J52" s="5">
-        <v>68.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,23 +2345,23 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>75</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>603000</v>
+        <v>125000</v>
       </c>
       <c r="G53" s="7">
-        <v>21000</v>
+        <v>11000</v>
       </c>
       <c r="H53" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I53" s="7">
-        <v>29429</v>
+        <v>9600</v>
       </c>
       <c r="J53" s="5">
         <v>68.59999999999999</v>
@@ -2378,14 +2378,14 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>94.2</v>
+        <v>93.5</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>101000</v>
+        <v>141000</v>
       </c>
       <c r="G54" s="7">
         <v>16000</v>
@@ -2394,10 +2394,10 @@
         <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>19333</v>
+        <v>19667</v>
       </c>
       <c r="J54" s="5">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-22T01:41:54+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-23T01:51:57+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>别人穿四合院，我为啥上战场</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
     <t>我老婆有白月光？她怎么不知道</t>
   </si>
   <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
-    <t>神通者</t>
+    <t>退休勇者买下魔王当女仆</t>
+  </si>
+  <si>
+    <t>东北往事•关东娘们儿与土匪</t>
   </si>
   <si>
     <t>大唐长生者，但开局在玄武门？</t>
   </si>
   <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>站中间抽两边，什么叫霸之意志呀</t>
+  </si>
+  <si>
+    <t>开局盗大墓，系统让我去自首</t>
+  </si>
+  <si>
     <t>青梅是性转祖国人？可我是大超</t>
   </si>
   <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>穿越乱世：每天一份拼好饭</t>
+  </si>
+  <si>
+    <t>抑郁少女总想自杀？那就恶堕吧！</t>
+  </si>
+  <si>
+    <t>我都成烛龙了，人类怎么才诞生？</t>
+  </si>
+  <si>
+    <t>原神：破产之后只能加入愚人众了</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>警告！邪神眷属正在杀入诡异副本</t>
+  </si>
+  <si>
+    <t>顶级智斗：开局给小天寄石墩子</t>
+  </si>
+  <si>
+    <t>综漫：捡碎片的我开局拼出虚式茈</t>
+  </si>
+  <si>
+    <t>穿成丧尸小萝莉，凤傲天求放过</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>我只想砍死各位，或者被各位砍死</t>
+  </si>
+  <si>
+    <t>别人夺嫡偷偷来，我家皇帝下圣旨</t>
+  </si>
+  <si>
+    <t>灵气复苏：开局获得呼吸法</t>
+  </si>
+  <si>
+    <t>转生火影，卡普模版</t>
+  </si>
+  <si>
+    <t>相亲失败！我把精神小妹捧成天后</t>
+  </si>
+  <si>
+    <t>一战：我成了白毛德皇的治国轮椅</t>
+  </si>
+  <si>
+    <t>镇国驸马爷</t>
+  </si>
+  <si>
+    <t>大秦我带秦始皇长生不老</t>
+  </si>
+  <si>
+    <t>名义：我避开祁同伟几十年</t>
+  </si>
+  <si>
+    <t>反派老婆破产后，她们都盯上我？</t>
+  </si>
+  <si>
+    <t>盗墓手法太熟练，惊呆校花学姐！</t>
+  </si>
+  <si>
+    <t>一人：继承不良帅，拥兵三百万！</t>
+  </si>
+  <si>
+    <t>肝肝肝肝肝！往死里肝！</t>
+  </si>
+  <si>
+    <t>地球不允许我这么牛逼的存在！</t>
+  </si>
+  <si>
+    <t>港综：骆天虹亲哥，开局金刚不坏</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
+    <t>亮剑：军校毕业，我给老李当参谋</t>
+  </si>
+  <si>
+    <t>全员悍匪：你管这叫正经公司？</t>
+  </si>
+  <si>
+    <t>四合院：从红二十五开始进步</t>
+  </si>
+  <si>
+    <t>天幕直播，先辈看我躺平生活</t>
+  </si>
+  <si>
+    <t>旧日家族求生，我家族谱全是禁忌</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>两界倒爷：从1988到2025</t>
+  </si>
+  <si>
+    <t>远离男主保命！校花后宫倒追我？</t>
+  </si>
+  <si>
+    <t>高考后，我每天一亿美金零花钱</t>
+  </si>
+  <si>
     <t>时停起手，邪神也得给我跪下！</t>
-  </si>
-  <si>
-    <t>抑郁少女总想自杀？那就恶堕吧！</t>
-  </si>
-  <si>
-    <t>退休勇者买下魔王当女仆</t>
-  </si>
-  <si>
-    <t>站中间抽两边，什么叫霸之意志呀</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>开局盗大墓，系统让我去自首</t>
-  </si>
-  <si>
-    <t>警告！邪神眷属正在杀入诡异副本</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>名义：我避开祁同伟几十年</t>
-  </si>
-  <si>
-    <t>入学第一天，千金学姐成了我老婆</t>
-  </si>
-  <si>
-    <t>穿越乱世：每天一份拼好饭</t>
-  </si>
-  <si>
-    <t>东北往事•关东娘们儿与土匪</t>
-  </si>
-  <si>
-    <t>我只想砍死各位，或者被各位砍死</t>
-  </si>
-  <si>
-    <t>灵气复苏：开局获得呼吸法</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>我都成烛龙了，人类怎么才诞生？</t>
-  </si>
-  <si>
-    <t>转生火影，卡普模版</t>
-  </si>
-  <si>
-    <t>综漫：捡碎片的我开局拼出虚式茈</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>1985，出租车司机的悠闲生活</t>
-  </si>
-  <si>
-    <t>别人夺嫡偷偷来，我家皇帝下圣旨</t>
-  </si>
-  <si>
-    <t>穿成丧尸小萝莉，凤傲天求放过</t>
-  </si>
-  <si>
-    <t>一战：我成了白毛德皇的治国轮椅</t>
-  </si>
-  <si>
-    <t>五哈：千年家族曝光，误闯天家！</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>姐姐，轻点撩</t>
-  </si>
-  <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
-  </si>
-  <si>
-    <t>魔龙与地下城：恶龙请求出狱</t>
-  </si>
-  <si>
-    <t>亮剑：军校毕业，我给老李当参谋</t>
-  </si>
-  <si>
-    <t>抗战：这个系统不正经</t>
-  </si>
-  <si>
-    <t>小区求生：每人每天给我一块面包</t>
-  </si>
-  <si>
-    <t>重生后无敌，我开始养成女帝</t>
-  </si>
-  <si>
-    <t>四合院，开局我选入赘</t>
-  </si>
-  <si>
-    <t>港综：骆天虹亲哥，开局金刚不坏</t>
-  </si>
-  <si>
-    <t>肝肝肝肝肝！往死里肝！</t>
-  </si>
-  <si>
-    <t>大秦我带秦始皇长生不老</t>
-  </si>
-  <si>
-    <t>奥特：最强债主！借债十倍返还！</t>
-  </si>
-  <si>
-    <t>我根骨平庸，但分身都是绝世天才</t>
-  </si>
-  <si>
-    <t>相亲失败！我把精神小妹捧成天后</t>
-  </si>
-  <si>
-    <t>名义：梁璐逼婚？家父赵蒙生</t>
-  </si>
-  <si>
-    <t>盗墓手法太熟练，惊呆校花学姐！</t>
-  </si>
-  <si>
-    <t>奥特：天蝎座第一道光</t>
-  </si>
-  <si>
-    <t>开局模拟被打爆，金丹爆星什么鬼</t>
-  </si>
-  <si>
-    <t>反派老婆破产后，她们都盯上我？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>323000</v>
+        <v>10226000</v>
       </c>
       <c r="G5" s="7">
-        <v>36000</v>
+        <v>49000</v>
       </c>
       <c r="H5" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>34250</v>
+        <v>54000</v>
       </c>
       <c r="J5" s="5">
-        <v>83.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>99.59999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>408000</v>
+        <v>360000</v>
       </c>
       <c r="G6" s="7">
-        <v>45000</v>
+        <v>37000</v>
       </c>
       <c r="H6" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>53000</v>
+        <v>34556</v>
       </c>
       <c r="J6" s="5">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>291000</v>
+        <v>440000</v>
       </c>
       <c r="G7" s="7">
-        <v>37000</v>
+        <v>32000</v>
       </c>
       <c r="H7" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I7" s="7">
-        <v>29875</v>
+        <v>48800</v>
       </c>
       <c r="J7" s="5">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>95.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>10177000</v>
+        <v>319000</v>
       </c>
       <c r="G8" s="7">
-        <v>51000</v>
+        <v>28000</v>
       </c>
       <c r="H8" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I8" s="7">
-        <v>55250</v>
+        <v>29667</v>
       </c>
       <c r="J8" s="5">
-        <v>81.3</v>
+        <v>80.8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>92.2</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>583000</v>
+        <v>160000</v>
       </c>
       <c r="G9" s="7">
-        <v>93000</v>
+        <v>24000</v>
       </c>
       <c r="H9" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>37875</v>
+        <v>19500</v>
       </c>
       <c r="J9" s="5">
-        <v>80.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>271000</v>
+        <v>235000</v>
       </c>
       <c r="G10" s="7">
-        <v>21000</v>
+        <v>40000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>28167</v>
+        <v>13556</v>
       </c>
       <c r="J10" s="5">
-        <v>79.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>77.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>3319000</v>
+        <v>637000</v>
       </c>
       <c r="G11" s="7">
-        <v>-225000</v>
+        <v>54000</v>
       </c>
       <c r="H11" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11" s="7">
-        <v>58250</v>
+        <v>39667</v>
       </c>
       <c r="J11" s="5">
-        <v>77.2</v>
+        <v>78</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -997,19 +997,19 @@
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>577000</v>
+        <v>201000</v>
       </c>
       <c r="G12" s="7">
-        <v>81000</v>
+        <v>33000</v>
       </c>
       <c r="H12" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>41000</v>
+        <v>11111</v>
       </c>
       <c r="J12" s="5">
-        <v>77.2</v>
+        <v>77.8</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>99</v>
+        <v>91.5</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>136000</v>
+        <v>375000</v>
       </c>
       <c r="G13" s="7">
-        <v>23000</v>
+        <v>16000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I13" s="7">
-        <v>18600</v>
+        <v>24778</v>
       </c>
       <c r="J13" s="5">
-        <v>77.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>90.7</v>
+        <v>98</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>359000</v>
+        <v>118000</v>
       </c>
       <c r="G14" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H14" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14" s="7">
-        <v>25875</v>
+        <v>7778</v>
       </c>
       <c r="J14" s="5">
-        <v>76.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93.3</v>
+        <v>89.7</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>230000</v>
+        <v>280000</v>
       </c>
       <c r="G15" s="7">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="H15" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>18250</v>
+        <v>25429</v>
       </c>
       <c r="J15" s="5">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>98.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>104000</v>
+        <v>240000</v>
       </c>
       <c r="G16" s="7">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I16" s="7">
-        <v>7000</v>
+        <v>17333</v>
       </c>
       <c r="J16" s="5">
-        <v>75.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>80</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>496000</v>
+        <v>114000</v>
       </c>
       <c r="G17" s="7">
-        <v>23000</v>
+        <v>10000</v>
       </c>
       <c r="H17" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7">
-        <v>43286</v>
+        <v>10375</v>
       </c>
       <c r="J17" s="5">
-        <v>74.8</v>
+        <v>74.3</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>94.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>104000</v>
+        <v>877000</v>
       </c>
       <c r="G18" s="7">
-        <v>10000</v>
+        <v>26000</v>
       </c>
       <c r="H18" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I18" s="7">
-        <v>10429</v>
+        <v>34111</v>
       </c>
       <c r="J18" s="5">
-        <v>74.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>95.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>237000</v>
+        <v>592000</v>
       </c>
       <c r="G19" s="7">
-        <v>24000</v>
+        <v>15000</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>40000</v>
+        <v>34500</v>
       </c>
       <c r="J19" s="5">
-        <v>74.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>89.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>363000</v>
+        <v>172000</v>
       </c>
       <c r="G20" s="7">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>20750</v>
+        <v>19200</v>
       </c>
       <c r="J20" s="5">
-        <v>74.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>81.59999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>851000</v>
+        <v>151000</v>
       </c>
       <c r="G21" s="7">
         <v>23000</v>
       </c>
       <c r="H21" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21" s="7">
-        <v>35125</v>
+        <v>5778</v>
       </c>
       <c r="J21" s="5">
-        <v>73.7</v>
+        <v>73.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>92.8</v>
+        <v>92.5</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>195000</v>
+        <v>191000</v>
       </c>
       <c r="G22" s="7">
-        <v>13000</v>
+        <v>19000</v>
       </c>
       <c r="H22" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I22" s="7">
-        <v>10250</v>
+        <v>17000</v>
       </c>
       <c r="J22" s="5">
-        <v>73.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>618000</v>
+        <v>511000</v>
       </c>
       <c r="G23" s="7">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="H23" s="7">
         <v>9</v>
       </c>
       <c r="I23" s="7">
-        <v>38375</v>
+        <v>39750</v>
       </c>
       <c r="J23" s="5">
-        <v>72.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,23 +1386,23 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>116000</v>
+        <v>145000</v>
       </c>
       <c r="G24" s="7">
-        <v>7000</v>
+        <v>16000</v>
       </c>
       <c r="H24" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I24" s="7">
-        <v>8875</v>
+        <v>7500</v>
       </c>
       <c r="J24" s="5">
         <v>72.7</v>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>88.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>535000</v>
+        <v>171000</v>
       </c>
       <c r="G25" s="7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H25" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>13500</v>
+        <v>10714</v>
       </c>
       <c r="J25" s="5">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>94.2</v>
+        <v>91.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>154000</v>
+        <v>114000</v>
       </c>
       <c r="G26" s="7">
-        <v>19000</v>
+        <v>11000</v>
       </c>
       <c r="H26" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
-        <v>19500</v>
+        <v>16000</v>
       </c>
       <c r="J26" s="5">
-        <v>71.7</v>
+        <v>72.5</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>82.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>431000</v>
+        <v>539000</v>
       </c>
       <c r="G27" s="7">
-        <v>22000</v>
+        <v>4000</v>
       </c>
       <c r="H27" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>23875</v>
+        <v>12444</v>
       </c>
       <c r="J27" s="5">
-        <v>71.5</v>
+        <v>72.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>88.8</v>
+        <v>92.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>161000</v>
+        <v>142000</v>
       </c>
       <c r="G28" s="7">
-        <v>8000</v>
+        <v>14000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I28" s="7">
-        <v>10833</v>
+        <v>5889</v>
       </c>
       <c r="J28" s="5">
-        <v>71.5</v>
+        <v>72.3</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>89.8</v>
+        <v>78.8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>150000</v>
+        <v>622000</v>
       </c>
       <c r="G29" s="7">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="H29" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I29" s="7">
-        <v>8375</v>
+        <v>34556</v>
       </c>
       <c r="J29" s="5">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>103000</v>
+        <v>458000</v>
       </c>
       <c r="G30" s="7">
-        <v>6000</v>
+        <v>41000</v>
       </c>
       <c r="H30" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30" s="7">
-        <v>7500</v>
+        <v>15556</v>
       </c>
       <c r="J30" s="5">
-        <v>71.2</v>
+        <v>71.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87.3</v>
+        <v>88.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>417000</v>
+        <v>120000</v>
       </c>
       <c r="G31" s="7">
-        <v>41000</v>
+        <v>4000</v>
       </c>
       <c r="H31" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I31" s="7">
-        <v>12375</v>
+        <v>8333</v>
       </c>
       <c r="J31" s="5">
-        <v>71.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>94.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>103000</v>
+        <v>449000</v>
       </c>
       <c r="G32" s="7">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="H32" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I32" s="7">
-        <v>17250</v>
+        <v>23222</v>
       </c>
       <c r="J32" s="5">
-        <v>71.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1681,30 +1681,28 @@
       <c r="A33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="5">
-        <v>9.6</v>
-      </c>
+      <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>88</v>
+        <v>86.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>167000</v>
+        <v>285000</v>
       </c>
       <c r="G33" s="7">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="H33" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I33" s="7">
-        <v>10000</v>
+        <v>11333</v>
       </c>
       <c r="J33" s="5">
-        <v>70.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,28 +1714,30 @@
       <c r="A34" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="5"/>
+      <c r="B34" s="5">
+        <v>9.6</v>
+      </c>
       <c r="C34" s="5">
-        <v>87</v>
+        <v>86.7</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>228000</v>
+        <v>172000</v>
       </c>
       <c r="G34" s="7">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H34" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I34" s="7">
-        <v>11500</v>
+        <v>9444</v>
       </c>
       <c r="J34" s="5">
-        <v>70.7</v>
+        <v>70</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>93.5</v>
+        <v>80.8</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>172000</v>
+        <v>397000</v>
       </c>
       <c r="G35" s="7">
         <v>20000</v>
       </c>
       <c r="H35" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I35" s="7">
-        <v>16500</v>
+        <v>21778</v>
       </c>
       <c r="J35" s="5">
-        <v>70.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>90.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>101000</v>
+        <v>282000</v>
       </c>
       <c r="G36" s="7">
-        <v>15000</v>
+        <v>32000</v>
       </c>
       <c r="H36" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I36" s="7">
-        <v>1625</v>
+        <v>12222</v>
       </c>
       <c r="J36" s="5">
-        <v>70.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>89.3</v>
+        <v>85.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>128000</v>
+        <v>240000</v>
       </c>
       <c r="G37" s="7">
-        <v>13000</v>
+        <v>3000</v>
       </c>
       <c r="H37" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I37" s="7">
-        <v>4875</v>
+        <v>30750</v>
       </c>
       <c r="J37" s="5">
-        <v>70.3</v>
+        <v>69.8</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>88.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>103000</v>
+        <v>153000</v>
       </c>
       <c r="G38" s="7">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="H38" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I38" s="7">
-        <v>3625</v>
+        <v>17750</v>
       </c>
       <c r="J38" s="5">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>80.5</v>
+        <v>87.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>342000</v>
+        <v>109000</v>
       </c>
       <c r="G39" s="7">
-        <v>12000</v>
+        <v>4000</v>
       </c>
       <c r="H39" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>21125</v>
+        <v>5889</v>
       </c>
       <c r="J39" s="5">
-        <v>69.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86</v>
+        <v>89.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>109000</v>
+        <v>141000</v>
       </c>
       <c r="G40" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H40" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>9375</v>
+        <v>9000</v>
       </c>
       <c r="J40" s="5">
-        <v>69.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>80.5</v>
+        <v>91.2</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>454000</v>
+        <v>121000</v>
       </c>
       <c r="G41" s="7">
-        <v>17000</v>
+        <v>11000</v>
       </c>
       <c r="H41" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>19500</v>
+        <v>16500</v>
       </c>
       <c r="J41" s="5">
-        <v>69.2</v>
+        <v>69.3</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>81.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>278000</v>
+        <v>234000</v>
       </c>
       <c r="G42" s="7">
-        <v>34000</v>
+        <v>20000</v>
       </c>
       <c r="H42" s="7">
         <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>18167</v>
+        <v>14167</v>
       </c>
       <c r="J42" s="5">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>199000</v>
+        <v>172000</v>
       </c>
       <c r="G43" s="7">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="H43" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>8375</v>
+        <v>10429</v>
       </c>
       <c r="J43" s="5">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,23 +2048,23 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>84.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>164000</v>
+        <v>151000</v>
       </c>
       <c r="G44" s="7">
-        <v>11000</v>
+        <v>1000</v>
       </c>
       <c r="H44" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I44" s="7">
-        <v>10833</v>
+        <v>7556</v>
       </c>
       <c r="J44" s="5">
         <v>69</v>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>95.3</v>
+        <v>79.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>110000</v>
+        <v>352000</v>
       </c>
       <c r="G45" s="7">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="H45" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I45" s="7">
-        <v>18333</v>
+        <v>19889</v>
       </c>
       <c r="J45" s="5">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>84.5</v>
+        <v>83.3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>250000</v>
+        <v>216000</v>
       </c>
       <c r="G46" s="7">
-        <v>59000</v>
+        <v>29000</v>
       </c>
       <c r="H46" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I46" s="7">
-        <v>9750</v>
+        <v>12444</v>
       </c>
       <c r="J46" s="5">
         <v>68.90000000000001</v>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>82.7</v>
+        <v>85.7</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>446000</v>
+        <v>182000</v>
       </c>
       <c r="G47" s="7">
-        <v>19000</v>
+        <v>9000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I47" s="7">
-        <v>12875</v>
+        <v>15200</v>
       </c>
       <c r="J47" s="5">
-        <v>68.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87</v>
+        <v>87.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>288000</v>
+        <v>113000</v>
       </c>
       <c r="G48" s="7">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I48" s="7">
-        <v>3375</v>
+        <v>3000</v>
       </c>
       <c r="J48" s="5">
-        <v>68.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>83.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>277000</v>
+        <v>111000</v>
       </c>
       <c r="G49" s="7">
-        <v>-2000</v>
+        <v>6000</v>
       </c>
       <c r="H49" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I49" s="7">
-        <v>11750</v>
+        <v>6778</v>
       </c>
       <c r="J49" s="5">
-        <v>68.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>90.5</v>
+        <v>79.8</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>160000</v>
+        <v>373000</v>
       </c>
       <c r="G50" s="7">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="H50" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I50" s="7">
-        <v>15500</v>
+        <v>18778</v>
       </c>
       <c r="J50" s="5">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>105000</v>
+        <v>427000</v>
       </c>
       <c r="G51" s="7">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="H51" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I51" s="7">
-        <v>6125</v>
+        <v>23333</v>
       </c>
       <c r="J51" s="5">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>81.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>317000</v>
+        <v>241000</v>
       </c>
       <c r="G52" s="7">
-        <v>19000</v>
+        <v>-3000</v>
       </c>
       <c r="H52" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I52" s="7">
-        <v>15125</v>
+        <v>5222</v>
       </c>
       <c r="J52" s="5">
-        <v>68.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>87.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>125000</v>
+        <v>200000</v>
       </c>
       <c r="G53" s="7">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="H53" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I53" s="7">
-        <v>9600</v>
+        <v>1667</v>
       </c>
       <c r="J53" s="5">
-        <v>68.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>93.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>141000</v>
+        <v>3045000</v>
       </c>
       <c r="G54" s="7">
-        <v>16000</v>
+        <v>-274000</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I54" s="7">
-        <v>19667</v>
+        <v>21333</v>
       </c>
       <c r="J54" s="5">
-        <v>68.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-24T01:47:22+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-25T01:44:00+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-25T01:44:00+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-26T01:49:43+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -10,19 +10,19 @@
     <sheet name="作品数据" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="68">
   <si>
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-26T01:49:43+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-27T08:52:26+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -68,13 +68,170 @@
   </si>
   <si>
     <t>达标日期列表</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>让你荒淫无道，千古一帝什么鬼？</t>
+  </si>
+  <si>
+    <t>名义：我避开祁同伟几十年</t>
+  </si>
+  <si>
+    <t>穿书成富二代，我直接救赎女主</t>
+  </si>
+  <si>
+    <t>屠城就能回蓝星？兄弟你早说啊！</t>
+  </si>
+  <si>
+    <t>我都成烛龙了，人类怎么才诞生？</t>
+  </si>
+  <si>
+    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
+  </si>
+  <si>
+    <t>轮回修仙：从考科举开始</t>
+  </si>
+  <si>
+    <t>有钱有势回县城，开局睡了白月光</t>
+  </si>
+  <si>
+    <t>列车求生，我能升华一切！</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>我老婆有白月光？她怎么不知道</t>
+  </si>
+  <si>
+    <t>觉醒伪神，神明弃我，我自为神</t>
+  </si>
+  <si>
+    <t>站中间抽两边，什么叫霸之意志呀</t>
+  </si>
+  <si>
+    <t>我都成仙了，才来万界聊天群？</t>
+  </si>
+  <si>
+    <t>穿成丧尸小萝莉，凤傲天求放过</t>
+  </si>
+  <si>
+    <t>离婚后，我成了刀枪炮！</t>
+  </si>
+  <si>
+    <t>满分高考状元：我带全县暴富</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>三角洲：FPS暴君降临</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
+    <t>四合院：我表哥是神棍</t>
+  </si>
+  <si>
+    <t>我的绝世表嫂</t>
+  </si>
+  <si>
+    <t>女多男少，开局分配辅导员老婆</t>
+  </si>
+  <si>
+    <t>力量每天增加百分之一我徒手爆星</t>
+  </si>
+  <si>
+    <t>反派老婆破产后，她们都盯上我？</t>
+  </si>
+  <si>
+    <t>大唐：开局获得一次顶级箭术</t>
+  </si>
+  <si>
+    <t>肝肝肝肝肝！往死里肝！</t>
+  </si>
+  <si>
+    <t>大唐长生者，但开局在玄武门？</t>
+  </si>
+  <si>
+    <t>三体：我还以为是全知域呢！</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
+  </si>
+  <si>
+    <t>每天属性翻一倍，我黑化爆杀一切</t>
+  </si>
+  <si>
+    <t>退休勇者买下魔王当女仆</t>
+  </si>
+  <si>
+    <t>让你暑假实习，你去地府当鬼差！</t>
+  </si>
+  <si>
+    <t>穿越黄毛，女主们把我当白月光了</t>
+  </si>
+  <si>
+    <t>重生98：带百万兄弟搞工业</t>
+  </si>
+  <si>
+    <t>只想躺平开民宿，咋就活成顶流了</t>
+  </si>
+  <si>
+    <t>原神：破产之后只能加入愚人众了</t>
+  </si>
+  <si>
+    <t>变身顶美，有颜真能为所欲为</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>大秦我带秦始皇长生不老</t>
+  </si>
+  <si>
+    <t>玩弄感情的坏男孩就要被病娇狠狠</t>
+  </si>
+  <si>
+    <t>让你拍反腐片，你拍人民的名义！</t>
+  </si>
+  <si>
+    <t>欢迎都显怀了，你还没释怀</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>开局模拟被打爆，金丹爆星什么鬼</t>
+  </si>
+  <si>
+    <t>地球不允许我这么牛逼的存在！</t>
+  </si>
+  <si>
+    <t>不娶还敢撩？再跑就把你关起来</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +262,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -126,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -149,11 +314,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -163,6 +343,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -561,12 +753,1714 @@
         <v>16</v>
       </c>
     </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5">
+        <v>94.8</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7">
+        <v>669000</v>
+      </c>
+      <c r="G5" s="7">
+        <v>36000</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3</v>
+      </c>
+      <c r="I5" s="7">
+        <v>39500</v>
+      </c>
+      <c r="J5" s="5">
+        <v>71</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5">
+        <v>96.8</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="7">
+        <v>478000</v>
+      </c>
+      <c r="G6" s="7">
+        <v>37000</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3</v>
+      </c>
+      <c r="I6" s="7">
+        <v>31500</v>
+      </c>
+      <c r="J6" s="5">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5">
+        <v>86.8</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="7">
+        <v>331000</v>
+      </c>
+      <c r="G7" s="7">
+        <v>51000</v>
+      </c>
+      <c r="H7" s="7">
+        <v>3</v>
+      </c>
+      <c r="I7" s="7">
+        <v>53000</v>
+      </c>
+      <c r="J7" s="5">
+        <v>70</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5">
+        <v>97.3</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="7">
+        <v>325000</v>
+      </c>
+      <c r="G8" s="7">
+        <v>31000</v>
+      </c>
+      <c r="H8" s="7">
+        <v>3</v>
+      </c>
+      <c r="I8" s="7">
+        <v>28500</v>
+      </c>
+      <c r="J8" s="5">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5">
+        <v>99</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="7">
+        <v>197000</v>
+      </c>
+      <c r="G9" s="7">
+        <v>29000</v>
+      </c>
+      <c r="H9" s="7">
+        <v>3</v>
+      </c>
+      <c r="I9" s="7">
+        <v>23000</v>
+      </c>
+      <c r="J9" s="5">
+        <v>69.2</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="7">
+        <v>339000</v>
+      </c>
+      <c r="G10" s="7">
+        <v>25000</v>
+      </c>
+      <c r="H10" s="7">
+        <v>3</v>
+      </c>
+      <c r="I10" s="7">
+        <v>31000</v>
+      </c>
+      <c r="J10" s="5">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="7">
+        <v>245000</v>
+      </c>
+      <c r="G11" s="7">
+        <v>29000</v>
+      </c>
+      <c r="H11" s="7">
+        <v>3</v>
+      </c>
+      <c r="I11" s="7">
+        <v>21500</v>
+      </c>
+      <c r="J11" s="5">
+        <v>68.2</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5">
+        <v>100</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="7">
+        <v>136000</v>
+      </c>
+      <c r="G12" s="7">
+        <v>20000</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3</v>
+      </c>
+      <c r="I12" s="7">
+        <v>16500</v>
+      </c>
+      <c r="J12" s="5">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5">
+        <v>97.3</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="7">
+        <v>193000</v>
+      </c>
+      <c r="G13" s="7">
+        <v>24000</v>
+      </c>
+      <c r="H13" s="7">
+        <v>3</v>
+      </c>
+      <c r="I13" s="7">
+        <v>19500</v>
+      </c>
+      <c r="J13" s="5">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5">
+        <v>95.7</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="7">
+        <v>211000</v>
+      </c>
+      <c r="G14" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>3</v>
+      </c>
+      <c r="I14" s="7">
+        <v>18500</v>
+      </c>
+      <c r="J14" s="5">
+        <v>66.3</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="7">
+        <v>682000</v>
+      </c>
+      <c r="G15" s="7">
+        <v>37000</v>
+      </c>
+      <c r="H15" s="7">
+        <v>3</v>
+      </c>
+      <c r="I15" s="7">
+        <v>38500</v>
+      </c>
+      <c r="J15" s="5">
+        <v>65.3</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="7">
+        <v>413000</v>
+      </c>
+      <c r="G16" s="7">
+        <v>41000</v>
+      </c>
+      <c r="H16" s="7">
+        <v>3</v>
+      </c>
+      <c r="I16" s="7">
+        <v>42000</v>
+      </c>
+      <c r="J16" s="5">
+        <v>64.8</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5">
+        <v>92.2</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="7">
+        <v>438000</v>
+      </c>
+      <c r="G17" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H17" s="7">
+        <v>3</v>
+      </c>
+      <c r="I17" s="7">
+        <v>20000</v>
+      </c>
+      <c r="J17" s="5">
+        <v>64.7</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="7">
+        <v>494000</v>
+      </c>
+      <c r="G18" s="7">
+        <v>27000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>3</v>
+      </c>
+      <c r="I18" s="7">
+        <v>17000</v>
+      </c>
+      <c r="J18" s="5">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="7">
+        <v>476000</v>
+      </c>
+      <c r="G19" s="7">
+        <v>48000</v>
+      </c>
+      <c r="H19" s="7">
+        <v>3</v>
+      </c>
+      <c r="I19" s="7">
+        <v>45500</v>
+      </c>
+      <c r="J19" s="5">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="7">
+        <v>423000</v>
+      </c>
+      <c r="G20" s="7">
+        <v>22000</v>
+      </c>
+      <c r="H20" s="7">
+        <v>3</v>
+      </c>
+      <c r="I20" s="7">
+        <v>16500</v>
+      </c>
+      <c r="J20" s="5">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5">
+        <v>93.3</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="7">
+        <v>146000</v>
+      </c>
+      <c r="G21" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>3</v>
+      </c>
+      <c r="I21" s="7">
+        <v>16500</v>
+      </c>
+      <c r="J21" s="5">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="7">
+        <v>157000</v>
+      </c>
+      <c r="G22" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H22" s="7">
+        <v>3</v>
+      </c>
+      <c r="I22" s="7">
+        <v>12000</v>
+      </c>
+      <c r="J22" s="5">
+        <v>64.2</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="7">
+        <v>234000</v>
+      </c>
+      <c r="G23" s="7">
+        <v>16000</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>20000</v>
+      </c>
+      <c r="J23" s="5">
+        <v>64</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="7">
+        <v>105000</v>
+      </c>
+      <c r="G24" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>3</v>
+      </c>
+      <c r="I24" s="7">
+        <v>10500</v>
+      </c>
+      <c r="J24" s="5">
+        <v>63.9</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="7">
+        <v>167000</v>
+      </c>
+      <c r="G25" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H25" s="7">
+        <v>3</v>
+      </c>
+      <c r="I25" s="7">
+        <v>12500</v>
+      </c>
+      <c r="J25" s="5">
+        <v>63.8</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5">
+        <v>85.5</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="7">
+        <v>267000</v>
+      </c>
+      <c r="G26" s="7">
+        <v>28000</v>
+      </c>
+      <c r="H26" s="7">
+        <v>3</v>
+      </c>
+      <c r="I26" s="7">
+        <v>30000</v>
+      </c>
+      <c r="J26" s="5">
+        <v>63.5</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5">
+        <v>93.3</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="7">
+        <v>177000</v>
+      </c>
+      <c r="G27" s="7">
+        <v>13000</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3</v>
+      </c>
+      <c r="I27" s="7">
+        <v>11500</v>
+      </c>
+      <c r="J27" s="5">
+        <v>63.2</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="7">
+        <v>252000</v>
+      </c>
+      <c r="G28" s="7">
+        <v>14000</v>
+      </c>
+      <c r="H28" s="7">
+        <v>3</v>
+      </c>
+      <c r="I28" s="7">
+        <v>17500</v>
+      </c>
+      <c r="J28" s="5">
+        <v>63.1</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5">
+        <v>79.8</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="7">
+        <v>536000</v>
+      </c>
+      <c r="G29" s="7">
+        <v>31000</v>
+      </c>
+      <c r="H29" s="7">
+        <v>3</v>
+      </c>
+      <c r="I29" s="7">
+        <v>40500</v>
+      </c>
+      <c r="J29" s="5">
+        <v>63</v>
+      </c>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5">
+        <v>89</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="7">
+        <v>138000</v>
+      </c>
+      <c r="G30" s="7">
+        <v>30000</v>
+      </c>
+      <c r="H30" s="7">
+        <v>3</v>
+      </c>
+      <c r="I30" s="7">
+        <v>20000</v>
+      </c>
+      <c r="J30" s="5">
+        <v>63</v>
+      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="7">
+        <v>406000</v>
+      </c>
+      <c r="G31" s="7">
+        <v>32000</v>
+      </c>
+      <c r="H31" s="7">
+        <v>3</v>
+      </c>
+      <c r="I31" s="7">
+        <v>34500</v>
+      </c>
+      <c r="J31" s="5">
+        <v>62.9</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5">
+        <v>92.3</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="7">
+        <v>202000</v>
+      </c>
+      <c r="G32" s="7">
+        <v>14000</v>
+      </c>
+      <c r="H32" s="7">
+        <v>3</v>
+      </c>
+      <c r="I32" s="7">
+        <v>12000</v>
+      </c>
+      <c r="J32" s="5">
+        <v>62.8</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5">
+        <v>92.8</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="7">
+        <v>123000</v>
+      </c>
+      <c r="G33" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H33" s="7">
+        <v>3</v>
+      </c>
+      <c r="I33" s="7">
+        <v>10500</v>
+      </c>
+      <c r="J33" s="5">
+        <v>62.7</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="7">
+        <v>160000</v>
+      </c>
+      <c r="G34" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H34" s="7">
+        <v>3</v>
+      </c>
+      <c r="I34" s="7">
+        <v>9500</v>
+      </c>
+      <c r="J34" s="5">
+        <v>62.3</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5">
+        <v>83.3</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="7">
+        <v>774000</v>
+      </c>
+      <c r="G35" s="7">
+        <v>29000</v>
+      </c>
+      <c r="H35" s="7">
+        <v>3</v>
+      </c>
+      <c r="I35" s="7">
+        <v>29500</v>
+      </c>
+      <c r="J35" s="5">
+        <v>62.2</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="7">
+        <v>171000</v>
+      </c>
+      <c r="G36" s="7">
+        <v>13000</v>
+      </c>
+      <c r="H36" s="7">
+        <v>3</v>
+      </c>
+      <c r="I36" s="7">
+        <v>14500</v>
+      </c>
+      <c r="J36" s="5">
+        <v>61.4</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5">
+        <v>85.8</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="7">
+        <v>233000</v>
+      </c>
+      <c r="G37" s="7">
+        <v>27000</v>
+      </c>
+      <c r="H37" s="7">
+        <v>3</v>
+      </c>
+      <c r="I37" s="7">
+        <v>19500</v>
+      </c>
+      <c r="J37" s="5">
+        <v>61.1</v>
+      </c>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5">
+        <v>89.8</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="7">
+        <v>317000</v>
+      </c>
+      <c r="G38" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H38" s="7">
+        <v>3</v>
+      </c>
+      <c r="I38" s="7">
+        <v>10500</v>
+      </c>
+      <c r="J38" s="5">
+        <v>61</v>
+      </c>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="7">
+        <v>209000</v>
+      </c>
+      <c r="G39" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H39" s="7">
+        <v>3</v>
+      </c>
+      <c r="I39" s="7">
+        <v>8500</v>
+      </c>
+      <c r="J39" s="5">
+        <v>61</v>
+      </c>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5">
+        <v>85.5</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="7">
+        <v>171000</v>
+      </c>
+      <c r="G40" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H40" s="7">
+        <v>3</v>
+      </c>
+      <c r="I40" s="7">
+        <v>18500</v>
+      </c>
+      <c r="J40" s="5">
+        <v>60.7</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5">
+        <v>90.2</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="7">
+        <v>108000</v>
+      </c>
+      <c r="G41" s="7">
+        <v>12000</v>
+      </c>
+      <c r="H41" s="7">
+        <v>3</v>
+      </c>
+      <c r="I41" s="7">
+        <v>8500</v>
+      </c>
+      <c r="J41" s="5">
+        <v>60.7</v>
+      </c>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="7">
+        <v>124000</v>
+      </c>
+      <c r="G42" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H42" s="7">
+        <v>3</v>
+      </c>
+      <c r="I42" s="7">
+        <v>7000</v>
+      </c>
+      <c r="J42" s="5">
+        <v>60.6</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="7">
+        <v>521000</v>
+      </c>
+      <c r="G43" s="7">
+        <v>28000</v>
+      </c>
+      <c r="H43" s="7">
+        <v>3</v>
+      </c>
+      <c r="I43" s="7">
+        <v>27000</v>
+      </c>
+      <c r="J43" s="5">
+        <v>60.2</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5">
+        <v>90.2</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="7">
+        <v>187000</v>
+      </c>
+      <c r="G44" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H44" s="7">
+        <v>3</v>
+      </c>
+      <c r="I44" s="7">
+        <v>6500</v>
+      </c>
+      <c r="J44" s="5">
+        <v>60.2</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="7">
+        <v>123000</v>
+      </c>
+      <c r="G45" s="7">
+        <v>31000</v>
+      </c>
+      <c r="H45" s="7">
+        <v>3</v>
+      </c>
+      <c r="I45" s="7">
+        <v>18000</v>
+      </c>
+      <c r="J45" s="5">
+        <v>60</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="4"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="7">
+        <v>271000</v>
+      </c>
+      <c r="G46" s="7">
+        <v>6000</v>
+      </c>
+      <c r="H46" s="7">
+        <v>3</v>
+      </c>
+      <c r="I46" s="7">
+        <v>6000</v>
+      </c>
+      <c r="J46" s="5">
+        <v>59.7</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5">
+        <v>82</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="7">
+        <v>376000</v>
+      </c>
+      <c r="G47" s="7">
+        <v>26000</v>
+      </c>
+      <c r="H47" s="7">
+        <v>3</v>
+      </c>
+      <c r="I47" s="7">
+        <v>22000</v>
+      </c>
+      <c r="J47" s="5">
+        <v>59.6</v>
+      </c>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5">
+        <v>88.3</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="7">
+        <v>122000</v>
+      </c>
+      <c r="G48" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H48" s="7">
+        <v>3</v>
+      </c>
+      <c r="I48" s="7">
+        <v>8000</v>
+      </c>
+      <c r="J48" s="5">
+        <v>59.6</v>
+      </c>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5">
+        <v>80.7</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="7">
+        <v>502000</v>
+      </c>
+      <c r="G49" s="7">
+        <v>30000</v>
+      </c>
+      <c r="H49" s="7">
+        <v>3</v>
+      </c>
+      <c r="I49" s="7">
+        <v>24500</v>
+      </c>
+      <c r="J49" s="5">
+        <v>59.5</v>
+      </c>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="4"/>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5">
+        <v>89.2</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="7">
+        <v>164000</v>
+      </c>
+      <c r="G50" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H50" s="7">
+        <v>3</v>
+      </c>
+      <c r="I50" s="7">
+        <v>5000</v>
+      </c>
+      <c r="J50" s="5">
+        <v>59.3</v>
+      </c>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="4"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5">
+        <v>87</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="7">
+        <v>160000</v>
+      </c>
+      <c r="G51" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H51" s="7">
+        <v>3</v>
+      </c>
+      <c r="I51" s="7">
+        <v>9000</v>
+      </c>
+      <c r="J51" s="5">
+        <v>59.1</v>
+      </c>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="4"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5">
+        <v>87</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="7">
+        <v>154000</v>
+      </c>
+      <c r="G52" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H52" s="7">
+        <v>3</v>
+      </c>
+      <c r="I52" s="7">
+        <v>9000</v>
+      </c>
+      <c r="J52" s="5">
+        <v>59.1</v>
+      </c>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="4"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="7">
+        <v>297000</v>
+      </c>
+      <c r="G53" s="7">
+        <v>20000</v>
+      </c>
+      <c r="H53" s="7">
+        <v>3</v>
+      </c>
+      <c r="I53" s="7">
+        <v>16500</v>
+      </c>
+      <c r="J53" s="5">
+        <v>58.7</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="4"/>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5">
+        <v>87</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="7">
+        <v>108000</v>
+      </c>
+      <c r="G54" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H54" s="7">
+        <v>3</v>
+      </c>
+      <c r="I54" s="7">
+        <v>7000</v>
+      </c>
+      <c r="J54" s="5">
+        <v>58.6</v>
+      </c>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O5"/>
+  <autoFilter ref="A4:O54"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1"/>
+    <hyperlink ref="E6" r:id="rId2"/>
+    <hyperlink ref="E7" r:id="rId3"/>
+    <hyperlink ref="E8" r:id="rId4"/>
+    <hyperlink ref="E9" r:id="rId5"/>
+    <hyperlink ref="E10" r:id="rId6"/>
+    <hyperlink ref="E11" r:id="rId7"/>
+    <hyperlink ref="E12" r:id="rId8"/>
+    <hyperlink ref="E13" r:id="rId9"/>
+    <hyperlink ref="E14" r:id="rId10"/>
+    <hyperlink ref="E15" r:id="rId11"/>
+    <hyperlink ref="E16" r:id="rId12"/>
+    <hyperlink ref="E17" r:id="rId13"/>
+    <hyperlink ref="E18" r:id="rId14"/>
+    <hyperlink ref="E19" r:id="rId15"/>
+    <hyperlink ref="E20" r:id="rId16"/>
+    <hyperlink ref="E21" r:id="rId17"/>
+    <hyperlink ref="E22" r:id="rId18"/>
+    <hyperlink ref="E23" r:id="rId19"/>
+    <hyperlink ref="E24" r:id="rId20"/>
+    <hyperlink ref="E25" r:id="rId21"/>
+    <hyperlink ref="E26" r:id="rId22"/>
+    <hyperlink ref="E27" r:id="rId23"/>
+    <hyperlink ref="E28" r:id="rId24"/>
+    <hyperlink ref="E29" r:id="rId25"/>
+    <hyperlink ref="E30" r:id="rId26"/>
+    <hyperlink ref="E31" r:id="rId27"/>
+    <hyperlink ref="E32" r:id="rId28"/>
+    <hyperlink ref="E33" r:id="rId29"/>
+    <hyperlink ref="E34" r:id="rId30"/>
+    <hyperlink ref="E35" r:id="rId31"/>
+    <hyperlink ref="E36" r:id="rId32"/>
+    <hyperlink ref="E37" r:id="rId33"/>
+    <hyperlink ref="E38" r:id="rId34"/>
+    <hyperlink ref="E39" r:id="rId35"/>
+    <hyperlink ref="E40" r:id="rId36"/>
+    <hyperlink ref="E41" r:id="rId37"/>
+    <hyperlink ref="E42" r:id="rId38"/>
+    <hyperlink ref="E43" r:id="rId39"/>
+    <hyperlink ref="E44" r:id="rId40"/>
+    <hyperlink ref="E45" r:id="rId41"/>
+    <hyperlink ref="E46" r:id="rId42"/>
+    <hyperlink ref="E47" r:id="rId43"/>
+    <hyperlink ref="E48" r:id="rId44"/>
+    <hyperlink ref="E49" r:id="rId45"/>
+    <hyperlink ref="E50" r:id="rId46"/>
+    <hyperlink ref="E51" r:id="rId47"/>
+    <hyperlink ref="E52" r:id="rId48"/>
+    <hyperlink ref="E53" r:id="rId49"/>
+    <hyperlink ref="E54" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-27T08:52:26+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-28T11:05:19+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>名义：我避开祁同伟几十年</t>
+  </si>
+  <si>
+    <t>我老婆有白月光？她怎么不知道</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>穿书成富二代，我直接救赎女主</t>
+  </si>
+  <si>
+    <t>我都成烛龙了，人类怎么才诞生？</t>
+  </si>
+  <si>
+    <t>屠城就能回蓝星？兄弟你早说啊！</t>
+  </si>
+  <si>
+    <t>让你荒淫无道，千古一帝什么鬼？</t>
+  </si>
+  <si>
+    <t>离婚后，我成了刀枪炮！</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>女多男少，开局分配辅导员老婆</t>
+  </si>
+  <si>
+    <t>让你拍反腐片，你拍人民的名义！</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>穿成丧尸小萝莉，凤傲天求放过</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
     <t>名义：开局我举报我自己</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>别人穿四合院，我为啥上战场</t>
-  </si>
-  <si>
-    <t>让你荒淫无道，千古一帝什么鬼？</t>
-  </si>
-  <si>
-    <t>名义：我避开祁同伟几十年</t>
-  </si>
-  <si>
-    <t>穿书成富二代，我直接救赎女主</t>
-  </si>
-  <si>
-    <t>屠城就能回蓝星？兄弟你早说啊！</t>
-  </si>
-  <si>
-    <t>我都成烛龙了，人类怎么才诞生？</t>
-  </si>
-  <si>
-    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
-  </si>
-  <si>
     <t>轮回修仙：从考科举开始</t>
   </si>
   <si>
+    <t>大唐长生者，但开局在玄武门？</t>
+  </si>
+  <si>
+    <t>三角洲：FPS暴君降临</t>
+  </si>
+  <si>
+    <t>欢迎都显怀了，你还没释怀</t>
+  </si>
+  <si>
+    <t>三体：我还以为是全知域呢！</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>反派老婆破产后，她们都盯上我？</t>
+  </si>
+  <si>
+    <t>大秦我带秦始皇长生不老</t>
+  </si>
+  <si>
     <t>有钱有势回县城，开局睡了白月光</t>
   </si>
   <si>
+    <t>名柯：我有三角洲召唤系统</t>
+  </si>
+  <si>
     <t>列车求生，我能升华一切！</t>
   </si>
   <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
     <t>猎魔人小姐，我真不是血族</t>
   </si>
   <si>
-    <t>我老婆有白月光？她怎么不知道</t>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
+  </si>
+  <si>
+    <t>魔法？我钢铁洪流直接平推！</t>
+  </si>
+  <si>
+    <t>我都成仙了，才来万界聊天群？</t>
   </si>
   <si>
     <t>觉醒伪神，神明弃我，我自为神</t>
   </si>
   <si>
-    <t>站中间抽两边，什么叫霸之意志呀</t>
-  </si>
-  <si>
-    <t>我都成仙了，才来万界聊天群？</t>
-  </si>
-  <si>
-    <t>穿成丧尸小萝莉，凤傲天求放过</t>
-  </si>
-  <si>
-    <t>离婚后，我成了刀枪炮！</t>
+    <t>末世重生，成为核电站供能无限</t>
+  </si>
+  <si>
+    <t>下载APP，才发现青梅好感爆了</t>
+  </si>
+  <si>
+    <t>让你暑假实习，你去地府当鬼差！</t>
+  </si>
+  <si>
+    <t>民国：张家逆子，我才是东北王</t>
+  </si>
+  <si>
+    <t>死亡游戏：开局欺诈师，假扮神明</t>
+  </si>
+  <si>
+    <t>不对劲，我穿越的都是里世界</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>堕落女主们和我一起腐烂</t>
+  </si>
+  <si>
+    <t>开局流落皇子，可我已经人间无敌</t>
+  </si>
+  <si>
+    <t>四合院：我表哥是神棍</t>
+  </si>
+  <si>
+    <t>神话1900：开局获得诅咒词条</t>
+  </si>
+  <si>
+    <t>九门：刚混成副官，师尊找来了？</t>
+  </si>
+  <si>
+    <t>开局豪门继承人，怎么还要上恋综</t>
+  </si>
+  <si>
+    <t>洪荒：我盘古第四清，帮场通天！</t>
   </si>
   <si>
     <t>满分高考状元：我带全县暴富</t>
   </si>
   <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>三角洲：FPS暴君降临</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>四合院：我表哥是神棍</t>
-  </si>
-  <si>
-    <t>我的绝世表嫂</t>
-  </si>
-  <si>
-    <t>女多男少，开局分配辅导员老婆</t>
-  </si>
-  <si>
-    <t>力量每天增加百分之一我徒手爆星</t>
-  </si>
-  <si>
-    <t>反派老婆破产后，她们都盯上我？</t>
-  </si>
-  <si>
-    <t>大唐：开局获得一次顶级箭术</t>
-  </si>
-  <si>
-    <t>肝肝肝肝肝！往死里肝！</t>
-  </si>
-  <si>
-    <t>大唐长生者，但开局在玄武门？</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>每天属性翻一倍，我黑化爆杀一切</t>
-  </si>
-  <si>
-    <t>退休勇者买下魔王当女仆</t>
-  </si>
-  <si>
-    <t>让你暑假实习，你去地府当鬼差！</t>
-  </si>
-  <si>
-    <t>穿越黄毛，女主们把我当白月光了</t>
-  </si>
-  <si>
-    <t>重生98：带百万兄弟搞工业</t>
-  </si>
-  <si>
-    <t>只想躺平开民宿，咋就活成顶流了</t>
-  </si>
-  <si>
-    <t>原神：破产之后只能加入愚人众了</t>
-  </si>
-  <si>
-    <t>变身顶美，有颜真能为所欲为</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>大秦我带秦始皇长生不老</t>
-  </si>
-  <si>
-    <t>玩弄感情的坏男孩就要被病娇狠狠</t>
-  </si>
-  <si>
-    <t>让你拍反腐片，你拍人民的名义！</t>
-  </si>
-  <si>
-    <t>欢迎都显怀了，你还没释怀</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>开局模拟被打爆，金丹爆星什么鬼</t>
-  </si>
-  <si>
-    <t>地球不允许我这么牛逼的存在！</t>
-  </si>
-  <si>
-    <t>不娶还敢撩？再跑就把你关起来</t>
+    <t>四合院：从红二十五开始进步</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>669000</v>
+        <v>211000</v>
       </c>
       <c r="G5" s="7">
+        <v>75000</v>
+      </c>
+      <c r="H5" s="7">
+        <v>4</v>
+      </c>
+      <c r="I5" s="7">
         <v>36000</v>
       </c>
-      <c r="H5" s="7">
-        <v>3</v>
-      </c>
-      <c r="I5" s="7">
-        <v>39500</v>
-      </c>
       <c r="J5" s="5">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>478000</v>
+        <v>368000</v>
       </c>
       <c r="G6" s="7">
-        <v>37000</v>
+        <v>43000</v>
       </c>
       <c r="H6" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="7">
-        <v>31500</v>
+        <v>33333</v>
       </c>
       <c r="J6" s="5">
-        <v>70.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>86.8</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>331000</v>
+        <v>555000</v>
       </c>
       <c r="G7" s="7">
-        <v>51000</v>
+        <v>61000</v>
       </c>
       <c r="H7" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" s="7">
-        <v>53000</v>
+        <v>31667</v>
       </c>
       <c r="J7" s="5">
-        <v>70</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>325000</v>
+        <v>446000</v>
       </c>
       <c r="G8" s="7">
-        <v>31000</v>
+        <v>89000</v>
       </c>
       <c r="H8" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
-        <v>28500</v>
+        <v>30333</v>
       </c>
       <c r="J8" s="5">
-        <v>69.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>197000</v>
+        <v>236000</v>
       </c>
       <c r="G9" s="7">
-        <v>29000</v>
+        <v>39000</v>
       </c>
       <c r="H9" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7">
-        <v>23000</v>
+        <v>28333</v>
       </c>
       <c r="J9" s="5">
-        <v>69.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>339000</v>
+        <v>286000</v>
       </c>
       <c r="G10" s="7">
-        <v>25000</v>
+        <v>41000</v>
       </c>
       <c r="H10" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7">
-        <v>31000</v>
+        <v>28000</v>
       </c>
       <c r="J10" s="5">
-        <v>68.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>97.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>245000</v>
+        <v>377000</v>
       </c>
       <c r="G11" s="7">
-        <v>29000</v>
+        <v>38000</v>
       </c>
       <c r="H11" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="7">
-        <v>21500</v>
+        <v>33333</v>
       </c>
       <c r="J11" s="5">
-        <v>68.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>100</v>
+        <v>88.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>136000</v>
+        <v>381000</v>
       </c>
       <c r="G12" s="7">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="H12" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="7">
-        <v>16500</v>
+        <v>52000</v>
       </c>
       <c r="J12" s="5">
-        <v>68.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>97.3</v>
+        <v>99.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>193000</v>
+        <v>276000</v>
       </c>
       <c r="G13" s="7">
-        <v>24000</v>
+        <v>42000</v>
       </c>
       <c r="H13" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="7">
-        <v>19500</v>
+        <v>27333</v>
       </c>
       <c r="J13" s="5">
-        <v>67.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>95.7</v>
+        <v>98.5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>211000</v>
+        <v>156000</v>
       </c>
       <c r="G14" s="7">
-        <v>19000</v>
+        <v>60000</v>
       </c>
       <c r="H14" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I14" s="7">
-        <v>18500</v>
+        <v>26333</v>
       </c>
       <c r="J14" s="5">
-        <v>66.3</v>
+        <v>72.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>84.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>682000</v>
+        <v>509000</v>
       </c>
       <c r="G15" s="7">
-        <v>37000</v>
+        <v>31000</v>
       </c>
       <c r="H15" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7">
-        <v>38500</v>
+        <v>31333</v>
       </c>
       <c r="J15" s="5">
-        <v>65.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>82.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>413000</v>
+        <v>189000</v>
       </c>
       <c r="G16" s="7">
-        <v>41000</v>
+        <v>51000</v>
       </c>
       <c r="H16" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7">
-        <v>42000</v>
+        <v>30333</v>
       </c>
       <c r="J16" s="5">
-        <v>64.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92.2</v>
+        <v>90.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>438000</v>
+        <v>576000</v>
       </c>
       <c r="G17" s="7">
-        <v>17000</v>
+        <v>74000</v>
       </c>
       <c r="H17" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="7">
-        <v>20000</v>
+        <v>41000</v>
       </c>
       <c r="J17" s="5">
-        <v>64.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>93.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>494000</v>
+        <v>471000</v>
       </c>
       <c r="G18" s="7">
-        <v>27000</v>
+        <v>58000</v>
       </c>
       <c r="H18" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="7">
-        <v>17000</v>
+        <v>47333</v>
       </c>
       <c r="J18" s="5">
-        <v>64.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>80.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>476000</v>
+        <v>193000</v>
       </c>
       <c r="G19" s="7">
-        <v>48000</v>
+        <v>36000</v>
       </c>
       <c r="H19" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
-        <v>45500</v>
+        <v>20000</v>
       </c>
       <c r="J19" s="5">
-        <v>64.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>93.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>423000</v>
+        <v>209000</v>
       </c>
       <c r="G20" s="7">
-        <v>22000</v>
+        <v>32000</v>
       </c>
       <c r="H20" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="7">
-        <v>16500</v>
+        <v>18333</v>
       </c>
       <c r="J20" s="5">
-        <v>64.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>93.3</v>
+        <v>92.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>146000</v>
+        <v>691000</v>
       </c>
       <c r="G21" s="7">
-        <v>19000</v>
+        <v>22000</v>
       </c>
       <c r="H21" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="7">
-        <v>16500</v>
+        <v>33667</v>
       </c>
       <c r="J21" s="5">
-        <v>64.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>94.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>157000</v>
+        <v>222000</v>
       </c>
       <c r="G22" s="7">
-        <v>15000</v>
+        <v>29000</v>
       </c>
       <c r="H22" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="7">
-        <v>12000</v>
+        <v>22667</v>
       </c>
       <c r="J22" s="5">
-        <v>64.2</v>
+        <v>71.3</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>90.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>234000</v>
+        <v>841000</v>
       </c>
       <c r="G23" s="7">
-        <v>16000</v>
+        <v>67000</v>
       </c>
       <c r="H23" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="7">
-        <v>20000</v>
+        <v>42000</v>
       </c>
       <c r="J23" s="5">
-        <v>64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>95.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>105000</v>
+        <v>319000</v>
       </c>
       <c r="G24" s="7">
-        <v>11000</v>
+        <v>52000</v>
       </c>
       <c r="H24" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="7">
-        <v>10500</v>
+        <v>37333</v>
       </c>
       <c r="J24" s="5">
-        <v>63.9</v>
+        <v>70.8</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>167000</v>
+        <v>196000</v>
       </c>
       <c r="G25" s="7">
-        <v>12000</v>
+        <v>32000</v>
       </c>
       <c r="H25" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="7">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="J25" s="5">
-        <v>63.8</v>
+        <v>70.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>85.5</v>
+        <v>95.7</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>267000</v>
+        <v>198000</v>
       </c>
       <c r="G26" s="7">
-        <v>28000</v>
+        <v>27000</v>
       </c>
       <c r="H26" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26" s="7">
-        <v>30000</v>
+        <v>18667</v>
       </c>
       <c r="J26" s="5">
-        <v>63.5</v>
+        <v>69.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>93.3</v>
+        <v>98.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>177000</v>
+        <v>236000</v>
       </c>
       <c r="G27" s="7">
-        <v>13000</v>
+        <v>35000</v>
       </c>
       <c r="H27" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="7">
-        <v>11500</v>
+        <v>11333</v>
       </c>
       <c r="J27" s="5">
-        <v>63.2</v>
+        <v>69</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>90.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>252000</v>
+        <v>225000</v>
       </c>
       <c r="G28" s="7">
-        <v>14000</v>
+        <v>23000</v>
       </c>
       <c r="H28" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="7">
-        <v>17500</v>
+        <v>15667</v>
       </c>
       <c r="J28" s="5">
-        <v>63.1</v>
+        <v>69</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>79.8</v>
+        <v>88.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>536000</v>
+        <v>428000</v>
       </c>
       <c r="G29" s="7">
-        <v>31000</v>
+        <v>52000</v>
       </c>
       <c r="H29" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="7">
-        <v>40500</v>
+        <v>32000</v>
       </c>
       <c r="J29" s="5">
-        <v>63</v>
+        <v>68.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89</v>
+        <v>93.5</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>138000</v>
+        <v>227000</v>
       </c>
       <c r="G30" s="7">
-        <v>30000</v>
+        <v>16000</v>
       </c>
       <c r="H30" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" s="7">
-        <v>20000</v>
+        <v>17667</v>
       </c>
       <c r="J30" s="5">
-        <v>63</v>
+        <v>67.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>82.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>406000</v>
+        <v>145000</v>
       </c>
       <c r="G31" s="7">
-        <v>32000</v>
+        <v>27000</v>
       </c>
       <c r="H31" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="7">
-        <v>34500</v>
+        <v>16000</v>
       </c>
       <c r="J31" s="5">
-        <v>62.9</v>
+        <v>67.8</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>92.3</v>
+        <v>84.3</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>202000</v>
+        <v>716000</v>
       </c>
       <c r="G32" s="7">
-        <v>14000</v>
+        <v>34000</v>
       </c>
       <c r="H32" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="7">
-        <v>12000</v>
+        <v>37000</v>
       </c>
       <c r="J32" s="5">
-        <v>62.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.8</v>
+        <v>92.2</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>123000</v>
+        <v>455000</v>
       </c>
       <c r="G33" s="7">
-        <v>11000</v>
+        <v>17000</v>
       </c>
       <c r="H33" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="7">
-        <v>10500</v>
+        <v>19000</v>
       </c>
       <c r="J33" s="5">
-        <v>62.7</v>
+        <v>67.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>92.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>160000</v>
+        <v>234000</v>
       </c>
       <c r="G34" s="7">
-        <v>11000</v>
+        <v>49000</v>
       </c>
       <c r="H34" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="7">
-        <v>9500</v>
+        <v>5333</v>
       </c>
       <c r="J34" s="5">
-        <v>62.3</v>
+        <v>67.5</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>83.3</v>
+        <v>88.8</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>774000</v>
+        <v>271000</v>
       </c>
       <c r="G35" s="7">
-        <v>29000</v>
+        <v>38000</v>
       </c>
       <c r="H35" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="7">
-        <v>29500</v>
+        <v>25667</v>
       </c>
       <c r="J35" s="5">
-        <v>62.2</v>
+        <v>67.3</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>88.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>171000</v>
+        <v>291000</v>
       </c>
       <c r="G36" s="7">
-        <v>13000</v>
+        <v>36000</v>
       </c>
       <c r="H36" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="7">
-        <v>14500</v>
+        <v>23667</v>
       </c>
       <c r="J36" s="5">
-        <v>61.4</v>
+        <v>66.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>85.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>233000</v>
+        <v>165000</v>
       </c>
       <c r="G37" s="7">
-        <v>27000</v>
+        <v>19000</v>
       </c>
       <c r="H37" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="7">
-        <v>19500</v>
+        <v>17333</v>
       </c>
       <c r="J37" s="5">
-        <v>61.1</v>
+        <v>66.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>89.8</v>
+        <v>78.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>317000</v>
+        <v>520000</v>
       </c>
       <c r="G38" s="7">
-        <v>12000</v>
+        <v>44000</v>
       </c>
       <c r="H38" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38" s="7">
-        <v>10500</v>
+        <v>45000</v>
       </c>
       <c r="J38" s="5">
-        <v>61</v>
+        <v>66.5</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>90.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>209000</v>
+        <v>298000</v>
       </c>
       <c r="G39" s="7">
-        <v>8000</v>
+        <v>35000</v>
       </c>
       <c r="H39" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" s="7">
-        <v>8500</v>
+        <v>21667</v>
       </c>
       <c r="J39" s="5">
-        <v>61</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>85.5</v>
+        <v>83</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>171000</v>
+        <v>489000</v>
       </c>
       <c r="G40" s="7">
-        <v>11000</v>
+        <v>46000</v>
       </c>
       <c r="H40" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>18500</v>
+        <v>32000</v>
       </c>
       <c r="J40" s="5">
-        <v>60.7</v>
+        <v>65.7</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>90.2</v>
+        <v>89</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>108000</v>
+        <v>187000</v>
       </c>
       <c r="G41" s="7">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="H41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="7">
-        <v>8500</v>
+        <v>17667</v>
       </c>
       <c r="J41" s="5">
-        <v>60.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>90.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>124000</v>
+        <v>121000</v>
       </c>
       <c r="G42" s="7">
-        <v>7000</v>
+        <v>14000</v>
       </c>
       <c r="H42" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="7">
-        <v>7000</v>
+        <v>4333</v>
       </c>
       <c r="J42" s="5">
-        <v>60.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>80.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>521000</v>
+        <v>414000</v>
       </c>
       <c r="G43" s="7">
-        <v>28000</v>
+        <v>74000</v>
       </c>
       <c r="H43" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="7">
-        <v>27000</v>
+        <v>25000</v>
       </c>
       <c r="J43" s="5">
-        <v>60.2</v>
+        <v>65.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>90.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>187000</v>
+        <v>120000</v>
       </c>
       <c r="G44" s="7">
-        <v>7000</v>
+        <v>34000</v>
       </c>
       <c r="H44" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7">
-        <v>6500</v>
+        <v>14000</v>
       </c>
       <c r="J44" s="5">
-        <v>60.2</v>
+        <v>65.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>84.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>123000</v>
+        <v>437000</v>
       </c>
       <c r="G45" s="7">
-        <v>31000</v>
+        <v>67000</v>
       </c>
       <c r="H45" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>18000</v>
+        <v>23667</v>
       </c>
       <c r="J45" s="5">
-        <v>60</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>89.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>271000</v>
+        <v>103000</v>
       </c>
       <c r="G46" s="7">
-        <v>6000</v>
+        <v>19000</v>
       </c>
       <c r="H46" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
-        <v>6000</v>
+        <v>12333</v>
       </c>
       <c r="J46" s="5">
-        <v>59.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>82</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>376000</v>
+        <v>140000</v>
       </c>
       <c r="G47" s="7">
-        <v>26000</v>
+        <v>20000</v>
       </c>
       <c r="H47" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="7">
-        <v>22000</v>
+        <v>8333</v>
       </c>
       <c r="J47" s="5">
-        <v>59.6</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>88.3</v>
+        <v>89</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>122000</v>
+        <v>263000</v>
       </c>
       <c r="G48" s="7">
-        <v>8000</v>
+        <v>11000</v>
       </c>
       <c r="H48" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48" s="7">
-        <v>8000</v>
+        <v>15333</v>
       </c>
       <c r="J48" s="5">
-        <v>59.6</v>
+        <v>64.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>80.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>502000</v>
+        <v>121000</v>
       </c>
       <c r="G49" s="7">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="H49" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I49" s="7">
-        <v>24500</v>
+        <v>8667</v>
       </c>
       <c r="J49" s="5">
-        <v>59.5</v>
+        <v>64.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>89.2</v>
+        <v>92.7</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>164000</v>
+        <v>103000</v>
       </c>
       <c r="G50" s="7">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="H50" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" s="7">
-        <v>5000</v>
+        <v>7333</v>
       </c>
       <c r="J50" s="5">
-        <v>59.3</v>
+        <v>64.8</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>160000</v>
+        <v>102000</v>
       </c>
       <c r="G51" s="7">
-        <v>9000</v>
+        <v>24000</v>
       </c>
       <c r="H51" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I51" s="7">
-        <v>9000</v>
+        <v>13333</v>
       </c>
       <c r="J51" s="5">
-        <v>59.1</v>
+        <v>64.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>87</v>
+        <v>91.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>154000</v>
+        <v>121000</v>
       </c>
       <c r="G52" s="7">
-        <v>11000</v>
+        <v>17000</v>
       </c>
       <c r="H52" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52" s="7">
-        <v>9000</v>
+        <v>10333</v>
       </c>
       <c r="J52" s="5">
-        <v>59.1</v>
+        <v>64.7</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>82.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>297000</v>
+        <v>113000</v>
       </c>
       <c r="G53" s="7">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="H53" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" s="7">
-        <v>16500</v>
+        <v>9667</v>
       </c>
       <c r="J53" s="5">
-        <v>58.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>87</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>108000</v>
+        <v>231000</v>
       </c>
       <c r="G54" s="7">
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="H54" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>7000</v>
+        <v>10667</v>
       </c>
       <c r="J54" s="5">
-        <v>58.6</v>
+        <v>64.5</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-28T11:05:19+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-29T06:50:37+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>女多男少，开局分配辅导员老婆</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>变身顶美，有颜真能为所欲为</t>
+  </si>
+  <si>
+    <t>屠城就能回蓝星？兄弟你早说啊！</t>
+  </si>
+  <si>
+    <t>轮回修仙：从考科举开始</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>让你荒淫无道，千古一帝什么鬼？</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>穿书成富二代，我直接救赎女主</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>我老婆有白月光？她怎么不知道</t>
+  </si>
+  <si>
     <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
   </si>
   <si>
-    <t>打开作品</t>
+    <t>民国：张家逆子，我才是东北王</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
     <t>名义：我避开祁同伟几十年</t>
   </si>
   <si>
-    <t>我老婆有白月光？她怎么不知道</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>穿书成富二代，我直接救赎女主</t>
+    <t>退休勇者买下魔王当女仆</t>
+  </si>
+  <si>
+    <t>觉醒伪神，神明弃我，我自为神</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
   </si>
   <si>
     <t>我都成烛龙了，人类怎么才诞生？</t>
   </si>
   <si>
-    <t>屠城就能回蓝星？兄弟你早说啊！</t>
-  </si>
-  <si>
-    <t>让你荒淫无道，千古一帝什么鬼？</t>
-  </si>
-  <si>
-    <t>离婚后，我成了刀枪炮！</t>
+    <t>满分高考状元：我带全县暴富</t>
+  </si>
+  <si>
+    <t>大唐长生者，但开局在玄武门？</t>
+  </si>
+  <si>
+    <t>四合院：从红二十五开始进步</t>
   </si>
   <si>
     <t>穿越成国公，咋就是封建余孽了？</t>
   </si>
   <si>
-    <t>别人穿四合院，我为啥上战场</t>
-  </si>
-  <si>
-    <t>女多男少，开局分配辅导员老婆</t>
+    <t>我一个贪官绑定勤政爱民系统？</t>
+  </si>
+  <si>
+    <t>末日：无限强化？开局强化我自己</t>
+  </si>
+  <si>
+    <t>聊天群约架，什么叫太上老君来了</t>
+  </si>
+  <si>
+    <t>列车求生，我能升华一切！</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
+    <t>红楼：庶子贾琮，开局收保护费</t>
+  </si>
+  <si>
+    <t>穿成丧尸小萝莉，凤傲天求放过</t>
+  </si>
+  <si>
+    <t>重生98：带百万兄弟搞工业</t>
+  </si>
+  <si>
+    <t>不娶还敢撩？再跑就把你关起来</t>
+  </si>
+  <si>
+    <t>反派老婆破产后，她们都盯上我？</t>
+  </si>
+  <si>
+    <t>欢迎都显怀了，你还没释怀</t>
   </si>
   <si>
     <t>让你拍反腐片，你拍人民的名义！</t>
   </si>
   <si>
+    <t>谁把我仙侠游戏退出键扣了？</t>
+  </si>
+  <si>
+    <t>站中间抽两边，什么叫霸之意志呀</t>
+  </si>
+  <si>
+    <t>同学们选武侠仙侠，我选洪荒世界</t>
+  </si>
+  <si>
+    <t>四合院：我表哥是神棍</t>
+  </si>
+  <si>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
     <t>全民恐怖求生：我觉醒加点序列！</t>
   </si>
   <si>
-    <t>穿成丧尸小萝莉，凤傲天求放过</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>轮回修仙：从考科举开始</t>
-  </si>
-  <si>
-    <t>大唐长生者，但开局在玄武门？</t>
+    <t>1953，旅长把我拐进哈工大</t>
+  </si>
+  <si>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>崩铁观影：天幕曝光我，震惊寰宇</t>
+  </si>
+  <si>
+    <t>我的绝世表嫂</t>
+  </si>
+  <si>
+    <t>重返高三，满仓抄底狂赚百亿</t>
+  </si>
+  <si>
+    <t>三体：我还以为是全知域呢！</t>
   </si>
   <si>
     <t>三角洲：FPS暴君降临</t>
-  </si>
-  <si>
-    <t>欢迎都显怀了，你还没释怀</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>反派老婆破产后，她们都盯上我？</t>
-  </si>
-  <si>
-    <t>大秦我带秦始皇长生不老</t>
-  </si>
-  <si>
-    <t>有钱有势回县城，开局睡了白月光</t>
-  </si>
-  <si>
-    <t>名柯：我有三角洲召唤系统</t>
-  </si>
-  <si>
-    <t>列车求生，我能升华一切！</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>魔法？我钢铁洪流直接平推！</t>
-  </si>
-  <si>
-    <t>我都成仙了，才来万界聊天群？</t>
-  </si>
-  <si>
-    <t>觉醒伪神，神明弃我，我自为神</t>
-  </si>
-  <si>
-    <t>末世重生，成为核电站供能无限</t>
-  </si>
-  <si>
-    <t>下载APP，才发现青梅好感爆了</t>
-  </si>
-  <si>
-    <t>让你暑假实习，你去地府当鬼差！</t>
-  </si>
-  <si>
-    <t>民国：张家逆子，我才是东北王</t>
-  </si>
-  <si>
-    <t>死亡游戏：开局欺诈师，假扮神明</t>
-  </si>
-  <si>
-    <t>不对劲，我穿越的都是里世界</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>堕落女主们和我一起腐烂</t>
-  </si>
-  <si>
-    <t>开局流落皇子，可我已经人间无敌</t>
-  </si>
-  <si>
-    <t>四合院：我表哥是神棍</t>
-  </si>
-  <si>
-    <t>神话1900：开局获得诅咒词条</t>
-  </si>
-  <si>
-    <t>九门：刚混成副官，师尊找来了？</t>
-  </si>
-  <si>
-    <t>开局豪门继承人，怎么还要上恋综</t>
-  </si>
-  <si>
-    <t>洪荒：我盘古第四清，帮场通天！</t>
-  </si>
-  <si>
-    <t>满分高考状元：我带全县暴富</t>
-  </si>
-  <si>
-    <t>四合院：从红二十五开始进步</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>211000</v>
+        <v>241000</v>
       </c>
       <c r="G5" s="7">
-        <v>75000</v>
+        <v>52000</v>
       </c>
       <c r="H5" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="7">
-        <v>36000</v>
+        <v>35750</v>
       </c>
       <c r="J5" s="5">
-        <v>76</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>368000</v>
+        <v>207000</v>
       </c>
       <c r="G6" s="7">
-        <v>43000</v>
+        <v>75000</v>
       </c>
       <c r="H6" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="7">
-        <v>33333</v>
+        <v>30000</v>
       </c>
       <c r="J6" s="5">
-        <v>75.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>555000</v>
+        <v>402000</v>
       </c>
       <c r="G7" s="7">
-        <v>61000</v>
+        <v>25000</v>
       </c>
       <c r="H7" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="7">
-        <v>31667</v>
+        <v>31250</v>
       </c>
       <c r="J7" s="5">
-        <v>74.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>446000</v>
+        <v>249000</v>
       </c>
       <c r="G8" s="7">
-        <v>89000</v>
+        <v>27000</v>
       </c>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7">
-        <v>30333</v>
+        <v>23750</v>
       </c>
       <c r="J8" s="5">
-        <v>74.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>236000</v>
+        <v>269000</v>
       </c>
       <c r="G9" s="7">
-        <v>39000</v>
+        <v>35000</v>
       </c>
       <c r="H9" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="7">
-        <v>28333</v>
+        <v>12750</v>
       </c>
       <c r="J9" s="5">
-        <v>74.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>286000</v>
+        <v>270000</v>
       </c>
       <c r="G10" s="7">
-        <v>41000</v>
+        <v>34000</v>
       </c>
       <c r="H10" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
-        <v>28000</v>
+        <v>17000</v>
       </c>
       <c r="J10" s="5">
-        <v>74</v>
+        <v>72.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>97.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>377000</v>
+        <v>413000</v>
       </c>
       <c r="G11" s="7">
-        <v>38000</v>
+        <v>32000</v>
       </c>
       <c r="H11" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
-        <v>33333</v>
+        <v>47000</v>
       </c>
       <c r="J11" s="5">
-        <v>73.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>88.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>381000</v>
+        <v>187000</v>
       </c>
       <c r="G12" s="7">
-        <v>50000</v>
+        <v>17000</v>
       </c>
       <c r="H12" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>52000</v>
+        <v>11250</v>
       </c>
       <c r="J12" s="5">
-        <v>73.8</v>
+        <v>70.8</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>99.7</v>
+        <v>89.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>276000</v>
+        <v>515000</v>
       </c>
       <c r="G13" s="7">
-        <v>42000</v>
+        <v>6000</v>
       </c>
       <c r="H13" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" s="7">
-        <v>27333</v>
+        <v>25000</v>
       </c>
       <c r="J13" s="5">
-        <v>73.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>98.5</v>
+        <v>89.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>156000</v>
+        <v>691000</v>
       </c>
       <c r="G14" s="7">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="7">
-        <v>26333</v>
+        <v>25250</v>
       </c>
       <c r="J14" s="5">
-        <v>72.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>95</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>509000</v>
+        <v>243000</v>
       </c>
       <c r="G15" s="7">
-        <v>31000</v>
+        <v>7000</v>
       </c>
       <c r="H15" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" s="7">
-        <v>31333</v>
+        <v>23000</v>
       </c>
       <c r="J15" s="5">
-        <v>72.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>95.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>189000</v>
+        <v>471000</v>
       </c>
       <c r="G16" s="7">
-        <v>51000</v>
+        <v>16000</v>
       </c>
       <c r="H16" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="7">
-        <v>30333</v>
+        <v>18250</v>
       </c>
       <c r="J16" s="5">
-        <v>72.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>90.2</v>
+        <v>88.7</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>576000</v>
+        <v>555000</v>
       </c>
       <c r="G17" s="7">
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="H17" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>41000</v>
+        <v>23750</v>
       </c>
       <c r="J17" s="5">
-        <v>71.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>87.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>471000</v>
+        <v>211000</v>
       </c>
       <c r="G18" s="7">
-        <v>58000</v>
+        <v>0</v>
       </c>
       <c r="H18" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="7">
-        <v>47333</v>
+        <v>27000</v>
       </c>
       <c r="J18" s="5">
-        <v>71.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>99.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>193000</v>
+        <v>137000</v>
       </c>
       <c r="G19" s="7">
-        <v>36000</v>
+        <v>16000</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>20000</v>
+        <v>7250</v>
       </c>
       <c r="J19" s="5">
-        <v>71.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>209000</v>
+        <v>446000</v>
       </c>
       <c r="G20" s="7">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="H20" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>18333</v>
+        <v>22750</v>
       </c>
       <c r="J20" s="5">
-        <v>71.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>92.5</v>
+        <v>87</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>691000</v>
+        <v>368000</v>
       </c>
       <c r="G21" s="7">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="H21" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="7">
-        <v>33667</v>
+        <v>25000</v>
       </c>
       <c r="J21" s="5">
-        <v>71.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>97.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>222000</v>
+        <v>224000</v>
       </c>
       <c r="G22" s="7">
-        <v>29000</v>
+        <v>15000</v>
       </c>
       <c r="H22" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="7">
-        <v>22667</v>
+        <v>8000</v>
       </c>
       <c r="J22" s="5">
-        <v>71.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>841000</v>
+        <v>554000</v>
       </c>
       <c r="G23" s="7">
-        <v>67000</v>
+        <v>34000</v>
       </c>
       <c r="H23" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="7">
-        <v>42000</v>
+        <v>42250</v>
       </c>
       <c r="J23" s="5">
-        <v>71.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>90</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>319000</v>
+        <v>293000</v>
       </c>
       <c r="G24" s="7">
-        <v>52000</v>
+        <v>12000</v>
       </c>
       <c r="H24" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="7">
-        <v>37333</v>
+        <v>8500</v>
       </c>
       <c r="J24" s="5">
-        <v>70.8</v>
+        <v>67.5</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>100</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>196000</v>
+        <v>286000</v>
       </c>
       <c r="G25" s="7">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="H25" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>14000</v>
+        <v>21000</v>
       </c>
       <c r="J25" s="5">
-        <v>70.5</v>
+        <v>67.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>95.7</v>
+        <v>90.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>198000</v>
+        <v>121000</v>
       </c>
       <c r="G26" s="7">
-        <v>27000</v>
+        <v>8000</v>
       </c>
       <c r="H26" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" s="7">
-        <v>18667</v>
+        <v>9250</v>
       </c>
       <c r="J26" s="5">
-        <v>69.3</v>
+        <v>67.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>98.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>236000</v>
+        <v>841000</v>
       </c>
       <c r="G27" s="7">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="7">
-        <v>11333</v>
+        <v>31500</v>
       </c>
       <c r="J27" s="5">
-        <v>69</v>
+        <v>66.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>96.5</v>
+        <v>88.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>225000</v>
+        <v>243000</v>
       </c>
       <c r="G28" s="7">
-        <v>23000</v>
+        <v>12000</v>
       </c>
       <c r="H28" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" s="7">
-        <v>15667</v>
+        <v>11000</v>
       </c>
       <c r="J28" s="5">
-        <v>69</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>88.7</v>
+        <v>83.5</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>428000</v>
+        <v>156000</v>
       </c>
       <c r="G29" s="7">
-        <v>52000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" s="7">
-        <v>32000</v>
+        <v>19750</v>
       </c>
       <c r="J29" s="5">
-        <v>68.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>93.5</v>
+        <v>89.7</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>227000</v>
+        <v>105000</v>
       </c>
       <c r="G30" s="7">
-        <v>16000</v>
+        <v>7000</v>
       </c>
       <c r="H30" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>17667</v>
+        <v>5750</v>
       </c>
       <c r="J30" s="5">
-        <v>67.8</v>
+        <v>65.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>94.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>145000</v>
+        <v>116000</v>
       </c>
       <c r="G31" s="7">
-        <v>27000</v>
+        <v>8000</v>
       </c>
       <c r="H31" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="7">
-        <v>16000</v>
+        <v>6250</v>
       </c>
       <c r="J31" s="5">
-        <v>67.8</v>
+        <v>65.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>84.3</v>
+        <v>88.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>716000</v>
+        <v>105000</v>
       </c>
       <c r="G32" s="7">
-        <v>34000</v>
+        <v>6000</v>
       </c>
       <c r="H32" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>37000</v>
+        <v>7750</v>
       </c>
       <c r="J32" s="5">
-        <v>67.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.2</v>
+        <v>79.3</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>455000</v>
+        <v>716000</v>
       </c>
       <c r="G33" s="7">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>19000</v>
+        <v>27750</v>
       </c>
       <c r="J33" s="5">
-        <v>67.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>98.5</v>
+        <v>85.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>234000</v>
+        <v>209000</v>
       </c>
       <c r="G34" s="7">
-        <v>49000</v>
+        <v>0</v>
       </c>
       <c r="H34" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="7">
-        <v>5333</v>
+        <v>13750</v>
       </c>
       <c r="J34" s="5">
-        <v>67.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>88.8</v>
+        <v>89.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>271000</v>
+        <v>105000</v>
       </c>
       <c r="G35" s="7">
-        <v>38000</v>
+        <v>5000</v>
       </c>
       <c r="H35" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" s="7">
-        <v>25667</v>
+        <v>5750</v>
       </c>
       <c r="J35" s="5">
-        <v>67.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>291000</v>
+        <v>193000</v>
       </c>
       <c r="G36" s="7">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="H36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>23667</v>
+        <v>15000</v>
       </c>
       <c r="J36" s="5">
-        <v>66.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>91.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>165000</v>
+        <v>136000</v>
       </c>
       <c r="G37" s="7">
-        <v>19000</v>
+        <v>5000</v>
       </c>
       <c r="H37" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" s="7">
-        <v>17333</v>
+        <v>6500</v>
       </c>
       <c r="J37" s="5">
-        <v>66.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>78.7</v>
+        <v>88.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>520000</v>
+        <v>124000</v>
       </c>
       <c r="G38" s="7">
-        <v>44000</v>
+        <v>8000</v>
       </c>
       <c r="H38" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I38" s="7">
-        <v>45000</v>
+        <v>7500</v>
       </c>
       <c r="J38" s="5">
-        <v>66.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>88.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>298000</v>
+        <v>225000</v>
       </c>
       <c r="G39" s="7">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="H39" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I39" s="7">
-        <v>21667</v>
+        <v>11750</v>
       </c>
       <c r="J39" s="5">
-        <v>65.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>83</v>
+        <v>86.5</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>489000</v>
+        <v>196000</v>
       </c>
       <c r="G40" s="7">
-        <v>46000</v>
+        <v>0</v>
       </c>
       <c r="H40" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I40" s="7">
-        <v>32000</v>
+        <v>10500</v>
       </c>
       <c r="J40" s="5">
-        <v>65.7</v>
+        <v>65.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>89</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>187000</v>
+        <v>576000</v>
       </c>
       <c r="G41" s="7">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="H41" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>17667</v>
+        <v>30750</v>
       </c>
       <c r="J41" s="5">
-        <v>65.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>95.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>121000</v>
+        <v>787000</v>
       </c>
       <c r="G42" s="7">
-        <v>14000</v>
+        <v>26000</v>
       </c>
       <c r="H42" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I42" s="7">
-        <v>4333</v>
+        <v>22500</v>
       </c>
       <c r="J42" s="5">
-        <v>65.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>414000</v>
+        <v>411000</v>
       </c>
       <c r="G43" s="7">
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43" s="7">
-        <v>25000</v>
+        <v>5250</v>
       </c>
       <c r="J43" s="5">
-        <v>65.3</v>
+        <v>64.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>90.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>120000</v>
+        <v>379000</v>
       </c>
       <c r="G44" s="7">
-        <v>34000</v>
+        <v>28000</v>
       </c>
       <c r="H44" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7">
-        <v>14000</v>
+        <v>14750</v>
       </c>
       <c r="J44" s="5">
-        <v>65.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>85.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>437000</v>
+        <v>263000</v>
       </c>
       <c r="G45" s="7">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="H45" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
-        <v>23667</v>
+        <v>11500</v>
       </c>
       <c r="J45" s="5">
-        <v>65.09999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>90.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>103000</v>
+        <v>116000</v>
       </c>
       <c r="G46" s="7">
-        <v>19000</v>
+        <v>6000</v>
       </c>
       <c r="H46" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>12333</v>
+        <v>7250</v>
       </c>
       <c r="J46" s="5">
-        <v>65.09999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>92.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>140000</v>
+        <v>471000</v>
       </c>
       <c r="G47" s="7">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H47" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="7">
-        <v>8333</v>
+        <v>35500</v>
       </c>
       <c r="J47" s="5">
-        <v>64.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2185,19 +2185,19 @@
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>263000</v>
+        <v>231000</v>
       </c>
       <c r="G48" s="7">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="H48" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
-        <v>15333</v>
+        <v>750</v>
       </c>
       <c r="J48" s="5">
-        <v>64.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>92.09999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>121000</v>
+        <v>716000</v>
       </c>
       <c r="G49" s="7">
-        <v>15000</v>
+        <v>26000</v>
       </c>
       <c r="H49" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7">
-        <v>8667</v>
+        <v>18750</v>
       </c>
       <c r="J49" s="5">
-        <v>64.8</v>
+        <v>64</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>92.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>103000</v>
+        <v>119000</v>
       </c>
       <c r="G50" s="7">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H50" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7">
-        <v>7333</v>
+        <v>8250</v>
       </c>
       <c r="J50" s="5">
-        <v>64.8</v>
+        <v>64</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>102000</v>
+        <v>562000</v>
       </c>
       <c r="G51" s="7">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="H51" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I51" s="7">
-        <v>13333</v>
+        <v>26750</v>
       </c>
       <c r="J51" s="5">
-        <v>64.8</v>
+        <v>63.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>91.2</v>
+        <v>80.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>121000</v>
+        <v>235000</v>
       </c>
       <c r="G52" s="7">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="H52" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I52" s="7">
-        <v>10333</v>
+        <v>16750</v>
       </c>
       <c r="J52" s="5">
-        <v>64.7</v>
+        <v>63.4</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>91.2</v>
+        <v>81.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>113000</v>
+        <v>198000</v>
       </c>
       <c r="G53" s="7">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="H53" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>9667</v>
+        <v>14000</v>
       </c>
       <c r="J53" s="5">
-        <v>64.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>90.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>231000</v>
+        <v>319000</v>
       </c>
       <c r="G54" s="7">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I54" s="7">
-        <v>10667</v>
+        <v>28000</v>
       </c>
       <c r="J54" s="5">
-        <v>64.5</v>
+        <v>63.2</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-29T06:50:37+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-30T05:03:17+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>变身顶美，有颜真能为所欲为</t>
   </si>
   <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>轮回修仙：从考科举开始</t>
+  </si>
+  <si>
+    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
+  </si>
+  <si>
+    <t>不是，让我一个剑修去联姻？</t>
+  </si>
+  <si>
+    <t>我老婆有白月光？她怎么不知道</t>
+  </si>
+  <si>
+    <t>名义：我避开祁同伟几十年</t>
+  </si>
+  <si>
     <t>屠城就能回蓝星？兄弟你早说啊！</t>
   </si>
   <si>
-    <t>轮回修仙：从考科举开始</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
+    <t>女尊，独自抚养妹妹们的正太哥哥</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>别人穿四合院，我为啥上战场</t>
   </si>
   <si>
     <t>让你荒淫无道，千古一帝什么鬼？</t>
   </si>
   <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>别人穿四合院，我为啥上战场</t>
+    <t>玩弄感情的坏男孩就要被病娇狠狠</t>
   </si>
   <si>
     <t>名义：开局我举报我自己</t>
   </si>
   <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>开局豪门继承人，怎么还要上恋综</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>不对劲，我穿越的都是里世界</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
     <t>穿书成富二代，我直接救赎女主</t>
   </si>
   <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>我老婆有白月光？她怎么不知道</t>
-  </si>
-  <si>
-    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
+    <t>名柯：我有三角洲召唤系统</t>
+  </si>
+  <si>
+    <t>三体：我还以为是全知域呢！</t>
+  </si>
+  <si>
+    <t>穿越黄毛，女主们把我当白月光了</t>
+  </si>
+  <si>
+    <t>大唐长生者，但开局在玄武门？</t>
+  </si>
+  <si>
+    <t>让你拍反腐片，你拍人民的名义！</t>
+  </si>
+  <si>
+    <t>觉醒伪神，神明弃我，我自为神</t>
   </si>
   <si>
     <t>民国：张家逆子，我才是东北王</t>
   </si>
   <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>名义：我避开祁同伟几十年</t>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>穿越异界，我靠剑道成神</t>
+  </si>
+  <si>
+    <t>列车求生，我能升华一切！</t>
+  </si>
+  <si>
+    <t>我都成烛龙了，人类怎么才诞生？</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>三角洲：FPS暴君降临</t>
+  </si>
+  <si>
+    <t>欢迎都显怀了，你还没释怀</t>
   </si>
   <si>
     <t>退休勇者买下魔王当女仆</t>
   </si>
   <si>
-    <t>觉醒伪神，神明弃我，我自为神</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>我都成烛龙了，人类怎么才诞生？</t>
-  </si>
-  <si>
-    <t>满分高考状元：我带全县暴富</t>
-  </si>
-  <si>
-    <t>大唐长生者，但开局在玄武门？</t>
-  </si>
-  <si>
     <t>四合院：从红二十五开始进步</t>
   </si>
   <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>我一个贪官绑定勤政爱民系统？</t>
+    <t>红楼：庶子贾琮，开局收保护费</t>
+  </si>
+  <si>
+    <t>穿成丧尸小萝莉，凤傲天求放过</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
   </si>
   <si>
     <t>末日：无限强化？开局强化我自己</t>
   </si>
   <si>
+    <t>大秦我带秦始皇长生不老</t>
+  </si>
+  <si>
+    <t>重生98：带百万兄弟搞工业</t>
+  </si>
+  <si>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
     <t>聊天群约架，什么叫太上老君来了</t>
   </si>
   <si>
-    <t>列车求生，我能升华一切！</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>红楼：庶子贾琮，开局收保护费</t>
-  </si>
-  <si>
-    <t>穿成丧尸小萝莉，凤傲天求放过</t>
-  </si>
-  <si>
-    <t>重生98：带百万兄弟搞工业</t>
-  </si>
-  <si>
-    <t>不娶还敢撩？再跑就把你关起来</t>
-  </si>
-  <si>
-    <t>反派老婆破产后，她们都盯上我？</t>
-  </si>
-  <si>
-    <t>欢迎都显怀了，你还没释怀</t>
-  </si>
-  <si>
-    <t>让你拍反腐片，你拍人民的名义！</t>
+    <t>灵气复苏：开局获得呼吸法</t>
+  </si>
+  <si>
+    <t>公路求生，什么叫你的载具是飞剑</t>
+  </si>
+  <si>
+    <t>同学们选武侠仙侠，我选洪荒世界</t>
   </si>
   <si>
     <t>谁把我仙侠游戏退出键扣了？</t>
-  </si>
-  <si>
-    <t>站中间抽两边，什么叫霸之意志呀</t>
-  </si>
-  <si>
-    <t>同学们选武侠仙侠，我选洪荒世界</t>
-  </si>
-  <si>
-    <t>四合院：我表哥是神棍</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
-  </si>
-  <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>1953，旅长把我拐进哈工大</t>
-  </si>
-  <si>
-    <t>公安局长之扫黑风暴</t>
-  </si>
-  <si>
-    <t>崩铁观影：天幕曝光我，震惊寰宇</t>
-  </si>
-  <si>
-    <t>我的绝世表嫂</t>
-  </si>
-  <si>
-    <t>重返高三，满仓抄底狂赚百亿</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
-  </si>
-  <si>
-    <t>三角洲：FPS暴君降临</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>99.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>241000</v>
+        <v>281000</v>
       </c>
       <c r="G5" s="7">
-        <v>52000</v>
+        <v>40000</v>
       </c>
       <c r="H5" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>35750</v>
+        <v>36600</v>
       </c>
       <c r="J5" s="5">
-        <v>78.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>97.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>207000</v>
+        <v>260000</v>
       </c>
       <c r="G6" s="7">
-        <v>75000</v>
+        <v>53000</v>
       </c>
       <c r="H6" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="7">
-        <v>30000</v>
+        <v>34600</v>
       </c>
       <c r="J6" s="5">
-        <v>76.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>402000</v>
+        <v>309000</v>
       </c>
       <c r="G7" s="7">
-        <v>25000</v>
+        <v>39000</v>
       </c>
       <c r="H7" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="7">
-        <v>31250</v>
+        <v>21400</v>
       </c>
       <c r="J7" s="5">
-        <v>74</v>
+        <v>78.3</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>95.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>249000</v>
+        <v>281000</v>
       </c>
       <c r="G8" s="7">
-        <v>27000</v>
+        <v>32000</v>
       </c>
       <c r="H8" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>23750</v>
+        <v>25400</v>
       </c>
       <c r="J8" s="5">
-        <v>73.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>269000</v>
+        <v>230000</v>
       </c>
       <c r="G9" s="7">
-        <v>35000</v>
+        <v>19000</v>
       </c>
       <c r="H9" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>12750</v>
+        <v>25400</v>
       </c>
       <c r="J9" s="5">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>97.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>270000</v>
+        <v>104000</v>
       </c>
       <c r="G10" s="7">
-        <v>34000</v>
+        <v>18000</v>
       </c>
       <c r="H10" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>17000</v>
+        <v>13800</v>
       </c>
       <c r="J10" s="5">
-        <v>72.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>82.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>413000</v>
+        <v>579000</v>
       </c>
       <c r="G11" s="7">
-        <v>32000</v>
+        <v>24000</v>
       </c>
       <c r="H11" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>47000</v>
+        <v>23800</v>
       </c>
       <c r="J11" s="5">
-        <v>72</v>
+        <v>75.2</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>96.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>187000</v>
+        <v>387000</v>
       </c>
       <c r="G12" s="7">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="H12" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="7">
-        <v>11250</v>
+        <v>23800</v>
       </c>
       <c r="J12" s="5">
-        <v>70.8</v>
+        <v>74.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>89.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>515000</v>
+        <v>414000</v>
       </c>
       <c r="G13" s="7">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="H13" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>25000</v>
+        <v>27400</v>
       </c>
       <c r="J13" s="5">
-        <v>70.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>89.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>691000</v>
+        <v>187000</v>
       </c>
       <c r="G14" s="7">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="H14" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I14" s="7">
-        <v>25250</v>
+        <v>29667</v>
       </c>
       <c r="J14" s="5">
-        <v>70.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>89.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>243000</v>
+        <v>486000</v>
       </c>
       <c r="G15" s="7">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H15" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>23000</v>
+        <v>17600</v>
       </c>
       <c r="J15" s="5">
-        <v>70.2</v>
+        <v>72.8</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>91.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>471000</v>
+        <v>201000</v>
       </c>
       <c r="G16" s="7">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="H16" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>18250</v>
+        <v>11800</v>
       </c>
       <c r="J16" s="5">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>88.7</v>
+        <v>89.7</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>555000</v>
+        <v>521000</v>
       </c>
       <c r="G17" s="7">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H17" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>23750</v>
+        <v>21200</v>
       </c>
       <c r="J17" s="5">
-        <v>69.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>86.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>211000</v>
+        <v>434000</v>
       </c>
       <c r="G18" s="7">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="H18" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="7">
-        <v>27000</v>
+        <v>41800</v>
       </c>
       <c r="J18" s="5">
-        <v>69.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>95.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>137000</v>
+        <v>139000</v>
       </c>
       <c r="G19" s="7">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="H19" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" s="7">
-        <v>7250</v>
+        <v>6600</v>
       </c>
       <c r="J19" s="5">
-        <v>69.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>446000</v>
+        <v>687000</v>
       </c>
       <c r="G20" s="7">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>22750</v>
+        <v>19400</v>
       </c>
       <c r="J20" s="5">
-        <v>69.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>87</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>368000</v>
+        <v>165000</v>
       </c>
       <c r="G21" s="7">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="H21" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" s="7">
-        <v>25000</v>
+        <v>17600</v>
       </c>
       <c r="J21" s="5">
-        <v>69.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>93.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>224000</v>
+        <v>120000</v>
       </c>
       <c r="G22" s="7">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H22" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I22" s="7">
-        <v>8000</v>
+        <v>11600</v>
       </c>
       <c r="J22" s="5">
-        <v>68.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>76.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>554000</v>
+        <v>448000</v>
       </c>
       <c r="G23" s="7">
-        <v>34000</v>
+        <v>2000</v>
       </c>
       <c r="H23" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" s="7">
-        <v>42250</v>
+        <v>18600</v>
       </c>
       <c r="J23" s="5">
-        <v>67.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>293000</v>
+        <v>137000</v>
       </c>
       <c r="G24" s="7">
-        <v>12000</v>
+        <v>17000</v>
       </c>
       <c r="H24" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>8500</v>
+        <v>11800</v>
       </c>
       <c r="J24" s="5">
-        <v>67.5</v>
+        <v>71.3</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>85.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>286000</v>
+        <v>219000</v>
       </c>
       <c r="G25" s="7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H25" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" s="7">
-        <v>21000</v>
+        <v>13000</v>
       </c>
       <c r="J25" s="5">
-        <v>67.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>90.8</v>
+        <v>87.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>121000</v>
+        <v>245000</v>
       </c>
       <c r="G26" s="7">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="H26" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
-        <v>9250</v>
+        <v>18800</v>
       </c>
       <c r="J26" s="5">
-        <v>67.3</v>
+        <v>71</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>79.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>841000</v>
+        <v>157000</v>
       </c>
       <c r="G27" s="7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H27" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>31500</v>
+        <v>12000</v>
       </c>
       <c r="J27" s="5">
-        <v>66.7</v>
+        <v>71</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>88.8</v>
+        <v>89</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>243000</v>
+        <v>211000</v>
       </c>
       <c r="G28" s="7">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="H28" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" s="7">
-        <v>11000</v>
+        <v>13800</v>
       </c>
       <c r="J28" s="5">
-        <v>66.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>83.5</v>
+        <v>92.3</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>156000</v>
+        <v>123000</v>
       </c>
       <c r="G29" s="7">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="H29" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I29" s="7">
-        <v>19750</v>
+        <v>6400</v>
       </c>
       <c r="J29" s="5">
-        <v>65.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89.7</v>
+        <v>81.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>105000</v>
+        <v>862000</v>
       </c>
       <c r="G30" s="7">
-        <v>7000</v>
+        <v>21000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>5750</v>
+        <v>29400</v>
       </c>
       <c r="J30" s="5">
-        <v>65.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>89.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>116000</v>
+        <v>597000</v>
       </c>
       <c r="G31" s="7">
-        <v>8000</v>
+        <v>21000</v>
       </c>
       <c r="H31" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" s="7">
-        <v>6250</v>
+        <v>28800</v>
       </c>
       <c r="J31" s="5">
-        <v>65.7</v>
+        <v>69.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>88.7</v>
+        <v>75.3</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>105000</v>
+        <v>585000</v>
       </c>
       <c r="G32" s="7">
-        <v>6000</v>
+        <v>31000</v>
       </c>
       <c r="H32" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>7750</v>
+        <v>40000</v>
       </c>
       <c r="J32" s="5">
-        <v>65.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>79.3</v>
+        <v>89.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>716000</v>
+        <v>147000</v>
       </c>
       <c r="G33" s="7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H33" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>27750</v>
+        <v>7800</v>
       </c>
       <c r="J33" s="5">
-        <v>65.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>85.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>209000</v>
+        <v>299000</v>
       </c>
       <c r="G34" s="7">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H34" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>13750</v>
+        <v>8000</v>
       </c>
       <c r="J34" s="5">
-        <v>65.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>105000</v>
+        <v>100000</v>
       </c>
       <c r="G35" s="7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H35" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>5750</v>
+        <v>9400</v>
       </c>
       <c r="J35" s="5">
-        <v>65.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>84.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>193000</v>
+        <v>731000</v>
       </c>
       <c r="G36" s="7">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>15000</v>
+        <v>25200</v>
       </c>
       <c r="J36" s="5">
-        <v>65.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>136000</v>
+        <v>284000</v>
       </c>
       <c r="G37" s="7">
-        <v>5000</v>
+        <v>-2000</v>
       </c>
       <c r="H37" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>6500</v>
+        <v>16400</v>
       </c>
       <c r="J37" s="5">
-        <v>65.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>88.2</v>
+        <v>77.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>124000</v>
+        <v>490000</v>
       </c>
       <c r="G38" s="7">
-        <v>8000</v>
+        <v>19000</v>
       </c>
       <c r="H38" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>7500</v>
+        <v>32200</v>
       </c>
       <c r="J38" s="5">
-        <v>65.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>85.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>225000</v>
+        <v>336000</v>
       </c>
       <c r="G39" s="7">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="H39" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" s="7">
-        <v>11750</v>
+        <v>25800</v>
       </c>
       <c r="J39" s="5">
-        <v>65.2</v>
+        <v>68.7</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.5</v>
+        <v>88</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>196000</v>
+        <v>199000</v>
       </c>
       <c r="G40" s="7">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H40" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>10500</v>
+        <v>9000</v>
       </c>
       <c r="J40" s="5">
-        <v>65.2</v>
+        <v>68.7</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>77.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>576000</v>
+        <v>228000</v>
       </c>
       <c r="G41" s="7">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41" s="7">
-        <v>30750</v>
+        <v>7200</v>
       </c>
       <c r="J41" s="5">
-        <v>65.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>80.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>787000</v>
+        <v>251000</v>
       </c>
       <c r="G42" s="7">
-        <v>26000</v>
+        <v>8000</v>
       </c>
       <c r="H42" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I42" s="7">
-        <v>22500</v>
+        <v>10400</v>
       </c>
       <c r="J42" s="5">
-        <v>64.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>88.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>411000</v>
+        <v>110000</v>
       </c>
       <c r="G43" s="7">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H43" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I43" s="7">
-        <v>5250</v>
+        <v>5600</v>
       </c>
       <c r="J43" s="5">
-        <v>64.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>83.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>379000</v>
+        <v>195000</v>
       </c>
       <c r="G44" s="7">
-        <v>28000</v>
+        <v>2000</v>
       </c>
       <c r="H44" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>14750</v>
+        <v>12400</v>
       </c>
       <c r="J44" s="5">
-        <v>64.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>84.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>263000</v>
+        <v>293000</v>
       </c>
       <c r="G45" s="7">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="H45" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>11500</v>
+        <v>19800</v>
       </c>
       <c r="J45" s="5">
-        <v>64.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>86.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>116000</v>
+        <v>123000</v>
       </c>
       <c r="G46" s="7">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H46" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I46" s="7">
-        <v>7250</v>
+        <v>6400</v>
       </c>
       <c r="J46" s="5">
-        <v>64.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>73.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>471000</v>
+        <v>448000</v>
       </c>
       <c r="G47" s="7">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H47" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I47" s="7">
-        <v>35500</v>
+        <v>23200</v>
       </c>
       <c r="J47" s="5">
-        <v>64.2</v>
+        <v>68</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>89</v>
+        <v>87.8</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>231000</v>
+        <v>140000</v>
       </c>
       <c r="G48" s="7">
-        <v>12000</v>
+        <v>4000</v>
       </c>
       <c r="H48" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7">
-        <v>750</v>
+        <v>6000</v>
       </c>
       <c r="J48" s="5">
-        <v>64.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>80.5</v>
+        <v>87.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>716000</v>
+        <v>123000</v>
       </c>
       <c r="G49" s="7">
-        <v>26000</v>
+        <v>7000</v>
       </c>
       <c r="H49" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I49" s="7">
-        <v>18750</v>
+        <v>7200</v>
       </c>
       <c r="J49" s="5">
-        <v>64</v>
+        <v>67.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>85.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>119000</v>
+        <v>109000</v>
       </c>
       <c r="G50" s="7">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="H50" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50" s="7">
-        <v>8250</v>
+        <v>7000</v>
       </c>
       <c r="J50" s="5">
-        <v>64</v>
+        <v>67.8</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>76</v>
+        <v>90.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>562000</v>
+        <v>137000</v>
       </c>
       <c r="G51" s="7">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="H51" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I51" s="7">
-        <v>26750</v>
+        <v>400</v>
       </c>
       <c r="J51" s="5">
-        <v>63.5</v>
+        <v>67.7</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>80.3</v>
+        <v>89.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>235000</v>
+        <v>104000</v>
       </c>
       <c r="G52" s="7">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="H52" s="7">
         <v>5</v>
       </c>
       <c r="I52" s="7">
-        <v>16750</v>
+        <v>12750</v>
       </c>
       <c r="J52" s="5">
-        <v>63.4</v>
+        <v>67.3</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>81.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>198000</v>
+        <v>403000</v>
       </c>
       <c r="G53" s="7">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="H53" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53" s="7">
-        <v>14000</v>
+        <v>16600</v>
       </c>
       <c r="J53" s="5">
-        <v>63.3</v>
+        <v>67.2</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>75</v>
+        <v>79.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>319000</v>
+        <v>804000</v>
       </c>
       <c r="G54" s="7">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="H54" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I54" s="7">
-        <v>28000</v>
+        <v>21400</v>
       </c>
       <c r="J54" s="5">
-        <v>63.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-30T05:03:17+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-08-31T05:10:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>诡舍2</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>女多男少，开局分配辅导员老婆</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>变身顶美，有颜真能为所欲为</t>
+    <t>轮回修仙：从考科举开始</t>
   </si>
   <si>
     <t>四合院：从亮剑到人民的名义</t>
   </si>
   <si>
-    <t>轮回修仙：从考科举开始</t>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>不是，让我一个剑修去联姻？</t>
+  </si>
+  <si>
+    <t>女尊，独自抚养妹妹们的正太哥哥</t>
+  </si>
+  <si>
+    <t>我老婆有白月光？她怎么不知道</t>
   </si>
   <si>
     <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
   </si>
   <si>
-    <t>不是，让我一个剑修去联姻？</t>
-  </si>
-  <si>
-    <t>我老婆有白月光？她怎么不知道</t>
+    <t>开局豪门继承人，怎么还要上恋综</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
   </si>
   <si>
     <t>名义：我避开祁同伟几十年</t>
   </si>
   <si>
+    <t>名柯：我有三角洲召唤系统</t>
+  </si>
+  <si>
+    <t>觉醒：EX级法师，开局无限火力</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>三体：我还以为是全知域呢！</t>
+  </si>
+  <si>
+    <t>穿成丧尸小萝莉，凤傲天求放过</t>
+  </si>
+  <si>
+    <t>高考落榜，买彩票狂中六亿</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>让你荒淫无道，千古一帝什么鬼？</t>
+  </si>
+  <si>
+    <t>不对劲，我穿越的都是里世界</t>
+  </si>
+  <si>
     <t>屠城就能回蓝星？兄弟你早说啊！</t>
   </si>
   <si>
-    <t>女尊，独自抚养妹妹们的正太哥哥</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>别人穿四合院，我为啥上战场</t>
-  </si>
-  <si>
-    <t>让你荒淫无道，千古一帝什么鬼？</t>
-  </si>
-  <si>
-    <t>玩弄感情的坏男孩就要被病娇狠狠</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>开局豪门继承人，怎么还要上恋综</t>
+    <t>游戏入侵：在诡异副本玩转搜打撤</t>
+  </si>
+  <si>
+    <t>觉醒伪神，神明弃我，我自为神</t>
+  </si>
+  <si>
+    <t>穿书成富二代，我直接救赎女主</t>
+  </si>
+  <si>
+    <t>穿越异界，我靠剑道成神</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>1995：从被抓到出轨开始</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>大唐长生者，但开局在玄武门？</t>
   </si>
   <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
-    <t>不对劲，我穿越的都是里世界</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>穿书成富二代，我直接救赎女主</t>
-  </si>
-  <si>
-    <t>名柯：我有三角洲召唤系统</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
-  </si>
-  <si>
-    <t>穿越黄毛，女主们把我当白月光了</t>
-  </si>
-  <si>
-    <t>大唐长生者，但开局在玄武门？</t>
-  </si>
-  <si>
-    <t>让你拍反腐片，你拍人民的名义！</t>
-  </si>
-  <si>
-    <t>觉醒伪神，神明弃我，我自为神</t>
+    <t>国运：我的队友是瞎子骗子戏子</t>
+  </si>
+  <si>
+    <t>列车求生，我能升华一切！</t>
+  </si>
+  <si>
+    <t>欢迎都显怀了，你还没释怀</t>
+  </si>
+  <si>
+    <t>三角洲：FPS暴君降临</t>
+  </si>
+  <si>
+    <t>大秦我带秦始皇长生不老</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
   </si>
   <si>
     <t>民国：张家逆子，我才是东北王</t>
   </si>
   <si>
+    <t>聊天群约架，什么叫太上老君来了</t>
+  </si>
+  <si>
+    <t>重生98：带百万兄弟搞工业</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
+  </si>
+  <si>
+    <t>全班同学拜大宗师，我拜菩提祖师</t>
+  </si>
+  <si>
     <t>我有一个女鬼催眠APP</t>
   </si>
   <si>
-    <t>穿越异界，我靠剑道成神</t>
-  </si>
-  <si>
-    <t>列车求生，我能升华一切！</t>
-  </si>
-  <si>
     <t>我都成烛龙了，人类怎么才诞生？</t>
   </si>
   <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>三角洲：FPS暴君降临</t>
-  </si>
-  <si>
-    <t>欢迎都显怀了，你还没释怀</t>
-  </si>
-  <si>
-    <t>退休勇者买下魔王当女仆</t>
-  </si>
-  <si>
-    <t>四合院：从红二十五开始进步</t>
-  </si>
-  <si>
-    <t>红楼：庶子贾琮，开局收保护费</t>
-  </si>
-  <si>
-    <t>穿成丧尸小萝莉，凤傲天求放过</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>末日：无限强化？开局强化我自己</t>
-  </si>
-  <si>
-    <t>大秦我带秦始皇长生不老</t>
-  </si>
-  <si>
-    <t>重生98：带百万兄弟搞工业</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
-  </si>
-  <si>
-    <t>聊天群约架，什么叫太上老君来了</t>
-  </si>
-  <si>
-    <t>灵气复苏：开局获得呼吸法</t>
-  </si>
-  <si>
-    <t>公路求生，什么叫你的载具是飞剑</t>
-  </si>
-  <si>
-    <t>同学们选武侠仙侠，我选洪荒世界</t>
-  </si>
-  <si>
-    <t>谁把我仙侠游戏退出键扣了？</t>
+    <t>村花的傻子老公</t>
+  </si>
+  <si>
+    <t>火影：人在木叶村，开局觉醒木遁</t>
+  </si>
+  <si>
+    <t>只想躺平开民宿，咋就活成顶流了</t>
+  </si>
+  <si>
+    <t>站中间抽两边，什么叫霸之意志呀</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>281000</v>
+        <v>380000</v>
       </c>
       <c r="G5" s="7">
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I5" s="7">
-        <v>36600</v>
+        <v>121500</v>
       </c>
       <c r="J5" s="5">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>260000</v>
+        <v>324000</v>
       </c>
       <c r="G6" s="7">
-        <v>53000</v>
+        <v>43000</v>
       </c>
       <c r="H6" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>34600</v>
+        <v>37667</v>
       </c>
       <c r="J6" s="5">
-        <v>80.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>309000</v>
+        <v>327000</v>
       </c>
       <c r="G7" s="7">
-        <v>39000</v>
+        <v>46000</v>
       </c>
       <c r="H7" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>21400</v>
+        <v>28833</v>
       </c>
       <c r="J7" s="5">
-        <v>78.3</v>
+        <v>81.8</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>97.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>281000</v>
+        <v>349000</v>
       </c>
       <c r="G8" s="7">
-        <v>32000</v>
+        <v>40000</v>
       </c>
       <c r="H8" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>25400</v>
+        <v>24500</v>
       </c>
       <c r="J8" s="5">
-        <v>78</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>230000</v>
+        <v>194000</v>
       </c>
       <c r="G9" s="7">
-        <v>19000</v>
+        <v>29000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>25400</v>
+        <v>19500</v>
       </c>
       <c r="J9" s="5">
-        <v>77</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>104000</v>
+        <v>118000</v>
       </c>
       <c r="G10" s="7">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>13800</v>
+        <v>13833</v>
       </c>
       <c r="J10" s="5">
-        <v>76.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>579000</v>
+        <v>216000</v>
       </c>
       <c r="G11" s="7">
-        <v>24000</v>
+        <v>29000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
-        <v>23800</v>
+        <v>29500</v>
       </c>
       <c r="J11" s="5">
-        <v>75.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>92.3</v>
+        <v>91.8</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>387000</v>
+        <v>596000</v>
       </c>
       <c r="G12" s="7">
-        <v>19000</v>
+        <v>17000</v>
       </c>
       <c r="H12" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>23800</v>
+        <v>22667</v>
       </c>
       <c r="J12" s="5">
-        <v>74.7</v>
+        <v>76.2</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>89.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>414000</v>
+        <v>241000</v>
       </c>
       <c r="G13" s="7">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>27400</v>
+        <v>23000</v>
       </c>
       <c r="J13" s="5">
-        <v>74</v>
+        <v>76.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>98.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>187000</v>
+        <v>140000</v>
       </c>
       <c r="G14" s="7">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="H14" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>29667</v>
+        <v>13000</v>
       </c>
       <c r="J14" s="5">
-        <v>73.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>91.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>486000</v>
+        <v>217000</v>
       </c>
       <c r="G15" s="7">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="H15" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>17600</v>
+        <v>12500</v>
       </c>
       <c r="J15" s="5">
-        <v>72.8</v>
+        <v>75.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>94</v>
+        <v>90.3</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>201000</v>
+        <v>399000</v>
       </c>
       <c r="G16" s="7">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="H16" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>11800</v>
+        <v>21833</v>
       </c>
       <c r="J16" s="5">
-        <v>72.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>89.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>521000</v>
+        <v>172000</v>
       </c>
       <c r="G17" s="7">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="7">
-        <v>21200</v>
+        <v>12500</v>
       </c>
       <c r="J17" s="5">
-        <v>72.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>79.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>434000</v>
+        <v>149000</v>
       </c>
       <c r="G18" s="7">
-        <v>21000</v>
+        <v>47000</v>
       </c>
       <c r="H18" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="7">
-        <v>41800</v>
+        <v>7000</v>
       </c>
       <c r="J18" s="5">
-        <v>72.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>94.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>139000</v>
+        <v>497000</v>
       </c>
       <c r="G19" s="7">
-        <v>19000</v>
+        <v>11000</v>
       </c>
       <c r="H19" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>6600</v>
+        <v>16500</v>
       </c>
       <c r="J19" s="5">
-        <v>71.8</v>
+        <v>74</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>88.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>687000</v>
+        <v>524000</v>
       </c>
       <c r="G20" s="7">
-        <v>-4000</v>
+        <v>3000</v>
       </c>
       <c r="H20" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" s="7">
-        <v>19400</v>
+        <v>18167</v>
       </c>
       <c r="J20" s="5">
-        <v>71.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>165000</v>
+        <v>227000</v>
       </c>
       <c r="G21" s="7">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="H21" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>17600</v>
+        <v>14167</v>
       </c>
       <c r="J21" s="5">
-        <v>71.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>92.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>120000</v>
+        <v>207000</v>
       </c>
       <c r="G22" s="7">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="H22" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>11600</v>
+        <v>12333</v>
       </c>
       <c r="J22" s="5">
-        <v>71.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.7</v>
+        <v>92.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>448000</v>
+        <v>101000</v>
       </c>
       <c r="G23" s="7">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="H23" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>18600</v>
+        <v>7833</v>
       </c>
       <c r="J23" s="5">
-        <v>71.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>137000</v>
+        <v>682000</v>
       </c>
       <c r="G24" s="7">
-        <v>17000</v>
+        <v>-5000</v>
       </c>
       <c r="H24" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="7">
-        <v>11800</v>
+        <v>15333</v>
       </c>
       <c r="J24" s="5">
-        <v>71.3</v>
+        <v>72.5</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>219000</v>
+        <v>448000</v>
       </c>
       <c r="G25" s="7">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="H25" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>13000</v>
+        <v>37167</v>
       </c>
       <c r="J25" s="5">
-        <v>71.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>87.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>245000</v>
+        <v>155000</v>
       </c>
       <c r="G26" s="7">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="H26" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="7">
-        <v>18800</v>
+        <v>12833</v>
       </c>
       <c r="J26" s="5">
-        <v>71</v>
+        <v>72.2</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>90.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>157000</v>
+        <v>406000</v>
       </c>
       <c r="G27" s="7">
-        <v>12000</v>
+        <v>-8000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>12000</v>
+        <v>21500</v>
       </c>
       <c r="J27" s="5">
-        <v>71</v>
+        <v>71.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>89</v>
+        <v>91.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>211000</v>
+        <v>105000</v>
       </c>
       <c r="G28" s="7">
-        <v>13000</v>
+        <v>8000</v>
       </c>
       <c r="H28" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>13800</v>
+        <v>5500</v>
       </c>
       <c r="J28" s="5">
-        <v>70.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>92.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>123000</v>
+        <v>615000</v>
       </c>
       <c r="G29" s="7">
-        <v>13000</v>
+        <v>30000</v>
       </c>
       <c r="H29" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>6400</v>
+        <v>38333</v>
       </c>
       <c r="J29" s="5">
-        <v>70.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>81.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>862000</v>
+        <v>245000</v>
       </c>
       <c r="G30" s="7">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="H30" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" s="7">
-        <v>29400</v>
+        <v>15667</v>
       </c>
       <c r="J30" s="5">
-        <v>70.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>80.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>597000</v>
+        <v>107000</v>
       </c>
       <c r="G31" s="7">
-        <v>21000</v>
+        <v>7000</v>
       </c>
       <c r="H31" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>28800</v>
+        <v>9000</v>
       </c>
       <c r="J31" s="5">
-        <v>69.7</v>
+        <v>71.5</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>75.3</v>
+        <v>90</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>585000</v>
+        <v>106000</v>
       </c>
       <c r="G32" s="7">
-        <v>31000</v>
+        <v>8000</v>
       </c>
       <c r="H32" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="7">
-        <v>40000</v>
+        <v>5833</v>
       </c>
       <c r="J32" s="5">
-        <v>69.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>89.8</v>
+        <v>87</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>147000</v>
+        <v>105000</v>
       </c>
       <c r="G33" s="7">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" s="7">
-        <v>7800</v>
+        <v>12667</v>
       </c>
       <c r="J33" s="5">
-        <v>69.3</v>
+        <v>71</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>89.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>299000</v>
+        <v>105000</v>
       </c>
       <c r="G34" s="7">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H34" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" s="7">
-        <v>8000</v>
+        <v>6333</v>
       </c>
       <c r="J34" s="5">
-        <v>69.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>88.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>100000</v>
+        <v>873000</v>
       </c>
       <c r="G35" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>9400</v>
+        <v>26333</v>
       </c>
       <c r="J35" s="5">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>81.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>731000</v>
+        <v>437000</v>
       </c>
       <c r="G36" s="7">
-        <v>15000</v>
+        <v>-11000</v>
       </c>
       <c r="H36" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="7">
-        <v>25200</v>
+        <v>13667</v>
       </c>
       <c r="J36" s="5">
-        <v>69.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>84.90000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>284000</v>
+        <v>128000</v>
       </c>
       <c r="G37" s="7">
-        <v>-2000</v>
+        <v>13000</v>
       </c>
       <c r="H37" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>16400</v>
+        <v>9333</v>
       </c>
       <c r="J37" s="5">
-        <v>68.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>77.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>490000</v>
+        <v>744000</v>
       </c>
       <c r="G38" s="7">
-        <v>19000</v>
+        <v>13000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="7">
-        <v>32200</v>
+        <v>23167</v>
       </c>
       <c r="J38" s="5">
-        <v>68.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>80.5</v>
+        <v>88</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>336000</v>
+        <v>202000</v>
       </c>
       <c r="G39" s="7">
-        <v>17000</v>
+        <v>3000</v>
       </c>
       <c r="H39" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>25800</v>
+        <v>8000</v>
       </c>
       <c r="J39" s="5">
-        <v>68.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>88</v>
+        <v>80.3</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>199000</v>
+        <v>353000</v>
       </c>
       <c r="G40" s="7">
-        <v>3000</v>
+        <v>17000</v>
       </c>
       <c r="H40" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>9000</v>
+        <v>24333</v>
       </c>
       <c r="J40" s="5">
-        <v>68.7</v>
+        <v>70.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>228000</v>
+        <v>469000</v>
       </c>
       <c r="G41" s="7">
-        <v>4000</v>
+        <v>21000</v>
       </c>
       <c r="H41" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>7200</v>
+        <v>22833</v>
       </c>
       <c r="J41" s="5">
-        <v>68.5</v>
+        <v>70</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>87</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>251000</v>
+        <v>172000</v>
       </c>
       <c r="G42" s="7">
         <v>8000</v>
       </c>
       <c r="H42" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>10400</v>
+        <v>5000</v>
       </c>
       <c r="J42" s="5">
-        <v>68.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>89.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>110000</v>
+        <v>504000</v>
       </c>
       <c r="G43" s="7">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="H43" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="7">
-        <v>5600</v>
+        <v>29167</v>
       </c>
       <c r="J43" s="5">
-        <v>68.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>85.8</v>
+        <v>86.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>195000</v>
+        <v>152000</v>
       </c>
       <c r="G44" s="7">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H44" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" s="7">
-        <v>12400</v>
+        <v>7333</v>
       </c>
       <c r="J44" s="5">
-        <v>68.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>82.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>293000</v>
+        <v>113000</v>
       </c>
       <c r="G45" s="7">
-        <v>22000</v>
+        <v>4000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I45" s="7">
-        <v>19800</v>
+        <v>6500</v>
       </c>
       <c r="J45" s="5">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>88.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>123000</v>
+        <v>143000</v>
       </c>
       <c r="G46" s="7">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="H46" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I46" s="7">
-        <v>6400</v>
+        <v>5500</v>
       </c>
       <c r="J46" s="5">
-        <v>68.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>448000</v>
+        <v>312000</v>
       </c>
       <c r="G47" s="7">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="H47" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" s="7">
-        <v>23200</v>
+        <v>19667</v>
       </c>
       <c r="J47" s="5">
-        <v>68</v>
+        <v>69.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.8</v>
+        <v>88.3</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>140000</v>
+        <v>175000</v>
       </c>
       <c r="G48" s="7">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="H48" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I48" s="7">
-        <v>6000</v>
+        <v>2167</v>
       </c>
       <c r="J48" s="5">
-        <v>67.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>87.3</v>
+        <v>86.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>123000</v>
+        <v>298000</v>
       </c>
       <c r="G49" s="7">
-        <v>7000</v>
+        <v>-1000</v>
       </c>
       <c r="H49" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I49" s="7">
-        <v>7200</v>
+        <v>6500</v>
       </c>
       <c r="J49" s="5">
-        <v>67.8</v>
+        <v>69</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>87.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>109000</v>
+        <v>278000</v>
       </c>
       <c r="G50" s="7">
-        <v>4000</v>
+        <v>-6000</v>
       </c>
       <c r="H50" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I50" s="7">
-        <v>7000</v>
+        <v>12667</v>
       </c>
       <c r="J50" s="5">
-        <v>67.8</v>
+        <v>69</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>90.2</v>
+        <v>85.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>137000</v>
+        <v>242000</v>
       </c>
       <c r="G51" s="7">
-        <v>7000</v>
+        <v>28000</v>
       </c>
       <c r="H51" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I51" s="7">
-        <v>400</v>
+        <v>7167</v>
       </c>
       <c r="J51" s="5">
-        <v>67.7</v>
+        <v>69</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>89.3</v>
+        <v>86</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>104000</v>
+        <v>228000</v>
       </c>
       <c r="G52" s="7">
-        <v>8000</v>
+        <v>32000</v>
       </c>
       <c r="H52" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I52" s="7">
-        <v>12750</v>
+        <v>6833</v>
       </c>
       <c r="J52" s="5">
-        <v>67.3</v>
+        <v>69</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>81.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>403000</v>
+        <v>571000</v>
       </c>
       <c r="G53" s="7">
-        <v>24000</v>
+        <v>30000</v>
       </c>
       <c r="H53" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I53" s="7">
-        <v>16600</v>
+        <v>17333</v>
       </c>
       <c r="J53" s="5">
-        <v>67.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>79.2</v>
+        <v>88.5</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>804000</v>
+        <v>395000</v>
       </c>
       <c r="G54" s="7">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="H54" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I54" s="7">
-        <v>21400</v>
+        <v>833</v>
       </c>
       <c r="J54" s="5">
-        <v>66.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-08-31T05:10:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-01T04:47:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>诡舍2</t>
   </si>
   <si>
-    <t>打开作品</t>
+    <t>轮回修仙：从考科举开始</t>
+  </si>
+  <si>
+    <t>女尊，独自抚养妹妹们的正太哥哥</t>
   </si>
   <si>
     <t>女多男少，开局分配辅导员老婆</t>
   </si>
   <si>
-    <t>轮回修仙：从考科举开始</t>
+    <t>身家300亿美刀，重回1988</t>
+  </si>
+  <si>
+    <t>女儿被诈两亿，天家千金遭曝光</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>觉醒：EX级法师，开局无限火力</t>
+  </si>
+  <si>
+    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
+  </si>
+  <si>
+    <t>名柯：我有三角洲召唤系统</t>
+  </si>
+  <si>
+    <t>不是，让我一个剑修去联姻？</t>
+  </si>
+  <si>
+    <t>名义：我避开祁同伟几十年</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
   </si>
   <si>
     <t>四合院：从亮剑到人民的名义</t>
   </si>
   <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>不是，让我一个剑修去联姻？</t>
-  </si>
-  <si>
-    <t>女尊，独自抚养妹妹们的正太哥哥</t>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>开局豪门继承人，怎么还要上恋综</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>三体：我还以为是全知域呢！</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>转生异能锁，开局逼校花超兽武装</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>穿成丧尸小萝莉，凤傲天求放过</t>
+  </si>
+  <si>
+    <t>让你暑假实习，你去地府当鬼差！</t>
+  </si>
+  <si>
+    <t>高考落榜，买彩票狂中六亿</t>
+  </si>
+  <si>
+    <t>大唐长生者，但开局在玄武门？</t>
+  </si>
+  <si>
+    <t>综漫：人在霓虹，开局永恒万花筒</t>
+  </si>
+  <si>
+    <t>游戏入侵：在诡异副本玩转搜打撤</t>
+  </si>
+  <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>让你荒淫无道，千古一帝什么鬼？</t>
+  </si>
+  <si>
+    <t>名义：我调任汉东，孙连城笑了！</t>
+  </si>
+  <si>
+    <t>反派老婆破产后，她们都盯上我？</t>
+  </si>
+  <si>
+    <t>封神：一年升一境，哪吒喊我爹！</t>
+  </si>
+  <si>
+    <t>不对劲，我穿越的都是里世界</t>
+  </si>
+  <si>
+    <t>屠城就能回蓝星？兄弟你早说啊！</t>
+  </si>
+  <si>
+    <t>与冯宝宝的婚后生活</t>
+  </si>
+  <si>
+    <t>大唐：言出法随，都以为我是仙！</t>
+  </si>
+  <si>
+    <t>三角洲：FPS暴君降临</t>
+  </si>
+  <si>
+    <t>觉醒伪神，神明弃我，我自为神</t>
   </si>
   <si>
     <t>我老婆有白月光？她怎么不知道</t>
   </si>
   <si>
-    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
-  </si>
-  <si>
-    <t>开局豪门继承人，怎么还要上恋综</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>名义：我避开祁同伟几十年</t>
-  </si>
-  <si>
-    <t>名柯：我有三角洲召唤系统</t>
-  </si>
-  <si>
-    <t>觉醒：EX级法师，开局无限火力</t>
+    <t>村长，收手吧，外面全是套路！</t>
+  </si>
+  <si>
+    <t>大秦我带秦始皇长生不老</t>
+  </si>
+  <si>
+    <t>同学们选武侠仙侠，我选洪荒世界</t>
   </si>
   <si>
     <t>猎魔人小姐，我真不是血族</t>
   </si>
   <si>
-    <t>别人穿四合院，我为啥上战场</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
-  </si>
-  <si>
-    <t>穿成丧尸小萝莉，凤傲天求放过</t>
-  </si>
-  <si>
-    <t>高考落榜，买彩票狂中六亿</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>让你荒淫无道，千古一帝什么鬼？</t>
-  </si>
-  <si>
-    <t>不对劲，我穿越的都是里世界</t>
-  </si>
-  <si>
-    <t>屠城就能回蓝星？兄弟你早说啊！</t>
-  </si>
-  <si>
-    <t>游戏入侵：在诡异副本玩转搜打撤</t>
-  </si>
-  <si>
-    <t>觉醒伪神，神明弃我，我自为神</t>
-  </si>
-  <si>
-    <t>穿书成富二代，我直接救赎女主</t>
-  </si>
-  <si>
-    <t>穿越异界，我靠剑道成神</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>1995：从被抓到出轨开始</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>大唐长生者，但开局在玄武门？</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>国运：我的队友是瞎子骗子戏子</t>
-  </si>
-  <si>
-    <t>列车求生，我能升华一切！</t>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>火影：人在木叶村，开局觉醒木遁</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
   </si>
   <si>
     <t>欢迎都显怀了，你还没释怀</t>
   </si>
   <si>
-    <t>三角洲：FPS暴君降临</t>
-  </si>
-  <si>
-    <t>大秦我带秦始皇长生不老</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>民国：张家逆子，我才是东北王</t>
-  </si>
-  <si>
-    <t>聊天群约架，什么叫太上老君来了</t>
-  </si>
-  <si>
-    <t>重生98：带百万兄弟搞工业</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>全班同学拜大宗师，我拜菩提祖师</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>我都成烛龙了，人类怎么才诞生？</t>
-  </si>
-  <si>
-    <t>村花的傻子老公</t>
-  </si>
-  <si>
-    <t>火影：人在木叶村，开局觉醒木遁</t>
-  </si>
-  <si>
-    <t>只想躺平开民宿，咋就活成顶流了</t>
-  </si>
-  <si>
-    <t>站中间抽两边，什么叫霸之意志呀</t>
+    <t>实习教出金牌班，家长要换班主任</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>380000</v>
+        <v>1753000</v>
       </c>
       <c r="G5" s="7">
-        <v>90000</v>
+        <v>556000</v>
       </c>
       <c r="H5" s="7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>121500</v>
+        <v>76714</v>
       </c>
       <c r="J5" s="5">
-        <v>89</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>324000</v>
+        <v>447000</v>
       </c>
       <c r="G6" s="7">
-        <v>43000</v>
+        <v>67000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I6" s="7">
-        <v>37667</v>
+        <v>103333</v>
       </c>
       <c r="J6" s="5">
-        <v>84.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>327000</v>
+        <v>373000</v>
       </c>
       <c r="G7" s="7">
         <v>46000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>28833</v>
+        <v>31286</v>
       </c>
       <c r="J7" s="5">
-        <v>81.8</v>
+        <v>82.8</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>349000</v>
+        <v>253000</v>
       </c>
       <c r="G8" s="7">
-        <v>40000</v>
+        <v>37000</v>
       </c>
       <c r="H8" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>24500</v>
+        <v>31000</v>
       </c>
       <c r="J8" s="5">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>194000</v>
+        <v>345000</v>
       </c>
       <c r="G9" s="7">
-        <v>29000</v>
+        <v>21000</v>
       </c>
       <c r="H9" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" s="7">
-        <v>19500</v>
+        <v>35286</v>
       </c>
       <c r="J9" s="5">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>118000</v>
+        <v>144000</v>
       </c>
       <c r="G10" s="7">
-        <v>14000</v>
+        <v>49000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
-        <v>13833</v>
+        <v>27000</v>
       </c>
       <c r="J10" s="5">
-        <v>77.8</v>
+        <v>76.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>216000</v>
+        <v>196000</v>
       </c>
       <c r="G11" s="7">
-        <v>29000</v>
+        <v>47000</v>
       </c>
       <c r="H11" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" s="7">
-        <v>29500</v>
+        <v>40667</v>
       </c>
       <c r="J11" s="5">
-        <v>77.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>91.8</v>
+        <v>93</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>596000</v>
+        <v>208000</v>
       </c>
       <c r="G12" s="7">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>22667</v>
+        <v>18714</v>
       </c>
       <c r="J12" s="5">
-        <v>76.2</v>
+        <v>75.8</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>91.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>241000</v>
+        <v>170000</v>
       </c>
       <c r="G13" s="7">
-        <v>11000</v>
+        <v>21000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>23000</v>
+        <v>9000</v>
       </c>
       <c r="J13" s="5">
-        <v>76.2</v>
+        <v>75.5</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>95.7</v>
+        <v>90.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>140000</v>
+        <v>249000</v>
       </c>
       <c r="G14" s="7">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
-        <v>13000</v>
+        <v>20857</v>
       </c>
       <c r="J14" s="5">
-        <v>75.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>217000</v>
+        <v>185000</v>
       </c>
       <c r="G15" s="7">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>12500</v>
+        <v>12571</v>
       </c>
       <c r="J15" s="5">
-        <v>75.2</v>
+        <v>74.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>90.3</v>
+        <v>92.3</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>399000</v>
+        <v>126000</v>
       </c>
       <c r="G16" s="7">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="H16" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I16" s="7">
-        <v>21833</v>
+        <v>13000</v>
       </c>
       <c r="J16" s="5">
-        <v>75.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>94.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>172000</v>
+        <v>405000</v>
       </c>
       <c r="G17" s="7">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="H17" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>12500</v>
+        <v>19571</v>
       </c>
       <c r="J17" s="5">
-        <v>74.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>95.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>149000</v>
+        <v>227000</v>
       </c>
       <c r="G18" s="7">
-        <v>47000</v>
+        <v>10000</v>
       </c>
       <c r="H18" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I18" s="7">
-        <v>7000</v>
+        <v>12143</v>
       </c>
       <c r="J18" s="5">
-        <v>74.5</v>
+        <v>73.3</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>90.7</v>
+        <v>85</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>497000</v>
+        <v>374000</v>
       </c>
       <c r="G19" s="7">
-        <v>11000</v>
+        <v>25000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>16500</v>
+        <v>24571</v>
       </c>
       <c r="J19" s="5">
-        <v>74</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>89.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>524000</v>
+        <v>277000</v>
       </c>
       <c r="G20" s="7">
-        <v>3000</v>
+        <v>19000</v>
       </c>
       <c r="H20" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" s="7">
-        <v>18167</v>
+        <v>8429</v>
       </c>
       <c r="J20" s="5">
-        <v>73.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>90.2</v>
+        <v>89.8</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>227000</v>
+        <v>149000</v>
       </c>
       <c r="G21" s="7">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>14167</v>
+        <v>12429</v>
       </c>
       <c r="J21" s="5">
-        <v>73.2</v>
+        <v>72.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>91.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>207000</v>
+        <v>115000</v>
       </c>
       <c r="G22" s="7">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>12333</v>
+        <v>6857</v>
       </c>
       <c r="J22" s="5">
-        <v>73.2</v>
+        <v>72.5</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>92.2</v>
+        <v>88.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>101000</v>
+        <v>239000</v>
       </c>
       <c r="G23" s="7">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I23" s="7">
-        <v>7833</v>
+        <v>13857</v>
       </c>
       <c r="J23" s="5">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>88.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>682000</v>
+        <v>678000</v>
       </c>
       <c r="G24" s="7">
-        <v>-5000</v>
+        <v>-4000</v>
       </c>
       <c r="H24" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I24" s="7">
-        <v>15333</v>
+        <v>12571</v>
       </c>
       <c r="J24" s="5">
-        <v>72.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>78.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>448000</v>
+        <v>165000</v>
       </c>
       <c r="G25" s="7">
-        <v>14000</v>
+        <v>27000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I25" s="7">
-        <v>37167</v>
+        <v>25667</v>
       </c>
       <c r="J25" s="5">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>89.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>155000</v>
+        <v>113000</v>
       </c>
       <c r="G26" s="7">
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="H26" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>12833</v>
+        <v>6000</v>
       </c>
       <c r="J26" s="5">
-        <v>72.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>84.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>406000</v>
+        <v>214000</v>
       </c>
       <c r="G27" s="7">
-        <v>-8000</v>
+        <v>7000</v>
       </c>
       <c r="H27" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>21500</v>
+        <v>11571</v>
       </c>
       <c r="J27" s="5">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>91.7</v>
+        <v>89.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>105000</v>
+        <v>201000</v>
       </c>
       <c r="G28" s="7">
-        <v>8000</v>
+        <v>13000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>5500</v>
+        <v>9571</v>
       </c>
       <c r="J28" s="5">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>76.59999999999999</v>
+        <v>90</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>615000</v>
+        <v>110000</v>
       </c>
       <c r="G29" s="7">
-        <v>30000</v>
+        <v>9000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>38333</v>
+        <v>8000</v>
       </c>
       <c r="J29" s="5">
-        <v>71.7</v>
+        <v>71.5</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>86.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>245000</v>
+        <v>897000</v>
       </c>
       <c r="G30" s="7">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="H30" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I30" s="7">
-        <v>15667</v>
+        <v>26000</v>
       </c>
       <c r="J30" s="5">
-        <v>71.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>89.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>107000</v>
+        <v>178000</v>
       </c>
       <c r="G31" s="7">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I31" s="7">
-        <v>9000</v>
+        <v>16250</v>
       </c>
       <c r="J31" s="5">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,23 +1650,23 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>106000</v>
+        <v>112000</v>
       </c>
       <c r="G32" s="7">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="H32" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>5833</v>
+        <v>5714</v>
       </c>
       <c r="J32" s="5">
         <v>71</v>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>87</v>
+        <v>86.3</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>105000</v>
+        <v>512000</v>
       </c>
       <c r="G33" s="7">
-        <v>6000</v>
+        <v>-12000</v>
       </c>
       <c r="H33" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" s="7">
-        <v>12667</v>
+        <v>13857</v>
       </c>
       <c r="J33" s="5">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,23 +1716,23 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>89.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>105000</v>
+        <v>459000</v>
       </c>
       <c r="G34" s="7">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="H34" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" s="7">
-        <v>6333</v>
+        <v>33429</v>
       </c>
       <c r="J34" s="5">
         <v>70.90000000000001</v>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>80.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>873000</v>
+        <v>173000</v>
       </c>
       <c r="G35" s="7">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="H35" s="7">
         <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>26333</v>
+        <v>12500</v>
       </c>
       <c r="J35" s="5">
-        <v>70.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>85.7</v>
+        <v>89.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>437000</v>
+        <v>220000</v>
       </c>
       <c r="G36" s="7">
-        <v>-11000</v>
+        <v>8000</v>
       </c>
       <c r="H36" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>13667</v>
+        <v>6000</v>
       </c>
       <c r="J36" s="5">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>87.7</v>
+        <v>92.2</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>128000</v>
+        <v>110000</v>
       </c>
       <c r="G37" s="7">
-        <v>13000</v>
+        <v>8000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>9333</v>
+        <v>8200</v>
       </c>
       <c r="J37" s="5">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>81.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>744000</v>
+        <v>166000</v>
       </c>
       <c r="G38" s="7">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="H38" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7">
-        <v>23167</v>
+        <v>12571</v>
       </c>
       <c r="J38" s="5">
-        <v>70.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>88</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>202000</v>
+        <v>395000</v>
       </c>
       <c r="G39" s="7">
-        <v>3000</v>
+        <v>-11000</v>
       </c>
       <c r="H39" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I39" s="7">
-        <v>8000</v>
+        <v>16857</v>
       </c>
       <c r="J39" s="5">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,14 +1914,14 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>80.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>353000</v>
+        <v>274000</v>
       </c>
       <c r="G40" s="7">
         <v>17000</v>
@@ -1930,10 +1930,10 @@
         <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>24333</v>
+        <v>19333</v>
       </c>
       <c r="J40" s="5">
-        <v>70.2</v>
+        <v>70</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>80.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>469000</v>
+        <v>121000</v>
       </c>
       <c r="G41" s="7">
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="H41" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I41" s="7">
-        <v>22833</v>
+        <v>16667</v>
       </c>
       <c r="J41" s="5">
         <v>70</v>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>88.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>172000</v>
+        <v>370000</v>
       </c>
       <c r="G42" s="7">
-        <v>8000</v>
+        <v>17000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I42" s="7">
-        <v>5000</v>
+        <v>23286</v>
       </c>
       <c r="J42" s="5">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>77.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>504000</v>
+        <v>633000</v>
       </c>
       <c r="G43" s="7">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="H43" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>29167</v>
+        <v>35429</v>
       </c>
       <c r="J43" s="5">
         <v>69.8</v>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.8</v>
+        <v>83.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>152000</v>
+        <v>564000</v>
       </c>
       <c r="G44" s="7">
-        <v>5000</v>
+        <v>-32000</v>
       </c>
       <c r="H44" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="7">
-        <v>7333</v>
+        <v>14857</v>
       </c>
       <c r="J44" s="5">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>87.3</v>
+        <v>90</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>113000</v>
+        <v>118000</v>
       </c>
       <c r="G45" s="7">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="H45" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I45" s="7">
-        <v>6500</v>
+        <v>1286</v>
       </c>
       <c r="J45" s="5">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>87.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>143000</v>
+        <v>489000</v>
       </c>
       <c r="G46" s="7">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="H46" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" s="7">
-        <v>5500</v>
+        <v>22429</v>
       </c>
       <c r="J46" s="5">
-        <v>69.3</v>
+        <v>69.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>80.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>312000</v>
+        <v>445000</v>
       </c>
       <c r="G47" s="7">
-        <v>19000</v>
+        <v>24000</v>
       </c>
       <c r="H47" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I47" s="7">
-        <v>19667</v>
+        <v>17857</v>
       </c>
       <c r="J47" s="5">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>88.3</v>
+        <v>84.8</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>175000</v>
+        <v>479000</v>
       </c>
       <c r="G48" s="7">
-        <v>9000</v>
+        <v>-18000</v>
       </c>
       <c r="H48" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I48" s="7">
-        <v>2167</v>
+        <v>11571</v>
       </c>
       <c r="J48" s="5">
-        <v>69.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
@@ -2221,16 +2221,16 @@
         <v>298000</v>
       </c>
       <c r="G49" s="7">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I49" s="7">
-        <v>6500</v>
+        <v>5571</v>
       </c>
       <c r="J49" s="5">
-        <v>69</v>
+        <v>69.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>83.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>278000</v>
+        <v>255000</v>
       </c>
       <c r="G50" s="7">
-        <v>-6000</v>
+        <v>27000</v>
       </c>
       <c r="H50" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I50" s="7">
-        <v>12667</v>
+        <v>9714</v>
       </c>
       <c r="J50" s="5">
-        <v>69</v>
+        <v>69.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>242000</v>
+        <v>516000</v>
       </c>
       <c r="G51" s="7">
-        <v>28000</v>
+        <v>12000</v>
       </c>
       <c r="H51" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" s="7">
-        <v>7167</v>
+        <v>26714</v>
       </c>
       <c r="J51" s="5">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>86</v>
+        <v>85.8</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>228000</v>
+        <v>215000</v>
       </c>
       <c r="G52" s="7">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="H52" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I52" s="7">
-        <v>6833</v>
+        <v>8714</v>
       </c>
       <c r="J52" s="5">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>81</v>
+        <v>86.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>571000</v>
+        <v>202000</v>
       </c>
       <c r="G53" s="7">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H53" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I53" s="7">
-        <v>17333</v>
+        <v>6857</v>
       </c>
       <c r="J53" s="5">
-        <v>68.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>88.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>395000</v>
+        <v>588000</v>
       </c>
       <c r="G54" s="7">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="H54" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I54" s="7">
-        <v>833</v>
+        <v>19429</v>
       </c>
       <c r="J54" s="5">
-        <v>68.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-01T04:47:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-02T04:08:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>诡舍2</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>轮回修仙：从考科举开始</t>
+  </si>
+  <si>
+    <t>女尊，独自抚养妹妹们的正太哥哥</t>
+  </si>
+  <si>
     <t>冒姓琅琊</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>诡舍2</t>
-  </si>
-  <si>
-    <t>轮回修仙：从考科举开始</t>
-  </si>
-  <si>
-    <t>女尊，独自抚养妹妹们的正太哥哥</t>
-  </si>
-  <si>
-    <t>女多男少，开局分配辅导员老婆</t>
+    <t>女儿被诈两亿，天家千金遭曝光</t>
   </si>
   <si>
     <t>身家300亿美刀，重回1988</t>
   </si>
   <si>
-    <t>女儿被诈两亿，天家千金遭曝光</t>
-  </si>
-  <si>
     <t>穿越成国公，咋就是封建余孽了？</t>
   </si>
   <si>
+    <t>转生异能锁，开局逼校花超兽武装</t>
+  </si>
+  <si>
+    <t>欢宋</t>
+  </si>
+  <si>
+    <t>封神：一年升一境，哪吒喊我爹！</t>
+  </si>
+  <si>
     <t>觉醒：EX级法师，开局无限火力</t>
   </si>
   <si>
+    <t>不是，让我一个剑修去联姻？</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
     <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
   </si>
   <si>
+    <t>三体：我还以为是全知域呢！</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>让你暑假实习，你去地府当鬼差！</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>大唐：言出法随，都以为我是仙！</t>
+  </si>
+  <si>
+    <t>名义：我调任汉东，孙连城笑了！</t>
+  </si>
+  <si>
+    <t>抗战：鬼子翻译？不，我代号财神</t>
+  </si>
+  <si>
+    <t>高考落榜，买彩票狂中六亿</t>
+  </si>
+  <si>
+    <t>综漫：人在霓虹，开局永恒万花筒</t>
+  </si>
+  <si>
+    <t>村长，收手吧，外面全是套路！</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>让你荒淫无道，千古一帝什么鬼？</t>
+  </si>
+  <si>
+    <t>重生：什么江湖大哥？资本大鳄！</t>
+  </si>
+  <si>
+    <t>穿成丧尸小萝莉，凤傲天求放过</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>大唐长生者，但开局在玄武门？</t>
+  </si>
+  <si>
+    <t>我老婆有白月光？她怎么不知道</t>
+  </si>
+  <si>
+    <t>村花的傻子老公</t>
+  </si>
+  <si>
+    <t>崩铁，死了47次，我决定去卖</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>火影：从离开木叶建立忍国开始</t>
+  </si>
+  <si>
+    <t>欢迎都显怀了，你还没释怀</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>游戏入侵：在诡异副本玩转搜打撤</t>
+  </si>
+  <si>
+    <t>大秦我带秦始皇长生不老</t>
+  </si>
+  <si>
+    <t>三角洲：FPS暴君降临</t>
+  </si>
+  <si>
+    <t>火影：人在木叶村，开局觉醒木遁</t>
+  </si>
+  <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>穿书成富二代，我直接救赎女主</t>
+  </si>
+  <si>
+    <t>玩弄感情的坏男孩就要被病娇狠狠</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
+  </si>
+  <si>
+    <t>开局豪门继承人，怎么还要上恋综</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
     <t>名柯：我有三角洲召唤系统</t>
   </si>
   <si>
-    <t>不是，让我一个剑修去联姻？</t>
-  </si>
-  <si>
     <t>名义：我避开祁同伟几十年</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>开局豪门继承人，怎么还要上恋综</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>转生异能锁，开局逼校花超兽武装</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>穿成丧尸小萝莉，凤傲天求放过</t>
-  </si>
-  <si>
-    <t>让你暑假实习，你去地府当鬼差！</t>
-  </si>
-  <si>
-    <t>高考落榜，买彩票狂中六亿</t>
-  </si>
-  <si>
-    <t>大唐长生者，但开局在玄武门？</t>
-  </si>
-  <si>
-    <t>综漫：人在霓虹，开局永恒万花筒</t>
-  </si>
-  <si>
-    <t>游戏入侵：在诡异副本玩转搜打撤</t>
-  </si>
-  <si>
-    <t>别人穿四合院，我为啥上战场</t>
-  </si>
-  <si>
-    <t>让你荒淫无道，千古一帝什么鬼？</t>
-  </si>
-  <si>
-    <t>名义：我调任汉东，孙连城笑了！</t>
-  </si>
-  <si>
-    <t>反派老婆破产后，她们都盯上我？</t>
-  </si>
-  <si>
-    <t>封神：一年升一境，哪吒喊我爹！</t>
-  </si>
-  <si>
-    <t>不对劲，我穿越的都是里世界</t>
-  </si>
-  <si>
-    <t>屠城就能回蓝星？兄弟你早说啊！</t>
-  </si>
-  <si>
-    <t>与冯宝宝的婚后生活</t>
-  </si>
-  <si>
-    <t>大唐：言出法随，都以为我是仙！</t>
-  </si>
-  <si>
-    <t>三角洲：FPS暴君降临</t>
-  </si>
-  <si>
-    <t>觉醒伪神，神明弃我，我自为神</t>
-  </si>
-  <si>
-    <t>我老婆有白月光？她怎么不知道</t>
-  </si>
-  <si>
-    <t>村长，收手吧，外面全是套路！</t>
-  </si>
-  <si>
-    <t>大秦我带秦始皇长生不老</t>
-  </si>
-  <si>
-    <t>同学们选武侠仙侠，我选洪荒世界</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>火影：人在木叶村，开局觉醒木遁</t>
-  </si>
-  <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>欢迎都显怀了，你还没释怀</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>96.2</v>
+        <v>98.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1753000</v>
+        <v>497000</v>
       </c>
       <c r="G5" s="7">
-        <v>556000</v>
+        <v>50000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I5" s="7">
-        <v>76714</v>
+        <v>90000</v>
       </c>
       <c r="J5" s="5">
-        <v>92.09999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>447000</v>
+        <v>419000</v>
       </c>
       <c r="G6" s="7">
-        <v>67000</v>
+        <v>46000</v>
       </c>
       <c r="H6" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I6" s="7">
-        <v>103333</v>
+        <v>33125</v>
       </c>
       <c r="J6" s="5">
-        <v>92</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,19 +832,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>373000</v>
+        <v>292000</v>
       </c>
       <c r="G7" s="7">
-        <v>46000</v>
+        <v>39000</v>
       </c>
       <c r="H7" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>31286</v>
+        <v>32333</v>
       </c>
       <c r="J7" s="5">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>81.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>253000</v>
+        <v>1758000</v>
       </c>
       <c r="G8" s="7">
-        <v>37000</v>
+        <v>5000</v>
       </c>
       <c r="H8" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I8" s="7">
-        <v>31000</v>
+        <v>67750</v>
       </c>
       <c r="J8" s="5">
-        <v>80.8</v>
+        <v>81.8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>345000</v>
+        <v>237000</v>
       </c>
       <c r="G9" s="7">
-        <v>21000</v>
+        <v>41000</v>
       </c>
       <c r="H9" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I9" s="7">
-        <v>35286</v>
+        <v>40750</v>
       </c>
       <c r="J9" s="5">
-        <v>79.3</v>
+        <v>80.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -931,19 +931,19 @@
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>144000</v>
+        <v>180000</v>
       </c>
       <c r="G10" s="7">
-        <v>49000</v>
+        <v>36000</v>
       </c>
       <c r="H10" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>27000</v>
+        <v>28800</v>
       </c>
       <c r="J10" s="5">
-        <v>76.8</v>
+        <v>80.2</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>98.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>196000</v>
+        <v>222000</v>
       </c>
       <c r="G11" s="7">
-        <v>47000</v>
+        <v>14000</v>
       </c>
       <c r="H11" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7">
-        <v>40667</v>
+        <v>18125</v>
       </c>
       <c r="J11" s="5">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>93</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>208000</v>
+        <v>189000</v>
       </c>
       <c r="G12" s="7">
-        <v>14000</v>
+        <v>24000</v>
       </c>
       <c r="H12" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>18714</v>
+        <v>25250</v>
       </c>
       <c r="J12" s="5">
-        <v>75.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>96.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>170000</v>
+        <v>101000</v>
       </c>
       <c r="G13" s="7">
-        <v>21000</v>
+        <v>9000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>9000</v>
+        <v>11833</v>
       </c>
       <c r="J13" s="5">
-        <v>75.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>90.3</v>
+        <v>95.5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>249000</v>
+        <v>122000</v>
       </c>
       <c r="G14" s="7">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="H14" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>20857</v>
+        <v>8833</v>
       </c>
       <c r="J14" s="5">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>185000</v>
+        <v>187000</v>
       </c>
       <c r="G15" s="7">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7">
-        <v>12571</v>
+        <v>10000</v>
       </c>
       <c r="J15" s="5">
-        <v>74.3</v>
+        <v>73.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>92.3</v>
+        <v>92</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>126000</v>
+        <v>134000</v>
       </c>
       <c r="G16" s="7">
         <v>8000</v>
       </c>
       <c r="H16" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>13000</v>
+        <v>12375</v>
       </c>
       <c r="J16" s="5">
-        <v>74</v>
+        <v>73.7</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>88.7</v>
+        <v>92.5</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>405000</v>
+        <v>298000</v>
       </c>
       <c r="G17" s="7">
-        <v>6000</v>
+        <v>21000</v>
       </c>
       <c r="H17" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7">
-        <v>19571</v>
+        <v>10000</v>
       </c>
       <c r="J17" s="5">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>91.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>227000</v>
+        <v>253000</v>
       </c>
       <c r="G18" s="7">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="H18" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7">
-        <v>12143</v>
+        <v>18750</v>
       </c>
       <c r="J18" s="5">
-        <v>73.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>85</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>374000</v>
+        <v>250000</v>
       </c>
       <c r="G19" s="7">
-        <v>25000</v>
+        <v>11000</v>
       </c>
       <c r="H19" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I19" s="7">
-        <v>24571</v>
+        <v>13500</v>
       </c>
       <c r="J19" s="5">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>277000</v>
+        <v>235000</v>
       </c>
       <c r="G20" s="7">
-        <v>19000</v>
+        <v>8000</v>
       </c>
       <c r="H20" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>8429</v>
+        <v>11625</v>
       </c>
       <c r="J20" s="5">
-        <v>72.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>149000</v>
+        <v>215000</v>
       </c>
       <c r="G21" s="7">
-        <v>9000</v>
+        <v>14000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" s="7">
-        <v>12429</v>
+        <v>10125</v>
       </c>
       <c r="J21" s="5">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>92.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>115000</v>
+        <v>124000</v>
       </c>
       <c r="G22" s="7">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="7">
-        <v>6857</v>
+        <v>7125</v>
       </c>
       <c r="J22" s="5">
-        <v>72.5</v>
+        <v>72.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>239000</v>
+        <v>135000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="H23" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I23" s="7">
-        <v>13857</v>
+        <v>16000</v>
       </c>
       <c r="J23" s="5">
-        <v>72.3</v>
+        <v>72</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>88.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>678000</v>
+        <v>184000</v>
       </c>
       <c r="G24" s="7">
-        <v>-4000</v>
+        <v>11000</v>
       </c>
       <c r="H24" s="7">
         <v>8</v>
       </c>
       <c r="I24" s="7">
-        <v>12571</v>
+        <v>12286</v>
       </c>
       <c r="J24" s="5">
-        <v>71.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,23 +1419,23 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>96.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>165000</v>
+        <v>105000</v>
       </c>
       <c r="G25" s="7">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="H25" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>25667</v>
+        <v>13167</v>
       </c>
       <c r="J25" s="5">
         <v>71.7</v>
@@ -1452,23 +1452,23 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>91</v>
+        <v>90.2</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>113000</v>
+        <v>119000</v>
       </c>
       <c r="G26" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H26" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I26" s="7">
-        <v>6000</v>
+        <v>8125</v>
       </c>
       <c r="J26" s="5">
         <v>71.59999999999999</v>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>88.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>214000</v>
+        <v>193000</v>
       </c>
       <c r="G27" s="7">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H27" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>11571</v>
+        <v>16000</v>
       </c>
       <c r="J27" s="5">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>89.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>201000</v>
+        <v>129000</v>
       </c>
       <c r="G28" s="7">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" s="7">
-        <v>9571</v>
+        <v>2500</v>
       </c>
       <c r="J28" s="5">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>110000</v>
+        <v>673000</v>
       </c>
       <c r="G29" s="7">
-        <v>9000</v>
+        <v>-5000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" s="7">
-        <v>8000</v>
+        <v>10375</v>
       </c>
       <c r="J29" s="5">
-        <v>71.5</v>
+        <v>71.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>81.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>897000</v>
+        <v>472000</v>
       </c>
       <c r="G30" s="7">
-        <v>24000</v>
+        <v>13000</v>
       </c>
       <c r="H30" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I30" s="7">
-        <v>26000</v>
+        <v>30875</v>
       </c>
       <c r="J30" s="5">
-        <v>71.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>95</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>178000</v>
+        <v>292000</v>
       </c>
       <c r="G31" s="7">
-        <v>18000</v>
+        <v>30000</v>
       </c>
       <c r="H31" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" s="7">
-        <v>16250</v>
+        <v>18600</v>
       </c>
       <c r="J31" s="5">
-        <v>71.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>90.2</v>
+        <v>87.3</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>112000</v>
+        <v>217000</v>
       </c>
       <c r="G32" s="7">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="H32" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I32" s="7">
-        <v>5714</v>
+        <v>10500</v>
       </c>
       <c r="J32" s="5">
-        <v>71</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>86.3</v>
+        <v>89.2</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>512000</v>
+        <v>121000</v>
       </c>
       <c r="G33" s="7">
-        <v>-12000</v>
+        <v>8000</v>
       </c>
       <c r="H33" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I33" s="7">
-        <v>13857</v>
+        <v>6250</v>
       </c>
       <c r="J33" s="5">
-        <v>70.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>77.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>459000</v>
+        <v>908000</v>
       </c>
       <c r="G34" s="7">
         <v>11000</v>
       </c>
       <c r="H34" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="7">
-        <v>33429</v>
+        <v>24125</v>
       </c>
       <c r="J34" s="5">
-        <v>70.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>86.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>173000</v>
+        <v>549000</v>
       </c>
       <c r="G35" s="7">
-        <v>8000</v>
+        <v>-15000</v>
       </c>
       <c r="H35" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>12500</v>
+        <v>11125</v>
       </c>
       <c r="J35" s="5">
-        <v>70.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>89.7</v>
+        <v>85.2</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>220000</v>
+        <v>302000</v>
       </c>
       <c r="G36" s="7">
-        <v>8000</v>
+        <v>26000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I36" s="7">
-        <v>6000</v>
+        <v>12875</v>
       </c>
       <c r="J36" s="5">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>92.2</v>
+        <v>87</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>110000</v>
+        <v>247000</v>
       </c>
       <c r="G37" s="7">
-        <v>8000</v>
+        <v>41000</v>
       </c>
       <c r="H37" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I37" s="7">
-        <v>8200</v>
+        <v>28750</v>
       </c>
       <c r="J37" s="5">
-        <v>70.8</v>
+        <v>70</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>85.7</v>
+        <v>80.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>166000</v>
+        <v>386000</v>
       </c>
       <c r="G38" s="7">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="H38" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>12571</v>
+        <v>23000</v>
       </c>
       <c r="J38" s="5">
-        <v>70.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>83.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>395000</v>
+        <v>160000</v>
       </c>
       <c r="G39" s="7">
-        <v>-11000</v>
+        <v>17000</v>
       </c>
       <c r="H39" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I39" s="7">
-        <v>16857</v>
+        <v>16750</v>
       </c>
       <c r="J39" s="5">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>82.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>274000</v>
+        <v>203000</v>
       </c>
       <c r="G40" s="7">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="H40" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I40" s="7">
-        <v>19333</v>
+        <v>6125</v>
       </c>
       <c r="J40" s="5">
-        <v>70</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>97.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>121000</v>
+        <v>608000</v>
       </c>
       <c r="G41" s="7">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="H41" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I41" s="7">
-        <v>16667</v>
+        <v>19500</v>
       </c>
       <c r="J41" s="5">
-        <v>70</v>
+        <v>69.3</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>80.2</v>
+        <v>87.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>370000</v>
+        <v>116000</v>
       </c>
       <c r="G42" s="7">
-        <v>17000</v>
+        <v>4000</v>
       </c>
       <c r="H42" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I42" s="7">
-        <v>23286</v>
+        <v>5500</v>
       </c>
       <c r="J42" s="5">
-        <v>69.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>74.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>633000</v>
+        <v>506000</v>
       </c>
       <c r="G43" s="7">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="H43" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I43" s="7">
-        <v>35429</v>
+        <v>21750</v>
       </c>
       <c r="J43" s="5">
-        <v>69.8</v>
+        <v>69.2</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>83.8</v>
+        <v>79.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>564000</v>
+        <v>384000</v>
       </c>
       <c r="G44" s="7">
-        <v>-32000</v>
+        <v>14000</v>
       </c>
       <c r="H44" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I44" s="7">
-        <v>14857</v>
+        <v>22125</v>
       </c>
       <c r="J44" s="5">
-        <v>69.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>90</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>118000</v>
+        <v>279000</v>
       </c>
       <c r="G45" s="7">
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="H45" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I45" s="7">
-        <v>1286</v>
+        <v>11500</v>
       </c>
       <c r="J45" s="5">
-        <v>69.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>80.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>489000</v>
+        <v>491000</v>
       </c>
       <c r="G46" s="7">
-        <v>20000</v>
+        <v>-21000</v>
       </c>
       <c r="H46" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I46" s="7">
-        <v>22429</v>
+        <v>9500</v>
       </c>
       <c r="J46" s="5">
-        <v>69.7</v>
+        <v>68.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>82.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>445000</v>
+        <v>232000</v>
       </c>
       <c r="G47" s="7">
-        <v>24000</v>
+        <v>-5000</v>
       </c>
       <c r="H47" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>17857</v>
+        <v>10125</v>
       </c>
       <c r="J47" s="5">
-        <v>69.7</v>
+        <v>68.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>84.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>479000</v>
+        <v>152000</v>
       </c>
       <c r="G48" s="7">
-        <v>-18000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>11571</v>
+        <v>5750</v>
       </c>
       <c r="J48" s="5">
-        <v>69.5</v>
+        <v>68.7</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>87.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>298000</v>
+        <v>526000</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H49" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I49" s="7">
-        <v>5571</v>
+        <v>24625</v>
       </c>
       <c r="J49" s="5">
-        <v>69.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>85.5</v>
+        <v>89</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>255000</v>
+        <v>138000</v>
       </c>
       <c r="G50" s="7">
-        <v>27000</v>
+        <v>21000</v>
       </c>
       <c r="H50" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7">
-        <v>9714</v>
+        <v>18500</v>
       </c>
       <c r="J50" s="5">
-        <v>69.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>77.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>516000</v>
+        <v>150000</v>
       </c>
       <c r="G51" s="7">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="H51" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I51" s="7">
-        <v>26714</v>
+        <v>11000</v>
       </c>
       <c r="J51" s="5">
-        <v>69.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>85.8</v>
+        <v>85.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>215000</v>
+        <v>398000</v>
       </c>
       <c r="G52" s="7">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="H52" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I52" s="7">
-        <v>8714</v>
+        <v>5375</v>
       </c>
       <c r="J52" s="5">
-        <v>69.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>86.5</v>
+        <v>83.3</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>202000</v>
+        <v>181000</v>
       </c>
       <c r="G53" s="7">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="H53" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>6857</v>
+        <v>10500</v>
       </c>
       <c r="J53" s="5">
-        <v>69.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>80.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>588000</v>
+        <v>371000</v>
       </c>
       <c r="G54" s="7">
-        <v>24000</v>
+        <v>-34000</v>
       </c>
       <c r="H54" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7">
-        <v>19429</v>
+        <v>12875</v>
       </c>
       <c r="J54" s="5">
-        <v>69.2</v>
+        <v>68.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-02T04:08:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-03T04:06:28+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,6 +76,9 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>身家300亿美刀，重回1988</t>
+  </si>
+  <si>
     <t>轮回修仙：从考科举开始</t>
   </si>
   <si>
@@ -85,142 +88,139 @@
     <t>冒姓琅琊</t>
   </si>
   <si>
+    <t>火影：从离开木叶建立忍国开始</t>
+  </si>
+  <si>
     <t>女儿被诈两亿，天家千金遭曝光</t>
   </si>
   <si>
-    <t>身家300亿美刀，重回1988</t>
+    <t>觉醒：EX级法师，开局无限火力</t>
+  </si>
+  <si>
+    <t>转生异能锁，开局逼校花超兽武装</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
   </si>
   <si>
     <t>穿越成国公，咋就是封建余孽了？</t>
   </si>
   <si>
-    <t>转生异能锁，开局逼校花超兽武装</t>
+    <t>大唐：言出法随，都以为我是仙！</t>
+  </si>
+  <si>
+    <t>让你荒淫无道，千古一帝什么鬼？</t>
+  </si>
+  <si>
+    <t>穿书成富二代，我直接救赎女主</t>
+  </si>
+  <si>
+    <t>综漫：人在霓虹，开局永恒万花筒</t>
+  </si>
+  <si>
+    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
   </si>
   <si>
     <t>欢宋</t>
   </si>
   <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>不是，让我一个剑修去联姻？</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>太子李承乾已死！你选的嘛陛下！</t>
+  </si>
+  <si>
+    <t>重生：什么江湖大哥？资本大鳄！</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>抗战：鬼子翻译？不，我代号财神</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>三体：我还以为是全知域呢！</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>让你暑假实习，你去地府当鬼差！</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>高考落榜，买彩票狂中六亿</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>大唐长生者，但开局在玄武门？</t>
+  </si>
+  <si>
+    <t>资本打压？我的电影越拍越红！</t>
+  </si>
+  <si>
+    <t>末日灾变序列</t>
+  </si>
+  <si>
+    <t>1995：从被抓到出轨开始</t>
+  </si>
+  <si>
+    <t>村花的傻子老公</t>
+  </si>
+  <si>
+    <t>名柯：我有三角洲召唤系统</t>
+  </si>
+  <si>
+    <t>我都攻克绝症了，渣一点怎么了？</t>
+  </si>
+  <si>
+    <t>游戏入侵：在诡异副本玩转搜打撤</t>
+  </si>
+  <si>
+    <t>名义：我调任汉东，孙连城笑了！</t>
+  </si>
+  <si>
+    <t>欢迎都显怀了，你还没释怀</t>
+  </si>
+  <si>
+    <t>开局睡了白月光，她要我割痔疮？</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
+  </si>
+  <si>
+    <t>包养姐姐闺蜜，被姐姐发现了</t>
+  </si>
+  <si>
     <t>封神：一年升一境，哪吒喊我爹！</t>
   </si>
   <si>
-    <t>觉醒：EX级法师，开局无限火力</t>
-  </si>
-  <si>
-    <t>不是，让我一个剑修去联姻？</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>让你暑假实习，你去地府当鬼差！</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>大唐：言出法随，都以为我是仙！</t>
-  </si>
-  <si>
-    <t>名义：我调任汉东，孙连城笑了！</t>
-  </si>
-  <si>
-    <t>抗战：鬼子翻译？不，我代号财神</t>
-  </si>
-  <si>
-    <t>高考落榜，买彩票狂中六亿</t>
-  </si>
-  <si>
-    <t>综漫：人在霓虹，开局永恒万花筒</t>
-  </si>
-  <si>
-    <t>村长，收手吧，外面全是套路！</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>让你荒淫无道，千古一帝什么鬼？</t>
-  </si>
-  <si>
-    <t>重生：什么江湖大哥？资本大鳄！</t>
-  </si>
-  <si>
-    <t>穿成丧尸小萝莉，凤傲天求放过</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>大唐长生者，但开局在玄武门？</t>
-  </si>
-  <si>
-    <t>我老婆有白月光？她怎么不知道</t>
-  </si>
-  <si>
-    <t>村花的傻子老公</t>
-  </si>
-  <si>
-    <t>崩铁，死了47次，我决定去卖</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>火影：从离开木叶建立忍国开始</t>
-  </si>
-  <si>
-    <t>欢迎都显怀了，你还没释怀</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>游戏入侵：在诡异副本玩转搜打撤</t>
-  </si>
-  <si>
-    <t>大秦我带秦始皇长生不老</t>
-  </si>
-  <si>
-    <t>三角洲：FPS暴君降临</t>
-  </si>
-  <si>
     <t>火影：人在木叶村，开局觉醒木遁</t>
   </si>
   <si>
     <t>别人穿四合院，我为啥上战场</t>
   </si>
   <si>
-    <t>穿书成富二代，我直接救赎女主</t>
-  </si>
-  <si>
-    <t>玩弄感情的坏男孩就要被病娇狠狠</t>
-  </si>
-  <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>我拿钱就走，九个姐姐全变病娇了</t>
-  </si>
-  <si>
-    <t>开局豪门继承人，怎么还要上恋综</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>名柯：我有三角洲召唤系统</t>
-  </si>
-  <si>
-    <t>名义：我避开祁同伟几十年</t>
+    <t>猎魔人小姐，我真不是血族</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>497000</v>
+        <v>581000</v>
       </c>
       <c r="G5" s="7">
-        <v>50000</v>
+        <v>84000</v>
       </c>
       <c r="H5" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>90000</v>
+        <v>88800</v>
       </c>
       <c r="J5" s="5">
-        <v>91.8</v>
+        <v>95.2</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>419000</v>
+        <v>217000</v>
       </c>
       <c r="G6" s="7">
-        <v>46000</v>
+        <v>37000</v>
       </c>
       <c r="H6" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>33125</v>
+        <v>30167</v>
       </c>
       <c r="J6" s="5">
-        <v>83.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>292000</v>
+        <v>454000</v>
       </c>
       <c r="G7" s="7">
-        <v>39000</v>
+        <v>35000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7">
-        <v>32333</v>
+        <v>33333</v>
       </c>
       <c r="J7" s="5">
-        <v>83.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>81.5</v>
+        <v>94.7</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>1758000</v>
+        <v>313000</v>
       </c>
       <c r="G8" s="7">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="H8" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
-        <v>67750</v>
+        <v>30714</v>
       </c>
       <c r="J8" s="5">
-        <v>81.8</v>
+        <v>79.8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>237000</v>
+        <v>1754000</v>
       </c>
       <c r="G9" s="7">
-        <v>41000</v>
+        <v>-4000</v>
       </c>
       <c r="H9" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I9" s="7">
-        <v>40750</v>
+        <v>59778</v>
       </c>
       <c r="J9" s="5">
-        <v>80.2</v>
+        <v>79.5</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -931,19 +931,19 @@
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>180000</v>
+        <v>185000</v>
       </c>
       <c r="G10" s="7">
-        <v>36000</v>
+        <v>25000</v>
       </c>
       <c r="H10" s="7">
         <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>28800</v>
+        <v>18400</v>
       </c>
       <c r="J10" s="5">
-        <v>80.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>92.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>222000</v>
+        <v>251000</v>
       </c>
       <c r="G11" s="7">
         <v>14000</v>
       </c>
       <c r="H11" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>18125</v>
+        <v>35400</v>
       </c>
       <c r="J11" s="5">
-        <v>75.5</v>
+        <v>77.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>189000</v>
+        <v>213000</v>
       </c>
       <c r="G12" s="7">
-        <v>24000</v>
+        <v>26000</v>
       </c>
       <c r="H12" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>25250</v>
+        <v>11778</v>
       </c>
       <c r="J12" s="5">
-        <v>75.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>94.8</v>
+        <v>95.2</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>101000</v>
+        <v>210000</v>
       </c>
       <c r="G13" s="7">
-        <v>9000</v>
+        <v>21000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>11833</v>
+        <v>24400</v>
       </c>
       <c r="J13" s="5">
-        <v>75.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>95.5</v>
+        <v>97.8</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>122000</v>
+        <v>140000</v>
       </c>
       <c r="G14" s="7">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I14" s="7">
-        <v>8833</v>
+        <v>8111</v>
       </c>
       <c r="J14" s="5">
-        <v>74.7</v>
+        <v>75.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>187000</v>
+        <v>157000</v>
       </c>
       <c r="G15" s="7">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="H15" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>10000</v>
+        <v>18600</v>
       </c>
       <c r="J15" s="5">
-        <v>73.7</v>
+        <v>75.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>92</v>
+        <v>92.3</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>134000</v>
+        <v>236000</v>
       </c>
       <c r="G16" s="7">
-        <v>8000</v>
+        <v>14000</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I16" s="7">
-        <v>12375</v>
+        <v>17667</v>
       </c>
       <c r="J16" s="5">
-        <v>73.7</v>
+        <v>75.2</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92.5</v>
+        <v>96.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>298000</v>
+        <v>150000</v>
       </c>
       <c r="G17" s="7">
-        <v>21000</v>
+        <v>15000</v>
       </c>
       <c r="H17" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>10000</v>
+        <v>15800</v>
       </c>
       <c r="J17" s="5">
-        <v>73.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>88.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>253000</v>
+        <v>512000</v>
       </c>
       <c r="G18" s="7">
-        <v>4000</v>
+        <v>40000</v>
       </c>
       <c r="H18" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="7">
-        <v>18750</v>
+        <v>31889</v>
       </c>
       <c r="J18" s="5">
-        <v>73.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>89.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>250000</v>
+        <v>249000</v>
       </c>
       <c r="G19" s="7">
-        <v>11000</v>
+        <v>17000</v>
       </c>
       <c r="H19" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I19" s="7">
-        <v>13500</v>
+        <v>10889</v>
       </c>
       <c r="J19" s="5">
-        <v>72.8</v>
+        <v>73.7</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>235000</v>
+        <v>208000</v>
       </c>
       <c r="G20" s="7">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I20" s="7">
-        <v>11625</v>
+        <v>15833</v>
       </c>
       <c r="J20" s="5">
-        <v>72.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>91.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>215000</v>
+        <v>259000</v>
       </c>
       <c r="G21" s="7">
-        <v>14000</v>
+        <v>6000</v>
       </c>
       <c r="H21" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21" s="7">
-        <v>10125</v>
+        <v>17333</v>
       </c>
       <c r="J21" s="5">
-        <v>72.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>91.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>124000</v>
+        <v>108000</v>
       </c>
       <c r="G22" s="7">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="H22" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>7125</v>
+        <v>11143</v>
       </c>
       <c r="J22" s="5">
-        <v>72.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>96.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>135000</v>
+        <v>131000</v>
       </c>
       <c r="G23" s="7">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="H23" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I23" s="7">
-        <v>16000</v>
+        <v>6667</v>
       </c>
       <c r="J23" s="5">
-        <v>72</v>
+        <v>73.3</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>88.5</v>
+        <v>91</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>184000</v>
+        <v>141000</v>
       </c>
       <c r="G24" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H24" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I24" s="7">
-        <v>12286</v>
+        <v>11778</v>
       </c>
       <c r="J24" s="5">
-        <v>71.7</v>
+        <v>73</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>88.09999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>105000</v>
+        <v>244000</v>
       </c>
       <c r="G25" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I25" s="7">
-        <v>13167</v>
+        <v>11333</v>
       </c>
       <c r="J25" s="5">
-        <v>71.7</v>
+        <v>72.8</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>90.2</v>
+        <v>97.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>119000</v>
+        <v>101000</v>
       </c>
       <c r="G26" s="7">
-        <v>9000</v>
+        <v>23000</v>
       </c>
       <c r="H26" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I26" s="7">
-        <v>8125</v>
+        <v>15500</v>
       </c>
       <c r="J26" s="5">
-        <v>71.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>89.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>193000</v>
+        <v>321000</v>
       </c>
       <c r="G27" s="7">
-        <v>15000</v>
+        <v>29000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>16000</v>
+        <v>20333</v>
       </c>
       <c r="J27" s="5">
-        <v>71.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>92.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>129000</v>
+        <v>410000</v>
       </c>
       <c r="G28" s="7">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="H28" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I28" s="7">
-        <v>2500</v>
+        <v>23111</v>
       </c>
       <c r="J28" s="5">
-        <v>71.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>88.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>673000</v>
+        <v>112000</v>
       </c>
       <c r="G29" s="7">
-        <v>-5000</v>
+        <v>7000</v>
       </c>
       <c r="H29" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>10375</v>
+        <v>12286</v>
       </c>
       <c r="J29" s="5">
-        <v>71.2</v>
+        <v>71.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>77.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>472000</v>
+        <v>311000</v>
       </c>
       <c r="G30" s="7">
         <v>13000</v>
       </c>
       <c r="H30" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I30" s="7">
-        <v>30875</v>
+        <v>10333</v>
       </c>
       <c r="J30" s="5">
-        <v>70.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>292000</v>
+        <v>257000</v>
       </c>
       <c r="G31" s="7">
-        <v>30000</v>
+        <v>7000</v>
       </c>
       <c r="H31" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I31" s="7">
-        <v>18600</v>
+        <v>12778</v>
       </c>
       <c r="J31" s="5">
-        <v>70.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>87.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>217000</v>
+        <v>408000</v>
       </c>
       <c r="G32" s="7">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I32" s="7">
-        <v>10500</v>
+        <v>5889</v>
       </c>
       <c r="J32" s="5">
-        <v>70.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>121000</v>
+        <v>672000</v>
       </c>
       <c r="G33" s="7">
-        <v>8000</v>
+        <v>-1000</v>
       </c>
       <c r="H33" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I33" s="7">
-        <v>6250</v>
+        <v>9111</v>
       </c>
       <c r="J33" s="5">
-        <v>70.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>80.2</v>
+        <v>88.3</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>908000</v>
+        <v>222000</v>
       </c>
       <c r="G34" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H34" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I34" s="7">
-        <v>24125</v>
+        <v>9778</v>
       </c>
       <c r="J34" s="5">
-        <v>70.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>86</v>
+        <v>81.8</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>549000</v>
+        <v>630000</v>
       </c>
       <c r="G35" s="7">
-        <v>-15000</v>
+        <v>22000</v>
       </c>
       <c r="H35" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I35" s="7">
-        <v>11125</v>
+        <v>19778</v>
       </c>
       <c r="J35" s="5">
-        <v>70.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>85.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>302000</v>
+        <v>123000</v>
       </c>
       <c r="G36" s="7">
-        <v>26000</v>
+        <v>4000</v>
       </c>
       <c r="H36" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I36" s="7">
-        <v>12875</v>
+        <v>7667</v>
       </c>
       <c r="J36" s="5">
-        <v>70.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>87</v>
+        <v>79.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>247000</v>
+        <v>547000</v>
       </c>
       <c r="G37" s="7">
-        <v>41000</v>
+        <v>21000</v>
       </c>
       <c r="H37" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I37" s="7">
-        <v>28750</v>
+        <v>24222</v>
       </c>
       <c r="J37" s="5">
-        <v>70</v>
+        <v>69.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>80.3</v>
+        <v>80</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>386000</v>
+        <v>917000</v>
       </c>
       <c r="G38" s="7">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="H38" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I38" s="7">
-        <v>23000</v>
+        <v>22444</v>
       </c>
       <c r="J38" s="5">
-        <v>69.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>92.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>160000</v>
+        <v>120000</v>
       </c>
       <c r="G39" s="7">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="H39" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>16750</v>
+        <v>1333</v>
       </c>
       <c r="J39" s="5">
-        <v>69.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>87</v>
+        <v>86.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>203000</v>
+        <v>215000</v>
       </c>
       <c r="G40" s="7">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H40" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I40" s="7">
-        <v>6125</v>
+        <v>6778</v>
       </c>
       <c r="J40" s="5">
         <v>69.40000000000001</v>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>80.7</v>
+        <v>85.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>608000</v>
+        <v>115000</v>
       </c>
       <c r="G41" s="7">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="H41" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" s="7">
-        <v>19500</v>
+        <v>9556</v>
       </c>
       <c r="J41" s="5">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>87.2</v>
+        <v>83.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>116000</v>
+        <v>324000</v>
       </c>
       <c r="G42" s="7">
-        <v>4000</v>
+        <v>22000</v>
       </c>
       <c r="H42" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I42" s="7">
-        <v>5500</v>
+        <v>13889</v>
       </c>
       <c r="J42" s="5">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>79.5</v>
+        <v>85.2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>506000</v>
+        <v>182000</v>
       </c>
       <c r="G43" s="7">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="H43" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I43" s="7">
-        <v>21750</v>
+        <v>9444</v>
       </c>
       <c r="J43" s="5">
         <v>69.2</v>
@@ -2044,28 +2044,30 @@
       <c r="A44" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="5"/>
+      <c r="B44" s="5">
+        <v>9</v>
+      </c>
       <c r="C44" s="5">
-        <v>79.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>384000</v>
+        <v>147000</v>
       </c>
       <c r="G44" s="7">
-        <v>14000</v>
+        <v>11000</v>
       </c>
       <c r="H44" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I44" s="7">
-        <v>22125</v>
+        <v>6833</v>
       </c>
       <c r="J44" s="5">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>84.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>279000</v>
+        <v>119000</v>
       </c>
       <c r="G45" s="7">
-        <v>24000</v>
+        <v>3000</v>
       </c>
       <c r="H45" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I45" s="7">
-        <v>11500</v>
+        <v>5222</v>
       </c>
       <c r="J45" s="5">
-        <v>69.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>84.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>491000</v>
+        <v>188000</v>
       </c>
       <c r="G46" s="7">
-        <v>-21000</v>
+        <v>4000</v>
       </c>
       <c r="H46" s="7">
         <v>9</v>
       </c>
       <c r="I46" s="7">
-        <v>9500</v>
+        <v>11250</v>
       </c>
       <c r="J46" s="5">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>83.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>232000</v>
+        <v>202000</v>
       </c>
       <c r="G47" s="7">
-        <v>-5000</v>
+        <v>-1000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I47" s="7">
-        <v>10125</v>
+        <v>5333</v>
       </c>
       <c r="J47" s="5">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>85.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>152000</v>
+        <v>154000</v>
       </c>
       <c r="G48" s="7">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7">
-        <v>5750</v>
+        <v>12600</v>
       </c>
       <c r="J48" s="5">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>77.2</v>
+        <v>79.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>526000</v>
+        <v>361000</v>
       </c>
       <c r="G49" s="7">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="H49" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I49" s="7">
-        <v>24625</v>
+        <v>18556</v>
       </c>
       <c r="J49" s="5">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>89</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>138000</v>
+        <v>130000</v>
       </c>
       <c r="G50" s="7">
-        <v>21000</v>
+        <v>10000</v>
       </c>
       <c r="H50" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50" s="7">
-        <v>18500</v>
+        <v>11800</v>
       </c>
       <c r="J50" s="5">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,23 +2279,23 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>150000</v>
+        <v>123000</v>
       </c>
       <c r="G51" s="7">
         <v>1000</v>
       </c>
       <c r="H51" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I51" s="7">
-        <v>11000</v>
+        <v>7714</v>
       </c>
       <c r="J51" s="5">
         <v>68.5</v>
@@ -2310,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>85.5</v>
+        <v>82.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>398000</v>
+        <v>295000</v>
       </c>
       <c r="G52" s="7">
-        <v>-10000</v>
+        <v>16000</v>
       </c>
       <c r="H52" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I52" s="7">
-        <v>5375</v>
+        <v>12000</v>
       </c>
       <c r="J52" s="5">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>83.3</v>
+        <v>84.7</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>181000</v>
+        <v>473000</v>
       </c>
       <c r="G53" s="7">
-        <v>-4000</v>
+        <v>-18000</v>
       </c>
       <c r="H53" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I53" s="7">
-        <v>10500</v>
+        <v>6444</v>
       </c>
       <c r="J53" s="5">
-        <v>68.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>82</v>
+        <v>85.7</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>371000</v>
+        <v>437000</v>
       </c>
       <c r="G54" s="7">
-        <v>-34000</v>
+        <v>-11000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I54" s="7">
-        <v>12875</v>
+        <v>4333</v>
       </c>
       <c r="J54" s="5">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-03T04:06:28+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-04T04:10:16+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -94,133 +94,133 @@
     <t>女儿被诈两亿，天家千金遭曝光</t>
   </si>
   <si>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
+  </si>
+  <si>
+    <t>大唐：言出法随，都以为我是仙！</t>
+  </si>
+  <si>
+    <t>转生异能锁，开局逼校花超兽武装</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>让你荒淫无道，千古一帝什么鬼？</t>
+  </si>
+  <si>
     <t>觉醒：EX级法师，开局无限火力</t>
   </si>
   <si>
-    <t>转生异能锁，开局逼校花超兽武装</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>我拿钱就走，九个姐姐全变病娇了</t>
-  </si>
-  <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>大唐：言出法随，都以为我是仙！</t>
-  </si>
-  <si>
-    <t>让你荒淫无道，千古一帝什么鬼？</t>
+    <t>我，酆都，在鸿钧成圣前立地府</t>
+  </si>
+  <si>
+    <t>欢宋</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>不是，让我一个剑修去联姻？</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>三体：我还以为是全知域呢！</t>
+  </si>
+  <si>
+    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
+  </si>
+  <si>
+    <t>管亥托孤，我带领黄巾争霸天下</t>
+  </si>
+  <si>
+    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>名义：开局我举报我自己</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>词条：开局万倍天赋，你要退婚？</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>退游六年，剑仙老婆现实找上门了</t>
+  </si>
+  <si>
+    <t>综漫：人在霓虹，开局永恒万花筒</t>
+  </si>
+  <si>
+    <t>抗战：鬼子翻译？不，我代号财神</t>
+  </si>
+  <si>
+    <t>屠城就能回蓝星？兄弟你早说啊！</t>
+  </si>
+  <si>
+    <t>名柯：我有三角洲召唤系统</t>
+  </si>
+  <si>
+    <t>资本打压？我的电影越拍越红！</t>
+  </si>
+  <si>
+    <t>崩铁，死了47次，我决定去卖</t>
+  </si>
+  <si>
+    <t>让你暑假实习，你去地府当鬼差！</t>
+  </si>
+  <si>
+    <t>开局流落皇子，可我已经人间无敌</t>
+  </si>
+  <si>
+    <t>重生：什么江湖大哥？资本大鳄！</t>
+  </si>
+  <si>
+    <t>北洋创始人</t>
   </si>
   <si>
     <t>穿书成富二代，我直接救赎女主</t>
   </si>
   <si>
-    <t>综漫：人在霓虹，开局永恒万花筒</t>
-  </si>
-  <si>
-    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
-  </si>
-  <si>
-    <t>欢宋</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>不是，让我一个剑修去联姻？</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
+    <t>四合院：我家住隔壁，看众禽互咬</t>
+  </si>
+  <si>
+    <t>村花的傻子老公</t>
+  </si>
+  <si>
+    <t>名义：我调任汉东，孙连城笑了！</t>
+  </si>
+  <si>
+    <t>开局睡了白月光，她要我割痔疮？</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>名义，汉东刘长生，谁与争锋！</t>
   </si>
   <si>
     <t>太子李承乾已死！你选的嘛陛下！</t>
   </si>
   <si>
-    <t>重生：什么江湖大哥？资本大鳄！</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>抗战：鬼子翻译？不，我代号财神</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>让你暑假实习，你去地府当鬼差！</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>高考落榜，买彩票狂中六亿</t>
-  </si>
-  <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>大唐长生者，但开局在玄武门？</t>
-  </si>
-  <si>
-    <t>资本打压？我的电影越拍越红！</t>
-  </si>
-  <si>
-    <t>末日灾变序列</t>
-  </si>
-  <si>
-    <t>1995：从被抓到出轨开始</t>
-  </si>
-  <si>
-    <t>村花的傻子老公</t>
-  </si>
-  <si>
-    <t>名柯：我有三角洲召唤系统</t>
-  </si>
-  <si>
-    <t>我都攻克绝症了，渣一点怎么了？</t>
-  </si>
-  <si>
-    <t>游戏入侵：在诡异副本玩转搜打撤</t>
-  </si>
-  <si>
-    <t>名义：我调任汉东，孙连城笑了！</t>
-  </si>
-  <si>
-    <t>欢迎都显怀了，你还没释怀</t>
-  </si>
-  <si>
-    <t>开局睡了白月光，她要我割痔疮？</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>包养姐姐闺蜜，被姐姐发现了</t>
-  </si>
-  <si>
-    <t>封神：一年升一境，哪吒喊我爹！</t>
-  </si>
-  <si>
-    <t>火影：人在木叶村，开局觉醒木遁</t>
-  </si>
-  <si>
-    <t>别人穿四合院，我为啥上战场</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
+    <t>三角洲：FPS暴君降临</t>
   </si>
 </sst>
 </file>
@@ -766,19 +766,19 @@
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>581000</v>
+        <v>655000</v>
       </c>
       <c r="G5" s="7">
-        <v>84000</v>
+        <v>74000</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7">
-        <v>88800</v>
+        <v>86333</v>
       </c>
       <c r="J5" s="5">
-        <v>95.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>217000</v>
+        <v>238000</v>
       </c>
       <c r="G6" s="7">
-        <v>37000</v>
+        <v>21000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>30167</v>
+        <v>28857</v>
       </c>
       <c r="J6" s="5">
-        <v>82.5</v>
+        <v>79.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>96.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>454000</v>
+        <v>478000</v>
       </c>
       <c r="G7" s="7">
-        <v>35000</v>
+        <v>24000</v>
       </c>
       <c r="H7" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="7">
-        <v>33333</v>
+        <v>32400</v>
       </c>
       <c r="J7" s="5">
-        <v>81.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>94.7</v>
+        <v>93</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>313000</v>
+        <v>330000</v>
       </c>
       <c r="G8" s="7">
-        <v>21000</v>
+        <v>17000</v>
       </c>
       <c r="H8" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="7">
-        <v>30714</v>
+        <v>29000</v>
       </c>
       <c r="J8" s="5">
-        <v>79.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -898,19 +898,19 @@
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>1754000</v>
+        <v>1751000</v>
       </c>
       <c r="G9" s="7">
-        <v>-4000</v>
+        <v>-3000</v>
       </c>
       <c r="H9" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="7">
-        <v>59778</v>
+        <v>53500</v>
       </c>
       <c r="J9" s="5">
-        <v>79.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>185000</v>
+        <v>201000</v>
       </c>
       <c r="G10" s="7">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>18400</v>
+        <v>18000</v>
       </c>
       <c r="J10" s="5">
-        <v>77.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>92.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>251000</v>
+        <v>257000</v>
       </c>
       <c r="G11" s="7">
-        <v>14000</v>
+        <v>6000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>35400</v>
+        <v>30500</v>
       </c>
       <c r="J11" s="5">
-        <v>77.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>98.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>213000</v>
+        <v>174000</v>
       </c>
       <c r="G12" s="7">
-        <v>26000</v>
+        <v>17000</v>
       </c>
       <c r="H12" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>11778</v>
+        <v>18333</v>
       </c>
       <c r="J12" s="5">
-        <v>77.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>95.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>210000</v>
+        <v>163000</v>
       </c>
       <c r="G13" s="7">
-        <v>21000</v>
+        <v>13000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>24400</v>
+        <v>15333</v>
       </c>
       <c r="J13" s="5">
-        <v>76.5</v>
+        <v>75.5</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>97.8</v>
+        <v>88.8</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>140000</v>
+        <v>218000</v>
       </c>
       <c r="G14" s="7">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="H14" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>8111</v>
+        <v>21667</v>
       </c>
       <c r="J14" s="5">
-        <v>75.8</v>
+        <v>74.3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>96.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>157000</v>
+        <v>153000</v>
       </c>
       <c r="G15" s="7">
-        <v>19000</v>
+        <v>13000</v>
       </c>
       <c r="H15" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I15" s="7">
-        <v>18600</v>
+        <v>8600</v>
       </c>
       <c r="J15" s="5">
-        <v>75.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>92.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>236000</v>
+        <v>243000</v>
       </c>
       <c r="G16" s="7">
-        <v>14000</v>
+        <v>7000</v>
       </c>
       <c r="H16" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="7">
-        <v>17667</v>
+        <v>16600</v>
       </c>
       <c r="J16" s="5">
-        <v>75.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>96.2</v>
+        <v>82.5</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>150000</v>
+        <v>540000</v>
       </c>
       <c r="G17" s="7">
-        <v>15000</v>
+        <v>28000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I17" s="7">
-        <v>15800</v>
+        <v>31500</v>
       </c>
       <c r="J17" s="5">
-        <v>74.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>83.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>512000</v>
+        <v>227000</v>
       </c>
       <c r="G18" s="7">
-        <v>40000</v>
+        <v>14000</v>
       </c>
       <c r="H18" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="7">
-        <v>31889</v>
+        <v>12000</v>
       </c>
       <c r="J18" s="5">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>249000</v>
+        <v>149000</v>
       </c>
       <c r="G19" s="7">
-        <v>17000</v>
+        <v>26000</v>
       </c>
       <c r="H19" s="7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I19" s="7">
-        <v>10889</v>
+        <v>35500</v>
       </c>
       <c r="J19" s="5">
-        <v>73.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.2</v>
+        <v>90.8</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>208000</v>
+        <v>114000</v>
       </c>
       <c r="G20" s="7">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="H20" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>15833</v>
+        <v>10500</v>
       </c>
       <c r="J20" s="5">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>259000</v>
+        <v>252000</v>
       </c>
       <c r="G21" s="7">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="H21" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="7">
-        <v>17333</v>
+        <v>11000</v>
       </c>
       <c r="J21" s="5">
-        <v>73.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>92.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>108000</v>
+        <v>147000</v>
       </c>
       <c r="G22" s="7">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I22" s="7">
-        <v>11143</v>
+        <v>11200</v>
       </c>
       <c r="J22" s="5">
-        <v>73.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>93.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>131000</v>
+        <v>140000</v>
       </c>
       <c r="G23" s="7">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="H23" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="7">
-        <v>6667</v>
+        <v>6900</v>
       </c>
       <c r="J23" s="5">
-        <v>73.3</v>
+        <v>72.2</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91</v>
+        <v>88.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>141000</v>
+        <v>264000</v>
       </c>
       <c r="G24" s="7">
         <v>7000</v>
       </c>
       <c r="H24" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="7">
-        <v>11778</v>
+        <v>12200</v>
       </c>
       <c r="J24" s="5">
-        <v>73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.8</v>
+        <v>86.3</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>244000</v>
+        <v>257000</v>
       </c>
       <c r="G25" s="7">
-        <v>9000</v>
+        <v>-2000</v>
       </c>
       <c r="H25" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25" s="7">
-        <v>11333</v>
+        <v>15400</v>
       </c>
       <c r="J25" s="5">
-        <v>72.8</v>
+        <v>71.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>97.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>101000</v>
+        <v>103000</v>
       </c>
       <c r="G26" s="7">
-        <v>23000</v>
+        <v>6000</v>
       </c>
       <c r="H26" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I26" s="7">
-        <v>15500</v>
+        <v>6500</v>
       </c>
       <c r="J26" s="5">
-        <v>72.5</v>
+        <v>71.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>85.8</v>
+        <v>88</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>321000</v>
+        <v>271000</v>
       </c>
       <c r="G27" s="7">
-        <v>29000</v>
+        <v>44000</v>
       </c>
       <c r="H27" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>20333</v>
+        <v>11000</v>
       </c>
       <c r="J27" s="5">
-        <v>72.3</v>
+        <v>71.2</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>84.3</v>
+        <v>82.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>410000</v>
+        <v>428000</v>
       </c>
       <c r="G28" s="7">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="H28" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="7">
-        <v>23111</v>
+        <v>22600</v>
       </c>
       <c r="J28" s="5">
-        <v>72.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>112000</v>
+        <v>670000</v>
       </c>
       <c r="G29" s="7">
-        <v>7000</v>
+        <v>-2000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I29" s="7">
-        <v>12286</v>
+        <v>8000</v>
       </c>
       <c r="J29" s="5">
-        <v>71.8</v>
+        <v>70.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>311000</v>
+        <v>575000</v>
       </c>
       <c r="G30" s="7">
-        <v>13000</v>
+        <v>28000</v>
       </c>
       <c r="H30" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="7">
-        <v>10333</v>
+        <v>24600</v>
       </c>
       <c r="J30" s="5">
-        <v>71.7</v>
+        <v>70.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>88.2</v>
+        <v>86.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>257000</v>
+        <v>163000</v>
       </c>
       <c r="G31" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H31" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>12778</v>
+        <v>11500</v>
       </c>
       <c r="J31" s="5">
-        <v>71.7</v>
+        <v>70.5</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>90.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>408000</v>
+        <v>656000</v>
       </c>
       <c r="G32" s="7">
-        <v>10000</v>
+        <v>26000</v>
       </c>
       <c r="H32" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="7">
-        <v>5889</v>
+        <v>20400</v>
       </c>
       <c r="J32" s="5">
-        <v>71.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>89</v>
+        <v>91.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>672000</v>
+        <v>272000</v>
       </c>
       <c r="G33" s="7">
-        <v>-1000</v>
+        <v>12000</v>
       </c>
       <c r="H33" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>9111</v>
+        <v>19750</v>
       </c>
       <c r="J33" s="5">
-        <v>71.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>88.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>222000</v>
+        <v>213000</v>
       </c>
       <c r="G34" s="7">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="H34" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I34" s="7">
-        <v>9778</v>
+        <v>14286</v>
       </c>
       <c r="J34" s="5">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>81.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>630000</v>
+        <v>116000</v>
       </c>
       <c r="G35" s="7">
-        <v>22000</v>
+        <v>4000</v>
       </c>
       <c r="H35" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>19778</v>
+        <v>11250</v>
       </c>
       <c r="J35" s="5">
-        <v>69.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>87.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>123000</v>
+        <v>350000</v>
       </c>
       <c r="G36" s="7">
         <v>4000</v>
       </c>
       <c r="H36" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I36" s="7">
-        <v>7667</v>
+        <v>7300</v>
       </c>
       <c r="J36" s="5">
-        <v>69.8</v>
+        <v>70.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>79.3</v>
+        <v>87.2</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>547000</v>
+        <v>185000</v>
       </c>
       <c r="G37" s="7">
-        <v>21000</v>
+        <v>3000</v>
       </c>
       <c r="H37" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" s="7">
-        <v>24222</v>
+        <v>8800</v>
       </c>
       <c r="J37" s="5">
-        <v>69.7</v>
+        <v>70.2</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>80</v>
+        <v>89.8</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>917000</v>
+        <v>136000</v>
       </c>
       <c r="G38" s="7">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="H38" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7">
-        <v>22444</v>
+        <v>3429</v>
       </c>
       <c r="J38" s="5">
-        <v>69.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,23 +1881,23 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>89.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>120000</v>
+        <v>271000</v>
       </c>
       <c r="G39" s="7">
-        <v>19000</v>
+        <v>11000</v>
       </c>
       <c r="H39" s="7">
         <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>1333</v>
+        <v>23167</v>
       </c>
       <c r="J39" s="5">
         <v>69.59999999999999</v>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.8</v>
+        <v>86</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>215000</v>
+        <v>224000</v>
       </c>
       <c r="G40" s="7">
         <v>2000</v>
       </c>
       <c r="H40" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I40" s="7">
-        <v>6778</v>
+        <v>9000</v>
       </c>
       <c r="J40" s="5">
-        <v>69.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>85.5</v>
+        <v>87.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>115000</v>
+        <v>168000</v>
       </c>
       <c r="G41" s="7">
-        <v>3000</v>
+        <v>13000</v>
       </c>
       <c r="H41" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I41" s="7">
-        <v>9556</v>
+        <v>5300</v>
       </c>
       <c r="J41" s="5">
-        <v>69.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>83.2</v>
+        <v>81</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>324000</v>
+        <v>337000</v>
       </c>
       <c r="G42" s="7">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="H42" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I42" s="7">
-        <v>13889</v>
+        <v>19714</v>
       </c>
       <c r="J42" s="5">
-        <v>69.2</v>
+        <v>69.5</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>182000</v>
+        <v>101000</v>
       </c>
       <c r="G43" s="7">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="H43" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I43" s="7">
-        <v>9444</v>
+        <v>5500</v>
       </c>
       <c r="J43" s="5">
         <v>69.2</v>
@@ -2044,30 +2044,28 @@
       <c r="A44" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="5">
-        <v>9</v>
-      </c>
+      <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>147000</v>
+        <v>248000</v>
       </c>
       <c r="G44" s="7">
-        <v>11000</v>
+        <v>-1000</v>
       </c>
       <c r="H44" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I44" s="7">
-        <v>6833</v>
+        <v>9700</v>
       </c>
       <c r="J44" s="5">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>86.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>119000</v>
+        <v>192000</v>
       </c>
       <c r="G45" s="7">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="H45" s="7">
         <v>10</v>
       </c>
       <c r="I45" s="7">
-        <v>5222</v>
+        <v>8000</v>
       </c>
       <c r="J45" s="5">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>83.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>188000</v>
+        <v>342000</v>
       </c>
       <c r="G46" s="7">
-        <v>4000</v>
+        <v>18000</v>
       </c>
       <c r="H46" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I46" s="7">
-        <v>11250</v>
+        <v>14300</v>
       </c>
       <c r="J46" s="5">
-        <v>68.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>86</v>
+        <v>83.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>202000</v>
+        <v>191000</v>
       </c>
       <c r="G47" s="7">
-        <v>-1000</v>
+        <v>3000</v>
       </c>
       <c r="H47" s="7">
         <v>10</v>
       </c>
       <c r="I47" s="7">
-        <v>5333</v>
+        <v>10333</v>
       </c>
       <c r="J47" s="5">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>86.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>154000</v>
+        <v>159000</v>
       </c>
       <c r="G48" s="7">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="H48" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I48" s="7">
-        <v>12600</v>
+        <v>11333</v>
       </c>
       <c r="J48" s="5">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>79.7</v>
+        <v>84.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>361000</v>
+        <v>309000</v>
       </c>
       <c r="G49" s="7">
-        <v>18000</v>
+        <v>-2000</v>
       </c>
       <c r="H49" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I49" s="7">
-        <v>18556</v>
+        <v>9100</v>
       </c>
       <c r="J49" s="5">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,23 +2244,23 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>86.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>130000</v>
+        <v>380000</v>
       </c>
       <c r="G50" s="7">
-        <v>10000</v>
+        <v>19000</v>
       </c>
       <c r="H50" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I50" s="7">
-        <v>11800</v>
+        <v>18600</v>
       </c>
       <c r="J50" s="5">
         <v>68.5</v>
@@ -2279,23 +2277,23 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>84.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>123000</v>
+        <v>281000</v>
       </c>
       <c r="G51" s="7">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H51" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I51" s="7">
-        <v>7714</v>
+        <v>2200</v>
       </c>
       <c r="J51" s="5">
         <v>68.5</v>
@@ -2312,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>82.3</v>
+        <v>84.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>295000</v>
+        <v>232000</v>
       </c>
       <c r="G52" s="7">
-        <v>16000</v>
+        <v>38000</v>
       </c>
       <c r="H52" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I52" s="7">
-        <v>12000</v>
+        <v>8200</v>
       </c>
       <c r="J52" s="5">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>84.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>473000</v>
+        <v>108000</v>
       </c>
       <c r="G53" s="7">
-        <v>-18000</v>
+        <v>7000</v>
       </c>
       <c r="H53" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I53" s="7">
-        <v>6444</v>
+        <v>13800</v>
       </c>
       <c r="J53" s="5">
-        <v>68.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>85.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>437000</v>
+        <v>405000</v>
       </c>
       <c r="G54" s="7">
-        <v>-11000</v>
+        <v>13000</v>
       </c>
       <c r="H54" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I54" s="7">
-        <v>4333</v>
+        <v>19800</v>
       </c>
       <c r="J54" s="5">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-04T04:10:16+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-05T04:06:30+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>转生异能锁，开局逼校花超兽武装</t>
+  </si>
+  <si>
+    <t>轮回修仙：从考科举开始</t>
+  </si>
+  <si>
     <t>身家300亿美刀，重回1988</t>
   </si>
   <si>
-    <t>轮回修仙：从考科举开始</t>
+    <t>大唐：言出法随，都以为我是仙！</t>
+  </si>
+  <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
+    <t>女儿被诈两亿，天家千金遭曝光</t>
+  </si>
+  <si>
+    <t>我，酆都，在鸿钧成圣前立地府</t>
+  </si>
+  <si>
+    <t>火影：从离开木叶建立忍国开始</t>
+  </si>
+  <si>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
   </si>
   <si>
     <t>女尊，独自抚养妹妹们的正太哥哥</t>
   </si>
   <si>
-    <t>冒姓琅琊</t>
-  </si>
-  <si>
-    <t>火影：从离开木叶建立忍国开始</t>
-  </si>
-  <si>
-    <t>女儿被诈两亿，天家千金遭曝光</t>
-  </si>
-  <si>
-    <t>我拿钱就走，九个姐姐全变病娇了</t>
-  </si>
-  <si>
-    <t>大唐：言出法随，都以为我是仙！</t>
-  </si>
-  <si>
-    <t>转生异能锁，开局逼校花超兽武装</t>
+    <t>退游六年，剑仙老婆现实找上门了</t>
   </si>
   <si>
     <t>让你守破道观，你咋真修仙了？</t>
   </si>
   <si>
+    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+  </si>
+  <si>
     <t>穿越成国公，咋就是封建余孽了？</t>
   </si>
   <si>
+    <t>欢宋</t>
+  </si>
+  <si>
     <t>让你荒淫无道，千古一帝什么鬼？</t>
   </si>
   <si>
-    <t>觉醒：EX级法师，开局无限火力</t>
-  </si>
-  <si>
-    <t>我，酆都，在鸿钧成圣前立地府</t>
-  </si>
-  <si>
-    <t>欢宋</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
+    <t>Fate：开局召唤喜悦闪</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>开局豪门继承人，怎么还要上恋综</t>
+  </si>
+  <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>名义：我调任汉东，孙连城笑了！</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>管亥托孤，我带领黄巾争霸天下</t>
+  </si>
+  <si>
+    <t>三体：我还以为是全知域呢！</t>
   </si>
   <si>
     <t>不是，让我一个剑修去联姻？</t>
   </si>
   <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>穿书成富二代，我直接救赎女主</t>
+  </si>
+  <si>
+    <t>西游降临：开局拜师通天教主！</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>开局流落皇子，可我已经人间无敌</t>
+  </si>
+  <si>
+    <t>你抢劫诡异良心不会痛吗？</t>
   </si>
   <si>
     <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
   </si>
   <si>
-    <t>管亥托孤，我带领黄巾争霸天下</t>
-  </si>
-  <si>
-    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>名义：开局我举报我自己</t>
-  </si>
-  <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
+    <t>四合院：我家住隔壁，看众禽互咬</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
+  </si>
+  <si>
+    <t>屠城就能回蓝星？兄弟你早说啊！</t>
+  </si>
+  <si>
+    <t>变身顶美，有颜真能为所欲为</t>
+  </si>
+  <si>
+    <t>抗战：鬼子翻译？不，我代号财神</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>名义，汉东刘长生，谁与争锋！</t>
+  </si>
+  <si>
+    <t>综漫：人在霓虹，开局永恒万花筒</t>
+  </si>
+  <si>
+    <t>崩铁，死了47次，我决定去卖</t>
+  </si>
+  <si>
+    <t>美综：谁说美剧没有人情世故？</t>
+  </si>
+  <si>
+    <t>超神：成为裁决天使后，我无敌了</t>
   </si>
   <si>
     <t>词条：开局万倍天赋，你要退婚？</t>
   </si>
   <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>退游六年，剑仙老婆现实找上门了</t>
-  </si>
-  <si>
-    <t>综漫：人在霓虹，开局永恒万花筒</t>
-  </si>
-  <si>
-    <t>抗战：鬼子翻译？不，我代号财神</t>
-  </si>
-  <si>
-    <t>屠城就能回蓝星？兄弟你早说啊！</t>
-  </si>
-  <si>
-    <t>名柯：我有三角洲召唤系统</t>
-  </si>
-  <si>
-    <t>资本打压？我的电影越拍越红！</t>
-  </si>
-  <si>
-    <t>崩铁，死了47次，我决定去卖</t>
-  </si>
-  <si>
-    <t>让你暑假实习，你去地府当鬼差！</t>
-  </si>
-  <si>
-    <t>开局流落皇子，可我已经人间无敌</t>
+    <t>太子李承乾已死！你选的嘛陛下！</t>
   </si>
   <si>
     <t>重生：什么江湖大哥？资本大鳄！</t>
   </si>
   <si>
-    <t>北洋创始人</t>
-  </si>
-  <si>
-    <t>穿书成富二代，我直接救赎女主</t>
-  </si>
-  <si>
-    <t>四合院：我家住隔壁，看众禽互咬</t>
-  </si>
-  <si>
-    <t>村花的傻子老公</t>
-  </si>
-  <si>
-    <t>名义：我调任汉东，孙连城笑了！</t>
-  </si>
-  <si>
-    <t>开局睡了白月光，她要我割痔疮？</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>名义，汉东刘长生，谁与争锋！</t>
-  </si>
-  <si>
-    <t>太子李承乾已死！你选的嘛陛下！</t>
-  </si>
-  <si>
-    <t>三角洲：FPS暴君降临</t>
+    <t>诡异：变身萝莉，诡王是我老爹？</t>
   </si>
 </sst>
 </file>
@@ -766,19 +766,19 @@
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>655000</v>
+        <v>725000</v>
       </c>
       <c r="G5" s="7">
-        <v>74000</v>
+        <v>70000</v>
       </c>
       <c r="H5" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>86333</v>
+        <v>84000</v>
       </c>
       <c r="J5" s="5">
-        <v>96.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>95.7</v>
+        <v>96.8</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>238000</v>
+        <v>245000</v>
       </c>
       <c r="G6" s="7">
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="H6" s="7">
         <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>28857</v>
+        <v>22429</v>
       </c>
       <c r="J6" s="5">
-        <v>79.8</v>
+        <v>78.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>93.7</v>
+        <v>92.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>478000</v>
+        <v>496000</v>
       </c>
       <c r="G7" s="7">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="H7" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7" s="7">
-        <v>32400</v>
+        <v>31091</v>
       </c>
       <c r="J7" s="5">
-        <v>79.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>93</v>
+        <v>92.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>330000</v>
+        <v>251000</v>
       </c>
       <c r="G8" s="7">
-        <v>17000</v>
+        <v>13000</v>
       </c>
       <c r="H8" s="7">
         <v>9</v>
       </c>
       <c r="I8" s="7">
-        <v>29000</v>
+        <v>26875</v>
       </c>
       <c r="J8" s="5">
-        <v>78.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>81</v>
+        <v>96.7</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>1751000</v>
+        <v>180000</v>
       </c>
       <c r="G9" s="7">
-        <v>-3000</v>
+        <v>17000</v>
       </c>
       <c r="H9" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I9" s="7">
-        <v>53500</v>
+        <v>15571</v>
       </c>
       <c r="J9" s="5">
-        <v>77.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>95.2</v>
+        <v>81</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>201000</v>
+        <v>1747000</v>
       </c>
       <c r="G10" s="7">
-        <v>16000</v>
+        <v>-4000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I10" s="7">
-        <v>18000</v>
+        <v>48273</v>
       </c>
       <c r="J10" s="5">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -964,19 +964,19 @@
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>257000</v>
+        <v>263000</v>
       </c>
       <c r="G11" s="7">
         <v>6000</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
-        <v>30500</v>
+        <v>27000</v>
       </c>
       <c r="J11" s="5">
-        <v>76.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>93.7</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>174000</v>
+        <v>170000</v>
       </c>
       <c r="G12" s="7">
-        <v>17000</v>
+        <v>21000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I12" s="7">
-        <v>18333</v>
+        <v>30667</v>
       </c>
       <c r="J12" s="5">
-        <v>76.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>93.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>163000</v>
+        <v>211000</v>
       </c>
       <c r="G13" s="7">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>15333</v>
+        <v>16857</v>
       </c>
       <c r="J13" s="5">
-        <v>75.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>88.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>218000</v>
+        <v>188000</v>
       </c>
       <c r="G14" s="7">
-        <v>8000</v>
+        <v>14000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
-        <v>21667</v>
+        <v>17714</v>
       </c>
       <c r="J14" s="5">
-        <v>74.3</v>
+        <v>74.5</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>153000</v>
+        <v>267000</v>
       </c>
       <c r="G15" s="7">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="H15" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I15" s="7">
-        <v>8600</v>
+        <v>11364</v>
       </c>
       <c r="J15" s="5">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>89.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>243000</v>
+        <v>319000</v>
       </c>
       <c r="G16" s="7">
-        <v>7000</v>
+        <v>-11000</v>
       </c>
       <c r="H16" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="7">
-        <v>16600</v>
+        <v>24556</v>
       </c>
       <c r="J16" s="5">
-        <v>73.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>82.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>540000</v>
+        <v>282000</v>
       </c>
       <c r="G17" s="7">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="H17" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>31500</v>
+        <v>17800</v>
       </c>
       <c r="J17" s="5">
-        <v>73.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>90.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>227000</v>
+        <v>162000</v>
       </c>
       <c r="G18" s="7">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="H18" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18" s="7">
-        <v>12000</v>
+        <v>8636</v>
       </c>
       <c r="J18" s="5">
-        <v>73</v>
+        <v>72.3</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>100</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>149000</v>
+        <v>308000</v>
       </c>
       <c r="G19" s="7">
-        <v>26000</v>
+        <v>37000</v>
       </c>
       <c r="H19" s="7">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I19" s="7">
-        <v>35500</v>
+        <v>13600</v>
       </c>
       <c r="J19" s="5">
-        <v>72.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.8</v>
+        <v>87.8</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>114000</v>
+        <v>245000</v>
       </c>
       <c r="G20" s="7">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I20" s="7">
-        <v>10500</v>
+        <v>15273</v>
       </c>
       <c r="J20" s="5">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>90.3</v>
+        <v>89.8</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>252000</v>
+        <v>119000</v>
       </c>
       <c r="G21" s="7">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H21" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I21" s="7">
-        <v>11000</v>
+        <v>9889</v>
       </c>
       <c r="J21" s="5">
-        <v>72.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>90.09999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>147000</v>
+        <v>565000</v>
       </c>
       <c r="G22" s="7">
-        <v>6000</v>
+        <v>25000</v>
       </c>
       <c r="H22" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="7">
-        <v>11200</v>
+        <v>30909</v>
       </c>
       <c r="J22" s="5">
-        <v>72.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>140000</v>
+        <v>168000</v>
       </c>
       <c r="G23" s="7">
-        <v>9000</v>
+        <v>14000</v>
       </c>
       <c r="H23" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I23" s="7">
-        <v>6900</v>
+        <v>12400</v>
       </c>
       <c r="J23" s="5">
-        <v>72.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,23 +1386,23 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>88.2</v>
+        <v>90.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>264000</v>
+        <v>148000</v>
       </c>
       <c r="G24" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>12</v>
+      </c>
+      <c r="I24" s="7">
         <v>7000</v>
-      </c>
-      <c r="H24" s="7">
-        <v>11</v>
-      </c>
-      <c r="I24" s="7">
-        <v>12200</v>
       </c>
       <c r="J24" s="5">
         <v>71.59999999999999</v>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>86.3</v>
+        <v>89.3</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>257000</v>
+        <v>155000</v>
       </c>
       <c r="G25" s="7">
-        <v>-2000</v>
+        <v>12000</v>
       </c>
       <c r="H25" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I25" s="7">
-        <v>15400</v>
+        <v>8455</v>
       </c>
       <c r="J25" s="5">
-        <v>71.3</v>
+        <v>71.2</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>90.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>103000</v>
+        <v>232000</v>
       </c>
       <c r="G26" s="7">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="H26" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" s="7">
-        <v>6500</v>
+        <v>545</v>
       </c>
       <c r="J26" s="5">
-        <v>71.3</v>
+        <v>71</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>271000</v>
+        <v>200000</v>
       </c>
       <c r="G27" s="7">
-        <v>44000</v>
+        <v>9000</v>
       </c>
       <c r="H27" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="7">
-        <v>11000</v>
+        <v>10200</v>
       </c>
       <c r="J27" s="5">
-        <v>71.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>428000</v>
+        <v>684000</v>
       </c>
       <c r="G28" s="7">
-        <v>18000</v>
+        <v>28000</v>
       </c>
       <c r="H28" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I28" s="7">
-        <v>22600</v>
+        <v>21091</v>
       </c>
       <c r="J28" s="5">
-        <v>71</v>
+        <v>70.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>88.8</v>
+        <v>89.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>670000</v>
+        <v>108000</v>
       </c>
       <c r="G29" s="7">
-        <v>-2000</v>
+        <v>5000</v>
       </c>
       <c r="H29" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29" s="7">
-        <v>8000</v>
+        <v>6364</v>
       </c>
       <c r="J29" s="5">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,23 +1584,23 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>80.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>575000</v>
+        <v>265000</v>
       </c>
       <c r="G30" s="7">
-        <v>28000</v>
+        <v>1000</v>
       </c>
       <c r="H30" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I30" s="7">
-        <v>24600</v>
+        <v>11182</v>
       </c>
       <c r="J30" s="5">
         <v>70.5</v>
@@ -1617,23 +1617,23 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>86.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>163000</v>
+        <v>150000</v>
       </c>
       <c r="G31" s="7">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I31" s="7">
-        <v>11500</v>
+        <v>10455</v>
       </c>
       <c r="J31" s="5">
         <v>70.5</v>
@@ -1650,23 +1650,23 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>82.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>656000</v>
+        <v>603000</v>
       </c>
       <c r="G32" s="7">
-        <v>26000</v>
+        <v>28000</v>
       </c>
       <c r="H32" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I32" s="7">
-        <v>20400</v>
+        <v>24909</v>
       </c>
       <c r="J32" s="5">
         <v>70.40000000000001</v>
@@ -1683,23 +1683,23 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>91.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>272000</v>
+        <v>446000</v>
       </c>
       <c r="G33" s="7">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="H33" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I33" s="7">
-        <v>19750</v>
+        <v>22182</v>
       </c>
       <c r="J33" s="5">
         <v>70.40000000000001</v>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>84.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>213000</v>
+        <v>253000</v>
       </c>
       <c r="G34" s="7">
         <v>5000</v>
       </c>
       <c r="H34" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I34" s="7">
-        <v>14286</v>
+        <v>9273</v>
       </c>
       <c r="J34" s="5">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>86.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>116000</v>
+        <v>402000</v>
       </c>
       <c r="G35" s="7">
-        <v>4000</v>
+        <v>50000</v>
       </c>
       <c r="H35" s="7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I35" s="7">
-        <v>11250</v>
+        <v>69500</v>
       </c>
       <c r="J35" s="5">
-        <v>70.3</v>
+        <v>69.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>88</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>350000</v>
+        <v>314000</v>
       </c>
       <c r="G36" s="7">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H36" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I36" s="7">
-        <v>7300</v>
+        <v>8727</v>
       </c>
       <c r="J36" s="5">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>87.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>185000</v>
+        <v>180000</v>
       </c>
       <c r="G37" s="7">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="H37" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I37" s="7">
-        <v>8800</v>
+        <v>5909</v>
       </c>
       <c r="J37" s="5">
-        <v>70.2</v>
+        <v>69.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>89.8</v>
+        <v>87.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>136000</v>
+        <v>101000</v>
       </c>
       <c r="G38" s="7">
-        <v>16000</v>
+        <v>6000</v>
       </c>
       <c r="H38" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I38" s="7">
-        <v>3429</v>
+        <v>5545</v>
       </c>
       <c r="J38" s="5">
-        <v>70.2</v>
+        <v>69.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>79.7</v>
+        <v>83</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>271000</v>
+        <v>249000</v>
       </c>
       <c r="G39" s="7">
-        <v>11000</v>
+        <v>-8000</v>
       </c>
       <c r="H39" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I39" s="7">
-        <v>23167</v>
+        <v>13273</v>
       </c>
       <c r="J39" s="5">
-        <v>69.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>224000</v>
+        <v>198000</v>
       </c>
       <c r="G40" s="7">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H40" s="7">
         <v>11</v>
       </c>
       <c r="I40" s="7">
-        <v>9000</v>
+        <v>7800</v>
       </c>
       <c r="J40" s="5">
-        <v>69.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>87.8</v>
+        <v>80.2</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>168000</v>
+        <v>401000</v>
       </c>
       <c r="G41" s="7">
-        <v>13000</v>
+        <v>21000</v>
       </c>
       <c r="H41" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I41" s="7">
-        <v>5300</v>
+        <v>18818</v>
       </c>
       <c r="J41" s="5">
-        <v>69.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>81</v>
+        <v>85.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>337000</v>
+        <v>351000</v>
       </c>
       <c r="G42" s="7">
-        <v>16000</v>
+        <v>1000</v>
       </c>
       <c r="H42" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I42" s="7">
-        <v>19714</v>
+        <v>6727</v>
       </c>
       <c r="J42" s="5">
-        <v>69.5</v>
+        <v>68.7</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>86.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>101000</v>
+        <v>609000</v>
       </c>
       <c r="G43" s="7">
-        <v>5000</v>
+        <v>42000</v>
       </c>
       <c r="H43" s="7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I43" s="7">
-        <v>5500</v>
+        <v>52000</v>
       </c>
       <c r="J43" s="5">
-        <v>69.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>84.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>248000</v>
+        <v>117000</v>
       </c>
       <c r="G44" s="7">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="H44" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I44" s="7">
-        <v>9700</v>
+        <v>10111</v>
       </c>
       <c r="J44" s="5">
-        <v>69.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>85.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>192000</v>
+        <v>283000</v>
       </c>
       <c r="G45" s="7">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="H45" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I45" s="7">
-        <v>8000</v>
+        <v>2182</v>
       </c>
       <c r="J45" s="5">
-        <v>69.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>82.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>342000</v>
+        <v>257000</v>
       </c>
       <c r="G46" s="7">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="H46" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I46" s="7">
-        <v>14300</v>
+        <v>9727</v>
       </c>
       <c r="J46" s="5">
-        <v>68.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>83.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>191000</v>
+        <v>207000</v>
       </c>
       <c r="G47" s="7">
-        <v>3000</v>
+        <v>-6000</v>
       </c>
       <c r="H47" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>10333</v>
+        <v>11750</v>
       </c>
       <c r="J47" s="5">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>83.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>159000</v>
+        <v>279000</v>
       </c>
       <c r="G48" s="7">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="H48" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I48" s="7">
-        <v>11333</v>
+        <v>21000</v>
       </c>
       <c r="J48" s="5">
-        <v>68.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>84.3</v>
+        <v>89.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>309000</v>
+        <v>198000</v>
       </c>
       <c r="G49" s="7">
-        <v>-2000</v>
+        <v>15000</v>
       </c>
       <c r="H49" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7">
-        <v>9100</v>
+        <v>16250</v>
       </c>
       <c r="J49" s="5">
-        <v>68.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>79.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>380000</v>
+        <v>179000</v>
       </c>
       <c r="G50" s="7">
-        <v>19000</v>
+        <v>24000</v>
       </c>
       <c r="H50" s="7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I50" s="7">
-        <v>18600</v>
+        <v>18500</v>
       </c>
       <c r="J50" s="5">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>87.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>281000</v>
+        <v>169000</v>
       </c>
       <c r="G51" s="7">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H51" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I51" s="7">
-        <v>2200</v>
+        <v>10714</v>
       </c>
       <c r="J51" s="5">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,23 +2310,23 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.3</v>
+        <v>82.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>232000</v>
+        <v>108000</v>
       </c>
       <c r="G52" s="7">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="H52" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I52" s="7">
-        <v>8200</v>
+        <v>11500</v>
       </c>
       <c r="J52" s="5">
         <v>68.40000000000001</v>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>85.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>108000</v>
+        <v>348000</v>
       </c>
       <c r="G53" s="7">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="H53" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>13800</v>
+        <v>18625</v>
       </c>
       <c r="J53" s="5">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,23 +2376,23 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>78.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>405000</v>
+        <v>145000</v>
       </c>
       <c r="G54" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H54" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>19800</v>
+        <v>16667</v>
       </c>
       <c r="J54" s="5">
         <v>68.3</v>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-05T04:06:30+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-06T04:14:11+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
-    <t>转生异能锁，开局逼校花超兽武装</t>
+    <t>身家300亿美刀，重回1988</t>
   </si>
   <si>
     <t>轮回修仙：从考科举开始</t>
   </si>
   <si>
-    <t>身家300亿美刀，重回1988</t>
+    <t>西游降临：开局拜师通天教主！</t>
+  </si>
+  <si>
+    <t>美综：谁说美剧没有人情世故？</t>
+  </si>
+  <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
+    <t>就想练练功，怎么就成了大宗师？</t>
+  </si>
+  <si>
+    <t>女尊，独自抚养妹妹们的正太哥哥</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>开始万倍加速空间，芶在最强宗门</t>
+  </si>
+  <si>
+    <t>女儿被诈两亿，天家千金遭曝光</t>
+  </si>
+  <si>
+    <t>火影：从离开木叶建立忍国开始</t>
+  </si>
+  <si>
+    <t>谍战：人在军统，手下全是穿越者</t>
   </si>
   <si>
     <t>大唐：言出法随，都以为我是仙！</t>
   </si>
   <si>
-    <t>冒姓琅琊</t>
-  </si>
-  <si>
-    <t>女儿被诈两亿，天家千金遭曝光</t>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
+  </si>
+  <si>
+    <t>退游六年，剑仙老婆现实找上门了</t>
+  </si>
+  <si>
+    <t>Fate：开局召唤喜悦闪</t>
+  </si>
+  <si>
+    <t>变身顶美，有颜真能为所欲为</t>
+  </si>
+  <si>
+    <t>觉醒：EX级法师，开局无限火力</t>
+  </si>
+  <si>
+    <t>欢宋</t>
+  </si>
+  <si>
+    <t>超神：成为裁决天使后，我无敌了</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
   </si>
   <si>
     <t>我，酆都，在鸿钧成圣前立地府</t>
   </si>
   <si>
-    <t>火影：从离开木叶建立忍国开始</t>
-  </si>
-  <si>
-    <t>我拿钱就走，九个姐姐全变病娇了</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>女尊，独自抚养妹妹们的正太哥哥</t>
-  </si>
-  <si>
-    <t>退游六年，剑仙老婆现实找上门了</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
-  </si>
-  <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>欢宋</t>
+    <t>直播间都在笑，国防却看沉默了</t>
   </si>
   <si>
     <t>让你荒淫无道，千古一帝什么鬼？</t>
   </si>
   <si>
-    <t>Fate：开局召唤喜悦闪</t>
+    <t>综漫：人在霓虹，开局永恒万花筒</t>
+  </si>
+  <si>
+    <t>星铁：纳努克直聘？我还是跳了吧</t>
+  </si>
+  <si>
+    <t>实习教出金牌班，家长要换班主任</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>死亡列车：开局SSS级天赋！</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>管亥托孤，我带领黄巾争霸天下</t>
+  </si>
+  <si>
+    <t>名义：我避开祁同伟几十年</t>
+  </si>
+  <si>
+    <t>名义：我调任汉东，孙连城笑了！</t>
   </si>
   <si>
     <t>魔女金词条？我反派先薅为敬！</t>
   </si>
   <si>
-    <t>开局豪门继承人，怎么还要上恋综</t>
-  </si>
-  <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>名义：我调任汉东，孙连城笑了！</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>管亥托孤，我带领黄巾争霸天下</t>
-  </si>
-  <si>
-    <t>三体：我还以为是全知域呢！</t>
-  </si>
-  <si>
     <t>不是，让我一个剑修去联姻？</t>
   </si>
   <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>穿书成富二代，我直接救赎女主</t>
-  </si>
-  <si>
-    <t>西游降临：开局拜师通天教主！</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
+    <t>屠城就能回蓝星？兄弟你早说啊！</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
+  </si>
+  <si>
+    <t>游戏入侵：我有一块剑骨头</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离你让我陌生</t>
+  </si>
+  <si>
+    <t>火影：人在木叶村，开局觉醒木遁</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
   </si>
   <si>
     <t>开局流落皇子，可我已经人间无敌</t>
   </si>
   <si>
-    <t>你抢劫诡异良心不会痛吗？</t>
-  </si>
-  <si>
-    <t>赶海：代娶丰腴美人，娇宠俏媳妇</t>
-  </si>
-  <si>
-    <t>四合院：我家住隔壁，看众禽互咬</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>屠城就能回蓝星？兄弟你早说啊！</t>
-  </si>
-  <si>
-    <t>变身顶美，有颜真能为所欲为</t>
+    <t>太子李承乾已死！你选的嘛陛下！</t>
   </si>
   <si>
     <t>抗战：鬼子翻译？不，我代号财神</t>
   </si>
   <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>名义，汉东刘长生，谁与争锋！</t>
-  </si>
-  <si>
-    <t>综漫：人在霓虹，开局永恒万花筒</t>
-  </si>
-  <si>
-    <t>崩铁，死了47次，我决定去卖</t>
-  </si>
-  <si>
-    <t>美综：谁说美剧没有人情世故？</t>
-  </si>
-  <si>
-    <t>超神：成为裁决天使后，我无敌了</t>
-  </si>
-  <si>
-    <t>词条：开局万倍天赋，你要退婚？</t>
-  </si>
-  <si>
-    <t>太子李承乾已死！你选的嘛陛下！</t>
-  </si>
-  <si>
-    <t>重生：什么江湖大哥？资本大鳄！</t>
-  </si>
-  <si>
-    <t>诡异：变身萝莉，诡王是我老爹？</t>
+    <t>我18岁纹开衫闯荡江湖</t>
   </si>
 </sst>
 </file>
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>725000</v>
+        <v>809000</v>
       </c>
       <c r="G5" s="7">
-        <v>70000</v>
+        <v>84000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="7">
         <v>84000</v>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>96.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>245000</v>
+        <v>274000</v>
       </c>
       <c r="G6" s="7">
-        <v>27000</v>
+        <v>23000</v>
       </c>
       <c r="H6" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>22429</v>
+        <v>26444</v>
       </c>
       <c r="J6" s="5">
-        <v>78.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>92.2</v>
+        <v>91.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>496000</v>
+        <v>509000</v>
       </c>
       <c r="G7" s="7">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="H7" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" s="7">
-        <v>31091</v>
+        <v>29583</v>
       </c>
       <c r="J7" s="5">
-        <v>78.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>251000</v>
+        <v>470000</v>
       </c>
       <c r="G8" s="7">
-        <v>13000</v>
+        <v>68000</v>
       </c>
       <c r="H8" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
-        <v>26875</v>
+        <v>69000</v>
       </c>
       <c r="J8" s="5">
-        <v>77.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>96.7</v>
+        <v>99.3</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>180000</v>
+        <v>228000</v>
       </c>
       <c r="G9" s="7">
-        <v>17000</v>
+        <v>30000</v>
       </c>
       <c r="H9" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>15571</v>
+        <v>19000</v>
       </c>
       <c r="J9" s="5">
-        <v>77.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>1747000</v>
+        <v>1745000</v>
       </c>
       <c r="G10" s="7">
-        <v>-4000</v>
+        <v>-2000</v>
       </c>
       <c r="H10" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="7">
-        <v>48273</v>
+        <v>44083</v>
       </c>
       <c r="J10" s="5">
-        <v>76.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>88.59999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>263000</v>
+        <v>115000</v>
       </c>
       <c r="G11" s="7">
-        <v>6000</v>
+        <v>19000</v>
       </c>
       <c r="H11" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>27000</v>
+        <v>13400</v>
       </c>
       <c r="J11" s="5">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,23 +990,23 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>100</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>170000</v>
+        <v>324000</v>
       </c>
       <c r="G12" s="7">
-        <v>21000</v>
+        <v>5000</v>
       </c>
       <c r="H12" s="7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I12" s="7">
-        <v>30667</v>
+        <v>22600</v>
       </c>
       <c r="J12" s="5">
         <v>74.7</v>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>91.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>211000</v>
+        <v>340000</v>
       </c>
       <c r="G13" s="7">
-        <v>10000</v>
+        <v>26000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I13" s="7">
-        <v>16857</v>
+        <v>10167</v>
       </c>
       <c r="J13" s="5">
-        <v>74.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>91.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>188000</v>
+        <v>106000</v>
       </c>
       <c r="G14" s="7">
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="H14" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I14" s="7">
-        <v>17714</v>
+        <v>5250</v>
       </c>
       <c r="J14" s="5">
-        <v>74.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
@@ -1099,16 +1099,16 @@
         <v>267000</v>
       </c>
       <c r="G15" s="7">
-        <v>15000</v>
+        <v>4000</v>
       </c>
       <c r="H15" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7">
-        <v>11364</v>
+        <v>24125</v>
       </c>
       <c r="J15" s="5">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>84.2</v>
+        <v>91</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>319000</v>
+        <v>220000</v>
       </c>
       <c r="G16" s="7">
-        <v>-11000</v>
+        <v>9000</v>
       </c>
       <c r="H16" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>24556</v>
+        <v>15875</v>
       </c>
       <c r="J16" s="5">
-        <v>72.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>90.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>282000</v>
+        <v>105000</v>
       </c>
       <c r="G17" s="7">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="H17" s="7">
         <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>17800</v>
+        <v>14000</v>
       </c>
       <c r="J17" s="5">
-        <v>72.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>91.09999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>162000</v>
+        <v>188000</v>
       </c>
       <c r="G18" s="7">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="H18" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7">
-        <v>8636</v>
+        <v>14625</v>
       </c>
       <c r="J18" s="5">
-        <v>72.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>88.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>308000</v>
+        <v>280000</v>
       </c>
       <c r="G19" s="7">
-        <v>37000</v>
+        <v>13000</v>
       </c>
       <c r="H19" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I19" s="7">
-        <v>13600</v>
+        <v>11500</v>
       </c>
       <c r="J19" s="5">
-        <v>72.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>87.8</v>
+        <v>90.3</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>245000</v>
+        <v>253000</v>
       </c>
       <c r="G20" s="7">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="H20" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="7">
-        <v>15273</v>
+        <v>14667</v>
       </c>
       <c r="J20" s="5">
-        <v>72.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.8</v>
+        <v>89</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>119000</v>
+        <v>199000</v>
       </c>
       <c r="G21" s="7">
-        <v>5000</v>
+        <v>11000</v>
       </c>
       <c r="H21" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I21" s="7">
-        <v>9889</v>
+        <v>16875</v>
       </c>
       <c r="J21" s="5">
-        <v>71.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>80.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>565000</v>
+        <v>288000</v>
       </c>
       <c r="G22" s="7">
-        <v>25000</v>
+        <v>6000</v>
       </c>
       <c r="H22" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>30909</v>
+        <v>15833</v>
       </c>
       <c r="J22" s="5">
-        <v>71.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>91.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>168000</v>
+        <v>180000</v>
       </c>
       <c r="G23" s="7">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>12400</v>
+        <v>12333</v>
       </c>
       <c r="J23" s="5">
-        <v>71.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>90.7</v>
+        <v>86.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>148000</v>
+        <v>668000</v>
       </c>
       <c r="G24" s="7">
-        <v>8000</v>
+        <v>59000</v>
       </c>
       <c r="H24" s="7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I24" s="7">
-        <v>7000</v>
+        <v>54333</v>
       </c>
       <c r="J24" s="5">
-        <v>71.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.3</v>
+        <v>90.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>155000</v>
+        <v>229000</v>
       </c>
       <c r="G25" s="7">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="H25" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I25" s="7">
-        <v>8455</v>
+        <v>10167</v>
       </c>
       <c r="J25" s="5">
-        <v>71.2</v>
+        <v>72.2</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>92.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>232000</v>
+        <v>125000</v>
       </c>
       <c r="G26" s="7">
-        <v>14000</v>
+        <v>6000</v>
       </c>
       <c r="H26" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I26" s="7">
-        <v>545</v>
+        <v>9500</v>
       </c>
       <c r="J26" s="5">
-        <v>71</v>
+        <v>72.2</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>87.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>200000</v>
+        <v>204000</v>
       </c>
       <c r="G27" s="7">
-        <v>9000</v>
+        <v>25000</v>
       </c>
       <c r="H27" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I27" s="7">
-        <v>10200</v>
+        <v>20667</v>
       </c>
       <c r="J27" s="5">
-        <v>70.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>82.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>684000</v>
+        <v>169000</v>
       </c>
       <c r="G28" s="7">
-        <v>28000</v>
+        <v>7000</v>
       </c>
       <c r="H28" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I28" s="7">
-        <v>21091</v>
+        <v>8500</v>
       </c>
       <c r="J28" s="5">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>89.2</v>
+        <v>91</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>108000</v>
+        <v>178000</v>
       </c>
       <c r="G29" s="7">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="H29" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I29" s="7">
-        <v>6364</v>
+        <v>25000</v>
       </c>
       <c r="J29" s="5">
-        <v>70.7</v>
+        <v>71.3</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>86.7</v>
+        <v>97</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>265000</v>
+        <v>171000</v>
       </c>
       <c r="G30" s="7">
-        <v>1000</v>
+        <v>34000</v>
       </c>
       <c r="H30" s="7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I30" s="7">
-        <v>11182</v>
+        <v>24000</v>
       </c>
       <c r="J30" s="5">
-        <v>70.5</v>
+        <v>71.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>150000</v>
+        <v>575000</v>
       </c>
       <c r="G31" s="7">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="H31" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I31" s="7">
-        <v>10455</v>
+        <v>29167</v>
       </c>
       <c r="J31" s="5">
-        <v>70.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>80.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>603000</v>
+        <v>210000</v>
       </c>
       <c r="G32" s="7">
-        <v>28000</v>
+        <v>3000</v>
       </c>
       <c r="H32" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I32" s="7">
-        <v>24909</v>
+        <v>10778</v>
       </c>
       <c r="J32" s="5">
-        <v>70.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>81.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>446000</v>
+        <v>174000</v>
       </c>
       <c r="G33" s="7">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="H33" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I33" s="7">
-        <v>22182</v>
+        <v>8500</v>
       </c>
       <c r="J33" s="5">
-        <v>70.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>87.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>253000</v>
+        <v>710000</v>
       </c>
       <c r="G34" s="7">
-        <v>5000</v>
+        <v>26000</v>
       </c>
       <c r="H34" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I34" s="7">
-        <v>9273</v>
+        <v>21500</v>
       </c>
       <c r="J34" s="5">
-        <v>70.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>78.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>402000</v>
+        <v>632000</v>
       </c>
       <c r="G35" s="7">
-        <v>50000</v>
+        <v>29000</v>
       </c>
       <c r="H35" s="7">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I35" s="7">
-        <v>69500</v>
+        <v>25250</v>
       </c>
       <c r="J35" s="5">
-        <v>69.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>314000</v>
+        <v>465000</v>
       </c>
       <c r="G36" s="7">
-        <v>5000</v>
+        <v>19000</v>
       </c>
       <c r="H36" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I36" s="7">
-        <v>8727</v>
+        <v>21917</v>
       </c>
       <c r="J36" s="5">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>87.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>180000</v>
+        <v>229000</v>
       </c>
       <c r="G37" s="7">
-        <v>12000</v>
+        <v>57000</v>
       </c>
       <c r="H37" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>5909</v>
+        <v>15167</v>
       </c>
       <c r="J37" s="5">
-        <v>69.7</v>
+        <v>70.2</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>101000</v>
+        <v>359000</v>
       </c>
       <c r="G38" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H38" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" s="7">
-        <v>5545</v>
+        <v>333</v>
       </c>
       <c r="J38" s="5">
-        <v>69.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>83</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>249000</v>
+        <v>112000</v>
       </c>
       <c r="G39" s="7">
-        <v>-8000</v>
+        <v>4000</v>
       </c>
       <c r="H39" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I39" s="7">
-        <v>13273</v>
+        <v>6167</v>
       </c>
       <c r="J39" s="5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>85.40000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>198000</v>
+        <v>302000</v>
       </c>
       <c r="G40" s="7">
         <v>6000</v>
       </c>
       <c r="H40" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I40" s="7">
-        <v>7800</v>
+        <v>2833</v>
       </c>
       <c r="J40" s="5">
-        <v>68.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>80.2</v>
+        <v>85.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>401000</v>
+        <v>205000</v>
       </c>
       <c r="G41" s="7">
-        <v>21000</v>
+        <v>5000</v>
       </c>
       <c r="H41" s="7">
         <v>12</v>
       </c>
       <c r="I41" s="7">
-        <v>18818</v>
+        <v>9727</v>
       </c>
       <c r="J41" s="5">
-        <v>68.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>85.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>351000</v>
+        <v>150000</v>
       </c>
       <c r="G42" s="7">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H42" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I42" s="7">
-        <v>6727</v>
+        <v>6583</v>
       </c>
       <c r="J42" s="5">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>84.7</v>
+        <v>85</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>609000</v>
+        <v>150000</v>
       </c>
       <c r="G43" s="7">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I43" s="7">
-        <v>52000</v>
+        <v>9583</v>
       </c>
       <c r="J43" s="5">
-        <v>68.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>83.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>117000</v>
+        <v>351000</v>
       </c>
       <c r="G44" s="7">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H44" s="7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I44" s="7">
-        <v>10111</v>
+        <v>6167</v>
       </c>
       <c r="J44" s="5">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>87.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>283000</v>
+        <v>328000</v>
       </c>
       <c r="G45" s="7">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="H45" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I45" s="7">
-        <v>2182</v>
+        <v>8500</v>
       </c>
       <c r="J45" s="5">
-        <v>68.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>83.7</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>257000</v>
+        <v>419000</v>
       </c>
       <c r="G46" s="7">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="H46" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I46" s="7">
-        <v>9727</v>
+        <v>18750</v>
       </c>
       <c r="J46" s="5">
-        <v>68.5</v>
+        <v>68.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>82.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>207000</v>
+        <v>125000</v>
       </c>
       <c r="G47" s="7">
-        <v>-6000</v>
+        <v>9000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I47" s="7">
-        <v>11750</v>
+        <v>5667</v>
       </c>
       <c r="J47" s="5">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>78.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>279000</v>
+        <v>170000</v>
       </c>
       <c r="G48" s="7">
-        <v>8000</v>
+        <v>17000</v>
       </c>
       <c r="H48" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I48" s="7">
-        <v>21000</v>
+        <v>21333</v>
       </c>
       <c r="J48" s="5">
-        <v>68.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,23 +2211,23 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>89.7</v>
+        <v>82.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>198000</v>
+        <v>328000</v>
       </c>
       <c r="G49" s="7">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="H49" s="7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I49" s="7">
-        <v>16250</v>
+        <v>11750</v>
       </c>
       <c r="J49" s="5">
         <v>68.40000000000001</v>
@@ -2244,23 +2244,23 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>99.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>179000</v>
+        <v>285000</v>
       </c>
       <c r="G50" s="7">
-        <v>24000</v>
+        <v>2000</v>
       </c>
       <c r="H50" s="7">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I50" s="7">
-        <v>18500</v>
+        <v>2167</v>
       </c>
       <c r="J50" s="5">
         <v>68.40000000000001</v>
@@ -2277,23 +2277,23 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.2</v>
+        <v>85.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>169000</v>
+        <v>187000</v>
       </c>
       <c r="G51" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H51" s="7">
+        <v>13</v>
+      </c>
+      <c r="I51" s="7">
         <v>6000</v>
-      </c>
-      <c r="H51" s="7">
-        <v>8</v>
-      </c>
-      <c r="I51" s="7">
-        <v>10714</v>
       </c>
       <c r="J51" s="5">
         <v>68.40000000000001</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>82.7</v>
+        <v>83.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
@@ -2323,10 +2323,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I52" s="7">
-        <v>11500</v>
+        <v>9857</v>
       </c>
       <c r="J52" s="5">
         <v>68.40000000000001</v>
@@ -2343,23 +2343,23 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>79.3</v>
+        <v>83.7</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>348000</v>
+        <v>117000</v>
       </c>
       <c r="G53" s="7">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H53" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I53" s="7">
-        <v>18625</v>
+        <v>9100</v>
       </c>
       <c r="J53" s="5">
         <v>68.3</v>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>94.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>145000</v>
+        <v>108000</v>
       </c>
       <c r="G54" s="7">
         <v>14000</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7">
-        <v>16667</v>
+        <v>5625</v>
       </c>
       <c r="J54" s="5">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-06T04:14:11+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-07T04:13:40+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>西游降临：开局拜师通天教主！</t>
+  </si>
+  <si>
     <t>身家300亿美刀，重回1988</t>
   </si>
   <si>
+    <t>美综：谁说美剧没有人情世故？</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
     <t>轮回修仙：从考科举开始</t>
   </si>
   <si>
-    <t>西游降临：开局拜师通天教主！</t>
-  </si>
-  <si>
-    <t>美综：谁说美剧没有人情世故？</t>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
+  </si>
+  <si>
+    <t>直播间都在笑，国防却看沉默了</t>
+  </si>
+  <si>
+    <t>女尊，独自抚养妹妹们的正太哥哥</t>
+  </si>
+  <si>
+    <t>变身顶美，有颜真能为所欲为</t>
   </si>
   <si>
     <t>冒姓琅琊</t>
   </si>
   <si>
+    <t>谍战：人在军统，手下全是穿越者</t>
+  </si>
+  <si>
+    <t>女儿被诈两亿，天家千金遭曝光</t>
+  </si>
+  <si>
+    <t>火影：从离开木叶建立忍国开始</t>
+  </si>
+  <si>
     <t>就想练练功，怎么就成了大宗师？</t>
   </si>
   <si>
-    <t>女尊，独自抚养妹妹们的正太哥哥</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>开始万倍加速空间，芶在最强宗门</t>
-  </si>
-  <si>
-    <t>女儿被诈两亿，天家千金遭曝光</t>
-  </si>
-  <si>
-    <t>火影：从离开木叶建立忍国开始</t>
-  </si>
-  <si>
-    <t>谍战：人在军统，手下全是穿越者</t>
+    <t>打卡双人骑行圈，开局拿捏假名媛</t>
+  </si>
+  <si>
+    <t>觉醒：EX级法师，开局无限火力</t>
+  </si>
+  <si>
+    <t>词条：开局万倍天赋，你要退婚？</t>
+  </si>
+  <si>
+    <t>欢宋</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>啊？我是背景通天的大佬？</t>
+  </si>
+  <si>
+    <t>退游六年，剑仙老婆现实找上门了</t>
+  </si>
+  <si>
+    <t>名义：搭档沙瑞金，让育良复婚！</t>
   </si>
   <si>
     <t>大唐：言出法随，都以为我是仙！</t>
   </si>
   <si>
+    <t>Fate：开局召唤喜悦闪</t>
+  </si>
+  <si>
+    <t>我，酆都，在鸿钧成圣前立地府</t>
+  </si>
+  <si>
+    <t>斯坦福留洋水货？不！给我再电斯</t>
+  </si>
+  <si>
+    <t>综漫：人在霓虹，开局永恒万花筒</t>
+  </si>
+  <si>
+    <t>让你荒淫无道，千古一帝什么鬼？</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
+    <t>不是，让我一个剑修去联姻？</t>
+  </si>
+  <si>
+    <t>星铁：纳努克直聘？我还是跳了吧</t>
+  </si>
+  <si>
     <t>灵气复苏：别装了，华夏真有仙！</t>
   </si>
   <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>我拿钱就走，九个姐姐全变病娇了</t>
-  </si>
-  <si>
-    <t>退游六年，剑仙老婆现实找上门了</t>
-  </si>
-  <si>
-    <t>Fate：开局召唤喜悦闪</t>
-  </si>
-  <si>
-    <t>变身顶美，有颜真能为所欲为</t>
-  </si>
-  <si>
-    <t>觉醒：EX级法师，开局无限火力</t>
-  </si>
-  <si>
-    <t>欢宋</t>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>名义：我避开祁同伟几十年</t>
+  </si>
+  <si>
+    <t>名义：我调任汉东，孙连城笑了！</t>
+  </si>
+  <si>
+    <t>游戏入侵：我有一块剑骨头</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>1995：我的恣意人生</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
+  </si>
+  <si>
+    <t>管亥托孤，我带领黄巾争霸天下</t>
   </si>
   <si>
     <t>超神：成为裁决天使后，我无敌了</t>
   </si>
   <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>我，酆都，在鸿钧成圣前立地府</t>
-  </si>
-  <si>
-    <t>直播间都在笑，国防却看沉默了</t>
-  </si>
-  <si>
-    <t>让你荒淫无道，千古一帝什么鬼？</t>
-  </si>
-  <si>
-    <t>综漫：人在霓虹，开局永恒万花筒</t>
-  </si>
-  <si>
-    <t>星铁：纳努克直聘？我还是跳了吧</t>
-  </si>
-  <si>
-    <t>实习教出金牌班，家长要换班主任</t>
-  </si>
-  <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>死亡列车：开局SSS级天赋！</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>管亥托孤，我带领黄巾争霸天下</t>
-  </si>
-  <si>
-    <t>名义：我避开祁同伟几十年</t>
-  </si>
-  <si>
-    <t>名义：我调任汉东，孙连城笑了！</t>
+    <t>我有一个女鬼催眠APP</t>
   </si>
   <si>
     <t>魔女金词条？我反派先薅为敬！</t>
   </si>
   <si>
-    <t>不是，让我一个剑修去联姻？</t>
-  </si>
-  <si>
-    <t>屠城就能回蓝星？兄弟你早说啊！</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>游戏入侵：我有一块剑骨头</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离你让我陌生</t>
-  </si>
-  <si>
-    <t>火影：人在木叶村，开局觉醒木遁</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
     <t>开局流落皇子，可我已经人间无敌</t>
-  </si>
-  <si>
-    <t>太子李承乾已死！你选的嘛陛下！</t>
-  </si>
-  <si>
-    <t>抗战：鬼子翻译？不，我代号财神</t>
-  </si>
-  <si>
-    <t>我18岁纹开衫闯荡江湖</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>809000</v>
+        <v>891000</v>
       </c>
       <c r="G5" s="7">
-        <v>84000</v>
+        <v>82000</v>
       </c>
       <c r="H5" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="7">
-        <v>84000</v>
+        <v>83778</v>
       </c>
       <c r="J5" s="5">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>274000</v>
+        <v>317000</v>
       </c>
       <c r="G6" s="7">
-        <v>23000</v>
+        <v>83000</v>
       </c>
       <c r="H6" s="7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I6" s="7">
-        <v>26444</v>
+        <v>96000</v>
       </c>
       <c r="J6" s="5">
-        <v>79.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>91.2</v>
+        <v>88.5</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>509000</v>
+        <v>536000</v>
       </c>
       <c r="G7" s="7">
-        <v>13000</v>
+        <v>66000</v>
       </c>
       <c r="H7" s="7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I7" s="7">
-        <v>29583</v>
+        <v>68250</v>
       </c>
       <c r="J7" s="5">
-        <v>77.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>87.5</v>
+        <v>96.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>470000</v>
+        <v>299000</v>
       </c>
       <c r="G8" s="7">
-        <v>68000</v>
+        <v>25000</v>
       </c>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I8" s="7">
-        <v>69000</v>
+        <v>26300</v>
       </c>
       <c r="J8" s="5">
-        <v>77.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.3</v>
+        <v>98.5</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>228000</v>
+        <v>258000</v>
       </c>
       <c r="G9" s="7">
         <v>30000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>19000</v>
+        <v>20833</v>
       </c>
       <c r="J9" s="5">
-        <v>77.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>81.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>1745000</v>
+        <v>400000</v>
       </c>
       <c r="G10" s="7">
-        <v>-2000</v>
+        <v>60000</v>
       </c>
       <c r="H10" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="7">
-        <v>44083</v>
+        <v>14000</v>
       </c>
       <c r="J10" s="5">
-        <v>75.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>98.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>115000</v>
+        <v>520000</v>
       </c>
       <c r="G11" s="7">
-        <v>19000</v>
+        <v>11000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I11" s="7">
-        <v>13400</v>
+        <v>28154</v>
       </c>
       <c r="J11" s="5">
-        <v>75.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>89.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>324000</v>
+        <v>218000</v>
       </c>
       <c r="G12" s="7">
-        <v>5000</v>
+        <v>19000</v>
       </c>
       <c r="H12" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>22600</v>
+        <v>17111</v>
       </c>
       <c r="J12" s="5">
-        <v>74.7</v>
+        <v>75.8</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>94.3</v>
+        <v>98.2</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>340000</v>
+        <v>198000</v>
       </c>
       <c r="G13" s="7">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="H13" s="7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I13" s="7">
-        <v>10167</v>
+        <v>24750</v>
       </c>
       <c r="J13" s="5">
-        <v>74.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>96.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>106000</v>
+        <v>333000</v>
       </c>
       <c r="G14" s="7">
-        <v>13000</v>
+        <v>9000</v>
       </c>
       <c r="H14" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I14" s="7">
-        <v>5250</v>
+        <v>21364</v>
       </c>
       <c r="J14" s="5">
-        <v>74.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>87.8</v>
+        <v>85.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>267000</v>
+        <v>714000</v>
       </c>
       <c r="G15" s="7">
-        <v>4000</v>
+        <v>46000</v>
       </c>
       <c r="H15" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I15" s="7">
-        <v>24125</v>
+        <v>52250</v>
       </c>
       <c r="J15" s="5">
-        <v>74.3</v>
+        <v>75</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>91</v>
+        <v>81.2</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>220000</v>
+        <v>1745000</v>
       </c>
       <c r="G16" s="7">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I16" s="7">
-        <v>15875</v>
+        <v>40692</v>
       </c>
       <c r="J16" s="5">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>95.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>105000</v>
+        <v>116000</v>
       </c>
       <c r="G17" s="7">
-        <v>22000</v>
+        <v>11000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="7">
-        <v>14000</v>
+        <v>13500</v>
       </c>
       <c r="J17" s="5">
-        <v>73.8</v>
+        <v>74.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>90.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>188000</v>
+        <v>273000</v>
       </c>
       <c r="G18" s="7">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="H18" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="7">
-        <v>14625</v>
+        <v>22111</v>
       </c>
       <c r="J18" s="5">
-        <v>73.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>92.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>280000</v>
+        <v>229000</v>
       </c>
       <c r="G19" s="7">
-        <v>13000</v>
+        <v>9000</v>
       </c>
       <c r="H19" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I19" s="7">
-        <v>11500</v>
+        <v>15111</v>
       </c>
       <c r="J19" s="5">
-        <v>73.5</v>
+        <v>73.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>253000</v>
+        <v>123000</v>
       </c>
       <c r="G20" s="7">
         <v>8000</v>
       </c>
       <c r="H20" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I20" s="7">
-        <v>14667</v>
+        <v>12500</v>
       </c>
       <c r="J20" s="5">
-        <v>73.3</v>
+        <v>73.5</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>199000</v>
+        <v>507000</v>
       </c>
       <c r="G21" s="7">
-        <v>11000</v>
+        <v>64000</v>
       </c>
       <c r="H21" s="7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I21" s="7">
-        <v>16875</v>
+        <v>37500</v>
       </c>
       <c r="J21" s="5">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,23 +1320,23 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>89.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>288000</v>
+        <v>244000</v>
       </c>
       <c r="G22" s="7">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I22" s="7">
-        <v>15833</v>
+        <v>10538</v>
       </c>
       <c r="J22" s="5">
         <v>73.09999999999999</v>
@@ -1360,19 +1360,19 @@
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>180000</v>
+        <v>187000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I23" s="7">
-        <v>12333</v>
+        <v>10333</v>
       </c>
       <c r="J23" s="5">
-        <v>73.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>86.3</v>
+        <v>91.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>668000</v>
+        <v>132000</v>
       </c>
       <c r="G24" s="7">
-        <v>59000</v>
+        <v>7000</v>
       </c>
       <c r="H24" s="7">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I24" s="7">
-        <v>54333</v>
+        <v>9273</v>
       </c>
       <c r="J24" s="5">
-        <v>73</v>
+        <v>72.5</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.2</v>
+        <v>94.3</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>229000</v>
+        <v>382000</v>
       </c>
       <c r="G25" s="7">
-        <v>11000</v>
+        <v>23000</v>
       </c>
       <c r="H25" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="7">
-        <v>10167</v>
+        <v>2077</v>
       </c>
       <c r="J25" s="5">
-        <v>72.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>90.5</v>
+        <v>89</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>125000</v>
+        <v>258000</v>
       </c>
       <c r="G26" s="7">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H26" s="7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I26" s="7">
-        <v>9500</v>
+        <v>13923</v>
       </c>
       <c r="J26" s="5">
-        <v>72.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>98.8</v>
+        <v>97</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>204000</v>
+        <v>175000</v>
       </c>
       <c r="G27" s="7">
-        <v>25000</v>
+        <v>53000</v>
       </c>
       <c r="H27" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" s="7">
-        <v>20667</v>
+        <v>39500</v>
       </c>
       <c r="J27" s="5">
-        <v>71.5</v>
+        <v>72.2</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,23 +1518,23 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>89.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>169000</v>
+        <v>288000</v>
       </c>
       <c r="G28" s="7">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="H28" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>8500</v>
+        <v>13571</v>
       </c>
       <c r="J28" s="5">
         <v>71.40000000000001</v>
@@ -1551,23 +1551,23 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>91</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>178000</v>
+        <v>257000</v>
       </c>
       <c r="G29" s="7">
-        <v>8000</v>
+        <v>21000</v>
       </c>
       <c r="H29" s="7">
         <v>5</v>
       </c>
       <c r="I29" s="7">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="J29" s="5">
         <v>71.3</v>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>97</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>171000</v>
+        <v>189000</v>
       </c>
       <c r="G30" s="7">
-        <v>34000</v>
+        <v>1000</v>
       </c>
       <c r="H30" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I30" s="7">
-        <v>24000</v>
+        <v>13111</v>
       </c>
       <c r="J30" s="5">
-        <v>71.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>79.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>575000</v>
+        <v>185000</v>
       </c>
       <c r="G31" s="7">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H31" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>29167</v>
+        <v>11286</v>
       </c>
       <c r="J31" s="5">
-        <v>71.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>87.2</v>
+        <v>86.8</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>210000</v>
+        <v>179000</v>
       </c>
       <c r="G32" s="7">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="H32" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>10778</v>
+        <v>20200</v>
       </c>
       <c r="J32" s="5">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,23 +1683,23 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>88.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>174000</v>
+        <v>140000</v>
       </c>
       <c r="G33" s="7">
-        <v>9000</v>
+        <v>20000</v>
       </c>
       <c r="H33" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>8500</v>
+        <v>9200</v>
       </c>
       <c r="J33" s="5">
         <v>70.7</v>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>82.2</v>
+        <v>87.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>710000</v>
+        <v>213000</v>
       </c>
       <c r="G34" s="7">
-        <v>26000</v>
+        <v>3000</v>
       </c>
       <c r="H34" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I34" s="7">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="J34" s="5">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>80.5</v>
+        <v>79.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>632000</v>
+        <v>582000</v>
       </c>
       <c r="G35" s="7">
-        <v>29000</v>
+        <v>7000</v>
       </c>
       <c r="H35" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I35" s="7">
-        <v>25250</v>
+        <v>27462</v>
       </c>
       <c r="J35" s="5">
-        <v>70.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>81.8</v>
+        <v>80</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>465000</v>
+        <v>659000</v>
       </c>
       <c r="G36" s="7">
-        <v>19000</v>
+        <v>27000</v>
       </c>
       <c r="H36" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I36" s="7">
-        <v>21917</v>
+        <v>25385</v>
       </c>
       <c r="J36" s="5">
-        <v>70.5</v>
+        <v>70.3</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>84.3</v>
+        <v>90.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>229000</v>
+        <v>111000</v>
       </c>
       <c r="G37" s="7">
-        <v>57000</v>
+        <v>9000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I37" s="7">
-        <v>15167</v>
+        <v>1846</v>
       </c>
       <c r="J37" s="5">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>90.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>359000</v>
+        <v>153000</v>
       </c>
       <c r="G38" s="7">
-        <v>11000</v>
+        <v>3000</v>
       </c>
       <c r="H38" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I38" s="7">
-        <v>333</v>
+        <v>9077</v>
       </c>
       <c r="J38" s="5">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>88.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>112000</v>
+        <v>184000</v>
       </c>
       <c r="G39" s="7">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="H39" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>6167</v>
+        <v>8667</v>
       </c>
       <c r="J39" s="5">
-        <v>70</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>89.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>302000</v>
+        <v>277000</v>
       </c>
       <c r="G40" s="7">
-        <v>6000</v>
+        <v>-3000</v>
       </c>
       <c r="H40" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I40" s="7">
-        <v>2833</v>
+        <v>10385</v>
       </c>
       <c r="J40" s="5">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>85.7</v>
+        <v>81</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>205000</v>
+        <v>481000</v>
       </c>
       <c r="G41" s="7">
-        <v>5000</v>
+        <v>16000</v>
       </c>
       <c r="H41" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I41" s="7">
-        <v>9727</v>
+        <v>21462</v>
       </c>
       <c r="J41" s="5">
-        <v>69.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>86.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>150000</v>
+        <v>307000</v>
       </c>
       <c r="G42" s="7">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H42" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I42" s="7">
-        <v>6583</v>
+        <v>3000</v>
       </c>
       <c r="J42" s="5">
-        <v>69.2</v>
+        <v>69.8</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85</v>
+        <v>86.2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>150000</v>
+        <v>211000</v>
       </c>
       <c r="G43" s="7">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H43" s="7">
         <v>13</v>
       </c>
       <c r="I43" s="7">
-        <v>9583</v>
+        <v>9417</v>
       </c>
       <c r="J43" s="5">
-        <v>69.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>351000</v>
+        <v>134000</v>
       </c>
       <c r="G44" s="7">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="H44" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I44" s="7">
-        <v>6167</v>
+        <v>6143</v>
       </c>
       <c r="J44" s="5">
-        <v>68.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>85.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>328000</v>
+        <v>1149000</v>
       </c>
       <c r="G45" s="7">
-        <v>30000</v>
+        <v>81000</v>
       </c>
       <c r="H45" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I45" s="7">
-        <v>8500</v>
+        <v>4846</v>
       </c>
       <c r="J45" s="5">
-        <v>68.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>80.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>419000</v>
+        <v>359000</v>
       </c>
       <c r="G46" s="7">
-        <v>18000</v>
+        <v>31000</v>
       </c>
       <c r="H46" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I46" s="7">
-        <v>18750</v>
+        <v>10231</v>
       </c>
       <c r="J46" s="5">
-        <v>68.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>85.7</v>
+        <v>86.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>125000</v>
+        <v>171000</v>
       </c>
       <c r="G47" s="7">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="H47" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I47" s="7">
-        <v>5667</v>
+        <v>8000</v>
       </c>
       <c r="J47" s="5">
-        <v>68.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>93.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>170000</v>
+        <v>102000</v>
       </c>
       <c r="G48" s="7">
-        <v>17000</v>
+        <v>4000</v>
       </c>
       <c r="H48" s="7">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I48" s="7">
-        <v>21333</v>
+        <v>5615</v>
       </c>
       <c r="J48" s="5">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>82.7</v>
+        <v>80.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>328000</v>
+        <v>433000</v>
       </c>
       <c r="G49" s="7">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="H49" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I49" s="7">
-        <v>11750</v>
+        <v>18385</v>
       </c>
       <c r="J49" s="5">
-        <v>68.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>87.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>285000</v>
+        <v>114000</v>
       </c>
       <c r="G50" s="7">
         <v>2000</v>
       </c>
       <c r="H50" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I50" s="7">
-        <v>2167</v>
+        <v>5846</v>
       </c>
       <c r="J50" s="5">
-        <v>68.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.2</v>
+        <v>89.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>187000</v>
+        <v>216000</v>
       </c>
       <c r="G51" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H51" s="7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I51" s="7">
-        <v>6000</v>
+        <v>18500</v>
       </c>
       <c r="J51" s="5">
-        <v>68.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>83.5</v>
+        <v>87.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>108000</v>
+        <v>287000</v>
       </c>
       <c r="G52" s="7">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H52" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I52" s="7">
-        <v>9857</v>
+        <v>2154</v>
       </c>
       <c r="J52" s="5">
-        <v>68.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>83.7</v>
+        <v>85.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>117000</v>
+        <v>149000</v>
       </c>
       <c r="G53" s="7">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="H53" s="7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I53" s="7">
-        <v>9100</v>
+        <v>6000</v>
       </c>
       <c r="J53" s="5">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>108000</v>
+        <v>191000</v>
       </c>
       <c r="G54" s="7">
-        <v>14000</v>
+        <v>4000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I54" s="7">
-        <v>5625</v>
+        <v>5846</v>
       </c>
       <c r="J54" s="5">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-07T04:13:40+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-08T04:14:48+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -82,145 +82,145 @@
     <t>西游降临：开局拜师通天教主！</t>
   </si>
   <si>
+    <t>觉醒：EX级法师，开局无限火力</t>
+  </si>
+  <si>
+    <t>打卡双人骑行圈，开局拿捏假名媛</t>
+  </si>
+  <si>
     <t>身家300亿美刀，重回1988</t>
   </si>
   <si>
+    <t>轮回修仙：从考科举开始</t>
+  </si>
+  <si>
+    <t>乡村王大莽</t>
+  </si>
+  <si>
+    <t>大明：开局轩辕剑，朱允熥杀疯了</t>
+  </si>
+  <si>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
+  </si>
+  <si>
+    <t>退游六年，剑仙老婆现实找上门了</t>
+  </si>
+  <si>
+    <t>变身顶美，有颜真能为所欲为</t>
+  </si>
+  <si>
+    <t>女尊，独自抚养妹妹们的正太哥哥</t>
+  </si>
+  <si>
+    <t>直播间都在笑，国防却看沉默了</t>
+  </si>
+  <si>
     <t>美综：谁说美剧没有人情世故？</t>
   </si>
   <si>
+    <t>啊？我是背景通天的大佬？</t>
+  </si>
+  <si>
+    <t>斯坦福留洋水货？不！给我再电斯</t>
+  </si>
+  <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
     <t>同学们都选阐教，我选截教杀疯了</t>
   </si>
   <si>
-    <t>轮回修仙：从考科举开始</t>
-  </si>
-  <si>
-    <t>我拿钱就走，九个姐姐全变病娇了</t>
-  </si>
-  <si>
-    <t>直播间都在笑，国防却看沉默了</t>
-  </si>
-  <si>
-    <t>女尊，独自抚养妹妹们的正太哥哥</t>
-  </si>
-  <si>
-    <t>变身顶美，有颜真能为所欲为</t>
-  </si>
-  <si>
-    <t>冒姓琅琊</t>
+    <t>天幕通原神，开局钟离你让我陌生</t>
+  </si>
+  <si>
+    <t>女儿被诈两亿，天家千金遭曝光</t>
+  </si>
+  <si>
+    <t>火影：从离开木叶建立忍国开始</t>
+  </si>
+  <si>
+    <t>欢宋</t>
+  </si>
+  <si>
+    <t>名义：搭档沙瑞金，让育良复婚！</t>
+  </si>
+  <si>
+    <t>我，酆都，在鸿钧成圣前立地府</t>
   </si>
   <si>
     <t>谍战：人在军统，手下全是穿越者</t>
   </si>
   <si>
-    <t>女儿被诈两亿，天家千金遭曝光</t>
-  </si>
-  <si>
-    <t>火影：从离开木叶建立忍国开始</t>
+    <t>网游：我的药剂永久持续</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>星铁：纳努克直聘？我还是跳了吧</t>
+  </si>
+  <si>
+    <t>超神：成为裁决天使后，我无敌了</t>
   </si>
   <si>
     <t>就想练练功，怎么就成了大宗师？</t>
   </si>
   <si>
-    <t>打卡双人骑行圈，开局拿捏假名媛</t>
-  </si>
-  <si>
-    <t>觉醒：EX级法师，开局无限火力</t>
-  </si>
-  <si>
-    <t>词条：开局万倍天赋，你要退婚？</t>
-  </si>
-  <si>
-    <t>欢宋</t>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
+    <t>大唐：言出法随，都以为我是仙！</t>
+  </si>
+  <si>
+    <t>综漫：人在霓虹，开局永恒万花筒</t>
+  </si>
+  <si>
+    <t>全民恐怖求生：我觉醒加点序列！</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>重生1955，我刷抖音造核武</t>
+  </si>
+  <si>
+    <t>诡异乱世：大乾第一巡夜人</t>
+  </si>
+  <si>
+    <t>诡异：变身萝莉，诡王是我老爹？</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>网游之绝世毒尊</t>
+  </si>
+  <si>
+    <t>Fate：开局召唤喜悦闪</t>
   </si>
   <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>啊？我是背景通天的大佬？</t>
-  </si>
-  <si>
-    <t>退游六年，剑仙老婆现实找上门了</t>
-  </si>
-  <si>
-    <t>名义：搭档沙瑞金，让育良复婚！</t>
-  </si>
-  <si>
-    <t>大唐：言出法随，都以为我是仙！</t>
-  </si>
-  <si>
-    <t>Fate：开局召唤喜悦闪</t>
-  </si>
-  <si>
-    <t>我，酆都，在鸿钧成圣前立地府</t>
-  </si>
-  <si>
-    <t>斯坦福留洋水货？不！给我再电斯</t>
-  </si>
-  <si>
-    <t>综漫：人在霓虹，开局永恒万花筒</t>
+    <t>管亥托孤，我带领黄巾争霸天下</t>
   </si>
   <si>
     <t>让你荒淫无道，千古一帝什么鬼？</t>
   </si>
   <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
+    <t>你管这叫警察？重炮都架租界口了</t>
   </si>
   <si>
     <t>不是，让我一个剑修去联姻？</t>
   </si>
   <si>
-    <t>星铁：纳努克直聘？我还是跳了吧</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>名义：我避开祁同伟几十年</t>
-  </si>
-  <si>
-    <t>名义：我调任汉东，孙连城笑了！</t>
-  </si>
-  <si>
     <t>游戏入侵：我有一块剑骨头</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>1995：我的恣意人生</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>管亥托孤，我带领黄巾争霸天下</t>
-  </si>
-  <si>
-    <t>超神：成为裁决天使后，我无敌了</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>开局流落皇子，可我已经人间无敌</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>99.90000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>891000</v>
+        <v>953000</v>
       </c>
       <c r="G5" s="7">
-        <v>82000</v>
+        <v>62000</v>
       </c>
       <c r="H5" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="7">
-        <v>83778</v>
+        <v>81600</v>
       </c>
       <c r="J5" s="5">
-        <v>95.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>317000</v>
+        <v>384000</v>
       </c>
       <c r="G6" s="7">
-        <v>83000</v>
+        <v>67000</v>
       </c>
       <c r="H6" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="7">
-        <v>96000</v>
+        <v>86333</v>
       </c>
       <c r="J6" s="5">
-        <v>88</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,23 +825,23 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>88.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>536000</v>
+        <v>588000</v>
       </c>
       <c r="G7" s="7">
-        <v>66000</v>
+        <v>52000</v>
       </c>
       <c r="H7" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="7">
-        <v>68250</v>
+        <v>65000</v>
       </c>
       <c r="J7" s="5">
         <v>80.7</v>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>299000</v>
+        <v>314000</v>
       </c>
       <c r="G8" s="7">
-        <v>25000</v>
+        <v>70000</v>
       </c>
       <c r="H8" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I8" s="7">
-        <v>26300</v>
+        <v>14786</v>
       </c>
       <c r="J8" s="5">
-        <v>79.7</v>
+        <v>78.7</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>98.5</v>
+        <v>99.8</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>258000</v>
+        <v>563000</v>
       </c>
       <c r="G9" s="7">
-        <v>30000</v>
+        <v>56000</v>
       </c>
       <c r="H9" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7">
-        <v>20833</v>
+        <v>43667</v>
       </c>
       <c r="J9" s="5">
-        <v>79.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>92.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>400000</v>
+        <v>315000</v>
       </c>
       <c r="G10" s="7">
-        <v>60000</v>
+        <v>16000</v>
       </c>
       <c r="H10" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I10" s="7">
-        <v>14000</v>
+        <v>25364</v>
       </c>
       <c r="J10" s="5">
-        <v>78.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>90.7</v>
+        <v>91.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>520000</v>
+        <v>536000</v>
       </c>
       <c r="G11" s="7">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="H11" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" s="7">
-        <v>28154</v>
+        <v>27286</v>
       </c>
       <c r="J11" s="5">
-        <v>76.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>93.7</v>
+        <v>98.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>218000</v>
+        <v>119000</v>
       </c>
       <c r="G12" s="7">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="H12" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I12" s="7">
-        <v>17111</v>
+        <v>8909</v>
       </c>
       <c r="J12" s="5">
-        <v>75.8</v>
+        <v>76.5</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>98.2</v>
+        <v>97.8</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>198000</v>
+        <v>114000</v>
       </c>
       <c r="G13" s="7">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="H13" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>24750</v>
+        <v>9143</v>
       </c>
       <c r="J13" s="5">
-        <v>75.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>90.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>333000</v>
+        <v>238000</v>
       </c>
       <c r="G14" s="7">
-        <v>9000</v>
+        <v>20000</v>
       </c>
       <c r="H14" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
-        <v>21364</v>
+        <v>17400</v>
       </c>
       <c r="J14" s="5">
-        <v>75.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>85.3</v>
+        <v>94.7</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>714000</v>
+        <v>309000</v>
       </c>
       <c r="G15" s="7">
-        <v>46000</v>
+        <v>21000</v>
       </c>
       <c r="H15" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7">
-        <v>52250</v>
+        <v>14500</v>
       </c>
       <c r="J15" s="5">
-        <v>75</v>
+        <v>75.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>81.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>1745000</v>
+        <v>743000</v>
       </c>
       <c r="G16" s="7">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="H16" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>40692</v>
+        <v>47600</v>
       </c>
       <c r="J16" s="5">
-        <v>74.8</v>
+        <v>75.3</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>93.3</v>
+        <v>90.7</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>116000</v>
+        <v>343000</v>
       </c>
       <c r="G17" s="7">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="H17" s="7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I17" s="7">
-        <v>13500</v>
+        <v>20417</v>
       </c>
       <c r="J17" s="5">
-        <v>74.7</v>
+        <v>75</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>88.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>273000</v>
+        <v>217000</v>
       </c>
       <c r="G18" s="7">
-        <v>6000</v>
+        <v>19000</v>
       </c>
       <c r="H18" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I18" s="7">
-        <v>22111</v>
+        <v>23600</v>
       </c>
       <c r="J18" s="5">
-        <v>74.3</v>
+        <v>75</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>90.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>229000</v>
+        <v>276000</v>
       </c>
       <c r="G19" s="7">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="H19" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>15111</v>
+        <v>20429</v>
       </c>
       <c r="J19" s="5">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>91.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>123000</v>
+        <v>202000</v>
       </c>
       <c r="G20" s="7">
-        <v>8000</v>
+        <v>27000</v>
       </c>
       <c r="H20" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I20" s="7">
-        <v>12500</v>
+        <v>35333</v>
       </c>
       <c r="J20" s="5">
-        <v>73.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>507000</v>
+        <v>161000</v>
       </c>
       <c r="G21" s="7">
-        <v>64000</v>
+        <v>21000</v>
       </c>
       <c r="H21" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>37500</v>
+        <v>11167</v>
       </c>
       <c r="J21" s="5">
-        <v>73.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>91.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>244000</v>
+        <v>1740000</v>
       </c>
       <c r="G22" s="7">
-        <v>15000</v>
+        <v>-5000</v>
       </c>
       <c r="H22" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I22" s="7">
-        <v>10538</v>
+        <v>37429</v>
       </c>
       <c r="J22" s="5">
-        <v>73.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>90.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>187000</v>
+        <v>417000</v>
       </c>
       <c r="G23" s="7">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="H23" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I23" s="7">
-        <v>10333</v>
+        <v>14214</v>
       </c>
       <c r="J23" s="5">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>132000</v>
+        <v>201000</v>
       </c>
       <c r="G24" s="7">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H24" s="7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>9273</v>
+        <v>19000</v>
       </c>
       <c r="J24" s="5">
-        <v>72.5</v>
+        <v>73.8</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>94.3</v>
+        <v>88.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>382000</v>
+        <v>278000</v>
       </c>
       <c r="G25" s="7">
-        <v>23000</v>
+        <v>5000</v>
       </c>
       <c r="H25" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I25" s="7">
-        <v>2077</v>
+        <v>20400</v>
       </c>
       <c r="J25" s="5">
-        <v>72.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>89</v>
+        <v>89.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>258000</v>
+        <v>235000</v>
       </c>
       <c r="G26" s="7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H26" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I26" s="7">
-        <v>13923</v>
+        <v>14200</v>
       </c>
       <c r="J26" s="5">
-        <v>72.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>97</v>
+        <v>91.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>175000</v>
+        <v>140000</v>
       </c>
       <c r="G27" s="7">
-        <v>53000</v>
+        <v>8000</v>
       </c>
       <c r="H27" s="7">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I27" s="7">
-        <v>39500</v>
+        <v>9167</v>
       </c>
       <c r="J27" s="5">
-        <v>72.2</v>
+        <v>72.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>87.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>288000</v>
+        <v>274000</v>
       </c>
       <c r="G28" s="7">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I28" s="7">
-        <v>13571</v>
+        <v>16200</v>
       </c>
       <c r="J28" s="5">
-        <v>71.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>95.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>257000</v>
+        <v>179000</v>
       </c>
       <c r="G29" s="7">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>16000</v>
+        <v>16833</v>
       </c>
       <c r="J29" s="5">
-        <v>71.3</v>
+        <v>71.7</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>86.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>189000</v>
+        <v>123000</v>
       </c>
       <c r="G30" s="7">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H30" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I30" s="7">
-        <v>13111</v>
+        <v>12571</v>
       </c>
       <c r="J30" s="5">
-        <v>71.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>185000</v>
+        <v>119000</v>
       </c>
       <c r="G31" s="7">
-        <v>5000</v>
+        <v>27000</v>
       </c>
       <c r="H31" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I31" s="7">
-        <v>11286</v>
+        <v>31500</v>
       </c>
       <c r="J31" s="5">
-        <v>70.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>86.8</v>
+        <v>83.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>179000</v>
+        <v>510000</v>
       </c>
       <c r="G32" s="7">
-        <v>1000</v>
+        <v>29000</v>
       </c>
       <c r="H32" s="7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I32" s="7">
-        <v>20200</v>
+        <v>22000</v>
       </c>
       <c r="J32" s="5">
-        <v>70.8</v>
+        <v>71.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>91.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>140000</v>
+        <v>195000</v>
       </c>
       <c r="G33" s="7">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I33" s="7">
-        <v>9200</v>
+        <v>8900</v>
       </c>
       <c r="J33" s="5">
-        <v>70.7</v>
+        <v>71.2</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>87.2</v>
+        <v>88.7</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>213000</v>
+        <v>229000</v>
       </c>
       <c r="G34" s="7">
-        <v>3000</v>
+        <v>13000</v>
       </c>
       <c r="H34" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>10000</v>
+        <v>17400</v>
       </c>
       <c r="J34" s="5">
-        <v>70.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>79.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>582000</v>
+        <v>126000</v>
       </c>
       <c r="G35" s="7">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="H35" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I35" s="7">
-        <v>27462</v>
+        <v>11143</v>
       </c>
       <c r="J35" s="5">
-        <v>70.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>659000</v>
+        <v>120000</v>
       </c>
       <c r="G36" s="7">
-        <v>27000</v>
+        <v>9000</v>
       </c>
       <c r="H36" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I36" s="7">
-        <v>25385</v>
+        <v>2357</v>
       </c>
       <c r="J36" s="5">
-        <v>70.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>90.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>111000</v>
+        <v>189000</v>
       </c>
       <c r="G37" s="7">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I37" s="7">
-        <v>1846</v>
+        <v>11800</v>
       </c>
       <c r="J37" s="5">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>153000</v>
+        <v>216000</v>
       </c>
       <c r="G38" s="7">
         <v>3000</v>
       </c>
       <c r="H38" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I38" s="7">
-        <v>9077</v>
+        <v>9364</v>
       </c>
       <c r="J38" s="5">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>87.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>184000</v>
+        <v>685000</v>
       </c>
       <c r="G39" s="7">
-        <v>10000</v>
+        <v>26000</v>
       </c>
       <c r="H39" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I39" s="7">
-        <v>8667</v>
+        <v>25429</v>
       </c>
       <c r="J39" s="5">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.09999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>277000</v>
+        <v>254000</v>
       </c>
       <c r="G40" s="7">
-        <v>-3000</v>
+        <v>-4000</v>
       </c>
       <c r="H40" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I40" s="7">
-        <v>10385</v>
+        <v>12643</v>
       </c>
       <c r="J40" s="5">
-        <v>70</v>
+        <v>70.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>81</v>
+        <v>91.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>481000</v>
+        <v>171000</v>
       </c>
       <c r="G41" s="7">
         <v>16000</v>
       </c>
       <c r="H41" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>21462</v>
+        <v>18500</v>
       </c>
       <c r="J41" s="5">
-        <v>69.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89.09999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>307000</v>
+        <v>154000</v>
       </c>
       <c r="G42" s="7">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="H42" s="7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="J42" s="5">
-        <v>69.8</v>
+        <v>70</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>211000</v>
+        <v>153000</v>
       </c>
       <c r="G43" s="7">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="H43" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I43" s="7">
-        <v>9417</v>
+        <v>9667</v>
       </c>
       <c r="J43" s="5">
-        <v>69.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>87.8</v>
+        <v>85.7</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>134000</v>
+        <v>273000</v>
       </c>
       <c r="G44" s="7">
-        <v>9000</v>
+        <v>-4000</v>
       </c>
       <c r="H44" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I44" s="7">
-        <v>6143</v>
+        <v>9357</v>
       </c>
       <c r="J44" s="5">
-        <v>69.8</v>
+        <v>69.5</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>87.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>1149000</v>
+        <v>386000</v>
       </c>
       <c r="G45" s="7">
-        <v>81000</v>
+        <v>27000</v>
       </c>
       <c r="H45" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I45" s="7">
-        <v>4846</v>
+        <v>11429</v>
       </c>
       <c r="J45" s="5">
-        <v>69.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>359000</v>
+        <v>1210000</v>
       </c>
       <c r="G46" s="7">
-        <v>31000</v>
+        <v>61000</v>
       </c>
       <c r="H46" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I46" s="7">
-        <v>10231</v>
+        <v>8857</v>
       </c>
       <c r="J46" s="5">
-        <v>69.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>86.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>171000</v>
+        <v>450000</v>
       </c>
       <c r="G47" s="7">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="H47" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I47" s="7">
-        <v>8000</v>
+        <v>18286</v>
       </c>
       <c r="J47" s="5">
-        <v>69.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>102000</v>
+        <v>186000</v>
       </c>
       <c r="G48" s="7">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="H48" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>5615</v>
+        <v>10000</v>
       </c>
       <c r="J48" s="5">
-        <v>69.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>80.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>433000</v>
+        <v>382000</v>
       </c>
       <c r="G49" s="7">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I49" s="7">
-        <v>18385</v>
+        <v>1929</v>
       </c>
       <c r="J49" s="5">
-        <v>69</v>
+        <v>68.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2251,19 +2251,19 @@
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>114000</v>
+        <v>116000</v>
       </c>
       <c r="G50" s="7">
         <v>2000</v>
       </c>
       <c r="H50" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I50" s="7">
-        <v>5846</v>
+        <v>5571</v>
       </c>
       <c r="J50" s="5">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>89.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>216000</v>
+        <v>572000</v>
       </c>
       <c r="G51" s="7">
-        <v>12000</v>
+        <v>-10000</v>
       </c>
       <c r="H51" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I51" s="7">
-        <v>18500</v>
+        <v>24786</v>
       </c>
       <c r="J51" s="5">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,23 +2310,23 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>87.2</v>
+        <v>88.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>287000</v>
+        <v>227000</v>
       </c>
       <c r="G52" s="7">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H52" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I52" s="7">
-        <v>2154</v>
+        <v>71</v>
       </c>
       <c r="J52" s="5">
         <v>68.5</v>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>85.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>149000</v>
+        <v>152000</v>
       </c>
       <c r="G53" s="7">
         <v>-1000</v>
       </c>
       <c r="H53" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I53" s="7">
-        <v>6000</v>
+        <v>8357</v>
       </c>
       <c r="J53" s="5">
-        <v>68.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2383,19 +2383,19 @@
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>191000</v>
+        <v>140000</v>
       </c>
       <c r="G54" s="7">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H54" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7">
-        <v>5846</v>
+        <v>6125</v>
       </c>
       <c r="J54" s="5">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-08T04:14:48+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-09T04:21:13+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>西游降临：开局拜师通天教主！</t>
+  </si>
+  <si>
+    <t>直播间都在笑，国防却看沉默了</t>
+  </si>
+  <si>
     <t>点子王行动哥随便弟，三人行很刑</t>
   </si>
   <si>
-    <t>西游降临：开局拜师通天教主！</t>
-  </si>
-  <si>
     <t>觉醒：EX级法师，开局无限火力</t>
   </si>
   <si>
+    <t>大明：开局轩辕剑，朱允熥杀疯了</t>
+  </si>
+  <si>
     <t>打卡双人骑行圈，开局拿捏假名媛</t>
   </si>
   <si>
+    <t>乡村王大莽</t>
+  </si>
+  <si>
+    <t>轮回修仙：从考科举开始</t>
+  </si>
+  <si>
+    <t>变身顶美，有颜真能为所欲为</t>
+  </si>
+  <si>
     <t>身家300亿美刀，重回1988</t>
   </si>
   <si>
-    <t>轮回修仙：从考科举开始</t>
-  </si>
-  <si>
-    <t>乡村王大莽</t>
-  </si>
-  <si>
-    <t>大明：开局轩辕剑，朱允熥杀疯了</t>
+    <t>超神：成为裁决天使后，我无敌了</t>
+  </si>
+  <si>
+    <t>退游六年，剑仙老婆现实找上门了</t>
+  </si>
+  <si>
+    <t>名义：搭档沙瑞金，让育良复婚！</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离你让我陌生</t>
   </si>
   <si>
     <t>我拿钱就走，九个姐姐全变病娇了</t>
   </si>
   <si>
-    <t>退游六年，剑仙老婆现实找上门了</t>
-  </si>
-  <si>
-    <t>变身顶美，有颜真能为所欲为</t>
+    <t>同学们都选阐教，我选截教杀疯了</t>
   </si>
   <si>
     <t>女尊，独自抚养妹妹们的正太哥哥</t>
   </si>
   <si>
-    <t>直播间都在笑，国防却看沉默了</t>
+    <t>开局东宫护卫，签到满级九阳神功</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>谍战：人在军统，手下全是穿越者</t>
   </si>
   <si>
     <t>美综：谁说美剧没有人情世故？</t>
   </si>
   <si>
-    <t>啊？我是背景通天的大佬？</t>
+    <t>女鬼吸我阳气？但我是邪修啊</t>
+  </si>
+  <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
+    <t>末世：我开局拥有一艘驱逐舰</t>
+  </si>
+  <si>
+    <t>网游：我的药剂永久持续</t>
+  </si>
+  <si>
+    <t>重生1955，我刷抖音造核武</t>
   </si>
   <si>
     <t>斯坦福留洋水货？不！给我再电斯</t>
   </si>
   <si>
-    <t>冒姓琅琊</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离你让我陌生</t>
+    <t>爱情公寓：开局拿下林妙妙</t>
+  </si>
+  <si>
+    <t>诡异乱世：大乾第一巡夜人</t>
+  </si>
+  <si>
+    <t>我，酆都，在鸿钧成圣前立地府</t>
   </si>
   <si>
     <t>女儿被诈两亿，天家千金遭曝光</t>
   </si>
   <si>
+    <t>欢宋</t>
+  </si>
+  <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>星空求生：开局虫族女皇钻我被窝</t>
+  </si>
+  <si>
+    <t>就想练练功，怎么就成了大宗师？</t>
+  </si>
+  <si>
+    <t>星铁：纳努克直聘？我还是跳了吧</t>
+  </si>
+  <si>
     <t>火影：从离开木叶建立忍国开始</t>
   </si>
   <si>
-    <t>欢宋</t>
-  </si>
-  <si>
-    <t>名义：搭档沙瑞金，让育良复婚！</t>
-  </si>
-  <si>
-    <t>我，酆都，在鸿钧成圣前立地府</t>
-  </si>
-  <si>
-    <t>谍战：人在军统，手下全是穿越者</t>
-  </si>
-  <si>
-    <t>网游：我的药剂永久持续</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>星铁：纳努克直聘？我还是跳了吧</t>
-  </si>
-  <si>
-    <t>超神：成为裁决天使后，我无敌了</t>
-  </si>
-  <si>
-    <t>就想练练功，怎么就成了大宗师？</t>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>诡异：变身萝莉，诡王是我老爹？</t>
+  </si>
+  <si>
+    <t>游戏入侵：我有一块剑骨头</t>
   </si>
   <si>
     <t>要当总统了，你跟我说系统来了？</t>
   </si>
   <si>
-    <t>大唐：言出法随，都以为我是仙！</t>
-  </si>
-  <si>
-    <t>综漫：人在霓虹，开局永恒万花筒</t>
-  </si>
-  <si>
-    <t>全民恐怖求生：我觉醒加点序列！</t>
-  </si>
-  <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>重生1955，我刷抖音造核武</t>
-  </si>
-  <si>
-    <t>诡异乱世：大乾第一巡夜人</t>
-  </si>
-  <si>
-    <t>诡异：变身萝莉，诡王是我老爹？</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>网游之绝世毒尊</t>
-  </si>
-  <si>
-    <t>Fate：开局召唤喜悦闪</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>管亥托孤，我带领黄巾争霸天下</t>
-  </si>
-  <si>
-    <t>让你荒淫无道，千古一帝什么鬼？</t>
-  </si>
-  <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>不是，让我一个剑修去联姻？</t>
-  </si>
-  <si>
-    <t>游戏入侵：我有一块剑骨头</t>
+    <t>公安局长之扫黑风暴</t>
+  </si>
+  <si>
+    <t>觉醒伪神，神明弃我，我自为神</t>
+  </si>
+  <si>
+    <t>开始万倍加速空间，芶在最强宗门</t>
+  </si>
+  <si>
+    <t>名义，汉东刘长生，谁与争锋！</t>
+  </si>
+  <si>
+    <t>崩铁，死了47次，我决定去卖</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>96.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>953000</v>
+        <v>999000</v>
       </c>
       <c r="G5" s="7">
-        <v>62000</v>
+        <v>46000</v>
       </c>
       <c r="H5" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="7">
-        <v>81600</v>
+        <v>78364</v>
       </c>
       <c r="J5" s="5">
-        <v>93.7</v>
+        <v>91.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>83.8</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>384000</v>
+        <v>650000</v>
       </c>
       <c r="G6" s="7">
-        <v>67000</v>
+        <v>62000</v>
       </c>
       <c r="H6" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>86333</v>
+        <v>64500</v>
       </c>
       <c r="J6" s="5">
-        <v>88.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>84.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>588000</v>
+        <v>250000</v>
       </c>
       <c r="G7" s="7">
-        <v>52000</v>
+        <v>33000</v>
       </c>
       <c r="H7" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>65000</v>
+        <v>25167</v>
       </c>
       <c r="J7" s="5">
-        <v>80.7</v>
+        <v>81</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>89.2</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>314000</v>
+        <v>395000</v>
       </c>
       <c r="G8" s="7">
-        <v>70000</v>
+        <v>11000</v>
       </c>
       <c r="H8" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7">
-        <v>14786</v>
+        <v>67500</v>
       </c>
       <c r="J8" s="5">
-        <v>78.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>563000</v>
+        <v>362000</v>
       </c>
       <c r="G9" s="7">
-        <v>56000</v>
+        <v>48000</v>
       </c>
       <c r="H9" s="7">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I9" s="7">
-        <v>43667</v>
+        <v>17000</v>
       </c>
       <c r="J9" s="5">
-        <v>77.8</v>
+        <v>79.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>92.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>315000</v>
+        <v>138000</v>
       </c>
       <c r="G10" s="7">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="H10" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I10" s="7">
-        <v>25364</v>
+        <v>11000</v>
       </c>
       <c r="J10" s="5">
-        <v>77.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,23 +957,23 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>91.7</v>
+        <v>94.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>536000</v>
+        <v>596000</v>
       </c>
       <c r="G11" s="7">
-        <v>16000</v>
+        <v>33000</v>
       </c>
       <c r="H11" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
-        <v>27286</v>
+        <v>41000</v>
       </c>
       <c r="J11" s="5">
         <v>77.3</v>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>119000</v>
+        <v>137000</v>
       </c>
       <c r="G12" s="7">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="H12" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I12" s="7">
-        <v>8909</v>
+        <v>9667</v>
       </c>
       <c r="J12" s="5">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>97.8</v>
+        <v>90.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>114000</v>
+        <v>547000</v>
       </c>
       <c r="G13" s="7">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I13" s="7">
-        <v>9143</v>
+        <v>26200</v>
       </c>
       <c r="J13" s="5">
-        <v>76.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>93.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>238000</v>
+        <v>770000</v>
       </c>
       <c r="G14" s="7">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="H14" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>17400</v>
+        <v>44167</v>
       </c>
       <c r="J14" s="5">
-        <v>75.8</v>
+        <v>76.3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>309000</v>
+        <v>326000</v>
       </c>
       <c r="G15" s="7">
-        <v>21000</v>
+        <v>11000</v>
       </c>
       <c r="H15" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I15" s="7">
-        <v>14500</v>
+        <v>24167</v>
       </c>
       <c r="J15" s="5">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>82.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>743000</v>
+        <v>245000</v>
       </c>
       <c r="G16" s="7">
-        <v>29000</v>
+        <v>16000</v>
       </c>
       <c r="H16" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>47600</v>
+        <v>17167</v>
       </c>
       <c r="J16" s="5">
-        <v>75.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>90.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>343000</v>
+        <v>329000</v>
       </c>
       <c r="G17" s="7">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H17" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I17" s="7">
-        <v>20417</v>
+        <v>15111</v>
       </c>
       <c r="J17" s="5">
-        <v>75</v>
+        <v>75.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>92.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>217000</v>
+        <v>291000</v>
       </c>
       <c r="G18" s="7">
-        <v>19000</v>
+        <v>17000</v>
       </c>
       <c r="H18" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="7">
-        <v>23600</v>
+        <v>16333</v>
       </c>
       <c r="J18" s="5">
-        <v>75</v>
+        <v>75.5</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>276000</v>
+        <v>215000</v>
       </c>
       <c r="G19" s="7">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="H19" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>20429</v>
+        <v>18167</v>
       </c>
       <c r="J19" s="5">
-        <v>74.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>97.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>202000</v>
+        <v>254000</v>
       </c>
       <c r="G20" s="7">
-        <v>27000</v>
+        <v>16000</v>
       </c>
       <c r="H20" s="7">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I20" s="7">
-        <v>35333</v>
+        <v>17273</v>
       </c>
       <c r="J20" s="5">
-        <v>74.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>93.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>161000</v>
+        <v>441000</v>
       </c>
       <c r="G21" s="7">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I21" s="7">
-        <v>11167</v>
+        <v>14867</v>
       </c>
       <c r="J21" s="5">
-        <v>74.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>80.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>1740000</v>
+        <v>350000</v>
       </c>
       <c r="G22" s="7">
-        <v>-5000</v>
+        <v>7000</v>
       </c>
       <c r="H22" s="7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I22" s="7">
-        <v>37429</v>
+        <v>19385</v>
       </c>
       <c r="J22" s="5">
-        <v>73.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>91.5</v>
+        <v>98.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>417000</v>
+        <v>118000</v>
       </c>
       <c r="G23" s="7">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="H23" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I23" s="7">
-        <v>14214</v>
+        <v>19500</v>
       </c>
       <c r="J23" s="5">
-        <v>73.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>92.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>201000</v>
+        <v>413000</v>
       </c>
       <c r="G24" s="7">
-        <v>15000</v>
+        <v>31000</v>
       </c>
       <c r="H24" s="7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I24" s="7">
-        <v>19000</v>
+        <v>3867</v>
       </c>
       <c r="J24" s="5">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>88.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>278000</v>
+        <v>133000</v>
       </c>
       <c r="G25" s="7">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H25" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I25" s="7">
-        <v>20400</v>
+        <v>12250</v>
       </c>
       <c r="J25" s="5">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>235000</v>
+        <v>282000</v>
       </c>
       <c r="G26" s="7">
         <v>6000</v>
       </c>
       <c r="H26" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I26" s="7">
-        <v>14200</v>
+        <v>18625</v>
       </c>
       <c r="J26" s="5">
-        <v>72.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>91.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>140000</v>
+        <v>104000</v>
       </c>
       <c r="G27" s="7">
         <v>8000</v>
       </c>
       <c r="H27" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>9167</v>
+        <v>8143</v>
       </c>
       <c r="J27" s="5">
-        <v>72.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>92.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>274000</v>
+        <v>1736000</v>
       </c>
       <c r="G28" s="7">
-        <v>17000</v>
+        <v>-4000</v>
       </c>
       <c r="H28" s="7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I28" s="7">
-        <v>16200</v>
+        <v>34667</v>
       </c>
       <c r="J28" s="5">
-        <v>72.7</v>
+        <v>73.2</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>86.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>179000</v>
+        <v>104000</v>
       </c>
       <c r="G29" s="7">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" s="7">
-        <v>16833</v>
+        <v>7000</v>
       </c>
       <c r="J29" s="5">
-        <v>71.7</v>
+        <v>73</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>88.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>123000</v>
+        <v>134000</v>
       </c>
       <c r="G30" s="7">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H30" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I30" s="7">
-        <v>12571</v>
+        <v>26000</v>
       </c>
       <c r="J30" s="5">
-        <v>71.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>99.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>119000</v>
+        <v>186000</v>
       </c>
       <c r="G31" s="7">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="H31" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I31" s="7">
-        <v>31500</v>
+        <v>17800</v>
       </c>
       <c r="J31" s="5">
-        <v>71.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>83.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>510000</v>
+        <v>175000</v>
       </c>
       <c r="G32" s="7">
-        <v>29000</v>
+        <v>14000</v>
       </c>
       <c r="H32" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>22000</v>
+        <v>11571</v>
       </c>
       <c r="J32" s="5">
-        <v>71.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>89.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>195000</v>
+        <v>202000</v>
       </c>
       <c r="G33" s="7">
-        <v>11000</v>
+        <v>18000</v>
       </c>
       <c r="H33" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>8900</v>
+        <v>21750</v>
       </c>
       <c r="J33" s="5">
-        <v>71.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>88.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>229000</v>
+        <v>163000</v>
       </c>
       <c r="G34" s="7">
-        <v>13000</v>
+        <v>9000</v>
       </c>
       <c r="H34" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I34" s="7">
-        <v>17400</v>
+        <v>11571</v>
       </c>
       <c r="J34" s="5">
-        <v>71.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>87.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>126000</v>
+        <v>179000</v>
       </c>
       <c r="G35" s="7">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H35" s="7">
         <v>8</v>
       </c>
       <c r="I35" s="7">
-        <v>11143</v>
+        <v>14429</v>
       </c>
       <c r="J35" s="5">
-        <v>70.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>91</v>
+        <v>84.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>120000</v>
+        <v>273000</v>
       </c>
       <c r="G36" s="7">
-        <v>9000</v>
+        <v>-5000</v>
       </c>
       <c r="H36" s="7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I36" s="7">
-        <v>2357</v>
+        <v>18091</v>
       </c>
       <c r="J36" s="5">
-        <v>70.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>86.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>189000</v>
+        <v>144000</v>
       </c>
       <c r="G37" s="7">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H37" s="7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I37" s="7">
-        <v>11800</v>
+        <v>8769</v>
       </c>
       <c r="J37" s="5">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.2</v>
+        <v>91.8</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>216000</v>
+        <v>240000</v>
       </c>
       <c r="G38" s="7">
-        <v>3000</v>
+        <v>13000</v>
       </c>
       <c r="H38" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I38" s="7">
-        <v>9364</v>
+        <v>933</v>
       </c>
       <c r="J38" s="5">
-        <v>70.3</v>
+        <v>70.7</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>79.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>685000</v>
+        <v>1275000</v>
       </c>
       <c r="G39" s="7">
-        <v>26000</v>
+        <v>65000</v>
       </c>
       <c r="H39" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" s="7">
-        <v>25429</v>
+        <v>12600</v>
       </c>
       <c r="J39" s="5">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>254000</v>
+        <v>251000</v>
       </c>
       <c r="G40" s="7">
-        <v>-4000</v>
+        <v>-3000</v>
       </c>
       <c r="H40" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I40" s="7">
-        <v>12643</v>
+        <v>11600</v>
       </c>
       <c r="J40" s="5">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>91.5</v>
+        <v>80.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>171000</v>
+        <v>525000</v>
       </c>
       <c r="G41" s="7">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I41" s="7">
-        <v>18500</v>
+        <v>21533</v>
       </c>
       <c r="J41" s="5">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>85.5</v>
+        <v>86.8</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>154000</v>
+        <v>109000</v>
       </c>
       <c r="G42" s="7">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I42" s="7">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="J42" s="5">
-        <v>70</v>
+        <v>69.7</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>86.3</v>
+        <v>85.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>153000</v>
+        <v>127000</v>
       </c>
       <c r="G43" s="7">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="H43" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I43" s="7">
-        <v>9667</v>
+        <v>9875</v>
       </c>
       <c r="J43" s="5">
-        <v>69.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2053,19 +2053,19 @@
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>273000</v>
+        <v>200000</v>
       </c>
       <c r="G44" s="7">
-        <v>-4000</v>
+        <v>5000</v>
       </c>
       <c r="H44" s="7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I44" s="7">
-        <v>9357</v>
+        <v>8545</v>
       </c>
       <c r="J44" s="5">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>84.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>386000</v>
+        <v>230000</v>
       </c>
       <c r="G45" s="7">
-        <v>27000</v>
+        <v>-5000</v>
       </c>
       <c r="H45" s="7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I45" s="7">
-        <v>11429</v>
+        <v>12455</v>
       </c>
       <c r="J45" s="5">
-        <v>69.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>1210000</v>
+        <v>267000</v>
       </c>
       <c r="G46" s="7">
-        <v>61000</v>
+        <v>-6000</v>
       </c>
       <c r="H46" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I46" s="7">
-        <v>8857</v>
+        <v>8333</v>
       </c>
       <c r="J46" s="5">
-        <v>69.3</v>
+        <v>68.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>81.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>450000</v>
+        <v>154000</v>
       </c>
       <c r="G47" s="7">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="H47" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I47" s="7">
-        <v>18286</v>
+        <v>8429</v>
       </c>
       <c r="J47" s="5">
-        <v>69.3</v>
+        <v>68.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>84.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>186000</v>
+        <v>146000</v>
       </c>
       <c r="G48" s="7">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I48" s="7">
-        <v>10000</v>
+        <v>6111</v>
       </c>
       <c r="J48" s="5">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>87.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>382000</v>
+        <v>125000</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H49" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I49" s="7">
-        <v>1929</v>
+        <v>2533</v>
       </c>
       <c r="J49" s="5">
-        <v>68.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>86.2</v>
+        <v>84</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>116000</v>
+        <v>779000</v>
       </c>
       <c r="G50" s="7">
-        <v>2000</v>
+        <v>34000</v>
       </c>
       <c r="H50" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I50" s="7">
-        <v>5571</v>
+        <v>9200</v>
       </c>
       <c r="J50" s="5">
-        <v>68.8</v>
+        <v>68.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>77.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>572000</v>
+        <v>667000</v>
       </c>
       <c r="G51" s="7">
-        <v>-10000</v>
+        <v>38000</v>
       </c>
       <c r="H51" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I51" s="7">
-        <v>24786</v>
+        <v>18800</v>
       </c>
       <c r="J51" s="5">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>88.2</v>
+        <v>85.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>227000</v>
+        <v>106000</v>
       </c>
       <c r="G52" s="7">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H52" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I52" s="7">
-        <v>71</v>
+        <v>4200</v>
       </c>
       <c r="J52" s="5">
-        <v>68.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>84.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>152000</v>
+        <v>336000</v>
       </c>
       <c r="G53" s="7">
-        <v>-1000</v>
+        <v>18000</v>
       </c>
       <c r="H53" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I53" s="7">
-        <v>8357</v>
+        <v>12400</v>
       </c>
       <c r="J53" s="5">
-        <v>68.5</v>
+        <v>68</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>85.2</v>
+        <v>80</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>140000</v>
+        <v>308000</v>
       </c>
       <c r="G54" s="7">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I54" s="7">
-        <v>6125</v>
+        <v>16000</v>
       </c>
       <c r="J54" s="5">
-        <v>68.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-09T04:21:13+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-10T04:18:21+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>西游降临：开局拜师通天教主！</t>
   </si>
   <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>开局东宫护卫，签到满级九阳神功</t>
+  </si>
+  <si>
+    <t>乡村王大莽</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>暴富，从带五个嫂子赶海开始</t>
+  </si>
+  <si>
+    <t>死刑当天，修仙者夺舍了我</t>
+  </si>
+  <si>
+    <t>重生1955，我刷抖音造核武</t>
+  </si>
+  <si>
+    <t>轮回修仙：从考科举开始</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离你让我陌生</t>
+  </si>
+  <si>
+    <t>美综：谁说美剧没有人情世故？</t>
+  </si>
+  <si>
+    <t>退游六年，剑仙老婆现实找上门了</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>名义：搭档沙瑞金，让育良复婚！</t>
+  </si>
+  <si>
+    <t>身家300亿美刀，重回1988</t>
+  </si>
+  <si>
     <t>直播间都在笑，国防却看沉默了</t>
   </si>
   <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>觉醒：EX级法师，开局无限火力</t>
+    <t>变身顶美，有颜真能为所欲为</t>
+  </si>
+  <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
+  </si>
+  <si>
+    <t>超神：成为裁决天使后，我无敌了</t>
+  </si>
+  <si>
+    <t>爱情公寓：开局拿下林妙妙</t>
   </si>
   <si>
     <t>大明：开局轩辕剑，朱允熥杀疯了</t>
   </si>
   <si>
+    <t>天幕：分子人类学</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>谍战：人在军统，手下全是穿越者</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>诡异乱世：大乾第一巡夜人</t>
+  </si>
+  <si>
+    <t>欢宋</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>我，酆都，在鸿钧成圣前立地府</t>
+  </si>
+  <si>
+    <t>游戏入侵：我有一块剑骨头</t>
+  </si>
+  <si>
     <t>打卡双人骑行圈，开局拿捏假名媛</t>
   </si>
   <si>
-    <t>乡村王大莽</t>
-  </si>
-  <si>
-    <t>轮回修仙：从考科举开始</t>
-  </si>
-  <si>
-    <t>变身顶美，有颜真能为所欲为</t>
-  </si>
-  <si>
-    <t>身家300亿美刀，重回1988</t>
-  </si>
-  <si>
-    <t>超神：成为裁决天使后，我无敌了</t>
-  </si>
-  <si>
-    <t>退游六年，剑仙老婆现实找上门了</t>
-  </si>
-  <si>
-    <t>名义：搭档沙瑞金，让育良复婚！</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离你让我陌生</t>
-  </si>
-  <si>
-    <t>我拿钱就走，九个姐姐全变病娇了</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>序列求生：开局金刚伏魔吓哭诡异</t>
+  </si>
+  <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>网游：我的药剂永久持续</t>
+  </si>
+  <si>
+    <t>女儿被诈两亿，天家千金遭曝光</t>
+  </si>
+  <si>
+    <t>星空求生：开局虫族女皇钻我被窝</t>
   </si>
   <si>
     <t>女尊，独自抚养妹妹们的正太哥哥</t>
   </si>
   <si>
-    <t>开局东宫护卫，签到满级九阳神功</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>谍战：人在军统，手下全是穿越者</t>
-  </si>
-  <si>
-    <t>美综：谁说美剧没有人情世故？</t>
-  </si>
-  <si>
-    <t>女鬼吸我阳气？但我是邪修啊</t>
-  </si>
-  <si>
-    <t>冒姓琅琊</t>
-  </si>
-  <si>
-    <t>末世：我开局拥有一艘驱逐舰</t>
-  </si>
-  <si>
-    <t>网游：我的药剂永久持续</t>
-  </si>
-  <si>
-    <t>重生1955，我刷抖音造核武</t>
+    <t>我的第六集团军战姬</t>
   </si>
   <si>
     <t>斯坦福留洋水货？不！给我再电斯</t>
   </si>
   <si>
-    <t>爱情公寓：开局拿下林妙妙</t>
-  </si>
-  <si>
-    <t>诡异乱世：大乾第一巡夜人</t>
-  </si>
-  <si>
-    <t>我，酆都，在鸿钧成圣前立地府</t>
-  </si>
-  <si>
-    <t>女儿被诈两亿，天家千金遭曝光</t>
-  </si>
-  <si>
-    <t>欢宋</t>
-  </si>
-  <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>星空求生：开局虫族女皇钻我被窝</t>
+    <t>规则怪谈：无所谓，系统会出手</t>
   </si>
   <si>
     <t>就想练练功，怎么就成了大宗师？</t>
   </si>
   <si>
-    <t>星铁：纳努克直聘？我还是跳了吧</t>
-  </si>
-  <si>
-    <t>火影：从离开木叶建立忍国开始</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>诡异：变身萝莉，诡王是我老爹？</t>
-  </si>
-  <si>
-    <t>游戏入侵：我有一块剑骨头</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
+    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+  </si>
+  <si>
+    <t>开始万倍加速空间，芶在最强宗门</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
   </si>
   <si>
     <t>公安局长之扫黑风暴</t>
   </si>
   <si>
-    <t>觉醒伪神，神明弃我，我自为神</t>
-  </si>
-  <si>
-    <t>开始万倍加速空间，芶在最强宗门</t>
-  </si>
-  <si>
     <t>名义，汉东刘长生，谁与争锋！</t>
-  </si>
-  <si>
-    <t>崩铁，死了47次，我决定去卖</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>94.8</v>
+        <v>93.7</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>999000</v>
+        <v>1035000</v>
       </c>
       <c r="G5" s="7">
-        <v>46000</v>
+        <v>36000</v>
       </c>
       <c r="H5" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="7">
-        <v>78364</v>
+        <v>74833</v>
       </c>
       <c r="J5" s="5">
-        <v>91.7</v>
+        <v>90.2</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>83.8</v>
+        <v>84.8</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>650000</v>
+        <v>708000</v>
       </c>
       <c r="G6" s="7">
-        <v>62000</v>
+        <v>58000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>64500</v>
+        <v>63571</v>
       </c>
       <c r="J6" s="5">
-        <v>82.2</v>
+        <v>82.5</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>99.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="G7" s="7">
-        <v>33000</v>
+        <v>5000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I7" s="7">
-        <v>25167</v>
+        <v>55000</v>
       </c>
       <c r="J7" s="5">
-        <v>81</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>89.2</v>
+        <v>99.8</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>395000</v>
+        <v>136000</v>
       </c>
       <c r="G8" s="7">
-        <v>11000</v>
+        <v>18000</v>
       </c>
       <c r="H8" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>67500</v>
+        <v>19200</v>
       </c>
       <c r="J8" s="5">
-        <v>80.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>362000</v>
+        <v>168000</v>
       </c>
       <c r="G9" s="7">
-        <v>48000</v>
+        <v>31000</v>
       </c>
       <c r="H9" s="7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I9" s="7">
-        <v>17000</v>
+        <v>11308</v>
       </c>
       <c r="J9" s="5">
-        <v>79.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>138000</v>
+        <v>480000</v>
       </c>
       <c r="G10" s="7">
-        <v>24000</v>
+        <v>39000</v>
       </c>
       <c r="H10" s="7">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I10" s="7">
-        <v>11000</v>
+        <v>16375</v>
       </c>
       <c r="J10" s="5">
-        <v>77.7</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>94.7</v>
+        <v>98.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>596000</v>
+        <v>116000</v>
       </c>
       <c r="G11" s="7">
-        <v>33000</v>
+        <v>17000</v>
       </c>
       <c r="H11" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
-        <v>41000</v>
+        <v>11429</v>
       </c>
       <c r="J11" s="5">
-        <v>77.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>99</v>
+        <v>97.2</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>137000</v>
+        <v>128000</v>
       </c>
       <c r="G12" s="7">
-        <v>18000</v>
+        <v>47000</v>
       </c>
       <c r="H12" s="7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I12" s="7">
-        <v>9667</v>
+        <v>12750</v>
       </c>
       <c r="J12" s="5">
-        <v>76.90000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>90.7</v>
+        <v>93.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>547000</v>
+        <v>207000</v>
       </c>
       <c r="G13" s="7">
-        <v>11000</v>
+        <v>21000</v>
       </c>
       <c r="H13" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>26200</v>
+        <v>18333</v>
       </c>
       <c r="J13" s="5">
-        <v>76.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>82.2</v>
+        <v>90</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>770000</v>
+        <v>554000</v>
       </c>
       <c r="G14" s="7">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I14" s="7">
-        <v>44167</v>
+        <v>25000</v>
       </c>
       <c r="J14" s="5">
-        <v>76.3</v>
+        <v>75.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>91.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>326000</v>
+        <v>232000</v>
       </c>
       <c r="G15" s="7">
-        <v>11000</v>
+        <v>17000</v>
       </c>
       <c r="H15" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>24167</v>
+        <v>18000</v>
       </c>
       <c r="J15" s="5">
-        <v>76.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>93.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>245000</v>
+        <v>301000</v>
       </c>
       <c r="G16" s="7">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="H16" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I16" s="7">
-        <v>17167</v>
+        <v>18667</v>
       </c>
       <c r="J16" s="5">
-        <v>75.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>94.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>329000</v>
+        <v>345000</v>
       </c>
       <c r="G17" s="7">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="H17" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="7">
-        <v>15111</v>
+        <v>15200</v>
       </c>
       <c r="J17" s="5">
-        <v>75.5</v>
+        <v>74.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1195,19 +1195,19 @@
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>291000</v>
+        <v>267000</v>
       </c>
       <c r="G18" s="7">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="H18" s="7">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I18" s="7">
-        <v>16333</v>
+        <v>11875</v>
       </c>
       <c r="J18" s="5">
-        <v>75.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>215000</v>
+        <v>303000</v>
       </c>
       <c r="G19" s="7">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>18167</v>
+        <v>15714</v>
       </c>
       <c r="J19" s="5">
-        <v>75.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>92.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>254000</v>
+        <v>325000</v>
       </c>
       <c r="G20" s="7">
-        <v>16000</v>
+        <v>-1000</v>
       </c>
       <c r="H20" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I20" s="7">
-        <v>17273</v>
+        <v>22231</v>
       </c>
       <c r="J20" s="5">
-        <v>75</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>93.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>441000</v>
+        <v>256000</v>
       </c>
       <c r="G21" s="7">
-        <v>24000</v>
+        <v>6000</v>
       </c>
       <c r="H21" s="7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>14867</v>
+        <v>22429</v>
       </c>
       <c r="J21" s="5">
-        <v>74.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>89.8</v>
+        <v>78.7</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>350000</v>
+        <v>771000</v>
       </c>
       <c r="G22" s="7">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="H22" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>19385</v>
+        <v>38000</v>
       </c>
       <c r="J22" s="5">
-        <v>74.2</v>
+        <v>72.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>98.7</v>
+        <v>81</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>118000</v>
+        <v>1733000</v>
       </c>
       <c r="G23" s="7">
-        <v>19000</v>
+        <v>-3000</v>
       </c>
       <c r="H23" s="7">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I23" s="7">
-        <v>19500</v>
+        <v>32312</v>
       </c>
       <c r="J23" s="5">
-        <v>74.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>96.2</v>
+        <v>87</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>413000</v>
+        <v>258000</v>
       </c>
       <c r="G24" s="7">
-        <v>31000</v>
+        <v>4000</v>
       </c>
       <c r="H24" s="7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I24" s="7">
-        <v>3867</v>
+        <v>16167</v>
       </c>
       <c r="J24" s="5">
-        <v>73.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>92.09999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>133000</v>
+        <v>246000</v>
       </c>
       <c r="G25" s="7">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H25" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>12250</v>
+        <v>14857</v>
       </c>
       <c r="J25" s="5">
-        <v>73.7</v>
+        <v>71.8</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>282000</v>
+        <v>213000</v>
       </c>
       <c r="G26" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H26" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
-        <v>18625</v>
+        <v>19600</v>
       </c>
       <c r="J26" s="5">
-        <v>73.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>93.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>104000</v>
+        <v>145000</v>
       </c>
       <c r="G27" s="7">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="H27" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>8143</v>
+        <v>10556</v>
       </c>
       <c r="J27" s="5">
-        <v>73.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>1736000</v>
+        <v>100000</v>
       </c>
       <c r="G28" s="7">
-        <v>-4000</v>
+        <v>7000</v>
       </c>
       <c r="H28" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>34667</v>
+        <v>8167</v>
       </c>
       <c r="J28" s="5">
-        <v>73.2</v>
+        <v>71.5</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>93.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>104000</v>
+        <v>152000</v>
       </c>
       <c r="G29" s="7">
-        <v>12000</v>
+        <v>7000</v>
       </c>
       <c r="H29" s="7">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I29" s="7">
-        <v>7000</v>
+        <v>5062</v>
       </c>
       <c r="J29" s="5">
-        <v>73</v>
+        <v>71.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>97.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>134000</v>
+        <v>138000</v>
       </c>
       <c r="G30" s="7">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="H30" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I30" s="7">
-        <v>26000</v>
+        <v>11444</v>
       </c>
       <c r="J30" s="5">
-        <v>72.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>90.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>186000</v>
+        <v>1338000</v>
       </c>
       <c r="G31" s="7">
-        <v>15000</v>
+        <v>63000</v>
       </c>
       <c r="H31" s="7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I31" s="7">
-        <v>17800</v>
+        <v>15750</v>
       </c>
       <c r="J31" s="5">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>89.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>175000</v>
+        <v>171000</v>
       </c>
       <c r="G32" s="7">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="H32" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I32" s="7">
-        <v>11571</v>
+        <v>11125</v>
       </c>
       <c r="J32" s="5">
-        <v>71.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>93</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>202000</v>
+        <v>148000</v>
       </c>
       <c r="G33" s="7">
-        <v>18000</v>
+        <v>4000</v>
       </c>
       <c r="H33" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I33" s="7">
-        <v>21750</v>
+        <v>8429</v>
       </c>
       <c r="J33" s="5">
-        <v>71.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>88.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>163000</v>
+        <v>421000</v>
       </c>
       <c r="G34" s="7">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="H34" s="7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I34" s="7">
-        <v>11571</v>
+        <v>4125</v>
       </c>
       <c r="J34" s="5">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>86.3</v>
+        <v>91.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>179000</v>
+        <v>284000</v>
       </c>
       <c r="G35" s="7">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="H35" s="7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I35" s="7">
-        <v>14429</v>
+        <v>1562</v>
       </c>
       <c r="J35" s="5">
-        <v>71.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>84.5</v>
+        <v>86.3</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>273000</v>
+        <v>179000</v>
       </c>
       <c r="G36" s="7">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="H36" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I36" s="7">
-        <v>18091</v>
+        <v>12625</v>
       </c>
       <c r="J36" s="5">
-        <v>71</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>144000</v>
+        <v>154000</v>
       </c>
       <c r="G37" s="7">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="H37" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I37" s="7">
-        <v>8769</v>
+        <v>6300</v>
       </c>
       <c r="J37" s="5">
-        <v>70.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>91.8</v>
+        <v>83.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>240000</v>
+        <v>558000</v>
       </c>
       <c r="G38" s="7">
-        <v>13000</v>
+        <v>-38000</v>
       </c>
       <c r="H38" s="7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>933</v>
+        <v>25200</v>
       </c>
       <c r="J38" s="5">
-        <v>70.7</v>
+        <v>70.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>85.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>1275000</v>
+        <v>544000</v>
       </c>
       <c r="G39" s="7">
-        <v>65000</v>
+        <v>19000</v>
       </c>
       <c r="H39" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" s="7">
-        <v>12600</v>
+        <v>21375</v>
       </c>
       <c r="J39" s="5">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>85.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>251000</v>
+        <v>112000</v>
       </c>
       <c r="G40" s="7">
-        <v>-3000</v>
+        <v>10000</v>
       </c>
       <c r="H40" s="7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>11600</v>
+        <v>10000</v>
       </c>
       <c r="J40" s="5">
         <v>70.09999999999999</v>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>80.7</v>
+        <v>90.3</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>525000</v>
+        <v>250000</v>
       </c>
       <c r="G41" s="7">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="H41" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" s="7">
-        <v>21533</v>
+        <v>1500</v>
       </c>
       <c r="J41" s="5">
-        <v>69.8</v>
+        <v>70</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>86.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>109000</v>
+        <v>141000</v>
       </c>
       <c r="G42" s="7">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H42" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I42" s="7">
-        <v>16000</v>
+        <v>21250</v>
       </c>
       <c r="J42" s="5">
-        <v>69.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85.5</v>
+        <v>83</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>127000</v>
+        <v>264000</v>
       </c>
       <c r="G43" s="7">
-        <v>1000</v>
+        <v>-9000</v>
       </c>
       <c r="H43" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I43" s="7">
-        <v>9875</v>
+        <v>15833</v>
       </c>
       <c r="J43" s="5">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>85.7</v>
+        <v>83.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>200000</v>
+        <v>112000</v>
       </c>
       <c r="G44" s="7">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H44" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I44" s="7">
-        <v>8545</v>
+        <v>13833</v>
       </c>
       <c r="J44" s="5">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>83.8</v>
+        <v>82.5</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>230000</v>
+        <v>323000</v>
       </c>
       <c r="G45" s="7">
-        <v>-5000</v>
+        <v>-27000</v>
       </c>
       <c r="H45" s="7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I45" s="7">
-        <v>12455</v>
+        <v>16071</v>
       </c>
       <c r="J45" s="5">
-        <v>69.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>84.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>267000</v>
+        <v>122000</v>
       </c>
       <c r="G46" s="7">
-        <v>-6000</v>
+        <v>14000</v>
       </c>
       <c r="H46" s="7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I46" s="7">
-        <v>8333</v>
+        <v>8667</v>
       </c>
       <c r="J46" s="5">
-        <v>68.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>84.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>154000</v>
+        <v>182000</v>
       </c>
       <c r="G47" s="7">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H47" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>8429</v>
+        <v>11000</v>
       </c>
       <c r="J47" s="5">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>85.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>146000</v>
+        <v>1070000</v>
       </c>
       <c r="G48" s="7">
-        <v>6000</v>
+        <v>70000</v>
       </c>
       <c r="H48" s="7">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I48" s="7">
-        <v>6111</v>
+        <v>8000</v>
       </c>
       <c r="J48" s="5">
-        <v>68.8</v>
+        <v>69</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>87.2</v>
+        <v>84.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>125000</v>
+        <v>127000</v>
       </c>
       <c r="G49" s="7">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I49" s="7">
-        <v>2533</v>
+        <v>8778</v>
       </c>
       <c r="J49" s="5">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>84</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>779000</v>
+        <v>349000</v>
       </c>
       <c r="G50" s="7">
-        <v>34000</v>
+        <v>28000</v>
       </c>
       <c r="H50" s="7">
         <v>16</v>
       </c>
       <c r="I50" s="7">
-        <v>9200</v>
+        <v>11800</v>
       </c>
       <c r="J50" s="5">
-        <v>68.5</v>
+        <v>68.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>79.3</v>
+        <v>86.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>667000</v>
+        <v>110000</v>
       </c>
       <c r="G51" s="7">
-        <v>38000</v>
+        <v>4000</v>
       </c>
       <c r="H51" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I51" s="7">
-        <v>18800</v>
+        <v>4188</v>
       </c>
       <c r="J51" s="5">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>85.5</v>
+        <v>85.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>106000</v>
+        <v>152000</v>
       </c>
       <c r="G52" s="7">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="H52" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I52" s="7">
-        <v>4200</v>
+        <v>5312</v>
       </c>
       <c r="J52" s="5">
-        <v>68.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>81.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>336000</v>
+        <v>805000</v>
       </c>
       <c r="G53" s="7">
-        <v>18000</v>
+        <v>26000</v>
       </c>
       <c r="H53" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I53" s="7">
-        <v>12400</v>
+        <v>10250</v>
       </c>
       <c r="J53" s="5">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>80</v>
+        <v>81.7</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>308000</v>
+        <v>355000</v>
       </c>
       <c r="G54" s="7">
-        <v>10000</v>
+        <v>19000</v>
       </c>
       <c r="H54" s="7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I54" s="7">
-        <v>16000</v>
+        <v>12812</v>
       </c>
       <c r="J54" s="5">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-10T04:18:21+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-11T04:17:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>西游降临：开局拜师通天教主！</t>
   </si>
   <si>
+    <t>开局东宫护卫，签到满级九阳神功</t>
+  </si>
+  <si>
     <t>点子王行动哥随便弟，三人行很刑</t>
   </si>
   <si>
-    <t>开局东宫护卫，签到满级九阳神功</t>
-  </si>
-  <si>
     <t>乡村王大莽</t>
   </si>
   <si>
+    <t>死刑当天，修仙者夺舍了我</t>
+  </si>
+  <si>
+    <t>我一写网文的，你让我混娱乐圈？</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离你让我陌生</t>
+  </si>
+  <si>
+    <t>重生1955，我刷抖音造核武</t>
+  </si>
+  <si>
+    <t>美综：谁说美剧没有人情世故？</t>
+  </si>
+  <si>
+    <t>爱情公寓：开局拿下林妙妙</t>
+  </si>
+  <si>
+    <t>暴富，从带五个嫂子赶海开始</t>
+  </si>
+  <si>
+    <t>名义：搭档沙瑞金，让育良复婚！</t>
+  </si>
+  <si>
+    <t>序列求生：开局金刚伏魔吓哭诡异</t>
+  </si>
+  <si>
+    <t>身家300亿美刀，重回1988</t>
+  </si>
+  <si>
+    <t>变身顶美，有颜真能为所欲为</t>
+  </si>
+  <si>
     <t>同学们都选阐教，我选截教杀疯了</t>
   </si>
   <si>
-    <t>暴富，从带五个嫂子赶海开始</t>
-  </si>
-  <si>
-    <t>死刑当天，修仙者夺舍了我</t>
-  </si>
-  <si>
-    <t>重生1955，我刷抖音造核武</t>
-  </si>
-  <si>
-    <t>轮回修仙：从考科举开始</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离你让我陌生</t>
-  </si>
-  <si>
-    <t>美综：谁说美剧没有人情世故？</t>
+    <t>冒姓琅琊</t>
   </si>
   <si>
     <t>退游六年，剑仙老婆现实找上门了</t>
   </si>
   <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>诡异乱世：大乾第一巡夜人</t>
+  </si>
+  <si>
+    <t>天幕：分子人类学</t>
+  </si>
+  <si>
+    <t>谍战：人在军统，手下全是穿越者</t>
+  </si>
+  <si>
+    <t>超神：成为裁决天使后，我无敌了</t>
+  </si>
+  <si>
+    <t>斩神：我有万界杀招系统</t>
+  </si>
+  <si>
+    <t>欢宋</t>
+  </si>
+  <si>
+    <t>我，酆都，在鸿钧成圣前立地府</t>
+  </si>
+  <si>
+    <t>网游：我的药剂永久持续</t>
+  </si>
+  <si>
+    <t>青梅是天命之女？可我既是天命！</t>
+  </si>
+  <si>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
+  </si>
+  <si>
+    <t>高武：看不起斩魄刀，流刃若火呢</t>
+  </si>
+  <si>
+    <t>楼层求生：从垃圾场开始变废为宝</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>大明：开局轩辕剑，朱允熥杀疯了</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>名义，汉东刘长生，谁与争锋！</t>
+  </si>
+  <si>
+    <t>女儿被诈两亿，天家千金遭曝光</t>
+  </si>
+  <si>
+    <t>婴儿开局，我的娘亲是画皮</t>
+  </si>
+  <si>
+    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
+  </si>
+  <si>
+    <t>女尊，独自抚养妹妹们的正太哥哥</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>游戏入侵：我有一块剑骨头</t>
+  </si>
+  <si>
     <t>穿越成国公，咋就是封建余孽了？</t>
   </si>
   <si>
-    <t>名义：搭档沙瑞金，让育良复婚！</t>
-  </si>
-  <si>
-    <t>身家300亿美刀，重回1988</t>
-  </si>
-  <si>
-    <t>直播间都在笑，国防却看沉默了</t>
-  </si>
-  <si>
-    <t>变身顶美，有颜真能为所欲为</t>
-  </si>
-  <si>
-    <t>冒姓琅琊</t>
-  </si>
-  <si>
-    <t>我拿钱就走，九个姐姐全变病娇了</t>
-  </si>
-  <si>
-    <t>超神：成为裁决天使后，我无敌了</t>
-  </si>
-  <si>
-    <t>爱情公寓：开局拿下林妙妙</t>
-  </si>
-  <si>
-    <t>大明：开局轩辕剑，朱允熥杀疯了</t>
-  </si>
-  <si>
-    <t>天幕：分子人类学</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>谍战：人在军统，手下全是穿越者</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>诡异乱世：大乾第一巡夜人</t>
-  </si>
-  <si>
-    <t>欢宋</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>我，酆都，在鸿钧成圣前立地府</t>
-  </si>
-  <si>
-    <t>游戏入侵：我有一块剑骨头</t>
-  </si>
-  <si>
-    <t>打卡双人骑行圈，开局拿捏假名媛</t>
+    <t>天渊</t>
+  </si>
+  <si>
+    <t>灵气复苏：别装了，华夏真有仙！</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
+    <t>开始万倍加速空间，芶在最强宗门</t>
+  </si>
+  <si>
+    <t>斯坦福留洋水货？不！给我再电斯</t>
   </si>
   <si>
     <t>四合院：从亮剑到人民的名义</t>
   </si>
   <si>
-    <t>序列求生：开局金刚伏魔吓哭诡异</t>
-  </si>
-  <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>网游：我的药剂永久持续</t>
-  </si>
-  <si>
-    <t>女儿被诈两亿，天家千金遭曝光</t>
-  </si>
-  <si>
     <t>星空求生：开局虫族女皇钻我被窝</t>
-  </si>
-  <si>
-    <t>女尊，独自抚养妹妹们的正太哥哥</t>
-  </si>
-  <si>
-    <t>我的第六集团军战姬</t>
-  </si>
-  <si>
-    <t>斯坦福留洋水货？不！给我再电斯</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>就想练练功，怎么就成了大宗师？</t>
-  </si>
-  <si>
-    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
-  </si>
-  <si>
-    <t>开始万倍加速空间，芶在最强宗门</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>公安局长之扫黑风暴</t>
-  </si>
-  <si>
-    <t>名义，汉东刘长生，谁与争锋！</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>93.7</v>
+        <v>93.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1035000</v>
+        <v>1067000</v>
       </c>
       <c r="G5" s="7">
-        <v>36000</v>
+        <v>32000</v>
       </c>
       <c r="H5" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="7">
-        <v>74833</v>
+        <v>71538</v>
       </c>
       <c r="J5" s="5">
-        <v>90.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>84.8</v>
+        <v>83.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>708000</v>
+        <v>756000</v>
       </c>
       <c r="G6" s="7">
-        <v>58000</v>
+        <v>48000</v>
       </c>
       <c r="H6" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="7">
-        <v>63571</v>
+        <v>61625</v>
       </c>
       <c r="J6" s="5">
-        <v>82.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,23 +825,23 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>87.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>400000</v>
+        <v>157000</v>
       </c>
       <c r="G7" s="7">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="H7" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>55000</v>
+        <v>19500</v>
       </c>
       <c r="J7" s="5">
         <v>79.90000000000001</v>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99.8</v>
+        <v>87.7</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>136000</v>
+        <v>402000</v>
       </c>
       <c r="G8" s="7">
-        <v>18000</v>
+        <v>2000</v>
       </c>
       <c r="H8" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>19200</v>
+        <v>46167</v>
       </c>
       <c r="J8" s="5">
-        <v>77.7</v>
+        <v>79.8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>168000</v>
+        <v>219000</v>
       </c>
       <c r="G9" s="7">
-        <v>31000</v>
+        <v>51000</v>
       </c>
       <c r="H9" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" s="7">
-        <v>11308</v>
+        <v>14143</v>
       </c>
       <c r="J9" s="5">
-        <v>77.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>96.40000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>480000</v>
+        <v>162000</v>
       </c>
       <c r="G10" s="7">
-        <v>39000</v>
+        <v>34000</v>
       </c>
       <c r="H10" s="7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>16375</v>
+        <v>15111</v>
       </c>
       <c r="J10" s="5">
-        <v>77.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>98.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>116000</v>
+        <v>616000</v>
       </c>
       <c r="G11" s="7">
-        <v>17000</v>
+        <v>71000</v>
       </c>
       <c r="H11" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I11" s="7">
-        <v>11429</v>
+        <v>79500</v>
       </c>
       <c r="J11" s="5">
-        <v>77.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>97.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>128000</v>
+        <v>253000</v>
       </c>
       <c r="G12" s="7">
-        <v>47000</v>
+        <v>21000</v>
       </c>
       <c r="H12" s="7">
         <v>9</v>
       </c>
       <c r="I12" s="7">
-        <v>12750</v>
+        <v>18375</v>
       </c>
       <c r="J12" s="5">
-        <v>76.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>93.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>207000</v>
+        <v>227000</v>
       </c>
       <c r="G13" s="7">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>18333</v>
+        <v>18571</v>
       </c>
       <c r="J13" s="5">
-        <v>76.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>554000</v>
+        <v>316000</v>
       </c>
       <c r="G14" s="7">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H14" s="7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
-        <v>25000</v>
+        <v>18300</v>
       </c>
       <c r="J14" s="5">
-        <v>75.8</v>
+        <v>75.5</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>232000</v>
+        <v>226000</v>
       </c>
       <c r="G15" s="7">
-        <v>17000</v>
+        <v>13000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>18000</v>
+        <v>18500</v>
       </c>
       <c r="J15" s="5">
-        <v>75.7</v>
+        <v>74.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1129,19 +1129,19 @@
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>301000</v>
+        <v>126000</v>
       </c>
       <c r="G16" s="7">
-        <v>19000</v>
+        <v>10000</v>
       </c>
       <c r="H16" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>18667</v>
+        <v>11250</v>
       </c>
       <c r="J16" s="5">
-        <v>75.5</v>
+        <v>73.7</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>345000</v>
+        <v>313000</v>
       </c>
       <c r="G17" s="7">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="H17" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7">
-        <v>15200</v>
+        <v>15000</v>
       </c>
       <c r="J17" s="5">
-        <v>74.7</v>
+        <v>73.2</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>93.5</v>
+        <v>92</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>267000</v>
+        <v>124000</v>
       </c>
       <c r="G18" s="7">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="H18" s="7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I18" s="7">
-        <v>11875</v>
+        <v>10333</v>
       </c>
       <c r="J18" s="5">
-        <v>74.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>91.5</v>
+        <v>86.3</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>303000</v>
+        <v>321000</v>
       </c>
       <c r="G19" s="7">
-        <v>12000</v>
+        <v>-4000</v>
       </c>
       <c r="H19" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I19" s="7">
-        <v>15714</v>
+        <v>20357</v>
       </c>
       <c r="J19" s="5">
-        <v>74.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>87.3</v>
+        <v>79.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>325000</v>
+        <v>778000</v>
       </c>
       <c r="G20" s="7">
-        <v>-1000</v>
+        <v>7000</v>
       </c>
       <c r="H20" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>22231</v>
+        <v>34125</v>
       </c>
       <c r="J20" s="5">
-        <v>73.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>86.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>256000</v>
+        <v>479000</v>
       </c>
       <c r="G21" s="7">
-        <v>6000</v>
+        <v>-1000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I21" s="7">
-        <v>22429</v>
+        <v>15353</v>
       </c>
       <c r="J21" s="5">
-        <v>73</v>
+        <v>72.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>78.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>771000</v>
+        <v>1732000</v>
       </c>
       <c r="G22" s="7">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I22" s="7">
-        <v>38000</v>
+        <v>30353</v>
       </c>
       <c r="J22" s="5">
-        <v>72.8</v>
+        <v>72.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>81</v>
+        <v>88.3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>1733000</v>
+        <v>347000</v>
       </c>
       <c r="G23" s="7">
-        <v>-3000</v>
+        <v>2000</v>
       </c>
       <c r="H23" s="7">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I23" s="7">
-        <v>32312</v>
+        <v>14000</v>
       </c>
       <c r="J23" s="5">
-        <v>72.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>87</v>
+        <v>88.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>258000</v>
+        <v>1173000</v>
       </c>
       <c r="G24" s="7">
-        <v>4000</v>
+        <v>103000</v>
       </c>
       <c r="H24" s="7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I24" s="7">
-        <v>16167</v>
+        <v>13588</v>
       </c>
       <c r="J24" s="5">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>87.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>246000</v>
+        <v>178000</v>
       </c>
       <c r="G25" s="7">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I25" s="7">
-        <v>14857</v>
+        <v>10667</v>
       </c>
       <c r="J25" s="5">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>88.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>213000</v>
+        <v>107000</v>
       </c>
       <c r="G26" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H26" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>19600</v>
+        <v>8000</v>
       </c>
       <c r="J26" s="5">
-        <v>71.7</v>
+        <v>71.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>89.2</v>
+        <v>87.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>145000</v>
+        <v>142000</v>
       </c>
       <c r="G27" s="7">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="H27" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="7">
-        <v>10556</v>
+        <v>10700</v>
       </c>
       <c r="J27" s="5">
-        <v>71.7</v>
+        <v>71</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>90</v>
+        <v>86.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>100000</v>
+        <v>247000</v>
       </c>
       <c r="G28" s="7">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I28" s="7">
-        <v>8167</v>
+        <v>13125</v>
       </c>
       <c r="J28" s="5">
-        <v>71.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90.7</v>
+        <v>86.8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>152000</v>
+        <v>195000</v>
       </c>
       <c r="G29" s="7">
         <v>7000</v>
       </c>
       <c r="H29" s="7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>5062</v>
+        <v>12833</v>
       </c>
       <c r="J29" s="5">
-        <v>71.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>87.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>138000</v>
+        <v>152000</v>
       </c>
       <c r="G30" s="7">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H30" s="7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I30" s="7">
-        <v>11444</v>
+        <v>8133</v>
       </c>
       <c r="J30" s="5">
-        <v>71.2</v>
+        <v>70.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>85.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>1338000</v>
+        <v>179000</v>
       </c>
       <c r="G31" s="7">
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="H31" s="7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I31" s="7">
-        <v>15750</v>
+        <v>11222</v>
       </c>
       <c r="J31" s="5">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>87.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>171000</v>
+        <v>144000</v>
       </c>
       <c r="G32" s="7">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="H32" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>11125</v>
+        <v>17600</v>
       </c>
       <c r="J32" s="5">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1681,28 +1681,30 @@
       <c r="A33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="5"/>
+      <c r="B33" s="5">
+        <v>9</v>
+      </c>
       <c r="C33" s="5">
-        <v>88.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>148000</v>
+        <v>137000</v>
       </c>
       <c r="G33" s="7">
-        <v>4000</v>
+        <v>15000</v>
       </c>
       <c r="H33" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>8429</v>
+        <v>14750</v>
       </c>
       <c r="J33" s="5">
-        <v>70.8</v>
+        <v>70.3</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>90.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>421000</v>
+        <v>255000</v>
       </c>
       <c r="G34" s="7">
-        <v>8000</v>
+        <v>-3000</v>
       </c>
       <c r="H34" s="7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I34" s="7">
-        <v>4125</v>
+        <v>14692</v>
       </c>
       <c r="J34" s="5">
-        <v>70.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>91.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>284000</v>
+        <v>248000</v>
       </c>
       <c r="G35" s="7">
-        <v>13000</v>
+        <v>6000</v>
       </c>
       <c r="H35" s="7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>1562</v>
+        <v>12600</v>
       </c>
       <c r="J35" s="5">
-        <v>70.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.3</v>
+        <v>89.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>179000</v>
+        <v>108000</v>
       </c>
       <c r="G36" s="7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H36" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>12625</v>
+        <v>9800</v>
       </c>
       <c r="J36" s="5">
-        <v>70.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>154000</v>
+        <v>292000</v>
       </c>
       <c r="G37" s="7">
         <v>8000</v>
       </c>
       <c r="H37" s="7">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I37" s="7">
-        <v>6300</v>
+        <v>1941</v>
       </c>
       <c r="J37" s="5">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>83.7</v>
+        <v>85.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>558000</v>
+        <v>147000</v>
       </c>
       <c r="G38" s="7">
-        <v>-38000</v>
+        <v>2000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I38" s="7">
-        <v>25200</v>
+        <v>9700</v>
       </c>
       <c r="J38" s="5">
-        <v>70.3</v>
+        <v>69.5</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>81.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>544000</v>
+        <v>1361000</v>
       </c>
       <c r="G39" s="7">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="H39" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39" s="7">
-        <v>21375</v>
+        <v>16176</v>
       </c>
       <c r="J39" s="5">
-        <v>70.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>90.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>112000</v>
+        <v>379000</v>
       </c>
       <c r="G40" s="7">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="H40" s="7">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I40" s="7">
-        <v>10000</v>
+        <v>13471</v>
       </c>
       <c r="J40" s="5">
-        <v>70.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>90.3</v>
+        <v>82.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>250000</v>
+        <v>255000</v>
       </c>
       <c r="G41" s="7">
-        <v>10000</v>
+        <v>-9000</v>
       </c>
       <c r="H41" s="7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I41" s="7">
-        <v>1500</v>
+        <v>13923</v>
       </c>
       <c r="J41" s="5">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>90.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>141000</v>
+        <v>121000</v>
       </c>
       <c r="G42" s="7">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="H42" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I42" s="7">
-        <v>21250</v>
+        <v>8400</v>
       </c>
       <c r="J42" s="5">
-        <v>69.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>264000</v>
+        <v>373000</v>
       </c>
       <c r="G43" s="7">
-        <v>-9000</v>
+        <v>24000</v>
       </c>
       <c r="H43" s="7">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I43" s="7">
-        <v>15833</v>
+        <v>12562</v>
       </c>
       <c r="J43" s="5">
-        <v>69.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>83.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>112000</v>
+        <v>301000</v>
       </c>
       <c r="G44" s="7">
-        <v>3000</v>
+        <v>-22000</v>
       </c>
       <c r="H44" s="7">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I44" s="7">
-        <v>13833</v>
+        <v>13533</v>
       </c>
       <c r="J44" s="5">
-        <v>69.5</v>
+        <v>68.7</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>82.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>323000</v>
+        <v>156000</v>
       </c>
       <c r="G45" s="7">
-        <v>-27000</v>
+        <v>4000</v>
       </c>
       <c r="H45" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I45" s="7">
-        <v>16071</v>
+        <v>5235</v>
       </c>
       <c r="J45" s="5">
-        <v>69.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>122000</v>
+        <v>156000</v>
       </c>
       <c r="G46" s="7">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="H46" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I46" s="7">
-        <v>8667</v>
+        <v>5909</v>
       </c>
       <c r="J46" s="5">
-        <v>69.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>84.5</v>
+        <v>83.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>182000</v>
+        <v>257000</v>
       </c>
       <c r="G47" s="7">
-        <v>7000</v>
+        <v>-10000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I47" s="7">
-        <v>11000</v>
+        <v>10588</v>
       </c>
       <c r="J47" s="5">
-        <v>69.2</v>
+        <v>68.5</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>85.5</v>
+        <v>82.3</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>1070000</v>
+        <v>1132000</v>
       </c>
       <c r="G48" s="7">
-        <v>70000</v>
+        <v>23000</v>
       </c>
       <c r="H48" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I48" s="7">
-        <v>8000</v>
+        <v>12118</v>
       </c>
       <c r="J48" s="5">
-        <v>69</v>
+        <v>68.3</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>84.7</v>
+        <v>85</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>127000</v>
+        <v>249000</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="H49" s="7">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I49" s="7">
-        <v>8778</v>
+        <v>6294</v>
       </c>
       <c r="J49" s="5">
-        <v>68.8</v>
+        <v>68.3</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>83.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>349000</v>
+        <v>440000</v>
       </c>
       <c r="G50" s="7">
-        <v>28000</v>
+        <v>19000</v>
       </c>
       <c r="H50" s="7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I50" s="7">
-        <v>11800</v>
+        <v>12588</v>
       </c>
       <c r="J50" s="5">
-        <v>68.7</v>
+        <v>68.2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86.5</v>
+        <v>85.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>110000</v>
+        <v>113000</v>
       </c>
       <c r="G51" s="7">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="H51" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I51" s="7">
-        <v>4188</v>
+        <v>4118</v>
       </c>
       <c r="J51" s="5">
-        <v>68.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>85.7</v>
+        <v>82.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>152000</v>
+        <v>183000</v>
       </c>
       <c r="G52" s="7">
         <v>1000</v>
       </c>
       <c r="H52" s="7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I52" s="7">
-        <v>5312</v>
+        <v>9889</v>
       </c>
       <c r="J52" s="5">
-        <v>68.5</v>
+        <v>68</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>82.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>805000</v>
+        <v>541000</v>
       </c>
       <c r="G53" s="7">
-        <v>26000</v>
+        <v>-3000</v>
       </c>
       <c r="H53" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I53" s="7">
-        <v>10250</v>
+        <v>19941</v>
       </c>
       <c r="J53" s="5">
-        <v>68.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>81.7</v>
+        <v>81.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>355000</v>
+        <v>113000</v>
       </c>
       <c r="G54" s="7">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="H54" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I54" s="7">
-        <v>12812</v>
+        <v>12000</v>
       </c>
       <c r="J54" s="5">
-        <v>68.09999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-11T04:17:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-12T04:16:44+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>我一写网文的，你让我混娱乐圈？</t>
+  </si>
+  <si>
+    <t>开局东宫护卫，签到满级九阳神功</t>
+  </si>
+  <si>
     <t>西游降临：开局拜师通天教主！</t>
   </si>
   <si>
-    <t>开局东宫护卫，签到满级九阳神功</t>
-  </si>
-  <si>
     <t>点子王行动哥随便弟，三人行很刑</t>
   </si>
   <si>
+    <t>天幕通原神，开局钟离你让我陌生</t>
+  </si>
+  <si>
+    <t>网游：我的药剂永久持续</t>
+  </si>
+  <si>
+    <t>婴儿开局，我的娘亲是画皮</t>
+  </si>
+  <si>
+    <t>美综：谁说美剧没有人情世故？</t>
+  </si>
+  <si>
     <t>乡村王大莽</t>
   </si>
   <si>
+    <t>暴富，从带五个嫂子赶海开始</t>
+  </si>
+  <si>
+    <t>青梅是天命之女？可我既是天命！</t>
+  </si>
+  <si>
+    <t>爱情公寓：开局拿下林妙妙</t>
+  </si>
+  <si>
+    <t>冒姓琅琊</t>
+  </si>
+  <si>
+    <t>重生1955，我刷抖音造核武</t>
+  </si>
+  <si>
+    <t>名义：搭档沙瑞金，让育良复婚！</t>
+  </si>
+  <si>
+    <t>谍战：人在军统，手下全是穿越者</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>身家300亿美刀，重回1988</t>
+  </si>
+  <si>
+    <t>超神：成为裁决天使后，我无敌了</t>
+  </si>
+  <si>
+    <t>楼层求生：从垃圾场开始变废为宝</t>
+  </si>
+  <si>
+    <t>高武：看不起斩魄刀，流刃若火呢</t>
+  </si>
+  <si>
     <t>死刑当天，修仙者夺舍了我</t>
   </si>
   <si>
-    <t>我一写网文的，你让我混娱乐圈？</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离你让我陌生</t>
-  </si>
-  <si>
-    <t>重生1955，我刷抖音造核武</t>
-  </si>
-  <si>
-    <t>美综：谁说美剧没有人情世故？</t>
-  </si>
-  <si>
-    <t>爱情公寓：开局拿下林妙妙</t>
-  </si>
-  <si>
-    <t>暴富，从带五个嫂子赶海开始</t>
-  </si>
-  <si>
-    <t>名义：搭档沙瑞金，让育良复婚！</t>
+    <t>斩神：我有万界杀招系统</t>
+  </si>
+  <si>
+    <t>亮剑：独立团军工之父，横扫晋地</t>
+  </si>
+  <si>
+    <t>无声1937</t>
+  </si>
+  <si>
+    <t>我，酆都，在鸿钧成圣前立地府</t>
+  </si>
+  <si>
+    <t>天幕：分子人类学</t>
+  </si>
+  <si>
+    <t>短综世界，混乱而有趣的世界</t>
+  </si>
+  <si>
+    <t>诡异乱世：大乾第一巡夜人</t>
   </si>
   <si>
     <t>序列求生：开局金刚伏魔吓哭诡异</t>
   </si>
   <si>
-    <t>身家300亿美刀，重回1988</t>
-  </si>
-  <si>
-    <t>变身顶美，有颜真能为所欲为</t>
+    <t>我拿钱就走，九个姐姐全变病娇了</t>
   </si>
   <si>
     <t>同学们都选阐教，我选截教杀疯了</t>
   </si>
   <si>
-    <t>冒姓琅琊</t>
+    <t>名义，汉东刘长生，谁与争锋！</t>
+  </si>
+  <si>
+    <t>战锤40K：俺寻思俺是原体</t>
+  </si>
+  <si>
+    <t>县城：女友出国要我卖房，给脸了</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>天渊</t>
+  </si>
+  <si>
+    <t>双修就变强，开局被黑丝校花缠上</t>
   </si>
   <si>
     <t>退游六年，剑仙老婆现实找上门了</t>
   </si>
   <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>诡异乱世：大乾第一巡夜人</t>
-  </si>
-  <si>
-    <t>天幕：分子人类学</t>
-  </si>
-  <si>
-    <t>谍战：人在军统，手下全是穿越者</t>
-  </si>
-  <si>
-    <t>超神：成为裁决天使后，我无敌了</t>
-  </si>
-  <si>
-    <t>斩神：我有万界杀招系统</t>
-  </si>
-  <si>
-    <t>欢宋</t>
-  </si>
-  <si>
-    <t>我，酆都，在鸿钧成圣前立地府</t>
-  </si>
-  <si>
-    <t>网游：我的药剂永久持续</t>
-  </si>
-  <si>
-    <t>青梅是天命之女？可我既是天命！</t>
-  </si>
-  <si>
-    <t>我拿钱就走，九个姐姐全变病娇了</t>
-  </si>
-  <si>
-    <t>高武：看不起斩魄刀，流刃若火呢</t>
-  </si>
-  <si>
-    <t>楼层求生：从垃圾场开始变废为宝</t>
+    <t>女尊，独自抚养妹妹们的正太哥哥</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
   </si>
   <si>
     <t>我有一个女鬼催眠APP</t>
   </si>
   <si>
+    <t>崩铁，死了47次，我决定去卖</t>
+  </si>
+  <si>
+    <t>东北振兴，千万员工BUFF拉满</t>
+  </si>
+  <si>
     <t>大明：开局轩辕剑，朱允熥杀疯了</t>
   </si>
   <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>名义，汉东刘长生，谁与争锋！</t>
+    <t>四合院：从亮剑到人民的名义</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>玩弄感情的坏男孩就要被病娇狠狠</t>
   </si>
   <si>
     <t>女儿被诈两亿，天家千金遭曝光</t>
-  </si>
-  <si>
-    <t>婴儿开局，我的娘亲是画皮</t>
-  </si>
-  <si>
-    <t>狩猎北大荒：投亲路上遇到狼拦路</t>
-  </si>
-  <si>
-    <t>女尊，独自抚养妹妹们的正太哥哥</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>游戏入侵：我有一块剑骨头</t>
-  </si>
-  <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>天渊</t>
-  </si>
-  <si>
-    <t>灵气复苏：别装了，华夏真有仙！</t>
-  </si>
-  <si>
-    <t>东北振兴，千万员工BUFF拉满</t>
-  </si>
-  <si>
-    <t>开始万倍加速空间，芶在最强宗门</t>
-  </si>
-  <si>
-    <t>斯坦福留洋水货？不！给我再电斯</t>
-  </si>
-  <si>
-    <t>四合院：从亮剑到人民的名义</t>
-  </si>
-  <si>
-    <t>星空求生：开局虫族女皇钻我被窝</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>93.2</v>
+        <v>85</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1067000</v>
+        <v>1005000</v>
       </c>
       <c r="G5" s="7">
-        <v>32000</v>
+        <v>-62000</v>
       </c>
       <c r="H5" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="7">
-        <v>71538</v>
+        <v>62000</v>
       </c>
       <c r="J5" s="5">
-        <v>89.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>83.7</v>
+        <v>88.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>756000</v>
+        <v>690000</v>
       </c>
       <c r="G6" s="7">
-        <v>48000</v>
+        <v>74000</v>
       </c>
       <c r="H6" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I6" s="7">
-        <v>61625</v>
+        <v>77667</v>
       </c>
       <c r="J6" s="5">
-        <v>81.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,19 +832,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>157000</v>
+        <v>180000</v>
       </c>
       <c r="G7" s="7">
-        <v>21000</v>
+        <v>23000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>19500</v>
+        <v>20000</v>
       </c>
       <c r="J7" s="5">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>87.7</v>
+        <v>81.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>402000</v>
+        <v>790000</v>
       </c>
       <c r="G8" s="7">
-        <v>2000</v>
+        <v>34000</v>
       </c>
       <c r="H8" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I8" s="7">
-        <v>46167</v>
+        <v>58556</v>
       </c>
       <c r="J8" s="5">
-        <v>79.8</v>
+        <v>79.5</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>219000</v>
+        <v>409000</v>
       </c>
       <c r="G9" s="7">
-        <v>51000</v>
+        <v>7000</v>
       </c>
       <c r="H9" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I9" s="7">
-        <v>14143</v>
+        <v>40571</v>
       </c>
       <c r="J9" s="5">
-        <v>78.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>162000</v>
+        <v>268000</v>
       </c>
       <c r="G10" s="7">
-        <v>34000</v>
+        <v>15000</v>
       </c>
       <c r="H10" s="7">
         <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>15111</v>
+        <v>18000</v>
       </c>
       <c r="J10" s="5">
-        <v>78.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>88.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>616000</v>
+        <v>156000</v>
       </c>
       <c r="G11" s="7">
-        <v>71000</v>
+        <v>12000</v>
       </c>
       <c r="H11" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>79500</v>
+        <v>16667</v>
       </c>
       <c r="J11" s="5">
-        <v>77.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>96.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>253000</v>
+        <v>133000</v>
       </c>
       <c r="G12" s="7">
-        <v>21000</v>
+        <v>12000</v>
       </c>
       <c r="H12" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>18375</v>
+        <v>9000</v>
       </c>
       <c r="J12" s="5">
-        <v>77.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>93.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>227000</v>
+        <v>324000</v>
       </c>
       <c r="G13" s="7">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I13" s="7">
-        <v>18571</v>
+        <v>17364</v>
       </c>
       <c r="J13" s="5">
-        <v>75.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>92.5</v>
+        <v>91.5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>316000</v>
+        <v>231000</v>
       </c>
       <c r="G14" s="7">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="H14" s="7">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I14" s="7">
-        <v>18300</v>
+        <v>14000</v>
       </c>
       <c r="J14" s="5">
-        <v>75.5</v>
+        <v>73.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>90.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>226000</v>
+        <v>137000</v>
       </c>
       <c r="G15" s="7">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I15" s="7">
-        <v>18500</v>
+        <v>11222</v>
       </c>
       <c r="J15" s="5">
-        <v>74.3</v>
+        <v>73.8</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1120,28 +1120,30 @@
       <c r="A16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="5"/>
+      <c r="B16" s="5">
+        <v>9</v>
+      </c>
       <c r="C16" s="5">
-        <v>92.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>126000</v>
+        <v>151000</v>
       </c>
       <c r="G16" s="7">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>11250</v>
+        <v>14600</v>
       </c>
       <c r="J16" s="5">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1157,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>89.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>313000</v>
+        <v>237000</v>
       </c>
       <c r="G17" s="7">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="H17" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>15000</v>
+        <v>17429</v>
       </c>
       <c r="J17" s="5">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,23 +1190,23 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>92</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>124000</v>
+        <v>1761000</v>
       </c>
       <c r="G18" s="7">
-        <v>12000</v>
+        <v>29000</v>
       </c>
       <c r="H18" s="7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I18" s="7">
-        <v>10333</v>
+        <v>30278</v>
       </c>
       <c r="J18" s="5">
         <v>73.2</v>
@@ -1221,26 +1223,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>86.3</v>
+        <v>88.8</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>321000</v>
+        <v>237000</v>
       </c>
       <c r="G19" s="7">
-        <v>-4000</v>
+        <v>10000</v>
       </c>
       <c r="H19" s="7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I19" s="7">
-        <v>20357</v>
+        <v>17500</v>
       </c>
       <c r="J19" s="5">
-        <v>72.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1256,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>79.5</v>
+        <v>89.3</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>778000</v>
+        <v>321000</v>
       </c>
       <c r="G20" s="7">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I20" s="7">
-        <v>34125</v>
+        <v>14222</v>
       </c>
       <c r="J20" s="5">
-        <v>72.3</v>
+        <v>72.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1289,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>88.2</v>
+        <v>90</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>479000</v>
+        <v>149000</v>
       </c>
       <c r="G21" s="7">
-        <v>-1000</v>
+        <v>7000</v>
       </c>
       <c r="H21" s="7">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I21" s="7">
-        <v>15353</v>
+        <v>10364</v>
       </c>
       <c r="J21" s="5">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1322,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>81.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>1732000</v>
+        <v>1253000</v>
       </c>
       <c r="G22" s="7">
-        <v>-1000</v>
+        <v>80000</v>
       </c>
       <c r="H22" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I22" s="7">
-        <v>30353</v>
+        <v>17278</v>
       </c>
       <c r="J22" s="5">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1355,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.3</v>
+        <v>85</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>347000</v>
+        <v>313000</v>
       </c>
       <c r="G23" s="7">
-        <v>2000</v>
+        <v>-8000</v>
       </c>
       <c r="H23" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I23" s="7">
-        <v>14000</v>
+        <v>18467</v>
       </c>
       <c r="J23" s="5">
-        <v>72.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1388,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>88.3</v>
+        <v>87.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>1173000</v>
+        <v>251000</v>
       </c>
       <c r="G24" s="7">
-        <v>103000</v>
+        <v>4000</v>
       </c>
       <c r="H24" s="7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I24" s="7">
-        <v>13588</v>
+        <v>12111</v>
       </c>
       <c r="J24" s="5">
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1426,19 +1428,19 @@
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>178000</v>
+        <v>117000</v>
       </c>
       <c r="G25" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H25" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>10667</v>
+        <v>9667</v>
       </c>
       <c r="J25" s="5">
-        <v>71.5</v>
+        <v>71.2</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1454,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>89.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>107000</v>
+        <v>252000</v>
       </c>
       <c r="G26" s="7">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="H26" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I26" s="7">
-        <v>8000</v>
+        <v>11167</v>
       </c>
       <c r="J26" s="5">
-        <v>71.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1487,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>87.8</v>
+        <v>85.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>142000</v>
+        <v>189000</v>
       </c>
       <c r="G27" s="7">
-        <v>4000</v>
+        <v>27000</v>
       </c>
       <c r="H27" s="7">
         <v>11</v>
       </c>
       <c r="I27" s="7">
-        <v>10700</v>
+        <v>16300</v>
       </c>
       <c r="J27" s="5">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1525,19 +1527,19 @@
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>247000</v>
+        <v>203000</v>
       </c>
       <c r="G28" s="7">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="H28" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>13125</v>
+        <v>12143</v>
       </c>
       <c r="J28" s="5">
-        <v>70.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1553,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>86.8</v>
+        <v>87.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>195000</v>
+        <v>103000</v>
       </c>
       <c r="G29" s="7">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" s="7">
-        <v>12833</v>
+        <v>7375</v>
       </c>
       <c r="J29" s="5">
-        <v>70.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1586,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>88.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>152000</v>
+        <v>217000</v>
       </c>
       <c r="G30" s="7">
-        <v>4000</v>
+        <v>36000</v>
       </c>
       <c r="H30" s="7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I30" s="7">
-        <v>8133</v>
+        <v>5722</v>
       </c>
       <c r="J30" s="5">
-        <v>70.8</v>
+        <v>70</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1630,13 +1632,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="7">
-        <v>11222</v>
+        <v>10100</v>
       </c>
       <c r="J31" s="5">
-        <v>70.3</v>
+        <v>70</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1652,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>87.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>144000</v>
+        <v>111000</v>
       </c>
       <c r="G32" s="7">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="H32" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I32" s="7">
-        <v>17600</v>
+        <v>7500</v>
       </c>
       <c r="J32" s="5">
-        <v>70.3</v>
+        <v>69.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1681,30 +1683,28 @@
       <c r="A33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="5">
-        <v>9</v>
-      </c>
+      <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>93.8</v>
+        <v>90.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>137000</v>
+        <v>252000</v>
       </c>
       <c r="G33" s="7">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="H33" s="7">
         <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>14750</v>
+        <v>18000</v>
       </c>
       <c r="J33" s="5">
-        <v>70.3</v>
+        <v>69.3</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>84.2</v>
+        <v>85.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>255000</v>
+        <v>179000</v>
       </c>
       <c r="G34" s="7">
-        <v>-3000</v>
+        <v>1000</v>
       </c>
       <c r="H34" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I34" s="7">
-        <v>14692</v>
+        <v>9700</v>
       </c>
       <c r="J34" s="5">
-        <v>70</v>
+        <v>69.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>88.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>248000</v>
+        <v>128000</v>
       </c>
       <c r="G35" s="7">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I35" s="7">
-        <v>12600</v>
+        <v>9429</v>
       </c>
       <c r="J35" s="5">
-        <v>69.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>89.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>108000</v>
+        <v>250000</v>
       </c>
       <c r="G36" s="7">
-        <v>10000</v>
+        <v>-5000</v>
       </c>
       <c r="H36" s="7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I36" s="7">
-        <v>9800</v>
+        <v>13286</v>
       </c>
       <c r="J36" s="5">
-        <v>69.7</v>
+        <v>69.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>89.3</v>
+        <v>83.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>292000</v>
+        <v>455000</v>
       </c>
       <c r="G37" s="7">
-        <v>8000</v>
+        <v>-24000</v>
       </c>
       <c r="H37" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I37" s="7">
-        <v>1941</v>
+        <v>13167</v>
       </c>
       <c r="J37" s="5">
-        <v>69.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>85.5</v>
+        <v>82.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>147000</v>
+        <v>403000</v>
       </c>
       <c r="G38" s="7">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="H38" s="7">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I38" s="7">
-        <v>9700</v>
+        <v>14056</v>
       </c>
       <c r="J38" s="5">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>82.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>1361000</v>
+        <v>169000</v>
       </c>
       <c r="G39" s="7">
-        <v>23000</v>
+        <v>6000</v>
       </c>
       <c r="H39" s="7">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>16176</v>
+        <v>7167</v>
       </c>
       <c r="J39" s="5">
-        <v>69.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>83</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>379000</v>
+        <v>258000</v>
       </c>
       <c r="G40" s="7">
-        <v>24000</v>
+        <v>36000</v>
       </c>
       <c r="H40" s="7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>13471</v>
+        <v>34000</v>
       </c>
       <c r="J40" s="5">
-        <v>69</v>
+        <v>68.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>82.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>255000</v>
+        <v>1367000</v>
       </c>
       <c r="G41" s="7">
-        <v>-9000</v>
+        <v>6000</v>
       </c>
       <c r="H41" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I41" s="7">
-        <v>13923</v>
+        <v>15611</v>
       </c>
       <c r="J41" s="5">
-        <v>69</v>
+        <v>68.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89</v>
+        <v>82.3</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>121000</v>
+        <v>1154000</v>
       </c>
       <c r="G42" s="7">
-        <v>6000</v>
+        <v>22000</v>
       </c>
       <c r="H42" s="7">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I42" s="7">
-        <v>8400</v>
+        <v>12667</v>
       </c>
       <c r="J42" s="5">
-        <v>69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>83.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>373000</v>
+        <v>127000</v>
       </c>
       <c r="G43" s="7">
-        <v>24000</v>
+        <v>7000</v>
       </c>
       <c r="H43" s="7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I43" s="7">
-        <v>12562</v>
+        <v>7800</v>
       </c>
       <c r="J43" s="5">
-        <v>68.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>301000</v>
+        <v>329000</v>
       </c>
       <c r="G44" s="7">
-        <v>-22000</v>
+        <v>-18000</v>
       </c>
       <c r="H44" s="7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I44" s="7">
-        <v>13533</v>
+        <v>11333</v>
       </c>
       <c r="J44" s="5">
-        <v>68.7</v>
+        <v>68.3</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>86.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>156000</v>
+        <v>281000</v>
       </c>
       <c r="G45" s="7">
-        <v>4000</v>
+        <v>-20000</v>
       </c>
       <c r="H45" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I45" s="7">
-        <v>5235</v>
+        <v>11438</v>
       </c>
       <c r="J45" s="5">
-        <v>68.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>156000</v>
+        <v>121000</v>
       </c>
       <c r="G46" s="7">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="H46" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>5909</v>
+        <v>11750</v>
       </c>
       <c r="J46" s="5">
-        <v>68.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>83.3</v>
+        <v>86.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>257000</v>
+        <v>292000</v>
       </c>
       <c r="G47" s="7">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="H47" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I47" s="7">
-        <v>10588</v>
+        <v>1833</v>
       </c>
       <c r="J47" s="5">
-        <v>68.5</v>
+        <v>68</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>82.3</v>
+        <v>80.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>1132000</v>
+        <v>329000</v>
       </c>
       <c r="G48" s="7">
-        <v>23000</v>
+        <v>12000</v>
       </c>
       <c r="H48" s="7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I48" s="7">
-        <v>12118</v>
+        <v>14071</v>
       </c>
       <c r="J48" s="5">
-        <v>68.3</v>
+        <v>67.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>85</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>249000</v>
+        <v>455000</v>
       </c>
       <c r="G49" s="7">
-        <v>-5000</v>
+        <v>15000</v>
       </c>
       <c r="H49" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I49" s="7">
-        <v>6294</v>
+        <v>12722</v>
       </c>
       <c r="J49" s="5">
-        <v>68.3</v>
+        <v>67.7</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>81.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>440000</v>
+        <v>145000</v>
       </c>
       <c r="G50" s="7">
-        <v>19000</v>
+        <v>-2000</v>
       </c>
       <c r="H50" s="7">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I50" s="7">
-        <v>12588</v>
+        <v>8636</v>
       </c>
       <c r="J50" s="5">
-        <v>68.2</v>
+        <v>67.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>113000</v>
+        <v>537000</v>
       </c>
       <c r="G51" s="7">
-        <v>3000</v>
+        <v>-4000</v>
       </c>
       <c r="H51" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I51" s="7">
-        <v>4118</v>
+        <v>18611</v>
       </c>
       <c r="J51" s="5">
-        <v>68.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>82.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>183000</v>
+        <v>241000</v>
       </c>
       <c r="G52" s="7">
-        <v>1000</v>
+        <v>-16000</v>
       </c>
       <c r="H52" s="7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I52" s="7">
-        <v>9889</v>
+        <v>9111</v>
       </c>
       <c r="J52" s="5">
-        <v>68</v>
+        <v>67.3</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>78.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>541000</v>
+        <v>161000</v>
       </c>
       <c r="G53" s="7">
-        <v>-3000</v>
+        <v>8000</v>
       </c>
       <c r="H53" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I53" s="7">
-        <v>19941</v>
+        <v>3056</v>
       </c>
       <c r="J53" s="5">
-        <v>67.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>81.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>113000</v>
+        <v>223000</v>
       </c>
       <c r="G54" s="7">
-        <v>1000</v>
+        <v>-32000</v>
       </c>
       <c r="H54" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I54" s="7">
-        <v>12000</v>
+        <v>10643</v>
       </c>
       <c r="J54" s="5">
-        <v>67.7</v>
+        <v>67.2</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
